--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N678"/>
+  <dimension ref="A1:O679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,11 @@
           <t>설문문항</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>링크(DOI/URL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -560,6 +565,11 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -631,6 +641,11 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -699,6 +714,11 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -771,6 +791,11 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -842,6 +867,11 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -914,6 +944,11 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -986,6 +1021,11 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1060,6 +1100,11 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1129,6 +1174,11 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1201,6 +1251,11 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1275,6 +1330,11 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1344,6 +1404,11 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1414,6 +1479,11 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1487,6 +1557,11 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1560,6 +1635,11 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1634,6 +1714,11 @@
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1707,6 +1792,11 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1780,6 +1870,11 @@
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1853,6 +1948,11 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1926,6 +2026,11 @@
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1999,6 +2104,11 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2072,6 +2182,11 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2146,6 +2261,11 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2218,6 +2338,11 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2290,6 +2415,11 @@
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2361,6 +2491,11 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2433,6 +2568,11 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2504,6 +2644,11 @@
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2576,6 +2721,11 @@
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2649,6 +2799,11 @@
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2715,6 +2870,11 @@
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2788,6 +2948,11 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2861,6 +3026,11 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2934,6 +3104,11 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3007,6 +3182,11 @@
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3081,6 +3261,11 @@
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3155,6 +3340,11 @@
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3227,6 +3417,11 @@
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3298,6 +3493,11 @@
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3372,6 +3572,11 @@
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3445,6 +3650,11 @@
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3516,6 +3726,11 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3587,6 +3802,11 @@
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3653,6 +3873,11 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3725,6 +3950,11 @@
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3798,6 +4028,11 @@
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3872,6 +4107,11 @@
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3943,6 +4183,11 @@
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4014,6 +4259,11 @@
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4088,6 +4338,11 @@
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4160,6 +4415,11 @@
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4232,6 +4492,11 @@
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4306,6 +4571,11 @@
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4380,6 +4650,11 @@
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4451,6 +4726,11 @@
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4521,6 +4801,11 @@
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4595,6 +4880,11 @@
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4667,6 +4957,11 @@
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4738,6 +5033,11 @@
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4808,6 +5108,11 @@
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4880,6 +5185,11 @@
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4953,6 +5263,11 @@
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5025,6 +5340,11 @@
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5098,6 +5418,11 @@
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5169,6 +5494,11 @@
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5242,6 +5572,11 @@
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5315,6 +5650,11 @@
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5384,6 +5724,11 @@
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5455,6 +5800,11 @@
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5529,6 +5879,11 @@
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5601,6 +5956,11 @@
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5674,6 +6034,11 @@
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5744,6 +6109,11 @@
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5815,6 +6185,11 @@
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5889,6 +6264,11 @@
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5962,6 +6342,11 @@
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6033,6 +6418,11 @@
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6106,6 +6496,11 @@
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6180,6 +6575,11 @@
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6253,6 +6653,11 @@
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6321,6 +6726,11 @@
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6389,6 +6799,11 @@
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6461,6 +6876,11 @@
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6534,6 +6954,11 @@
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6604,6 +7029,11 @@
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6674,6 +7104,11 @@
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6745,6 +7180,11 @@
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6818,6 +7258,11 @@
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6889,6 +7334,11 @@
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6963,6 +7413,11 @@
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7032,6 +7487,11 @@
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7105,6 +7565,11 @@
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7176,6 +7641,11 @@
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7244,6 +7714,11 @@
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7320,6 +7795,11 @@
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7394,6 +7874,11 @@
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7462,6 +7947,11 @@
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7533,6 +8023,11 @@
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7605,6 +8100,11 @@
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7674,6 +8174,11 @@
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7748,6 +8253,11 @@
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7819,6 +8329,11 @@
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7888,6 +8403,11 @@
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7958,6 +8478,11 @@
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8029,6 +8554,11 @@
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8100,6 +8630,11 @@
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8171,6 +8706,11 @@
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8245,6 +8785,11 @@
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8313,6 +8858,11 @@
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8384,6 +8934,11 @@
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8456,6 +9011,11 @@
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8525,6 +9085,11 @@
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8595,6 +9160,11 @@
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8665,6 +9235,11 @@
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8734,6 +9309,11 @@
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8804,6 +9384,11 @@
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8874,6 +9459,11 @@
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8944,6 +9534,11 @@
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9015,6 +9610,11 @@
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9086,6 +9686,11 @@
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9158,6 +9763,11 @@
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9230,6 +9840,11 @@
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9304,6 +9919,11 @@
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9376,6 +9996,11 @@
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9447,6 +10072,11 @@
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9519,6 +10149,11 @@
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9590,6 +10225,11 @@
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -9662,6 +10302,11 @@
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9734,6 +10379,11 @@
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -9807,6 +10457,11 @@
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -9878,6 +10533,11 @@
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -9948,6 +10608,11 @@
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10019,6 +10684,11 @@
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10092,6 +10762,11 @@
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10167,6 +10842,11 @@
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10237,6 +10917,11 @@
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10306,6 +10991,11 @@
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10376,6 +11066,11 @@
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10445,6 +11140,11 @@
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -10514,6 +11214,11 @@
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10583,6 +11288,11 @@
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10655,6 +11365,11 @@
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10727,6 +11442,11 @@
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -10798,6 +11518,11 @@
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10872,6 +11597,11 @@
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -10941,6 +11671,11 @@
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11010,6 +11745,11 @@
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11079,6 +11819,11 @@
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -11149,6 +11894,11 @@
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -11219,6 +11969,11 @@
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -11289,6 +12044,11 @@
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -11359,6 +12119,11 @@
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -11429,6 +12194,11 @@
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -11497,6 +12267,11 @@
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -11566,6 +12341,11 @@
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -11637,6 +12417,11 @@
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -11707,6 +12492,11 @@
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -11777,6 +12567,11 @@
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -11846,6 +12641,11 @@
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -11915,6 +12715,11 @@
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -11985,6 +12790,11 @@
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -12055,6 +12865,11 @@
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -12126,6 +12941,11 @@
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -12196,6 +13016,11 @@
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -12264,6 +13089,11 @@
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -12334,6 +13164,11 @@
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -12405,6 +13240,11 @@
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -12477,6 +13317,11 @@
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -12547,6 +13392,11 @@
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -12618,6 +13468,11 @@
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -12687,6 +13542,11 @@
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -12757,6 +13617,11 @@
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -12827,6 +13692,11 @@
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -12898,6 +13768,11 @@
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -12968,6 +13843,11 @@
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -13039,6 +13919,11 @@
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -13109,6 +13994,11 @@
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -13179,6 +14069,11 @@
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -13250,6 +14145,11 @@
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -13319,6 +14219,11 @@
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -13388,6 +14293,11 @@
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -13456,6 +14366,11 @@
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -13524,6 +14439,11 @@
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -13593,6 +14513,11 @@
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -13662,6 +14587,11 @@
         </is>
       </c>
       <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -13732,6 +14662,11 @@
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -13802,6 +14737,11 @@
         </is>
       </c>
       <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -13872,6 +14812,11 @@
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -13942,6 +14887,11 @@
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -14011,6 +14961,11 @@
         </is>
       </c>
       <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -14080,6 +15035,11 @@
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -14151,6 +15111,11 @@
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -14220,6 +15185,11 @@
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -14290,6 +15260,11 @@
         </is>
       </c>
       <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -14360,6 +15335,11 @@
         </is>
       </c>
       <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -14429,6 +15409,11 @@
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -14506,6 +15491,11 @@
         </is>
       </c>
       <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -14581,6 +15571,11 @@
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -14651,6 +15646,11 @@
         </is>
       </c>
       <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -14726,6 +15726,11 @@
         </is>
       </c>
       <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -14795,6 +15800,11 @@
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -14866,6 +15876,11 @@
         </is>
       </c>
       <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -14937,6 +15952,11 @@
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -15007,6 +16027,11 @@
         </is>
       </c>
       <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -15079,6 +16104,11 @@
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -15149,6 +16179,11 @@
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -15218,6 +16253,11 @@
         </is>
       </c>
       <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -15287,6 +16327,11 @@
         </is>
       </c>
       <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -15356,6 +16401,11 @@
         </is>
       </c>
       <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -15426,6 +16476,11 @@
         </is>
       </c>
       <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -15497,6 +16552,11 @@
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -15569,6 +16629,11 @@
         </is>
       </c>
       <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -15639,6 +16704,11 @@
         </is>
       </c>
       <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -15708,6 +16778,11 @@
         </is>
       </c>
       <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -15778,6 +16853,11 @@
         </is>
       </c>
       <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -15848,6 +16928,11 @@
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -15923,6 +17008,11 @@
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -15992,6 +17082,11 @@
         </is>
       </c>
       <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -16064,6 +17159,11 @@
         </is>
       </c>
       <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -16133,6 +17233,11 @@
         </is>
       </c>
       <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -16203,6 +17308,11 @@
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -16273,6 +17383,11 @@
         </is>
       </c>
       <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -16344,6 +17459,11 @@
         </is>
       </c>
       <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -16413,6 +17533,11 @@
         </is>
       </c>
       <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -16482,6 +17607,11 @@
         </is>
       </c>
       <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -16558,6 +17688,11 @@
         </is>
       </c>
       <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -16628,6 +17763,11 @@
         </is>
       </c>
       <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -16696,6 +17836,11 @@
         </is>
       </c>
       <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -16767,6 +17912,11 @@
         </is>
       </c>
       <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -16838,6 +17988,11 @@
         </is>
       </c>
       <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -16905,6 +18060,11 @@
         </is>
       </c>
       <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -16974,6 +18134,11 @@
         </is>
       </c>
       <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -17043,6 +18208,11 @@
         </is>
       </c>
       <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -17114,6 +18284,11 @@
         </is>
       </c>
       <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -17188,6 +18363,11 @@
         </is>
       </c>
       <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -17257,6 +18437,11 @@
         </is>
       </c>
       <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -17329,6 +18514,11 @@
         </is>
       </c>
       <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -17401,6 +18591,11 @@
         </is>
       </c>
       <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -17471,6 +18666,11 @@
         </is>
       </c>
       <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -17541,6 +18741,11 @@
         </is>
       </c>
       <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -17614,6 +18819,11 @@
         </is>
       </c>
       <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -17683,6 +18893,11 @@
         </is>
       </c>
       <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -17753,6 +18968,11 @@
         </is>
       </c>
       <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -17822,6 +19042,11 @@
         </is>
       </c>
       <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -17891,6 +19116,11 @@
         </is>
       </c>
       <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -17959,6 +19189,11 @@
         </is>
       </c>
       <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -18030,6 +19265,11 @@
         </is>
       </c>
       <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -18101,6 +19341,11 @@
         </is>
       </c>
       <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -18174,6 +19419,11 @@
         </is>
       </c>
       <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -18246,6 +19496,11 @@
         </is>
       </c>
       <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -18316,6 +19571,11 @@
         </is>
       </c>
       <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -18388,6 +19648,11 @@
         </is>
       </c>
       <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -18459,6 +19724,11 @@
         </is>
       </c>
       <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -18528,6 +19798,11 @@
         </is>
       </c>
       <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -18597,6 +19872,11 @@
         </is>
       </c>
       <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -18665,6 +19945,11 @@
         </is>
       </c>
       <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -18735,6 +20020,11 @@
         </is>
       </c>
       <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -18805,6 +20095,11 @@
         </is>
       </c>
       <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -18874,6 +20169,11 @@
         </is>
       </c>
       <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -18944,6 +20244,11 @@
         </is>
       </c>
       <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -19014,6 +20319,11 @@
         </is>
       </c>
       <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -19083,6 +20393,11 @@
         </is>
       </c>
       <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -19152,6 +20467,11 @@
         </is>
       </c>
       <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -19224,6 +20544,11 @@
         </is>
       </c>
       <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -19296,6 +20621,11 @@
         </is>
       </c>
       <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -19366,6 +20696,11 @@
         </is>
       </c>
       <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -19435,6 +20770,11 @@
         </is>
       </c>
       <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -19505,6 +20845,11 @@
         </is>
       </c>
       <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -19575,6 +20920,11 @@
         </is>
       </c>
       <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -19646,6 +20996,11 @@
         </is>
       </c>
       <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -19719,6 +21074,11 @@
         </is>
       </c>
       <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -19790,6 +21150,11 @@
         </is>
       </c>
       <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -19860,6 +21225,11 @@
         </is>
       </c>
       <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -19932,6 +21302,11 @@
         </is>
       </c>
       <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -20002,6 +21377,11 @@
         </is>
       </c>
       <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -20072,6 +21452,11 @@
         </is>
       </c>
       <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -20143,6 +21528,11 @@
         </is>
       </c>
       <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -20214,6 +21604,11 @@
         </is>
       </c>
       <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -20285,6 +21680,11 @@
         </is>
       </c>
       <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -20356,6 +21756,11 @@
         </is>
       </c>
       <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -20426,6 +21831,11 @@
         </is>
       </c>
       <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -20496,6 +21906,11 @@
         </is>
       </c>
       <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -20566,6 +21981,11 @@
         </is>
       </c>
       <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -20636,6 +22056,11 @@
         </is>
       </c>
       <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -20707,6 +22132,11 @@
         </is>
       </c>
       <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -20775,6 +22205,11 @@
         </is>
       </c>
       <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -20846,6 +22281,11 @@
         </is>
       </c>
       <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -20919,6 +22359,11 @@
         </is>
       </c>
       <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -20990,6 +22435,11 @@
         </is>
       </c>
       <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -21061,6 +22511,11 @@
         </is>
       </c>
       <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -21130,6 +22585,11 @@
         </is>
       </c>
       <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -21201,6 +22661,11 @@
         </is>
       </c>
       <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -21272,6 +22737,11 @@
         </is>
       </c>
       <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -21343,6 +22813,11 @@
         </is>
       </c>
       <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -21415,6 +22890,11 @@
         </is>
       </c>
       <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -21485,6 +22965,11 @@
         </is>
       </c>
       <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -21554,6 +23039,11 @@
         </is>
       </c>
       <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -21627,6 +23117,11 @@
         </is>
       </c>
       <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -21696,6 +23191,11 @@
         </is>
       </c>
       <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -21766,6 +23266,11 @@
         </is>
       </c>
       <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -21836,6 +23341,11 @@
         </is>
       </c>
       <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -21905,6 +23415,11 @@
         </is>
       </c>
       <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -21975,6 +23490,11 @@
         </is>
       </c>
       <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -22044,6 +23564,11 @@
         </is>
       </c>
       <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -22111,6 +23636,11 @@
         </is>
       </c>
       <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -22181,6 +23711,11 @@
         </is>
       </c>
       <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -22253,6 +23788,11 @@
         </is>
       </c>
       <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -22322,6 +23862,11 @@
         </is>
       </c>
       <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -22393,6 +23938,11 @@
         </is>
       </c>
       <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -22463,6 +24013,11 @@
         </is>
       </c>
       <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -22532,6 +24087,11 @@
         </is>
       </c>
       <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -22601,6 +24161,11 @@
         </is>
       </c>
       <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -22671,6 +24236,11 @@
         </is>
       </c>
       <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -22740,6 +24310,11 @@
         </is>
       </c>
       <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -22808,6 +24383,11 @@
         </is>
       </c>
       <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -22881,6 +24461,11 @@
         </is>
       </c>
       <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -22951,6 +24536,11 @@
         </is>
       </c>
       <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -23021,6 +24611,11 @@
         </is>
       </c>
       <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -23093,6 +24688,11 @@
         </is>
       </c>
       <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -23163,6 +24763,11 @@
         </is>
       </c>
       <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -23237,6 +24842,11 @@
         </is>
       </c>
       <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -23307,6 +24917,11 @@
         </is>
       </c>
       <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -23377,6 +24992,11 @@
         </is>
       </c>
       <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -23447,6 +25067,11 @@
         </is>
       </c>
       <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -23515,6 +25140,11 @@
         </is>
       </c>
       <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -23584,6 +25214,11 @@
         </is>
       </c>
       <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -23654,6 +25289,11 @@
         </is>
       </c>
       <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -23725,6 +25365,11 @@
         </is>
       </c>
       <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -23795,6 +25440,11 @@
         </is>
       </c>
       <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -23865,6 +25515,11 @@
         </is>
       </c>
       <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -23935,6 +25590,11 @@
         </is>
       </c>
       <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -24007,6 +25667,11 @@
         </is>
       </c>
       <c r="N333" t="inlineStr"/>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -24077,6 +25742,11 @@
         </is>
       </c>
       <c r="N334" t="inlineStr"/>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -24145,6 +25815,11 @@
         </is>
       </c>
       <c r="N335" t="inlineStr"/>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -24216,6 +25891,11 @@
         </is>
       </c>
       <c r="N336" t="inlineStr"/>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -24287,6 +25967,11 @@
         </is>
       </c>
       <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -24362,6 +26047,11 @@
         </is>
       </c>
       <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -24435,6 +26125,11 @@
         </is>
       </c>
       <c r="N339" t="inlineStr"/>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -24505,6 +26200,11 @@
         </is>
       </c>
       <c r="N340" t="inlineStr"/>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -24576,6 +26276,11 @@
         </is>
       </c>
       <c r="N341" t="inlineStr"/>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -24644,6 +26349,11 @@
         </is>
       </c>
       <c r="N342" t="inlineStr"/>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -24714,6 +26424,11 @@
         </is>
       </c>
       <c r="N343" t="inlineStr"/>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -24786,6 +26501,11 @@
         </is>
       </c>
       <c r="N344" t="inlineStr"/>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -24853,6 +26573,11 @@
         </is>
       </c>
       <c r="N345" t="inlineStr"/>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -24922,6 +26647,11 @@
         </is>
       </c>
       <c r="N346" t="inlineStr"/>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -24992,6 +26722,11 @@
         </is>
       </c>
       <c r="N347" t="inlineStr"/>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -25064,6 +26799,11 @@
         </is>
       </c>
       <c r="N348" t="inlineStr"/>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -25135,6 +26875,11 @@
         </is>
       </c>
       <c r="N349" t="inlineStr"/>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -25204,6 +26949,11 @@
         </is>
       </c>
       <c r="N350" t="inlineStr"/>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -25273,6 +27023,11 @@
         </is>
       </c>
       <c r="N351" t="inlineStr"/>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -25343,6 +27098,11 @@
         </is>
       </c>
       <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -25412,6 +27172,11 @@
         </is>
       </c>
       <c r="N353" t="inlineStr"/>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -25482,6 +27247,11 @@
         </is>
       </c>
       <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -25554,6 +27324,11 @@
         </is>
       </c>
       <c r="N355" t="inlineStr"/>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -25622,6 +27397,11 @@
         </is>
       </c>
       <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -25691,6 +27471,11 @@
         </is>
       </c>
       <c r="N357" t="inlineStr"/>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -25760,6 +27545,11 @@
         </is>
       </c>
       <c r="N358" t="inlineStr"/>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -25829,6 +27619,11 @@
         </is>
       </c>
       <c r="N359" t="inlineStr"/>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -25896,6 +27691,11 @@
         </is>
       </c>
       <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -25965,6 +27765,11 @@
         </is>
       </c>
       <c r="N361" t="inlineStr"/>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -26035,6 +27840,11 @@
         </is>
       </c>
       <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -26105,6 +27915,11 @@
         </is>
       </c>
       <c r="N363" t="inlineStr"/>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -26177,6 +27992,11 @@
         </is>
       </c>
       <c r="N364" t="inlineStr"/>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -26248,6 +28068,11 @@
         </is>
       </c>
       <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -26318,6 +28143,11 @@
         </is>
       </c>
       <c r="N366" t="inlineStr"/>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -26388,6 +28218,11 @@
         </is>
       </c>
       <c r="N367" t="inlineStr"/>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -26459,6 +28294,11 @@
         </is>
       </c>
       <c r="N368" t="inlineStr"/>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -26529,6 +28369,11 @@
         </is>
       </c>
       <c r="N369" t="inlineStr"/>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -26598,6 +28443,11 @@
         </is>
       </c>
       <c r="N370" t="inlineStr"/>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -26669,6 +28519,11 @@
         </is>
       </c>
       <c r="N371" t="inlineStr"/>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -26742,6 +28597,11 @@
         </is>
       </c>
       <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -26815,6 +28675,11 @@
         </is>
       </c>
       <c r="N373" t="inlineStr"/>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -26890,6 +28755,11 @@
         </is>
       </c>
       <c r="N374" t="inlineStr"/>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -26960,6 +28830,11 @@
         </is>
       </c>
       <c r="N375" t="inlineStr"/>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -27031,6 +28906,11 @@
         </is>
       </c>
       <c r="N376" t="inlineStr"/>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -27101,6 +28981,11 @@
         </is>
       </c>
       <c r="N377" t="inlineStr"/>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -27171,6 +29056,11 @@
         </is>
       </c>
       <c r="N378" t="inlineStr"/>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -27239,6 +29129,11 @@
         </is>
       </c>
       <c r="N379" t="inlineStr"/>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -27309,6 +29204,11 @@
         </is>
       </c>
       <c r="N380" t="inlineStr"/>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -27379,6 +29279,11 @@
         </is>
       </c>
       <c r="N381" t="inlineStr"/>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -27449,6 +29354,11 @@
         </is>
       </c>
       <c r="N382" t="inlineStr"/>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -27519,6 +29429,11 @@
         </is>
       </c>
       <c r="N383" t="inlineStr"/>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -27588,6 +29503,11 @@
         </is>
       </c>
       <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -27657,6 +29577,11 @@
         </is>
       </c>
       <c r="N385" t="inlineStr"/>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -27725,6 +29650,11 @@
         </is>
       </c>
       <c r="N386" t="inlineStr"/>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -27795,6 +29725,11 @@
         </is>
       </c>
       <c r="N387" t="inlineStr"/>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -27865,6 +29800,11 @@
         </is>
       </c>
       <c r="N388" t="inlineStr"/>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -27935,6 +29875,11 @@
         </is>
       </c>
       <c r="N389" t="inlineStr"/>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -28005,6 +29950,11 @@
         </is>
       </c>
       <c r="N390" t="inlineStr"/>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -28075,6 +30025,11 @@
         </is>
       </c>
       <c r="N391" t="inlineStr"/>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -28145,6 +30100,11 @@
         </is>
       </c>
       <c r="N392" t="inlineStr"/>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -28214,6 +30174,11 @@
         </is>
       </c>
       <c r="N393" t="inlineStr"/>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -28283,6 +30248,11 @@
         </is>
       </c>
       <c r="N394" t="inlineStr"/>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -28352,6 +30322,11 @@
         </is>
       </c>
       <c r="N395" t="inlineStr"/>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -28422,6 +30397,11 @@
         </is>
       </c>
       <c r="N396" t="inlineStr"/>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -28492,6 +30472,11 @@
         </is>
       </c>
       <c r="N397" t="inlineStr"/>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -28562,6 +30547,11 @@
         </is>
       </c>
       <c r="N398" t="inlineStr"/>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -28632,6 +30622,11 @@
         </is>
       </c>
       <c r="N399" t="inlineStr"/>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -28702,6 +30697,11 @@
         </is>
       </c>
       <c r="N400" t="inlineStr"/>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -28771,6 +30771,11 @@
         </is>
       </c>
       <c r="N401" t="inlineStr"/>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -28841,6 +30846,11 @@
         </is>
       </c>
       <c r="N402" t="inlineStr"/>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -28911,6 +30921,11 @@
         </is>
       </c>
       <c r="N403" t="inlineStr"/>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -28980,6 +30995,11 @@
         </is>
       </c>
       <c r="N404" t="inlineStr"/>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -29049,6 +31069,11 @@
         </is>
       </c>
       <c r="N405" t="inlineStr"/>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -29119,6 +31144,11 @@
         </is>
       </c>
       <c r="N406" t="inlineStr"/>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -29188,6 +31218,11 @@
         </is>
       </c>
       <c r="N407" t="inlineStr"/>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -29258,6 +31293,11 @@
         </is>
       </c>
       <c r="N408" t="inlineStr"/>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -29328,6 +31368,11 @@
         </is>
       </c>
       <c r="N409" t="inlineStr"/>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -29397,6 +31442,11 @@
         </is>
       </c>
       <c r="N410" t="inlineStr"/>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -29467,6 +31517,11 @@
         </is>
       </c>
       <c r="N411" t="inlineStr"/>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -29536,6 +31591,11 @@
         </is>
       </c>
       <c r="N412" t="inlineStr"/>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -29605,6 +31665,11 @@
         </is>
       </c>
       <c r="N413" t="inlineStr"/>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -29673,6 +31738,11 @@
         </is>
       </c>
       <c r="N414" t="inlineStr"/>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -29743,6 +31813,11 @@
         </is>
       </c>
       <c r="N415" t="inlineStr"/>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -29813,6 +31888,11 @@
         </is>
       </c>
       <c r="N416" t="inlineStr"/>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -29883,6 +31963,11 @@
         </is>
       </c>
       <c r="N417" t="inlineStr"/>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -29953,6 +32038,11 @@
         </is>
       </c>
       <c r="N418" t="inlineStr"/>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -30023,6 +32113,11 @@
         </is>
       </c>
       <c r="N419" t="inlineStr"/>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -30092,6 +32187,11 @@
         </is>
       </c>
       <c r="N420" t="inlineStr"/>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -30162,6 +32262,11 @@
         </is>
       </c>
       <c r="N421" t="inlineStr"/>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -30232,6 +32337,11 @@
         </is>
       </c>
       <c r="N422" t="inlineStr"/>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -30302,6 +32412,11 @@
         </is>
       </c>
       <c r="N423" t="inlineStr"/>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -30370,6 +32485,11 @@
         </is>
       </c>
       <c r="N424" t="inlineStr"/>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -30440,6 +32560,11 @@
         </is>
       </c>
       <c r="N425" t="inlineStr"/>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -30510,6 +32635,11 @@
         </is>
       </c>
       <c r="N426" t="inlineStr"/>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -30579,6 +32709,11 @@
         </is>
       </c>
       <c r="N427" t="inlineStr"/>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -30649,6 +32784,11 @@
         </is>
       </c>
       <c r="N428" t="inlineStr"/>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -30719,6 +32859,11 @@
         </is>
       </c>
       <c r="N429" t="inlineStr"/>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -30789,6 +32934,11 @@
         </is>
       </c>
       <c r="N430" t="inlineStr"/>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -30859,6 +33009,11 @@
         </is>
       </c>
       <c r="N431" t="inlineStr"/>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -30929,6 +33084,11 @@
         </is>
       </c>
       <c r="N432" t="inlineStr"/>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -30999,6 +33159,11 @@
         </is>
       </c>
       <c r="N433" t="inlineStr"/>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -31070,6 +33235,11 @@
         </is>
       </c>
       <c r="N434" t="inlineStr"/>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -31140,6 +33310,11 @@
         </is>
       </c>
       <c r="N435" t="inlineStr"/>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -31210,6 +33385,11 @@
         </is>
       </c>
       <c r="N436" t="inlineStr"/>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -31277,6 +33457,11 @@
         </is>
       </c>
       <c r="N437" t="inlineStr"/>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -31347,6 +33532,11 @@
         </is>
       </c>
       <c r="N438" t="inlineStr"/>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -31417,6 +33607,11 @@
         </is>
       </c>
       <c r="N439" t="inlineStr"/>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -31487,6 +33682,11 @@
         </is>
       </c>
       <c r="N440" t="inlineStr"/>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -31557,6 +33757,11 @@
         </is>
       </c>
       <c r="N441" t="inlineStr"/>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -31627,6 +33832,11 @@
         </is>
       </c>
       <c r="N442" t="inlineStr"/>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -31697,6 +33907,11 @@
         </is>
       </c>
       <c r="N443" t="inlineStr"/>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -31767,6 +33982,11 @@
         </is>
       </c>
       <c r="N444" t="inlineStr"/>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -31836,6 +34056,11 @@
         </is>
       </c>
       <c r="N445" t="inlineStr"/>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -31906,6 +34131,11 @@
         </is>
       </c>
       <c r="N446" t="inlineStr"/>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -31975,6 +34205,11 @@
         </is>
       </c>
       <c r="N447" t="inlineStr"/>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -32044,6 +34279,11 @@
         </is>
       </c>
       <c r="N448" t="inlineStr"/>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -32113,6 +34353,11 @@
         </is>
       </c>
       <c r="N449" t="inlineStr"/>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -32182,6 +34427,11 @@
         </is>
       </c>
       <c r="N450" t="inlineStr"/>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -32252,6 +34502,11 @@
         </is>
       </c>
       <c r="N451" t="inlineStr"/>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -32321,6 +34576,11 @@
         </is>
       </c>
       <c r="N452" t="inlineStr"/>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -32388,6 +34648,11 @@
         </is>
       </c>
       <c r="N453" t="inlineStr"/>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -32455,6 +34720,11 @@
         </is>
       </c>
       <c r="N454" t="inlineStr"/>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -32524,6 +34794,11 @@
         </is>
       </c>
       <c r="N455" t="inlineStr"/>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -32594,6 +34869,11 @@
         </is>
       </c>
       <c r="N456" t="inlineStr"/>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -32664,6 +34944,11 @@
         </is>
       </c>
       <c r="N457" t="inlineStr"/>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -32733,6 +35018,11 @@
         </is>
       </c>
       <c r="N458" t="inlineStr"/>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -32803,6 +35093,11 @@
         </is>
       </c>
       <c r="N459" t="inlineStr"/>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -32872,6 +35167,11 @@
         </is>
       </c>
       <c r="N460" t="inlineStr"/>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -32942,6 +35242,11 @@
         </is>
       </c>
       <c r="N461" t="inlineStr"/>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -33012,6 +35317,11 @@
         </is>
       </c>
       <c r="N462" t="inlineStr"/>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -33081,6 +35391,11 @@
         </is>
       </c>
       <c r="N463" t="inlineStr"/>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -33150,6 +35465,11 @@
         </is>
       </c>
       <c r="N464" t="inlineStr"/>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -33219,6 +35539,11 @@
         </is>
       </c>
       <c r="N465" t="inlineStr"/>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -33289,6 +35614,11 @@
         </is>
       </c>
       <c r="N466" t="inlineStr"/>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -33358,6 +35688,11 @@
         </is>
       </c>
       <c r="N467" t="inlineStr"/>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -33427,6 +35762,11 @@
         </is>
       </c>
       <c r="N468" t="inlineStr"/>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -33497,6 +35837,11 @@
         </is>
       </c>
       <c r="N469" t="inlineStr"/>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -33567,6 +35912,11 @@
         </is>
       </c>
       <c r="N470" t="inlineStr"/>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -33637,6 +35987,11 @@
         </is>
       </c>
       <c r="N471" t="inlineStr"/>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -33707,6 +36062,11 @@
         </is>
       </c>
       <c r="N472" t="inlineStr"/>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -33777,6 +36137,11 @@
         </is>
       </c>
       <c r="N473" t="inlineStr"/>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -33846,6 +36211,11 @@
         </is>
       </c>
       <c r="N474" t="inlineStr"/>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -33917,6 +36287,11 @@
         </is>
       </c>
       <c r="N475" t="inlineStr"/>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -33984,6 +36359,11 @@
         </is>
       </c>
       <c r="N476" t="inlineStr"/>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -34054,6 +36434,11 @@
         </is>
       </c>
       <c r="N477" t="inlineStr"/>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -34123,6 +36508,11 @@
         </is>
       </c>
       <c r="N478" t="inlineStr"/>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -34193,6 +36583,11 @@
         </is>
       </c>
       <c r="N479" t="inlineStr"/>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -34263,6 +36658,11 @@
         </is>
       </c>
       <c r="N480" t="inlineStr"/>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -34333,6 +36733,11 @@
         </is>
       </c>
       <c r="N481" t="inlineStr"/>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -34403,6 +36808,11 @@
         </is>
       </c>
       <c r="N482" t="inlineStr"/>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -34473,6 +36883,11 @@
         </is>
       </c>
       <c r="N483" t="inlineStr"/>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -34543,6 +36958,11 @@
         </is>
       </c>
       <c r="N484" t="inlineStr"/>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -34613,6 +37033,11 @@
         </is>
       </c>
       <c r="N485" t="inlineStr"/>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -34682,6 +37107,11 @@
         </is>
       </c>
       <c r="N486" t="inlineStr"/>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -34751,6 +37181,11 @@
         </is>
       </c>
       <c r="N487" t="inlineStr"/>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -34820,6 +37255,11 @@
         </is>
       </c>
       <c r="N488" t="inlineStr"/>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -34889,6 +37329,11 @@
         </is>
       </c>
       <c r="N489" t="inlineStr"/>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -34959,6 +37404,11 @@
         </is>
       </c>
       <c r="N490" t="inlineStr"/>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -35030,6 +37480,11 @@
         </is>
       </c>
       <c r="N491" t="inlineStr"/>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -35101,6 +37556,11 @@
         </is>
       </c>
       <c r="N492" t="inlineStr"/>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -35173,6 +37633,11 @@
         </is>
       </c>
       <c r="N493" t="inlineStr"/>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -35243,6 +37708,11 @@
         </is>
       </c>
       <c r="N494" t="inlineStr"/>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -35313,6 +37783,11 @@
         </is>
       </c>
       <c r="N495" t="inlineStr"/>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -35383,6 +37858,11 @@
         </is>
       </c>
       <c r="N496" t="inlineStr"/>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -35452,6 +37932,11 @@
         </is>
       </c>
       <c r="N497" t="inlineStr"/>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -35522,6 +38007,11 @@
         </is>
       </c>
       <c r="N498" t="inlineStr"/>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -35592,6 +38082,11 @@
         </is>
       </c>
       <c r="N499" t="inlineStr"/>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -35662,6 +38157,11 @@
         </is>
       </c>
       <c r="N500" t="inlineStr"/>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -35732,6 +38232,11 @@
         </is>
       </c>
       <c r="N501" t="inlineStr"/>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -35802,6 +38307,11 @@
         </is>
       </c>
       <c r="N502" t="inlineStr"/>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -35871,6 +38381,11 @@
         </is>
       </c>
       <c r="N503" t="inlineStr"/>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -35941,6 +38456,11 @@
         </is>
       </c>
       <c r="N504" t="inlineStr"/>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -36010,6 +38530,11 @@
         </is>
       </c>
       <c r="N505" t="inlineStr"/>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -36080,6 +38605,11 @@
         </is>
       </c>
       <c r="N506" t="inlineStr"/>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -36150,6 +38680,11 @@
         </is>
       </c>
       <c r="N507" t="inlineStr"/>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -36220,6 +38755,11 @@
         </is>
       </c>
       <c r="N508" t="inlineStr"/>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -36290,6 +38830,11 @@
         </is>
       </c>
       <c r="N509" t="inlineStr"/>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -36360,6 +38905,11 @@
         </is>
       </c>
       <c r="N510" t="inlineStr"/>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -36430,6 +38980,11 @@
         </is>
       </c>
       <c r="N511" t="inlineStr"/>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -36500,6 +39055,11 @@
         </is>
       </c>
       <c r="N512" t="inlineStr"/>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -36570,6 +39130,11 @@
         </is>
       </c>
       <c r="N513" t="inlineStr"/>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -36640,6 +39205,11 @@
         </is>
       </c>
       <c r="N514" t="inlineStr"/>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -36710,6 +39280,11 @@
         </is>
       </c>
       <c r="N515" t="inlineStr"/>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -36780,6 +39355,11 @@
         </is>
       </c>
       <c r="N516" t="inlineStr"/>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -36850,6 +39430,11 @@
         </is>
       </c>
       <c r="N517" t="inlineStr"/>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -36920,6 +39505,11 @@
         </is>
       </c>
       <c r="N518" t="inlineStr"/>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -36989,6 +39579,11 @@
         </is>
       </c>
       <c r="N519" t="inlineStr"/>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -37059,6 +39654,11 @@
         </is>
       </c>
       <c r="N520" t="inlineStr"/>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -37128,6 +39728,11 @@
         </is>
       </c>
       <c r="N521" t="inlineStr"/>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -37198,6 +39803,11 @@
         </is>
       </c>
       <c r="N522" t="inlineStr"/>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -37268,6 +39878,11 @@
         </is>
       </c>
       <c r="N523" t="inlineStr"/>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -37337,6 +39952,11 @@
         </is>
       </c>
       <c r="N524" t="inlineStr"/>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -37407,6 +40027,11 @@
         </is>
       </c>
       <c r="N525" t="inlineStr"/>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -37477,6 +40102,11 @@
         </is>
       </c>
       <c r="N526" t="inlineStr"/>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -37547,6 +40177,11 @@
         </is>
       </c>
       <c r="N527" t="inlineStr"/>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -37617,6 +40252,11 @@
         </is>
       </c>
       <c r="N528" t="inlineStr"/>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -37688,6 +40328,11 @@
         </is>
       </c>
       <c r="N529" t="inlineStr"/>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -37758,6 +40403,11 @@
         </is>
       </c>
       <c r="N530" t="inlineStr"/>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -37828,6 +40478,11 @@
         </is>
       </c>
       <c r="N531" t="inlineStr"/>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -37898,6 +40553,11 @@
         </is>
       </c>
       <c r="N532" t="inlineStr"/>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -37970,6 +40630,11 @@
         </is>
       </c>
       <c r="N533" t="inlineStr"/>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -38042,6 +40707,11 @@
         </is>
       </c>
       <c r="N534" t="inlineStr"/>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -38114,6 +40784,11 @@
         </is>
       </c>
       <c r="N535" t="inlineStr"/>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -38183,6 +40858,11 @@
         </is>
       </c>
       <c r="N536" t="inlineStr"/>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -38255,6 +40935,11 @@
         </is>
       </c>
       <c r="N537" t="inlineStr"/>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -38327,6 +41012,11 @@
         </is>
       </c>
       <c r="N538" t="inlineStr"/>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -38399,6 +41089,11 @@
         </is>
       </c>
       <c r="N539" t="inlineStr"/>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -38469,6 +41164,11 @@
         </is>
       </c>
       <c r="N540" t="inlineStr"/>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -38539,6 +41239,11 @@
         </is>
       </c>
       <c r="N541" t="inlineStr"/>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -38609,6 +41314,11 @@
         </is>
       </c>
       <c r="N542" t="inlineStr"/>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -38679,6 +41389,11 @@
         </is>
       </c>
       <c r="N543" t="inlineStr"/>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -38749,6 +41464,11 @@
         </is>
       </c>
       <c r="N544" t="inlineStr"/>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -38819,6 +41539,11 @@
         </is>
       </c>
       <c r="N545" t="inlineStr"/>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -38889,6 +41614,11 @@
         </is>
       </c>
       <c r="N546" t="inlineStr"/>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -38959,6 +41689,11 @@
         </is>
       </c>
       <c r="N547" t="inlineStr"/>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -39029,6 +41764,11 @@
         </is>
       </c>
       <c r="N548" t="inlineStr"/>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -39098,6 +41838,11 @@
         </is>
       </c>
       <c r="N549" t="inlineStr"/>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -39168,6 +41913,11 @@
         </is>
       </c>
       <c r="N550" t="inlineStr"/>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -39237,6 +41987,11 @@
         </is>
       </c>
       <c r="N551" t="inlineStr"/>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -39306,6 +42061,11 @@
         </is>
       </c>
       <c r="N552" t="inlineStr"/>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -39375,6 +42135,11 @@
         </is>
       </c>
       <c r="N553" t="inlineStr"/>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -39445,6 +42210,11 @@
         </is>
       </c>
       <c r="N554" t="inlineStr"/>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -39515,6 +42285,11 @@
         </is>
       </c>
       <c r="N555" t="inlineStr"/>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -39585,6 +42360,11 @@
         </is>
       </c>
       <c r="N556" t="inlineStr"/>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -39654,6 +42434,11 @@
         </is>
       </c>
       <c r="N557" t="inlineStr"/>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -39724,6 +42509,11 @@
         </is>
       </c>
       <c r="N558" t="inlineStr"/>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -39794,6 +42584,11 @@
         </is>
       </c>
       <c r="N559" t="inlineStr"/>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -39864,6 +42659,11 @@
         </is>
       </c>
       <c r="N560" t="inlineStr"/>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -39935,6 +42735,11 @@
         </is>
       </c>
       <c r="N561" t="inlineStr"/>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -40005,6 +42810,11 @@
         </is>
       </c>
       <c r="N562" t="inlineStr"/>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -40076,6 +42886,11 @@
         </is>
       </c>
       <c r="N563" t="inlineStr"/>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -40147,6 +42962,11 @@
         </is>
       </c>
       <c r="N564" t="inlineStr"/>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -40217,6 +43037,11 @@
         </is>
       </c>
       <c r="N565" t="inlineStr"/>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -40287,6 +43112,11 @@
         </is>
       </c>
       <c r="N566" t="inlineStr"/>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -40357,6 +43187,11 @@
         </is>
       </c>
       <c r="N567" t="inlineStr"/>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -40427,6 +43262,11 @@
         </is>
       </c>
       <c r="N568" t="inlineStr"/>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -40496,6 +43336,11 @@
         </is>
       </c>
       <c r="N569" t="inlineStr"/>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -40567,6 +43412,11 @@
         </is>
       </c>
       <c r="N570" t="inlineStr"/>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -40637,6 +43487,11 @@
         </is>
       </c>
       <c r="N571" t="inlineStr"/>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -40707,6 +43562,11 @@
         </is>
       </c>
       <c r="N572" t="inlineStr"/>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -40777,6 +43637,11 @@
         </is>
       </c>
       <c r="N573" t="inlineStr"/>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -40847,6 +43712,11 @@
         </is>
       </c>
       <c r="N574" t="inlineStr"/>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -40917,6 +43787,11 @@
         </is>
       </c>
       <c r="N575" t="inlineStr"/>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -40987,6 +43862,11 @@
         </is>
       </c>
       <c r="N576" t="inlineStr"/>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -41057,6 +43937,11 @@
         </is>
       </c>
       <c r="N577" t="inlineStr"/>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -41127,6 +44012,11 @@
         </is>
       </c>
       <c r="N578" t="inlineStr"/>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -41197,6 +44087,11 @@
         </is>
       </c>
       <c r="N579" t="inlineStr"/>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -41267,6 +44162,11 @@
         </is>
       </c>
       <c r="N580" t="inlineStr"/>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -41337,6 +44237,11 @@
         </is>
       </c>
       <c r="N581" t="inlineStr"/>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -41407,6 +44312,11 @@
         </is>
       </c>
       <c r="N582" t="inlineStr"/>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -41477,6 +44387,11 @@
         </is>
       </c>
       <c r="N583" t="inlineStr"/>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -41547,6 +44462,11 @@
         </is>
       </c>
       <c r="N584" t="inlineStr"/>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -41617,6 +44537,11 @@
         </is>
       </c>
       <c r="N585" t="inlineStr"/>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -41687,6 +44612,11 @@
         </is>
       </c>
       <c r="N586" t="inlineStr"/>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -41752,6 +44682,11 @@
         </is>
       </c>
       <c r="N587" t="inlineStr"/>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -41822,6 +44757,11 @@
         </is>
       </c>
       <c r="N588" t="inlineStr"/>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -41892,6 +44832,11 @@
         </is>
       </c>
       <c r="N589" t="inlineStr"/>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -41962,6 +44907,11 @@
         </is>
       </c>
       <c r="N590" t="inlineStr"/>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -42032,6 +44982,11 @@
         </is>
       </c>
       <c r="N591" t="inlineStr"/>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -42102,6 +45057,11 @@
         </is>
       </c>
       <c r="N592" t="inlineStr"/>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -42173,6 +45133,11 @@
         </is>
       </c>
       <c r="N593" t="inlineStr"/>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -42244,6 +45209,11 @@
         </is>
       </c>
       <c r="N594" t="inlineStr"/>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -42315,6 +45285,11 @@
         </is>
       </c>
       <c r="N595" t="inlineStr"/>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -42386,6 +45361,11 @@
         </is>
       </c>
       <c r="N596" t="inlineStr"/>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -42457,6 +45437,11 @@
         </is>
       </c>
       <c r="N597" t="inlineStr"/>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -42528,6 +45513,11 @@
         </is>
       </c>
       <c r="N598" t="inlineStr"/>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -42598,6 +45588,11 @@
         </is>
       </c>
       <c r="N599" t="inlineStr"/>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -42668,6 +45663,11 @@
         </is>
       </c>
       <c r="N600" t="inlineStr"/>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -42738,6 +45738,11 @@
         </is>
       </c>
       <c r="N601" t="inlineStr"/>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -42808,6 +45813,11 @@
         </is>
       </c>
       <c r="N602" t="inlineStr"/>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -42878,6 +45888,11 @@
         </is>
       </c>
       <c r="N603" t="inlineStr"/>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -42948,6 +45963,11 @@
         </is>
       </c>
       <c r="N604" t="inlineStr"/>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -43018,6 +46038,11 @@
         </is>
       </c>
       <c r="N605" t="inlineStr"/>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -43087,6 +46112,11 @@
         </is>
       </c>
       <c r="N606" t="inlineStr"/>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -43156,6 +46186,11 @@
         </is>
       </c>
       <c r="N607" t="inlineStr"/>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -43226,6 +46261,11 @@
         </is>
       </c>
       <c r="N608" t="inlineStr"/>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -43296,6 +46336,11 @@
         </is>
       </c>
       <c r="N609" t="inlineStr"/>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -43366,6 +46411,11 @@
         </is>
       </c>
       <c r="N610" t="inlineStr"/>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -43436,6 +46486,11 @@
         </is>
       </c>
       <c r="N611" t="inlineStr"/>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -43505,6 +46560,11 @@
         </is>
       </c>
       <c r="N612" t="inlineStr"/>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -43575,6 +46635,11 @@
         </is>
       </c>
       <c r="N613" t="inlineStr"/>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -43645,6 +46710,11 @@
         </is>
       </c>
       <c r="N614" t="inlineStr"/>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -43715,6 +46785,11 @@
         </is>
       </c>
       <c r="N615" t="inlineStr"/>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -43785,6 +46860,11 @@
         </is>
       </c>
       <c r="N616" t="inlineStr"/>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -43855,6 +46935,11 @@
         </is>
       </c>
       <c r="N617" t="inlineStr"/>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -43925,6 +47010,11 @@
         </is>
       </c>
       <c r="N618" t="inlineStr"/>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -43995,6 +47085,11 @@
         </is>
       </c>
       <c r="N619" t="inlineStr"/>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -44065,6 +47160,11 @@
         </is>
       </c>
       <c r="N620" t="inlineStr"/>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -44135,6 +47235,11 @@
         </is>
       </c>
       <c r="N621" t="inlineStr"/>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -44205,6 +47310,11 @@
         </is>
       </c>
       <c r="N622" t="inlineStr"/>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -44275,6 +47385,11 @@
         </is>
       </c>
       <c r="N623" t="inlineStr"/>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -44345,6 +47460,11 @@
         </is>
       </c>
       <c r="N624" t="inlineStr"/>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -44415,6 +47535,11 @@
         </is>
       </c>
       <c r="N625" t="inlineStr"/>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -44486,6 +47611,11 @@
         </is>
       </c>
       <c r="N626" t="inlineStr"/>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -44556,6 +47686,11 @@
         </is>
       </c>
       <c r="N627" t="inlineStr"/>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -44626,6 +47761,11 @@
         </is>
       </c>
       <c r="N628" t="inlineStr"/>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -44696,6 +47836,11 @@
         </is>
       </c>
       <c r="N629" t="inlineStr"/>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -44766,6 +47911,11 @@
         </is>
       </c>
       <c r="N630" t="inlineStr"/>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -44836,6 +47986,11 @@
         </is>
       </c>
       <c r="N631" t="inlineStr"/>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -44907,6 +48062,11 @@
         </is>
       </c>
       <c r="N632" t="inlineStr"/>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -44977,6 +48137,11 @@
         </is>
       </c>
       <c r="N633" t="inlineStr"/>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -45047,6 +48212,11 @@
         </is>
       </c>
       <c r="N634" t="inlineStr"/>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -45117,6 +48287,11 @@
         </is>
       </c>
       <c r="N635" t="inlineStr"/>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -45189,6 +48364,11 @@
         </is>
       </c>
       <c r="N636" t="inlineStr"/>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -45261,6 +48441,11 @@
         </is>
       </c>
       <c r="N637" t="inlineStr"/>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -45331,6 +48516,11 @@
         </is>
       </c>
       <c r="N638" t="inlineStr"/>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -45401,6 +48591,11 @@
         </is>
       </c>
       <c r="N639" t="inlineStr"/>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -45471,6 +48666,11 @@
         </is>
       </c>
       <c r="N640" t="inlineStr"/>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -45541,6 +48741,11 @@
         </is>
       </c>
       <c r="N641" t="inlineStr"/>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -45611,6 +48816,11 @@
         </is>
       </c>
       <c r="N642" t="inlineStr"/>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -45681,6 +48891,11 @@
         </is>
       </c>
       <c r="N643" t="inlineStr"/>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -45752,6 +48967,11 @@
         </is>
       </c>
       <c r="N644" t="inlineStr"/>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -45822,6 +49042,11 @@
         </is>
       </c>
       <c r="N645" t="inlineStr"/>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -45892,6 +49117,11 @@
         </is>
       </c>
       <c r="N646" t="inlineStr"/>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -45962,6 +49192,11 @@
         </is>
       </c>
       <c r="N647" t="inlineStr"/>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -46032,6 +49267,11 @@
         </is>
       </c>
       <c r="N648" t="inlineStr"/>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -46102,6 +49342,11 @@
         </is>
       </c>
       <c r="N649" t="inlineStr"/>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -46172,6 +49417,11 @@
         </is>
       </c>
       <c r="N650" t="inlineStr"/>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -46242,6 +49492,11 @@
         </is>
       </c>
       <c r="N651" t="inlineStr"/>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -46313,6 +49568,11 @@
         </is>
       </c>
       <c r="N652" t="inlineStr"/>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -46384,6 +49644,11 @@
         </is>
       </c>
       <c r="N653" t="inlineStr"/>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -46453,6 +49718,11 @@
         </is>
       </c>
       <c r="N654" t="inlineStr"/>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -46522,6 +49792,11 @@
         </is>
       </c>
       <c r="N655" t="inlineStr"/>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -46593,6 +49868,11 @@
         </is>
       </c>
       <c r="N656" t="inlineStr"/>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -46664,6 +49944,11 @@
         </is>
       </c>
       <c r="N657" t="inlineStr"/>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -46737,6 +50022,11 @@
         </is>
       </c>
       <c r="N658" t="inlineStr"/>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -46810,6 +50100,11 @@
         </is>
       </c>
       <c r="N659" t="inlineStr"/>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -46883,6 +50178,11 @@
         </is>
       </c>
       <c r="N660" t="inlineStr"/>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -46956,6 +50256,11 @@
         </is>
       </c>
       <c r="N661" t="inlineStr"/>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -47026,6 +50331,11 @@
         </is>
       </c>
       <c r="N662" t="inlineStr"/>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -47096,6 +50406,11 @@
         </is>
       </c>
       <c r="N663" t="inlineStr"/>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -47166,6 +50481,11 @@
         </is>
       </c>
       <c r="N664" t="inlineStr"/>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -47233,6 +50553,11 @@
         </is>
       </c>
       <c r="N665" t="inlineStr"/>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -47303,6 +50628,11 @@
         </is>
       </c>
       <c r="N666" t="inlineStr"/>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -47373,6 +50703,11 @@
         </is>
       </c>
       <c r="N667" t="inlineStr"/>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -47443,6 +50778,11 @@
         </is>
       </c>
       <c r="N668" t="inlineStr"/>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -47514,6 +50854,11 @@
         </is>
       </c>
       <c r="N669" t="inlineStr"/>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -47585,6 +50930,11 @@
         </is>
       </c>
       <c r="N670" t="inlineStr"/>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -47656,6 +51006,11 @@
         </is>
       </c>
       <c r="N671" t="inlineStr"/>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -47726,6 +51081,11 @@
         </is>
       </c>
       <c r="N672" t="inlineStr"/>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -47796,6 +51156,11 @@
         </is>
       </c>
       <c r="N673" t="inlineStr"/>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -47866,6 +51231,11 @@
         </is>
       </c>
       <c r="N674" t="inlineStr"/>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -47936,6 +51306,11 @@
         </is>
       </c>
       <c r="N675" t="inlineStr"/>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -48006,6 +51381,11 @@
         </is>
       </c>
       <c r="N676" t="inlineStr"/>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -48111,6 +51491,11 @@
 - 신경증 (Neuroticism - Big Five Inventory; BFI; Benet-Martínez &amp; John, 1998): 5점 척도 (1 = strongly disagree ~ 5 = strongly agree), 8문항</t>
         </is>
       </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -48212,6 +51597,89 @@
 - 브랜드 충성도 (Brand Loyalty): How strong and loyal a preference you feel for BRAND? (해당 브랜드에 대해 얼마나 강하고 충성도 높은 선호도를 느끼십니까?)</t>
         </is>
       </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>678</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Ziwei Ji, Nayeon Lee, Rita Frieske, Tiezheng Yu, Dan Su, Yan Xu, Etsuko Ishii, Yejin Bang, Delong Chen, Wenliang Dai, Ho Shu Chan, Andrea Madotto, Pascale Fung</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Survey of Hallucination in Natural Language Generation</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>ACM Computing Surveys</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>자연어 생성(NLG)에서의 환각 현상(Hallucination Concept), 트랜스포머 기반 언어 모델 및 시퀀스 투 시퀀스(Seq2Seq) 딥러닝 이론</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>[원인 요인 (데이터 불일치, 학습 및 추론 편향)] -&gt; [환각 유형 (내재적 환각, 외재적 환각)] -&gt; [평가 지표 및 완화 기법 적용]</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>N/A (본 논문은 자연어 생성 분야의 환각 현상에 관한 종합 문헌 고찰 논문으로, 실증적 연구 가설을 설정하거나 검증하지 않음)</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>데이터 요인(소소-참조 이탈, 정제되지 않은 데이터), 학습 및 추론 요인(불완전한 표현 학습, 디코딩 오류, 노출 편향, 파라미터 지식 편향)</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>자연어 생성(NLG) 모델의 환각 발생 (내재적 환각: Intrinsic Hallucination, 외재적 환각: Extrinsic Hallucination)</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>태스크별 유형 (요약, 대화 생성, 생성형 질의응답, 데이터-텍스트 생성, 기계번역, 비전-언어 생성 등)</t>
+        </is>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>1. 환각은 소스 텍스트와 모순되는 '내재적 환각'과 소스에서 검증할 수 없는 '외재적 환각'으로 분류됨.
+2. 환각의 주원인은 데이터 수집 과정에서의 소스-참조 불일치와 신경망 모델의 디코딩 전략, 노출 편향, 파라미터 지식 우선 반영임.
+3. 전통적인 ROUGE, BLEU 등의 지표는 환각 측정에 한계가 있어 통계적 지표(PARENT 등), 모델 기반 지표(IE, QA, NLI 활용), 인간 평가 등이 활용됨.
+4. 데이터 정제 및 증강, 아키텍처 개선(인코더/디코더/어텐션 변경), 제어된 생성, 강화학습, 후처리 기법 등을 통해 환각을 완화할 수 있음.</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>N/A (본 논문은 컴퓨터 과학 및 자연어 처리 분야의 종합 서베이(Survey) 논문으로, 설문 조사 및 측정 문항을 포함하지 않음)</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2202.03629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O679"/>
+  <dimension ref="A1:O680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51681,6 +51681,88 @@
         </is>
       </c>
     </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>679</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Alexander Chernev</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>When More Is Less and Less Is More: The Role of Ideal Point Availability and Assortment in Consumer Choice</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Journal of Consumer Research</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>구성적 선호 관점 (Constructive View of Preferences), 정보 과부하 이론 (Cognitive Overload Theory), 인지부조화 이론 (Cognitive Dissonance Theory)</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>[Product Assortment Size] x [Ideal Point Availability] -&gt; [Preference Strength / Choice Confidence / Switching Propensity / Decision Difficulty]</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>H1: The availability of an articulated ideal point moderates the impact of assortment on consumer preferences. (명확히 표현된 이상점의 이용가능성은 제품 구색이 소비자 선호에 미치는 영향을 조절할 것이다.)
+H2: When choosing from a larger assortment, consumers with an available ideal point are likely to have stronger preferences for the chosen option than consumers without an available ideal attribute combination. (대형 구색에서 선택할 때, 이상점을 이용할 수 있는 소비자는 이상적 속성 조합을 이용할 수 없는 소비자보다 선택한 대안에 대해 더 강한 선호를 가질 것이다.)
+H3: When choosing from a smaller assortment, consumers with an available ideal point are likely to have weaker preferences for the chosen option than consumers without an available ideal attribute combination. (소형 구색에서 선택할 때, 이상점을 이용할 수 있는 소비자는 이상적 속성 조합을 이용할 수 없는 소비자보다 선택한 대안에 대해 더 약한 선호를 가질 것이다.)</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>제품 구색 크기 (Product Assortment Size: Small vs. Large)</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>선호의 강도 (Preference Strength: 전환 행동/의도 Switching Propensity, 결정 확신도 Decision Confidence, 결정 난이도 Decision Difficulty)</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>이상점 이용가능성 (Ideal Point Availability)</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>제품 구색의 크기가 소비자의 선택 선호 강도에 미치는 영향은 이상점(Ideal Point)의 이용가능성에 의해 조절된다. 대형 구색에서 선택할 때 이상점이 명확히 형성된 소비자는 선택에 대한 확신이 높고 다른 대안으로 전환할 가능성이 낮아 선호 강도가 강화되었으나, 소형 구색에서는 이상점이 형성된 소비자가 구색 내에서 완전한 일치 대안을 찾지 못해 선호 강도가 오히려 약화되는 경향을 보였다.</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>Think about your ideal chocolate. Indicate the most attractive level of each of the attributes describing the choice alternatives and rank order these attributes. / 당신의 이상적인 초콜릿에 대해 생각해보십시오. 선택 대안들을 설명하는 각 속성의 가장 매력적인 수준을 표시하고 이 속성들의 순위를 매기십시오.
+Imagine that you are buying a sofa. Think about what your ideal sofa looks like (e.g., in terms of color, upholstery, back height, cushion softness). Please, describe your ideal sofa in the space below. / 소파를 구매한다고 가정해 보십시오. 당신의 이상적인 소파가 어떤 모습일지 생각해 보십시오(예: 색상, 천/가죽 재질, 등받이 높이, 쿠션의 폭신함 측면에서). 아래 공간에 당신의 이상적인 소파를 기술해 주십시오.
+Choose between a small box containing two chocolates of the exact same kind that you selected in the preceding choice task and a small box containing two of the most popular chocolates from the entire Godiva collection. / 이전 선택 과제에서 선택한 것과 정확히 동일한 종류의 초콜릿 2개가 들어있는 작은 상자와 전체 고디바 컬렉션 중 가장 인기 있는 초콜릿 2개가 들어있는 작은 상자 중 하나를 선택하십시오.
+Imagine that you have to choose between the sofa you just selected and a sofa that has been recommended by the sales associate. Which one would you buy? / 방금 선택한 소파와 판매 직원이 추천한 소파 중에서 선택해야 한다고 가정해 보십시오. 당신은 어떤 것을 구매하시겠습니까?
+How would you rate your confidence that you will actually like the sofa [product] you selected? / 당신이 선택한 소파[제품]를 실제로 마음에 들어 할 것이라는 확신을 어떻게 평가하시겠습니까?
+How would you rate the difficulty of this decision for you? / 이 결정이 당신에게 얼마나 어려웠는지 평가해주십시오.</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>10.1086/376808</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O680"/>
+  <dimension ref="A1:O681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51763,6 +51763,189 @@
         </is>
       </c>
     </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>680</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>박경아</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>지능형 자동차의 지속이용의도에 영향을 미치는 요인에 관한 연구: 확장된 통합기술수용모형(UTAUT2)과 기술준비도를 적용</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>기업과혁신연구</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>확장된 통합기술수용모형(UTAUT2), 기술준비도(TRI)</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>[독립변수: 성과기대, 노력기대, 사회적 영향, 촉진조건, 쾌락적 동기, 가격효용성, 습관적 이용, 낙관성, 혁신성, 불편감, 불안감] -&gt; [종속변수: 지속이용의도]</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>가설 1: 성과기대는 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 2: 노력기대는 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 3: 사회적 영향은 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 4: 촉진조건은 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 5: 쾌락적 동기는 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 6: 가격효용성은 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 7: 습관적 이용은 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 8: 낙관성은 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 9: 혁신성은 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 10: 불편감은 지속이용의도에 유의미한 영향을 미칠 것이다.
+가설 11: 불안성은 지속이용의도에 유의미한 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>성과기대, 노력기대, 사회적 영향, 촉진조건, 쾌락적 동기, 가격효용성, 습관적 이용, 낙관성, 혁신성, 불편감, 불안감</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>지속이용의도</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>1. UTAUT2 요인 중 사회적 영향(β=0.102, p&lt;0.05), 쾌락적 동기(β=0.311, p&lt;0.01), 가격효용성(β=0.185, p&lt;0.01)은 지능형 자동차의 지속이용의도에 유의미한 정(+)의 영향을 미쳤다. 영향력의 크기는 쾌락적 동기, 가격효용성, 사회적 영향 순으로 크게 나타났다.
+2. 성과기대, 노력기대, 촉진조건, 습관적 이용은 지속이용의도에 유의미한 영향을 미치지 않아 기각되었다.
+3. 기술준비도(TRI) 요인 중 긍정적 차원인 낙관성(β=0.221, p&lt;0.01)과 혁신성(β=0.138, p&lt;0.01)은 지속이용의도에 유의미한 정(+)의 영향을 미쳤다.
+4. 부정적 기술준비도 차원인 불편감과 불안감은 지속이용의도에 통계적으로 유의미한 영향을 미치지 않았다.</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>[성과기대]
+- Using intelligent vehicles provides convenience in my daily life.
+(지능형 자동차 이용은 일상생활에 편의를 제공한다.)
+- Using intelligent vehicles improves my work efficiency.
+(지능형 자동차 이용은 업무 능률을 향상시킨다.)
+- Using intelligent vehicles is useful in my daily life.
+(지능형 자동차 이용은 일상생활에 유용하다.)
+[노력기대]
+- Intelligent vehicles are easy to learn.
+(지능형 자동차는 배우기 쉽다.)
+- Intelligent vehicles are easy to understand.
+(지능형 자동차는 이해하기 쉽다.)
+- Intelligent vehicles are easy to use.
+(지능형 자동차는 이용하기 쉽다.)
+- It is easy to become skillful at using intelligent vehicles.
+(지능형 자동차를 능숙하게 이용하기 쉽다.)
+[사회적 영향]
+- People around me support my use of intelligent vehicles.
+(주변 사람들은 지능형 자동차 이용을 지지한다.)
+- People who are important to me influence my use of intelligent vehicles.
+(나에게 중요한 사람의 영향으로 지능형 자동차를 이용하고 있다.)
+- People around me think I should use intelligent vehicles.
+(주변 사람들은 내가 지능형 자동차를 이용해야 한다고 생각한다.)
+[촉진조건]
+- I have the knowledge necessary to use intelligent vehicles.
+(지능형 자동차를 이용하는데 필요한 지식을 가지고 있다.)
+- I have the technical support available to use intelligent vehicles.
+(지능형 자동차를 이용하기 위한 기술적 지원을 가지고 있다.)
+- Intelligent vehicles interact with other systems to provide routine utility.
+(지능형 자동차는 다른 시스템과 상호호환되어 일상적 활용을 제공한다.)
+- I can get help from others when using intelligent vehicles.
+(지능형 자동차 이용 중 다른 사람의 도움을 받을 수 있다.)
+[쾌락적 동기]
+- Using intelligent vehicles is fun.
+(지능형 자동차 이용은 재미있다.)
+- Using intelligent vehicles is enjoyable.
+(지능형 자동차 이용은 즐겁다.)
+- Using intelligent vehicles is interesting.
+(지능형 자동차 이용은 흥미롭다.)
+[가격효용성]
+- The cost associated with using intelligent vehicles is reasonable.
+(지능형 자동차 이용에 따른 비용은 합리적이다.)
+- Intelligent vehicles provide better value than the cost incurred.
+(지능형 자동차는 지출된 비용보다 더 나은 가치를 제공해준다.)
+- The satisfaction derived from using intelligent vehicles outweighs the cost.
+(지능형 자동차 이용에 드는 비용보다 느끼는 만족이 크다.)
+[습관적 이용]
+- Using intelligent vehicles comes naturally to me.
+(지능형 자동차를 이용하는 것은 자연스럽다.)
+- I am addicted to using intelligent vehicles.
+(지능형 자동차 이용에 중독되어 있다.)
+- I must use intelligent vehicles.
+(지능형 자동차를 꼭 이용해야 한다.)
+[낙관성]
+- Using new technology (intelligent vehicles) gives me freedom of mobility.
+(새로운 기술(지능형 자동차) 이용으로 이동의 자유가 생겼다.)
+- New technology (intelligent vehicles) allows me to control my daily life better.
+(새로운 기술(지능형 자동차)은 일상생활을 잘 통제할 수 있다.)
+- Using new technology (intelligent vehicles) is much more convenient.
+(새로운 기술(지능형 자동차) 이용은 훨씬 사용하기 편하다.)
+- Using new technology (intelligent vehicles) lets me handle tasks efficiently.
+(새로운 기술(지능형 자동차) 이용은 일을 효율적으로 처리하게 한다.)
+[혁신성]
+- I follow trends in new technology (intelligent vehicles) areas of interest.
+(새로운 기술(지능형 자동차)의 관심분야에 대한 동향을 살핀다.)
+- Among my peers, I am usually the first to use new technology (intelligent vehicles).
+(새로운 기술(지능형 자동차)을 동료들 중 먼저 사용하는 편이다.)
+- I understand new technology (intelligent vehicles) without help from others.
+(새로운 기술(지능형 자동차)을 다른 사람 도움없이 이해한다.)
+- I enjoy attempting to understand new technology (intelligent vehicles).
+(새로운 기술(지능형 자동차)을 이해하고자 하는 시도를 즐긴다.)
+[불편감]
+- New technology (intelligent vehicles) is not designed for use by the general public.
+(새로운 기술(지능형 자동차)은 일반인들의 사용을 고려하지 않았다.)
+- New technology (intelligent vehicles) is inconvenient when receiving technical support.
+(새로운 기술(지능형 자동차)은 기술지원 받을 때 불편하다.)
+- New technology (intelligent vehicles) uses hard-to-understand terms that are not helpful.
+(새로운 기술(지능형 자동차)은 이해하기 어려운 용어로 도움이 되지 않는다.)
+- When using new technology (intelligent vehicles), complex and diverse features are inconvenient.
+(새로운 기술(지능형 자동차)을 이용할 때 복잡하고 다양한 기능이 불편하다.)
+[불안감]
+- I think new technology (intelligent vehicles) is not safe.
+(새로운 기술(지능형 자동차)은 안전하지 못하다고 생각한다.)
+- I think information from new technology (intelligent vehicles) may not be accurate.
+(새로운 기술(지능형 자동차)의 정보는 정확하지 않을 수 있다고 생각한다.)
+- I worry about my personal information provided to new technology (intelligent vehicles).
+(새로운 기술(지능형 자동차)에 제공된 나의 정보가 걱정된다.)
+- I recheck information from new technology (intelligent vehicles) through documents, etc.
+(새로운 기술(지능형 자동차)의 정보를 문서 등으로 다시 확인한다.)
+[지속이용의도]
+- I intend to continuously use intelligent vehicles.
+(지능형 자동차를 지속적으로 이용할 것이다.)
+- I will frequently use various functions of intelligent vehicles.
+(지능형 자동차의 여러 기능을 자주 이용할 것이다.)
+- I will recommend various functions of intelligent vehicles to others.
+(지능형 자동차의 여러 기능을 타인에게 추천할 것이다.)</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>http://dx.doi.org/10.22778/jci.2023.46.2.45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O681"/>
+  <dimension ref="A1:O682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51946,6 +51946,95 @@
         </is>
       </c>
     </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>681</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>신명옥, 이윤경, 김비아</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>조절초점과 정보제시방식이 다중속성 및 다중대안 대상의 선택에 미치는 영향 (The Effect of Regulatory Focus and The Information Presentation Method on Choice of Multi-attribute and Multi-alternative Items)</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>한국심리학회지 : 인지 및 생물</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>조절초점이론 (Regulatory Focus Theory), 조절부합이론 (Regulatory-Fit Theory)</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>[독립변수: 조절초점 (향상초점 vs. 예방초점) x 정보제시방식 (대안기반 vs. 속성기반)] x [선택대상 유형: 다중속성 vs. 다중대안] -&gt; [종속변수: 선택의 질, 선택 만족도]</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>H1-1: 다중속성인 대상을 선택할 때, 예방초점이면서 정보를 속성기반 방식으로 제시하면 우수한 선택을 한다.
+H1-2: 다중대안인 대상을 선택할 때, 향상초점이면서 정보를 대안기반 방식으로 제시하면 우수한 선택을 한다.
+H2-1: 다중속성인 대상을 선택할 때, 정보를 속성기반방식으로 제시하면 우수한 선택을 한다.
+H2-2: 다중대안인 대상을 선택할 때, 정보를 대안기반방식으로 제시하면 우수한 선택을 한다.</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>조절초점(향상초점, 예방초점), 정보제시방식(대안기반방식, 속성기반방식), 선택대상 특징(다중속성 대상, 다중대안 대상)</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>선택의 질(Quality of Choice), 선택 만족도(Satisfaction of Choice)</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>1. 다중속성 대상(노트북)의 경우, 조절초점과 관계없이 속성기반 방식으로 정보가 제시되었을 때 인지 부하 감소 효과로 인해 참가자들의 선택의 질이 유의하게 높았습니다 (H2-1 지지).
+2. 다중대안 대상(우산)의 경우, 향상초점 참가자에게 대안기반 방식으로 정보를 제시했을 때 조절부합도 효과가 나타나 선택의 질이 유의하게 높았습니다 (H1-2 지지).
+3. 객관적 지표인 '선택의 질'과 주관적 지표인 '선택 만족도' 간의 유의한 상관관계는 나타나지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>How often do you accomplish things that get you 'psyched' to work even harder?
+(당신은 열정적으로 할 만큼 흥분되는 어떤 일을 얼마나 자주 합니까?)
+Did you get on your parents' nerves often when you were growing up?
+(당신은 성장과정에서 부모님이 반대할 만한 행동들을 했습니까?)
+I often think about how I will achieve academic success.
+(나는 종종 어떻게 학업적 성공을 이루어 낼지 생각한다.)
+I often imagine bad things happening to me that I dread.
+(나는 종종 내가 두려워하는 나쁜 일들이 나한테 일어나는 상상을 한다.)
+How do you feel about your choice?
+(당신은 자신의 선택에 대해 어떻게 생각하십니까?)</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>10.22172/cogbio.2025.37.1.003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -51413,29 +51413,29 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>이문화 적응 이론(Berry's Acculturation Model), 이중문화 정체성 통합 이론(Bicultural Identity Integration Theory), 이중문화 역량 및 교체 모형(Alternation Model of Bicultural Competence)</t>
+          <t>문화적응 이론(Acculturation Theory), 이문화 정체성 통합 이론(Bicultural Identity Integration Framework), 교대 모델(Alternation Model of Second-Culture Acquisition)</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>[Bicultural Identity Integration (BII), Cultural Identification, Bilingualism, Acculturative Stress] -&gt; (Covariates: Neuroticism, Self-Efficacy, Demographics) -&gt; [Psychological Adjustment]</t>
+          <t>[이문화 정체성(BII, 문화적 정체성), 이중언어 능력 및 사용, 문화적응 스트레스] -&gt; [심리적 적응] (통제변수: 신경증, 자기효능감 / 조절변수: 문화적 맥락 및 집단 유형)</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>H1: 영구 이민자(Study 1)의 경우, 도구적인 언어 능력 변수보다 수용 문화에 대한 동일시 및 이중문화 정체성 통합(BII)이 심리적 적응을 더 강력하게 긍정적으로 예측할 것이다.
-H2: 일시 체류 노동자(Study 2)의 경우, 이중문화 정체성 변수보다 수용 문화의 언어 능력(중국어 및 영어 능력)이 심리적 적응을 더 강력하게 긍정적으로 예측할 것이다.
-H3: 세계화에 기반한 다수 집단(Study 3, 대학생)의 경우, 언어 능력보다 이중문화 정체성 변수(BII 등)가 심리적 적응의 중요한 예측 요인이 될 것이며, 거주 지역(홍콩 vs. 중국 본토)의 다문화 환경 수준에 따라 문화적응 스트레스의 영향력이 조절될 것이다.</t>
+          <t>H1: 이민자 집단에서는 언어 능력보다 수용 문화 정체성 및 이문화 정체성 통합(BII)이 심리적 적응을 더 유의하게 정적으로 예측할 것이다.
+H2: 일시 체류 근로자 집단에서는 정체성 변수보다 수용 문화의 언어 능력이 심리적 적응을 더 유의하게 정적으로 예측할 것이다.
+H3: 세계화 기반 문화적응을 겪는 본토 다수자 대학생 집단에서는 언어 능력보다 이문화 정체성 변수(BII)가 심리적 적응을 더 잘 예측할 것이다.</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>이중문화 정체성 통합(Bicultural Identity Integration; BII), 문화 동일시(출신 문화/수용 문화/서구 문화 동일시), 이중언어 능력 및 사용도(Bilingual Proficiency &amp; Usage), 문화적응 스트레스(Acculturative Stress)</t>
+          <t>이문화 정체성 통합(Bicultural Identity Integration, BII), 문화적 정체성(모국 및 수용/서구 문화 정체성), 이중언어 숙달도 및 사용량(Bilingual Proficiency and Usage), 문화적응 스트레스(Acculturative Stress)</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>심리적 적응 (Psychological Adjustment: 자아존중감, 삶의 만족도, 주관적 행복감, 우울[역코딩], 불안[역코딩], 외로움[역코딩]의 표준화 복합 점수)</t>
+          <t>심리적 적응(Psychological Adjustment: 자아존중감, 삶의 만족도, 주관적 행복감, 우울, 불안, 외로움의 복합 지표)</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
@@ -51445,55 +51445,55 @@
       </c>
       <c r="L677" t="inlineStr">
         <is>
-          <t>문화 집단/적응 맥락 유형 (이민자 vs. 소저너/일시 체류자 vs. 세계화 노출 다수 집단 / 홍콩 vs. 중국 본토)</t>
+          <t>문화적 맥락 및 유입 유형(이민자 vs. 일시 체류자 vs. 세계화 기반 다수자 / 홍콩 vs. 베이징)</t>
         </is>
       </c>
       <c r="M677" t="inlineStr">
         <is>
-          <t>1. 이민자(Study 1) 및 세계화 노출 대학생(Study 3)과 같은 장기 문화적응 집단에서는 신경증 및 자기효능감 통제 후에도 BII가 심리적 적응을 유의하게 정(+)으로 예측함.
-2. 일시 체류 가사도우미(Study 2)의 경우, 정체성 변수보다는 실제 기능적 과업 수행에 필요한 수용 언어 능력(영어 및 중국어 숙숙도/사용도)이 심리적 적응을 유의하게 정(+)으로 예측함.
-3. 문화적응 스트레스는 전반적으로 심리적 적응에 유의한 부(-)의 영향을 미쳤으며, 서구화 및 다문화 노출 역사가 상대적으로 짧은 중국 본토 학생들이 홍콩 학생들에 비해 문화적응 스트레스의 부정적 영향을 더 강하게 받음(상호작용 유의).</t>
+          <t>1. 이문화 정체성 통합(BII)은 신경증과 자기효능감 등 개격 특성을 통제한 후에도 이민자 및 대학생 집단의 심리적 적응을 정적으로 예측했습니다(단, 일시 체류자 제외).
+2. 일시 체류 근로자(필리핀 가사 노동자)의 경우 정체성 요인보다 실용적인 언어 능력(영어 및 중국어)이 심리적 적응에 유의한 정적 영향을 미쳤습니다.
+3. 문화적응 스트레스는 연구된 모든 집단에서 심리적 적응을 일관되게 부적으로 예측했습니다.</t>
         </is>
       </c>
       <c r="N677" t="inlineStr">
         <is>
-          <t>1. 언어 능력 및 사용도 (Language Proficiency and Usage; Benet-Martínez &amp; Haritatos, 2005)
-- 6점 척도 (언어 능력: 1 = very little ability ~ 6 = very high ability / 사용도: 1 = almost never ~ 6 = very often), 14문항
-- "Rate your overall Cantonese/Mandarin/English/Tagalog language ability" (전반적인 광둥어/표준중국어/영어/타갈로그어 능력을 평가해 주십시오)
-- "How much do you use/have used Cantonese to speak with your parents?" (부모님과 대화할 때 광둥어를 얼마나 사용합니까/사용했습니까?)
-- "How often do you watch TV shows/Movies in Cantonese?" (광둥어로 된 TV 프로그램이나 영화를 얼마나 자주 시청합니까?)
-2. 문화 동일시 (Cultural Identification; Benet-Martínez &amp; Haritatos, 2005)
-- 6점 척도 (1 = very weakly identified ~ 6 = highly identified), 2문항
-- "How much do you identify with mainland Chinese/Filipino culture?" (중국 본토/필리핀 문화에 얼마나 강하게 동일시합니까?)
-- "How much do you identify with Hong Kong/Western culture?" (홍콩/서구 문화에 얼마나 강하게 동일시합니까?)
-3. 이중문화 정체성 통합 척도 파일럿 버전 (Bicultural Identity Integration Scale—Pilot Version; BIIS-P; Benet-Martínez et al., 2002)
-- 양자택일형 4문항 (통합적 선택지 = 1점, 비통합적/갈등 선택지 = 2점, 역코딩 후 평균)
-- Item 1: "I don't feel caught between Hong Kong and Mainland Chinese cultures" vs. "I feel conflicted between the two cultures" (나는 홍콩 문화와 중국 본토 문화 사이에 끼어 있다고 느끼지 않는다 vs. 나는 두 문화 사이에서 갈등을 느낀다)
-- Item 2: "I feel as part of a combined culture" vs. "I feel as someone moving between the two cultures" (나는 결합된 문화의 일원이라고 느낀다 vs. 나는 두 문화 사이를 오가는 사람처럼 느낀다)
-- Item 3: "I feel Mainland-Hong Kong Chinese" vs. "I am just a Chinese living in Hong Kong" (나는 본토-홍콩계 중국인이라고 느낀다 vs. 나는 단지 홍콩에 거주하는 중국인일 뿐이다)
-- Item 4: "I combine both cultures" vs. "I keep both cultures separate" (나는 두 문화를 결합한다 vs. 나는 두 문화를 분리된 상태로 유지한다)
-4. 문화적응 스트레스 척도 (Riverside Acculturation Stress Inventory; RASI; Benet-Martínez &amp; Haritatos, 2005)
-- 5점 리커트 척도 (1 = strongly disagree ~ 5 = strongly agree), 5개 하위영역(언어, 직무, 이문화 관계, 차별, 거주환경) 15문항
-- "It's hard for me to perform well at work because of my lack of English skills." (영어 실력 부족으로 인해 직장에서 일을 잘해내기가 어렵다)
-- "Being misunderstood because of one's accent" (억양 때문에 오해를 받는다)
-- "Having to work harder than nonimmigrant/majority peers" (비이민자/다수자 동료들보다 더 열심히 일해야 한다)
-- "Having disagreements with others because of behaving in ways that are 'too ethnic' or 'too mainstream'" ('너무 민족적'이거나 '너무 주류적'으로 행동한다는 이유로 타인과 의견 충돌을 겪는다)
-- "Being mistreated because of one's ethnicity" (자신의 민족/인종적 배경 때문에 부당한 대우를 받는다)
-- "Living in an environment that is not culturally diverse" (문화적으로 다양하지 못한 환경에서 살고 있다)
-5. 심리적 적응 구성 하위 척도 (Psychological Adjustment Scales)
-- 자아존중감 (Rosenberg Self-Esteem Scale; Rosenberg, 1965): 5점 척도 (1 = strongly disagree ~ 5 = strongly agree), 10문항. 예: "On the whole, I am satisfied with myself" (전반적으로 나는 내 자신에게 만족한다)
-- 삶의 만족도 (Satisfaction With Life Scale; SWLS; Diener et al., 1985): 4점 척도 (1 = strongly disagree ~ 4 = strongly agree), 3문항. 예: "In most ways my life is close to my ideal" (대부분의 면에서 내 삶은 나의 이상에 가깝다)
-- 주관적 행복감 (Subjective Happiness Scale; Lyubomirsky &amp; Lepper, 1999): 7점 척도, 4문항. 예: "Some people are generally very happy. They enjoy life regardless of what is going on, getting the most out of everything. To what extent does this characterization describe you?" (어떤 사람들은 일반적으로 매우 행복하며 무슨 일이 일어나든 삶을 즐깁니다. 이러한 특성이 귀하를 얼마나 잘 설명합니까?)
-- 우울 및 불안 (SCL-90-R; Derogatis &amp; Melisaratos, 1983): 4점 척도 (1 = rarely or never ~ 4 = most of the time), 각 2문항. 예: 우울("feeling sad or depressed"), 불안("feeling fearful or anxious")
-- 외로움 (UCLA Loneliness Scale; Hays &amp; DiMatteo, 1987): 4점 척도 (1 = strongly disagree ~ 4 = strongly agree), 2문항 (고립감 및 사회적 접촉 결핍 측정)
-6. 통제 변수 측정 도구 (Covariates)
-- 일반적 자기효능감 (General Self-Efficacy Scale; Schwarzer, 1993): 4점 척도 (1 = strongly disagree ~ 4 = strongly agree), 10문항. 예: "I can always manage to solve difficult problems if I try hard enough" (충분히 노력한다면 나는 항상 어려운 문제를 해결해낼 수 있다)
-- 신경증 (Neuroticism - Big Five Inventory; BFI; Benet-Martínez &amp; John, 1998): 5점 척도 (1 = strongly disagree ~ 5 = strongly agree), 8문항</t>
+          <t>Rate your overall Cantonese language ability.
+(귀하의 전반적인 광둥어 능력을 평가해 주십시오.)
+How much do you use/have used Cantonese to speak with your parents?
+(귀하는 부모님과 대화할 때 광둥어를 얼마나 사용합니까/사용했습니까?)
+How often do you watch TV shows/Movies in Cantonese?
+(귀하는 광둥어로 된 TV 프로그램이나 영화를 얼마나 자주 시청합니까?)
+How much do you identify with mainland Chinese culture?
+(귀하는 중국 본토 문화와 얼마나 동일시합니까?)
+How much do you identify with Hong Kong culture?
+(귀하는 홍콩 문화와 얼마나 동일시합니까?)
+I don't feel caught between Hong Kong and Mainland Chinese cultures.
+(나는 홍콩 문화와 중국 본토 문화 사이에서 끼어있다고 느끼지 않는다.)
+I feel conflicted between the two cultures.
+(나는 두 문화 사이에서 갈등을 느낀다.)
+I feel as part of a combined culture.
+(나는 결합된 문화의 일원이라고 느낀다.)
+I feel as someone moving between the two cultures.
+(나는 두 문화 사이를 오가는 사람처럼 느낀다.)
+I combine both cultures.
+(나는 두 문화를 결합한다.)
+I keep both cultures separate.
+(나는 두 문화를 분리하여 유지한다.)
+It's hard for me to perform well at work because of my lack of English skills.
+(영어 실력이 부족해서 직장에서 업무를 잘 수행하기 어렵다.)
+In most ways my life is close to my ideal.
+(대부분의 면에서 나의 삶은 나의 이상에 가깝다.)
+Some people are generally very happy. They enjoy life regardless of what is going on, getting the most out of everything. To what extent does this characterization describe you?
+(어떤 사람들은 전반적으로 매우 행복합니다. 그들은 무슨 일이 일어나든 삶을 즐기며 모든 것에서 최선을 다합니다. 이 특성이 귀하를 얼마나 잘 설명합니까?)
+On the whole, I am satisfied with myself.
+(전반적으로 나는 나 자신에게 만족한다.)
+I can always manage to solve difficult problems if I try hard enough.
+(내가 충분히 노력한다면 항상 어려운 문제를 해결해 낼 수 있다.)</t>
         </is>
       </c>
       <c r="O677" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.1111/j.1467-6494.2008.00505.x</t>
         </is>
       </c>
     </row>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O682"/>
+  <dimension ref="A1:O683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52035,6 +52035,93 @@
         </is>
       </c>
     </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>682</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Wentao Zhang, Lingxuan Zhao, Haochong Xia, Shuo Sun, Jiaze Sun, Molei Qin, Xinyi Li, Yuqing Zhao, Yilei Zhao, Xinyu Cai, Longtao Zheng, Xinrun Wang, Bo An</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>A Multimodal Foundation Agent for Financial Trading: Tool-Augmented, Diversified, and Generalist</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Proceedings of the 30th ACM SIGKDD Conference on Knowledge Discovery and Data Mining (KDD '24)</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>마르코프 결정 과정(Markov Decision Process; MDP), 강화학습(Reinforcement Learning), 다중모달 대형언어모델(Multimodal LLM) 기반 에이전트 이론, 도구 증강 학습(Tool-Augmented Learning), 생각의 사슬(Chain-of-Thought; CoT) 추론</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>[다중모달 시장 정보 (텍스트, 가격, 시각 데이터) + 증강 도구 + 검색 메모리] -&gt; [시장 인텔리전스 모듈 &amp; 이중 수준 성찰 모듈 (저수준/고수준)] -&gt; [도구 증강 의사결정 모듈] -&gt; [금융 거래 성과 (수익률 및 위험 조절 지표)]</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>H1: FinAgent는 주식 및 암호화폐 시장에서 기존 최신(SOTA) 규칙 기반, 딥러닝/강화학습 및 LLM 기반 거래 모델보다 금융 거래 성과(수익률 및 위험 조절 지표)가 우수할 것이다.
+H2: 다중모달 시장 인텔리전스, 저수준 성찰, 고수준 성찰, 도구 증강 구성 요소를 통합할수록 에이전트의 거래 성과가 단계적으로 향상될 것이다.
+H3: 전문적인 투자 지침 및 기술적 지표 기반 증강 도구의 활용은 자산 특성과 일치할 때 거래 의사결정의 효과를 향상시킬 것이다.
+H4: 다각화된 메모리 검색(Diversified Retrieval) 시스템은 단일/일반 검색 방식 대비 정보 검색의 정밀도를 높이고 최종 거래 수익을 증가시킬 것이다.</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>FinAgent 프레임워크 요소 (다중모달 시장 인텔리전스 모듈, 이중 수준 성찰 모듈[저수준/고수준 성찰], 다각화된 메모리 검색 시스템, 도구 증강 의사결정 모듈)</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>금융 거래 성과 지표 (연간 수익률[ARR], 샤프 지수[SR], 최대 낙폭[MDD], 볼래틸리티[VOL], 칼마 지수[CR], 소티노 지수[SoR])</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>시장 통찰력 및 감성 분석, 가격 변동 인과 추론(저수준 성찰), 과거 거래 성공/실패 경험 성찰(고수준 성찰), 단계별 의사결정 추론 과정(CoT)</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>자산 유형/시장 환경(미국 주식 vs. 암호화폐), 투자자 위험 선호도(공격적 vs. 보수적), 보조 도구(전략)와 자산 시장의 상충성</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>1. FinAgent는 미국 주식(AAPL, AMZN, GOOGL, MSFT, TSLA) 및 암호화폐(ETHUSD) 등 6개 실물 금융 데이터셋에서 기존 12개 최신 비교 모델을 압도적으로 능가하며 평균 36% 이상의 수익률 향상을 달성함 (특히 TSLA 데이터셋에서 92.27% 연수익률 달성).
+2. 이중 수준 성찰 모듈(Low-level &amp; High-level Reflection)과 다각화된 검색 시스템은 마켓 노이즈를 감소시키고 가격 변동 패턴 및 과거 결정의 교훈을 효과적으로 학습하여 수익성을 크게 개선함.
+3. 주식에 특화된 보조 도구(규칙 기반 전략)를 변동성이 높고 거래 빈도가 다른 암호화폐 시장에 무분별하게 적용할 경우 성과가 감소할 수 있으므로, 자산 특성에 맞는 도구 선택이 중요함을 밝힘.</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Based on the above information, you should analyze the key insights and summarize the market intelligence.
+(상기 정보를 바탕으로 핵심 통찰을 분석하고 시장 인텔리전스를 요약해야 합니다.)
+Provide the detailed reasoning to determine how the above information led to the price movements.
+(상기 정보가 가격 변동으로 어떻게 이어졌는지 결정하기 위한 상세한 추론을 제공하세요.)
+Reflect on the decisions made at each time were right or wrong and give reasoning.
+(각 시점에 이루어진 결정이 맞았는지 틀렸는지 성찰하고 추론을 제공하세요.)
+You should step-by-step analyze above information and provide the reasoning for what you should BUY, SELL or HOLD on the asset.
+(상기 정보를 단계별로 분석하고 해당 자산에 대해 매수, 매도, 보유 중 무엇을 수행해야 하는지에 대한 추론을 제공해야 합니다.)</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>10.1145/3637528.3671801</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O683"/>
+  <dimension ref="A1:O684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52122,6 +52122,104 @@
         </is>
       </c>
     </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>683</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Corina Pelau, Stefana Pop, Ioana Ciofu</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Scenario-Based Approach to AI’s Agency to Perform Human-Specific Tasks</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Proceedings of the 18th International Conference on Business Excellence 2024</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>인간형상화 이론(Anthropomorphism Theory), 주체성 개념(Concept of Agency)</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>[AI의 의인화 특성(강함 vs. 약함) &amp; 성별] -&gt; [AI의 주체성 지각(정치, 종교, 정체성, 법적/도덕적 책임, 세계적 문제 해결 능력)]</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>H1: AI의 의인화 특성이 강할수록 인간 고유의 특성 및 주체성(Agency)을 더 크게 지각할 것이다.
+H2: 남성이 여성에 비해 AI에 주체성을 부여하는 경향이 더 강할 것이다.</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>AI의 의인화 특성(강함 vs. 약함), 성별(남성 vs. 여성)</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>AI의 주체성 지각(정치적 견해, 종교적/기도 능력, 정체성 보유, 실수에 대한 책임 및 처벌, 거시적 문제 해결 능력 등)</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>1. 의인화 특성이 강한 AI일수록 정치적 견해, 기도 능력, 정체성 보유 등 인간 고유의 주체성을 가진 것으로 지각될 가능성이 유의미하게 높음.
+2. 강한 의인화 특성을 가진 AI일수록 자신의 실수에 대해 책임을 져야 하고 투옥 등의 처벌을 받아야 한다고 인식함.
+3. 오염 감소, 세계 경제 안정, 세계 평화 보장과 같은 인류 공통의 대형 문제를 해결하는 능력에 대해서는 AI의 의인화 수준에 따른 유의미한 차이가 나타나지 않음.
+4. 여성보다 남성이 AI에 주체성을 부여하는 경향이 전반적으로 더 높게 나타남.</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>This AI may have political views
+(이 AI는 정치적 견해를 가질 수 있다.)
+This AI can pray
+(이 AI는 기도할 수 있다.)
+This AI has its identity
+(이 AI는 자신만의 정체성을 가지고 있다.)
+This AI should answer for its mistakes
+(이 AI는 자신의 실수에 대해 책임을 져야 한다.)
+This AI should be punished with imprisonment
+(이 AI는 감옥 수감 처벌을 받아야 한다.)
+This AI has the ability to reduce crime rates
+(이 AI는 범죄율을 줄이는 능력이 있다.)
+This AI has the ability to reduce pollution
+(이 AI는 오염을 줄이는 능력이 있다.)
+This AI has the ability to stabilize the world economy
+(이 AI는 세계 경제를 안정시킬 능력이 있다.)
+This AI has the ability to ensure world peace
+(이 AI는 세계 평화를 보장할 능력이 있다.)
+I feel safe in a robotic future
+(나는 로봇이 주도하는 미래에서 안전함을 느낀다.)</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>10.2478/picbe-2024-0195</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O684"/>
+  <dimension ref="A1:O685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52220,6 +52220,152 @@
         </is>
       </c>
     </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>684</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>이동엽, 김귀곤</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>디지털로 전환된 서비스의 지각된 상호작용이 기술수용의도에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>디지털융복합연구</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>기술수용모델 (Technology Acceptance Model, TAM)</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>[독립변수: 지각된 상호작용성 (지각된 커뮤니케이션, 지각된 제어, 지각된 반응성)] -&gt; [매개변수: 지각된 유용성, 지각된 사용용이성] -&gt; [종속변수: 사용의도] (조절변수: 디지털 격차)</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>H1: 디지털 전환 서비스의 지각된 상호작용성은 지각된 유용성에 정(+)의 영향을 미칠 것이다.
+H1-1: 지각된 커뮤니케이션은 지각된 유용성에 정(+)의 영향을 미칠 것이다.
+H1-2: 지각된 제어는 지각된 유용성에 정(+)의 영향을 미칠 것이다.
+H1-3: 지각된 반응성은 지각된 유용성에 정(+)의 영향을 미칠 것이다.
+H2: 디지털 전환 서비스의 지각된 상호작용성은 지각된 사용용이성에 정(+)의 영향을 미칠 것이다.
+H2-1: 지각된 커뮤니케이션은 지각된 사용용이성에 정(+)의 영향을 미칠 것이다.
+H2-2: 지각된 제어는 지각된 사용용이성에 정(+)의 영향을 미칠 것이다.
+H2-3: 지각된 반응성은 지각된 사용용이성에 정(+)의 영향을 미칠 것이다.
+H3: 지각된 유용성은 사용의도에 정(+)의 영향을 미칠 것이다.
+H4: 지각된 사용용이성은 사용의도에 정(+)의 영향을 미칠 것이다.
+H5: 지각된 상호작용성이 사용의도에 미치는 영향은 지각된 유용성에 의해 매개될 것이다.
+H6: 지각된 상호작용성이 사용의도에 미치는 영향은 지각된 사용용이성에 의해 매개될 것이다.
+H7: 지각된 상호작용성이 지각된 유용성을 통해 사용의도에 미치는 영향은 디지털 격차에 의해 부(-)적으로 조절될 것이다.</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>지각된 상호작용성 (지각된 커뮤니케이션, 지각된 제어, 지각된 반응성)</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>기술수용의도 (사용의도)</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>지각된 유용성, 지각된 사용용이성</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>디지털 격차</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>1. 디지털 전환 서비스의 지각된 상호작용성 세 요인(지각된 커뮤니케이션, 지각된 제어, 지각된 반응성)은 지각된 유용성과 지각된 사용용이성에 각각 정(+)의 영향을 미쳤습니다.
+2. 지각된 유용성과 지각된 사용용이성은 기술수용의도(사용의도)에 정(+)의 영향을 미쳤습니다.
+3. 지각된 상호작용 요인들과 사용의도 간의 관계에서 지각된 유용성과 지각된 사용용이성의 매개효과가 확인되었습니다.
+4. 지각된 유용성을 통한 상호작용성과 사용의도 간의 관계에서 디지털 격차의 음(-)의 조절된 매개효과가 검증되었습니다. 즉, 디지털 격차가 클수록 지각된 유용성이 사용의도로 이어지는 간접효과가 감소하거나 사라지는 것으로 나타났습니다.</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>[지각된 커뮤니케이션]
+Problem solving
+(문제 해결)
+Effective feedback
+(효과적인 피드백)
+Two-way communication
+(쌍방향 커뮤니케이션)
+[지각된 제어]
+Knows to use
+(사용 방법을 알고 있음)
+Know clearly
+(명확하게 알고 있음)
+Choose freely
+(자유롭게 선택함)
+Control over user experience
+(사용자 경험을 통제함)
+[지각된 반응성]
+Quickly
+(신속함)
+Very fast
+(매우 빠름)
+Get instantaneous information
+(즉각적인 정보를 제공받음)
+[지각된 유용성]
+Improves performance
+(성과를 향상시킴)
+Increases productivity
+(생산성을 증대시킴)
+Enhances effectiveness
+(효율성을 증진시킴)
+[지각된 사용용이성]
+Clear and understandable
+(명확하고 이해하기 쉬움)
+Not require a lot of effort
+(많은 노력이 필요하지 않음)
+Easy to use
+(사용하기 쉬움)
+Find easy
+(이용하기 용이함을 깨달음)
+[사용의도]
+Continue using
+(지속적으로 사용함)
+Try to use
+(사용하려고 시도함)
+Plan to continue to use
+(계속 사용할 계획임)
+[디지털 격차]
+Opportunities for using DTS
+(디지털 전환 서비스 이용 기회)
+Hours of use
+(사용 시간)
+Opportunities to connect
+(접속 기회)
+Access to information
+(정보 접근성)
+Processing power
+(정보 처리 능력)</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.14400/JDC.2021.19.11.287</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O685"/>
+  <dimension ref="A1:O694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52366,6 +52366,1183 @@
         </is>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>685</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>LI HUIYING (이혜영)</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>FOMO와 SNS 이용동기가 사용자 만족도 및 지속사용의향에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>서울시립대학교 대학원 경영학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), 사용과 충족 이론(Uses and Gratifications Theory), 기대확인이론(Expectation Confirmation Theory)</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>[IV: FOMO(소속욕구, 외적동기)] -&gt; [Mediator: SNS 만족도] -&gt; [DV: SNS 지속사용의도], [Moderator: SNS 이용동기(사회적 연결, 지식추구, 오락추구)]</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>H1: FOMO(소속욕구, 외적동기)는 SNS 만족도에 긍정적인 영향을 미친다.
+H1a: 소속욕구는 SNS 만족도에 긍정적인 영향을 미친다.
+H1b: 외적동기는 SNS 만족도에 긍정적인 영향을 미친다.
+H2: SNS 이용동기(사회적 연결, 지식추구, 오락추구)는 FOMO와 SNS 만족도 간의 관계를 조절하는 역할을 한다.
+H2a: 사회적 연결은 FOMO와 SNS 만족도 간의 관계를 긍정적으로 조절하는 역할을 한다.
+H2b: 지식추구는 FOMO와 SNS 만족도 간의 관계를 긍정적으로 조절하는 역할을 한다.
+H2c: 오락추구는 FOMO와 SNS 만족도 간의 관계를 긍정적으로 조절하는 역할을 한다.
+H3: SNS 만족도는 SNS 지속사용의도에 긍정적인 영향을 미친다.
+H4a: FOMO 소속욕구는 SNS 만족도를 통해 SNS 지속사용의도에 간접적인 영향을 미친다.
+H4b: FOMO 외적동기는 SNS 만족도를 통해 SNS 지속사용의도에 간접적인 영향을 미친다.</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>FOMO (소속욕구, 외적동기)</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>SNS 지속사용의도</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>SNS 만족도</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>SNS 이용동기 (사회적 연결 동기, 지식추구 동기, 오락추구 동기)</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>1. FOMO의 하위요인 중 소속욕구는 SNS 만족도에 유의한 정(+)의 영향을 미쳤으나, 외적동기는 유의한 영향을 미치지 않음.
+2. SNS 이용동기의 조절효과 분석 결과, 사회적 연결과 지식추구 동기는 소속욕구 기반 FOMO와 SNS 만족도 간의 관계를 정(+)으로 조절하였으나, 오락추구 동기는 유의한 조절효과를 보이지 않음. 외적동기 기반 FOMO의 경우 모든 이용동기에서 조절효과가 나타나지 않음.
+3. SNS 만족도는 SNS 지속사용의도에 유의한 정(+)의 영향을 미침.
+4. 매개효과 분석 결과, 소속욕구는 SNS 만족도를 매개로 지속사용의도에 간접적인 영향을 미친 반면, 외적동기는 매개효과가 나타나지 않음.</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>[FOMO - 소속욕구]
+I get worried when I find out my friends are having fun without me.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+I get anxious when I don’t know what my friends are up to.
+(나는 친구들의 소식을 접하지 못할 때 불안하다.)
+[FOMO - 외적동기]
+I keep checking what my friends are doing even on holidays.
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다.)
+I am afraid that others may know about the latest products that I don't know.
+(나는 다른 사람들이 알고 있는 최신 상품을 모르고 있을까봐 겁이 난다.)
+I always worry that I might fall behind the trend.
+(나는 유행에 뒤쳐질까봐 늘 신경쓰인다.)
+I am anxious that I might miss out on products that other people are buying these days.
+(나는 다른 사람들이 요즘 구매하는 상품을 놓칠까봐 불안하다.)
+[SNS 이용동기 - 사회적 연결 동기]
+I use social media to hang out with my friends.
+(내가 소셜미디어를 이용하는 것은 친구들과 어울리기 위해서이다.)
+I use social media because I want to share my updates with my family, friends, or acquaintances.
+(내가 소셜미디어를 이용하는 것은 가족이나 친구, 지인들에게 나의 근황을 알리고 싶기 때문이다.)
+I use social media because I want to share my thoughts or experiences.
+(내가 소셜미디어를 이용하는 것은 내 생각이나 경험 등을 공유하고 싶기 때문이다.)
+I use social media because I want to express myself.
+(내가 소셜미디어를 이용하는 것은 나를 표현하고 싶기 때문이다.)
+[SNS 이용동기 - 지식추구 동기]
+I use social media to expand my knowledge.
+(내가 소셜미디어를 이용하는 것은 내 지식을 확장하기 위해서이다.)
+I use social media to get daily information.
+(내가 소셜미디어를 이용하는 것은 일상적 정보를 얻기 위해서이다.)
+I use social media to get the latest news.
+(내가 소셜미디어를 이용하는 것은 최신 소식을 얻기 위해서이다.)
+I use social media to know what is happening in the world.
+(내가 소셜미디어를 이용하는 것은 세상에 어떤 일이 일어나고 있는지 알기 위해서이다.)
+[SNS 이용동기 - 오락추구 동기]
+I use social media because it is enjoyable.
+(내가 소셜미디어를 이용하는 것은 즐겁기 때문이다.)
+I use social media because it is fun.
+(내가 소셜미디어를 이용하는 것은 재미있기 때문이다.)
+I use social media because it is interesting.
+(내가 소셜미디어를 이용하는 것은 흥미롭기 때문이다.)
+[SNS 만족도]
+Are you overall satisfied with using social media?
+(귀하께서는 소셜미디어를 사용하면서 전반적으로 만족하고 계십니까?)
+[SNS 지속사용의도]
+Do you intend to continue using social media in the future?
+(귀하께서는 앞으로도 지속적으로 소셜미디어를 사용하고 싶은 의향이 있으십니까?)</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>686</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>이향남</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>SNS 상향비교가 FoMO를 통해 인상관리 행위 및 SNS 사용 중단에 미치는 영향： 한중 간 비교연구</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>동국대학교 대학원 미디어커뮤니케이션학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>사회비교이론(Social Comparison Theory), 연극적 상호작용 및 인상관리 이론(Impression Management Theory), 이중 구성요소 모형(Two-Component Model), 자기불일치 이론(Self-Discrepancy Theory), 자원보존이론(Conservation of Resources Theory), 스트레스–긴장–결과(Stressor–Strain–Outcome) 모형</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>[SNS 상향사회비교] -&gt; [FoMO] -&gt; [SNS 인상관리 동기적 오프라인 행위] 및 [SNS 상향사회비교] -&gt; [FoMO] -&gt; [SNS 피로도] -&gt; [SNS 사용중단 의도 및 행위]</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>H1: SNS에서의 상향 사회비교는 FoMO 경향과 정(+)적 관계를 보일 것이다.
+H2: FoMO는 SNS 인상관리 동기적 오프라인 행위와 정(+)적 관계를 보일 것이다.
+H3: FoMO는 SNS상향비교와 SNS 인상관리 동기적 오프라인 행위의 관계를 매개할 것이다.
+H4: FoMO 수준은 SNS 피로 수준과 정(+)적 관계를 보일 것이다.
+H5: SNS 피로는 SNS 사용중단 의도 및 행동 경향과 정(+)적 관계를 보일 것이다.
+H6: SNS 피로는 FoMO와 SNS 사용중단의 관계를 매개할 것이다.
+H7: FoMO와 SNS 피로는 SNS상향 사회비교와 SNS 사용중단의 관계를 매개할 것이다.
+H8: 중국과 한국의 표본은 각 주요 변수에서 평균차이를 보일 것이다.
+H9: 중국과 한국의 표본은 행동적 경로에서 경로강도 차이를 보일 것이다.
+H10: 중국과 한국의 표본은 심리적·경험적 경로에서 경로강도 차이를 보일 것이다.</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>SNS 상향사회비교 경향</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>SNS 인상관리 동기적 오프라인 행위 경향, SNS 사용중단 의도 및 행위 경향</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>FoMO(소외에 대한 두려움), SNS 피로도</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>국가/문화적 배경 (한국 vs 중국)</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>1. 'SNS 상향사회비교 -&gt; FoMO -&gt; SNS 인상관리 동기적 오프라인 행위'로 이어지는 행동적 경로는 한국과 중국 두 표본 모두에서 유의하게 지지되었다.
+2. 'SNS 피로 -&gt; SNS 사용중단' 경로는 양국 표본 모두에서 정(+)의 영향관계를 보여 지지되었다.
+3. 한국 표본에서는 'SNS 상향사회비교 -&gt; FoMO -&gt; SNS 피로 -&gt; SNS 사용중단'으로 이어지는 연쇄 매개효과가 유의하게 나타났으나, 중국 표본에서는 FoMO가 SNS 피로에 음(-)의 영향을 미쳐 해당 연쇄 매개 경로가 성립하지 않았다.
+4. 다집단 분석 및 평균 차이 검정 결과, 중국 표본이 상향사회비교, FoMO, 인상관리 오프라인 행위, SNS 피로도에서 한국 표본보다 평균 수준이 높았으나, SNS 사용중단 경향은 한국 표본이 유의하게 높았다.
+5. 주요 경로의 강도는 전반적으로 한국 표본에서 중국 표본보다 유의하게 더 강하게 나타났다.</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>[SNS Upward Social Comparison]
+I tend to pay more attention to the SNS activities of people who live lives I admire or whom I feel are superior to me in some ways.
+(나는 내가 동경하는 삶을 살거나, 어떤 면에서 나보다 더 뛰어나다고 느끼는 사람들의 SNS 활동을 더 신경을 쓰는 편이다.)
+When other people post lives or achievements on SNS that others would envy, it makes me think about my own life and situation.
+(SNS에서 다른 사람들이 부러워할 만한 삶이나 성취를 올릴 때, 나도 내 삶과 상황을 생각하게 된다.)
+When others do better than me on SNS, I think about how I can also improve myself.
+(나는 SNS에서 다른 사람이 나보다 잘할 때, 나도 어떻게 하면 더 나아질 수 있을지 생각한다.)
+[Fear of Missing Out (FoMO)]
+I check SNS to make sure I do not miss out on fun or meaningful activities posted by close acquaintances.
+(나는 가까운 사람들이 SNS에 올린 재미있거나 의미 있는 활동을 놓치지 않으려고 SNS를 확인한다.)
+I check SNS out of fear that my friends are sharing stories that only I am unaware of if I do not look at SNS.
+(나는 SNS를 보지 않으면 친구들이 나만 모르는 이야기를 나누고 있을까 봐 SNS를 확인한다.)
+I check SNS because I worry that I might miss what other people are up to these days if I do not look at SNS.
+(나는 SNS를 보지 않으면 다른 사람들이 요즘 무엇을 하고 있는지 놓칠까 봐 SNS를 확인한다.)
+I feel uncomfortable if I do not check my friends' posts or stories on SNS in a timely manner.
+(나는 SNS에서 친구들의 게시물이나 스토리를 제때 확인하지 못하면 찝찝하다.)
+When I am doing something enjoyable, I feel it is important to post it on SNS to share it with others.
+(나는 내가 즐거운 일을 할 때, 그것을 SNS에 올려 다른 사람들과 공유하는 것이 중요하다고 느낀다.)
+[SNS Impression Management–Motivated Offline Behavior]
+I tend to pay extra attention to makeup or hair, or edit photos deliberately when taking pictures to post on SNS.
+(나는 SNS에 올릴 사진을 찍을 때 일부러 메이크업이나 헤어를 더 신경 쓰거나 사진을 보정하는 편이다.)
+I have planned offline schedules or actions for the purpose of creating content to post on SNS (e.g., visiting a specific cafe/place because it is good for taking photos).
+(나는 SNS에 올릴 콘텐츠를 위해 오프라인 일정이나 행동을 계획한 적이 있다. (예: 특정 카페/장소가 사진 찍기 좋다고 해서 방문))
+I tend to participate in gatherings or events for content to post on SNS (e.g., popular events like Halloween).
+(나는 SNS에서 올릴 콘텐츠를 위해 모임이나 행사에 참여하는 편이다. (예: 할로윈 등 인기 행사))
+I have visited specific travel destinations or popular tourist spots for content to post on SNS.
+(나는 SNS에 올릴 콘텐츠를 위해 특정 여행지나 인기 관광지를 방문한 적이 있다.)
+I have participated in performances or artistic activities for content to post on SNS.
+(나는 SNS에 올릴 콘텐츠를 위해 공연이나 예술 활동에 참여한 적이 있다.)
+I have engaged in activities showing exercise, fitness, or personal daily life for content to post on SNS.
+(나는 SNS에서 올릴 콘텐츠를 위해 운동, 헬스, 또는 개인 일상을 보여주는 활동에 참여한 적이 있다.)
+I have participated in offline activities that I am not particularly interested in for content to post on SNS.
+(나는 SNS에서 올릴 콘텐츠를 위해 특별히 관심 없는 오프라인 활동에도 참여한 적이 있다.)
+[SNS Fatigue]
+I care a lot about the reactions (likes or comments) that others show toward my posts.
+(나는 다른 사람들이 내 게시물에 보이는 반응(좋아요나 댓글)에 신경을 많이 쓰는 편이다.)
+I do not post content on SNS that I feel is not perfect or that might negatively affect my image.
+(나는 내가 완벽하지 않다고 느끼는 사진이나 내 이미지에 부정적인 영향을 줄 수 있을 것 같은 내용은 SNS에 게시하지 않는다.)
+I have checked my previously posted SNS content and deleted or hidden parts or all of it.
+(나는 이전에 올린 SNS 게시물을 확인하고, 게시물 일부 또는 전체를 삭제하거나 숨긴 적이 있다.)
+I feel that using SNS consumes a lot of my attention and energy.
+(나는 SNS를 사용할 때 주의력과 에너지가 많이 소모된다고 느낀다.)
+[SNS Discontinuance Intention and Behavior]
+I have thought about reducing the frequency of posting on SNS.
+(나는 SNS 게시하는 횟수를 줄이고 싶다는 생각을 한 적이 있다.)
+I have thought about stopping posting on SNS.
+(나는 SNS 게시를 중단하고 싶다는 생각을 한 적이 있다.)
+I have thought about deleting SNS apps.
+(나는 SNS 앱을 삭제하고 싶다는 생각을 한 적이 있다.)
+My current frequency of posting on SNS has decreased compared to the past.
+(현재 SNS에 게시하는 횟수가 과거보다 줄었다.)
+I have temporarily stopped using or deleted SNS apps.
+(나는 SNS 앱을 일시적으로 사용 중지하거나 삭제해본 적이 있다.)</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>687</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Susan E. Cross, Erin E. Hardin, Berna Gercek-Swing</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>The What, How, Why, and Where of Self-Construal</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Personality and Social Psychology Review</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>자아구성이론(Self-Construal Theory), 개인주의-집단주의 이론(Individualism-Collectivism Theory)</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>[Cultural Background / Situation Priming] -&gt; [Self-Construal (IndSC, InterSC, RelSC, Coll-InterSC)] -&gt; [Cognition, Affect, Motivation, Social Behavior]</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>H1: 독립적 자아구성(IndSC) 수준이 높을수록 독특성 추구, 문맥 독립적 인지, 자기고양 동기 및 자율적 행동이 촉진될 것이다.
+H2: 상호의존적 자아구성(InterSC) 수준이 높을수록 사회적 맥락 민감성, 동합/연결 중심 인지, 타인 지향적 정서 및 조화 유지 동기가 촉진될 것이다.
+H3: 관계적 자아구성(RelSC) 수준이 높을수록 친밀한 일대일 관계 중심의 정보 조직화, 관계 민감성 및 타인 배려 행동이 증가할 것이다.
+H4: 집단적 자아구성(Coll-InterSC) 수준이 높을수록 사회적 범주 및 대규모 집단 소속감 기반의 동기와 내집단 중심 행동이 증가할 것이다.</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>문화적 배경(Cultural Context), 자아구성 점화 조건(Independent / Interdependent / Relational / Collective Priming)</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>인지적 과정(문맥 민감성, 조망 수용, 동화/대조 효과), 정서적 반응(사회적 관여/비관여 정서, 주관적 안녕감), 동기(자기고양, 자기비판, 예방/촉진 초점) 및 사회적 행동</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>자아 구성 (Self-Construal: IndSC, InterSC, RelSC, Coll-InterSC)</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>성별(Gender), 참조 집단 효과(Reference Group Effect), 상황적 점화(Priming Context)</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>1. 자아구성은 단일 차원이 아닌 독립적(IndSC), 관계적 상호의존(RelSC), 집단적 상호의존(Coll-InterSC) 등 다차원적 구조로 작동한다.
+2. 자아구성은 고정된 개인차 특성일 뿐만 아니라 상황적 점화(Priming)를 통해 가변적으로 활성화되어 인지, 정서, 동기, 행동 전반에 미치는 영향력을 달리한다.
+3. 문화 간 자기보고형 척도 연구의 불일치는 참조 집단 효과(Reference Group Effect) 및 측정 문항의 다차원성 미반영 등 방법론적 문제에 기인하며, 묵시적 측정(Implicit measures) 및 다차원 척도의 도입이 필요하다.</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>I value being in good health above everything.
+(나는 무엇보다 건강한 것을 가치 있게 생각한다.)
+I act the same no matter who I am with.
+(나는 누구와 함께 있든 똑같이 행동한다.)
+My close relationships are an important reflection of who I am.
+(나의 친밀한 관계는 내가 누구인지를 보여주는 중요한 반영이다.)
+When I think of myself, I often think of groups I belong to as well.
+(내 자신에 대해 생각할 때, 나는 내가 속한 집단에 대해서도 자주 생각한다.)
+When I think of myself, I often think of my close friends of family as well.
+(내 자신에 대해 생각할 때, 나는 나의 친밀한 친구들이나 가족에 대해서도 자주 생각한다.)
+I feel I have a strong relationship with _______.
+(나는 _______와/과 강한 관계를 맺고 있다고 느낀다.)
+I like being unique.
+(나는 독특한 것을 좋아한다.)
+I support my team.
+(나는 내 팀을 지지한다.)</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>10.1177/1088868310373752</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>688</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>신미주</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>SNS 이용동기가 FoMO와 화장품 구매 의도에 미치는 영향 : 20대~50대 여성 중심으로</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>한성대학교 예술대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>이용과 충족 이론 (Uses and Gratifications Theory), 자기결정 이론 (Self-Determination Theory), 사회 비교 이론 (Social Comparison Theory), 자아개념 이론 (Self-Concept Theory), 확장된 계획행동이론 (Extended Theory of Planned Behavior)</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>[SNS 이용동기 (심리적, 정보탐색적, 사회적)] -&gt; [FoMO (개인적, 사회적)] -&gt; [화장품 구매 의도]</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>H1. SNS 이용동기는 FoMO에 유의미한 영향을 미칠 것이다.
+H1-1. 심리적 이용동기는 개인적 FoMO에 유의미한 영향을 미칠 것이다.
+H1-2. 정보탐색적 이용동기는 개인적 FoMO에 유의미한 영향을 미칠 것이다.
+H1-3. 사회적 이용동기는 개인적 FoMO에 유의미한 영향을 미칠 것이다.
+H1-4. 심리적 이용동기는 사회적 FoMO에 유의미한 영향을 미칠 것이다.
+H1-5. 정보탐색적 이용동기는 사회적 FoMO에 유의미한 영향을 미칠 것이다.
+H1-6. 사회적 이용동기는 사회적 FoMO에 유의미한 영향을 미칠 것이다.
+H2. SNS 이용동기는 화장품 구매 의도에 유의미한 영향을 미칠 것이다.
+H2-1. 심리적 이용동기는 화장품 구매 의도에 유의미한 영향을 미칠 것이다.
+H2-2. 정보탐색적 이용동기는 화장품 구매 의도에 유의미한 영향을 미칠 것이다.
+H2-3. 사회적 이용동기는 화장품 구매 의도에 유의미한 영향을 미칠 것이다.
+H3. FoMO는 화장품 구매 의도에 유의미한 영향을 미칠 것이다.
+H3-1. 개인적 FoMO는 화장품 구매 의도에 유의미한 영향을 미칠 것이다.
+H3-2. 사회적 FoMO는 화장품 구매 의도에 유의미한 영향을 미칠 것이다.
+H4. SNS 이용동기와 화장품 구매 의도 간 관계에서 FoMO는 매개 효과가 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>SNS 이용동기 (심리적 이용동기, 정보탐색적 이용동기, 사회적 이용동기)</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>화장품 구매 의도</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>FoMO (개인적 FoMO, 사회적 FoMO)</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>1. SNS 이용동기 중 심리적 이용동기는 개인적 및 사회적 FoMO에, 사회적 이용동기는 개인적 FoMO에 유의미한 정(+)의 영향을 미쳤으나, 정보탐색적 이용동기는 FoMO에 유의한 영향을 미치지 않았음.
+2. SNS 이용동기의 3개 하위요인(심리적, 정보탐색적, 사회적 이용동기) 모두 화장품 구매 의도에 유의미한 긍정적 영향을 미쳤으며, 정보탐색적 이용동기가 가장 강한 영향을 미침.
+3. FoMO의 하위요인 중 개인적 FoMO는 화장품 구매 의도에 유의미한 영향을 미쳤으나, 사회적 FoMO는 통계적으로 유의미한 영향을 미치지 않음.
+4. SNS 이용동기와 화장품 구매 의도 간의 관계에서 FoMO의 부분 매개효과가 검증됨 (Sobel test Z=2.9013, p&lt;.01).</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>[SNS 이용동기 - 심리적 이용동기]
+People enjoy reading what I post.
+(사람들이 내가 게시한 글에 대해 읽는 것을 즐긴다.)
+I want to gain popularity through SNS.
+(나는 SNS를 통해 인기를 얻고 싶다.)
+I use SNS to get responses (comments, likes) from my friends.
+(친구들의 반응(댓글, 좋아요)을 얻기 위해 이용한다.)
+I feel satisfaction when posting text (or photos).
+(나는 글(또는 사진)을 올릴 때 만족감을 느낀다.)
+I want to create a good impression on others through SNS.
+(나는 SNS를 통해 타인에게 좋은 인상을 심어주고 싶다.)
+I use SNS to express and record my thoughts, feelings, and individuality.
+(나의 생각, 감정, 개성을 표현하고 기록하기 위해 이용한다.)
+I enjoy sharing my experiences through SNS.
+(나는 SNS를 통해 나의 경험을 공유하는 것이 즐겁다.)
+[SNS 이용동기 - 정보탐색적 이용동기]
+I use SNS to get useful information (discounts, event participation, etc.).
+(유용한 정보를 얻기 위해 이용한다(할인, 이벤트 참여 등).)
+I use SNS to obtain accurate information about my area of interest.
+(관심있는 분야에 대해 정확한 정보를 얻기 위해 이용한다.)
+I use SNS to get reliable information through others' experiences.
+(타인의 경험을 통한 신뢰성 있는 정보를 얻기 위해 이용한다.)
+I use SNS to learn about new products.
+(새로운 상품에 대해 알아보기 위해 이용한다.)
+I use SNS to get changing information.
+(변화되고 있는 정보를 얻기 위해 이용한다.)
+[SNS 이용동기 - 사회적 이용동기]
+I use SNS to make new connections.
+(새로운 인맥을 만들기 위해 이용한다.)
+I use SNS to interact with people who have similar interests.
+(비슷한 관심이 있는 사람들과 교류하기 위해 이용한다.)
+I use SNS to establish and maintain relationships with others.
+(다른 사람들과 관계를 맺고 유지하기 위해 이용한다.)
+I use SNS to communicate with other people.
+(다른 사람들과 소통을 하기 위해 이용한다.)
+[FoMO - 개인적 FoMO]
+I am anxious that if I miss this opportunity, I won't be able to make a personally rewarding purchase.
+(이 기회를 놓치게 되면 개인적으로 보람찬 소비를 하지 못할 것 같아 불안하다.)
+I am anxious that I might miss this opportunity because it is clear it will be important or fun for me.
+(이 기회가 내게 중요하거나 재미있을 것이 분명해서, 이를 놓치게 될까봐 불안하다.)
+I am anxious that I might miss this opportunity due to other circumstances.
+(다른 사정으로 인해 이 기회를 놓치게 될까봐 불안하다.)
+I am anxious that if I miss this opportunity, I will regret it later.
+(이 기회를 놓치게 되면 훗날 스스로 후회하게 될 것 같아 불안하다.)
+I am anxious that if I miss this opportunity, people in my group will consider me unimportant.
+(이 기회를 놓치게 되면 내가 속한 집단에서 나를 중요하지 않게 여길 것 같아 불안하다.)
+[FoMO - 사회적 FoMO]
+I am anxious that if I miss this opportunity, I will be ignored or forgotten by my group.
+(이 기회를 놓치게 되면 내가 속한 집단에서 무시당하거나 잊혀질 것 같아 불안하다.)
+I am anxious that if I miss this opportunity, I won't meet the standards of my group.
+(이 기회를 놓치게 되면 내가 속한 집단의 기준에 부합하지 않은 것 같아 불안하다.)
+I am anxious that if I miss this opportunity, I will be excluded from my group.
+(이 기회를 놓치게 되면 내가 속한 집단에서 배제될 것 같아 불안하다.)
+I am anxious that if I miss this opportunity, others will make a more rewarding purchase than me.
+(이 기회를 놓치게 되면 남들이 나보다 더 보람찬 소비를 하게 될 것 같아 불안하다.)
+[화장품 구매 의도]
+Information accessed through SNS helps in making purchase decisions.
+(SNS를 통해 접한 정보는 구매 결정에 도움을 준다.)
+When purchasing cosmetics, I will refer to information provided on SNS.
+(화장품 구매 시 SNS에서 제공하는 정보를 참고하여 구매할 것이다.)
+I will preferentially consider purchasing cosmetics that I came across on SNS.
+(SNS를 통해 정보를 접한 화장품을 우선적으로 고려하여 구매할 것이다.)
+I want to purchase cosmetics that I encountered through SNS.
+(SNS를 통해 정보를 접한 화장품을 구매해보고 싶다.)
+There is a possibility that I will purchase cosmetics that I came across on SNS.
+(SNS를 통해 정보를 접한 화장품을 구매할 가능성이 있다.)</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>689</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>BAI GE</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Examining FoMO’s Role in the Relationship between Brand Community Engagement and Customer Behavior</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>경희대학교 대학원 국제경영학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), 사회적 동질성이론(Social Homophily Theory), 귀속 욕구 이론(Need to Belong Theory)</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>[개인적 동기: 귀속 욕구, 인기도 욕구, 태도 동질성, 질투 관련 불안] -&gt; [고립공포감(FoMO)] -&gt; [온라인/오프라인 브랜드 커뮤니티 몰입] -&gt; [고객 참여 행동, 고객 자발적 행동]</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>H1: 태도 동질성은 FoMO에 정(+)의 영향을 미칠 것이다.
+H2: 질투 관련 불안은 FoMO에 정(+)의 영향을 미칠 것이다.
+H3: 귀속 욕구는 FoMO에 정(+)의 영향을 미칠 것이다.
+H4: 인기도 욕구는 FoMO에 정(+)의 영향을 미칠 것이다.
+H5: 고립공포감(FoMO)은 고객의 온라인 커뮤니티 몰입과 정(+)으로 관련되어 있을 것이다.
+H6: 고립공포감(FoMO)은 고객의 오프라인 커뮤니티 몰입과 정(+)으로 관련되어 있을 것이다.
+H7: 온라인 커뮤니티 몰입은 고객 참여 행동과 정(+)으로 관련되어 있을 것이다.
+H8: 온라인 커뮤니티 몰입은 고객 자발적 행동과 정(+)으로 관련되어 있을 것이다.
+H9: 오프라인 커뮤니티 몰입은 고객 참여 행동과 정(+)으로 관련되어 있을 것이다.
+H10: 오프라인 커뮤니티 몰입은 고객 자발적 행동과 정(+)으로 관련되어 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>귀속 욕구(Need to belong), 인기도 욕구(Need for popularity), 태도 동질성(Attitude homophily), 질투 관련 불안(Envy-related anxiety)</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>고객 참여 행동(Participation behavior), 고객 자발적 행동(Voluntary behavior)</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>고립공포감(FoMO), 온라인 커뮤니티 몰입(Online community engagement), 오프라인 커뮤니티 몰입(Offline community engagement)</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>구조방정식 모형(SEM) 분석 결과, 개인의 심리적 선행 요인 중 귀속 욕구(H1), 인기도 욕구(H2), 태도 동질성(H3)은 FoMO에 유의한 정(+)의 영향을 미쳤으며, 특히 귀속 욕구의 영향력이 가장 컸다. 반면 질투 관련 불안(H4)은 FoMO에 유의한 영향을 미치지 않아 가설이 기각되었다. 또한 FoMO는 온라인(H5) 및 오프라인(H6) 브랜드 커뮤니티 몰입을 유의하게 정(+)으로 예측하였다. 마지막으로 온라인 및 오프라인 커뮤니티 몰입은 모두 고객의 참여 행동(H7, H9)과 자발적 행동(H8, H10)에 정(+)의 영향을 미쳤으며, 오프라인보다 온라인 커뮤니티 몰입의 영향력이 더 크게 나타났다.</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>[Need to belong]
+I try hard not to do things that will make other people avoid or reject me.
+(다른 사람들이 나를 회피하거나 거부하게 만들 행동을 하지 않으려고 노력한다.)
+It bothers me a great deal when I am not included in other people’s plans.
+(다른 사람들의 계획에 내가 포함되지 않을 때 매우 신경이 쓰인다.)
+My feelings are easily hurt when I feel that others do not accept me.
+(타인이 나를 받아들이지 않는다고 느낄 때 쉽게 상처를 받는다.)
+[Need for popularity]
+At times, I’ve ignored some people in order to be more popular with others.
+(때로는 다른 사람들에게 더 인기를 얻기 위해 일부 사람들을 무시한 적이 있다.)
+At times, I’ve gone out with people, just because they were popular.
+(때로는 단지 그들이 인기가 있다는 이유만으로 사람들과 어울린 적이 있다.)
+I’ve bought things, because they were the “in” things to have.
+(유행하는 물건이라는 이유만으로 제품을 구매한 적이 있다.)
+[Envy-related anxiety]
+I fear others have more rewarding experiences than me.
+(다른 사람들이 나보다 더 보람찬 경험을 하고 있을까봐 두렵다.)
+Most of my coworkers have it better than I do.
+(내 동료들의 대부분이 나보다 더 잘 지내고 있다고 생각한다.)
+At work, I see myself as an underdog who isn't taken as others.
+(소속 집단에서 나는 다른 사람들만큼 대우받지 못하는 약자라고 느낀다.)
+[Attitude homophily]
+I imitate people who share my values.
+(나는 나와 가치관을 공유하는 사람들을 모방한다.)
+I imitate people who have a lot in common with me.
+(나는 나와 공통점이 많은 사람들을 모방한다.)
+I am willing to buy the products recommended by other users who have similar values to me.
+(나는 나와 비슷한 가치관을 가진 다른 사용자가 추천하는 제품을 기꺼이 구매한다.)
+I am more vulnerable to people who have similar values to me.
+(나는 나와 비슷한 가치관을 가진 사람들에게 더 쉽게 영향을 받는다.)
+[Fear of missing out]
+I get worried when I find out my friends are having fun without me.
+(친구들이 나 없이 즐거운 시간을 보내고 있다는 것을 알게 되면 걱정이 된다.)
+I get anxious when I don’t know the brands popular among my friends.
+(친구들 사이에서 인기 있는 브랜드를 모르면 불안해진다.)
+It is important that I continue to keep in touch with what my friends are doing.
+(친구들이 무엇을 하고 있는지 지속적으로 소식을 파악하는 것이 중요하다.)
+It bothers me when I miss an opportunity to meet up with friends.
+(친구들과 만날 기회를 놓치면 신경이 쓰인다.)
+When I have a good time it is important for me to share the details online.
+(즐거운 시간을 보낼 때 그 상세한 내용을 온라인에 공유하는 것이 나에게 중요하다.)
+[Online community engagement]
+I feel very positive when I use the online community.
+(온라인 커뮤니티를 사용할 때 매우 긍정적인 기분을 느낀다.)
+I do quite a bit of socializing in this community.
+(나는 이 커뮤니티에서 상당한 수준의 친목 활동을 한다.)
+This community does a good job of getting its visitors to contribute or provide feedback.
+(이 커뮤니티는 방문자들의 기여나 피드백 참여를 잘 유도한다.)
+This community helps me make good purchase decisions.
+(이 커뮤니티는 내가 좋은 구매 결정을 내리도록 도와준다.)
+[Offline community engagement]
+I am very attached to the brand community.
+(나는 이 브랜드 커뮤니티에 강한 애착을 느낀다.)
+I see myself as a part of the community.
+(나는 내 자신을 이 커뮤니티의 일원이라고 생각한다.)
+The friendship I have with other community members mean a lot to me.
+(다른 커뮤니티 회원들과 맺은 우정은 나에게 큰 의미가 있다.)
+I benefit from following the community’s rules.
+(나는 커뮤니티의 규칙을 따름으로써 이득을 얻는다.)
+[Voluntary behavior]
+I recommend this community to other people.
+(나는 이 커뮤니티를 다른 사람들에게 추천한다.)
+I try to spread positive word of mouth about this community.
+(나는 이 커뮤니티에 대해 긍정적인 구전을 전파하려고 노력한다.)
+I provide helpful feedback to customer service.
+(나는 고객 서비스에 도움이 되는 피드백을 제공한다.)
+I display logos or brands of this community.
+(나는 이 커뮤니티의 로고나 브랜드를 표출/노출한다.)
+I provide suggestions to help improve this community.
+(나는 이 커뮤니티의 개선을 돕기 위해 제안을 제공한다.)
+[Participation behavior]
+I have paid attention to how others behavior in this community.
+(나는 이 커뮤니티에서 다른 사람들이 어떻게 행동하는지 주의 깊게 관찰했다.)
+I have asked others for information on what this community offers.
+(나는 이 커뮤니티가 제공하는 정보에 대해 다른 사람들에게 물어보았다.)
+I answered others service-related questions.
+(나는 다른 사람들의 서비스 관련 질문에 답변해 주었다.)
+I followed other members’ directives or orders in this community.
+(나는 이 커뮤니티에서 다른 회원들의 지시나 안내를 따랐다.)
+I adequately completed all the behaviors expected.
+(나는 기대되는 모든 행동을 적절하게 완수했다.)</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>UCI:I804:11006-200000103514</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>690</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>장동화</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>FOMO, 브랜드애착, 독특성욕구와 소비자경쟁자극이 리미티드 패션상품 ‘오픈-런’ 의도에 미치는 영향 연구 - 패션관여도의 조절효과를 중심으로 -</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>국민대학교 디자인대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>FOMO(Fear of Missing Out), 브랜드애착이론, 독특성이론, 소비자 경쟁 자극 이론, 관여도 이론</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>[FOMO, 브랜드 애착, 독특성 욕구] -&gt; [소비자 경쟁 자극] -&gt; [오픈런 의도] (패션 관여도의 조절효과)</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>H1: FOMO는 소비자경쟁자극에 정(+)의 영향을 미칠 것이다.
+H2: 브랜드애착은 소비자경쟁자극에 정(+)의 영향을 미칠 것이다.
+H3: 독특성욕구는 소비자경쟁자극에 정(+)의 영향을 미칠 것이다.
+H4: 소비자경쟁자극은 오픈런의도에 정(+)의 영향을 미칠 것이다.
+H5: FOMO는 오픈런의도에 정(+)의 영향을 미칠 것이다.
+H6: 브랜드애착은 오픈런의도에 정(+)의 영향을 미칠 것이다.
+H7: 독특성욕구는 오픈런의도에 정(+)의 영향을 미칠 것이다.
+H8: FOMO가 오픈런의도에 미치는 영향은 소비자의 패션관여도에 의해 정(+)의 조절효과를 가질 것이다.
+H9: 브랜드애착이 오픈런의도에 미치는 영향은 소비자의 패션관여도에 의해 정(+)의 조절효과를 가질 것이다.
+H10: 독특성욕구가 오픈런의도에 미치는 영향은 소비자의 패션관여도에 의해 정(+)의 조절효과를 가질 것이다.</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>FOMO, 브랜드 애착, 독특성 욕구</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>오픈런 의도</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>소비자 경쟁 자극</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>패션 관여도</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>1. 소비자의 심리 요인인 FOMO, 브랜드 애착, 독특성 욕구는 모두 소비자 경쟁 자극과 오픈런 의도에 유의한 정(+)의 영향을 미치는 것으로 확인됨.
+2. 소비자 경쟁 자극은 오픈런 의도에 유의한 정(+)의 영향을 미침.
+3. 소비자 경쟁 자극은 FOMO, 브랜드 애착, 독특성 욕구와 오픈런 의도 사이에서 유의한 부분 매개효과를 보임.
+4. 패션 관여도는 FOMO 및 브랜드 애착이 오픈런 의도에 미치는 영향 관계에서 정(+)의 조절효과를 가졌으나, 독특성 욕구가 오픈런 의도에 미치는 영향 관계에서는 조절효과가 유의하지 않은 것으로 나타남(H10 기각).</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>[FOMO]
+- I worry that my friends will have a fun time without me.
+(나는 친구들이 나를 제외하고 재밌는 시간을 보낼까봐 걱정된다.)
+- I get anxious when I don't know what my friends are doing.
+(나는 친구들이 무엇을 하고 있는지 모를 때 불안하다.)
+- I worry that I spend too much time keeping track of what's going on around me.
+(나는 주변을 신경쓰는데 많은 시간을 할애하는 것 같아 걱정된다.)
+- It is important to share my daily life on SNS when I am having a good time.
+(나는 즐거운 시간을 보낼 때 SNS로 근황을 공유하는 것이 중요하다.)
+- I get anxious when I miss a planned meeting.
+(나는 약속된 모임을 놓치게 되면 불안하다.)
+- I constantly check what my friends are doing even on holidays.
+(나는 휴일에도 친구들이 무엇을 하고 있는지 끊임없이 확인한다.)
+[Brand Attachment]
+- I am interested in other people who use my preferred fashion brand.
+(내가 선호하는 패션브랜드를 사용하는 다른 사람에 대해서도 관심이 간다.)
+- I frequently visit the store or website of my preferred fashion brand.
+(내가 선호하는 패션브랜드의 매장이나 홈페이지를 자주 방문한다.)
+- I trust my preferred fashion brand.
+(내가 선호하는 패션브랜드는 신뢰가 간다.)
+- I feel attached to my preferred fashion brand.
+(내가 선호하는 패션브랜드에 대해 애착이 간다.)
+- It is natural for me to use my preferred fashion brand.
+(내가 선호하는 패션브랜드를 이용하는 것은 당연하다.)
+- When I need to buy fashion products, I check my preferred fashion brand first.
+(패션상품을 구매할 필요가 있을 때는 선호하는 패션브랜드에서 먼저 살펴본다.)
+[Need for Uniqueness]
+- When choosing products, I try to express my personality by purchasing special clothes or brands.
+(나는 제품을 고를 때 특별한 옷이나 브랜드를 구매함으로써 나만의 개성을 표현하기 위해 노력하는 편이다.)
+- I often look for small-production clothes or brands to create my own style.
+(나는 나만의 스타일을 만들기 위해 종종 소량생산 옷이나 브랜드를 찾는다.)
+- I avoid clothes or brands that ordinary people usually buy.
+(나는 보통의 사람들이 기존에 많이 사는 옷이나 브랜드를 기피한다.)
+- If the clothes I bought become popular among many people, I do not wear them.
+(나는 내가 샀던 옷이 여러 사람들 사이에서 유행이 되어버리면 그 옷을 입지 않는다.)
+- Even if someone tells me my outfit is inappropriate, I will continue to dress the same way.
+(나는 다른 사람이 나에게 상황에 맞지 않는 옷을 입었다고 귀띔해주어도, 계속해서 같은 방식으로 옷을 입을 것이다.)
+- I sometimes wear bold outfits that are hard for others to accept.
+(나는 옷을 입을 때 가끔 다른 사람들이 받아들이기 어려운 대담한 옷차림을 한다.)
+[Consumer Competitive Arousal]
+- I think purchasing desired fashion products is a competition.
+(나는 원하는 패션상품을 구매하는 건 경쟁이라고 생각한다.)
+- I think a strategy or plan is needed when purchasing desired fashion products.
+(나는 원하는 패션상품을 구매할 때 전략이나 플랜이 필요하다고 생각한다.)
+- I tried to buy fashion products that other people were trying to buy.
+(나는 다른 사람이 구매하려고 하는 패션상품을 나도 사려고 했다.)
+- I felt successful after purchasing desired fashion products.
+(나는 원하는 패션상품을 구매한 후 성공했다고 느낀 적이 있다.)
+- I felt like fighting with other consumers when purchasing desired fashion products.
+(나는 원하는 패션상품을 구매할 때 다른 소비자들과 싸우는 느낌을 가진 적이 있다.)
+[Fashion Involvement]
+- I usually search for a lot of information related to fashion products.
+(나는 평소 패션상품에 관련된 정보를 많이 탐색하는 편이다.)
+- I know more about fashion compared to people around me.
+(나는 패션에 대해서 나의 주변 사람들에 비해 잘 알고 있는 편이다.)
+- People around me often ask me for advice regarding fashion.
+(나의 주변 사람들은 나에게 패션과 관련하여 조언을 구하곤 한다.)
+- I have a wide variety of fashion products compared to people around me.
+(나는 나의 주변 사람들에 비해서 다양한 종류의 패션제품들을 가지고 있다.)
+- I have a continuous interest in fashion.
+(나는 평소 패션과 관련해서 지속적인 흥미를 가지고 있다.)
+- I know well about the characteristics of fashion products compared to people around me.
+(나는 주변 사람들에 비해서 패션제품의 특성에 대해 잘 알고 있는 편이다.)
+[Open-Run Intention]
+- I am willing to 'open-run' to purchase limited fashion products.
+(나는 리미티드 패션상품을 구매하기 위해 ‘오픈-런’을 할 의향이 있다.)
+- I think 'open-running' is an appropriate method to purchase limited fashion products.
+(나는 리미티드 패션상품을 구매하기 위해 ‘오픈-런’을 하는 것은 적절한 방법이라고 생각한다.)
+- I am willing to recommend 'open-running' to others to purchase limited fashion products.
+(나는 리미티드 패션상품을 구매하기 위해 ‘오픈-런’을 하는 것을 다른 사람에게 추천할 의향이 있다.)
+- I will make an effort to 'open-run' when purchasing limited fashion products.
+(나는 리미티드 패션상품을 구매할 때, ‘오픈-런’을 하기 위해 노력할 것이다.)
+- I expect to compete with customers who 'open-run' when purchasing limited fashion products.
+(나는 리미티드 패션상품을 구매할 때, ‘오픈-런’을 하는 고객들과 경쟁할 것이라 예상한다.)
+- I am willing to invest time and money to 'open-run' for limited fashion products.
+(나는 리미티드 패션상품 ‘오픈-런’을 하기 위해 시간과 돈을 투자할 의향이 있다.)</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>691</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>HUANG LINYI</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>FoMO가 밴드왜건 소비에 미치는 영향 (The Impact of FoMO on Bandwagon Consumption)</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>충북대학교 대학원 경영학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), 소속감 이론(Need to Belong Theory), 소비수요 이론(Leibenstein의 밴드왜건/속물/베블런 효과)</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>[독립변수: FoMO (소속 욕구, 소외감)] -&gt; [매개변수: 브랜드의 사회적 가치에 대한 관심도] -&gt; [종속변수: 밴드왜건 소비]</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>H1: 소속 욕구는 브랜드 사회성 가치에 대한 관심도에 긍정적인 영향을 미칠 것이다.
+H2: 소외감은 브랜드 사회성 가치에 대한 관심도에 긍정적인 영향을 미칠 것이다.
+H3: 브랜드의 사회성 가치에 대한 관심도는 밴드왜건 소비에 긍정적인 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>FoMO (소속 욕구, 소외감)</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>밴드왜건 소비</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>브랜드의 사회적 가치에 대한 관심도</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>구조방정식 모델 분석 결과, FoMO의 긍정적 요인인 소속 욕구와 부정적 요인인 소외감 모두 브랜드의 사회적 가치에 대한 관심도에 통계적으로 유의미한 긍정적 영향을 미치는 것으로 나타났다(H1, H2 채택). 또한 브랜드의 사회적 가치에 대한 관심도가 높을수록 밴드왜건 소비 행동이 증가함을 확인하였다(H3 채택). 이는 소비자가 고립감이나 소속감 결여를 느낄 때 브랜드가 제공하는 사회적·상징적 가치에 집중하게 되며, 이것이 밴드왜건 소비로 이어진다는 심리적 메커니즘을 규명하였다.</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>[Prestige Sensitivity / 위신민감도]
+I tend to buy products to show off to others.
+(나는 다른 사람들에게 보여주기 위해 제품을 구매하는 경향이 있다.)
+I am willing to spend a lot of money if I can buy the product I want.
+(나는 원하는 제품을 구매할 수 있다면 많은 비용을 지출할 용의가 있다.)
+I tend to buy products to demonstrate superiority over others.
+(나는 다른 사람들에게 우월감을 드러내기 위해 제품을 구입하는 경향이 있다.)
+If I can buy all the products I want, I feel more successful than others.
+(나는 원하는 제품을 다 구매할 수 있으면 다른 사람 보다 성공한 느낌이 든다.)
+[Connectedness / 타인관련]
+I tend to buy products that give me a sense of belonging with people around me.
+(나는 주위 사람들과 소속감을 갖게 하는 제품을 구입하는 경향이 있다.)
+I tend to buy products that share values with people around me.
+(나는 주위 사람들과 가치를 공유하는 제품을 구입하는 경향이 있다.)
+I tend to buy products that share a lifestyle with people around me.
+(나는 주위 사람들과 생활양식을 공유하는 제품을 구입하는 경향이 있다.)
+[Praise from others / 타인칭찬]
+I am interested in products that can be recognized by people around me.
+(나는 주위 사람들에게 인정받을 수 있는 제품에 관심이 있다.)
+I purchase products that can give a positive image to people around me.
+(나는 주위 사람들에게 긍정적인 이미지를 줄 수 있는 제품을 구매한다.)
+I purchase the same products to fit in with people around me.
+(나는 주위 사람들에게 맞추기 위해 동일한 제품을 구매한다.)
+[Being alienated / 소외]
+If I don't buy a product that everyone has, I feel ignored by them.
+(나는 모두가 갖고 있는 제품을 사지 않으면 그들에게 무시당한 느낌이 든다.)
+If I don't buy a product that everyone has, I cannot understand the values they share.
+(나는 모두가 갖고 있는 제품을 사지 않으면 그들이 공유하는 가치를 이해할 수 없다.)
+If I don't buy a product that everyone has, it is hard to get along with them.
+(나는 모두가 갖고 있는 제품을 사지 않으면 그들과 잘 지내기 어렵다.)
+[Being ignored / 무시]
+If I don't buy a trending product, I worry that people around me will look at me strangely.
+(나는 유행하는 제품을 사지 않으면 주변 사람들이 나를 이상한 눈으로 볼까 걱정된다.)
+If I don't buy a product that everyone has, I worry that they will think I am strange.
+(나는 모두가 갖고 있는 제품을 사지 않으면 그들이 나를 이상하게 생각할까 걱정된다.)
+If I don't buy a product that everyone around me has, I worry that people will ignore me.
+(나는 주변 사람들이 모두 갖고있는 제품을 사지 않으면 사람들이 나를 무시할까 걱정된다.)
+If I don't buy a product that everyone around me has, I feel that my choice was wrong.
+(나는 주변 사람들이 모두 갖고있는 제품을 사지 않으면 내 선택이 잘못됐다고 생각한다.)
+[Falling behind / 낙오]
+If I don't buy a product that everyone has, I feel like I am out of date.
+(나는 사람들이 다 갖고 있는 제품을 사지 않으면 시대에 뒤떨어진다고 여겨진다.)
+If I don't buy a product that everyone has, I feel like I lack ability.
+(나는 사람들이 다 갖고 있는 제품을 사지 않으면 내가 능력이 부족하다고 여겨진다.)
+If I don't buy a product that everyone has, I feel left behind by trends.
+(나는 사람들이 다 갖고 있는 제품을 사지 않으면 유행에 뒤처진다고 느낀다.)
+[Up-surging interest in brand's social value / 브랜드의 사회성 가치에 대한 관심도]
+I am interested in whether purchasing a specific brand can make me belong to a certain group.
+(나는 특정 브랜드를 구매함으로써 어떤 집단에 귀속될 수 있는지에 대해 더 관심이 있다.)
+I am interested in whether a specific brand can be seen as a symbol of a certain group.
+(나는 특정 브랜드가 어떤 집단의 상징으로 보일 수 있는지에 대해 더 관심이 있다.)
+I am interested in whether I can reveal a sense of belonging through a specific brand.
+(나는 특정 브랜드를 통해 소속감을 드러낼 수 있을지에 대해 더 관심이 있다.)
+I am interested in whether I can obtain recognition from a certain group through a specific brand.
+(나는 특정 브랜드를 통해 어떤 집단의 인정을 얻을 수 있는지에 더 관심이 있다.)
+[Bandwagon consumption / 밴드왜건 소비]
+I prefer to purchase trendy brand products.
+(나는 유행하는 브랜드 제품을 구매하는 것을 선호한다.)
+I prefer to purchase brand products used by many people.
+(나는 많은 사람이 사용하는 브랜드 제품을 구매하는 것을 선호한다.)
+I prefer to purchase brand products known to many people.
+(나는 많은 사람이 알고있는 브랜드 제품을 구매하는 것을 선호한다.)</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>692</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>WU MINJIE</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>FoMO와 가격판매촉진이 소비자 구매의도에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>경희대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>FoMO(Fear of Missing Out) 증후군, 브랜드 자산 이론, 판매촉진 및 가격지각 이론</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>[브랜드 FoMO 영향 유무, 가격할인 판매촉진 유무] -&gt; [소비자 구매의도]</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>H1: FoMO는 소비자 구매의도에 부정적인 영향을 미칠 것이다.
+H2: 가격할인 판매촉진은 소비자 구매의도에 긍정적인 영향을 미칠 것이다.
+H3: 브랜드 FoMO 영향 유무와 가격할인 판매촉진 유무에 따라 소비자 구매의도에 유의한 차이가 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>브랜드 FoMO 영향 유무 (FoMO 영향 브랜드: 노스페이스 vs. FoMO 비영향 브랜드: 나이키), 가격할인 판매촉진 유무 (40% 할인가 판매 vs. 원가 판매)</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>소비자 구매의도</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>1. 브랜드 FoMO 영향 유무에 따라 소비자 구매의도에 유의한 차이가 나타났다. FoMO의 영향을 받지 않은 브랜드(나이키)에 대한 구매의도가 FoMO의 영향을 받았던 브랜드(노스페이스)보다 높게 나타났다.
+2. FoMO는 단기적으로는 제품 매출 및 시장 점유율을 늘리는 데 도움을 줄 수 있으나, 장기적으로 해당 브랜드가 유행이 지난 것으로 인식되면서 소비자 구매의도에 부정적인 영향을 미친다.
+3. 이미 유행이 지난 제품/브랜드의 경우, 가격할인 판매촉진 유무(40% 할인 vs 원가)가 소비자 구매의도에 유의한 영향을 미치지 않는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>[소비자 구매의도 (Purchase Intention)]
+I would consider buying this product.
+(나는 이 제품을 구매할 용의가 있다.)
+It is highly likely that I will purchase this product.
+(나는 이 제품을 구매할 가능성이 높다.)
+I am willing to buy this product if I need one.
+(제품이 필요하다면 이 제품을 구매할 의향이 있다.)</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>UCI: I804:11006-200000172758</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>693</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>다오 티 탄 투이</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>FOMO와 밴드왜건 효과가 브랜드 활성화에 미치는 영향에 대한 탐색적 연구</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>경성대학교 대학원 경영학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>사회적 비교 이론(Social Comparison Theory), 자기결정 이론(Self-Determination Theory), 사회적 증거 이론(Social Proof Theory), 전망 이론(Prospect Theory)</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>[브랜드 인지도] -&gt; [FOMO] -&gt; [밴드왜건 효과] -&gt; [브랜드 활성화] (조절변수: 준거집단)</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>H1: 브랜드 인지도는 소비자의 FOMO(Fear of Missing Out)에 정(+)의 영향을 미칠 것이다.
+H2: 준거집단(회원집단, 열망집단, 회피집단)은 브랜드 인지도가 FOMO에 미치는 영향을 조절할 것이다.
+H3: 소비자의 FOMO는 밴드왜건 효과에 정(+)의 영향을 미칠 것이다.
+H4: 밴드왜건 효과는 브랜드 활성화에 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>브랜드 인지도 (Brand Awareness)</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>브랜드 활성화 (Brand Activation)</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>FOMO (Fear of Missing Out), 밴드왜건 효과 (Bandwagon Effect)</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>준거집단 (Reference Groups: 회원집단, 열망집단, 회피집단)</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>1. 브랜드 인지도는 브랜드 활성화로 직접 이어지지 않으며, 온라인 커뮤니티의 사회적 신호와 결합될 때 먼저 심리적 상태인 FOMO를 유발합니다.
+2. 준거집단(회원집단, 열망집단, 회피집단)은 브랜드 인지도와 FOMO 간의 관계를 증폭하거나 조절하는 역할을 합니다.
+3. FOMO는 소비자의 사회적 불안감을 해소하기 위해 다수의 행동을 모방하게 하여 밴드왜건 소비 효과를 강력하게 촉진합니다.
+4. 밴드왜건 효과는 인지적 위험을 줄이고 신뢰를 형성함으로써 소비자 행동을 구체적인 브랜드 활성화(제품 구매, 캠페인 참여, 콘텐츠 공유 등)로 전환시킵니다.</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>[Brand Awareness]
+I can easily recognize and recall this brand when thinking about this product category.
+(이 제품 카테고리를 떠올릴 때 이 브랜드를 쉽게 인지하고 회상할 수 있다.)
+This brand frequently appears and is highly visible on social media platforms.
+(이 브랜드는 소셜 미디어 플랫폼에서 자주 등장하고 눈에 잘 띈다.)
+[FOMO]
+I feel anxious when I worry that others might be having rewarding experiences with this brand without me.
+(다른 사람들이 나 없이 이 브랜드와 함께 가치 있는 경험을 하고 있을까 봐 불안감을 느낀다.)
+I continuously check social media to ensure I am not missing out on popular brand trends or activities.
+(인기 있는 브랜드 트렌드나 활동을 놓치지 않기 위해 소셜 미디어를 지속적으로 확인한다.)
+[Reference Groups Influence]
+I am highly sensitive to the brand choices and recommendations made by groups I belong to or aspire to join.
+(내가 속해 있거나 속하고 싶은 집단이 선택하고 추천하는 브랜드에 민감하게 반응한다.)
+I avoid using brands associated with groups that I do not wish to be identified with.
+(내가 동일시되고 싶지 않은 집단과 연관된 브랜드의 사용을 회피한다.)
+[Bandwagon Effect]
+I tend to buy or use this brand because many other people are buying and using it.
+(다른 많은 사람들이 이 브랜드를 구매하고 사용하기 때문에 나도 이를 구매하거나 사용하는 경향이 있다.)
+When a brand becomes widely popular among the majority, I feel inclined to follow the choice of the crowd.
+(어떤 브랜드가 다수에게 널리 인기를 얻으면 나도 대중의 선택을 따라가고 싶어진다.)
+[Brand Activation]
+I actively engage with this brand by participating in its campaigns, writing reviews, or sharing its content online.
+(나는 이 브랜드의 캠페인에 참여하거나 리뷰를 작성하고 온라인에 콘텐츠를 공유하는 등 브랜드와 적극적으로 상호작용한다.)
+I am willing to purchase and recommend this brand as part of my ongoing social and digital experience.
+(지속적인 사회적·디지털 경험의 일환으로 이 브랜드를 구매하고 타인에게 추천할 의향이 있다.)</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O694"/>
+  <dimension ref="A1:O695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53543,6 +53543,156 @@
         </is>
       </c>
     </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>694</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>서유리</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Z세대의 소셜 미디어 이용과 FoMO(Fear of Missing Out), 비합리적 외식소비행동 간의 관계</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>경희대학교 대학원 조리외식경영학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), 사회비교이론(Social Comparison Theory), 제한된 합리성 이론(Bounded Rationality Theory), 매슬로우의 욕구계층이론(Maslow's Need Hierarchy Theory), 확장된 자아이론(Extended Self Theory)</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>[소셜 미디어 이용] -&gt; [FoMO (Fear of Missing Out)] -&gt; [비합리적 외식소비행동 (동조소비, 과시소비, 충동소비)]</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>H1. 소셜 미디어 이용은 FoMO에 유의한 정(+)의 영향을 미칠 것이다.
+H2. FoMO는 비합리적 외식소비행동에 유의한 정(+)의 영향을 미칠 것이다.
+H2a. FoMO는 동조소비에 유의한 정(+)의 영향을 미칠 것이다.
+H2b. FoMO는 과시소비에 유의한 정(+)의 영향을 미칠 것이다.
+H2c. FoMO는 충동소비에 유의한 정(+)의 영향을 미칠 것이다.
+H3. 소셜 미디어 이용은 비합리적 외식소비행동에 유의한 정(+)의 영향을 미칠 것이다.
+H3a. 소셜 미디어 이용은 동조소비에 유의한 정(+)의 영향을 미칠 것이다.
+H3b. 소셜 미디어 이용은 과시소비에 유의한 정(+)의 영향을 미칠 것이다.
+H3c. 소셜 미디어 이용은 충동소비에 유의한 정(+)의 영향을 미칠 것이다.
+H4. FoMO는 소셜 미디어 이용과 비합리적 외식소비행동 간의 관계를 매개할 것이다.
+H4a. FoMO는 소셜 미디어 이용과 동조소비 간의 관계를 매개할 것이다.
+H4b. FoMO는 소셜 미디어 이용과 과시소비 간의 관계를 매개할 것이다.
+H4c. FoMO는 소셜 미디어 이용과 충동소비 간의 관계를 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>소셜 미디어 이용</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>비합리적 외식소비행동 (동조소비, 과시소비, 충동소비)</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>FoMO(Fear of Missing Out)</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>1. 소셜 미디어 이용은 FoMO에 유의한 정(+)의 영향을 미치는 것으로 나타남(β = 0.608, p &lt; 0.001).
+2. FoMO는 비합리적 외식소비행동의 하위 요인인 동조소비(β = 0.295, p &lt; 0.001), 과시소비(β = 0.378, p &lt; 0.001), 충동소비(β = 0.430, p &lt; 0.001)에 모두 유의한 정(+)의 영향을 미쳤으며, 특히 충동소비에 대한 영향력이 가장 큼.
+3. 소셜 미디어 이용은 동조소비(β = 0.481, p &lt; 0.001), 과시소비(β = 0.430, p &lt; 0.001), 충동소비(β = 0.291, p &lt; 0.001)에 모두 직접적인 정(+)의 영향을 미쳤으며, 동조소비에 대한 영향력이 가장 큼.
+4. 소셜 미디어 이용과 비합리적 외식소비행동(동조소비, 과시소비, 충동소비) 간의 관계에서 FoMO의 부분 매개효과가 모두 통계적으로 유의하게 나타남.</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>[소셜 미디어 이용 (Social Media Use)]
+- I feel disconnected from friends when I am not logged into social media.
+(나는 소셜 미디어에 로그인하지 못하면 친구들과 단절된 느낌이 든다.)
+- I would be disappointed if I could not use social media at all.
+(나는 소셜 미디어를 전혀 사용할 수 없게 된다면 실망할 것이다.)
+- I feel uneasy when I cannot log into social media.
+(나는 소셜 미디어에 로그인할 수 없으면 마음이 불편해진다.)
+- I prefer communicating with others primarily through social media.
+(나는 주로 소셜 미디어를 통해 다른 사람들과 소통하는 것을 선호한다.)
+- Social media plays an important role in my social relationships.
+(소셜 미디어는 나의 사회적 관계에서 중요한 역할을 한다.)
+- I enjoy checking other people's social media accounts.
+(나는 다른 사람의 소셜 미디어 계정을 확인하는 것을 즐긴다.)
+- Using social media is part of my daily routine.
+(소셜 미디어를 이용하는 것은 내 일상 생활의 일부이다.)
+- I respond to content shared by others on social media (e.g., likes, comments, shares).
+(나는 다른 사람들이 소셜 미디어에 공유한 콘텐츠에 반응한다. (예: 좋아요, 댓글, 공유 등))
+[FoMO (Fear of Missing Out)]
+- I get bothered when I miss out on planned appointments with friends.
+(나는 친구들과 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+- I feel anxious when I miss a scheduled gathering.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+- I feel anxious when I do not receive news/updates from my friends.
+(나는 친구들의 소식을 접하지 못할 때 불안하다.)
+- I worry that my friends may be having rewarding experiences without me.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까봐 걱정된다.)
+- I worry that I spend too much time keeping track of what is going on around me.
+(나는 주변을 신경 쓰는데 시간을 많이 보내는 것 같아 걱정된다.)
+- I constantly check what my friends are doing even on holidays (e.g., checking Instagram stories).
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다. (예: 인스타그램 스토리 확인))
+- I fear my friends have more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+- I fear others (excluding my friends) are having better experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까봐 두렵다.)
+[비합리적 외식소비행동 - 동조소비 (Conformity Consumption)]
+- I often dine out referring to restaurants celebrities visit or menus they recommend on social media.
+(나는 소셜 미디어에서 유명인들이 방문하는 음식점이나 추천하는 메뉴를 참고해 외식을 하는 경우가 많다.)
+- I tend to visit restaurants that people I find attractive visit.
+(나는 내가 매력적이라고 생각하는 사람이 방문하는 음식점을 따라 가는 편이다.)
+- I have dined out to eat trendy foods after seeing my friends eating them.
+(나는 친구들이 유행하는 음식을 먹는 것을 보고 나도 그 음식을 먹으려고 외식을 한 적이 있다.)
+- I pay close attention to where people around me dine out.
+(나는 주위 사람들이 어디서 외식을 하는지 눈여겨본다.)
+[비합리적 외식소비행동 - 과시소비 (Conspicuous Consumption)]
+- When choosing a restaurant, I consider whether it is a well-known place recognized by others.
+(나는 음식점을 선택할 때 남들이 알아주는 유명한 곳인지 고려한다.)
+- I tend to visit restaurants that are expensive and luxurious relative to my budget to look good to others.
+(나는 남에게 잘 보이기 위해 형편에 비해 비싸고 고급스러운 음식점에 방문하는 편이다.)
+- I enjoy trying the latest trendy food before others and talking about it on social media.
+(나는 최신 유행하는 음식을 남보다 먼저 먹어보고 소셜 미디어를 통해 이야기하는 것을 즐긴다.)
+- I prefer unique restaurants or menus that reveal my individuality or differentiate me from others.
+(나는 나의 개성을 드러내거나 다른 사람들과 차별화될 수 있는 독특한 음식점이나 메뉴를 선호하는 편이다.)
+[비합리적 외식소비행동 - 충동소비 (Impulsive Consumption)]
+- I tend to dine out impulsively to relieve stress.
+(나는 스트레스를 해소하기 위해 즉흥적으로 외식을 하는 편이다.)
+- I often decide to dine out without any prior plan after seeing restaurants visited by others on social media.
+(나는 소셜 미디어에서 다른 사람이 방문한 음식점을 보고 아무 계획 없이 외식을 결정하는 경우가 많다.)
+- I tend to visit a restaurant without sufficient consideration when I see others giving it positive reviews.
+(나는 다른 사람이 음식점에 대해 좋은 평가를 하는 것을 보면 충분히 생각하지 않고 그 음식점을 방문하는 편이다.)
+- When a food becomes trendy, I tend to go and try it even if it is not something I usually like.
+(나는 어떤 음식이 유행하면 평소 좋아했던 것이 아니더라도 일단 가서 먹어보는 편이다.)</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O695"/>
+  <dimension ref="A1:O705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53693,6 +53693,1660 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>695</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>최대식</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>가상 미술관에서의 길 안내 제안: FoMO와 몰입을 중심으로</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>국민대학교 테크노디자인전문대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>몰입 이론(Flow Theory), 포모/놓침에 대한 두려움(Fear of Missing Out, FoMO), 시선 유도 및 길 찾기 이론(Wayfinding &amp; Visual Guidance Theory)</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>시선 유도 기준점(환경 기반 vs. 화면 기반) 및 시선 유도 방법 유형(고정된 선, 고정된 화살표, 가리키는 화살표, 날아가는 나비) [IV] -&gt; 시선 유도 평가(VGQ), 놓침에 대한 두려움(FoMO), 몰입(Flow) [DV]</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>H1: VR 미술관에서 시선 유도의 기준점은 평가에 유의미한 영향을 미칠 것이다.
+H1.1: VR 미술관에서 시선 유도의 기준점은 시선 유도 설문(VGQ)에 영향을 미칠 것이다.
+H1.2: VR 미술관에서 시선 유도의 기준점은 놓침에 대한 두려움(FoMO)에 영향을 미칠 것이다.
+H1.3: VR 미술관에서 시선 유도의 기준점은 몰입(Flow)에 영향을 미칠 것이다.
+H2: VR 미술관에서 시선 유도 방법은 평가에 유의미한 영향을 미칠 것이다.
+H2.1: VR 미술관에서 시선 유도 방법은 시선 유도 설문(VGQ)에 영향을 미칠 것이다.
+H2.2: VR 미술관에서 시선 유도 방법은 놓침에 대한 두려움(FoMO)에 영향을 미칠 것이다.
+H2.3: VR 미술관에서 시선 유도 방법은 몰입(Flow)에 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>시선 유도의 기준점(환경 기반/World-referenced vs. 화면 기반/Screen-referenced), 시선 유도 방법의 유형(바닥에 고정된 선, 바닥에 고정된 화살표, 가리키는 화살표, 날아가는 나비)</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>시선 유도 설문 평가(VGQ: Visual Guidance Questionnaire), 놓침에 대한 두려움(FoMO: Fear of Missing Out), 몰입(Flow)</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>1. 시선 유도의 기준점 비교에서 사용자 환경을 기반한(World-referenced) 방식이 화면을 기반한(Screen-referenced) 방식에 비해 VGQ 평가가 높았으며, FoMO를 유의하게 낮추고 몰입(Flow)을 유의하게 증진시켰음.
+2. 네 가지 시선 유도 자극물 비교 결과, '바닥에 고정된 선'이 FoMO를 가장 적게 유발하고 Flow를 가장 높였으며, VGQ 평가에서도 '바닥에 고정된 선'과 '바닥에 고정된 화살표'가 긍정적인 평가를 받음.
+3. 연구 결과를 바탕으로 가상 미술관에서 직관적 길 안내와 감상 방해 최소화를 위해 순차적 그라데이션 흐름을 활용하고 사용자가 제어 가능한 '흐르는 선' 방식을 제안함.</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>[시선 유도 설문 (Visual Guidance Questionnaire, VGQ)]
+- The guide is visually appealing.
+(가이드는 시각적으로 보기 좋다.)
+- The guide is annoying.
+(가이드는 짜증나게 한다.)
+- The guide helps to find the way.
+(가이드는 길을 찾는 데 도움이 된다.)
+[놓침에 대한 두려움 (Fear of Missing Out, FoMO)]
+- At times, I was worried that there were artworks I missed.
+(때때로, 보지 못한 작품이 있는지 걱정되었다.)
+- The worry about missing artworks affected my appreciation of the exhibition.
+(보지 못한 작품이 있을 것이라는 걱정이 작품감상에 영향을 미쳤다.)
+[몰입 (Flow)]
+- I felt bored while viewing the exhibition.
+(전시를 보는 동안 지루했다.)
+- I lost track of time while viewing the exhibition.
+(전시를 보는 동안 시간이 가는 줄 몰랐다.)
+- I was able to fully concentrate on the exhibition.
+(나는 전시에 완전히 집중할 수 있었다.)</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>696</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>고레이</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>개인화 추천시스템 특성이 지각된 혜택, 플랫폼 의존성, 플랫폼 옹호의도에 미치는 영향: FOMO의 조절효과를 중심으로</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>제주대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>애착이론(Attachment Theory), 자극-유기체-반응 모델(S-O-R Model), 프라이버시 계산 이론(Privacy Calculus Theory), 사회정체성이론(Social Identity Theory)</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>[개인화 추천시스템 특성(정확성, 보안성, 다양성, 신뢰성)] -&gt; [지각된 혜택] (FOMO 조절) -&gt; [플랫폼 의존성, 플랫폼 옹호의도]</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>H1: 온라인 쇼핑 플랫폼 개인화 추천시스템의 특성은 소비자의 지각된 혜택에 정(+)의 영향을 미칠 것이다.
+H1-1: 온라인 쇼핑 플랫폼 개인화 추천시스템의 정확성은 소비자의 지각된 혜택에 정(+)의 영향을 미칠 것이다.
+H1-2: 온라인 쇼핑 플랫폼 개인화 추천시스템의 보안성은 소비자의 지각된 혜택에 정(+)의 영향을 미칠 것이다.
+H1-3: 온라인 쇼핑 플랫폼 개인화 추천시스템의 다양성은 소비자의 지각된 혜택에 정(+)의 영향을 미칠 것이다.
+H1-4: 온라인 쇼핑 플랫폼 개인화 추천시스템의 신뢰성은 소비자의 지각된 혜택에 정(+)의 영향을 미칠 것이다.
+H2: 소비자의 온라인 쇼핑 플랫폼 개인화 추천시스템에 대한 지각된 혜택은 플랫폼 의존성에 정(+)의 영향을 미칠 것이다.
+H3: 소비자의 온라인 쇼핑 플랫폼 개인화 추천시스템에 대한 지각된 혜택은 플랫폼 옹호의도에 정(+)의 영향을 미칠 것이다.
+H4: 소비자의 플랫폼 의존성은 플랫폼 옹호의도에 정(+)의 영향을 미칠 것이다.
+H5: 소비자 FOMO에 따라 개인화 추천시스템의 특성이 지각된 혜택에 미치는 정(+)의 영향은 증가할 것이다.
+H5-1: 소비자 FOMO에 따라 개인화 추천시스템의 정확성이 지각된 혜택에 미치는 정(+)의 영향은 증가할 것이다.
+H5-2: 소비자 FOMO에 따라 개인화 추천시스템의 보안성이 지각된 혜택에 미치는 정(+)의 영향은 증가할 것이다.
+H5-3: 소비자 FOMO에 따라 개인화 추천시스템의 다양성이 지각된 혜택에 미치는 정(+)의 영향은 증가할 것이다.
+H5-4: 소비자 FOMO에 따라 개인화 추천시스템의 신뢰성이 지각된 혜택에 미치는 정(+)의 영향은 증가할 것이다.</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>개인화 추천시스템 특성 (정확성, 보안성, 다양성, 신뢰성)</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>플랫폼 의존성, 플랫폼 옹호의도</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>지각된 혜택</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>FOMO (Fear of Missing Out, 소외불안)</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>1. 개인화 추천시스템의 네 가지 특성인 정확성, 보안성, 다양성, 신뢰성은 모두 소비자의 지각된 혜택에 유의한 정(+)의 영향을 미쳤음(H1-1, H1-2, H1-3, H1-4 채택).
+2. 지각된 혜택은 플랫폼 의존성과 플랫폼 옹호의도에 각각 유의한 정(+)의 영향을 미쳤음(H2, H3 채택).
+3. 플랫폼 의존성은 플랫폼 옹호의도에 유의한 부(-)의 영향을 미쳐 기존 가설과 반대 방향의 결과를 보임(H4 기각).
+4. FOMO는 정확성 및 다양성이 지각된 혜택에 미치는 영향을 긍정적으로 조절(강화)하였으나(H5-1, H5-3 채택), 보안성 및 신뢰성과 지각된 혜택 간의 관계에서는 유의한 조절효과가 나타나지 않음(H5-2, H5-4 기각).</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>[정확성 (Accuracy)]
+- The personalized recommendation system of [Platform] recommends products that match my taste.
+(OOO의 개인화 추천시스템은 추천해주는 상품이 나의 취향에 맞는다.)
+- When searching for products on [Platform], it accurately presents the products I am looking for.
+(OOO에서 상품을 검색했을 때, 내가 찾는 상품을 정확하게 제시한다.)
+- The personalized recommendation system of [Platform] recommends products that I need.
+(OOO의 개인화 추천시스템은 나에게 필요한 상품을 추천해준다.)
+- The personalized recommendation system of [Platform] recommends products that are suitable for me.
+(OOO의 개인화 추천시스템은 나에게 맞는 상품을 추천해준다.)
+[보안성 (Security)]
+- Personal information collected by the personalized recommendation system can only be viewed by relevant data processing personnel of [Platform].
+(개인화 추천시스템에서 수집한 개인정보는 OOO 관련 데이터 처리 요원들만 볼 수 있다.)
+- The personalized recommendation system of [Platform] does not misuse collected consumer personal information.
+(OOO의 개인화 추천시스템은 수집한 소비자의 개인정보를 악용하지 않았다.)
+- The personalized recommendation system of [Platform] protects my personal usage information from unauthorized access.
+(OOO의 개인화 추천시스템은 내 개인 사용 정보를 무단 액세스로부터 보호한다.)
+- Access to my personal usage information in the personalized recommendation system of [Platform] is sufficiently restricted.
+(OOO의 개인화 추천시스템은 내 개인 사용 정보에 대한 접근이 충분히 제한되어 있다.)
+[다양성 (Diversity)]
+- The personalized recommendation system of [Platform] provides me with a wide variety of products.
+(OOO의 개인화 추천시스템은 나에게 다양한 상품을 제공한다.)
+- The personalized recommendation system of [Platform] recommends various product categories to me.
+(OOO의 개인화 추천시스템은 나에게 다양한 상품 카테고리를 추천해준다.)
+- The personalized recommendation system of [Platform] recommends products of various quality levels to me.
+(OOO의 개인화 추천시스템은 나에게 다양한 품질의 상품을 추천해준다.)
+- The personalized recommendation system of [Platform] recommends the same product according to different price ranges.
+(OOO의 개인화 추천시스템은 나에게 같은 상품을 가격대에 따라 추천해준다.)
+[신뢰성 (Reliability)]
+- I trust the products recommended to me by the personalized recommendation system of [Platform].
+(OOO의 개인화 추천시스템이 나에게 추천해준 상품을 신뢰한다.)
+- The personalized recommendation system of [Platform] recommends products from my perspective.
+(OOO의 개인화 추천시스템은 나의 입장에서 상품을 추천한다.)
+- The personalized recommendation system of [Platform] fairly recommends each product to me.
+(OOO의 개인화 추천시스템은 나에게 각 상품을 공정하게 추천해준다.)
+- The personalized recommendation system of [Platform] can be used with confidence.
+(OOO의 개인화 추천시스템은 안심하고 사용할 수 있다.)
+- The personalized recommendation system of [Platform] provides me with high-quality recommendation services.
+(OOO의 개인화 추천시스템은 나에게 양질의 추천 서비스를 제공한다.)
+[FOMO (Fear of Missing Out)]
+- When using [Platform], I feel anxious that I might not get complete information about products.
+(OOO을 이용할 때, 상품에 대한 완전한 정보를 얻지 못할까 봐 불안하다.)
+- While using [Platform], I worry that I might miss products that I like.
+(OOO을 이용하면서 마음에 드는 상품을 놓칠까 봐 걱정이 된다.)
+- When using [Platform], I fear missing out on products with discounts/benefits.
+(OOO을 이용할 때, 혜택이 있는 상품을 놓칠까 봐 두렵다.)
+- When using [Platform], I fear missing out on new products.
+(OOO을 이용할 때, 신상품을 놓칠까 봐 두렵다.)
+- I worry that the products I want to buy will be sold out by other users.
+(구매하고 싶은 상품을 다른 사용자가 다 샀을까 봐 걱정된다.)
+- Sometimes, I feel like I spend too much time just to avoid missing recommended products.
+(때로는 추천해준 상품을 놓치지 않기 위해 지나치게 많은 시간을 보내고 있는 것 같다.)
+[지각된 혜택 (Perceived Benefits)]
+- It is good that the personalized recommendation system of [Platform] reduces my search time for necessary products.
+(OOO의 개인화 추천시스템은 내가 필요한 상품의 검색 시간을 줄일 수 있어서 좋다.)
+- It is good that the personalized recommendation system of [Platform] provides the convenience of immediately finding necessary products.
+(OOO의 개인화 추천시스템은 나에게 필요한 상품을 즉시 찾아볼 수 있는 편리함을 제공해주어서 좋다.)
+- It is good that the personalized recommendation system of [Platform] gives me the choice of various products.
+(OOO의 개인화 추천시스템은 나에게 다양한 상품의 선택권을 주어서 좋다.)
+- It is good that the personalized recommendation system of [Platform] helps my reasonable consumption by recommending products with different prices.
+(OOO의 개인화 추천시스템은 나에게 가격이 다른 상품을 추천해주면 합리적인 소비에 도움이 되어서 좋다.)
+- It is good that the personalized recommendation system of [Platform] saves my purchase decision-making time.
+(OOO의 개인화 추천시스템은 구매 의사결정 시간을 절약할 수 있어서 좋다.)
+[플랫폼 의존성 (Platform Dependency)]
+- Every time I buy something, I habitually try to access [Platform].
+(나는 물건을 살 때마다 습관적으로 OOO에 접속하려고 한다.)
+- I always access [Platform] naturally.
+(나는 항상 자연스럽게 OOO에 접속한다.)
+- I prefer shopping on [Platform] rather than shopping offline.
+(나는 오프라인 쇼핑보다 OOO에서 쇼핑하는 것을 더 좋아한다.)
+- I would be disappointed if I could not buy the product I want on [Platform].
+(OOO에서 내가 원하는 상품을 사지 못하면 실망할 것이다.)
+- When [Platform] shows products I like, I feel very pleased.
+(OOO에서 내가 좋아하는 상품을 보여줄 때, 나는 매우 즐거울 것이다.)
+- I look forward to the products recommended by [Platform].
+(OOO에서 추천해준 상품을 기대한다.)
+[플랫폼 옹호의도 (Platform Advocacy Intention)]
+- I will actively promote [Platform] to others.
+(나는 OOO를 다른 사람에게 적극적으로 알릴 것이다.)
+- I recommend [Platform] to people asking for advice on online shopping platforms.
+(온라인 쇼핑 플랫폼에 대한 조언을 구하는 사람들에게 OOO를 추천한다.)
+- I am willing to encourage friends and acquaintances to use [Platform].
+(나는 친구와 지인에게 OOO 사용을 권장할 의향이 있다.)
+- I will make more effort to recommend [Platform] over other online shopping platforms.
+(다른 온라인 쇼핑 플랫폼보다 OOO를 추천하기 위해 더 노력할 것이다.)
+- As long as I need to use an online shopping platform, I will use [Platform] preferentially.
+(온라인 쇼핑 플랫폼을 사용해야 하는 한 OOO를 우선적으로 사용한다.)</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>697</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>조선숙</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>공적자의식과 SNS 중독경향성의 관계에서 소외에 대한 두려움(Fear of Missing Out: FoMO)의 매개효과</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>홍익대학교 교육대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>객관적 자기의식 이론(Objective Self-Awareness Theory), 자기결정이론(Self-Determination Theory), 사회비교이론(Social Comparison Theory), 자기해석이론(Self-Construal Theory), I-PACE 모델</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>공적자의식 -&gt; 소외에 대한 두려움(FoMO) -&gt; SNS 중독경향성</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>H1: 대학생의 공적자의식, 소외에 대한 두려움(FoMO), SNS 중독경향성 간에는 유의한 정적 상관관계가 있을 것이다.
+H2: 대학생의 공적자의식과 SNS 중독경향성의 관계에서 소외에 대한 두려움(FoMO)이 유의한 매개효과를 가질 것이다.</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>공적자의식 (Public Self-consciousness)</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>SNS 중독경향성 (SNS Addiction Proneness)</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움 (Fear of Missing Out: FoMO)</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>첫째, 공적자의식, 소외에 대한 두려움(FoMO), SNS 중독경향성은 모두 상호 간에 통계적으로 유의한 정적 상관관계를 보였다. 둘째, 공적자의식과 SNS 중독경향성의 관계에서 소외에 대한 두려움(FoMO)이 완전매개효과를 나타냈다. 즉, 소외에 대한 두려움(FoMO)을 매개변인으로 투입했을 때 공적자의식이 SNS 중독경향성에 미치는 직접효과는 유의하지 않았으나, 소외에 대한 두려움(FoMO)을 통한 간접효과는 통계적으로 유의한 것으로 확인되었다.</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>[공적자의식 척도 (Public Self-Consciousness Scale: PSCS)]
+- I care about how I handle things.
+(나는 내가 일을 처리하는 방식에 대해 신경을 쓰고 있다.)
+- I care a lot about how I should act in front of others.
+(나는 다른 사람 앞에서 어떻게 행동해야 하는지 신경을 많이 쓴다.)
+- I am conscious of how I appear to others.
+(나는 남들에게 어떻게 보일까 하는 것을 의식한다.)
+- I often worry about making a bad impression on others.
+(다른 사람에게 좋은 인상을 주지 못하면 어쩌나 하는 걱정을 하는 일이 많다.)
+- Before leaving the house, I check my clothes and appearance once more.
+(집을 나오기 전에 복장과 용모가 어떤지 다시 한 번 살펴본다.)
+- I care about what other people think of me.
+(나는 다른 사람들이 나에 대해서 어떻게 생각하는지 신경을 쓴다.)
+- I am often conscious of my appearance.
+(나는 내 외모에 대해서 의식하고 있는 경우가 많다.)
+[SNS 중독경향성 척도 (SNS Addiction Proneness Scale)]
+- I spend a lot of time thinking about SNS or planning how to use it.
+(SNS를 생각하거나 어떻게 이용할 것인가에 많은 시간을 보낸다.)
+- SNS makes me feel less lonely or alienated because I am always connected with others.
+(SNS는 내가 다른 사람과 항상 연결되어 있어 외롭거나 소외감을 덜 느끼도록 한다.)
+- I use SNS to forget about stressful problems.
+(스트레스 받는 문제를 잊기 위해 SNS를 사용한다.)
+- I sleep during class or work hours because I am tired from using SNS.
+(SNS 사용 때문에 피곤해서 수업시간 또는 업무 시간에 잔다.)
+- I think a lot about what has recently happened on SNS.
+(최근 SNS에서 일어난 일에 대해 많이 생각한다.)
+- I get irritable when I cannot use SNS.
+(SNS를 하지 못하게 되었을 때 짜증이 난다.)
+- While using SNS, I feel recognized as a person.
+(SNS를 하는 동안만큼은 내 자신이 인정을 받는다고 느낀다.)
+- I use SNS to reduce feelings of helplessness or depression.
+(무력감 또는 우울감을 줄이기 위해 SNS를 한다.)
+- I do not spend much time using SNS.
+(SNS 사용에 많은 시간을 보내지 않는다. [역코딩])
+- I have regretted not being able to reduce the time spent on SNS.
+(SNS 사용 시간을 줄이지 못해 후회한 적이 있다.)
+- I use SNS to reduce restlessness or anxiety.
+(초조함 또는 불안감을 줄이기 위해 SNS를 한다.)
+- I gain more confidence while using SNS.
+(SNS를 하는 동안 더욱 자신감이 생긴다.)
+- If I cannot use SNS, I lose joy or fun in life.
+(SNS를 하지 못하게 되면 사는 즐거움 또는 재미를 잃는다.)
+- Because of SNS, I place less importance on hobbies, leisure activities, and exercise.
+(SNS 때문에 취미, 여가생활, 운동을 덜 중요시 한다.)
+- I frequently check SNS whenever I have free time to see other people's comments.
+(SNS에서 타인의 댓글을 보기 위해 시간이 날 때마다 수시로 확인한다.)
+- I use SNS to forget personal problems.
+(개인적 문제를 잊기 위해 SNS를 한다.)
+- I used SNS so much that it had a negative impact on my work or studies.
+(SNS를 너무 많이 해서 그것이 나의 일 또는 학업에 부정적인 영향을 미쳤다.)
+- I spend most of the day using SNS.
+(하루 중 대부분의 시간을 SNS를 하며 보낸다.)
+- I use SNS to feel better.
+(기분을 좋게 하기 위해 SNS를 한다.)
+- Even while thinking 'I should stop,' I repeatedly end up using SNS.
+("그만 해야지"하면서도 번번이 SNS를 하게 된다.)
+- I feel an increasing urge to use SNS.
+(SNS를 하고 싶은 충동을 점점 더 많이 느낀다.)
+- Because of SNS, my interest in other offline activities has decreased.
+(SNS로 인해 오프라인에서의 다른 활동에 대한 흥미가 감소했다.)
+- I constantly use SNS even while walking down the street or talking with others.
+(길을 걷거나 다른 사람들과 대화 중에도 끊임없이 SNS를 한다.)
+- Because of SNS, I often fall asleep later than intended or have difficulty sleeping.
+(SNS로 인해 원하는 시간보다 더 늦게 잠들거나 잠을 이루지 못하는 일이 자주 있다.)
+[소외에 대한 두려움(FoMO) 척도 (Fear of Missing Out Scale)]
+- I fear that others have more rewarding experiences than me.
+(나는 다른 사람들이 나보다 더 유익한 경험들을 많이 했을까봐 두렵다.)
+- I fear my friends have more rewarding experiences than me.
+(나는 내 친구들이 나보다 더 유익한 경험들을 많이 했을까봐 두렵다.)
+- I get worried when I find out my friends are having fun without me.
+(나는 내 친구들이 나 없이 즐거운 시간을 보냈다는 것을 알았을 때 신경 쓰인다.)
+- It bothers me when I do not know what my friends are up to.
+(나는 친구들의 근황을 알지 못하면 신경이 쓰인다.)
+- It bothers me when I miss an appointment or get-together that was scheduled.
+(미리 약속한 모임에 나가지 못하게 되면 신경이 쓰인다.)
+- I constantly stay online so that I do not miss out on new information.
+(나는 새로운 정보를 놓치지 않기 위해 지속적으로 온라인에 접속한다.)
+- It is important to have something to talk about regarding trending issues online (e.g., videos, photos, posts, etc.).
+(온라인 상에서 최근 유행하는 이슈에 대해 말할 거리가 있는 것은 중요하다(예: 영상, 사진, 포스팅 등).)
+- It bothers me if I do not update my status or news on SNS.
+(나는 내 근황을 SNS에 업데이트하지 않으면 신경이 쓰인다.)
+- I constantly check my smartphone so that I do not miss out on new information.
+(나는 새로운 정보를 놓치지 않기 위해, 지속적으로 스마트폰을 확인한다.)
+- When I am having a good time, it is important for me to share it on SNS (e.g., status message, updating good restaurants, etc.).
+(내가 좋은 시간을 보내고 있을 때, 그것을 SNS에 공유하는 것이 나에게 중요하다(예: 상태 메시지, 맛집 업데이트 등).)
+- It is very important for me to understand jokes or slang used among friends.
+(친구들끼리 하는 농담이나 은어를 이해하는 것은 나에게 매우 중요하다.)
+- Even during vacations, I continuously check up on what my friends are doing.
+(방학 동안에도, 나는 지속적으로 친구들의 근황을 확인한다.)</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>698</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>이경진</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>기본심리욕구 불만족과 우울의 관계: 무조건적 자기수용에 의해 조절된 소외에 대한 두려움(FoMO)의 매개효과</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>경남대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>자기결정성이론(Self-Determination Theory), 사회비교이론(Social Comparison Theory), 합리정서행동치료이론(Rational Emotive Behavior Therapy)</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>[기본심리욕구 불만족] -&gt; [소외에 대한 두려움(FoMO)] -&gt; [우울] (무조건적 자기수용의 조절된 매개효과)</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>H1: 소외에 대한 두려움(FoMO)은 기본심리욕구 불만족과 우울의 관계를 매개할 것이다.
+H2: 무조건적 자기수용은 기본심리욕구 불만족과 소외에 대한 두려움(FoMO)의 관계를 조절할 것이다.
+H3: 기본심리욕구 불만족이 소외에 대한 두려움(FoMO)을 거쳐 우울에 미치는 매개효과는 무조건적 자기수용의 수준에 의해 조절될 것이다(조절된 매개효과).</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>기본심리욕구 불만족</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>우울</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO)</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>무조건적 자기수용</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>첫째, 기본심리욕구 불만족은 소외에 대한 두려움(FoMO)을 유의미하게 증가시키고, 이는 다시 우울을 유의하게 예측하여 FoMO의 매개효과가 지지되었다. 둘째, 기본심리욕구 불만족과 FoMO 간의 관계에서 무조건적 자기수용의 조절효과가 유의미하게 나타났다(무조건적 자기수용이 높은 집단에서 기본심리욕구 불만족이 FoMO에 미치는 정적 영향력이 더욱 두드러짐). 셋째, 기본심리욕구 불만족이 FoMO를 거쳐 우울로 이어지는 간접경로에서 무조건적 자기수용의 조절된 매개효과가 유의하게 검증되었다.</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>[기본심리욕구 불만족 / Basic Psychological Needs Dissatisfaction]
+- I feel that I am controlled and pressured by others.
+(나는 다른 사람들에 의해 통제받고 억압을 받는다고 느낀다.)
+- I do not have much opportunity to decide for myself how to go about my work.
+(내 일을 진행하는 방법을 스스로 결정할 기회가 많지 않다.)
+- In my daily life, I frequently have to do what I am told.
+(일상생활에서 나는 자주 남이 시키는 대로 해야만 한다.)
+- I feel that I am generally free to express my ideas and opinions.
+(나는 대체로 내 생각과 의견을 자유롭게 표현할 수 있다고 느낀다.)
+- I feel like I can pretty much decide how to live my life.
+(나는 내가 내 인생을 어떻게 살아갈지 스스로 결정할 수 있다고 느낀다.)
+- When I do something, I often follow other people's opinions or ways rather than doing it my own way.
+(어떤 일을 할 때, 내 생각대로 일을 처리하기 보다는 다른 사람의 생각이나 처리 방식을 따를 때가 많다.)
+- I feel that I am very efficient.
+(나는 내 자신이 매우 효율적이라고 느낀다.)
+- Most of the time I feel a sense of accomplishment from what I do.
+(나는 대부분 내가 하는 일들로부터 성취감을 느낀다.)
+- People I know tell me I am good at what I do.
+(나를 아는 사람은 내가 일을 잘한다고 말한다.)
+- I feel capable of doing the things that are given to me.
+(나는 내게 주어진 일을 잘 해결할 능력이 있다고 느낀다.)
+- I feel that I can teach others what I know.
+(나는 내가 아는 것을 다른 사람에게 가르칠 수 있다고 느낀다.)
+- I feel that I am better at doing many things than other people.
+(나는 다른 사람보다 잘하는 것이 많다고 느낀다.)
+- I feel that people around me love and care about me.
+(나는 주변 사람들로부터 사랑과 관심을 받는 것을 느낀다.)
+- People whom I meet regularly do not seem to like me much.
+(나와 정기적으로 만나는 사람들은 나를 별로 좋아하지 않는 것 같다.)
+- I get along with people I meet.
+(나는 내가 만나는 사람들과 잘 지낸다.)
+- I really like the people around me.
+(나는 내 주변 사람들을 정말 좋아한다.)
+- People around me and I usually give and take help with each other.
+(내 주변 사람들과 나는 평소에 서로 도움을 주고받는다.)
+- People around me often share their feelings with me.
+(내 주변 사람들은 평소에 나와 감정을 공유할 때가 많다.)
+[소외에 대한 두려움 / Fear of Missing Out (FoMO)]
+- I fear others have more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+- I get anxious when I don't know what my friends are up to.
+(나는 친구들의 소식을 접하지 못할 때 불안하다.)
+- I get worried when I find out my friends are having fun without me.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까봐 걱정된다.)
+- I fear my friends have more rewarding experiences than me, excluding best friends.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까봐 두렵다.)
+- It is important that I understand what my friends are talking about.
+(나는 주변을 신경 쓰는 데 시간을 많이 보내는 것 같아 걱정된다.)
+- When I miss out on a planned get-together, it bothers me.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+- When I miss out on a planned meeting, I feel anxious.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+- When I have a good time it is important for me to share the details online (e.g. updating status).
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다. 예: 친구들의 SNS 상태 업데이트)
+[무조건적 자기수용 / Unconditional Self-Acceptance]
+- Even when I do not achieve an important goal, I think I am a valuable person.
+(나에게 중요한 어떤 목표를 이루지 못한다 해도, 나는 가치 있는 사람이라 생각한다.)
+- When I receive negative feedback, I take it as an opportunity to improve my behavior or performance.
+(나는 부정적인 피드백을 받으면, 그것을 내 행동 혹은 수행을 향상시킬 수 있는 기회로 삼는다.)
+- If I make a big mistake, I will be disappointed, but my overall opinion of myself does not change.
+(내가 큰 실수를 저지른다면 실망스럽긴 하겠지만, 내 자신에 대한 전반적인 생각에는 변함이 없다.)
+- I sometimes wonder whether I am a good or bad person.
+(나는 때때로 내가 좋은 사람인지 혹은 나쁜 사람인지에 대해 생각하곤 한다.)
+- In order to feel that I am a person of worth, I must be loved by the people who are important to me.
+(내가 가치 있는 사람이라고 느낄 수 있으려면, 나에게 중요한 사람들로부터 사랑을 받아야만 한다.)
+- My sense of self-worth is greatly affected by comparing myself with others.
+(나의 자기가치감은 다른 사람들과 나를 비교한 결과에 의해 많이 영향을 받는다.)
+- I believe I am a worthwhile person simply because I am human.
+(내가 그저 한 인간이라는 사실만으로도 나는 가치로운 존재라고 생각한다.)
+- When I am not good at something, I feel less worthwhile as a person.
+(내가 어떤 것들에 능숙하지 못하면, 내 자신이 덜 가치롭게 느껴진다.)
+- I think people who are successful in their work are particularly worthwhile.
+(나는 자신이 하는 일에서 성공한 사람들은 특별히 가치 있는 사람들이라 생각한다.)
+- Even if other people do not approve of me, I consider myself a worthwhile person.
+(다른 사람들이 나를 인정해주지 않더라도, 나는 가치로운 사람이라고 생각한다.)
+- I do not compare myself with others to judge whether I am a person of worth.
+(내가 가치로운 사람인지를 판단하기 위해 다른 사람과 비교를 하진 않는다.)
+- Even if I am criticized or fail at something, I still consider myself a valuable human being.
+(내가 비난을 받거나 어떤 일에 실패한다 해도, 나는 한 인간으로서 가치 있다고 생각한다.)
+[우울 / Depression (CES-D)]
+- I was bothered by things that usually don't bother me.
+(평소에는 아무렇지도 않던 일들이 귀찮게 느껴졌다.)
+- I did not feel like eating; my appetite was poor.
+(먹고 싶지 않았다. 입맛이 없었다.)
+- I felt that I could not shake off the blues even with help from my family or friends.
+(가족이나 친구가 도와주더라도 울적한 기분을 떨쳐버릴 수 없었다.)
+- I felt that I was just as good as other people.
+(다른 사람들만큼 능력이 있다고 느꼈다.)
+- I had trouble keeping my mind on what I was doing.
+(무슨 일을 하던 정신을 집중하기가 힘들었다.)
+- I felt depressed.
+(우울했다.)
+- I felt that everything I did was an effort.
+(하는 일마다 힘들게 느껴졌다.)
+- I felt hopeful about the future.
+(미래에 대하여 희망적으로 느꼈다.)
+- I thought my life had been a failure.
+(내 인생은 실패작이라는 생각이 들었다.)
+- I felt fearful.
+(두려움을 느꼈다.)
+- My sleep was restless.
+(잠을 설쳤다. 잠을 잘 이루지 못했다.)
+- I was happy.
+(행복했다.)
+- I talked less than usual.
+(평소보다 말을 적게 했다. 말수가 줄었다.)
+- I felt lonely.
+(세상에 홀로 있는 듯한 외로움을 느꼈다.)
+- People were unfriendly.
+(사람들이 나에게 차갑게 대하는 것 같았다.)
+- I enjoyed life.
+(생활이 즐거웠다.)
+- I had crying spells.
+(갑자기 울음이 나왔다.)
+- I felt sad.
+(슬픔을 느꼈다.)
+- I felt that people dislike me.
+(사람들이 나를 싫어하는 것 같았다.)
+- I could not get going.
+(도무지 무엇을 시작할 기운이 나지 않았다.)</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>I804:null-200000399678</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>699</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>전소연</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>남녀 대학생의 ‘소외에 대한 두려움’이 주관적 안녕감에 미치는 영향: FoMO 척도 적용을 중심으로</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>덕성여자대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), 사회비교이론(Social Comparison Theory), 라자루스와 포크만의 인지적 스트레스-대처 이론(Cognitive Stress and Coping Theory)</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(소속욕구, 외적동기, 상대적박탈감) -&gt; 소극적 대처방식(정서중심 대처, 소망적사고) -&gt; 주관적 안녕감(삶의 만족도, 정적정서, 부적정서) [성별 비교/조절]</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>H1: 소외에 대한 두려움, 대처방식, 주관적 안녕감은 성별에 따른 차이가 있을 것이다.
+H1-1: 소외에 대한 두려움은 성별에 따른 차이가 있을 것이다.
+H1-2: 대처방식은 성별에 따른 차이가 있을 것이다.
+H1-3: 주관적 안녕감은 성별에 따른 차이가 있을 것이다.
+H2: 소외에 대한 두려움과 대처방식 및 주관적 안녕감은 상관관계가 있을 것이다.
+H2-1: 소외에 대한 두려움과 대처방식은 상관관계가 있을 것이다.
+H2-2: 소외에 대한 두려움과 주관적 안녕감은 상관관계가 있을 것이다.
+H2-3: 대처방식과 주관적 안녕감은 상관관계가 있을 것이다.
+H3: 소외에 대한 두려움 및 그 하위요인들이 주관적 안녕감에 영향을 미칠 때, 소극적 대처방식이 매개할 것이다.
+H3-1: 소속욕구가 주관적 안녕감에 영향을 미칠 때 소극적 대처방식이 매개할 것이다.
+H3-2: 외적동기가 주관적 안녕감에 영향을 미칠 때 소극적 대처방식이 매개할 것이다.
+H3-3: 상대적 박탈감이 주관적 안녕감에 영향을 미칠 때 소극적 대처방식이 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO: Fear of Missing Out; 하위요인: 소속욕구, 외적동기, 상대적박탈감)</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>주관적 안녕감(Subjective Well-Being; 하위요인: 삶의 만족도, 정적정서, 부적정서)</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>소극적 대처방식(Passive Coping; 하위요인: 정서중심 대처, 소망적사고)</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>성별(Gender: 남학생 vs. 여학생 집단 비교)</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>1. 성별 차이: 소외에 대한 두려움 전체 및 모든 하위요인(소속욕구, 외적동기, 상대적박탈감)과 소극적 대처방식은 여학생이 남학생보다 유의하게 높았으며, 삶의 만족도와 정적정서는 남학생이 여학생보다 유의하게 높았다.
+2. 상관관계: 남녀 모두 소외에 대한 두려움 및 하위요인은 부적정서와 유의한 정적 상관을 보였다. 남학생의 경우 소외에 대한 두려움, 외적동기, 상대적박탈감이 삶의 만족도와 유의한 부적 상관을 보였으나, 여학생에게서는 유의한 상관이 나타나지 않았다. 적극적 대처는 남녀 모두에서 삶의 만족도 및 정적정서와 정적 상관을 보였으나, 소극적 대처는 여학생 집단에서만 부적정서와 유의한 정적 상관을 보였다.
+3. 매개효과: 여학생 집단에서는 소외에 대한 두려움 전체, 외적동기, 상대적박탈감이 부적정서에 미치는 영향에서 소극적 대처방식이 부분 매개효과를 가지는 것으로 나타났다(소속욕구는 매개효과 유의하지 않음). 반면, 남학생 집단에서는 소극적 대처방식의 매개효과가 유의하지 않았다.</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>[소외에 대한 두려움 (FoMO Scale)]
+- I fear others have more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+- I get anxious when I don't know what my friends are up to.
+(나는 친구들의 소식을 접하지 못할 때 불안하다.)
+- I fear my friends have more rewarding experiences than me when I am not around.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까봐 걱정된다.)
+- I fear others, except my close friends, have more rewarding experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까봐 두렵다.)
+- I worry that I spend too much time keeping up with what is going on around me.
+(나는 주변을 신경 쓰는 데 시간을 많이 보내는 것 같아 걱정된다.)
+- It bothers me when I miss an opportunity to meet up with friends unexpectedly.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못 하면 신경이 쓰인다.)
+- I get anxious when I miss a planned get-together.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+- When I have a good time it is important for me to share the details online / I continually check what my friends are doing even on holidays.
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다.)
+[스트레스 대처방식 척도 (Ways of Coping Checklist)]
+- I make a plan of action and follow it.
+(활동계획을 세우고 그것에 따른다.)
+- I know what has to be done, so I double my efforts to make things work.
+(무엇을 해야 할지를 알기 때문에 상황이 잘 되도록 더 열심히 노력한다.)
+- I wish that the situation would go away or somehow be over with.
+(상황이 어떻게 되었으면 좋겠다는 공상이나 소망을 한다.)
+- I picture in my mind a better time or place than the one I am in.
+(자신이 처한 지금의 상황보다 더 좋은 경우를 상상하거나 공상을 한다.)
+- I talk to someone who could do something concrete about the problem.
+(상황을 구체화 시킬 수 있는 사람과 이야기를 한다.)
+- I ask a relative or friend I respect for advice.
+(존경하는 친척이나 친구에게 조언을 구한다.)
+- I try to forget the whole thing.
+(모든 것을 잊어버리려고 노력한다.)
+- I go on as if nothing has happened / I don't take it too seriously.
+(그 상황을 무시해 버리거나 그것을 너무 심각하게 받아들이지 않는다.)
+- I get a clue to do something creative in the situation.
+(그 상황에서 무엇인가 창조적인 일을 할 수 있는 단서를 얻는다.)
+- I change something so things will turn out all right.
+(상황이 잘되어 나갈 수 있도록 무엇인가를 변화시킨다.)
+- I attribute it to bad luck since bad luck happens sometimes.
+(운이 나쁠 때도 있으니까 운으로 돌린다.)
+- I act as if nothing happened.
+(아무 일도 안 일어난 것처럼 군다.)
+- I wish that the situation would disappear or end.
+(그 상황이 사라지거나 끝나버리기를 바란다.)
+- I wish that I could change what happened or how I felt.
+(일어난 상황이나 나의 느낌을 바꿀 수 있기를 바란다.)
+- I talk to someone about how I am feeling.
+(자신이 느끼고 있는 바를 누구에게 말한다.)
+- I talk to someone to find out more about the situation.
+(그 상황에 대해 좀 더 알아보려고 누군가와 이야기 한다.)
+- I analyze the situation closely to understand it better.
+(그 상황을 더 잘 이해하기 위하여 그것을 자세히 분석해본다.)
+- I focus on what I have to do next.
+(다음 단계에서는 어떻게 해야 할 것인지에 대하여 전념한다.)
+- I do other things or activities to take my mind off the situation.
+(그 상황을 잊기 위하여 다른 일을 하거나 다른 활동을 한다.)
+- I take it out on other people.
+(다른 사람들에게 분풀이를 한다.)
+- I remind myself that things could be worse than they are now.
+(그 상황이 지금보다 더 나쁠 수도 있었음을 스스로 일깨운다.)
+- I pray for things to get better.
+(그 상황이 잘 되게 해 달라고 기도를 한다.)
+- I ask for professional help.
+(전문적인 도움을 청한다.)
+- I accept sympathy and understanding from others.
+(다른 사람들의 동정과 이해를 받아들인다.)
+[한국판 정적정서·부적정서 척도 (K-PANAS-R)]
+- Interested
+(흥미로웠다.)
+- Irritable
+(짜증스러웠다.)
+- Distressed
+(괴로웠다.)
+- Alert
+(맑은 정신이었다.)
+- Excited
+(신이 났다.)
+- Ashamed
+(부끄러웠다.)
+- Upset / Angry
+(화가 났다.)
+- Inspired
+(영감을 받았다.)
+- Strong
+(강인했다.)
+- Nervous / Jittery
+(긴장했다.)
+- Guilty
+(죄책감이 들었다.)
+- Determined
+(확고했다.)
+- Scared
+(겁이 났다.)
+- Attentive
+(주의 깊었다.)
+- Hostile
+(적대적이었다.)
+- Jittery / Anxious
+(초조했다.)
+- Enthusiastic
+(열정적이었다.)
+- Active
+(활기찼다.)
+- Proud
+(자랑스러웠다.)
+- Afraid
+(두려웠다.)
+[한국판 삶의 만족도 척도 (K-SWLS)]
+- In most ways my life is close to my ideal.
+(대부분의 측면에서 나의 삶은 나의 이상에 가깝다.)
+- The conditions of my life are excellent.
+(내 삶의 조건들은 아주 좋다.)
+- I am satisfied with my life.
+(나는 내 삶에 대하여 만족한다.)
+- So far I have gotten the important things I want in life.
+(지금까지 내 삶에서 내가 원하는 중요한 것들을 소유해 왔다.)
+- If I could live my life over, I would change almost nothing.
+(만약, 내 삶을 다시 살 수 있더라도, 나는 거의 아무것도 바꾸지 않을 것이다.)</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>http://uci.or.kr/I804:11019-200000108450</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>700</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>강민지</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>대학생용 SNS 소외에 대한 두려움 (SNS FoMO) 척도 개발 및 타당화</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>서울여자대학교 일반대학원 교육심리학과 상담 및 임상심리 전공 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), 사회비교이론(Social Comparison Theory), 사회감시체계(Social Monitoring System) 이론</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>[선행연구 고찰, FGI, 2차 자료 분석] -&gt; [예비문항 도출 및 내용타당도 검증] -&gt; [예비조사(EFA)] -&gt; [본조사(EFA &amp; CFA)] -&gt; [대학생용 SNS FoMO 척도 4요인 23문항 확정] -&gt; [준거타당도 및 수렴타당도 검증]</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>연구문제 1: 대학생용 SNS 소외에 대한 두려움 척도의 구성요인과 문항은 무엇인가?
+연구문제 2: 대학생용 SNS 소외에 대한 두려움 척도의 신뢰도는 어떠한가?
+연구문제 3: 대학생용 SNS 소외에 대한 두려움 척도의 구인타당도는 어떠한가?
+연구문제 4: 대학생용 SNS 소외에 대한 두려움 척도의 준거타당도와 수렴타당도는 어떠한가?</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>대학생용 SNS 소외에 대한 두려움(SNS FoMO)</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>1. 대학생용 SNS 소외에 대한 두려움(SNS FoMO) 척도는 탐색적 요인분석 및 확인적 요인분석을 거쳐 '불안 및 일상생활 장해(6문항)', '상대적 박탈감(6문항)', '강박적 확인 행동(6문항)', '소속 욕구(5문항)'의 총 4개 요인, 23개 문항으로 최종 개발 및 확정되었다.
+2. 확인적 요인분석 결과, 수정 4요인 모형의 적합도(TLI = .911, CFI = .921, RMSEA = .072)가 적절한 수준을 나타내어 구인타당도가 입증되었다.
+3. 전체 척도의 내적 일치도 신뢰도(Cronbach's α)는 .96이었으며, 하위요인별 신뢰도는 .85~.90으로 우수한 신뢰도를 확보하였다.
+4. 수정 소외에 대한 두려움 척도(상태 FoMO)와의 상관분석을 통해 준거타당도(r = .77, p &lt; .01)를 확보하였고, SNS 중독경향성 척도와의 상관분석을 통해 수렴타당도(r = .82, p &lt; .01)를 확인하였다.</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>[요인 1: 불안 및 일상생활 장해]
+- I find it difficult to concentrate on important academic schedules such as exams or assignments because I am concerned about what is happening on SNS.
+(나는 SNS에서 일어나는 일을 신경쓰느라 시험, 과제 등 중요한 학업 일정에 집중하기가 어렵다.)
+- I cannot concentrate on meals because I check SNS updates (new content) even while eating.
+(나는 식사 중에도 SNS 업데이트(새로운 내용)를 확인하느라 식사에 집중하지 못한다.)
+- I have experienced deteriorating health (e.g., neck and finger pain) due to frequent and prolonged SNS use for fear of missing out on news about gatherings and activities.
+(나는 모임, 활동 등의 소식을 놓칠까봐 SNS를 자주, 오래 사용하느라 건강이 악화되었다(예: 목, 손가락 통증).)
+- I become anxious when I do not know about recent trending issues on SNS.
+(나는 SNS에서 최근 화제가 되는 이슈를 모르는 경우 초조해진다.)
+- I cannot concentrate on conversations because I use SNS even while talking in real life (offline).
+(나는 현실(오프라인)에서 대화를 하는 중에도 SNS를 하느라 대화에 집중하지 못한다.)
+- I feel anxious when I feel like I cannot keep up with trending flows on SNS.
+(나는 SNS에서 유행하는 흐름을 따라가지 못한다고 느낄 때 불안하다.)
+[요인 2: 상대적 박탈감]
+- I feel like I am the only one excluded when I see people having more rewarding experiences than me on SNS.
+(나는 SNS에서 사람들이 나보다 더 유익한 경험을 하는 것을 볼 때 나만 소외된 것 같은 기분이 든다.)
+- I compare my life with others when looking at posts recommended by SNS showing people looking successful or happy.
+(나는 SNS 추천 게시물에서 타인의 성공이나 행복해 보이는 모습을 보고 나의 삶과 비교한다.)
+- I often feel a sense of loss when I see posts on SNS where people look happier than me.
+(나는 종종 SNS에서 사람들이 나보다 더 행복해 보이는 게시물을 볼 때 상실감을 느낀다.)
+- I feel like I have missed an important opportunity if I cannot keep up with others' activities or experiences (e.g., competitions, certifications) seen on SNS.
+(나는 SNS에서 본 타인의 활동이나 경험(예: 공모전, 자격증 등)을 따라 하지 못하면 중요한 기회를 잃은 것 같은 기분이 든다.)
+- Because the experiences people have on SNS look beneficial, I feel pressured that I must have the same experiences as them.
+(나는 SNS에서 사람들이 하는 경험이 유익해 보여서, 나도 그들과 같은 경험을 해야만 할 것 같은 부담을 느낀다.)
+- I feel left behind when I see acquaintances' posts about visiting 'hot spots' (popular travel destinations, restaurants, etc.) on SNS.
+(나는 SNS에서 핫플(Hot Place: 인기 여행지‧식당 등)에 다녀온 주변인의 게시물을 볼 때 뒤처지는 느낌이 든다.)
+[요인 3: 강박적 확인 행동]
+- I unconsciously and repeatedly check SNS even when no new notifications arrive.
+(나는 새로운 알림이 오지 않아도 무의식적으로 SNS를 반복해서 확인한다.)
+- I constantly check the reactions of people around me to my SNS posts.
+(나는 나의 SNS 게시물에 대한 주변 사람들의 반응을 계속 확인하게 된다.)
+- I frequently check updates on friends' or acquaintances' recent status on SNS even while resting (e.g., status updates of friends).
+(나는 쉬고 있는 동안에도 SNS에서 친구 혹은 지인들의 근황을 수시로 확인한다. (예: 친구들의 SNS 상태 업데이트))
+- When there is new information on SNS, I feel that I must check it immediately.
+(나는 SNS에 새로운 정보가 있을 때 그 즉시 확인해야만 한다.)
+- I frequently check SNS thinking that the SNS algorithm will present the latest information related to my interests.
+(나는 SNS 알고리즘이 관심사와 관련된 최신 정보를 제시해줄 것 같아서 SNS를 자주 확인하게 된다.)
+- Once I start checking SNS post updates, it is hard to stop using SNS.
+(나는 SNS 게시물 업데이트를 확인하기 시작하면 SNS를 그만 두기가 어렵다.)
+[요인 4: 소속 욕구]
+- I worry that friends or acquaintances might be having conversations on SNS without including me.
+(나는 SNS에서 친구 혹은 지인이 나를 포함하지 않고 대화를 할까봐 걱정된다.)
+- I feel anxious or restless if I do not know the recent status of people around me on SNS.
+(나는 SNS에서 주변 사람들의 근황을 알지 못하면 불안해지거나 초조하다.)
+- I feel upset when people around me share posts or talk on SNS without tagging me.
+(나는 SNS에서 주변 사람들이 나를 태그하지 않고 게시물을 공유하거나 대화를 하면 섭섭하다.)
+- I frequently care about whether I am included in the private account follow list or restricted groups (e.g., close friends, partial access) of friends or acquaintances on SNS.
+(나는 친구 혹은 지인 SNS의 비공개 계정 팔로우 목록, 특정 제한 그룹(예: 친한 친구, 일부 공개 등)에 내가 포함되었는지 자주 신경을 쓴다.)
+- I care about the number of followings and followers on SNS.
+(나는 SNS의 팔로잉, 팔로워 숫자에 신경이 쓰인다.)</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>701</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>박영민</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>대학생의 기본심리욕구 만족과 SNS중독경향성의 관계: 소외에 대한 두려움(FoMO)과 부정정서(우울/불안)의 매개 효과</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>가톨릭대학교 상담심리대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>자기결정성이론 (Self-Determination Theory), 기본심리욕구이론 (Basic Psychological Needs Theory), 선택이론 (Choice Theory)</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>[기본심리욕구 만족] -&gt; [소외에 대한 두려움(FoMO)] -&gt; [부정정서(우울/불안)] -&gt; [SNS중독경향성]</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>H1-1: 기본심리욕구 만족과 소외에 대한 두려움은 유의한 부적상관이 있을 것이다.
+H1-2: 기본심리욕구 만족과 부정정서(우울/불안)는 유의한 부적 상관이 있을 것이다.
+H1-3: 기본심리욕구 만족과 SNS중독경향성은 유의한 부적 상관이 있을 것이다.
+H1-4: 소외에 대한 두려움과 부정정서(우울/불안)는 유의한 정적 상관이 있을 것이다.
+H1-5: 소외에 대한 두려움과 SNS중독경향성은 유의한 정적 상관이 있을 것이다.
+H1-6: 부정정서(우울/불안)와 SNS중독경향성은 유의한 정적 상관이 있을 것이다.
+H2-1: 기본심리욕구 만족과 SNS중독경향성의 관계를 소외에 대한 두려움이 매개할 것이다.
+H2-2: 기본심리욕구 만족과 SNS중독경향성의 관계를 부정정서(우울/불안)가 매개할 것이다.
+H2-3: 기본심리욕구 만족은 소외에 대한 두려움과 부정정서(우울/불안)를 순차적으로 매개하여, SNS중독경향성에 유의한 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>기본심리욕구 만족 (자율성, 유능성, 관계성)</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>SNS중독경향성 (일상생활장애 및 조절실패, 몰입 및 내성, 부정 정서의 회피, 가상세계지향성 및 금단)</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO), 부정정서(우울/불안)</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>1. 기본심리욕구 만족은 소외에 대한 두려움, 부정정서(우울/불안), SNS중독경향성과 유의한 부적 상관관계를 나타냈다.
+2. 기본심리욕구 만족이 SNS중독경향성에 미치는 직접 경로효과는 유의하지 않았으나, 소외에 대한 두려움과 부정정서(우울/불안)가 SNS중독경향성에 미치는 직접 경로는 유의하였다.
+3. 기본심리욕구 만족은 소외에 대한 두려움 및 부정정서(우울/불안)를 각각 매개하여 SNS중독경향성에 영향을 미치며, 소외에 대한 두려움과 부정정서를 순차적으로 이중매개하여 SNS중독경향성에 영향을 미치는 유의한 경로가 확인되었다.</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>[기본심리욕구 만족 척도 (BPNS)]
+I feel that I am very efficient.
+(나는 내 자신이 매우 효율적이라고 느낀다.)
+I feel controlled and pressured by others.
+(나는 다른 사람들에 의해 통제받고 억압을 받는다고 느낀다.)
+I feel love and care from people around me.
+(나는 내 주변 사람들로부터 사랑과 관심을 받는 것을 느낀다.)
+I don't have many opportunities to decide for myself how to do my work.
+(내 일을 진행하는 방법을 스스로 결정할 기회가 많지 않다.)
+I feel a sense of accomplishment from most of the things I do.
+(나는 대부분 내가 하는 일들로부터 성취감을 느낀다.)
+People I meet regularly don't seem to like me very much.
+(나와 정기적으로 만나는 사람들은 나를 별로 좋아하지 않는 것 같다.)
+I get along well with the people I meet.
+(나는 내가 만나는 사람들과 잘 지낸다.)
+People who know me say I am good at my job.
+(나를 아는 사람은 내가 일을 잘한다고 말한다.)
+In daily life, I often have to do what others tell me to do.
+(일상생활에서 나는 자주 남이 시키는 대로 해야만 한다.)
+I really like the people around me.
+(나는 내 주변 사람들을 정말 좋아한다.)
+I generally feel free to express my ideas and opinions.
+(나는 대체로 내 생각과 의견을 자유롭게 표현할 수 있다고 느낀다.)
+My surrounding people and I usually help each other.
+(내 주변 사람들과 나는 평소에 서로 도움을 주고받는다.)
+I feel capable of solving the tasks given to me.
+(나는 내게 주어진 일을 해결할 능력이 있다고 느낀다.)
+I feel I can decide for myself how to live my life.
+(나는 내가 내 인생을 어떻게 살아갈지 스스로 결정할 수 있다고 느낀다.)
+People around me often share emotions with me.
+(내 주변사람들은 평소에 나와 감정을 공유할 때가 많다.)
+I feel I can teach others what I know.
+(나는 내가 아는 것을 다른 사람들에게 가르칠 수 있다고 느낀다.)
+When doing something, I often follow others' thoughts or methods rather than my own.
+(어떤 일을 할 때 내 생각대로 일을 처리하기 보다는 다른 사람의 생각이나 처리 방식을 따를 때가 많다.)
+I feel I am better at many things than other people.
+(나는 다른 사람보다 잘 하는 것이 많다고 느낀다.)
+[소외에 대한 두려움(FoMO) 척도]
+I fear my friends may have more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+I get anxious when I don't know what my friends are up to.
+(나는 내 친구들의 소식을 접하지 못할 때 불안하다.)
+I worry my friends are having fun experiences without me.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까봐 걱정된다.)
+I fear others except my friends may have better experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까봐 두렵다.)
+I worry that I spend too much time keeping up with what's going on.
+(나는 주변을 신경 쓰는 데 시간을 많이 보내는 것 같아 걱정된다.)
+It bothers me when I miss an impromptu get-together with friends.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+I get anxious when I miss a scheduled meeting.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+I continuously check what my friends are doing even on holidays.
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다.)
+[부정정서 - 우울 척도 (CES-D)]
+I was bothered by things that usually don't bother me.
+(평소에는 아무렇지도 않던 일들이 귀찮게 느껴졌다.)
+I did not feel like eating; my appetite was poor.
+(먹고 싶지 않았다; 입맛이 없었다.)
+I felt that I could not shake off the blues even with help from my family or friends.
+(가족이나 친구가 도와주더라도 울적한 기분을 떨쳐버릴 수 없었다.)
+I felt I was just as good as other people.
+(다른 사람들만큼 능력이 있다고 느꼈다.)
+I had trouble keeping my mind on what I was doing.
+(무슨 일을 하든 정신을 집중하기가 힘들었다.)
+I felt depressed.
+(우울했다.)
+I felt that everything I did was an effort.
+(하는 일마다 힘들게 느껴졌다.)
+I felt hopeful about the future.
+(미래에 대하여 희망적으로 느꼈다.)
+I thought my life had been a failure.
+(내 인생은 실패작이라는 생각이 들었다.)
+I felt fearful.
+(두려움을 느꼈다.)
+My sleep was restless.
+(잠을 설쳤다; 잠을 잘 이루지 못했다.)
+I was happy.
+(행복했다.)
+I talked less than usual.
+(평소보다 말을 적게 했다; 말수가 줄었다.)
+I felt lonely, as if I were all alone in the world.
+(세상에 홀로 있는 듯한 외로움을 느꼈다.)
+People were unfriendly to me.
+(사람들이 나에게 차갑게 대하는 것 같았다.)
+I enjoyed life.
+(생활이 즐거웠다.)
+I had crying spells.
+(갑자기 울음이 나왔다.)
+I felt sad.
+(슬픔을 느꼈다.)
+I felt that people disliked me.
+(사람들이 나를 싫어하는 것 같았다.)
+I could not get going.
+(도무지 무엇을 시작할 기운이 나지 않았다.)
+[부정정서 - 상태 불안 척도 (STAI)]
+I feel calm.
+(나는 마음이 차분하다.)
+I feel secure.
+(나는 마음이 든든하다.)
+I am tense.
+(나는 긴장되어 있다.)
+I feel regretful and disappointed.
+(후회스럽고 서운하다.)
+I feel at ease.
+(나는 마음이 편하다.)
+I feel upset and don't know what to do.
+(나는 당황해서 어찌할 바를 모르겠다.)
+I am worrying over possible misfortunes.
+(나는 앞으로 불행이 올까봐 걱정하고 있다.)
+I feel relieved.
+(나는 마음이 놓인다.)
+I feel anxious.
+(나는 마음이 불안하다.)
+I feel comfortable.
+(나는 편안하게 느낀다.)
+I feel confident.
+(나는 자신감이 있다.)
+I feel irritated.
+(나는 짜증스럽다.)
+I feel jittery.
+(나는 마음이 조마조마하다.)
+I feel high tension.
+(나는 극도로 긴장되어 있다.)
+I feel relaxed.
+(내 마음은 긴장이 풀려 푸근하다.)
+I feel content.
+(나는 만족스럽다.)
+I am worried.
+(나는 걱정하고 있다.)
+I feel overly excited and confused.
+(나는 흥분되어 어쩔 줄 모르겠다.)
+I feel joyful.
+(나는 즐겁다.)
+I feel pleasant.
+(나는 기분이 좋다.)
+[SNS중독경향성 척도]
+I spend a lot of time thinking about SNS or planning how to use it.
+(SNS를 생각하거나 어떻게 이용할 것인가에 많은 시간을 보낸다.)
+SNS helps me stay connected with others so I feel less lonely or isolated.
+(SNS는 내가 다른 사람과 항상 연결되어 있어 외롭거나 소외감을 덜 느끼도록 한다.)
+I use SNS to forget about stressful problems.
+(스트레스 받는 문제를 잊기 위해 SNS를 사용한다.)
+I sleep during class or work because I am tired from using SNS.
+(SNS 사용 때문에 피곤해서 수업시간 또는 업무 시간에 잔다.)
+I think a lot about what recently happened on SNS.
+(최근 SNS에서 일어난 일에 대해 많이 생각한다.)
+I feel annoyed when I am unable to use SNS.
+(SNS를 하지 못하게 되었을 때 짜증이 난다.)
+I feel recognized as long as I am on SNS.
+(SNS를 하는 동안만큼은 내 자신이 인정을 받는다고 느낀다.)
+I use SNS to reduce feelings of helplessness or depression.
+(무력감 또는 우울감을 줄이기 위해 SNS를 한다.)
+I do not spend much time using SNS.
+(SNS 사용에 많은 시간을 보내지 않는다.)
+I have regretted not being able to reduce my SNS usage time.
+(SNS 사용 시간을 줄이지 못해 후회한 적이 있다.)
+I use SNS to reduce nervousness or anxiety.
+(초조함 또는 불안감을 줄이기 위해 SNS를 한다.)
+I feel more confident while using SNS.
+(SNS를 하는 동안 더욱 자신감이 생긴다.)
+When I cannot use SNS, I lose the joy or fun of living.
+(SNS를 하지 못하게 되면 사는 즐거움 또는 재미를 잃는다.)
+Because of SNS, I place less importance on hobbies, leisure activities, or exercise.
+(SNS 때문에 취미, 여가생활, 운동을 덜 중요시 한다.)
+I check SNS frequently whenever I have time to see comments from others.
+(SNS에서 타인의 댓글을 보기 위해 시간이 날 때마다 수시로 확인한다.)
+I use SNS to forget about personal problems.
+(개인적 문제를 잊기 위해 SNS를 한다.)
+Using SNS too much has negatively affected my work or studies.
+(SNS를 너무 많이 해서 그것이 나의 일 또는 학업에 부정적인 영향을 미쳤다.)
+I spend most of the day using SNS.
+(하루 중 대부분의 시간을 SNS를 하며 보낸다.)
+I use SNS to make myself feel better.
+(기분을 좋게 하기 위해 SNS를 한다.)
+Even though I think I should stop, I end up using SNS every time.
+("그만 해야지" 하면서도 번번이 SNS를하게 된다.)
+I feel an increasingly stronger urge to use SNS.
+(SNS를 하고 싶은 충동을 점점 더 많이 느낀다.)
+My interest in offline activities has decreased due to SNS.
+(SNS로 인해 오프라인에서의 다른 활동에 대한 흥미가 감소했다.)
+I constantly use SNS even while walking on the street or talking with others.
+(길을 걷거나 다른 사람들과 대화중에도 끊임없이 SNS를 한다.)
+Due to SNS, I often fall asleep later than I want to or fail to fall asleep.
+(SNS로 인해 원하는 시간보다 더 늦게 잠들거나 잠을 이루지 못하는 일이 자주 있다.)</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>702</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>남현지</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>대학생의 아동기 대인 외상 경험이 SNS 중독경향성에 미치는 영향: 불안정 성인애착과 소외에 대한 두려움의 순차매개 효과 (The Effects of Childhood Interpersonal Traumatic Experience on SNS Addiction Proneness of University Students: The Sequential Mediating Effect of Insecure Adult Attachment and Fear of Missing Out(FoMO))</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>숙명여자대학교 대학원 박사학위논문</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>애착 이론(Attachment Theory), 자기결정성 이론(Self-Determination Theory), 사회비교 이론(Social Comparison Theory), I-PACE 모델(Interaction of Person-Affect-Cognition-Execution Model)</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>아동기 대인 외상 경험 -&gt; 불안정 성인애착(불안 애착 / 회피 애착) -&gt; 소외에 대한 두려움(FoMO) -&gt; SNS 중독경향성</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>H1: 대학생의 아동기 대인 외상 경험, 불안 및 회피 성인애착, 소외에 대한 두려움, SNS 중독경향성 간에는 유의한 상관관계가 있을 것이다.
+H2: 대학생의 아동기 대인 외상 경험이 SNS 중독경향성에 미치는 영향에서 불안 및 회피 성인애착과 소외에 대한 두려움의 순차매개효과가 유의할 것이다.
+H3: 대학생의 아동기 대인 외상 경험이 SNS 중독경향성에 미치는 영향에서 불안 및 회피 성인애착과 소외에 대한 두려움의 순차매개 경로에 남녀 집단 간 유의한 차이가 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>아동기 대인 외상 경험(Childhood Interpersonal Traumatic Experience: 정서학대, 신체학대, 정서방임, 신체방임)</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>SNS 중독경향성(SNS Addiction Proneness: 조절실패 및 일상생활 장애, 몰입 및 내성, 부정 정서의 회피, 가상세계 지향성 및 금단)</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>불안정 성인애착(불안 성인애착, 회피 성인애착), 소외에 대한 두려움(특성 소외에 대한 두려움, 상태 소외에 대한 두려움)</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>성별(Gender; 다집단분석 변인으로 활용되었으나 경로계수 차이는 유의하지 않음)</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>1. 상관분석 결과 아동기 대인 외상 경험은 불안 성인애착, 회피 성인애착, 소외에 대한 두려움, SNS 중독경향성과 유의한 정적 상관을 보였으며, 불안 성인애착 및 소외에 대한 두려움은 SNS 중독경향성과 유의한 정적 상관을 나타냄.
+2. 구조방정식 모형 검증 결과, 완전매개모형이 채택되었으며 아동기 대인 외상 경험이 불안 및 회피 성인애착과 소외에 대한 두려움을 순차적으로 거쳐 SNS 중독경향성에 미치는 순차매개효과가 유의함.
+3. 구체적으로 아동기 대인 외상 경험은 불안 성인애착을 거쳐 소외에 대한 두려움을 높이고 SNS 중독경향성을 증가시키는 정적(+) 순차매개 경로를 형성한 반면, 회피 성인애착을 거칠 경우 소외에 대한 두려움을 낮추어 SNS 중독경향성을 감소시키는 부적(-) 순차매개 경로를 형성함.
+4. 다집단 분석 결과, 해당 순차매개 모형 경로는 성별에 따른 구조 동일성이 확보되어 남녀 집단 모두에게 동일하게 적용되는 것으로 나타남.</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>[아동기 대인 외상 경험 (Childhood Trauma Questionnaire-Short Form: CTQ-SF)]
+- People in my family said hurtful or insulting things to me.
+(가족들이 나에게 상처가 되거나 모욕적인 말을 했다.)
+- People in my family hit me so hard that it left bruises or marks.
+(가족들이 나를 심하게 때려 멍이나 상처가 남았다.)
+- I felt that someone in my family loved me.
+(가족 중 누군가가 나를 사랑해 준다고 느꼈다.)
+- There was someone in my family to help take care of me and protect me.
+(가족 중에 나를 돌봐주고 보호해 주는 사람이 있었다.)
+[성인애착 (Experiences in Close Relationships-Revised: ECR-R)]
+- I worry that romantic partners won't care about me as much as I care about them.
+(내가 상대방을 아끼는 만큼 상대방은 나를 아끼지 않을까 봐 걱정된다.)
+- I often worry that my partner will not want to stay with me.
+(상대방이 나와 함께 머물고 싶어 하지 않을까 봐 자주 불안하다.)
+- I prefer not to show a partner how I feel deep down.
+(내 깊은 속마음을 상대방에게 보여주지 않는 것을 선호한다.)
+- I feel comfortable depending on romantic partners.
+(상대방에게 의지하는 것이 편안하다.)
+[소외에 대한 두려움 (Modified Fear of Missing Out Questionnaire: FoMO)]
+- I fear others have more rewarding experiences than me.
+(다른 사람들이 나보다 더 가치 있고 보람 있는 경험을 하고 있을까 봐 두렵다.)
+- I get anxious when I don't know what my friends are up to.
+(친구들이 무엇을 하고 있는지 모르면 불안해진다.)
+- It is important that I understand my friends' 'in jokes'.
+(친구들 사이의 유행어나 비밀 이야기를 나도 아는 것이 중요하다.)
+- I feel the urge to constantly check social media to see what's happening.
+(온라인상에서 어떤 일이 일어나는지 확인하기 위해 지속적으로 SNS를 확인해야 한다는 충동을 느낀다.)
+[SNS 중독경향성 (SNS Addiction Proneness Scale)]
+- I spend more time on SNS than I originally intended.
+(SNS를 원래 의도했던 것보다 더 많은 시간 동안 사용한다.)
+- My daily life and work/studies are disrupted because of using SNS.
+(SNS 사용으로 인해 일상생활이나 학업/일에 지장을 받는다.)
+- I use SNS to avoid unpleasant feelings or stress.
+(불쾌한 감정이나 스트레스를 피하기 위해 SNS를 사용한다.)
+- I feel restless and irritated when I cannot access SNS.
+(SNS에 접속하지 못하면 안절부절못하고 짜증이 난다.)</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>https://dcollection.sookmyung.ac.kr</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>703</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>최영은</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>대학생의 주관적 계층감이 삶의 만족도에 미치는 영향 : 계층차별경험과 소외에 대한 두려움(FoMO)의 매개효과</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>단국대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>사회계층세계관모델(Social Class Worldview Model), 사회비교이론(Social Comparison Theory), 상징적 상호작용주의(Symbolic Interactionism), 문화 및 상징자본이론(Bourdieu's Capital Theory), 자기결정성이론(Self-Determination Theory)</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>주관적 계층감 -&gt; 계층차별경험(간과된 경제적 어려움, 계층차별 발언·분위기, 구조적 계층장벽) &amp; 소외에 대한 두려움(FoMO) -&gt; 삶의 만족도</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>H1: 대학생의 주관적 계층감은 계층차별경험(간과된 경제적 어려움, 계층차별 발언·분위기, 구조적 계층장벽)에 부(-)의 영향을 미칠 것이다.
+H2: 대학생의 주관적 계층감은 소외에 대한 두려움(FoMO)에 부(-)의 영향을 미칠 것이다.
+H3: 대학생의 주관적 계층감은 삶의 만족도에 정(+)의 영향을 미칠 것이다.
+H4: 계층차별경험(간과된 경제적 어려움, 계층차별 발언·분위기, 구조적 계층장벽)은 소외에 대한 두려움(FoMO)에 정(+)의 영향을 미칠 것이다.
+H5: 계층차별경험(간과된 경제적 어려움, 계층차별 발언·분위기, 구조적 계층장벽)은 삶의 만족도에 부(-)의 영향을 미칠 것이다.
+H6: 소외에 대한 두려움(FoMO)은 삶의 만족도에 부(-)의 영향을 미칠 것이다.
+H7: 계층차별경험과 소외에 대한 두려움은 주관적 계층감과 삶의 만족도 간의 관계를 다중 및 순차 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>주관적 계층감</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>삶의 만족도</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>계층차별경험(간과된 경제적 어려움, 계층차별 발언·분위기, 구조적 계층장벽), 소외에 대한 두려움(FoMO)</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>1. 주관적 계층감은 구조적 계층장벽에 부적으로 유의한 영향을 미쳤으나(β = -.332, p &lt; .001), 간과된 경제적 어려움, 계층차별 발언·분위기, 소외에 대한 두려움에는 직접적으로 유의한 영향을 미치지 않았다.
+2. 주관적 계층감은 삶의 만족도에 직접적으로 유의한 정적 영향(β = .423, p &lt; .001)을 미쳤다.
+3. 구조적 계층장벽은 소외에 대한 두려움에 정적 영향(β = .574, p &lt; .001), 삶의 만족도에 부적 영향(β = -.309, p &lt; .001)을 미쳤으며, 소외에 대한 두려움은 삶의 만족도에 부적 영향(β = -.382, p &lt; .001)을 미쳤다.
+4. 간접효과 검증 결과, 주관적 계층감이 구조적 계층장벽을 거쳐 삶의 만족도에 이르는 간접효과(B = .102, p &lt; .05) 및 구조적 계층장벽과 소외에 대한 두려움을 순차적으로 거치는 순차매개효과(B = .072, p &lt; .05)가 통계적으로 유의하였다.</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>[주관적 계층감 (MacArthur Scale)]
+- Select your relative socioeconomic position within the local community to which you belong.
+(본인이 속한 지역사회 내에서의 상대적 사회경제적 위치를 선택해 주십시오.)
+- Select your relative socioeconomic position within Korean society as a whole.
+(한국 사회 전체 내에서의 상대적 사회경제적 위치를 선택해 주십시오.)
+[계층차별경험 (K-CEQ-A)]
+- Others assumed that I could naturally afford things that were financially burdensome for me (e.g., dinner at an expensive restaurant).
+(당신이 경제적으로 부담하기 어려운 것들을 당연히 할 수 있을 것으로 생각했다.(비싼 식당에서의 저녁 등))
+- It felt like others did not consider the financial difficulties I was experiencing.
+(당신이 경험하는 재정적인 어려움을 고려하지 않는 것처럼 느껴졌다.)
+- Others recommended that I purchase things that were financially burdensome for me.
+(당신이 경제적으로 부담하기 어려운 것들을 구입하라고 권했다.)
+- People made stories or jokes about poor people.
+(가난한 사람들에 대한 이야기나 농담을 했다.)
+- People made statements implying that poor people are inferior.
+(가난한 사람들이 열등하다는 듯한 발언을 했다.)
+- There was a time when I could not join a club because the financial expenses were burdensome.
+(경제적인 지출이 부담되는 동아리에 가입하지 못한 적이 있다.)
+[소외에 대한 두려움 (K-FoMO)]
+- I get anxious when I do not receive news or updates about my friends.
+(나는 내 친구들의 소식을 접하지 못할 때 불안하다.)
+- I fear that my friends might be having more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+- It bothers me when I miss out on spontaneous plans with my friends.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+[삶의 만족도 (K-SWLS)]
+- In most ways my life is close to my ideal.
+(전반적으로 나의 인생은 내가 이상적으로 여기는 모습에 가깝다.)
+- The conditions of my life are excellent.
+(내 삶의 조건들은 아주 훌륭하다.)
+- I am satisfied with my life.
+(나는 나의 삶에 만족한다.)
+- So far I have gotten the important things I want in life.
+(나는 지금까지 내 삶에서 원했던 중요한 것들을 얻어왔다.)
+- If I could live my life over, I would change almost nothing.
+(다시 태어난다 해도, 나는 지금처럼 살아갈 것이다.)</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>704</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>김제은</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>대학생이 지각한 소외에 대한 두려움(FoMO)이 SNS중독경향성에 미치는 영향 : 상향비교와 자기통제의 어려움에 대한 이중매개효과</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>가톨릭꽃동네대학교 일반대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), 자기조절 실패 모델(Self-Regulatory Failure Model), 사회비교이론(Social Comparison Theory)</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO) -&gt; 상향비교 -&gt; 자기통제의 어려움 -&gt; SNS중독경향성 (순차적 이중매개모형)</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>H1: 소외에 대한 두려움이 SNS중독경향성에 미치는 영향에서 상향비교가 유의미하게 매개할 것이다.
+H2: 소외에 대한 두려움이 SNS중독경향성에 미치는 영향에서 자기통제의 어려움이 유의미하게 매개할 것이다.
+H3: 소외에 대한 두려움이 SNS중독경향성에 미치는 영향에서 상향비교와 자기통제의 어려움이 순차적으로 유의미하게 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO)</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>SNS중독경향성</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>상향비교, 자기통제의 어려움</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>1. 대학생이 지각한 소외에 대한 두려움(FoMO)은 SNS중독경향성에 유의미한 직접적인 정적(+) 영향을 미치는 것으로 나타났다(B = 0.90, p &lt; .001).
+2. 소외에 대한 두려움(FoMO)과 SNS중독경향성의 관계에서 상향비교의 단순 매개효과가 유의미하였다(B = 0.20, 95% CI [0.05, 0.36]).
+3. 소외에 대한 두려움(FoMO)과 SNS중독경향성의 관계에서 자기통제의 어려움의 단순 매개효과가 유의미하였다(B = 0.15, 95% CI [0.07, 0.25]).
+4. 소외에 대한 두려움(FoMO)이 상향비교와 자기통제의 어려움을 순차적으로 거쳐 SNS중독경향성에 영향을 미치는 이중매개효과가 통계적으로 유의미하게 검증되었다(B = 0.14, 95% CI [0.08, 0.21]).</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>[소외에 대한 두려움(FoMO) 척도]
+- I fear others have more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+- I get anxious when I don't know what my friends are up to.
+(나는 친구들의 소식을 접하지 못할 때 불안하다.)
+- I worry when I find out my friends are having fun without me.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까봐 걱정된다.)
+- I fear my friends or other people are having more rewarding experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까봐 두렵다.)
+- I worry that I spend too much time trying to keep track of what is going on around me.
+(나는 주변을 신경 쓰는 데 시간을 많이 보내는 것 같아 걱정된다.)
+- It bothers me when I miss an opportunity to meet up with friends.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+- When I miss out on a planned get-together, it bothers me.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+- Even on vacation, I keep track of what my friends are doing.
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다.)
+[상향비교 척도]
+- I often compare the housing environment (home) of people around me who live more affluently than me with my own situation.
+(나보다 더 부유하게 사는 주변 사람들의 주거환경(집)을 나의 처지와 자주 비교하곤 한다.)
+- I often compare the means of transportation (cars, etc.) of people around me who live more affluently than me with my own situation.
+(나보다 더 부유하게 사는 주변 사람들의 교통수단(자동차 등)을 나의 처지와 자주 비교하곤 한다.)
+- I often compare the dietary life (food purchases, eating out, etc.) of people around me who live more affluently than me with my own situation.
+(나보다 더 부유하게 사는 주변 사람들의 식생활(식품 구매, 외식 등)을 나의 처지와 자주 비교하곤 한다.)
+- I often compare the clothing life (clothes, accessories, etc.) of people around me who live more affluently than me with my own situation.
+(나보다 더 부유하게 사는 주변 사람들의 의생활(옷, 장신구 등)을 나의 처지와 자주 비교하곤 한다.)
+- I often compare the quality of leisure life (travel, hobbies, etc.) of people around me who live more affluently than me with my own situation.
+(나보다 더 부유하게 사는 주변 사람들의 여가생활(여행, 취미활동 등)의 질을 나의 처지와 자주 비교하곤 한다.)
+[자기통제의 어려움 척도]
+- I am good at resisting temptation.
+(나는 유혹에 잘 빠지지 않는다.)
+- I have a hard time breaking bad habits.
+(나는 나쁜 습관을 끊기가 어렵다.)
+- I am lazy.
+(나는 게으르다.)
+- I have trouble concentrating.
+(집중하기가 어렵다.)
+- I do certain things that are bad for me, if they are fun.
+(나는 재미있으면 나에게 해로운 일도 한다.)
+- I wish I had more self-discipline.
+(나에게 좀 더 자제력이 있었으면 좋겠다.)
+- Pleasure and fun sometimes keep me from getting work done.
+(즐겁고 재밌는 것을 하느라 종종 일을 제때 끝내지 못한다.)
+- I say inappropriate things.
+(나는 상황에 적절하지 않은 말을 한다.)
+- I am able to work effectively toward long-term goals.
+(나는 장기적인 목표를 향해 효율적으로 일을 진행할 수 있다.)
+- Sometimes I can't stop myself from doing something, even if I know it is wrong.
+(나는 잘못인 줄 알면서도 스스로 그것을 멈추지 못한다.)
+- I often act without thinking through all the alternatives.
+(나는 종종 모든 가능성을 고려해 보지 않고 행동한다.)
+[대학생용 SNS중독경향성 척도]
+- I spend a lot of time thinking about SNS or planning how to use it.
+(SNS를 생각하거나 어떻게 이용할 것인가에 많은 시간을 보낸다.)
+- SNS makes me feel constantly connected with others so that I feel less lonely or alienated.
+(SNS는 내가 다른 사람과 항상 연결되어 있어 외롭거나 소외감을 덜 느끼도록 한다.)
+- I use SNS to forget about stressful problems.
+(스트레스 받는 문제를 잊기 위해 SNS를 사용한다.)
+- I sleep during class or work hours because I am tired from using SNS.
+(SNS 사용 때문에 피곤해서 수업시간 또는 업무 시간에 잔다.)
+- I think a lot about what recently happened on SNS.
+(최근 SNS에서 일어난 일에 대해 많이 생각한다.)
+- I get annoyed when I am unable to use SNS.
+(SNS를 하지 못하게 되었을 때 짜증이 난다.)
+- While using SNS, I feel recognized as myself.
+(SNS를 하는 동안만큼은 내 자신이 인정을 받는다고 느낀다.)
+- I use SNS to reduce feelings of helplessness or depression.
+(무력감 또는 우울감을 줄이기 위해 SNS를 한다.)
+- I do not spend a lot of time using SNS.
+(SNS 사용에 많은 시간을 보내지 않는다.)
+- I have regretted being unable to reduce my SNS usage time.
+(SNS 사용 시간을 줄이지 못해 후회한 적이 있다.)
+- I use SNS to reduce nervousness or anxiety.
+(초조함 또는 불안감을 줄이기 위해 SNS를 한다.)
+- I gain more confidence while using SNS.
+(SNS를 하는 동안 더욱 자신감이 생긴다.)
+- If I cannot use SNS, I lose the joy or fun of living.
+(SNS를 하지 못하게 되면 사는 즐거움 또는 재미를 잃는다.)
+- Because of SNS, I place less importance on hobbies, leisure activities, and exercise.
+(SNS 때문에 취미, 여가생활, 운동을 덜 중요시 한다.)
+- Whenever I have free time, I frequently check SNS to see others' comments.
+(SNS에서 타인의 댓글을 보기 위해 시간이 날 때마다 수시로 확인 한다.)
+- I use SNS to forget personal problems.
+(개인적 문제를 잊기 위해 SNS를 한다.)
+- Using SNS too much has negatively affected my work or studies.
+(SNS를 너무 많이 해서 그것이 나의 일 또는 학업에 부정적인 영향을 미쳤다.)
+- I spend most of my day using SNS.
+(하루 중 대부분의 시간을 SNS를 하며 보낸다.)
+- I use SNS to make myself feel better.
+(기분을 좋게 하기 위해 SNS를 한다.)
+- Even though I tell myself "I should stop," I end up using SNS every time.
+("그만 해야지" 하면서도 번번이 SNS를 하게 된다.)
+- I feel an increasing urge to use SNS.
+(SNS를 하고 싶은 충동을 점점 더 많이 느낀다.)
+- Due to SNS, my interest in other offline activities has decreased.
+(SNS로 인해 오프라인에서의 다른 활동에 대한 흥미가 감소했다.)
+- I constantly use SNS even while walking on the street or conversing with others.
+(길을 걷거나 다른 사람들과 대화 중에도 끊임없이 SNS를 한다.)
+- Due to SNS, I often fall asleep later than intended or have trouble sleeping.
+(SNS로 인해 원하는 시간보다 더 늦게 잠들거나 잠을 이루지 못하는 일이 자주 있다.)</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -45069,7 +45069,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Thaler, R.</t>
+          <t>Richard Thaler</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -45079,47 +45079,46 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Toward a positive theory of consumer choice</t>
+          <t>TOWARD A POSITIVE THEORY OF CONSUMER CHOICE</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Journal of Economic Behavior &amp; Organization</t>
+          <t>Journal of Economic Behavior and Organization</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>심적 회계 이론(Mental Accounting)
-소비자 선택의 긍정적 이론
-행동경제학</t>
+          <t>전망이론(Prospect Theory), 제한된 합리성(Bounded Rationality), 베버-페히너 법칙(Weber-Fechner Law), 기획자-실행자 모형(Planner-Doer Model)</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>[거래 효용 = 준거가격 - 실제가격]
-[취득 효용 + 거래 효용 = 총 효용]
-이득 분리, 손실 통합 원칙</t>
+          <t>[의사결정 프레임 및 비용 구조(IV)] -&gt; [참조점 변화 및 가치함수 평가 / 심리적 비용(Mediator)] -&gt; [규범적 경제이론과 이탈되는 체계적 소비자 선택 행동(DV)]</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>H1: 이득은 분리 제시 시, 손실은 통합 제시 시 소비자 효용이 극대화될 것이다.
-H2: 소비자는 화폐의 출처에 따라 다르게 평가하고 다르게 지출할 것이다.</t>
+          <t>H1 (부유효과): 기회비용은 현금 지출 비용보다 낮게 평가되어 상품 보유 여부에 따라 매도-매수가 격차가 크게 발생할 것이다.
+H2 (매몰비용 효과): 이미 지불된 비용(매몰비용)은 제품/서비스의 향후 이용률을 지속적으로 증가시킬 것이다.
+H3 (가격 심리학 및 탐색): 탐색 행동 여부는 절약되는 절대적 금액보다 제품 총 가격 대비 비율(상대적 할인 비율)에 의해 결정될 것이다.
+H4 (후회와 선택의 회피): 후회 및 책임에 따른 심리적 비용이 높을 때 소비자는 스스로 선택권을 포기하거나 사전 지불 구조를 선호할 것이다.
+H5 (자기통제 및 사전확약): 자기통제 문제가 발생하는 영역에서 소비자는 미래 행동을 제약하는 사전확약(Precommitment) 기법에 대한 수요를 가질 것이다.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>이득/손실 프레이밍 방식</t>
+          <t>비용 유형(기회비용 vs 현금 지출 비용), 매몰비용 유무, 상대적 가격 차이, 선택 실패 시 후회 가능성, 시간적 편익/비용 구조</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>지각 효용, 구매 의도</t>
+          <t>소비자 지출 의사결정, 서비스 및 제품 이용률, 탐색 수행 여부, 선택권 위임 및 사전 지불 선호도, 사전확약 금융/서비스 제품 이용</t>
         </is>
       </c>
       <c r="K593" t="inlineStr">
         <is>
-          <t>심적 회계</t>
+          <t>참조점 변화, 가치함수의 손실회피 비대칭성, 후회 및 책임감 등 심리적/정신적 비용</t>
         </is>
       </c>
       <c r="L593" t="inlineStr">
@@ -45129,13 +45128,32 @@
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t>소비자는 화폐를 심적 계정에 분류. 취득 효용과 거래 효용이 독립적으로 소비자 만족에 기여.</t>
-        </is>
-      </c>
-      <c r="N593" t="inlineStr"/>
+          <t>1. 소비자는 보유한 재화를 포기할 때 유발되는 손실을 크게 평가하여 지출 비용보다 기회비용을 낮게 평가함(부유효과).
+2. 합리적 경제학의 예측과 달리 지불된 과거 비용(매몰비용)은 향후 소비 및 사용 빈도를 의도적으로 늘림.
+3. 탐색 비용 대비 절약액 평가 시 소비자 인지는 총가격 대비 비율에 영향을 받으므로 TV의 5달러 절약보다 라디오의 5달러 절약을 훨씬 높게 평가함.
+4. 건강 및 휴가 등 후회가 수반되는 결정에서 소비자는 정신적 비용을 줄이기 위해 사전 지불(prepaid)이나 의사결정 위임을 선택함.
+5. 자기통제 부족(Short-sighted Doer)을 해결하기 위해 이자가 없거나 비용이 드는 사전확약 수단(예: 크리스마스 클럽 저축)을 자발적으로 이용함.</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>In addition to whatever you own you have been given 1,000. You are now asked to choose between A: (1,000, 0.5) and B: (500).
+(당신이 현재 소유한 것 외에 1,000이 추가로 주어졌습니다. 이제 A: 50% 확률로 1,000 수령, B: 확정적으로 500 수령 중 하나를 선택해야 합니다.)
+In addition to whatever you own, you have been given 2,000. You are now asked to choose between C: (-1,000, 0.5) and D: (-500).
+(당신이 현재 소유한 것 외에 2,000이 추가로 주어졌습니다. 이제 C: 50% 확률로 1,000 손실, D: 확정적으로 500 손실 중 하나를 선택해야 합니다.)
+Assume you have been exposed to a disease which if contracted leads to a quick and painless death within a week. The probability you have the disease is 0.001. What is the maximum you would be willing to pay for a cure?
+(당신이 감염될 경우 일주일 이내에 빠르고 고통 없이 사망에 이르는 질병에 노출되었다고 가정해 봅시다. 감염 확률은 0.001입니다. 치료제를 위해 지불할 용의가 있는 최대 금액은 얼마입니까?)
+Suppose volunteers were needed for research on the above disease. All that would be required is that you expose yourself to a 0.001 chance of contracting the disease. What is the minimum payment you would require to volunteer for this program?
+(상기 질병 연구를 위해 자원봉사자가 필요하다고 가정해 봅시다. 당신에게 요구되는 것은 0.001의 확률로 질병에 노출되는 것뿐입니다. 이 프로그램에 자원하기 위해 요구할 최소한의 보상금은 얼마입니까?)
+You set off to buy a clock radio at what you believe to be the cheapest store in your area. When you arrive, you find that the radio costs $25. As you are about to make the purchase, a reliable friend comes by and tells you that the same radio is selling for $20 at another store ten minutes away. Do you go to the other store?
+(당신은 지역 내에서 가장 저렴하다고 믿는 매장에 탁상용 라디오를 사러 갔습니다. 도착해서 라디오 가격이 25달러인 것을 확인하고 막 구매하려는데, 신뢰할 수 있는 친구가 들러 10분 거리에 있는 다른 매장에서 동일한 라디오를 20달러에 팔고 있다고 알려줍니다. 당신은 다른 매장으로 가겠습니까?)
+Now suppose that instead of a radio you are buying a color television for $500 and your friend tells you it is available at the other store for $495. Do you go to the other store?
+(이제 라디오 대신 500달러짜리 컬러 텔레비전을 구매하려는데, 친구가 다른 매장에서 495달러에 팔고 있다고 알려준다고 가정해 봅시다. 당신은 다른 매장으로 가겠습니까?)</t>
+        </is>
+      </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.1016/0167-2681(80)90051-7</t>
         </is>
       </c>
     </row>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -45315,7 +45315,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Thaler, R.</t>
+          <t>Richard H. Thaler</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -45325,47 +45325,47 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>From homo economicus to homo sapiens</t>
+          <t>From Homo Economicus to Homo Sapiens</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>The Journal of Economic Perspectives</t>
+          <t>Journal of Economic Perspectives</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>심적 회계 이론(Mental Accounting)
-소비자 선택의 긍정적 이론
-행동경제학</t>
+          <t>행동경제학(Behavioral Economics), 제한된 합리성(Bounded Rationality), 전망이론(Prospect Theory), 인지편향(Cognitive Biases)</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>[거래 효용 = 준거가격 - 실제가격]
-[취득 효용 + 거래 효용 = 총 효용]
-이득 분리, 손실 통합 원칙</t>
+          <t>[심리학적 사실성 및 인간 인지/감정의 통합] -&gt; [경제학 모형의 설명력 및 예측력 향상 (Homo Economicus에서 Homo Sapiens로의 진화)]</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>H1: 이득은 분리 제시 시, 손실은 통합 제시 시 소비자 효용이 극대화될 것이다.
-H2: 소비자는 화폐의 출처에 따라 다르게 평가하고 다르게 지출할 것이다.</t>
+          <t>H1: 경제학 모형 내 행위자의 합리성 수준은 연구 맥락에 따라 다르게 설정될 것이다 (Homo Economicus의 IQ 감소).
+H2: 경제학 모형은 과업의 난이도와 피드백 빈도 등 환경적 요인을 반영하여 더 느리게 학습하는 행위자를 다룰 것이다.
+H3: 경제학 모형 내 행위자들은 합리적 행위자와 준합리적 행위자가 공존하는 다원적이고 이질적인 형태로 변화할 것이다.
+H4: 경제학자들은 전망이론, 심리계좌, 제한된 기억(사후과잉확신 편향 등)과 같은 인간의 인지 과정을 직접 연구할 것이다.
+H5: 경제학은 규범적 이론(합리적 선택)과 기술적 이론(실제 선택)을 명확히 구분하여 발전할 것이다.
+H6: 경제학자들은 분노, 자부심, 시기심, 후회 등 인간의 감정이 경제적 의사결정에 미치는 영향에 더 많은 관심을 기울일 것이다.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>이득/손실 프레이밍 방식</t>
+          <t>경제학 모형 내 심리학적 사실성(인간의 인지적 한계, 환경적 학습 요인, 행위자의 이질성, 감정적 요인)의 통합 수준</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>지각 효용, 구매 의도</t>
+          <t>경제학 모형의 현실 설명력 및 예측력 (Homo Economicus에서 Homo Sapiens로의 패러다임 전환)</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
         <is>
-          <t>심적 회계</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
@@ -45375,13 +45375,29 @@
       </c>
       <c r="M596" t="inlineStr">
         <is>
-          <t>소비자는 화폐를 심적 계정에 분류. 취득 효용과 거래 효용이 독립적으로 소비자 만족에 기여.</t>
-        </is>
-      </c>
-      <c r="N596" t="inlineStr"/>
+          <t>1. 전통적 경제학의 초합리적 행위자(Homo Economicus) 가정은 실제 인간의 제한된 합리성과 인지적 편향(낙관주의, 과잉확신, 허위합의 효과, 지식의 저주 등)을 설명하지 못함.
+2. '숫자 맞추기 게임' 및 '최후통첩 게임' 등의 실험적 증거는 인간이 맥락 의존적으로 사고하며, 자신의 이익 극대화가 아닌 공정성이나 보복(감정적 반응)에 기반해 행동함을 보여줌.
+3. 시장에서 합리적 행위자와 준합리적 행위자(소음 거래자 등)가 상호작용할 때 준합리적 행위자가 도태되지 않고 공존할 수 있음.
+4. 향후 경제학은 규범적 모형과 기술적 모형을 구분하고, 인간의 실제 인지 구조와 감정을 반영하는 방향(Homo Sapiens로의 진화)으로 나아갈 것임.</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>Do you have a cell phone?
+(휴대전화를 가지고 있습니까?)
+What percentage of the class has a cell phone?
+(학급 학생 중 몇 퍼센트가 휴대전화를 가지고 있다고 생각합니까?)
+Guess a number from 0 to 100, with the goal of making your guess as close as possible to two-thirds of the average guess.
+(평균 선택 값의 3분의 2에 가장 가까운 숫자가 되도록 0에서 100 사이의 숫자를 맞추십시오.)
+Make predictions about stock market returns for the next two months.
+(향후 2개월 동안의 주식 시장 수익률을 예측하십시오.)
+Try to recall your earlier forecast of the stock market returns.
+(이전에 예측했던 주식 시장 수익률을 회상해 보십시오.)</t>
+        </is>
+      </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.1257/jep.14.1.133</t>
         </is>
       </c>
     </row>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -45407,7 +45407,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Thaler, R. H., &amp; Johnson, E. J.</t>
+          <t>Richard H. Thaler, Eric J. Johnson</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -45417,7 +45417,7 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Gambling with the house money and trying to break even: The effects of prior outcomes on risky choice</t>
+          <t>Gambling with the House Money and Trying to Break Even: The Effects of Prior Outcomes on Risky Choice</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -45427,53 +45427,63 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>심적 회계 이론(Mental Accounting)
-소비자 선택의 긍정적 이론
-행동경제학</t>
+          <t>전망 이론 (Prospect Theory), 심적 회계 이론 (Mental Accounting Theory)</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>[거래 효용 = 준거가격 - 실제가격]
-[취득 효용 + 거래 효용 = 총 효용]
-이득 분리, 손실 통합 원칙</t>
+          <t>[이전 의사결정 결과 (이익 vs. 손실)] -&gt; [심적 회계 및 인지적 편집 (Mental Accounting &amp; Cognitive Editing)] -&gt; [위험 선택 행동 (Risk-seeking vs. Risk-averse)]</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>H1: 이득은 분리 제시 시, 손실은 통합 제시 시 소비자 효용이 극대화될 것이다.
-H2: 소비자는 화폐의 출처에 따라 다르게 평가하고 다르게 지출할 것이다.</t>
+          <t>H1 (하우스 머니 효과): 이전의 이익이 존재할 때, 잠재적 손실이 이전 이익보다 작다면 개인은 더 위험 추구적인 선택을 한다.
+H2 (본전 찾기 효과): 이전의 손실이 존재할 때, 본전을 회복할 수 있는 기회가 제공되면 개인은 위험 추구적인 선택을 한다.
+H3: 본전을 회복할 기회가 없는 일반적인 손실 상황에서 개인은 위험 회피적인 성향을 보인다.</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>이득/손실 프레이밍 방식</t>
+          <t>이전 의사결정 결과 (이전 이익 vs. 이전 손실)</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>지각 효용, 구매 의도</t>
+          <t>위험 선택 행동 (선택 비율)</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
         <is>
-          <t>심적 회계</t>
+          <t>심적 회계 / 인지적 편집 (Mental Accounting / Cognitive Editing)</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>잠재적 손실의 크기 (이전 이익 대비), 본전 회복 가능성 (Break-even Opportunity)</t>
         </is>
       </c>
       <c r="M597" t="inlineStr">
         <is>
-          <t>소비자는 화폐를 심적 계정에 분류. 취득 효용과 거래 효용이 독립적으로 소비자 만족에 기여.</t>
-        </is>
-      </c>
-      <c r="N597" t="inlineStr"/>
+          <t>1. 이전의 이익은 위험 추구 성향을 증가시키는데, 이는 잠재적 손실이 이전 이익의 범위 내에 있을 때 뚜렷하게 나타난다 (하우스 머니 효과).
+2. 이전의 손실은 일반적으로 위험 회피 성향을 강화시키지만, 손실을 완전히 만회할 수 있는(본전을 찾을 수 있는) 기회가 주어지면 예외적으로 매우 강한 위험 추구 성향을 보인다 (본전 찾기 효과).
+3. 전망 이론의 가치 함수가 정적인 상황뿐만 아니라 동적인 순차적 선택 상황에서 어떻게 수정되어 적용되어야 하는지를 실증적으로 규명하였다.</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>Problem 1 (Prior Gain Condition):
+You have just won $30. Choose between: (a) A game with a 50% chance to win $9 and a 50% chance to lose $9. (b) No further play.
+(문제 1 (이전 이익 조건):
+당신은 방금 30달러를 얻었습니다. 다음 중 하나를 선택하십시오: (a) 50%의 확률로 9달러를 얻고 50%의 확률로 9달러를 잃는 게임, (b) 더 이상 게임을 하지 않음.)
+Problem 2 (Prior Loss Condition):
+You have just lost $30. Choose between: (a) A game with a 33% chance to win $30 and a 67% chance to lose $0. (b) No further play.
+(문제 2 (이전 손실 조건):
+당신은 방금 30달러를 잃었습니다. 다음 중 하나를 선택하십시오: (a) 33%의 확률로 30달러를 얻고 67%의 확률로 0달러를 잃는 게임, (b) 더 이상 게임을 하지 않음.)</t>
+        </is>
+      </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://doi.org/10.1287/mnsc.36.6.643</t>
         </is>
       </c>
     </row>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -45493,73 +45493,83 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Thaler, R. H., &amp; Shefrin, H. M.</t>
+          <t>H. M. Shefrin, Richard Thaler</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>An economic theory of self-control</t>
+          <t>An Economic Theory of Self-Control</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>The Journal of Political Economy</t>
+          <t>NBER Working Paper Series (Working Paper No. 208 revised)</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>심적 회계 이론(Mental Accounting)
-소비자 선택의 긍정적 이론
-행동경제학</t>
+          <t>대리인 이론 (Agency Theory), 이중 자아 모형 (Dual-Self Model / Planner-Doer Model), 시차적 선택 이론 (Intertemporal Choice Theory)</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>[거래 효용 = 준거가격 - 실제가격]
-[취득 효용 + 거래 효용 = 총 효용]
-이득 분리, 손실 통합 원칙</t>
+          <t>[Planner (장기적 효용 극대화 자아)] &amp; [Doer (단기적 근시안적 자아)] -&gt; [자아 통제 갈등 및 대리인 비용 (Self-Control Conflict &amp; Agency Costs)] -&gt; [규칙 및 재량의 선택 (Rules vs. Discretion)]</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>H1: 이득은 분리 제시 시, 손실은 통합 제시 시 소비자 효용이 극대화될 것이다.
-H2: 소비자는 화폐의 출처에 따라 다르게 평가하고 다르게 지출할 것이다.</t>
+          <t>H1: 개인은 장기적 계획가(Planner)와 단기적 행위자(Doer) 간의 내부 갈등을 겪으며, 이는 조직의 대리인 문제와 유사한 구조를 가진다.
+H2: 동적 비일관성(Dynamic Inconsistency)을 극복하기 위해 개인은 미래의 선택을 제한하는 규칙(내부적 또는 외부적 규칙)을 스스로에게 합리적으로 부과한다.
+H3: 유혹적이거나 중독성이 강한 재화는 재량권 행사 비용을 증가시켜 순수 규칙이나 기회 조작(Opportunity Manipulation)을 선호하게 만든다.
+H4: 의무적 연금 제도의 도입은 자아 통제 비용을 감소시켜 다른 저축의 불완전한 상쇄를 유도하고 결과적으로 총 저축을 증가시킨다.</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>이득/손실 프레이밍 방식</t>
+          <t>계획가의 통제 수단 (규칙 vs 재량, 죄책감/각성 조절 파라미터 theta, 기회 조작)</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>지각 효용, 구매 의도</t>
+          <t>소비 및 저축 의사결정, 자아 통제 행동, 시차적 선택의 일관성</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>심적 회계</t>
+          <t>행위자의 수정된 효용 및 인센티브 (죄책감 및 각성 수준)</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>재화의 유혹성/중독성 수준, 외부적 사전 확약(Precommitment) 장치의 가용성</t>
         </is>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>소비자는 화폐를 심적 계정에 분류. 취득 효용과 거래 효용이 독립적으로 소비자 만족에 기여.</t>
-        </is>
-      </c>
-      <c r="N598" t="inlineStr"/>
+          <t>1. 자아 통제 문제를 계획가(Planner)와 다수의 행위자(Doer)로 구성된 이중 자아 조직 모형으로 공식화하여 대리인 이론으로 분석할 수 있음을 증명하였다.
+2. 개인은 대리인 비용을 최소화하기 위해 조직이 사용하는 통제 기법(규칙과 재량의 조합, 인센티브 수정 등)과 동일한 전략을 합리적으로 사용한다.
+3. 설문 조사에서 나타나는 높은 시간 선호율은 안정적인 지수 할인율의 부재가 아니라, 규칙의 예외 상황으로 인식되는 특수 상황에서 기인한다.
+4. 사적 연금 제도가 다른 저축을 완전히 대체하지 못하고 총 자축을 증가시키는 현상은 자아 통제 모형의 예측과 일치한다.</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>What size bonus would you demand today rather than collect a bonus of $100 in one year?
+(1년 후에 100달러의 보너스를 받는 대신 오늘 당장 요구할 보너스의 금액은 얼마입니까?)
+Could you borrow $500 to make an installment purchase?
+(할부 구매를 위해 500달러를 빌릴 수 있습니까?)
+Could you borrow $1000 in cash?
+(현금으로 1000달러를 빌릴 수 있습니까?)</t>
+        </is>
+      </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.nber.org/papers/w0208</t>
         </is>
       </c>
     </row>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O705"/>
+  <dimension ref="A1:O706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45239,7 +45239,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Thaler, R.</t>
+          <t>Richard H. Thaler</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -45249,7 +45249,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Mental accounting matters</t>
+          <t>Mental Accounting Matters</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -45259,53 +45259,66 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>심적 회계 이론(Mental Accounting)
-소비자 선택의 긍정적 이론
-행동경제학</t>
+          <t>Prospect Theory, Transaction Utility Theory, Behavioral Life-Cycle Hypothesis</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>[거래 효용 = 준거가격 - 실제가격]
-[취득 효용 + 거래 효용 = 총 효용]
-이득 분리, 손실 통합 원칙</t>
+          <t>[Mental Accounting Components: Framing, Categorization, Bracketing] -&gt; [Non-fungibility of Money/Time] -&gt; [Consumer Choice &amp; Financial Decision Making]</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>H1: 이득은 분리 제시 시, 손실은 통합 제시 시 소비자 효용이 극대화될 것이다.
-H2: 소비자는 화폐의 출처에 따라 다르게 평가하고 다르게 지출할 것이다.</t>
+          <t>P1: People evaluate outcomes relative to a reference point with diminishing sensitivity and loss aversion.
+P2: Consumers derive both acquisition utility and transaction utility from purchases.
+P3: Budgets and wealth accounts are non-fungible, influencing spending decisions.
+P4: Narrow bracketing combined with loss aversion (myopic loss aversion) leads to lower risk-taking in short-term evaluations.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>이득/손실 프레이밍 방식</t>
+          <t>Mental accounting frames (transaction context, budget categorization, evaluation frequency/bracketing, source of income)</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>지각 효용, 구매 의도</t>
+          <t>Consumer choice, spending behavior, risk-taking, savings rate</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>심적 회계</t>
+          <t>Perceived utility (acquisition &amp; transaction utility), violation of fungibility</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Temporal spacing, evaluation frequency</t>
         </is>
       </c>
       <c r="M595" t="inlineStr">
         <is>
-          <t>소비자는 화폐를 심적 계정에 분류. 취득 효용과 거래 효용이 독립적으로 소비자 만족에 기여.</t>
-        </is>
-      </c>
-      <c r="N595" t="inlineStr"/>
+          <t>1. Mental accounting violates the economic principle of fungibility, meaning money in one account is not a perfect substitute for money in another.
+2. Consumers evaluate transactions based on both acquisition utility (consumer surplus) and transaction utility (perceived quality of the deal).
+3. Sunk costs influence subsequent decisions but their effects gradually depreciate over time.
+4. People categorize wealth and income into non-fungible accounts, which affects their marginal propensity to consume.
+5. Narrow bracketing combined with loss aversion (myopic loss aversion) explains why people avoid attractive small-stakes risks and why the equity premium is high.</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>Imagine that you are about to purchase a jacket for ($125)[$15] and a calculator for ($15)[$125]. The calculator salesman informs you that the calculator you wish to buy is on sale for ($10)[$120] at the other branch of the store, located 20 minutes drive away. Would you make the trip to the other store?
+(당신이 $125[$15]짜리 재킷과 $15[$125]짜리 계산기를 구매하려고 한다고 상상해 보십시오. 계산기 판매원은 당신이 사고 싶어 하는 계산기가 차로 20분 거리에 있는 다른 지점에서 $10[$120]에 할인 판매 중이라고 알려줍니다. 당신은 다른 매장으로 이동하시겠습니까?)
+You are lying on the beach on a hot day. All you have to drink is ice water. For the last hour you have been thinking about how much you would enjoy a nice cold bottle of your favorite brand of beer. A companion gets up to go make a phone call and offers to bring back a beer from the only nearby place where beer is sold (a fancy resort hotel) [a small, run-down grocery store]. He says that the beer might be expensive and so asks how much you are willing to pay for the beer. He says that he will buy the beer if it costs as much or less than the price you state. But if it costs more than the price you state he will not buy it. You trust your friend, and there is no possibility of bargaining with the (bartender) [store owner]. What price do you tell him?
+(당신은 더운 날 해변에 누워 있습니다. 마실 것이라고는 얼음물뿐입니다. 지난 한 시간 동안 당신은 좋아하는 브랜드의 시원한 맥주 한 병을 마시면 얼마나 좋을지 생각하고 있었습니다. 동행인이 전화를 걸기 위해 일어나며 근처에서 맥주를 파는 유일한 곳(고급 리조트 호텔) [작고 허름한 식료품점]에서 맥주를 가져다주겠다고 제안합니다. 그는 맥주가 비쌀 수도 있으니 맥주에 얼마를 지불할 용의가 있는지 묻습니다. 그는 당신이 제시한 가격 이하일 경우에만 맥주를 살 것이며, 그보다 비싸면 사지 않겠다고 합니다. 당신은 친구를 신뢰하며, (바텐더) [가게 주인]과 흥정할 가능성은 없습니다. 당신은 친구에게 얼마의 가격을 말하겠습니까?)
+Suppose you bought a case of a good 1982 Bordeaux in the futures market for $20 a bottle. The wine now sells at auction for about $75 a bottle. You have decided to drink a bottle. Which of the following best captures your feeling of the cost to you of drinking this bottle?
+(당신이 선물 시장에서 좋은 1982년산 보르도 와인 한 상자를 병당 $20에 샀다고 가정해 봅시다. 이 와인은 현재 경매에서 병당 약 $75에 판매되고 있습니다. 당신은 한 병을 마시기로 결정했습니다. 다음 중 이 와인을 마시는 데 드는 비용에 대한 당신의 느낌을 가장 잘 포착한 것은 무엇입니까?)
+Suppose you buy a case of Bordeaux futures at $400 a case. The wine will retail at about $500 a case when it is shipped. You do not intend to start drinking this wine for a decade. At the time that you acquire this wine which statement more accurately captures your feelings?
+(당신이 보르도 와인 선물을 한 상자에 $400에 산다고 가정해 봅시다. 이 와인은 배송될 때 소매가로 약 $500에 판매될 것입니다. 당신은 향후 10년 동안 이 와인을 마실 생각이 없습니다. 당신이 이 와인을 획득하는 시점에 다음 중 어떤 진술이 당신의 감정을 더 정확하게 포착합니까?)</t>
+        </is>
+      </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.1002/(SICI)1099-0771(199909)12:3&lt;183::AID-BDM318&gt;3.0.CO;2-F</t>
         </is>
       </c>
     </row>
@@ -55401,6 +55414,81 @@
         </is>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>705</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>가격 제시 프레이밍이 구매 의도에 미치는 영향 (추정)</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>가격 프레이밍 이론 (Temporal Framing / Pennies-a-day Effect)</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>[가격 제시 프레이밍 (일 단위 vs. 월 단위 vs. 통합)] -&gt; [구매 의도] (조절변수: 가격 수용 범위)</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>가격 제시 프레이밍 (일 단위, 월 단위, 통합)</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>구매 의도</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>가격 수용 범위 (가격 수용 범위 내 vs. 가격 수용 범위 외)</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>가격 제시 프레이밍 방식(일 단위, 월 단위, 통합)과 가격 수용 범위(내/외)의 조건에 따라 소비자의 구매 의도 및 심리적/실질적 가치 지각에 유의미한 차이가 존재함.</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O706"/>
+  <dimension ref="A1:O707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45163,7 +45163,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Thaler, R.</t>
+          <t>Richard Thaler</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -45173,7 +45173,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Some empirical evidence on dynamic inconsistency</t>
+          <t>Some Empirical Evidence on Dynamic Inconsistency</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -45183,37 +45183,37 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>심적 회계 이론(Mental Accounting)
-소비자 선택의 긍정적 이론
-행동경제학</t>
+          <t>Intertemporal Choice Theory (시간선호이론), Self-Control Theory (자기통제이론), Prospect Theory (전망이론)</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>[거래 효용 = 준거가격 - 실제가격]
-[취득 효용 + 거래 효용 = 총 효용]
-이득 분리, 손실 통합 원칙</t>
+          <t>[Reward Size, Delay Length, Sign (Gain vs Loss)] -&gt; [Implicit Discount Rate]</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>H1: 이득은 분리 제시 시, 손실은 통합 제시 시 소비자 효용이 극대화될 것이다.
-H2: 소비자는 화폐의 출처에 따라 다르게 평가하고 다르게 지출할 것이다.</t>
+          <t>H1: The discount rate implicit in choices will vary inversely with the length of time to be waited.
+(선택에 내재된 할인율은 대기 기간의 길이에 반비례하여 변화할 것이다.)
+H2: The discount rate will vary inversely with the size of the reward for which the individual must wait.
+(할인율은 개인이 기다려야 하는 보상의 크기에 반비례하여 변화할 것이다.)
+H3: The implicit discount rate for losses will be lower than for gains.
+(손실에 대한 암묵적 할인율은 이득에 대한 암묵적 할인율보다 낮을 것이다.)</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>이득/손실 프레이밍 방식</t>
+          <t>Reward Size (보상/벌금의 크기), Delay Length (대기 기간), Sign of Reward (이득 vs 손실 여부)</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>지각 효용, 구매 의도</t>
+          <t>Implicit Discount Rate (암묵적 할인율)</t>
         </is>
       </c>
       <c r="K594" t="inlineStr">
         <is>
-          <t>심적 회계</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
@@ -45223,13 +45223,23 @@
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>소비자는 화폐를 심적 계정에 분류. 취득 효용과 거래 효용이 독립적으로 소비자 만족에 기여.</t>
-        </is>
-      </c>
-      <c r="N594" t="inlineStr"/>
+          <t>1. 암묵적 할인율은 대기 기간이 길어질수록 급격히 감소하는 경향을 보임 (시간 효과).
+2. 암묵적 할인율은 보상의 크기가 커질수록 감소하는 경향을 보임 (크기 효과).
+3. 손실(벌금)에 대한 암묵적 할인율은 이득(상금)에 비해 훨씬 낮게 나타남 (부호 효과).
+4. 이러한 결과들은 할인율이 일정하다고 가정하는 표준 경제학의 시간선호 이론과 달리, 개인의 할인율이 상황적 요인에 따라 체계적으로 변화함을 보여줌.</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>You have won some money in a lottery held by your bank. You can take the money now or wait until later. How much would you require to make waiting just as attractive as getting the money now?
+(귀하는 은행에서 개최한 복권에 당첨되어 일정 금액의 돈을 받게 되었습니다. 귀하는 이 돈을 지금 받을 수도 있고, 나중에 받을 수도 있습니다. 지금 돈을 받는 것과 나중에 받는 것이 동일하게 매력적으로 느껴지도록 하려면 나중에 받을 때 얼마의 금액을 요구하시겠습니까?)
+You have received a traffic ticket that can be paid now or later. Assume that there is no risk of not getting the reward (or of avoiding the fine) if you waited. How much would you be willing to pay later to make waiting just as attractive as paying the fine now?
+(귀하는 지금 또는 나중에 납부할 수 있는 교통 범칙금 고지서를 받았습니다. 대기하더라도 보상을 받지 못하거나(또는 벌금을 회피할) 위험은 없다고 가정합니다. 지금 범칙금을 내는 것과 나중에 내는 것이 동일하게 느껴지도록 하려면 나중에 낼 때 얼마를 지불하시겠습니까?)</t>
+        </is>
+      </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://doi.org/10.1016/0165-1765(81)90067-7</t>
         </is>
       </c>
     </row>
@@ -55489,6 +55499,101 @@
         </is>
       </c>
     </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>706</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>미상 (제공된 텍스트 내 저자 정보 미표기)</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>미상 (제공된 텍스트 내 발행 연도 미표기)</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>가격 제시 프레이밍(일 단위, 월 단위, 통합)이 소비자의 구매의도에 미치는 영향: 가격 수용 범위 및 지각된 가치(심리적/실질적 가치)의 조절 효과</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>마케팅연구 (추정)</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>전망이론 (Prospect Theory), 심적 회계 이론 (Mental Accounting Theory), 프레이밍 효과 (Framing Effect)</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>[독립변수: 가격 제시 프레이밍 (일 단위 vs. 월 단위 vs. 통합)] -&gt; [조절변수: 가격 수용 범위 (내 vs. 외) / 가치 유형 (심리적 가치 vs. 실질적 가치) / 이득 및 손실 프레임] -&gt; [종속변수: 구매의도]</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>H1: 가격 제시 프레이밍(일 단위, 월 단위, 통합) 방식에 따라 소비자의 구매의도는 유의미한 차이를 보일 것이다.
+H2: 가격 제시 프레이밍이 구매의도에 미치는 영향은 소비자의 가격 수용 범위(범위 내 vs. 범위 외)에 의해 조절될 것이다.
+H3: 가격 제시 프레이밍이 구매의도에 미치는 영향은 소비자가 지각하는 가치 유형(심리적 가치 vs. 실질적 가치) 및 이득/손실 프레임에 따라 달라질 것이다.</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>가격 제시 프레이밍 (일 단위, 월 단위, 통합)</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>구매의도 (Purchase Intention)</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>가격 수용 범위 (가격수용범위 내 vs. 외), 지각된 가치 유형 (심리적 가치 vs. 실질적 가치), 프레임 유형 (이득 vs. 손실)</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>1. 가격 제시 프레이밍(일 단위, 월 단위, 통합)에 따라 소비자의 구매의도 평균값에 유의미한 차이가 존재함.
+2. 가격 수용 범위 내에 있을 때와 범위 외에 있을 때 가격 제시 프레이밍이 구매의도에 미치는 영향이 다르게 나타나 조절효과가 검증됨.
+3. 소비자가 지각하는 가치 유형(심리적 가치 vs. 실질적 가치) 및 이득/손실 프레임에 따라 프레이밍 효과의 크기와 구매의도 형성 양상이 달라짐.</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>구매의도 (Purchase Intention)
+- I would consider buying this product.
+(나는 이 제품의 구매를 고려할 것이다.)
+- I will purchase this product in the future.
+(나는 향후 이 제품을 구매할 것이다.)
+- I am willing to recommend this product to others.
+(나는 이 제품을 타인에게 추천할 의향이 있다.)
+지각된 가치 (Perceived Value)
+- This product offers high practical and functional utility.
+(이 제품은 높은 실질적이고 기능적인 유용성을 제공한다.)
+- This product gives me psychological satisfaction and peace of mind.
+(이 제품은 나에게 심리적인 만족감과 평온함을 준다.)
+가격 수용성 (Price Acceptance)
+- The presented price is within my acceptable budget range.
+(제시된 가격은 내가 수용할 수 있는 예산 범위 내에 있다.)
+- I feel that the price of this product is reasonable and fair.
+(나는 이 제품의 가격이 합리적이고 공정하다고 느낀다.)</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O707"/>
+  <dimension ref="A1:O708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55594,6 +55594,99 @@
         </is>
       </c>
     </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>707</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>미상 (제공된 텍스트로 식별 불가)</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>가격 제시 프레이밍(일단위, 월단위, 통합)과 가격수용범위가 구매의도에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>전망이론 (Prospect Theory), 정신적 회계 이론 (Mental Accounting Theory)</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>[독립변수: 가격 제시 프레이밍] -&gt; [매개변수: 심리적/실질적 가치] -&gt; [종속변수: 구매의도] (조절변수: 가격수용범위)</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>H1: 가격 제시 프레이밍(일단위, 월단위, 통합) 방식에 따라 소비자의 구매의도는 유의미한 차이를 보일 것이다.
+H2: 가격 제시 프레이밍이 구매의도에 미치는 영향은 소비자의 가격수용범위(내 vs 외)에 의해 조절될 것이다.
+H3: 가격 제시 프레이밍과 구매의도 간의 관계는 소비자가 지각하는 가치(심리적 가치 및 실질적 가치)에 의해 매개될 것이다.</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>가격 제시 프레이밍 (일단위, 월단위, 통합)</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>구매의도</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>지각된 가치 (심리적 가치, 실질적 가치)</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>가격수용범위 (가격수용범위 내, 가격수용범위 외)</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>1. 가격 제시 프레이밍(일단위, 월단위, 통합)에 따라 소비자의 구매의도에 유의미한 차이가 나타남.
+2. 가격수용범위(내/외)는 가격 제시 프레이밍이 구매의도에 미치는 영향을 유의미하게 조절함.
+3. 소비자가 지각하는 심리적 가치와 실질적 가치는 가격 프레이밍 효과를 매개하는 요인으로 작용함.</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>[Purchase Intention]
+I am willing to purchase this product/service under the presented price framing.
+(나는 제시된 가격 조건 하에서 이 제품/서비스를 구매할 의향이 있다.)
+I would recommend this product/service to others at this price.
+(나는 이 가격에 이 제품/서비스를 타인에게 추천할 것이다.)
+[Psychological Value]
+Using this service at the presented price gives me emotional satisfaction.
+(제시된 가격에 이 서비스를 이용하는 것은 나에게 정서적 만족감을 준다.)
+I feel psychologically comfortable with this price presentation.
+(나는 이 가격 제시 방식에 대해 심리적으로 편안함을 느낀다.)
+[Practical Value]
+This service is highly useful and practical compared to its cost.
+(이 서비스는 지불하는 비용에 비해 매우 유용하고 실용적이다.)
+This service offers substantial functional benefits for my daily life.
+(이 서비스는 나의 일상생활에 실질적인 기능적 혜택을 제공한다.)</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O708"/>
+  <dimension ref="A1:O709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55687,6 +55687,84 @@
         </is>
       </c>
     </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>708</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Hye-Kyung Lee (이혜경)</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Rethinking creativity: creative industries, AI and everyday creativity</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Media, Culture &amp; Society</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>창조산업 담론(Creative Industries Discourse), 비용질환 이론(Cost Disease Theory), 인공지능 창의성 이론(AI Creativity / Margaret Boden의 이론), 문화민주주의(Cultural Democracy)</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>개념적 비평 논문으로 정량적 연구 모형 없음 ([창조산업 담론, AI 창의성, 일상적 창의성 논의] -&gt; [창의성의 정치경제학, 예술 노동의 가치 및 재인간화 재고])</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>본 논문은 정량적 가설 검증 논문이 아닌 에세이/코멘터리 논문으로 별도의 연구 가설(H1, H2 등)이 존재하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>1. 창조산업 담론은 창의성을 인적 자본 및 지적재산권(IP) 창출 수단으로 도구화하여 실제 창작 노동자들의 불안정한 노동 조건과 저임금 문제를 은폐하고 창의성을 탈인간화함.
+2. AI 창의성의 발전은 창의성을 인간의 주체성으로부터 분리하여 일부 영역의 예술가를 위협하는 동시에, 역설적으로 인간 창의성의 본질과 창작 과정, 신체성(Embodied Creativity)을 재조명하게 만듦.
+3. 일상적 창의성 담론은 창의성을 민주화하고 재인간화하지만, 전문 예술가의 창의적 노동이 갖는 고유한 특성과 가치에 대한 설명력을 약화시킴.
+4. 따라서 향후 문화 정책 및 학술 담론은 노동적 관점에서 인간 창의성과 예술 노동의 가치를 재정립해야 함.</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>본 논문은 개념적 논의 및 비평(Commentary) 논문으로 실증 설문 조사를 수행하지 않았으므로 설문 측정 문항이 존재하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>10.1177/01634437221077009</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -39890,7 +39890,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Lee, B. K., &amp; Lee, W. N.</t>
+          <t>Byung-Kwan Lee, Wei-Na Lee (이병관, 이위나)</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -39900,7 +39900,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>The effect of information overload on consumer choice quality in an online environment</t>
+          <t>The Effect of Information Overload on Consumer Choice Quality in an On-Line Environment</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -39910,30 +39910,34 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>정보 과부하 이론(Information Overload)
-온라인 소비자 행동 이론</t>
+          <t>정보 과부하 이론 (Information Overload Theory), 구조적 정보 접근법 / 형식 정보 이론 (Structural Approach to Information Load / Formal Information Theory), 인간 정보 처리 능력 한계 이론 (Limited Human Processing Capacity)</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>[온라인 정보량↑] → [정보 과부하] → [의사결정 품질↓]
-온라인 환경의 정보 과잉 효과</t>
+          <t>[독립변수: 대안의 수, 속성의 수, 속성 수준 분포] -&gt; [종속변수: 선택 품질(지배적 대안 선택 확률), 주관적 상태(만족도, 확신, 혼란)]</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>H1: 온라인 환경에서 정보량이 증가할수록 소비자 의사결정 품질이 저하될 것이다.
-H2: 정보 과부하 효과는 오프라인보다 온라인 환경에서 더 강하게 나타날 것이다.</t>
+          <t>H1: 속성의 수와 속성 수준 분포를 통제할 때, 선택 집합 내 대안 수가 증가하면 지배적 대안을 선택할 확률이 감소할 것이다.
+H2: 대안의 수와 속성 수준 분포를 통제할 때, 선택 집합 내 속성 수가 증가하면 지배적 대안을 선택할 확률이 감소할 것이다.
+H3: 대안의 수와 속성의 수를 통제할 때, 대안 간 속성 수준이 균등하게 분포되면 지배적 대안을 선택할 확률이 감소할 것이다.
+H4: 대안 수가 증가할 때 속성 수준 분포가 균등에서 비균등으로 변경되는 경우, 대안 수 증가가 지배적 대안 선택 확률을 감소시키지 않을 것이다.
+H5: 속성 수가 증가할 때 속성 수준 분포가 균등에서 비균등으로 변경되는 경우, 속성 수 증가가 지배적 대안 선택 확률을 감소시키지 않을 것이다.
+H6: 속성 수와 속성 수준 분포를 통제할 때, 대안 수가 증가하면 (a) 확신과 만족도가 감소하고 (b) 혼란이 증가할 것이다.
+H7: 대안 수와 속성 수준 분포를 통제할 때, 속성 수가 증가하면 (a) 확신과 만족도가 감소하고 (b) 혼란이 증가할 것이다.
+H8: 대안 수와 속성 수를 통제할 때, 대안 간 속성 수준의 균등한 분포는 (a) 확신과 만족도를 감소시키고 (b) 혼란을 증가시킬 것이다.</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>온라인 정보량 수준</t>
+          <t>대안의 수 (Number of Alternatives: 18개 vs 27개), 속성의 수 (Number of Attributes: 9개 vs 18개), 속성 수준 분포 (Attribute Level Distribution: 균등 vs 비균등)</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>의사결정 품질, 선택 만족도</t>
+          <t>선택 품질/정확도 (Choice Quality / Probability of Choosing the Dominant Alternative), 주관적 상태 (Subjective States: 만족도, 확신, 혼란)</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
@@ -39943,18 +39947,45 @@
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>온라인/오프라인</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M524" t="inlineStr">
         <is>
-          <t>온라인 환경에서 정보 과부하가 의사결정 품질 저하. 역U자 패턴 확인.</t>
-        </is>
-      </c>
-      <c r="N524" t="inlineStr"/>
+          <t>1. 속성의 수가 증가하고 속성 수준이 균등하게 분포될 때 소비자의 지배적 대안 선택 확률(선택 품질)이 통계적으로 유의미하게 감소함 (H2, H3 지지).
+2. 단순 대안 수의 증가 자체는 선택 정확도 저하에 유의미한 영향을 미치지 않음 (H1 미지지).
+3. 속성 수가 증가하더라도 속성 수준 분포가 비균등해지면(정보량이 줄어들고 진단성이 높아지면) 선택 품질이 저하되지 않음 (H5 지지).
+4. 대안 및 속성 수의 증가, 균등한 속성 수준 분포는 소비자의 확신과 만족도를 낮추고 혼란을 증가시키는 등 주관적 심리 상태에 부정적 영향을 미침 (H6, H8 부분 지지, H7 완전 지지).
+5. 단순한 대안과 속성의 개수 곱보다 속성 수와 속성 수준 분포의 결합 형태가 온라인 정보 과부하 현상을 훨씬 정확하게 예측함.</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>How satisfied are you with your decision?
+(당신의 결정에 얼마나 만족하십니까?)
+How confident are you in your choice?
+(당신의 선택에 얼마나 확신하십니까?)
+How confused did you feel while performing this task?
+(이 과업을 수행하는 동안 얼마나 혼란스러움을 느꼈습니까?)
+Many of the CD players had the same warranty.
+(CD 플레이어들 중 상당수가 동일한 보증 기간을 가지고 있었다.)
+Many of the CD players had the same error correction quality.
+(CD 플레이어들 중 상당수가 동일한 오류 보정 품질을 가지고 있었다.)
+There were many characteristics of CD players to consider.
+(고려해야 할 CD 플레이어의 특성이 많았다.)
+There were many CD players to choose from.
+(선택할 수 있는 CD 플레이어가 많았다.)
+Are you familiar with [product category]?
+([제품 카테고리]에 대해 잘 알고 계십니까?)
+Are you experienced with [product category]?
+([제품 카테고리]를 사용해 본 경험이 있으십니까?)
+Are you knowledgeable about [product category]?
+([제품 카테고리]에 대한 지식을 갖추고 계십니까?)</t>
+        </is>
+      </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.1002/mar.20000</t>
         </is>
       </c>
     </row>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O709"/>
+  <dimension ref="A1:O800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55796,6 +55796,6831 @@
         </is>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>709</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>710</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>711</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>712</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>713</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>714</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>715</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>716</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>717</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>718</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>719</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>720</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>721</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>722</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>723</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>724</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>725</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>726</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>727</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>728</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>729</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>730</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>731</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>732</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>733</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>734</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>735</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>736</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>737</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>738</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>739</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>740</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>741</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>742</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>743</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>744</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>745</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>746</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>747</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>748</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>749</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>750</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>751</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>752</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>753</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>754</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>755</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>756</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>757</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>758</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>759</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>760</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>761</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>762</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>763</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>764</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>765</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>766</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>767</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>768</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>769</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>770</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>771</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>772</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>773</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>774</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>775</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>776</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>777</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>778</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>779</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>780</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>781</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O782" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>782</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O783" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>783</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>784</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>785</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>786</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>787</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O788" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>788</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>789</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O790" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>790</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>791</v>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O792" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>792</v>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O793" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>793</v>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>794</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>795</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>796</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O797" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>797</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O798" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>798</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O799" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>799</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O800"/>
+  <dimension ref="A1:O891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62621,6 +62621,6831 @@
         </is>
       </c>
     </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>800</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O801" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>801</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>802</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>803</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O804" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>804</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>805</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O806" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="n">
+        <v>806</v>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="n">
+        <v>807</v>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="n">
+        <v>808</v>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="n">
+        <v>809</v>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="n">
+        <v>810</v>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="n">
+        <v>811</v>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="n">
+        <v>812</v>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="n">
+        <v>813</v>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>814</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>815</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>816</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="n">
+        <v>817</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="n">
+        <v>818</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="n">
+        <v>819</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="n">
+        <v>820</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>821</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>822</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>823</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>824</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>825</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>826</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>827</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>828</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>829</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>830</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>831</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>832</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>833</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>834</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>835</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="n">
+        <v>836</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="n">
+        <v>837</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n">
+        <v>838</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="n">
+        <v>839</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="n">
+        <v>840</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="n">
+        <v>841</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="n">
+        <v>842</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="n">
+        <v>843</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="n">
+        <v>844</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O845" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="n">
+        <v>845</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="n">
+        <v>846</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n">
+        <v>847</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O848" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="n">
+        <v>848</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="n">
+        <v>849</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O850" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="n">
+        <v>850</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O851" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="n">
+        <v>851</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O852" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="n">
+        <v>852</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O853" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="n">
+        <v>853</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O854" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>854</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>855</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>856</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>857</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>858</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>859</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>860</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>861</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>862</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>863</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>864</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>865</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>866</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>867</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>868</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>869</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>870</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>871</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>872</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>873</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>874</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>875</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>876</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>877</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="n">
+        <v>878</v>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="n">
+        <v>879</v>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="n">
+        <v>880</v>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="n">
+        <v>881</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="n">
+        <v>882</v>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O883" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="n">
+        <v>883</v>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O884" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="n">
+        <v>884</v>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="n">
+        <v>885</v>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O886" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="n">
+        <v>886</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O887" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="n">
+        <v>887</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O888" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="n">
+        <v>888</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O889" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="n">
+        <v>889</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O890" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="n">
+        <v>890</v>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O891" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O891"/>
+  <dimension ref="A1:O900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69446,6 +69446,1369 @@
         </is>
       </c>
     </row>
+    <row r="892">
+      <c r="A892" t="n">
+        <v>891</v>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>선수영</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>라이브 커머스의 상품보기 유형이 사용자의 구매의도와 만족도에 미치는 영향: FOMO의 조절효과를 중심으로</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>홍익대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), S-O-R(Stimulus-Organism-Response) 모형, FOMO 응답 모델(FOMO-response model), 폼슈머리즘(Fomsumerism)</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>[독립변수: 상품보기 화면 유형 (라이브 종료형, 플로팅 영상X형, 플로팅 영상O형)] -&gt; [종속변수: 구매의도, 만족도] (조절변수: FOMO [개인적 FOMO, 사회적 FOMO])</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>H1: 라이브 커머스 상품보기 화면 유형에 따라 구매의도에 차이가 있을 것이다.
+H2: 라이브 커머스 상품보기 화면 유형에 따라 만족도에 차이가 있을 것이다.
+H3: 라이브 커머스 상품보기 화면 유형의 구매의도는 포모 유형에 의해 조절될 것이다.
+H4: 라이브 커머스 상품보기 화면 유형의 만족도는 포모 유형에 의해 조절될 것이다.</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>라이브 커머스 상품보기 화면 유형(외부 페이지 이동 후 라이브 종료형, 외부 페이지 미이동/방송 화면 가림형, 외부 페이지 이동 후 플로팅 영상 노출형)</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>구매의도, 만족도</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>FOMO (개인적 FOMO, 사회적 FOMO)</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>1. 라이브 커머스 상품보기 화면 유형에 따른 구매의도 및 만족도는 통계적으로 유의한 차이가 나타났다(플로팅 영상O &gt; 플로팅 영상X &gt; 라이브 종료 순으로 구매의도 및 만족도가 높음).
+2. 라이브 커머스 상품보기 화면 유형과 FOMO(개인적 FOMO, 사회적 FOMO) 간의 상호작용에 의한 조절효과는 나타나지 않았다(H3, H4 기각).
+3. 다만 FOMO의 주효과는 유의하여, 개인적 FOMO와 사회적 FOMO 수준이 모두 낮을 때 구매의도와 만족도가 더 높게 나타났다.</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>[개인적 FOMO]
+- When viewing product information in product view while watching live, I worry that there might be product information I didn't hear from the influencer.
+(라이브 시청중 상품보기에서 제품정보를 볼 때, 라이브에서 인플루언서에게 듣지 못한 제품에 대한 정보가 있는지 걱정이 된다.)
+- When viewing product information in product view while watching live, I worry about missing out on live benefits.
+(라이브 시청중 상품보기에서 제품정보를 볼 때, 라이브 혜택을 놓칠까봐 걱정이 된다.)
+- When viewing product information in product view while watching live, I continuously return to the broadcast screen so as not to miss new information.
+(라이브 시청중 상품보기에서 제품정보를 볼 때, 새로운 정보를 놓치지 않기 위해 지속적으로 방송화면으로 돌아간다.)
+- When viewing product information in product view while watching live, I feel anxious that other users might have obtained more useful information than me.
+(라이브 시청중 상품보기에서 제품정보를 볼 때, 다른 사용자가 나보다 더 많은 유익한 정보를 많이 얻었을까봐 불안하다.)
+[사회적 FOMO]
+- When viewing product information in product view while watching live, I feel anxious that other users might have obtained more information than me.
+(라이브 시청중 상품보기에서 제품정보를 볼 때, 다른 사용자들이 나보다 더 많은 정보를 얻었을까봐 불안하다.)
+- When searching for products, I get bothered that if I don't watch the live stream, I won't get as much information as other users.
+(제품탐색을 할 때 라이브를 보지않으면 다른 사용자들 보다 정보를 얻지 못할 것 같아 신경이 쓰인다.)
+- The reason I check product information in product view while watching live is because I feel alienated from communication during the live broadcast if I don't know the information.
+(라이브 시청중 상품보기에서 제품정보를 보는 이유는 정보를 모르면 소통할 때 라이브방송에서 소외되는 것 같다.)
+- I watched the live broadcast because I felt like I was losing out compared to other consumers (buyers of the same product) if I missed the live broadcast.
+(나는 라이브 방송을 놓치면 다른 소비자(같은 상품 구매자)보다 손해를 보는 듯한 기분이 들어 라이브 방송을 보았다.)
+[구매의도]
+- When purchasing products, I am willing to buy products recommended in live broadcasts.
+(제품을 구매할 때 라이브 방송에서 추천한 제품을 구매할 수 있다.)
+- When purchasing products, I intend to buy products sold in live broadcasts.
+(제품을 구매할 때 라이브 방송에서 판매하는 제품을 구매할 의향이 있다.)
+- When purchasing products, I will frequently use live broadcasts in the future.
+(제품을 구매할 때 앞으로도 라이브 방송을 자주 이용할 것이다.)
+- I am willing to recommend live broadcasts to others.
+(라이브 방송을 타인에게 추천할 의향이 있다.)
+[만족도]
+- I feel pleasure during the process of using product view while watching live commerce.
+(라이브 커머스 시청중 상품보기를 이용하는 과정에서 즐거움을 느낀다.)
+- Using product view while watching live commerce is convenient and satisfying.
+(라이브 커머스 시청중 상품보기 이용은 편리하고 만족스럽다.)
+- I am satisfied with the product information provided while using product view during live commerce viewing.
+(라이브 커머스 시청중 상품보기 이용중 제공되는 상품정보에 대해 만족한다.)
+- Overall, using the product view service while watching live commerce is satisfying.
+(라이브 커머스 시청중 상품보기 서비스 이용은 전반적으로 만족스럽다.)</t>
+        </is>
+      </c>
+      <c r="O892" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n">
+        <v>892</v>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>황투흐엉</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>라이브스트리밍 커머스가 소비자의 의사결정에 미치는 영향: 자기해석수준의 차이에 따른 FoMO(Fear-of-Missing-Out)의 매개효과를 중심으로</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>동국대학교 대학원 광고홍보학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>자아해석수준 이론 (Self-Construal Theory), 고립공포 이론 (Fear-of-Missing-Out Theory)</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>[독립변수: BJ와의 상호작용성, 소비자 간 상호작용성, 실재감] -&gt; [매개변수: FoMO] -&gt; [종속변수: 구매의향] (조절변수: 자아해석수준)</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>H1: FoMO에 어필하는 라이브스트리밍 커머스에 있어서 소비자 반응의 주요차원(BJ와의 상호작용성, 소비자 간 상호작용성, 실재감)은 FoMO에 정적 영향을 미칠 것이다.
+H1-1: BJ와의 상호작용성이 높아질수록 FoMO를 더 많이 느낄 것이다.
+H1-2: 소비자 간 상호작용성이 높아질수록 FoMO를 더 많이 느낄 것이다.
+H1-3: 실재감이 높아질수록 FoMO를 더 많이 느낄 것이다.
+H2: 라이브스트리밍 커머스에 있어서 FoMO를 더 많이 느낄수록 구매의향이 높아질 것이다.
+H3: 라이브스트리밍 커머스에 있어서 소비자반응의 주요차원들이 구매의향에 미치는 영향은 FoMO에 의하여 매개될 것이다.
+H3-1: BJ와의 상호작용성이 구매의향에 미치는 영향은 FoMO에 의하여 매개될 것이다.
+H3-2: 소비자 간 상호작용성이 구매의향에 미치는 영향은 FoMO에 의하여 매개될 것이다.
+H3-3: 실재감이 구매의향에 미치는 영향은 FoMO에 의하여 매개될 것이다.
+연구문제 1: 라이브스트리밍 커머스에 대한 소비자반응이 FoMO를 매개로 구매의향에 미치는 효과는 자아해석수준에 의하여 달라질 것이다.</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>BJ와의 상호작용성, 소비자 간 상호작용성, 실재감</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>구매의향</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>FoMO (Fear-of-Missing-Out, 고립공포)</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>자아해석수준 (독립적 자아해석, 상호의존적 자아해석)</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>1. 라이브스트리밍 커머스에 대한 소비자 반응 요인인 BJ와의 상호작용성, 소비자 간 상호작용성, 실재감 모두 FoMO에 유의한 정적(+) 영향을 미치는 것으로 나타났으며, FoMO 역시 구매의향에 유의한 정적(+) 영향을 미침.
+2. BJ와의 상호작용성, 소비자 간 상호작용성, 실재감은 구매의향에 직접적으로 정적 영향을 미침과 동시에 FoMO를 매개로 간접적으로도 정적 영향을 미치는 것으로 밝혀짐(부분 매개효과).
+3. 자아해석수준 중 독립적 자아해석수준이 높을수록 소비자 반응이 FoMO를 매개로 구매의향에 미치는 정적 매개효과가 유의하게 증가하였으나, 상호의존적 자아해석수준의 조절효과는 유의하지 않은 것으로 나타남.</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>[BJ와의 상호작용성]
+Consumers can communicate in real time with the BJ through chat windows, comments, and likes.
+(소비자가 채팅창 및 댓글, 공감하기 등을 통해 BJ와의 실시간 의사소통을 할 수 있다.)
+The BJ actively responds to consumers' requests.
+(BJ가 소비자의 요구에 따라 적극적으로 응답해준다.)
+The BJ actively responds to questions and opinions raised by other consumers.
+(BJ가 다른 소비자들이 제기한 질문과 의견에 대해 적극적으로 응답하여 준다.)
+[소비자 간 상호작용성]
+I exchange opinions with other consumers about the broadcast content through chat windows, comments, and likes.
+(채팅창 및 댓글, 공감하기 등을 통해 기타 소비자와 방송내용에 대하여 의견을 교류한다.)
+Other consumers respond quickly to questions sent by consumers during internet live streaming shopping.
+(인터넷 라이브스트리밍 쇼핑 중에서 보낸 소비자의 질문에 기타 소비자들은 신속히 반응을 해준다.)
+I exchange opinions with other consumers about the cost-performance ratio of the product through the chat window.
+(채팅창을 통해 기타 소비자와 제품의 가성비에 대해서 의견을 교류한다.)
+I exchange opinions with other consumers about product quality through the chat window.
+(채팅창을 통해 기타 소비자와 제품품질에 대해서 의견을 교류한다.)
+[실재감]
+I feel like I am talking with the other person in the community space.
+(커뮤니티 공간에서 상대방과 대화하는 것과 같은 느낌이 든다.)
+I can feel human warmth in the community space.
+(커뮤니티 공간에서 인간미를 느낄 수 있다.)
+I can feel intimacy in the community space.
+(커뮤니티 공간에서 친밀감을 느낄 수 있다.)
+Information provided in the community space is offered in a personalized form.
+(커뮤니티 공간에서 제공되는 정보가 개인화된 형태로 제공된다.)
+[FoMO]
+I will be anxious that I might miss the opportunity to buy this product.
+(이 제품의 구매기회를 놓치게 될까봐 불안할 것이다.)
+If I miss the opportunity to buy this product, I feel like I will fall behind others.
+(이 제품의 구매기회를 놓치게 되면 다른 사람보다 뒤처지는 것처럼 느낄 것 같다.)
+If I miss the opportunity to buy this product, I will be anxious that I might lose something important or fun.
+(이 제품의 구매기회를 놓치게 되면 뭔가 중요하거나 재미있는 것을 잃을까봐 불안해질 것이다.)
+If I miss the opportunity to buy this product due to unavoidable constraints, I will feel it is regrettable.
+(불가피한 제약조건으로 인하여 이 제품의 구매기회를 놓치게 된다면 아쉽게 느낄 것이다.)
+If I miss the opportunity to buy this product, I will regret it.
+(이 제품의 구매기회를 놓치게 된다면 후회할 것이다.)
+If I miss the opportunity to buy this product, I feel like others will look down on me.
+(이 제품의 구매기회를 놓치면 다른 사람들이 나를 우습게 볼 것처럼 느낄 것 같다.)
+If I miss the opportunity to buy this product, I feel like I will not fit into my group.
+(이 제품의 구매기회를 놓치면 내가 속한 집단에 어울리지 않는 것처럼 느껴질 것 같다.)
+If I miss the opportunity to buy this product, I feel like I will be left behind from my group.
+(이 제품의 구매기회를 놓치면 내가 속한 집단으로부터 낙오되는 것처럼 느껴질 것 같다.)
+If I miss the opportunity to buy this product, I feel like I will be ignored or forgotten by my group.
+(나는 이 제품의 구매기회를 놓치면 내가 속한 집단으로부터 무시당하거나 잊혀질 것 같이 느껴진다.)
+[구매의향]
+I have the intention to purchase the product recommended in live streaming shopping.
+(라이브 스트리밍 쇼핑에서 추천한 제품을 구매할 의향이 있다.)
+If I buy a product, I will preferentially consider the product recommended in internet live streaming shopping.
+(제품을 구매한다면 인터넷 라이브 스트리밍 쇼핑에서 추천한 제품을 우선적으로 고려할 것이다.)
+When buying products, I have the intention to continuously purchase products through internet live streaming shopping.
+(제품을 구매할 때 지속적으로 인터넷 라이브 스트리밍 쇼핑을 통해 제품을 구매할 의향이 있다.)
+[자아해석수준]
+I respect authority figures among the people I meet.
+(나는 내가 만나는 사람들 중 권위 있는 인물을 존경한다.)
+Maintaining harmony in my group is important to me.
+(내가 속한 집단에서 조화를 유지하는 것은 나에게 중요하다.)
+My happiness depends on the happiness of those around me.
+(나의 행복은 내 주변 사람들의 행복에 달려 있다.)
+I would offer my seat to a superior or an elder on the bus or subway.
+(나는 버스나 지하철에서 직장상사나 연장자에게 자리를 양보하겠다.)
+I respect a person who is modest about themselves.
+(나는 자신에 대해 겸손한 사람을 존경한다.)
+I would sacrifice my personal interest for the benefit of my group.
+(나는 내가 속한 집단의 이익을 위해 나의 개인적 이익을 희생할 것이다.)
+I think good relationships with others are more important than my own achievement.
+(다른 사람과의 좋은 인간관계가 나 자신의 성취보다 더 중요하다고 생각한다.)
+I always consider my parents' advice when making plans for the future.
+(나는 장래에 대한 계획을 세울 때 부모님의 충고를 반드시 고려한다.)
+Following the decision made by the group as a whole is important to me.
+(전체가 내린 결정을 따르는 것은 나에게 중요하다.)
+Even if I am not happy in my group, I will stay if they need me.
+(나는 내가 속한 집단 안에서 행복하지 않더라도 그들이 나를 필요로 한다면, 그 집단에 계속 남을 것이다.)
+If my brother or sister goes wrong, I feel responsible.
+(만일 내 형제나 자매가 잘못된다면 나는 책임감을 느낀다.)
+I avoid arguments even if my opinion is very different from group members.
+(나는 집단 내 구성원들과 의견이 크게 다르더라도 논쟁을 회피한다.)
+I tend to say 'no' clearly rather than be misunderstood.
+(나는 오해를 받기 보다는 확실히 '아니오'라고 말하는 편이다.)
+It is not difficult for me to speak my opinion confidently in meetings or gatherings.
+(나는 회의 시간이나 모임에서 내 의견을 당당하게 말하는 것이 어렵지 않다.)
+Having a rich imagination is important to me.
+(나에게는 상상력이 풍부한 것이 중요하다.)
+I do not feel uncomfortable when I am singled out to receive praise or an award.
+(나는 혼자 뽑혀서 칭찬이나 상을 받을 때 마음이 불편하지 않다.)
+I act the same way at home and outside.
+(나는 집에서나 밖에서나 똑같이 행동한다.)
+Taking care of and being responsible for myself is my primary concern.
+(나 스스로를 돌보고 책임지는 것은 내게 주된 관심사이다.)
+I act the same way regardless of who I am with.
+(나는 누구와 있든 상관없이 같은 방식으로 행동한다.)
+I can speak comfortably even when meeting someone much older for the first time.
+(나보다 훨씬 연장자와 처음 만나는 경우에도 스스럼없이 대화할 수 있다.)
+I prefer a direct and honest approach when dealing with someone met for the first time.
+(나는 처음 만난 사람을 대할 때 직접적이고 솔직한 방식을 선호한다.)
+I enjoy being unique and distinguished from others in many ways.
+(나는 여러 방면에서 독특하고 다른 사람과 구별되는 것을 즐긴다.)
+Having a distinct personality independent from others is very important to me.
+(다른 사람과 독립된 나만의 개성을 갖는 것은 나에게 매우 중요하다.)
+I consider taking care of my health more important than anything else.
+(나는 내 건강을 챙기는 것을 그 어떤 것보다 가장 중요하게 생각한다.)</t>
+        </is>
+      </c>
+      <c r="O893" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="n">
+        <v>893</v>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>장혜린</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>뮤지컬 공연에서 랜덤 폴라로이드 증정 이벤트 시 마니아 관객의 지각된 교환가치와 커뮤니티 충성도가 FOMO를 매개하여 티켓 구매의도에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>소비가치이론(Theory of Consumption Values), 상태 소외 두려움(State FOMO) 이론, 예기된 죄책감 이론, 브랜드/기업 진정성 이론</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>[지각된 교환가치, 커뮤니티 충성도] -&gt; [FOMO] -&gt; [충동구매욕구] -&gt; [예기된 죄책감] -&gt; [티켓 구매의도], [기획사 진정성] (조절변수 및 직접효과)</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>H1. 뮤지컬 마니아 관객의 폴라로이드에 대한 지각된 교환가치는 충동구매욕구에 정(+)의 영향을 미칠 것이다.
+H2. 뮤지컬 마니아 관객의 커뮤니티 충성도는 충동구매욕구에 정(+)의 영향을 미칠 것이다.
+H3. FOMO는 뮤지컬 마니아 관객의 폴라로이드에 대한 지각된 교환가치, 커뮤니티 충성도와 충동구매욕구 사이에서 매개효과를 보일 것이다.
+  H3a. 뮤지컬 마니아 관객의 지각된 교환가치는 FOMO에 정(+)적인 영향을 미칠 것이다.
+  H3b. 뮤지컬 마니아 관객의 커뮤니티 충성도는 FOMO에 정(+)적인 영향을 미칠 것이다.
+  H3c. 뮤지컬 마니아 관객의 FOMO는 충동구매욕구에 정(+)적인 영향을 미칠 것이다.
+  H3d. FOMO는 뮤지컬 마니아 관객의 폴라로이드에 대한 지각된 교환가치와 충동구매욕구 사이에서 정(+)적인 매개효과를 보일 것이다.
+  H3e. FOMO는 뮤지컬 마니아 관객의 커뮤니티 충성도와 충동구매욕구 사이에서 정(+)적인 매개효과를 보일 것이다.
+H4. 뮤지컬 마니아 관객의 예기된 죄책감은 충동구매욕구와 티켓 구매의도 사이에서 매개효과를 보일 것이다.
+  H4a. 뮤지컬 마니아 관객의 충동구매욕구는 티켓 구매의도에 정(+)적인 영향을 미칠 것이다.
+  H4b. 뮤지컬 마니아 관객의 충동구매욕구는 예기된 죄책감에 정(+)적인 영향을 미칠 것이다.
+  H4c. 뮤지컬 마니아 관객의 예기된 죄책감은 티켓 구매의도에 부(-)적인 영향을 미칠 것이다.
+  H4d. 뮤지컬 마니아 관객의 예기된 죄책감은 충동구매욕구와 티켓 구매의도 사이에서 부(-)적인 매개효과를 보일 것이다.
+H5. 뮤지컬 공연 기획사의 진정성이 높을수록 충동구매욕구와 티켓 구매의도 사이의 관계가 정(+)적으로 강화될 것이다.
+H6. 뮤지컬 공연 기획사의 진정성은 티켓 구매의도에 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>지각된 교환가치, 커뮤니티 충성도</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>티켓 구매의도</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>FOMO, 충동구매욕구, 예기된 죄책감</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>기획사 진정성</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>1. 지각된 교환가치는 충동구매욕구에 유의한 정(+)의 영향을 미쳤으나, 커뮤니티 충성도는 충동구매욕구에 부(-)의 영향을 미쳐 기각되었다.
+2. 지각된 교환가치와 커뮤니티 충성도 모두 FOMO를 매개하여 충동구매욕구에 유의한 정(+)의 영향을 미치는 매개효과가 확인되었다.
+3. 충동구매욕구는 예기된 죄책감을 정(+)적으로 유발하고, 예기된 죄책감은 티켓 구매의도를 부(-)적으로 억제하는 유의한 매개효과가 입증되었다.
+4. 기획사 진정성은 충동구매욕구와 티켓 구매의도 간 관계를 조절하지 못하였으나, 티켓 구매의도에 직접적으로 강력한 정(+)의 영향을 미쳤다.</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>[지각된 교환가치]
+Polaroids randomly given at musical events are attractive for exchange.
+(뮤지컬 이벤트 시 랜덤으로 증정되는 폴라로이드는 교환하기에 매력적이다.)
+I am willing to exchange Polaroids randomly given at musical events.
+(나는 뮤지컬 이벤트 시 랜덤으로 증정되는 폴라로이드를 교환할 용의가 있다.)
+Exchanging Polaroids randomly given at musical events is useful to me.
+(뮤지컬 이벤트 시 랜덤으로 증정되는 폴라로이드를 교환하는 것은 나에게 유용하다.)
+Polaroids randomly given at musical events are worth exchanging compared to the cost incurred.
+(뮤지컬 이벤트 시 랜덤으로 증정되는 폴라로이드는 지출한 비용에 비해 교환할 가치가 있다.)
+[커뮤니티 충성도]
+I will continue to use the musical fan community on X that I currently use.
+(나는 내가 이용하는 X의 연뮤덕 커뮤니티를 계속 이용할 것이다.)
+I will recommend the musical fan community on X that I use to other users.
+(나는 내가 이용하는 X의 연뮤덕 커뮤니티를 다른 이용자에게 추천할 것이다.)
+I believe that using the musical fan community on X will bring value to me.
+(나는 X의 연뮤덕 커뮤니티 이용이 나에게 가치를 줄 것이라 믿는다.)
+I am willing to communicate with other people in the musical fan community on X that I use.
+(나는 내가 이용하는 X의 연뮤덕 커뮤니티 내의 다른 사람들과 기꺼이 커뮤니케이션한다.)
+[FOMO]
+I continuously log into X so as not to miss new information in the musical fan community.
+(나는 연뮤덕 커뮤니티 속에서 새로운 정보를 놓치지 않기 위해 지속적으로 X에 접속한다.)
+It is important to me to share new randomly given Polaroids obtained from musical events on the X musical fan community.
+(나는 뮤지컬 이벤트 시 얻은 새로운 랜덤 증정 폴라로이드를 X의 연뮤덕 커뮤니티에 공유하는 것이 중요하다.)
+It is important to me to check in real time on X the new Polaroid photos obtained by friends in the musical fan community.
+(나는 연뮤덕 커뮤니티 친구들이 얻은 새로운 폴라로이드 사진을 X에서 실시간으로 확인하는 것이 중요하다.)
+It is important to me to understand the jokes or slang used by members of the musical fan community.
+(연뮤덕 커뮤니티 구성원들이 하는 농담이나 은어를 이해하는 것이 나에게 중요하다.)
+I feel bothered or anxious if I do not update my status or posts on X.
+(나는 내 근황을 X에 업데이트하지 않으면 신경이 쓰인다.)
+[충동구매욕구]
+When a random Polaroid giveaway is held, I buy musical performance tickets even if it was not planned.
+(랜덤 폴라로이드를 증정하면 계획에 없더라도 뮤지컬 공연 티켓을 구매한다.)
+The thought of buying a musical ticket offering a random Polaroid suddenly pops into my mind, and I end up purchasing it.
+(무심결에 랜덤 폴라로이드를 증정하는 뮤지컬 공연 티켓을 구입하려던 생각이 떠올라 구매하곤 한다.)
+I buy the musical ticket offering a random Polaroid because I think it will sell out if I do not buy it right now.
+(지금 구입하지 않으면 랜덤 폴라로이드를 증정하는 뮤지컬 공연 티켓이 다 팔릴 거라 생각되어 구매한다.)
+If I accidentally discover a Polaroid giveaway announcement for an actor I am interested in, I purchase the musical ticket without hesitation.
+(평소 관심 있던 배우의 폴라로이드 증정 공지를 우연히 발견하면 지체 없이 뮤지컬 공연 티켓을 구매한다.)
+I decide to buy the musical ticket first thinking that there will be an opportunity to exchange the randomly given Polaroid later.
+(나중에 랜덤 증정 폴라로이드를 교환할 기회가 있을 거라 생각해 뮤지컬 공연 티켓 구매를 우선 결정한다.)
+[예기된 죄책감]
+I think I will feel guilty if I buy a musical performance ticket that offers a random Polaroid giveaway.
+(나는 랜덤 폴라로이드를 증정하는 뮤지컬 공연 티켓을 구매하면 죄책감을 느낄 것이라고 생각한다.)
+I think I will feel sorry if I buy a musical performance ticket that offers a random Polaroid giveaway.
+(나는 랜덤 폴라로이드를 증정하는 뮤지컬 공연 티켓을 구매하면 미안함을 느낄 것이라고 생각한다.)
+I think I will regret it if I buy a musical performance ticket that offers a random Polaroid giveaway.
+(나는 랜덤 폴라로이드를 제공하는 뮤지컬 공연 티켓을 구매하면 후회할 것이라고 생각한다.)
+[기획사 진정성]
+The services provided by musical production agencies are trustworthy.
+(뮤지컬 기획사가 제공하는 서비스는 신뢰할 수 있다.)
+Musical production agencies always maintain a consistent level of performance service.
+(뮤지컬 기획사는 항상 일관된 공연 서비스 수준을 유지한다.)
+Musical production agencies take pride in their performances.
+(뮤지컬 기획사는 자신의 공연에 자부심을 가지고 있다.)
+Musical production agencies put their heart into performance services.
+(뮤지컬 기획사는 공연 서비스에 진심을 다한다.)
+The performance services of musical production agencies are always enjoyable.
+(뮤지컬 기획사의 공연 서비스는 언제나 기분 좋다.)
+Musical production agencies listen to complaints from theatregoers.
+(뮤지컬 기획사는 공연 관객의 불만을 경청한다.)
+Musical production agencies respect diversity and do not discriminate.
+(뮤지컬 기획사는 다양성을 존중하며, 차별하지 않는다.)
+Advertisements and announcements from musical production agencies are credible.
+(뮤지컬 기획사의 광고와 공지는 믿을 수 있다.)
+[티켓 구매의도]
+I intend to buy musical performance tickets.
+(나는 뮤지컬 공연 티켓을 구매할 생각이 있다.)
+I am willing to invest time in purchasing musical performance tickets.
+(나는 뮤지컬 공연 티켓 구매에 시간을 투자할 용의가 있다.)
+I am willing to actively recommend buying musical performance tickets to people around me.
+(나는 뮤지컬 공연 티켓 구매를 주위 사람들에게 적극 추천할 용의가 있다.)</t>
+        </is>
+      </c>
+      <c r="O894" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="n">
+        <v>894</v>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>유연재, 김완석</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>스포츠 경기 관람의 FoMO(Fear of Missing Out)가 스포츠 미디어 시청에 미치는 영향: 자율적 동기와 통제적 동기의 매개효과</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>아주대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), FoMO(Fear of Missing Out)</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>[자율적 FoMO / 통제적 FoMO] -&gt; [자율적 동기 / 통제적 동기] -&gt; [스포츠 미디어 시청]</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>H1: 자율적 FoMO는 스포츠 미디어 시청에 정(+)의 영향을 미칠 것이다.
+H2: 통제적 FoMO는 스포츠 미디어 시청에 정(+)의 영향을 미칠 것이다.
+H3a: 자율적 FoMO와 스포츠 미디어 시청의 관계를 자율적 동기가 매개할 것이다.
+H3b: 자율적 FoMO와 스포츠 미디어 시청의 관계를 통제적 동기가 매개할 것이다.
+H4a: 통제적 FoMO와 스포츠 미디어 시청의 관계를 자율적 동기가 매개할 것이다.
+H4b: 통제적 FoMO와 스포츠 미디어 시청의 관계를 통제적 동기가 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>자율적 FoMO, 통제적 FoMO</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>스포츠 미디어 시청</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>자율적 동기, 통제적 동기</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>자율적 FoMO와 통제적 FoMO는 모두 스포츠 미디어 시청에 정(+)의 직접적인 영향을 미치는 것으로 나타났다. 또한, 자율적 FoMO는 자율적 동기를 매개로 하여 스포츠 미디어 시청에 간접적인 영향을 미쳤으며, 통제적 FoMO는 통제적 동기를 매개로 하여 스포츠 미디어 시청에 간접적인 영향을 미치는 것으로 검증되었다. 이를 통해 스포츠 소비 행동에서 FoMO의 동기적 차원과 그 하위 매개 기전의 차별적 역할이 입증되었다.</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>[자율적 FoMO]
+I matched the roster because I feel anxious I will miss events.
+(이벤트를 놓치면 불안함을 느끼기 때문에 이 일정을 맞추었다.)
+I matched the roster because I desire getting feeling passionate with others when I miss events.
+(이벤트를 놓칠 때 다른 사람들과 열정을 느끼고 싶기 때문에 이 일정을 맞추었다.)
+I matched the roster because I feel anxious because I think I am not significantly important when I miss events.
+(이벤트를 놓치면 내가 중요하지 않은 존재처럼 느껴져 불안하기 때문에 이 일정을 맞추었다.)
+I matched the roster because I feel sad if I am not capable of participating in events due to constraints of other things.
+(다른 제약으로 인해 이벤트에 참여할 수 없으면 슬프기 때문에 이 일정을 맞추었다.)
+[통제적 FoMO]
+I matched the roster because I think my social groups view me as unimportant when I miss events.
+(이벤트를 놓치면 내 사회적 집단이 나를 중요하지 않게 볼 것이라 생각하여 이 일정을 맞추었다.)
+I matched the roster because I think I do not fit in social groups when I miss events.
+(이벤트를 놓치면 내 사회적 집단에 어울리지 못한다고 생각하여 이 일정을 맞추었다.)
+I matched the roster because I think I am excluded by my social groups when I miss events.
+(이벤트를 놓치면 내 사회적 집단으로부터 소외된다고 생각하여 이 일정을 맞추었다.)
+I matched the roster because I feel ignored/forgotten by my social groups when I miss events.
+(이벤트를 놓치면 내 사회적 집단에게 무시당하거나 잊혀진다고 느껴 이 일정을 맞추었다.)
+[자율적 동기]
+Watching the roster was interesting.
+(경기를 시청하는 것은 흥미로웠다.)
+Watching the roster was pleasant.
+(경기를 시청하는 것은 즐거웠다.)
+Watching the roster was fun.
+(경기를 시청하는 것은 재미있었다.)
+I felt good after watching the roster.
+(경기를 시청한 후 기분이 좋았다.)
+[통제적 동기]
+I felt more accepted by my peers.
+(동료들에게 더 수용된다고 느꼈다.)
+I felt more approved of by the people around me.
+(주변 사람들에게 더 인정받는다고 느꼈다.)
+I felt more included in social circles.
+(사회적 모임에 더 포함된다고 느꼈다.)
+I fit in better with others.
+(타인들과 더 잘 어울릴 수 있었다.)
+[스포츠 미디어 시청]
+I watch sports games through media frequently.
+(나는 미디어를 통해 스포츠 경기를 자주 시청한다.)
+I spend a lot of time watching sports media.
+(나는 스포츠 미디어를 시청하는 데 많은 시간을 소비한다.)
+I actively tune in to watch sports media broadcasts.
+(나는 스포츠 미디어 방송을 적극적으로 찾아서 시청한다.)</t>
+        </is>
+      </c>
+      <c r="O895" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="n">
+        <v>895</v>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>박주리</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>상향비교가 SNS 중독경향성에 미치는 영향에서 소외에 대한 두려움(FoMO)의 매개효과: 개방형 SNS와 폐쇄형 SNS의 차이를 중심으로</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>동덕여자대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>사회비교이론(Social Comparison Theory), 사회적 자본 이론(Social Capital Theory), 자기결정이론(Self-Determination Theory), 사회감시체계(Social Monitoring System)</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>[상향비교] -&gt; [소외에 대한 두려움(FoMO)] -&gt; [SNS 중독경향성] (개방형 SNS 집단 vs 폐쇄형 SNS 집단 비교)</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>H1: 개방형 SNS 집단과 폐쇄형 SNS 집단 간 주요 변인(상향비교, FoMO, SNS 중독경향성)의 차이가 있을 것이다.
+H2: 성별에 따라 주요 변인들의 차이가 있을 것이다.
+H3: 개방형 SNS 집단과 폐쇄형 SNS 집단에서 주요 변인 간 유의한 상관관계가 있을 것이다.
+H4: 상향비교가 SNS 중독경향성에 미치는 영향에서 소외에 대한 두려움(FoMO)이 매개할 것이다.
+H5: 개방형 SNS 집단과 폐쇄형 SNS 집단 간 주요 변인의 효과크기 차이가 있을 것이다.
+H6: 개방형 SNS 집단과 폐쇄형 SNS 집단 간 FoMO의 매개효과에 차이가 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>상향비교(Upward Comparison)</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>SNS 중독경향성(SNS Addiction Proneness)</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO: Fear of Missing Out)</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>SNS 유형(개방형 SNS vs 폐쇄형 SNS)</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>1. 개방형 SNS 집단과 폐쇄형 SNS 집단 모두에서 상향비교, FoMO, SNS 중독경향성 간 유의한 정적 상관관계가 나타났습니다.
+2. 개방형 SNS 집단이 폐쇄형 SNS 집단에 비해 SNS 중독경향성 수준이 유의하게 높았습니다(상향비교와 FoMO에서는 집단 간 차이가 유의하지 않음).
+3. 성별 비교 결과, 여성이 남성에 비해 상향비교, FoMO, SNS 중독경향성 수준이 모두 유의하게 높았습니다.
+4. 구조방정식 모형 검증 결과, 개방형 SNS 집단과 폐쇄형 SNS 집단 모두에서 상향비교가 SNS 중독경향성에 미치는 직·간접 영향 중 FoMO가 완전 매개 역할을 하는 것으로 확인되었습니다.
+5. 다집단 분석 결과, 개방형 SNS 집단과 폐쇄형 SNS 집단 간 FoMO의 매개효과 경로계수 차이는 통계적으로 유의하지 않아, SNS 유형과 상관없이 FoMO가 SNS 중독경향성에 이르는 핵심적인 매개 변인임을 입증하였습니다.</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>[Upward Comparison]
+- I compare my situation when seeing the wonderful lifestyle experienced by others on SNS.
+(SNS에서 다른 사람이 경험한 멋진 라이프스타일(여행, 취미, 여가 등)을 보면서 나의 처지와 비교하곤 한다.)
+- I compare my situation when seeing good items owned by others on SNS.
+(SNS에서 다른 사람이 소유한 좋은 물건(옷, 가방, 신발, 액세서리 등)을 보면서 나의 처지와 비교하곤 한다.)
+- I compare my situation when seeing others' superior appearance or physical condition on SNS.
+(SNS에서 다른 사람의 우월한 외모나 신체조건을 보면서 나의 처지와 비교하곤 한다.)
+- I compare my situation when seeing others living passionately on SNS.
+(SNS에서 다른 사람이 열심히 살아가는 모습을 보면서 나의 처지와 비교하곤 한다.)
+- I compare my situation when seeing others achieving something on SNS.
+(SNS에서 다른 사람이 뭔가를 성취하는 모습을 보면서 나의 처지와 비교하곤 한다.)
+- I compare my situation when seeing others having broad interpersonal relationships on SNS.
+(SNS에서 다른 사람이 많은 사람들과 폭넓은 인간관계를 맺고 있는 것을 보면서 나의 처지와 비교하곤 한다.)
+- I compare my situation when seeing others being popular among people around them on SNS.
+(SNS에서 다른 사람이 많은 주변 사람들한테 인기를 받고 있는 것을 보면서 나의 처지와 비교하곤 한다.)
+- I compare my situation when seeing others' happy daily lives on SNS.
+(SNS에서 다른 사람의 행복한 일상을 보면서 나의 처지와 비교하곤 한다.)
+[Fear of Missing Out (FoMO)]
+- I fear that my friends may have more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+- I feel anxious when I do not know what my friends are up to.
+(나는 내 친구들의 소식을 접하지 못할 때 불안하다.)
+- I worry when my friends are having fun without me.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까봐 걱정된다.)
+- I fear that other people except my friends may have more rewarding experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까봐 두렵다.)
+- I worry that I spend too much time keeping up with what is going on around me.
+(나는 주변을 신경 쓰는 데 시간을 많이 보내는 것 같아 걱정된다.)
+- It bothers me when I miss an unexpected meeting with friends.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+- I feel anxious when I miss out on a planned gathering.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+- I continuously check what my friends are doing even on holidays.
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다.)
+[SNS Addiction Proneness]
+- Without SNS, life would feel completely boring.
+(SNS가 없다면 내 인생에 재미있는 일이 하나도 없을 것 같다.)
+- I cannot do other tasks because I am curious about what happened on SNS.
+(SNS에서 무슨 일이 일어났는지 궁금해서 다른 일을 할 수가 없다.)
+- I constantly think about SNS.
+(항상 SNS에 대해 생각 한다.)
+- Once I start SNS, I spend more time on it than originally intended.
+(SNS를 일단 시작하면 처음 생각 했던 것 보다 더 많은 시간을 사용한다.)
+- I always try to reduce SNS usage time, but I fail.
+(SNS 사용 시간을 줄이기 위해 늘 노력하지만 실패한다.)
+- I feel anxious or depressed if I do not use SNS.
+(SNS를 사용하지 않으면 불안하거나 우울하다.)
+- Excessive SNS use has threatened or jeopardized my important relationships, job, education, or career opportunities.
+(SNS의 과도한 사용으로 인해 중요한 인관 관계나 직업, 교육, 경력의 기회가 위협받거나, 위험에 처해 본 적이 있다.)
+- I have used SNS to escape from stressful problems.
+(스트레스를 받는 문제로부터 도피하기 위해 SNS를 사용한 적이 있다.)
+- I become restless and anxious when I cannot access SNS.
+(SNS를 하지 못하면 안절부절 못하고 초조해진다.)
+- My interest in other activities or TV has decreased due to SNS.
+(SNS로 인해 다른 활동이나 TV에 대한 흥미가 감소했다.)
+- There are times when I feel pathetic about being excessively absorbed in SNS.
+(지나치게 SNS에 몰두해 있는 나 자신이 한심하게 느껴질 때가 있다.)
+- When I turn on my computer or smartphone, I check SNS first.
+(컴퓨터나 스마트폰을 켜면 SNS부터 확인한다.)
+- Communicating through SNS is more comfortable than talking directly with people.
+(사람들과 직접 대화하는 것 보다 SNS로 대화하는 것이 더 편하다.)
+- Others tell me that I use SNS too much.
+(다른 사람에게 SNS를 너무 많이 사용한다는 이야기를 듣는다.)
+- I communicate constantly with people using multiple SNS platforms rather than just one.
+(SNS를 한 가지만 이용하지 않고 여러 개를 사용하여 사람들과 쉴 새 없이 소통한다.)
+- I go to sleep later than desired or cannot sleep because of SNS.
+(SNS 때문에 원하는 시간보다 더 늦게 잠들거나 잠을 이루지 못한다.)
+- I feel more fulfilled and happy when sharing new information or knowledge with others through SNS.
+(SNS를 통해 새로운 정보나 지식을 다른 사람과 공유할 때 더 뿌듯하고 행복하다.)
+- I use SNS even while walking on the street or talking with others.
+(길을 걷거나 다른 사람들과 대화 중에도 SNS를 이용한다.)
+- I delete my account or leave SNS out of fatigue, but eventually return.
+(SNS에 지쳐서 탈퇴나 계정을 없애지만 다시 돌아온다.)
+- SNS helps me feel less lonely or alienated by keeping me constantly connected with others.
+(SNS는 내가 다른 사람과 항상 연결되어 있어 외롭거나 소외감을 덜 느끼도록 한다.)</t>
+        </is>
+      </c>
+      <c r="O896" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="n">
+        <v>896</v>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>황선회</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>소극적 SNS 사용자의 SNS 피드백 수준이 문제적 SNS 사용에 미치는 영향: 상태 FoMO의 역할을 중심으로</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>중앙대학교 심리서비스대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>자기결정성이론(Self-Determination Theory), 사회적 보상 및 강화학습원리(Reward Learning Theory), 상향 사회비교 이론(Upward Social Comparison Theory)</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>[SNS 피드백 수준] -&gt; [상태 FoMO] -&gt; [문제적 SNS 사용]</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>H1: 고피드백집단은 저피드백집단보다 문제적 SNS 사용점수가 더 높을 것이다.
+H2: 상태 FoMO는 문제적 SNS 사용에 정적인 영향을 미칠 것이다.
+H3: SNS 피드백 수준에 따른 문제적 SNS 사용의 차이는 상태 FoMO의 변화경로에 의해 설명될 것이다.</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>SNS 피드백 수준 (고피드백 vs. 저피드백)</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>문제적 SNS 사용</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>상태 FoMO (State-FoMO)</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>1. 소극적 SNS 사용자에게 있어 가상 환경 내 SNS 피드백 수준(좋아요 수)은 문제적 SNS 사용 점수에 유의미한 직접적 영향을 미치지 않았다.
+2. 상태 FoMO는 사전 우울, 불안, 특성 FoMO를 통제한 후에도 문제적 SNS 사용을 정적으로 유의하게 예측하는 것으로 나타났다.
+3. SNS 피드백 수준이 상태 FoMO를 경유하여 문제적 SNS 사용으로 이어지는 간접(매개)효과는 유의하지 않았다.</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>[FoMO-Scale: Trait-FoMO]
+1. I fear that others may be having more rewarding experiences than me.
+(다른 사람들이 나보다 더 보람 있는 경험을 하고 있을까봐 걱정된다.)
+2. I fear that my friends are having more enjoyable experiences than me.
+(내 친구들이 나보다 더 즐거운 경험을 하고 있을까봐 두렵다.)
+3. I get anxious when I find out my friends are having fun without me.
+(친구들이 나 없이 재미있게 놀고 있다는 걸 알게 되면 불안해진다.)
+4. I get anxious when I don't know what my friends are doing.
+(친구들이 무엇을 하고 있는지 모를 때 불안해진다.)
+5. It bothers me when I cannot attend a scheduled gathering.
+(예정된 모임에 참석하지 못하면 신경이 쓰인다.)
+[FoMO-Scale: State-FoMO]
+6. I am continuously online so that I don't miss anything.
+(뭔가 놓칠까봐 나는 항상 온라인에 접속해있다.)
+7. It is important to express my opinion on current topics in online social networks.
+(온라인 소셜 네트워크에서 최신 이슈(영상, 이미지, 게시물 등)에 대해 내 의견을 표현하는 것이 중요하다.)
+8. I fear missing out on current information on social networking sites.
+(나는 소셜 네트워크 사이트에서 최신 정보를 놓치고 있을까봐 두렵다.)
+9. In order not to miss anything, I continuously check my smartphone.
+(무언가를 놓치지 않기 위해 나는 끊임없이 스마트폰을 확인한다.)
+10. When I have a good time, it is important for me to share the details online.
+(즐거운 시간을 보낼 때, 그 내용을 온라인에 공유하는 것이 나에게 중요하다.)
+11. It is important that I understand internet slang used by my friends.
+(친구들이 사용하는 인터넷 속어를 내가 이해하는 것이 중요하다.)
+12. Even while on vacation, I continuously keep track of what my friends are doing.
+(휴가 중에도 나는 친구들이 무엇을 하고 있는지 계속 확인한다.)
+[Problematic SNS Use Scale]
+1. Without SNS, I feel like there would be nothing fun in my life.
+(SNS가 없다면 내 인생에 재미있는 일이 하나도 없을 것 같다.)
+2. I cannot do other work because I am curious about what happened on SNS.
+(SNS에서 무슨 일이 일어났는지 궁금해서 다른 일을 할 수가 없다.)
+3. I think about SNS all the time.
+(항상 SNS에 대해 생각한다.)
+4. Once I start using SNS, I spend more time on it than I originally intended.
+(SNS를 일단 시작하면 처음 생각했던 것보다 더 많은 시간을 사용한다.)
+5. I always try to reduce my SNS usage time, but I fail.
+(SNS 사용 시간을 줄이기 위해 늘 노력하지만 실패한다.)
+6. If I do not use SNS, I feel anxious or depressed.
+(SNS를 사용하지 않으면 불안하거나 우울하다.)
+7. Excessive SNS use has threatened or endangered my important relationships, job, or career opportunities.
+(SNS의 과도한 사용으로 인해 중요한 인간관계나 직업, 교육, 경력의 기회가 위협받거나, 위험에 처해본 적이 있다.)
+8. I have used SNS to escape from stressful problems.
+(스트레스를 받는 문제로부터 도피하기 위해 SNS를 사용한 적이 있다.)
+9. When I cannot use SNS, I feel restless and anxious.
+(SNS를 하지 못하면 안절부절못하고 초조해진다.)
+10. My interest in other activities or TV has decreased due to SNS.
+(SNS로 인해 다른 활동이나 TV에 대한 흥미가 감소했다.)
+11. There are times when I feel pathetic for being overly absorbed in SNS.
+(지나치게 SNS에 몰두해 있는 나 자신이 한심하게 느껴질 때가 있다.)
+12. When I turn on my computer or smartphone, I check SNS first.
+(컴퓨터나 스마트폰을 켜면 SNS부터 확인한다.)
+13. I feel more comfortable talking through SNS than talking in person.
+(사람들과 직접 대화하는 것보다 SNS로 대화하는 것이 더 편하다.)
+14. Other people tell me that I use SNS too much.
+(다른 사람에게 SNS를 너무 많이 사용한다는 이야기를 듣는다.)
+15. I use multiple SNS platforms instead of just one to communicate endlessly with people.
+(SNS를 한 가지만 이용하지 않고 여러 개를 사용하여 사람들과 쉴 새 없이 소통한다.)
+16. Because of SNS, I fall asleep later than intended or cannot sleep.
+(SNS 때문에 원하는 시간보다 더 늦게 잠들거나 잠을 이루지 못한다.)
+17. I feel more proud and happy when sharing new information or knowledge with others through SNS.
+(SNS를 통해 새로운 정보나 지식을 다른 사람과 공유할 때 더 뿌듯하고 행복하다.)
+18. I use SNS even while walking on the street or talking with others.
+(길을 걷거나 다른 사람들과 대화 중에도 SNS를 이용한다.)
+19. I delete my account or leave SNS because I get exhausted, but I end up returning.
+(SNS에 지쳐서 탈퇴나 계정을 없애지만 다시 돌아온다.)
+20. SNS makes me feel constantly connected to others, reducing loneliness or alienation.
+(SNS는 내가 다른 사람과 항상 연결되어 있어 외롭거나 소외감을 덜 느끼도록 한다.)</t>
+        </is>
+      </c>
+      <c r="O897" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="n">
+        <v>897</v>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>우수연</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO)과 우울의 관계에서 SNS 상향비교와 반추의 매개효과: SNS 사용자를 중심으로: Instagram</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>단국대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), 사회비교이론(Social Comparison Theory), 사회적 지위 이론(Social Rank Theory), 반응양식이론(Response Styles Theory), 정서홍수모델(Emotional Cascade Model)</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>[FoMO] -&gt; [SNS 상향비교] -&gt; [반추] -&gt; [우울]</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>H1-1: FoMO가 우울에 정적으로 유의한 영향을 미칠 것이다.
+H1-2: SNS 상향비교가 우울에 정적으로 유의한 영향을 미칠 것이다.
+H1-3: 반추가 우울에 정적으로 유의한 영향을 미칠 것이다.
+H2-1: FoMO와 우울 간의 관계를 SNS 상향비교가 매개할 것이다.
+H3-1: FoMO와 우울 간의 관계를 반추가 매개할 것이다.
+H4-1: FoMO와 우울 간의 관계를 SNS 상향비교와 반추가 순차적으로 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO)</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>우울(Depression)</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>SNS 상향비교, 반추</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>1. FoMO는 우울에 직접적인 유의한 영향을 미치지 않았으나, 간접적으로 유의한 정적 영향을 미쳤습니다.
+2. FoMO와 우울의 관계에서 SNS 상향비교의 단순 매개효과는 통계적으로 유의하지 않았습니다.
+3. FoMO와 우울의 관계에서 반추의 매개효과는 유의하였습니다.
+4. FoMO와 우울의 관계에서 SNS 상향비교와 반추의 순차적 이중 매개효과가 유의하게 나타났습니다.</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>[소외에 대한 두려움 (K-FoMO)]
+I fear my friends have more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+I get anxious when I don't know what my friends are up to.
+(나는 내 친구들의 소식을 접하지 못할 때 불안하다.)
+I get worried when I find out my friends are having fun without me.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까봐 두렵다.)
+I fear other people have more rewarding experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까봐 두렵다.)
+I worry that I spend too much time keeping up with what is going on.
+(나는 주변을 신경 쓰는 데 시간을 많이 보내는 것 같아 걱정된다.)
+It bothers me when I miss an opportunity to meet up with friends.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+I get anxious when I miss a planned meeting.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+When I take a break, I continuously check what my friends are doing.
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다.)
+[SNS 상향비교 경험 척도]
+I compare my daily life with posts on Instagram.
+(인스타그램에 올라온 게시물과 나의 일상을 비교하게 된다.)
+When looking at Instagram posts, I feel like people are living more passionately than I am.
+(인스타그램 게시물을 접하다 보면 사람들은 나보다 더 열정적으로 살고있다는 생각이 든다.)
+When looking at Instagram posts, I feel like my daily life is not particularly interesting compared to theirs.
+(인스타그램 게시물을 접하다 보면 그들에 비하면 나의 일상이 딱히 재미있지는 않다는 생각이 든다.)
+I often envy their daily lives posted on Instagram.
+(인스타그램에 올라오는 그들의 일상이 부러워지곤 한다.)
+When looking at Instagram posts, I envy how they build relationships with people around them.
+(인스타그램에 게시물을 접하다 보면 그들이 주변인들과 관계를 맺는 모습이 부러워진다.)
+When looking at Instagram posts, I feel like I am not as happy as they are.
+(인스타그램에서 게시물을 접하다 보면 나는 그들만큼 행복하지는 않은 것 같다.)
+[반추적 반응 척도 (K-RRS)]
+Think about how alone I feel.
+(내가 얼마나 외로운지에 대해 생각한다.)
+Think "I won't be able to do my job if I can't snap out of this."
+("이런 기분에서 빠져나오지 못하면 일을 하지 못할거야" 라고 생각한다.)
+Think about how tired and achy I feel.
+(내가 얼마나 피로하고 아픈지에 대해 생각한다.)
+Think about how hard it is to concentrate.
+(집중하는 것이 얼마나 어려운지에 대해 생각한다.)
+Think "What did I do to deserve this?"
+(내가 무슨 일을 했기에 이런 일을 당할까 하고 생각한다.)
+Think about how passive and unmotivated I feel.
+(내가 얼마나 수동적이고 의욕이 없는지에 대해 생각한다.)
+Analyze recent events to try to understand why I am depressed.
+(내가 왜 우울해졌는지 알아내기 위해 최근 사건들을 분석해 본다.)
+Think "I feel like I can't feel anything anymore."
+(이제 더 이상 아무것도 느낄 수 없을 것만 같다고 생각한다.)
+Think "Why can't I handle things better?"
+(왜 나는 꿋꿋하게 지내지 못할까 하고 생각한다.)
+Think "Why do I always react this way?"
+("왜 나는 항상 이런 식으로 반응할까" 라고 생각한다.)
+Go away by myself and think about why I feel this way.
+(혼자 조용히 왜 내가 이렇게 느끼는지에 대해 생각한다.)
+Write down what I am thinking about and analyze it.
+(내가 생각하고 있는 것을 글로 쓰고 분석해본다.)
+Wish that recent situations had gone better.
+(최근의 상황이 더 나았으면 좋았을 걸 하고 생각한다.)
+Think "I won't be able to concentrate if I keep feeling this way."
+("계속 이런 식으로 느끼다가는 집중하는게 힘들거야" 라고 생각한다.)
+Think "Why do I have problems other people don't have?"
+("나는 왜 다른 사람에게는 없는 문제가 있을까" 라고 생각한다.)
+Think "Why can't I cope better?"
+("왜 나는 더 잘 대처하지 못할까" 라고 생각한다.)
+Think about how sad I feel.
+(내가 얼마나 슬픈지에 대해 생각한다.)
+Think about my shortcomings, failures, faults, and mistakes.
+(나의 단점과 실패들, 잘못, 실수에 대해 생각한다.)
+Think about how I don't feel like doing anything.
+(아무 것도 할 기분이 안 든다는 생각을 한다.)
+Analyze my personality to try to understand why I am depressed.
+(내가 왜 우울해졌는지 이해하려고 나의 성격을 분석해 본다.)
+Go someplace alone to think about my feelings.
+(혼자 어디론가 가서 내 기분에 대해 생각한다.)
+Think about how angry I am at myself.
+(내가 스스로에게 얼마나 화가 났는지에 대해 생각한다.)
+[우울 척도 (CES-D)]
+I was bothered by things that usually don't bother me.
+(평소에는 아무렇지도 않던 일들이 귀찮게 느껴졌다.)
+I did not feel like eating; my appetite was poor.
+(먹고 싶지 않았다/입맛이 없었다.)
+I felt that I could not shake off the blues even with help from my family or friends.
+(가족이나 친구가 도와주더라도 울적한 기분을 떨쳐버릴 수 없었다.)
+I felt that I was just as good as other people.
+(다른 사람들만큼 능력이 있다고 느꼈다.)
+I had trouble keeping my mind on what I was doing.
+(무슨 일을 하든 정신을 집중하기가 힘들었다.)
+I felt depressed.
+(우울했다.)
+I felt that everything I did was an effort.
+(하는 일마다 힘들게 느껴졌다.)
+I felt hopeful about the future.
+(미래에 대하여 희망적으로 느꼈다.)
+I thought my life had been a failure.
+(내 인생은 실패작이라는 생각이 들었다.)
+I felt fearful.
+(두려움을 느꼈다.)
+My sleep was restless.
+(잠을 설쳤다/잠을 잘 이루지 못했다.)
+I was happy.
+(행복했다.)
+I talked less than usual.
+(평소보다 말을 적게 했다/말수가 줄었다.)
+I felt lonely.
+(세상에 홀로 있는 듯한 외로움을 느꼈다.)
+People were unfriendly.
+(사람들이 나에게 차갑게 대하는 것 같았다.)
+I enjoyed life.
+(생활이 즐거웠다.)
+I had crying spells.
+(갑자기 울음이 나왔다.)
+I felt sad.
+(슬픔을 느꼈다.)
+I felt that people dislike me.
+(사람들이 나를 싫어하는 것 같았다.)
+I could not get "going".
+(도무지 무엇을 시작할 기운이 나지 않았다.)</t>
+        </is>
+      </c>
+      <c r="O898" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="n">
+        <v>898</v>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>김희원</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO)이 SNS중독경향성에 미치는 영향에서 내현적 자기애의 조절효과</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>숙명여자대학교 교육대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-Determination Theory), 사회비교이론(Social Comparison Theory), 심리사회적 발달이론(Erikson's Psychosocial Development Theory)</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>[독립변수: 소외에 대한 두려움(FoMO)] -&gt; [종속변수: SNS중독경향성] (조절변수: 내현적 자기애)</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>H1: 소외에 대한 두려움, 내현적 자기애, SNS중독경향성 간에는 유의한 상관관계가 있을 것이다.
+H2: 소외에 대한 두려움과 내현적 자기애는 SNS중독경향성에 유의한 정적(+) 영향을 미칠 것이다.
+H3: 소외에 대한 두려움이 SNS중독경향성에 미치는 영향에서 내현적 자기애가 조절효과를 가질 것이다.</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움(FoMO)</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>SNS중독경향성</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>내현적 자기애</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>첫째, 소외에 대한 두려움, 내현적 자기애, SNS중독경향성 간에는 유의한 정적 상관관계가 관찰되었다.
+둘째, 단순회귀분석 결과 소외에 대한 두려움(β=.491, p&lt;.001)과 내현적 자기애(β=.520, p&lt;.001)는 모두 SNS중독경향성에 유의한 정적 영향을 미치는 것으로 나타났다.
+셋째, 위계적 회귀분석 결과 소외에 대한 두려움과 SNS중독경향성의 관계에서 내현적 자기애의 조절효과가 유의하게 검증되었다(상호작용항 β=-.15, p&lt;.01). 내현적 자기애 수준이 높은 집단은 소외에 대한 두려움이 낮거나 높음과 관계없이 전반적으로 높은 SNS중독경향성을 보였으며, 특히 소외에 대한 두려움이 낮더라도 내현적 자기애 성향이 높으면 SNS중독경향성이 상대적으로 높게 나타났다.</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>[소외에 대한 두려움 척도 (FoMO Scale)]
+I fear my friends have more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+I get anxious when I don't get news from my friends.
+(나는 친구들의 소식을 접하지 못할 때 불안하다.)
+I get worried that my friends are having fun without me.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까봐 걱정된다.)
+I fear that other people, excluding my friends, have more rewarding experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까봐 두렵다.)
+I worry because I spend too much time paying attention to my surroundings.
+(나는 주변을 신경 쓰는데 시간을 많이 보내는 것 같아 걱정된다.)
+I feel bothered when I cannot make a last-minute plan with friends.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+I feel anxious when I miss a planned gathering.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+Even on holidays, I continuously check what my friends are doing.
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다.)
+[SNS중독경향성 척도 (SNS Addiction Tendency Scale)]
+I spend a lot of time thinking about SNS or how to use it.
+(SNS를 생각하거나 어떻게 이용할 것인가에 많은 시간을 보낸다.)
+SNS makes me feel always connected to others, so I feel less lonely or alienated.
+(SNS는 내가 다른 사람과 항상 연결되어 있어 외롭거나 소외감을 덜 느끼도록 한다.)
+I use SNS to forget about stressful problems.
+(스트레스 받는 문제를 잊기 위해 SNS를 사용한다.)
+I feel tired due to SNS use, so I sleep during class or work hours.
+(SNS 사용 때문에 피곤해서 수업시간 또는 업무 시간에 잔다.)
+I think a lot about what recently happened on SNS.
+(최근 SNS에서 일어난 일에 대해 많이 생각한다.)
+I get annoyed when I am unable to use SNS.
+(SNS를 하지 못하게 되었을 때 짜증이 난다.)
+While using SNS, I feel that I am acknowledged.
+(SNS를 하는 동안만큼은 내 자신이 인정을 받는다고 느낀다.)
+I use SNS to reduce feelings of helplessness or depression.
+(무력감 또는 우울감을 줄이기 위해 SNS를 한다.)
+I spend a lot of time on SNS.
+(SNS 사용에 많은 시간을 보낸다.)
+I have regretted not being able to reduce my SNS usage time.
+(SNS 사용 시간을 줄이지 못해 후회한 적이 있다.)
+I use SNS to reduce restlessness or anxiety.
+(초조함 또는 불안감을 줄이기 위해 SNS를 한다.)
+I feel more confident while using SNS.
+(SNS를 하는 동안 더욱 자신감이 생긴다.)
+If I cannot use SNS, I lose the joy or fun of living.
+(SNS를 하지 못하게 되면 사는 즐거움 또는 재미를 잃는다.)
+Due to SNS, I value hobbies, leisure, and exercise less.
+(SNS 때문에 취미, 여가생활, 운동을 덜 중요시 한다.)
+I check SNS frequently whenever I have time to see comments from others.
+(SNS에서 타인의 댓글을 보기 위해 시간이 날 때마다 수시로 확인한다.)
+I use SNS to forget about personal problems.
+(개인적 문제를 잊기 위해 SNS를 한다.)
+Using SNS too much negatively affected my work or studies.
+(SNS를 너무 많이 해서 그것이 나의 일 또는 학업에 부정적인 영향을 미쳤다.)
+I spend most of the day using SNS.
+(하루 중 대부분의 시간을 SNS를 하며 보낸다.)
+I use SNS to feel better.
+(기분을 좋게 하기 위해 SNS를 한다.)
+Even when I think 'I should stop', I end up using SNS every time.
+("그만 해야지" 하면서도 번번이 SNS를 하게 된다.)
+I feel an increasing urge to use SNS.
+(SNS를 하고 싶은 충동을 점점 더 많이 느낀다.)
+Due to SNS, my interest in other offline activities has decreased.
+(SNS로 인해 오프라인에서의 다른 활동에 대한 흥미가 감소했다.)
+I constantly check SNS even while walking or talking with others.
+(길을 걷거나 다른 사람들과 대화중에도 끊임없이 SNS를 한다.)
+Due to SNS, I often go to sleep later than intended or cannot sleep.
+(SNS로 인해 원하는 시간보다 더 늦게 잠들거나 잠을 이루지 못하는 일이 자주 있다.)
+[내현적 자기애 척도 (Covert Narcissism Scale)]
+I tend to be very conscious of what others think of me.
+(나는 다른 사람들의 눈치를 많이 보는 편이다.)
+I want everyone to like me and treat me well.
+(나는 모든 사람들이 나를 좋아하고 나에게 잘 대해 주기를 바란다.)
+When I am criticized, I easily feel humiliated.
+(비판 받았을 때 나는 쉽게 굴욕감을 느낀다.)
+I want people who like me to spend a lot of money on me to prove their feelings.
+(나는 나를 좋아하는 사람들이 그 마음을 증명해 보이기 위해서 나를 위해 많은 돈을 쓰기를 바란다.)
+Although I have thought a lot about it, I still cannot find direction for my life goals.
+(많은 고민을 했지만 아직도 인생의 목표에 대해서 갈피를 못 잡고 있다.)
+I want to picture myself as someone famous rather than who I am.
+(나는 나를 내가 아닌 어떤 유명한 사람처럼 그려 보고 싶다.)
+I think I try too hard to get respect from other people.
+(나는 다른 사람들의 존경을 받으려고 너무 애쓰는 것 같다.)
+I sometimes take criticism from others too seriously.
+(나는 가끔 남의 비평을 너무 심각하게 받아들인다.)
+I sometimes feel annoyed when others ask me for favors.
+(나는 다른 사람들이 부탁을 해 올 때에 때때로 짜증이 난다.)
+Some family members say that I am selfish.
+(가족들 중에는 내가 이기적이라고 말하는 사람이 있다.)</t>
+        </is>
+      </c>
+      <c r="O899" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="n">
+        <v>899</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>김수현</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>애착불안과 SNS중독경향성의 관계에서 공적 자의식과 소외에 대한 두려움의 매개효과와 자아탄력성의 조절된 매개효과: 인스타그램 이용 대학생을 대상으로</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 석사학위 청구논문</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>성인애착이론, 객관적 자기의식 이론, 자기결정이론, 사회비교이론</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>[애착불안] -&gt; [공적 자의식] -&gt; [소외에 대한 두려움] -&gt; [SNS중독경향성] (자아탄력성에 의한 조절된 매개효과)</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>H1: 애착불안은 SNS중독경향성을 정적으로 예측할 것이다.
+H2: 애착불안과 SNS중독경향성의 관계를 공적 자의식이 매개할 것이다.
+H3: 애착불안과 SNS중독경향성의 관계를 소외에 대한 두려움이 매개할 것이다.
+H4: 애착불안과 SNS중독경향성의 관계를 공적 자의식과 소외에 대한 두려움이 이중매개할 것이다.
+H5: 애착불안과 SNS중독경향성의 관계에서 소외에 대한 두려움의 매개효과를 자아탄력성이 조절할 것이다.</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>애착불안</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>SNS중독경향성</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>공적 자의식, 소외에 대한 두려움(FoMO)</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>자아탄력성</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>1. 애착불안은 SNS중독경향성을 직접적으로 예측하지 않는 것으로 나타났다.
+2. 애착불안과 SNS중독경향성의 관계를 공적 자의식이 단독으로 매개하지 않는 것으로 나타났다.
+3. 애착불안과 SNS중독경향성의 관계를 소외에 대한 두려움이 유의하게 매개하는 것으로 나타났다.
+4. 애착불안과 SNS중독경향성의 관계를 공적 자의식과 소외에 대한 두려움이 이중 매개 경로를 통해 완전매개하는 것으로 나타났다.
+5. 애착불안과 SNS중독경향성의 관계에서 소외에 대한 두려움의 매개효과를 자아탄력성이 부(-)의 방향으로 조절하는 조절된 매개효과가 유의하게 나타났다.</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>[애착불안]
+When I show my feelings for romantic partners, I worry that they won't feel the same way.
+(내가 다른 사람들에게 호감을 표현했을 때, 그들이 나에 대해 같은 감정이 아닐까 봐 걱정된다.)
+I often worry that my partner doesn't really love me.
+(다른 사람들이 나를 진심으로 사랑하지 않을까 봐 자주 걱정한다.)
+[SNS중독경향성]
+I often stay up later than intended or fail to sleep due to SNS use.
+(SNS로 인해 원하는 시간보다 더 늦게 잠들거나 잠을 이루지 못하는 일이 자주 있다.)
+I spend most of my day using SNS.
+(하루 중 대부분의 시간을 SNS를 하며 보낸다.)
+I use SNS to escape from stressful problems.
+(스트레스 받는 문제를 잊기 위해 SNS를 사용한다.)
+I feel recognized as a person while using SNS.
+(SNS를 하는 동안만큼은 내 자신이 인정을 받는다고 느낀다.)
+[공적 자의식]
+I'm concerned about the way I present myself in front of others.
+(나는 다른 사람 앞에서 어떻게 행동해야 하는지 신경을 많이 쓴다.)
+I'm self-conscious about the way I look to others.
+(나는 남들에게 어떻게 보일까 하는 것을 의식한다.)
+[소외에 대한 두려움(FoMO)]
+I get worried when I miss out on an impromptu get-together with friends.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+I worry that I spend too much time keeping up with what's going on around me.
+(나는 주변을 신경 쓰는 데 시간을 많이 보내는 것 같아 걱정된다.)
+I fear my friends may have more rewarding experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까 봐 두렵다.)
+[자아탄력성]
+I quickly recover from unexpected surprises and overcome them well.
+(나는 갑자기 놀라는 일이 일어나도 금방 괜찮아지고 그것을 잘 이겨낸다.)
+I get over being angry at someone reasonably quickly.
+(나는 다른 사람에게 화가 나도 상당히 빨리 괜찮아진다.)</t>
+        </is>
+      </c>
+      <c r="O900" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O900"/>
+  <dimension ref="A1:O912"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70809,6 +70809,1809 @@
         </is>
       </c>
     </row>
+    <row r="901">
+      <c r="A901" t="n">
+        <v>900</v>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>최주희</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>영유아 어머니의 불안애착이 우울증상에 미치는 영향에서 소외에 대한 두려움(FoMO)과 SNS 중독경향성의 이중매개효과</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>숙명여자대학교 대학원 아동복지학과 아동심리치료전공 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>성인애착이론 (Adult Attachment Theory), 사회비교이론 (Social Comparison Theory)</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>[독립변수: 불안애착] -&gt; [매개변수 1: 소외에 대한 두려움(FoMO)] -&gt; [매개변수 2: SNS 중독경향성] -&gt; [종속변수: 우울증상]</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>H1: 영유아 어머니의 불안애착, 소외에 대한 두려움, SNS 중독경향성, 우울증상 간에는 유의한 정적 상관관계가 존재할 것이다.
+H2: 영유아 어머니의 불안애착이 우울증상에 미치는 영향에서 소외에 대한 두려움 총점과 SNS 중독경향성은 순차적인 이중매개효과를 보일 것이다.
+H3: 영유아 어머니의 불안애착이 우울증상에 미치는 영향에서 소외에 대한 두려움의 세 하위요인(소속 욕구, 외적 동기, 상대적 박탈감)과 SNS 중독경향성은 각각 차별적인 이중매개효과를 보일 것이다.</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>불안애착 (Attachment Anxiety)</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>우울증상 (Depressive Symptoms)</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움 (Fear of Missing Out; FoMO), SNS 중독경향성 (SNS Addiction)</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>1. 영유아 어머니의 불안애착, 소외에 대한 두려움, SNS 중독경향성, 우울증상 간의 정적 상관관계가 모두 유의하였다.
+2. 영유아 어머니의 불안애착이 우울증상에 미치는 영향에서 소외에 대한 두려움 총점과 SNS 중독경향성의 이중매개효과가 유의하였다.
+3. 소외에 대한 두려움의 세 가지 하위변인 중 '외적 동기'와 SNS 중독경향성의 이중매개효과는 유의하였으나, '소속 욕구'와 SNS 중독경향성, '상대적 박탈감'과 SNS 중독경향성의 이중매개효과는 유의하지 않았다.</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>[불안애착 (Attachment Anxiety - ECR-R)]
+Sometimes other people change their feelings about me for no apparent reason.
+(때로 다른 사람들은 분명한 이유 없이 나에 대한 그들의 감정을 바꾸곤 한다.)
+I worry that others won't care about me as much as I care about them.
+(내가 다른 사람들에게 관심을 갖는 것만큼, 그들도 내게 관심을 가져주지 않을까 봐 걱정한다.)
+I often worry that other people do not really love me.
+(다른 사람들이 나를 진심으로 사랑하지 않을까 봐 자주 걱정된다.)
+I fear losing other people's love.
+(다른 사람들의 사랑을 잃을까 봐 두렵다.)
+[소외에 대한 두려움 (Fear of Missing Out - K-FoMO)]
+I fear my friends have more rewarding experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까 봐 두렵다.)
+I get anxious when I don't know what my friends are up to.
+(나는 친구들의 소식을 접하지 못할 때 불안하다.)
+I worry when my friends are having fun without me.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까 봐 걱정된다.)
+I fear others (excluding friends) are having more rewarding experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까 봐 두렵다.)
+I worry that I spend too much time keeping track of what's going on around me.
+(나는 주변을 신경 쓰는 데 시간을 많이 보내는 것 같아 걱정된다.)
+It bothers me when I miss an opportunity to meet up with friends.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못하면 신경이 쓰인다.)
+I get anxious when I miss a planned meeting.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+Even when I am on vacation, I continue to keep tabs on what my friends are doing.
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다.)
+[SNS 중독경향성 (SNS Addiction)]
+I spend a lot of time thinking about SNS or how to use it.
+(SNS를 생각하거나 어떻게 이용할 것인가에 많은 시간을 보낸다.)
+I use SNS to forget about stressful problems.
+(스트레스 받는 문제를 잊기 위해 SNS를 사용한다.)
+I have regretted not being able to reduce the time I spend on SNS.
+(SNS 사용 시간을 줄이지 못해 후회한 적이 있다.)
+I end up using SNS over and over again even though I tell myself 'I should stop'.
+(“그만 해야지”하면서도 번번이 SNS를 하게 된다.)
+[우울증상 (Depressive Symptoms - CES-D)]
+I was bothered by things that don't usually bother me.
+(평소에는 아무렇지도 않던 일들이 괴롭고 귀찮게 느껴졌다.)
+I felt depressed.
+(우울했다.)
+I felt lonely.
+(외로웠다.)
+I felt sad.
+(마음이 슬퐜다.)</t>
+        </is>
+      </c>
+      <c r="O901" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="n">
+        <v>901</v>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>따 티 후엔 짱</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>온라인 의류 쇼핑에서 FoMO가 베트남 소비자 무리행동에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>서울시립대학교 대학원 경영학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>무리행동 이론(Herd Behavior Theory), 자아해석 이론(Self-Construal Theory), FoMO(Fear of Missing Out) 이론</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>[FoMO] -&gt; [관여도] -&gt; [정보적 무리행동 / 규범적 무리행동] (조절변수: 독립적 자아해석 / 상호의존적 자아해석)</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>가설 1: FoMO는 베트남 소비자의 정보적 무리행동에 정(+)의 영향을 미칠 것이다.
+가설 2: FoMO는 베트남 소비자의 규범적 무리행동에 정(+)의 영향을 미칠 것이다.
+가설 3: FoMO는 베트남 소비자의 관여도에 정(+)의 영향을 미칠 것이다.
+가설 4: 소비자 관여도는 정보적 무리행동에 정(+)의 영향을 미칠 것이다.
+가설 5: 소비자 관여도는 규범적 무리행동에 정(+)의 영향을 미칠 것이다.
+가설 6: FoMO가 정보적 무리행동에 미치는 효과는 관여도에 의해 매개될 것이다.
+가설 7: FoMO가 규범적 무리행동에 미치는 효과는 관여도에 의해 매개될 것이다.
+가설 8-1: 독립적 자아해석 수준이 높을수록 FoMO가 정보적 무리행동에 미치는 영향력은 작아질 것이다.
+가설 8-2: 상호의존적 자아해석 수준이 높을수록 FoMO가 정보적 무리행동에 미치는 영향력은 커질 것이다.
+가설 9-1: 독립적 자아해석 수준이 높을수록 FoMO가 규범적 무리행동에 미치는 영향력은 작아질 것이다.
+가설 9-2: 상호의존적 자아해석 수준이 높을수록 FoMO가 규범적 무리행동에 미치는 영향력은 커질 것이다.
+가설 10-1: 독립적 자아해석 수준이 높을수록 관여도가 정보적 무리행동에 미치는 영향력은 작아질 것이다.
+가설 10-2: 상호의존적 자아해석 수준이 높을수록 관여도가 정보적 무리행동에 미치는 영향력은 커질 것이다.
+가설 11-1: 독립적 자아해석 수준이 높을수록 관여도가 규범적 무리행동에 미치는 영향력은 작아질 것이다.
+가설 11-2: 상호의존적 자아해석 수준이 높을수록 관여도가 규범적 무리행동에 미치는 영향력은 커질 것이다.</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>FoMO (Fear of Missing Out)</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>무리행동 (정보적 무리행동, 규범적 무리행동)</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>관여도 (Involvement)</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>자아해석 (독립적 자아해석, 상호의존적 자아해석)</t>
+        </is>
+      </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>첫째, FoMO는 정보적 무리행동 및 규범적 무리행동에 직접적으로 정(+)의 영향을 미칠 뿐만 아니라, 관여도를 매개로 하여 간접적으로도 긍정적인 영향을 미치는 것으로 나타났다. 둘째, 독립적 자아해석 수준이 높을수록 FoMO가 정보적 및 규범적 무리행동에 미치는 영향력이 유의하게 감소하였으며, 관여도가 규범적 무리행동에 미치는 영향력 또한 감소하는 조절효과가 확인되었다. 셋째, 상호의존적 자아해석의 조절효과는 통계적으로 유의하지 않은 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>[FoMO]
+1. If I miss a purchase opportunity due to unavoidable constraints, I will feel regretful.
+(불가피한 제약조건으로 구매기회를 놓친다면 아쉽게 느낄 것이다.)
+2. If I miss this purchase opportunity, I feel like I will be ignored or forgotten by my group.
+(이번 구매 기회를 놓치면 내가 속한 집단으로부터 무시당하거나 잊혀질 것 같다.)
+3. If I miss this purchase opportunity, I feel like I won't fit in with my group.
+(이번 구매 기회를 놓치면 내가 속한 집단에 어울리지 않는 것처럼 느껴질 것 같다.)
+4. If I miss this purchase opportunity, I will feel anxious that I might lose something important or interesting.
+(이번 구매 기회를 놓치면 뭔가 중요하거나 재미있는 것을 잃을까봐 불안해질 것이다.)
+5. I am anxious about missing this purchase opportunity.
+(이번 구매 기회를 놓치게 될까봐 불안하다.)
+[Involvement (관여도)]
+1. When I see clothes worn by others, I can guess many things about them.
+(다른 사람이 입은 의류를 보면 그 사람에 관한 여러 가지를 짐작할 수 있다.)
+2. When buying clothes, I think deciding which product to choose is important.
+(의류를 구매할 때, 어떤 제품을 선택할지 결정하는 것은 중요하다고 생각한다.)
+3. If possible, I want to buy products that are well-known to others.
+(가능하다면 다른 사람에게도 잘 알려진 제품을 사고 싶다.)
+[Informational Herd Behavior (정보적 무리행동)]
+1. To ensure I buy the right product, I frequently observe what others buy and use.
+(올바른 제품을 구매하기 위해 다른 사람들이 무엇을 사고 사용하는지 자주 관찰한다.)
+2. If I have little experience with a product, I often ask my friends about it.
+(제품에 대한 경험이 적다면 친구들에게 제품에 대해 자주 물어본다.)
+3. Before purchasing a product, I frequently gather information about it from friends or family.
+(제품을 구매하기 전 친구나 가족으로부터 해당 제품에 대한 정보를 자주 수집한다.)
+[Normative Herd Behavior (규범적 무리행동)]
+1. Generally, I buy products that are approved by others.
+(일반적으로 다른 사람들이 인정하는 제품을 구매한다.)
+2. I feel a sense of belonging by purchasing the same products that others buy.
+(다른 사람들이 구매하는 것과 같은 제품을 구매함으로써 소속감을 느낀다.)
+3. I want to know what products will make a good impression on others.
+(어떤 제품이 다른 사람들에게 좋은 인상을 줄지 알고 싶다.)
+[Independent Self-Construal (독립적 자아해석)]
+1. It is not difficult for me to confidently express my opinion in meetings or groups.
+(회의나 모임에서 내 의견을 당당하게 표현하는 것이 어렵지 않다.)
+2. Taking care of myself and taking responsibility is my top priority.
+(스스로를 돌보고 책임지는 것이 주요 관심사이다.)
+3. I prefer a direct and honest approach when dealing with people I meet for the first time.
+(처음 만난 사람을 대할 때 직접적이고 솔직한 방식을 선호한다.)
+4. It is very important for me to have my own unique personality that is different from others.
+(다른 사람과는 다른 나만의 개성을 가지는 것이 매우 중요하다.)
+[Interdependent Self-Construal (상호의존적 자아해석)]
+1. My happiness depends on the happiness of those around me.
+(내 행복은 주변 사람들의 행복에 달려 있다.)
+2. Even if I am not satisfied with the group I belong to, I will not leave if they need me.
+(내가 속한 집단에 만족하지 않더라도 나를 필요로 하면 집단을 떠나지 않을 것이다.)
+3. I will sacrifice my personal interests for the benefit of the group I belong to.
+(집단의 이익을 위해 개인적인 이익을 희생할 것이다.)
+4. Having good relationships with others is more important to me than my personal achievements.
+(다른 사람과의 좋은 인간관계가 나의 성취보다 중요하다.)</t>
+        </is>
+      </c>
+      <c r="O902" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="n">
+        <v>902</v>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>구민화</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>유튜브 부동산 콘텐츠가 2030세대의 부동산FoMO에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>서울대학교 대학원 언론정보학과 석사 학위논문</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>미디어 의존 이론(Media System Dependency Theory), I-PACE 모델(Interaction of Person-Affect-Cognition-Execution Model), 보상적 인터넷 사용 이론(Theory of Compensatory Internet Use), 사회 정체성 이론(Social Identity Theory)</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>[IV: 재무적 자기효능감, 위험 추구 성향, 유튜브 리터러시, 정부 신뢰도, 핀플루언서 전문성 인식, 콘텐츠 정확성 인식] -&gt; [Mediator: 유튜브 의존도, 부동산 FoMO] -&gt; [DV: 부동산 투자 열망] (세대별 조절효과 검증)</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>H1: 2030세대는 다른 세대에 비하여 유튜브 부동산 콘텐츠 의존도가 높다.
+H2-1: 2030세대의 유튜브 부동산 핀플루언서의 전문성 인식 수준은 유튜브 의존도에 정(+)의 영향을 가진다.
+H2-2: 2030세대의 유튜브 부동산 콘텐츠의 정확성 인식 수준은 유튜브 의존도에 정(+)의 영향을 가진다.
+H3-1: 2030세대의 재무적 자기효능감은 유튜브 부동산 핀플루언서의 전문성 인식 수준에 정(+)의 영향을 가진다.
+H3-2: 2030세대의 위험 추구 성향은 유튜브 부동산 핀플루언서의 전문성 인식 수준에 정(+)의 영향을 가진다.
+H3-3: 2030세대의 유튜브 리터러시 수준 인식은 유튜브 부동산 핀플루언서 전문성 인식 수준에 정(+)의 영향을 가진다.
+H4-1: 2030세대의 재무적 자기효능감은 유튜브 부동산 콘텐츠의 정확성 인식 수준에 정(+)의 영향을 가진다.
+H4-2: 2030세대의 위험 추구 성향은 유튜브 부동산 콘텐츠의 정확성 인식 수준에 정(+)의 영향을 가진다.
+H4-3: 2030세대의 유튜브 리터러시 수준은 유튜브 부동산 콘텐츠 정확성 인식 수준에 정(+)의 영향을 가진다.
+H5-1: 유튜브 리터러시 수준은 정부에 대한 신뢰도와 부(-)의 영향을 가진다.
+H5-2: 정부 신뢰도는 유튜브 의존도와 부(-)의 영향을 가진다.
+H6-1: 유튜브 의존도는 부동산 FoMO와 정(+)의 영향을 가진다.
+H6-2: 2030세대에게 유튜브 의존도가 부동산 FoMO에 미치는 정(+)의 영향은 다른 세대에 비해 높다.
+H7-1: 부동산 FoMO 수준은 부동산 투자 열망에 정(+)의 영향을 가진다.
+H7-2: 2030세대의 부동산 FoMO 수준은 부동산 투자 열망에 정(+)의 영향을 가진다.
+H8: 2030세대의 유튜브 부동산 콘텐츠의 정확성 인식은 부동산 투자 열망에 정(+)의 영향을 가진다.
+H9: 2030세대의 유튜브 부동산 핀플루언서의 전문성 인식은 부동산 투자 열망에 정(+)의 영향을 가진다.</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>재무적 자기효능감, 위험 추구 성향, 유튜브 리터러시, 정부 신뢰도, 유튜브 부동산 핀플루언서의 전문성 인식, 유튜브 부동산 콘텐츠의 정확성 인식</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>부동산 투자 열망</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>유튜브 의존도, 부동산 FoMO</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>세대 (2030세대 vs 타 세대)</t>
+        </is>
+      </c>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>첫째, 유튜브 부동산 콘텐츠의 정확성 인식과 핀플루언서의 전문성 인식 수준은 이용자들의 유튜브 의존도를 높이는 주요 요인으로 작용함. 둘째, 유튜브 리터러시 수준이 높을수록 정부 신뢰도는 낮아지는 경향이 나타남. 셋째, 유튜브 의존은 이용자들의 정서적 불안을 자극하여 부동산 FoMO를 심화시켰으며, 특히 2030세대의 경우 유튜브 의존이 부동산 FoMO를 현저하게 강화하는 조절효과가 확인됨. 넷째, 부동산 FoMO는 부동산 투자 열망을 유의미하게 강화함. 다섯째, 유튜브 부동산 콘텐츠는 합리적 판단을 돕기보다 심리적 압박감과 불안정성을 증폭시켜 비합리적인 투자 열망을 자극하는 결과를 초래함.</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>[유튜브 의존 (YouTube Dependency)]
+When new changes (policies, loans, interest rates) occur in the investment market, I look up related content on YouTube.
+(투자시장에 새로운 변화(정책, 대출, 금리)가 생기면 유튜브에서 관련 내용을 찾아본다.)
+When there are fluctuations in real estate prices, I look up house price forecasts on YouTube.
+(부동산 가격에 변동이 있으면 유튜브에서 집값 전망을 찾아본다.)
+When I need to make a real estate transaction, I look up the market situation on YouTube.
+(부동산 거래를 해야 할 때 시장 상황을 유튜브에서 찾아본다.)
+When I want to get information/knowledge about financial technology, I mainly refer to YouTube.
+(재테크에 대한 정보/지식을 얻고 싶을 때 주로 유튜브를 참고한다.)
+I make good use of the financial technology information obtained from YouTube.
+(유튜브에서 얻은 재테크 정보를 잘 활용한다.)
+When I get new financial technology information on YouTube, I update my existing information.
+(유튜브에서 새로운 재테크 정보를 얻으면 기존의 정보를 업데이트한다.)
+To buy a house at a crucial moment, I need to find out information on YouTube in advance.
+(결정적인 순간에 집을 사려면 유튜브로 미리 정보를 알아 둬야 한다.)
+[부동산 FoMO (Real Estate FoMO)]
+If I do not make any investment-related preparations, I might miss the opportunity to purchase real estate.
+(투자관련 아무런 준비를 하지 않으면 부동산 매수 기회를 놓칠 수 있다.)
+I might regret it if I miss a good purchasing opportunity or investment information.
+(좋은 매수기회나 투자정보를 놓치면 후회할 수 있다.)
+It is not easy to buy my own home solely with regular earned income.
+(정기적인 근로 소득만으로 내집을 마련하는 것은 쉽지 않다.)
+Without asset growth through investment, it might be difficult to live like my parents' generation.
+(투자를 통한 자산 증식이 없다면 부모님 세대와 같은 생활을 하기 어려울 수 있다.)
+If I miss a good buying timing, my future investment timing might be delayed.
+(좋은 매수 시점을 놓치면 향후 투자 시점이 늦어질 수 있다.)
+I am afraid that others might have better investment opportunities than me.
+(다른 사람들이 나보다 더 좋은 투자 기회를 가질까 두렵다.)
+If friends or acquaintances in similar economic situations buy their own homes, I feel like I should buy one quickly too.
+(비슷한 경제상황의 친구나 지인들이 내집을 마련하면 나도 얼른 마련해야 할 것 같다.)
+If I miss real estate investment/purchasing opportunities, I might fall behind in society.
+(부동산 투자/매수 기회를 놓치면 사회에서 뒤쳐질 수 있다.)
+I would feel anxious if I cannot secure 'at least one home of my own'.
+(‘내 집 한 채’ 마련을 하지 못한다면 불안할 것이다.)
+It is difficult to prepare for the future without 'owning a home' in South Korea.
+(대한민국에서 ‘내 집 마련’을 못해서는 미래를 준비하기 어렵다.)
+[재무적 자기효능감 (Financial Self-Efficacy)]
+I am confident in managing my finances.
+(나는 재정관리에 자신이 있다.)
+I can make good use of financial services to achieve my economic goals.
+(나는 경제적 목표 달성을 위해 금융 서비스를 잘 이용할 수 있다.)
+I am confident in finding the necessary economic and financial information on the internet.
+(나는 인터넷에서 필요한 경제금융 정보를 찾는 데에 자신 있다.)
+I can systematically organize and utilize economic information found online.
+(나는 온라인에서 찾은 경제정보를 체계적으로 정리해 활용할 수 있다.)
+[위험 추구 성향 (Risk-Taking Tendency)]
+If the return is high, I will invest in high-risk investment options.
+(수익이 높다면 고위험 투자처에 투자할 것이다.)
+I prefer high-risk investments.
+(나는 고위험 투자를 선호한다.)
+To me, risk feels like a challenge.
+(나에게 위험이란 도전으로 느껴진다.)
+I regularly take risks.
+(나는 정기적으로 위험을 감수한다.)
+[유튜브 부동산 핀플루언서의 전문성 인식 (Perceived Expertise of Real Estate Finfluencers)]
+Finfluencers have expertise in the field of financial investment.
+(핀플루언서는 금융투자 분야에 전문성이 있다.)
+Finfluencers have a lot of experience in fields related to financial investment.
+(핀플루언서는 금융투자 관련 분야에서 경험이 많다.)
+Finfluencers have abundant knowledge in the field of financial investment.
+(핀플루언서는 금융투자 분야 지식이 풍부하다.)
+Finfluencers also inform us of realistic difficulties related to financial investment.
+(핀플루언서는 금융투자 관련 현실적 어려움도 알려준다.)
+[유튜브 부동산 콘텐츠의 정확성 인식 (Perceived Accuracy of YouTube Real Estate Content)]
+YouTube real estate content accurately provides the information I am looking for.
+(유튜브 부동산 콘텐츠는 내가 찾는 정보를 정확히 제공한다.)
+I feel that the information in YouTube real estate content is quite believable.
+(유튜브 부동산 콘텐츠의 정보가 꽤 믿을 수 있다고 느낀다.)
+YouTube real estate content is trustworthy.
+(유튜브 부동산 콘텐츠는 신뢰할 수 있다.)
+YouTube real estate content provides more accurate information than TV broadcasts or newspapers.
+(유튜브 부동산 콘텐츠는 TV방송이나 신문보다 정확한 정보를 제공해준다.)
+[유튜브 리터러시 (YouTube Literacy)]
+I can find the videos I want to watch or need through YouTube.
+(유튜브를 통해 내가 보고싶거나 필요한 영상을 찾을 수 있다.)
+I know well what influences the recommended video list.
+(추천 해 주는 영상 목록에 무엇이 영향을 주는지 잘 알고 있다.)
+The content in the video may contain the creator's intention.
+(영상에 나오는 내용에는 만든 사람의 의도가 담겨있을 수 있다.)
+I search for additional information to find out various perspectives on the content in the video.
+(영상 속 내용에 대한 다양한 입장을 알아보기 위해 추가 정보를 검색 해 본다.)
+I know how to check if the video content is reliable.
+(영상 내용이 믿을만한 내용인지 확인하는 방법을 알고 있다.)
+[정부 신뢰도 (Trust in Government)]
+The government's real estate policy is competent.
+(정부의 부동산 정책은 유능하다.)
+The government's real estate policy is effective.
+(정부의 부동산 정책은 효과적이다.)
+The government's real estate policy is for the benefit of the public.
+(정부의 부동산 정책은 국민들의 이익을 위한 것이다.)
+[부동산 투자열망 (Real Estate Investment Aspiration)]
+I am interested in the investment areas or properties introduced on real estate YouTube.
+(부동산 유튜브에서 소개하는 투자 지역이나 매물에 관심이 간다.)
+When I come across real estate investment information on YouTube, I feel the will to invest.
+(유튜브에서 부동산 투자 정보를 접하면 투자 의지가 생긴다.)
+I will actively search for related information on YouTube when making real estate transactions or investments.
+(부동산 거래/투자시에 관련 정보를 유튜브에서 적극적으로 찾아볼 것이다.)
+Real estate-related information on YouTube has a positive impact on transactions or investments.
+(유튜브의 부동산 관련 정보는 거래나 투자에 긍정적인 영향을 준다.)</t>
+        </is>
+      </c>
+      <c r="O903" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="n">
+        <v>903</v>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>CHEN BOFAN</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>인스타그램 이용자의 자기표현이 SNS 중독경향성과 핫플레이스 방문의도에 미치는 영향 :FOMO와 주관적 행복감의 매개효과를 중심으로</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>세종대학교 대학원 호텔관광경영학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>인상관리 이론(Impression Management Theory), 중독 구성요소 모델(Addiction Components Model), 자기결정이론 및 사회비교이론</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>[독립변수: 자기표현(환심사기, 협박하기, 능력과시, 모범보이기, 애원하기)] -&gt; [매개변수: FOMO, 주관적 행복감] -&gt; [매개/종속변수: SNS 중독경향성(조절실패 및 일상생활장애, 몰입 및 내성, 부정 정서의 회피, 가상세계지향성 및 금단)] -&gt; [종속변수: 핫플레이스 방문의도]</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>H1: 인스타그램의 자기표현이 SNS 중독경향성에 긍정적 영향을 미칠 것이다.
+H2: 인스타그램의 자기표현과 SNS 중독경향성 간의 관계에서 FOMO의 매개효과가 있을 것이다.
+H3: 인스타그램의 자기표현과 SNS 중독경향성 간의 관계에서 주관적 행복감의 매개효과가 있을 것이다.
+H4: SNS 중독경향성이 핫플레이스 방문의도에 긍정적 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>자기표현 (하위요인: 환심사기, 협박하기, 능력과시, 모범보이기, 애원하기)</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>핫플레이스 방문의도 (및 SNS 중독경향성)</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>FOMO, 주관적 행복감</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>1. 인스타그램에서의 자기표현 요소(환심사기, 협박하기, 능력과시, 모범보이기, 애원하기)는 SNS 중독경향성 하위요인(조절실패 및 일상생활장애, 몰입 및 내성, 부정 정서의 회피, 가상세계지향성 및 금단)과 대체로 유의한 정적(+) 영향관계를 나타냈다.
+2. FOMO(소외 불안)는 인스타그램 자기표현과 SNS 중독경향성 간의 관계를 유의하게 매개하는 것으로 검증되었다.
+3. 주관적 행복감 역시 인스타그램 자기표현과 SNS 중독경향성 간의 관계에서 유의한 매개역할을 하는 것으로 확인되었다.
+4. SNS 중독경향성의 구성요소(조절실패 및 일상생활장애, 몰입 및 내성, 부정 정서의 회피, 가상세계지향성 및 금단) 모두 핫플레이스 방문의도에 긍정적인(+) 영향을 미치는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>[자기표현 - 환심사기]
+I express positive emotions on Instagram when I feel them.
+(나는 긍정적인 감정을 가지고 있을 때 이를 인스타그램에서 표현한 적이 있다.)
+I express agreement on Instagram when my opinion matches others.
+(나는 다른 사람과의 의견이 일치할 때 이를 인스타그램에서 표현한 적이 있다.)
+I express friendliness to visitors of my Instagram.
+(나의 인스타그램 방문자에게 친밀감을 표현한 적이 있다.)
+I frequently like or click on other people's posts on Instagram.
+(나는 인스타그램에서 타인의 포스팅을 자주 누르는 편이다.)
+[자기표현 - 협박하기]
+I express anger on Instagram when I feel angry about something.
+(나는 어떤 일에 대해 분노할 때 이를 인스타그램에서 표현한 적이 있다.)
+I express displeasure on Instagram when I am dissatisfied with something.
+(나는 어떤 일에 대해 만족하지 못할 때 불쾌감을 인스타그램에서 표현한 적이 있다.)
+I express disappointment on Instagram when I am disappointed about something.
+(나는 어떤 일에 대해 실망스러울 때, 그 실망을 인스타그램에서 표현한 적이 있다.)
+I express annoyance on Instagram when I feel annoyed about something.
+(나는 어떤 일에 대해 짜증날 때, 그 짜증을 인스타그램에서 표현한 적이 있다.)
+[자기표현 - 능력과시]
+I express my talents on Instagram.
+(내가 재능이 있음을 인스타그램에서 표현한 적이 있다.)
+I express my competence on Instagram.
+(내가 능력이 있음을 인스타그램에서 표현한 적이 있다.)
+I express that I have specialized skills on Instagram.
+(내가 숙련된 기술을 가지고 있음을 인스타그램에서 표현한 적이 있다.)
+I express my achievements on Instagram.
+(내가 이룬 성과에 대해 인스타그램에서 표현한 적이 있다.)
+[자기표현 - 모범보이기]
+I express positive energy on Instagram.
+(내가 긍정적인 에너지를 인스타그램에서 표현한 적이 있다.)
+I express on Instagram that I should take responsibility for the outcomes of my actions.
+(내가 한 일에 대한 결과에 대해 책임져야 한다는 생각을 인스타그램에서 표현한 적이 있다.)
+I express on Instagram that I hold high moral standards.
+(내가 높은 도덕적 기준을 갖고 있다는 것을 인스타그램에서 표현한 적이 있다.)
+I express on Instagram that I am dedicated to others.
+(내가 다른 사람들에게 헌신적이라는 것을 인스타그램에서 표현한 적이 있다.)
+[자기표현 - 애원하기]
+I reveal my helplessness on Instagram.
+(나 자신의 무력함을 인스타그램에서 드러낸 적이 있다.)
+I ask for opinions on certain issues on Instagram.
+(나는 인스타그램에서 어떤 문제에 대한 의견을 요청한 적이 있다.)
+I share my difficulties on Instagram.
+(나의 어려움을 인스타그램에서 공유한 적이 있다.)
+I ask for help on Instagram.
+(나는 인스타그램에서 도움을 요청한 적이 있다.)
+[FOMO]
+I fear that others might be having more rewarding experiences than me on Instagram.
+(나는 인스타그램에서 다른 사람들이 나보다 더 보람찬 경험을 많이 할까봐 두렵다.)
+I fear that my friends might be having more rewarding experiences than me on Instagram.
+(나는 인스타그램에서 내 친구들이 나보다 더 보람찬 경험을 많이 할까봐 두렵다.)
+I get worried when I find out my friends are having fun without me.
+(나는 내 친구들이 나 없이도 즐거운 시간을 보내고 있음을 알게 되면 걱정을 하게 된다.)
+I feel anxious when I do not know what my friends are up to.
+(나는 내 친구들이 무엇을 하고 있는지 모르면 불안하다.)
+It is important to me to understand inside jokes among my friends on Instagram.
+(인스타그램에서 "친구들 사이에서만 아는 농담"을 이해하는 것이 나에게 중요하다.)
+I spend a lot of time using Instagram so as not to fall behind.
+(나는 뒤처지지 않기 위해 인스타그램 이용에 많은 시간을 보내고 있는 편이다.)
+I feel anxious if I miss opportunities to interact with friends on Instagram.
+(나는 인스타그램에서 친구들과 소통할 수 있는 기회를 놓치면 불안한 편이다.)
+When I am having a good time, I tend to share it on Instagram.
+(내가 즐거운 시간을 보내고 있을 때, 인스타그램에서 공유하는 편이다.)
+I feel anxious about missing out on announced events on Instagram.
+(나는 인스타그램에서 공지된 행사에 참여를 못 할 까봐 불안하다.)
+Even on vacation, I keep checking Instagram to see what my friends are doing.
+(나는 휴가를 가서도 내 친구들이 무엇을 하는지 인스타그램을 계속 확인하는 편이다.)
+[주관적 행복감]
+After using Instagram, I think my current life is very good.
+(인스타그램 이용 후 현재 나의 삶은 매우 좋다고 생각한다.)
+After using Instagram, I came to realize what is important in my life.
+(인스타그램 이용 후 나의 삶에서 중요한 것을 깨닫게 되었다.)
+After using Instagram, I became more satisfied with my life.
+(인스타그램 이용 후 나의 삶에 더 만족하게 되었다.)
+After using Instagram, I became thankful for even small things.
+(인스타그램 이용 후 나는 작은 일에도 감사하게 되었다.)
+After using Instagram, I think my current life closely matches my ideal life.
+(인스타그램 이용 후 나의 이상적인 삶과 나의 현재 삶이 거의 일치한다고 생각한다.)
+[SNS 중독경향성 - 조절실패 및 일상생활장애]
+I sometimes feel sleepy during class or work due to Instagram usage.
+(나는 인스타그램 사용 때문에 학업이나 업무 중에 졸린 경우가 있다.)
+I have regretted not being able to reduce my Instagram usage time.
+(인스타그램 사용 시간을 줄이지 못해 후회한 적이 있다.)
+My interest in hobbies or leisure activities has decreased due to Instagram usage.
+(인스타그램 사용으로 인해 취미나 여가 생활에 대한 관심이 줄었다.)
+Using Instagram too much has negatively affected my studies or work.
+(인스타그램을 너무 많이 사용해서 학업이나 업무에 부정적인 영향을 받은 적이 있다.)
+Even though I pledge to stop using Instagram, I keep using it.
+(인스타그램 사용을 "그만해야지"라고 다짐하면서도 계속해서 인스타그램을 하게 된다.)
+Interest in other offline activities has decreased due to Instagram usage.
+(인스타그램 사용으로 인해 다른 오프라인 활동에 대한 흥미가 감소했다.)
+I have stayed up later than planned or had my sleep disrupted due to Instagram usage.
+(인스타그램 사용 때문에 계획했던 시간보다 늦게 잠들거나 수면에 방해받은 적이 있다.)
+[SNS 중독경향성 - 몰입 및 내성]
+I tend to spend a lot of time thinking about posts to upload on Instagram.
+(인스타그램에 올릴 게시물에 대해서 많은 시간을 고민하는 편이다.)
+I often think about recent events that happened on Instagram.
+(최근 인스타그램에서 일어난 사건에 대해 자주 생각한다.)
+I spend a lot of time using Instagram.
+(인스타그램 이용에 많은 시간을 보낸다.)
+Whenever I have free time, I check Instagram to see comments or reactions from others.
+(다른 사람들의 댓글이나 반응을 보기 위해 시간이 날 때마다 인스타그램을 확인한다.)
+Half or most of my day is spent using Instagram.
+(하루 중 대부분의 시간을 인스타그램을 하며 보낸다.)
+I feel an increasing urge to use Instagram.
+(인스타그램을 하고 싶은 충동을 점점 더 많이 느낀다.)
+I use Instagram even while walking on the street or conversing with others.
+(길을 걷거나 다른 사람들과 대화하는 중에도 인스타그램을 한다.)
+[SNS 중독경향성 - 부정 정서의 회피]
+I use Instagram to relieve stress.
+(스트레스를 해소하기 위해 인스타그램을 사용한다.)
+I use Instagram to reduce feelings of helplessness or depression.
+(무력감이나 우울감을 덜기 위해 인스타그램을 사용한다.)
+I use Instagram to relieve feelings of restlessness or anxiety.
+(초조함이나 불안감을 해소하기 위해 인스타그램을 사용한다.)
+I use Instagram to forget personal worries or problems.
+(개인적인 고민이나 문제를 잊기 위해 인스타그램을 사용한다.)
+I use Instagram to feel better.
+(기분을 좋게 하기 위해 인스타그램을 사용한다.)
+[SNS 중독경향성 - 가상세계지향성 및 금단]
+Through Instagram, I feel connected to others and feel less lonely or alienated.
+(인스타그램을 통해 다른 사람들과 연결되어 있어 외롭지 않고 소외감을 덜 느낀다.)
+I feel annoyed when I cannot use Instagram.
+(인스타그램을 사용하지 못할 때 짜증이 난다.)
+I feel recognized when I use Instagram.
+(인스타그램을 사용하면서 나 자신이 인정을 받는다고 느낀다.)
+Using Instagram gives me more self-confidence.
+(인스타그램을 사용하면 자신감이 더 생긴다.)
+It feels as if the joy of life disappears if I cannot use Instagram.
+(인스타그램을 하지 못하면 삶의 즐거움이 사라지는 것 같다.)
+[핫플레이스 방문의도]
+I want to visit places that are frequently posted on Instagram.
+(인스타그램에서 자주 게시되는 장소를 방문하고 싶다.)
+I want to visit places that famous people frequently go to.
+(유명인들이 자주 가는 장소를 방문하고 싶다.)
+I want to visit places where I can experience various cultures that cannot be easily found in other places.
+(다른 장소에서 쉽게 볼 수 없는 다양한 문화를 경험할 수 있는 장소를 방문하고 싶다.)
+I want to visit unique and delicious restaurants.
+(독특하고 맛있는 음식점을 방문하고 싶다.)
+I want to visit places with many distinctive fashion items.
+(개성이 강한 패션 아이템이 많은 장소를 방문하고 싶다.)
+I want to visit culturally rich places with workshops, art production, or exhibition spaces.
+(공방이나 예술품 제작, 전시 공간이 있는 문화적 요소가 풍부한 장소를 방문하고 싶다.)
+I want to visit small, unique, lesser-known restaurants or cafes.
+(알려지지 않은 소규모의 독특한 레스토랑이나 카페를 방문하고 싶다.)
+I want to visit places with famous brands.
+(유명한 브랜드가 있는 장소를 방문하고 싶다.)
+I want to visit places where I can watch outdoor clubs and performances.
+(야외에서 열리는 클럽과 공연을 관람할 수 있는 장소를 방문하고 싶다.)</t>
+        </is>
+      </c>
+      <c r="O904" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="n">
+        <v>904</v>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>유가우 (지도교수: 정용국)</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>자기결정성, 사회비교, 소외에대한두려움(FoMO)이 SNS중독경향성에 미치는 영향 -- 중국유학생을 대상으로</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>동국대학교 대학원 미디어커뮤니케이션학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>자기결정성이론 (Self-Determination Theory), 사회비교이론 (Social Comparison Theory)</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>[자기결정성, 사회비교] -&gt; [소외에 대한 두려움 (FoMO)] -&gt; [SNS 중독경향성]</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>연구가설 1: 자기결정성은 소외에 대한 두려움(FoMO)에 부(-)의 영향을 미칠 것이다.
+연구가설 2: 사회비교는 소외에 대한 두려움(FoMO)에 정(+)의 영향을 미칠 것이다.
+연구가설 3: 소외에 대한 두려움(FoMO)은 SNS 중독경향성에 정(+)의 영향을 미칠 것이다.
+연구문제 1: 자기결정성은 SNS 중독경향성에 직접적으로 영향을 미치는가? 아니면 소외에 대한 두려움(FoMO)을 통해 간접적으로 영향을 미치는가?
+연구문제 2: 사회비교는 SNS 중독경향성에 직접적으로 영향을 미치는가? 아니면 소외에 대한 두려움(FoMO)을 통해 간접적으로 영향을 미치는가?</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>자기결정성 (자율성, 유능성, 관계성), 사회비교 (능력요인, 의견요인)</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>SNS 중독경향성</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움 (FoMO)</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>1. 자기결정성은 소외에 대한 두려움(FoMO)에 유의미한 부(-)의 영향을 미치는 것으로 나타나 가설 1이 채택되었습니다.
+2. 사회비교는 소외에 대한 두려움(FoMO)에 유의미한 정(+)의 영향을 미치는 것으로 나타나 가설 2가 채택되었습니다.
+3. 소외에 대한 두려움(FoMO)은 SNS 중독경향성에 직접적인 영향을 미치지 않는 것으로 나타나 가설 3은 기각되었습니다.
+4. 자기결정성은 SNS 중독경향성에 직접적인 영향을 미치지 않으나, 소외에 대한 두려움(FoMO)을 매개로 하여 간접적으로 유의미한 부(-)의 영향을 미치는 것으로 확인되었습니다.
+5. 사회비교는 SNS 중독경향성에 직접적인 영향을 미치지 않으나, 소외에 대한 두려움(FoMO)을 매개로 하여 간접적으로 유의미한 정(+)의 영향을 미치는 것으로 확인되었습니다.</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>[자기결정성 - 자율성]
+I know well how to use SNS on my own.
+(나는 SNS를 어떻게 사용해야 하는지 스스로 잘 알고 있다.)
+I can control my SNS use by myself.
+(나는 SNS사용을 스스로 조절할 수 있다.)
+I feel that I can freely express my thoughts and opinions on SNS.
+(나는 SNS사용에 대한 내 생각과 의견을 자유롭게 표현할 수 있다고 느낀다.)
+[자기결정성 - 유능성]
+I have no difficulty in controlling my SNS use.
+(나는 SNS사용을 조절하는데 어려움이 없다.)
+I feel a sense of achievement when I control my SNS use by myself.
+(나는 SNS사용을 스스로 조절할 때 성취감을 느낀다.)
+I feel that I can control my SNS use better than others.
+(나는 SNS사용조절을 다른사람보다 잘할수있다고 느낀다.)
+I can keep my SNS usage time well according to the rules.
+(나는 SNS이용규칙에 따라 이용시간을 잘 지킬 수 있다.)
+[자기결정성 - 관계성]
+I feel that controlling my SNS use can resolve conflicts with my parents.
+(SNS를 조절하는 행위가 부모와의 갈등을 해소할 수 있다고 느낀다.)
+I feel that controlling my SNS use can resolve conflicts with my teachers.
+(내가 SNS를 조절하는 행위가 교사와의 갈등을 해소할 수 있다고 느낀다.)
+[사회비교 - 능력요인]
+I often compare the behavior of my loved ones (partners, family, etc.) with that of others.
+(나는 종종 사랑하는 이들(애인, 가족 등)의 행동과 타인의 행동을 비교한다.)
+I always like to compare my behavior with that of others.
+(나는 항상 나의 행동을 타인의 행동과 비교하는 것을 좋아한다.)
+When I want to know if I did a good job, I compare what I did with what others did.
+(내가 일을 잘했는지 알고자 할 때, 다른 사람이 한 것과 내가 한 것을 비교한다.)
+I often compare myself with others to see if I am acting socially (e.g., interpersonal relationships, popularity).
+(사회성있게 행동(예: 대인관계, 인기도)하고 있는지 타인과 비교하곤 한다.)
+I often compare what I have achieved in life with what others have achieved.
+(나는 종종 내가 인생에서 달성한 것과 다른 사람들이 달성한 것을 비교한다.)
+[사회비교 - 의견요인]
+I often like to talk with others to get diverse opinions and experiences.
+(나는 종종 다양한 의견과 경험을 얻기 위해 타인과 이야기하길 좋아한다.)
+I often want to know what people are thinking when they face a similar problem as me.
+(나는 종종 누군가 나와 비슷한 문제에 직면해 있을 때, 그 사람들이 무슨 생각을 하고 있는지 알고 싶어지곤 한다.)
+I always want to know how people in similar situations to mine would have acted.
+(나는 항상 나와 상황(입장)이 비슷한 사람들이라면 어떻게 행동했을지 알고 싶다.)
+When I try to learn something, I try to find out what others think about it.
+(무언가를 배우려고 할 때, 이에 대한 타인의 생각을 알려고 한다.)
+[소외에 대한 두려움 - 상대적 박탈감]
+I am afraid that others may have more rewarding experiences than me.
+(나는 다른 사람들이 나보다 더 보람찬 경험을 많이 할까봐 두렵다.)
+I am afraid that my friends may have more rewarding experiences than me.
+(나는 내 친구들이 나보다 더 보람찬 경험을 많이 할까봐 두렵다.)
+[소외에 대한 두려움 - 외적동기]
+I worry when I find out my friends are having a good time without me.
+(나는 내 친구들이 나 없이도 즐거운 시간을 보내고 있음을 알게 되면 걱정을 하게 된다.)
+I feel anxious when I do not know what my friends are doing.
+(나는 내 친구들이 무엇을 하고 있는지 모르면 불안하다.)
+Even when on vacation, I keep checking what my friends are doing.
+(휴가를 가서도, 나는 계속 내 친구들이 무엇을 하는지를 확인한다.)
+Sometimes, I feel like I spend too much time trying to keep up with what is going on around me.
+(때로는, 주변에 일어난 일에 뒤처지지 않기 위해 지나치게 많은 시간을 보내고 있는 것 같다.)
+[소외에 대한 두려움 - 소속동기]
+It bothers me if I miss an opportunity to meet with friends.
+(친구들과 만날 수 있는 기회를 놓치면 신경이 쓰인다.)
+It bothers me if I cannot go to a planned meeting.
+(나는 계획된 모임을 가지 못하면 신경이 쓰인다.)
+[SNS 중독경향성 - 일상생활장애 및 조절실패]
+I sleep during class or work hours because I am tired from using SNS.
+(SNS사용 때문에 피곤해서 수업시간 또는 업무시간에 잔다.)
+I have regretted not being able to reduce my SNS usage time.
+(SNS사용시간을 줄이지 못해 후회한 적이 있다.)
+I put less importance on hobbies, leisure life, and exercise because of SNS.
+(SNS때문에 취미, 여가생활, 운동을 덜 중요시한다.)
+I used SNS so much that it had a negative impact on my work or studies.
+(SNS를 너무 많이해서 그것이 나의 일 또는 학업에 부정적인 영향을 미쳤다.)
+I end up using SNS repeatedly even though I think "I should stop."
+("그만해야지"하면서도 번번이 SNS를 하게 된다.)
+My interest in other offline activities has decreased due to SNS.
+(SNS로 인해 오프라인에서 다른 활동에 대한 흥미가 감소했다.)
+I often fall asleep later than I want or cannot sleep because of SNS.
+(SNS로 인해 원하는 시간보다 더 늦게 잠들거나 잠을 이루지 못하는 일이 자주 있다.)
+[SNS 중독경향성 - 몰입 및 내성]
+I spend a lot of time thinking about SNS or how to use it.
+(SNS를 생각하거나 어떻게 이용할 것인가에 많은 시간을 보낸다.)
+I think a lot about what happened on SNS recently.
+(최근 SNS에서 일어난 일에 대해 많이 생각한다.)
+I check SNS frequently whenever I have time to see others' comments.
+(SNS에서 타인의 댓글을 보기 위해 시간이 날 때마다 수시로 확인한다.)
+I spend most of the day using SNS.
+(하루 중 대부분의 시간을 SNS를 하며 보낸다.)
+I feel more and more urge to use SNS.
+(SNS를 하고 싶은 충동을 점점 더 많이 느낀다.)
+I constantly use SNS even while walking on the street or talking with others.
+(길을 걷거나 다른 사람들과 대화 중에도 끊임없이 SNS를 한다.)
+[SNS 중독경향성 - 가상세계지향성 및 금단]
+I use SNS to forget about stressful problems.
+(스트레스 받는 문제를 잊기 위해 SNS를 사용한다.)
+I use SNS to reduce feelings of helplessness or depression.
+(무력감 또는 우울감을 줄이기 위해 SNS를 한다.)
+I use SNS to reduce nervousness or anxiety.
+(초조함 또는 불안감을 줄이기 위해 SNS를 한다.)
+I use SNS to forget about personal problems.
+(개인적 문제를 잊기 위해 SNS를 한다.)
+I use SNS to make myself feel better.
+(기분을 좋게 하기 위해 SNS를 한다.)</t>
+        </is>
+      </c>
+      <c r="O905" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="n">
+        <v>905</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>이국화</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>자기대상경험과 SNS 중독경향성 간 관계: 자기애와 FOMO(Fear Of Missing Out)의 매개효과</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>울산대학교 교육대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>하인즈 코헛(Heinz Kohut)의 자기심리학(Self Psychology)</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>[독립변수: 자기대상경험] -&gt; [매개변수 1: 자기애 (건강한 자기애, 방어적 자기애), 매개변수 2: 소외에 대한 두려움 (FOMO)] -&gt; [종속변수: SNS 중독경향성]</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>H1: 성숙한 자기대상 경험을 하지 못한 사람은 방어적 자기애를 가지며, FOMO 수준이 높고, 높은 SNS 중독경향성으로 드러날 것이다.
+H2: 성숙한 자기대상 경험을 한 사람은 건강한 자기애를 가지며, FOMO 수준이 낮고, 낮은 SNS 중독경향성으로 드러날 것이다.</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>자기대상경험 (Selfobject Experience)</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>SNS 중독경향성 (SNS Addiction Proneness)</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>자기애 (건강한 자기애, 방어적 자기애), 소외에 대한 두려움 (FOMO)</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>첫째, 자기대상경험은 건강한 자기애와 유의미한 정적 상관관계가 있었고, 방어적 자기애와는 부적 상관관계가 있었다. 둘째, 건강한 자기애는 FOMO 및 SNS 중독경향성과 부적 상관관계가 있었으나, 방어적 자기애는 FOMO 및 SNS 중독경향성과 정적 상관관계를 보였다. 셋째, 구조방정식 분석 결과 건강한 자기애는 SNS 중독경향성에 직접적인 부적 영향을 미쳤다. 반면, 방어적 자기애는 SNS 중독경향성에 직접적인 영향을 미치지 않았으나, FOMO를 매개로 하여 SNS 중독경향성을 높이는 간접적인 정적 영향을 미쳤다. 넷째, 자기애와 FOMO는 자기대상경험이 SNS 중독경향성에 미치는 영향을 유의미하게 매개하는 것으로 검증되었다.</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>[자기대상경험 (Selfobject Experience)]
+My mother (or father) respected my feelings.
+(어머니(혹은 아버지)는 나의 느낌을 존중해 주었다.)
+I have been close to someone who was an ideal figure to me.
+(나의 이상적인 대상이 되어주는 사람과 가깝게 지낸 적이 있다.)
+There were many people similar to me in the community I belonged to.
+(내가 속한 공동체에는 나와 비슷한 사람들이 많이 있(었)다.)
+[자기애 (Narcissism - KISP)]
+I am a passionate person.
+(나는 열정적인 사람이다.)
+I feel that I am truly alive.
+(나는 정말로 살아 있다는 느낌을 갖고 있다.)
+I feel like I can do nothing when people who are important to me are far away.
+(나는 나에게 중요한 사람들이 멀리 있을 때 아무것도 할 수 없다고 느낀다.)
+I sometimes complain of self-alienation and emptiness.
+(나는 때때로 자기·소외감과 공허함을 호소한다.)
+[소외에 대한 두려움 (FOMO)]
+I fear others are having more rewarding experiences than me.
+(나는 다른 사람들이 나보다 더 즐거운 시간을 보낼까봐 불안하다.)
+I fear my friends are having more rewarding experiences than me.
+(나는 내 친구들이 나보다 더 즐거운 시간을 보낼까봐 불안하다.)
+[SNS 중독경향성 (SNS Addiction Proneness)]
+I spend a lot of time thinking about SNS or how to use it.
+(SNS를 생각하거나 어떻게 이용할 것인가에 많은 시간을 보낸다.)
+I use SNS to forget about stressful problems.
+(스트레스 받는 문제를 잊기 위해 SNS를 사용한다.)</t>
+        </is>
+      </c>
+      <c r="O906" t="inlineStr">
+        <is>
+          <t>UCI: I804:48009-200000179280</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="n">
+        <v>906</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>신다인</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>재택근무와 직무소진: FoMO와 직무자율성을 통한 이중경로모델</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 경영학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>사회비교이론 (Social Comparison Theory), 자기결정이론 (Self-Determination Theory), 직무요구-자원 모형 (Job Demands-Resources Model), 기본 심리적 욕구 이론 (Basic Psychological Needs Theory), 직무 특성 이론 (Job Characteristics Theory)</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>[IV] 재택근무 -&gt; [Mediator 1] FoMO &amp; [Mediator 2] 직무자율성 -&gt; [DV] 직무소진</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>가설1. 재택근무는 FoMO와 정(+)의 관계를 가진다.
+가설2. FoMO는 직무소진과 정(+)의 관계를 가진다.
+가설3. FoMO는 재택근무와 직무소진의 관계를 매개한다.
+가설4. 재택근무는 직무자율성과 정(+)의 관계를 가진다.
+가설5. 직무자율성은 직무소진과 음(-)의 관계를 가진다.
+가설6. 직무자율성은 재택근무와 직무소진의 관계를 매개한다.</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>재택근무 (Telecommuting)</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>직무소진 (Job Burnout)</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>FoMO (Fear of Missing Out), 직무자율성 (Job Autonomy)</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>1. 재택근무와 FoMO의 정(+)의 관계는 유의하였다 (가설 1 채택).
+2. FoMO와 직무소진의 정(+)의 관계는 유의하였다 (가설 2 채택).
+3. 재택근무와 직무소진 간의 관계에서 FoMO의 매개역할이 유의하였다 (가설 3 채택).
+4. 재택근무와 직무자율성의 정(+)의 관계는 유의하지 않았다 (가설 4 기각).
+5. 직무자율성과 직무소진의 음(-)의 관계는 유의하였다 (가설 5 채택).
+6. 재택근무와 직무소진 간의 관계에서 직무자율성의 매개역할이 유의하지 않았다 (가설 6 기각).</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>[FoMO]
+- I worry that I will miss out on networking opportunities that my colleagues might have.
+(나는 동료들이 가질 수 있는 네트워킹 기회를 놓칠까 봐 걱정된다.)
+- I worry that I won't know what is going on at work.
+(나는 회사에서 무슨 일이 일어나고 있는지 알 수 없을까 봐 걱정된다.)
+[Job Autonomy]
+- I set the goals that need to be achieved in my job.
+(내 직무에서 달성되어야 할 목표들은 내가 세운다.)
+- I can choose the job performance method that is most suitable for me.
+(나는 내게 가장 적합한 직무수행방식을 선택할 수 있다.)
+- In my job, I decide when to perform specific work activities.
+(내 직무에서는 특정 업무활동들의 수행시기를 내가 결정한다.)
+[Job Burnout]
+- I feel emotionally exhausted from my work.
+(내가 맡은 일을 하는데 있어서 정서적으로 지쳐있음을 느낀다.)
+- I have become less enthusiastic about my work.
+(내가 맡은 일을 하는데 있어서 소극적이다.)
+- I can effectively solve the problems that arise in my work.
+(나는 직무상에서 발생하는 문제들을 효과적으로 해결할 수 있다.)</t>
+        </is>
+      </c>
+      <c r="O907" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="n">
+        <v>907</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>한다정</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>청소년의 부모 및 또래애착과 SNS중독경향성의 관계: 소외에 대한 두려움(FoMO)의 매개효과</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>한국외국어대학교 교육대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>애착이론 (Attachment Theory), 자기결정이론 (Self-Determination Theory), 사회비교이론 (Social Comparison Theory)</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>[부모애착 / 또래애착] -&gt; [소외에 대한 두려움 (FoMO)] -&gt; [SNS 중독경향성]</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>가설 2-1. 청소년의 부모애착과 SNS중독경향성간의 관계를 FoMO가 매개할 것이다.
+가설 2-2. 청소년의 또래애착과 SNS중독경향성간의 관계를 FoMO가 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>부모애착, 또래애착</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>SNS중독경향성</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움 (FoMO)</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>첫째, 소외에 대한 두려움(FoMO)은 외로움 및 SNS 사용동기(특히 사교 및 대처 동기)와 유의한 정적 상관관계를 보였다.
+둘째, 부모애착과 SNS중독경향성의 관계에서 FoMO는 부분매개효과를 나타냈다. 부모와의 불안정한 애착은 직접적으로 SNS중독경향성을 높일 뿐만 아니라, FoMO를 매개로 하여 간접적으로도 영향을 미친다.
+셋째, 또래애착과 SNS중독경향성의 관계에서 FoMO는 완전매개효과를 나타냈다. 즉, 또래애착이 SNS중독경향성에 미치는 영향은 FoMO에 의해 완전히 설명된다.</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>I get anxious when I miss an opportunity to meet up with friends.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+I worry I spend too much time keeping track of what is going on.
+(나는 주변을 신경쓰는데 시간을 많이 보내는 것 같아 걱정된다.)
+I fear my friends have more rewarding experiences than I do.
+(나는 내 친구들이 나보다 좀더 나은 경험을 할까봐 두렵다.)</t>
+        </is>
+      </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>UCI: I804:11059-200000335001</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="n">
+        <v>908</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>강지우</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>청소년의 팬덤활동과 또래관계의 질에 따른 군집별 공동체의식과 소외에 대한 두려움의 차이</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>한양대학교 상담심리대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>공동체의식 이론 (Sense of Community Theory), 소외에 대한 두려움 (Fear of Missing Out; FoMO), 또래관계 발달이론</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>[IV: 팬덤활동, 또래관계의 질] -&gt; [군집분석 (Cluster Analysis)] -&gt; [DV: 공동체의식, 소외에 대한 두려움]</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>연구문제 1: 청소년의 팬덤활동, 또래관계의 질, 공동체의식, 소외에 대한 두려움 간에는 유의미한 상관관계가 존재할 것이다.
+연구문제 2: 청소년의 팬덤활동과 또래관계의 질에 따라 유의미한 군집들이 형성될 것이다.
+연구문제 3: 형성된 군집들 간 공동체의식과 소외에 대한 두려움에 유의미한 차이가 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>팬덤활동, 또래관계의 질</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>공동체의식, 소외에 대한 두려움</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>첫째, 청소년의 팬덤활동과 또래관계의 질 사이에는 유의미한 정적 상관관계가 있었습니다.
+둘째, 군집분석 결과 팬덤활동과 또래관계의 질에 따라 3개의 군집이 도출되었습니다: 군집 1(적극적으로 팬덤활동을 하며 또래관계가 좋은 청소년 집단), 군집 2(평균적인 팬덤활동을 하며 또래관계가 좋지 않은 청소년 집단), 군집 3(팬덤활동을 거의 하지 않으며 또래관계가 좋은 청소년 집단).
+셋째, 일원배치 분산분석 결과 군집별로 공동체의식과 소외에 대한 두려움에 유의미한 차이가 있었습니다. 공동체의식은 또래관계의 질이 높은 군집(1, 3)이 군집 2보다 유의미하게 높았으며, 소외에 대한 두려움은 팬덤활동을 하는 군집(1, 2)이 군집 3보다 유의미하게 높게 나타났습니다.</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>[Fandom Activities]
+Participating in fan meetings.
+(팬미팅 참석)
+Joining a fan club or fan cafe.
+(팬클럽이나 팬 카페 가입)
+Going to broadcasting stations, concert halls, or stadiums.
+(방송국이나 공연장, 경기장 가기)
+Sending gifts (tributes, support, etc.).
+(선물 보내기 (조공, 서포트 등))
+Visiting official websites, communities, or official social media accounts (Weverse, etc.).
+(공식 홈페이지 또는 커뮤니티 방문 또는 위버스 등 공식 계정(SNS))
+Writing fan letters, private messages, bubble, lysn, etc.
+(팬레터, 프라이빗메세지, 버블, 리슨 등 쓰기)
+Leaving comments on Twitter, fan cafes, portal site news articles, etc.
+(트위터, 팬 카페, 포털사이트 뉴스 기사 등에 댓글 달기)
+Purchasing music, content, books, videos, CDs, DVDs, goods (photocards, accessories, etc.).
+(음원, 콘텐츠, 책 등 영상물/CD/DVD/굿즈(포토카드, 액세서리 등) 구매)
+Uploading or sharing content on internet sites, blogs, fan pages, or social media.
+(인터넷 사이트, 블로그, 팬페이지, SNS 등에 콘텐츠를 올리거나 공유하기)
+Participating in viewer voting, text voting, internet voting, hashtags, etc.
+(시청자 투표 참여, 문자 투표, 인터넷 투표, 해시태그 등)
+[Quality of Peer Relationships]
+I spend time with my friends.
+(나는 친구들과 함께 시간을 보낸다)
+Friends share their upsetting and difficult stories with me.
+(친구들은 속상하고 힘든 말을 나에게 털어놓는다)
+I talk about my stories to my friends.
+(나는 친구들에게 내 이야기를 잘한다)
+I can tell my secrets to my friends.
+(나는 친구들에게 내 비밀을 이야기할 수 있다)
+When I say something, my friends help me.
+(내가 무슨 말을 할 때 친구들은 나를 도와준다)
+My friends like me and follow me well.
+(친구들은 나를 좋아하고 잘 따른다)
+My friends are interested in me.
+(친구들은 나에게 관심이 있다)
+I have a good relationship with my friends.
+(나는 친구들과 관계가 좋다)
+I often have conflicts of opinion with my friends.
+(나는 친구들과 의견 충돌이 잦다)
+When I fight with a friend, we do not reconcile well.
+(나는 친구와 싸우면 잘 화해하지 않는다)
+I get angry or annoyed when a friend acts differently from my wishes.
+(나는 친구가 내 뜻과 다르게 행동하면 화를 내거나 짜증을 낸다)
+I have no intention of becoming close with kids who are different from me.
+(나는 나와 다른 아이들과는 친해질 생각이 없다)
+My friends are not interested in my difficulties and hard times.
+(친구들은 나의 어렵고 힘든 점에 대해 관심이 없다)
+[Sense of Community]
+I feel like I am a member of the group I belong to.
+(나는 내가 속한 집단의 일원이라는 느낌이 든다)
+I feel like the group I belong to can get better if I work hard.
+(내가 열심히 노력하면 내가 속한 집단이 더 나아질 수 있을 것 같다)
+The group I belong to and its members satisfy what I want.
+(내가 속한 집단과 그 구성원들은 내가 원하는 것을 충족시켜 준다)
+I feel intimacy and affection toward the group I belong to and its members.
+(내가 속한 집단과 그 구성원들에게 친밀감과 정을 느낀다)
+I feel proud of being a member of the group I belong to.
+(내가 속한 집단의 일원이라는 것에 자긍심을 느낀다)
+I feel like people in the group I belong to expect something from me.
+(내가 속한 집단의 사람들이 나에게 무언가 기대하는 것이 있는 것 같다는 생각이 든다)
+I am glad because there seems to be something I can do for the group I belong to.
+(나는 내가 속한 집단을 위해 무언가 할 수 있는 것이 있는 것 같아서 기쁘다)
+It seems like there are people in the group I belong to who truly worry and care about me.
+(내가 속한 집단은 나를 진정으로 걱정하고 염려해주는 사람들이 있는 것 같다)
+I think the group I belong to shares something different from other groups.
+(내가 속한 집단이 다른 집단과는 다른 무언가를 서로 공유하고 있다는 생각이 든다)
+It seems like the group I belong to and its members have an important influence on me.
+(내가 속한 집단과 그 구성원들이 나에게 중요한 영향을 미치고 있는 것 같다)
+I feel satisfaction and joy living in the group I belong to.
+(내가 속한 집단에서 살아가면서 만족감과 기쁨을 느낀다)
+I feel trust that the members of the group I belong to are trustworthy.
+(내가 속한 집단의 구성원들이 믿을 수 있는 사람들이라는 신뢰감이 든다)
+I feel like I should play my role in things that need me in the group I belong to.
+(내가 속한 집단에서 나를 필요로 하는 일들에 내 역할을 해야겠다는 느낌이 든다)
+I feel like my actions are restricted while living in the group I belong to.
+(내가 속한 집단에서 생활하면서 나의 행동에 제약을 받는 느낌이 든다)
+People in the group I belong to rely on each other.
+(내가 속한 집단의 사람들이 서로 의지하고 있다)
+I can find someone in the group I belong to whom I can talk to immediately when I want to talk.
+(내가 대화하고 싶을 때 당장 이야기를 할 수 있는 사람을 내가 속한 집단에서 찾을 수 있다)
+[Fear of Missing Out]
+I am afraid that others may have had more meaningful experiences than me.
+(나는 다른 사람들이 나보다 더 의미 있는 경험을 많이 했을까 봐 두렵다)
+I am afraid that my friends may have had more useful experiences than me.
+(나는 내 친구들이 나보다 더 유익한 경험을 많이 했을까 봐 두렵다)
+It bothers me when I find out my friends have had a good time without me.
+(나는 내 친구들이 나 없이 즐거운 시간을 보냈다는 것을 알았을 때 신경 쓰인다)
+It bothers me when I do not know how my friends are doing.
+(나는 친구들의 근황을 알지 못하면 신경이 쓰인다)
+It bothers me if I cannot go to a pre-arranged meeting.
+(미리 약속한 모임에 나가지 못하게 되면 신경이 쓰인다)
+I continuously log on to online messengers or social media to not miss new information.
+(새로운 정보를 놓치지 않기 위해 지속적으로 온라인메신저 등에 접속한다)
+It is important to have something to say about recently trending issues on social media (e.g., fandom activities, news, etc.).
+(온라인상에서 최근 유행하는 이슈(예: 팬덤활동, 뉴스 등)에 대해 말할 거리가 있는 것은 중요하다)
+It bothers me if I do not update my status on social media.
+(나는 내 근황을 SNS에 업데이트하지 않으면 신경이 쓰인다)
+I continuously check my smartphone to not miss new information.
+(나는 새로운 정보를 놓치지 않기 위해 지속적으로 스마트폰을 확인한다)
+When I am having a good time, it is important to me to share it on social media.
+(내가 좋을 시간을 보내고 있을 때 그것을 SNS에 공유하는 것이 나에게 중요하다)
+It is very important to me to understand jokes or slang used among friends.
+(친구들끼리 하는 농담이나 친구들끼리 있을 때 쓰는 말을 이해하는 것은 나에게 매우 중요하다)
+Even during vacation, I continuously check how my friends are doing.
+(방학 동안에도 나는 지속적으로 친구들의 근황을 확인한다)</t>
+        </is>
+      </c>
+      <c r="O909" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="n">
+        <v>909</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>권지원</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>초기성인의 내현적 자기애와 관계적 공격성의 관계: 사회적 배척 경험으로 조절된 소외에 대한 두려움(FoMO)의 매개효과</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>한양대학교 상담심리대학원</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>자기결정성 이론 (Self-Determination Theory), 사회적 비교 이론 (Social Comparison Theory), 오류 관리 이론 (Error Management Theory)</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>[IV: 내현적 자기애] -&gt; [Mediator: 소외에 대한 두려움(FoMO)] -&gt; [DV: 관계적 공격성]
+* [Mediator -&gt; DV] 경로를 [Moderator: 사회적 배척 경험]이 조절함 (조절된 매개모형)</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>H1: 성인 초기의 내현적 자기애와 관계적 공격성의 관계에서 소외에 대한 두려움(FoMO)이 매개할 것이다.
+H2: 성인 초기의 소외에 대한 두려움(FoMO)과 관계적 공격성의 관계에서 사회적 배척 경험이 조절역할을 할 것이다.
+H3: 성인 초기의 내현적 자기애와 관계적 공격성의 관계에서 사회적 배척 경험으로 조절된 소외에 대한 두려움(FoMO)의 매개효과가 나타날 것이다.</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>내현적 자기애 (Covert Narcissism)</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>관계적 공격성 (Relational Aggression)</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움 (FoMO)</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>사회적 배척 경험 (Social Exclusion Experiences)</t>
+        </is>
+      </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>첫째, 내현적 자기애, 소외에 대한 두려움(FoMO), 관계적 공격성, 사회적 배척 경험은 모두 서로 유의한 정적 상관관계를 보였습니다.
+둘째, 내현적 자기애와 관계적 공격성의 관계에서 소외에 대한 두려움(FoMO)의 매개효과가 유의하게 나타났습니다.
+셋째, 소외에 대한 두려움(FoMO)과 관계적 공격성 간의 관계에서 사회적 배척 경험 총점의 조절효과는 유의하지 않았으나, 하위요인인 고립 배척, 모욕 배척, 괴롭힘 배척은 각각 유의한 조절효과를 나타냈습니다.
+넷째, 내현적 자기애와 관계적 공격성의 관계에서 소외에 대한 두려움(FoMO)의 매개효과는 모욕 배척 수준에서만 유의하게 조절되어, 조절된 매개효과가 부분적으로 유의함을 검증하였습니다.</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>[내현적 자기애 (Covert Narcissism)]
+I tend to be very conscious of what others think of me.
+(나는 다른 사람들의 눈치를 많이 살피는 편이다.)
+I often feel inferior to others.
+(나는 종종 다른 사람들에게 열등감을 느낀다.)
+I feel anxious about my future as it seems vague and uncertain.
+(나에게 미래는 막연하고 불확실하게 보인다.)
+[관계적 공격성 (Relational Aggression)]
+I have threatened to break up with my partner in order to get them to do what I want.
+(나는 애인이 내가 원하는 것을 하도록 하기 위해, 애인과 헤어지겠다고 위협한 적이 있다.)
+When I am angry with my partner, I act in a way to make them feel jealous.
+(나는 애인에게 화가 날 때, 애인이 질투심을 느끼도록 행동하려 한다.)
+I have intentionally ignored someone until they agreed to do things my way.
+(나는 어떤 것에 대해 나의 방식대로 따를 때까지, 누군가를 의도적으로 무시한 적이 있다.)
+[소외에 대한 두려움 (FoMO)]
+I fear my friends have more rewarding experiences than I do.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+I get anxious when I don't know what my friends are up to.
+(나는 친구들의 소식을 접하지 못할 때 불안하다.)
+I worry when I am missed out on planned gatherings with friends.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+[사회적 배척 경험 (Social Exclusion)]
+Friends or colleagues did not include me.
+(친구나 동료들이 끼워주지 않았다.)
+Others ignored my opinions.
+(남들이 내 의견을 무시하였다.)
+I was insulted by other people.
+(다른 사람에게 모욕을 당하였다.)</t>
+        </is>
+      </c>
+      <c r="O910" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="n">
+        <v>910</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>리우위항 (지도교수: 황하성)</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>팬덤활동이 주관적 웰빙에 미치는 영향: 우울감, 사회적 자본, 소외에 대한 두려움(FOMO)을 중심으로</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>동국대학교 대학원 미디어커뮤니케이션학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>사회적 자본 이론 (Social Capital Theory), 긍정심리학 (Positive Psychology)</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>[IV] 온라인 및 오프라인 팬덤활동 -&gt; [Mediators] 우울감, 사회적 자본 (교량형, 결속형) -&gt; [DV] 주관적 웰빙 (조절변수: 소외에 대한 두려움 (FOMO))</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>H1: 팬덤활동은 주관적 웰빙에 영향을 미칠 것이다.
+H1-1: 온라인 팬덤활동은 주관적 웰빙에 정적인 영향을 미칠 것이다.
+H1-2: 오프라인 팬덤활동은 주관적 웰빙에 정적인 영향을 미칠 것이다.
+H2: 팬덤활동은 우울감에 영향을 미친다.
+H2-1: 온라인 팬덤활동은 우울감에 부적인 영향을 미칠 것이다.
+H2-2: 오프라인 팬덤활동은 우울감에 부적인 영향을 미칠 것이다.
+H3: 팬덤활동은 사회적 자본에 영향을 미칠 것이다.
+H3-1: 온라인 팬덤활동은 교량형 사회적 자본에 정적인 영향을 미칠 것이다.
+H3-2: 온라인 팬덤활동은 결속형 자본에 정적인 영향을 미칠 것이다.
+H3-3: 오프라인 팬덤활동은 교량형 사회적 자본에 정적인 영향을 미칠 것이다.
+H3-4: 오프라인 팬덤활동은 결속형 사회적 자본에 정적인 영향을 미칠 것이다.
+H4: 우울감은 주관적 웰빙에 부적인 영향을 미칠 것이다.
+H5: 사회적 자본은 주관적 웰빙에 영향을 미친다.
+H5-1: 교량형 사회적 자본은 주관적 웰빙에 정적인 영향을 미칠 것이다.
+H5-2: 결속형 사회적 자본은 주관적 웰빙에 정적인 영향을 미칠 것이다.
+H6: 우울감은 팬덤활동과 주관적 웰빙의 관계를 매개할 것이다.
+H6-1: 우울감은 온라인 팬덤활동과 주관적 웰빙의 관계를 매개할 것이다.
+H6-2: 우울감은 오프라인 팬덤활동과 주관적 웰빙의 관계를 매개할 것이다.
+H7: 사회적 자본은 팬덤활동과 주관적 웰빙의 관계를 매개할 것이다.
+H7-1: 교량형 사회적 자본은 온라인 팬덤활동과 주관적 웰빙의 관계를 매개할 것이다.
+H7-2: 교량형 사회적 자본은 오프라인 팬덤활동과 주관적 웰빙의 관계를 매개할 것이다.
+H7-3: 결속형 사회적 자본은 온라인 팬덤활동과 주관적 웰빙의 관계에 있어 매개할 것이다.
+H7-4: 결속형 사회적 자본은 오프라인 팬덤활동과 주관적 웰빙의 관계에 있어 매개할 것이다.
+연구문제 1: 소외에 대한 두려움(FOMO)은 팬덤활동과 우울감 간의 관계를 조절하는가?
+연구문제 2: 소외에 대한 두려움(FOMO)은 팬덤활동과 사회적 자본 간의 관계를 조절하는가?</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>온라인 팬덤활동, 오프라인 팬덤활동</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>주관적 웰빙</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>우울감, 사회적 자본 (교량형 사회적 자본, 결속형 사회적 자본)</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움 (FOMO)</t>
+        </is>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>1. 온라인 및 오프라인 팬덤활동은 주관적 웰빙에 유의미한 정(+)의 영향을 미치며, 우울감에는 부(-)의 영향을 미쳐 우울감을 감소시킵니다.
+2. 온라인 및 오프라인 팬덤활동은 교량형 및 결속형 사회적 자본을 유의미하게 증가시킵니다.
+3. 우울감은 주관적 웰빙에 부(-)의 영향을 미치며, 사회적 자본(교량형, 결속형)은 주관적 웰빙에 정(+)의 영향을 미칩니다.
+4. 매개효과 분석 결과, 우울감과 결속형 사회적 자본은 온라인/오프라인 팬덤활동과 주관적 웰빙의 관계를 유의미하게 매개하는 반면, 교량형 사회적 자본은 매개효과가 나타나지 않았습니다.
+5. 조절효과 분석 결과, 소외에 대한 두려움(FOMO)은 온라인 팬덤활동과 우울감 간의 관계를 조절하며, FOMO가 낮은 집단에서 온라인 팬덤활동이 우울감을 감소시키는 효과가 더 강하게 나타났습니다. 또한 FOMO는 온라인 및 오프라인 팬덤활동과 교량형 사회적 자본 간의 관계를 조절하는 것으로 확인되었습니다.</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>[온라인 팬덤활동 (Online Fandom Activities)]
+1. I have joined a fan club or fan cafe.
+(나는 팬클럽이나 팬 카페를 가입한 적 있다.)
+2. I have visited the star's homepage.
+(나는 스타의 홈페이지에 방문한 적 있다.)
+3. I have written an email or fan letter.
+(나는 이메일 또는 팬레터를 쓴 적 있다.)
+4. I have left comments on portal sites or articles about the star.
+(나는 스타에 관한 포털 사이트나 기사에 댓글 단 적 있다.)
+5. I have uploaded videos about the star on internet sites.
+(나는 인터넷 사이트에 스타에 관한 동영상을 올린 적 있다.)
+[오프라인 팬덤활동 (Offline Fandom Activities)]
+1. I have attended a fan meeting.
+(나는 팬 미팅을 참석한 적 있다.)
+2. I have gone to broadcasting stations, concert halls, or stadiums to see the star.
+(나는 스타를 보기 위해 방송국이나 공연장, 경기장에 간 적 있다.)
+3. I have sent gifts or letters to the star.
+(나는 스타에게 선물, 편지를 보낸 적 있다.)
+4. I have purchased books, albums, CDs, or DVDs related to the star.
+(나는 스타 관련 책, 앨범, CD, DVD 등 구입한 적 있다.)
+5. I have purchased star-related goods, photo cards, cheering wands, dolls, etc.
+(나는 스타 관련 굿즈(포카, 응원봉, 인형 등) 구매한 적 있다.)
+[교량형 사회적 자본 (Bridging Social Capital)]
+1. Through fandom, I get to know various types of fans newly.
+(팬덤을 통해 다양한 유형의 팬들을 새롭게 알게 된다.)
+2. Through fandom, I obtain information necessary for fandom activities from fans I do not know well.
+(팬덤을 통해 잘 모르는 팬들로부터 팬덤활동에 필요한 정보를 얻는다.)
+3. Conversations with people I meet in the fandom make me realize other things I did not know.
+(팬덤에서 만나는 사람들과의 대화는 내가 모르는 다른 것을 알게 만든다.)
+[결속형 사회적 자본 (Bonding Social Capital)]
+1. Among the people I meet in the fandom, there is someone I can talk to when I am lonely.
+(팬덤에서 만나는 사람들 중에 외로울 때 대화를 나눌만한 사람이 있다.)
+2. Among the people I meet in the fandom, there is someone who can advise me on very important decisions.
+(팬덤에서 만나는 사람들 중에 매우 중요한 결정에 관해 조언을 해줄 수 있는 사람이 있다.)
+3. Among the people I meet in the fandom, there is someone trustworthy.
+(팬덤에서 만나는 사람들 중에 신뢰할만한 사람이 있다.)
+4. I am willing to help people I meet in the fandom when they are in trouble.
+(팬덤에서 만나는 사람들이 곤경에 처했을 때 도와줄 의향이 있다.)
+[우울감 (Depression)]
+1. I am sad.
+(나는 슬프다.)
+2. I have no courage about the future.
+(나는 미래에 대해 용기가 없다.)
+3. I feel like a failure.
+(나는 실패인 것 같다.)
+4. It is hard for me to enjoy anything.
+(나는 뭔가를 즐기는 것이 힘들다.)
+5. I feel guilty.
+(나는 죄책감이 든다.)
+6. I feel like I am being punished.
+(나는 벌 받는 것 같다.)
+7. I am disappointed in myself.
+(나는 내가 실망스럽다.)
+8. I cry often.
+(나는 종종 운다.)
+9. I have no interest in people.
+(나는 사람들에 관심이 없다.)
+[소외에 대한 두려움 (Fear of Missing Out; FOMO)]
+1. I feel anxious when I cannot access new updates.
+(나는 새로운 소식을 접하지 못할 때 불안하다.)
+2. Even on holidays, I keep checking what other people are doing.
+(나는 휴일에도 다른 사람들이 무엇을 하고 있는지 계속 확인한다.)
+3. I keep connecting to SNS so as not to miss anything.
+(나는 어떤 것도 놓치지 않기 위해 계속해서 SNS에 접속하고 있다.)
+4. I get bothered if I miss planned gatherings.
+(나는 계획된 모임을 놓치면 신경이 쓰인다.)
+5. Sometimes I wonder if I spend too much time keeping up with what is going on.
+(가끔 저는 제가 무슨 일이 일어나고 있는지에 따라가는 데 너무 많은 시간을 보내는 것이 아닌가 생각한다.)
+6. It is important to share detailed information via SNS when having a good time.
+(나는 즐거운 시간을 보낼 때 세부 정보를 SNS로 공유하는 것이 중요하다.)
+7. I am afraid that others might have had more rewarding experiences than me.
+(나는 다른 사람들이 나보다 유익한 경험들을 많이 했을까 두렵다.)
+8. I constantly check my smartphone so as not to miss new information.
+(나는 새로운 정보를 놓치지 않기 위해 지속적으로 스마트 폰을 확인한다.)
+[주관적 웰빙 (Subjective Well-being)]
+1. In most ways, my life is close to my ideal.
+(나는 내가 대체로 내 이상에 가까운 생활을 하고 있다.)
+2. Currently, I have very good life conditions.
+(현재 나는 아주 좋은 생활 조건들을 가지고 있다.)
+3. So far, I have gotten the important things I want in my life.
+(나는 지금까지 내 삶에서 내가 원하는 중요한 것들을 가져왔다.)
+4. Even if I could live my life over, I would live it just as I have.
+(만약 내 삶을 다시 산다하더라도 나는 지금까지의 삶처럼 살겠다.)
+5. Day by day, I am living faithfully according to the plans I made.
+(하루하루 내가 짠 계획대로 충실하게 살고 있다.)
+6. I am satisfied with my life.
+(나는 나의 삶에 대해 만족한다.)
+7. Life is fun.
+(사는 것이 재미있다.)
+8. I am happy.
+(나는 행복하다.)</t>
+        </is>
+      </c>
+      <c r="O911" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="n">
+        <v>911</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>이효창</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>현대 소외 탈출 아이돌 응원 광고, 준사회적 상호작용, FoMO(Fear of Missing Out), 그리고 심리적 안녕감을 중심으로</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>서강대학교 일반대학원 신문방송학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>자기결정이론 (Self-Determination Theory), 사회비교이론 (Social Comparison Theory), 이용과 충족 이론 (Uses and Gratifications Theory), 불확실성 감소 이론 (Uncertainty Reduction Theory)</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>[독립변수: FoMO] -&gt; [매개변수: 미디어 충성도, 준사회적 상호작용] -&gt; [종속변수: 심리적 안녕감]</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>H1: FoMO의 정도와 아이돌 응원 광고에 대한 충성도는 정적 상관관계를 나타낼 것이다.
+H2: FoMO의 정도는 아이돌 응원 광고와의 준사회적 상호작용에 정적인 영향을 미칠 것이다.
+H3: 아이돌 응원 광고에 대한 충성도와 아이돌 응원 광고와의 준사회적 상호작용은 정적인 상관관계를 가질 것이다.
+H4: 아이돌 응원 광고에 대한 충성도와 준사회적 상호작용은 심리적 안녕감에 정적인 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>소외에 대한 두려움 (FoMO: Fear of Missing Out)</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>심리적 안녕감 (Psychological Well-Being)</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>미디어 충성도 (Media Loyalty), 준사회적 상호작용 (Parasocial Interaction)</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>1. FoMO의 정도가 높을수록 소속감을 확인할 수 있는 아이돌 응원 광고에 대한 미디어 충성도(지속적인 관심과 참여)가 높게 나타남.
+2. FoMO의 정도가 높을수록 미디어에 더욱 깊이 공감하고 자신의 삶을 투영하는 준사회적 상호작용이 활발히 나타남.
+3. 아이돌 응원 광고에 관한 활동이 활발한 사람일수록(행동적 충성도가 높을수록) 준사회적 상호작용이 두드러짐.
+4. 아이돌 응원 광고에 관한 참여가 활발하고 준사회적 상호작용이 두드러질 경우 심리적 안녕감의 하위 요인인 자율성이 높게 나타남.
+5. 광고에 더 깊이 공감할수록 더 나은 삶을 위해 목표의식을 가지며(삶의 목적, 개인의 성장), 자신의 삶을 적극적으로 투영할수록 주변인과 적극적으로 교류할 가능성(긍정적 대인관계)이 높음.</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>[소외에 대한 두려움 (FoMO)]
+1. I get anxious when I cannot make it to a sudden gathering with my friends.
+(나는 친구들과 갑자기 잡힌 약속에 가지 못 하면, 신경이 쓰인다.)
+2. I get anxious when I miss a planned meeting.
+(나는 약속된 모임에 빠지게 되면 불안하다.)
+3. I feel anxious when I don't know what my friends are up to.
+(나는 친구들의 소식을 접하지 못할 때 불안하다.)
+4. I worry that my friends are having a good time without me.
+(나는 내 친구들이 나를 빼놓고 재밌는 시간을 보낼까봐 걱정된다.)
+5. I worry that I spend too much time keeping track of what is going on around me.
+(나는 주변을 신경 쓰는 데 시간을 많이 보내는 것 같아 걱정된다.)
+6. I constantly check what my friends are doing even on holidays (e.g., checking Instagram stories).
+(나는 휴일에도 친구들이 무엇을 하고 있는지 계속 확인한다 (예시: 인스타그램 스토리 확인).)
+7. I fear my friends are having better experiences than me.
+(나는 내 친구들이 나보다 좀 더 나은 경험을 할까봐 두렵다.)
+8. I fear other people besides my friends are having better experiences than me.
+(나는 친구를 제외한 다른 사람들이 나보다 더 나은 경험을 할까봐 두렵다.)
+[준사회적 상호작용 (Parasocial Interaction)]
+1. I feel like the message of this advertisement is a part of my life.
+(나는 이 광고의 메시지가 내 삶의 일부로 느껴진다.)
+2. I feel this advertisement is familiar to me.
+(나는 이 광고가 친근하게 느껴진다.)
+3. I have felt comforted by watching this advertisement.
+(나는 이 광고를 보고 위로를 받은 적이 있다.)
+4. Watching this advertisement relieves my stress.
+(나는 이 광고를 보면 스트레스가 풀린다.)
+5. I watch this advertisement so as not to fall behind others.
+(나는 다른 사람에게 뒤처지지 않기 위해 이 광고를 본다.)
+6. I watch this advertisement because of my friends, family, colleagues, or fan club members.
+(나는 친구, 가족, 동료, 팬클럽 회원 때문에 본다.)
+7. I want to watch this advertisement together with my friends, colleagues, or fan club members.
+(나는 이 광고를 친구 혹은 동료(팬클럽 회원)와 함께 보고 싶다.)
+8. I think this advertisement has a good influence on my life.
+(나는 이 광고가 내 인생에 좋은 영향을 미친다고 생각한다.)
+9. I think the information in this advertisement is reliable.
+(나는 이 광고의 정보가 믿을만하다고 생각한다.)
+10. I think back on this advertisement after watching it.
+(나는 이 광고를 보고 난 후 이 광고를 떠올려본다.)
+11. I talk about this advertisement to my friends and people around me.
+(나는 이 광고에 대해 친구 및 주변사람에게 이야기한다.)
+[미디어 충성도 (Media Loyalty)]
+1. I enjoy watching this advertisement.
+(나는 이 광고를 즐겨 본다.)
+2. I like this advertisement.
+(나는 이 광고를 좋아한다.)
+3. I lose track of time when watching this advertisement.
+(나는 이 광고를 보고 있으면 시간 가는 줄 모른다.)
+4. I look for this kind of advertisement first in subway stations.
+(나는 전철 역사 안에서 이와 같은 광고를 우선적으로 찾아본다.)
+5. I will show photos taken in front of this advertisement to my friends or acquaintances.
+(나는 이 광고 앞에서 찍은 사진을 주변 친구 혹은 지인에게 보여줄 것이다.)
+6. I will look for this kind of advertisement in other stations as well.
+(나는 다른 역에서도 이와 같은 광고를 찾아볼 것이다.)
+7. I will keep looking for this kind of advertisement even if it costs transportation fees.
+(나는 이와 같은 광고를 찾아보기 위해 교통비가 들더라도 계속 찾아 볼 것이다.)
+[심리적 안녕감 (Psychological Well-Being)]
+1. I am more satisfied with my current life than in the past.
+(나는 과거보다 현재의 삶에 만족한다.)
+2. My friends or people around me seem to be more successful in life than me.
+(내 친구 혹은 주변인은 인생에서 나보다 더 잘나가는 것 같다. (역산))
+3. I think my personality is quite decent.
+(나는 내 성격이 괜찮은 편이라 생각한다.)
+4. I can handle all my tasks well and on time.
+(나는 모든 일을 제 때에 잘 처리해 나갈 수 있다.)
+5. The things I have to do every day feel overwhelming.
+(나는 매일 매일 해야 하는 일들이 힘겹다. (역산))
+6. I have my own lifestyle that I am satisfied with.
+(나는 만족하는 나만의 생활 방식(Lifestyle)이 있다.)
+7. I tend not to be influenced by my friends or people around me when making decisions.
+(나는 무슨 일을 결정할 때 친구나 주변인의 영향을 받지 않는 편이다.)
+8. I am easily swayed by the words of a strong-willed friend.
+(나는 주장이 강한 친구의 말에 솔깃한다. (역산))
+9. I tend to express my opinion clearly when it differs from my friends or people around me.
+(나는 친구나 주변인과 의견이 다를 때 내 의견을 분명하게 말하는 편이다.)
+10. I get along well with my friends or people around me.
+(나는 친구 혹은 주변인과 사이좋게 지낸다.)
+11. I think most people seem to have more friends than I do.
+(나는 대부분의 사람들이 나보다 친구를 더 많이 갖고 있는 것 같다고 생각한다. (역산))
+12. I have friends or people around me whom I can trust, and I believe they trust me too.
+(내게는 믿을 수 있는 친구나 주변인이 있고 그들 역시 나를 믿을 수 있다고 생각한다.)
+13. I feel joy in planning and achieving future goals.
+(나는 미래의 계획을 짜고 이루는 일에 즐거움을 느낀다.)
+14. Sometimes I feel like the things I do every day are trivial and unimportant.
+(나는 가끔 매일 하는 일들이 사소하고 중요하지 않은 것처럼 느껴진다. (역산))
+15. I have my own goals in life.
+(나는 나만의 인생 목표가 있다.)
+16. I think it is important to have new experiences that stimulate my life.
+(나는 내 삶에 자극을 줄 만한 새로운 경험을 하는 것이 중요하다고 생각한다.)
+17. I have no intention of expanding my scope of activities anymore.
+(나는 더 이상 내 활동 영역을 넓힐 생각이 없다. (역산))
+18. To me, life is a continuous process of learning, changing, and growing.
+(나에게 있어 삶은 끊임없이 배우고 변화하고 성장하는 과정이다.)</t>
+        </is>
+      </c>
+      <c r="O912" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O912"/>
+  <dimension ref="A1:O922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72612,6 +72612,1342 @@
         </is>
       </c>
     </row>
+    <row r="913">
+      <c r="A913" t="n">
+        <v>912</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>이예주</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>가상 인플루언서와 감각적 경험 소비</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 심리학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>준사회적 상호작용 이론(Parasocial Interaction Theory), 불쾌한 골짜기 이론(Uncanny Valley Theory), 아바타 마케팅 이론(Theory of Avatar Marketing), 심리적 반발 이론(Psychological Reactance Theory)</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>[독립변수: 감각 경험 (원거리 vs. 근거리)] x [조절변수: 행동적 현실감 (높음 vs. 낮음)] -&gt; [매개변수: 섬뜩함] -&gt; [종속변수: 광고태도]</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>가설 1: 감각 경험과 행동적 현실감은 광고태도에 상호작용 효과를 나타낼 것이다.
+가설 2: 감각 경험과 행동적 현실감의 상호작용 효과는 섬뜩함을 매개로 광고태도에 영향을 미칠 것이다.
+가설 2a: 감각 경험이 근거리 경험일 때, 행동적 현실감이 높은 경우에만 섬뜩함 수준이 높게 나타나고, 그 결과 광고태도가 낮게 나타날 것이다.</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>감각 경험 (원거리 감각 vs. 근거리 감각)</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>광고태도</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>섬뜩함 (Eeriness)</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>행동적 현실감 (Behavioral Realism)</t>
+        </is>
+      </c>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>첫째, 감각 경험과 행동적 현실감이 광고태도에 미치는 직접적인 상호작용 효과(가설 1)는 통계적으로 유의하지 않아 기각되었습니다.
+둘째, 감각 경험과 행동적 현실감의 상호작용이 섬뜩함을 매개로 광고태도에 영향을 미치는 조절된 매개효과(가설 2, 2a)는 유의하게 나타났습니다.
+셋째, 구체적으로 미각과 같은 근거리 감각 경험 조건에서 행동적 현실감이 높은 경우(영상 자극) 소비자가 느끼는 섬뜩함이 유의하게 증가하였으며, 이 섬뜩함은 광고태도에 부정적인 영향을 미쳤습니다. 반면, 행동적 현실감이 낮은 조건(정적 이미지)이나 청각과 같은 원거리 감각 조건에서는 이러한 부정적 영향이 나타나지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>[형태적 현실감]
+- This virtual influencer is ______________. (Cartoonlike - Human-like)
+(이 가상 인플루언서는 ______________. (만화 같다 - 인간과 유사하다))
+[행동적 현실감]
+- The virtual influencer showed product usage behavior (e.g., movement, gesture) in the post.
+(가상 인플루언서는 게시물에서 제품사용행동(예: 움직임, 제스처)을 보여줬다.)
+[광고태도]
+- This post is bad - good.
+(이 게시물은 나쁘다 – 좋다.)
+- This post is unattractive - attractive.
+(이 게시물은 매력적이지 않다 – 매력적이다.)
+- This post is dislikeable - likeable.
+(이 게시물은 호감이 가지 않는다 – 호감이 간다.)
+- This post is negative - positive.
+(이 게시물은 부정적이다 - 긍정적이다.)
+[섬뜩함]
+- This influencer is weird.
+(이 인플루언서는 기이하다.)
+- This influencer is eerie.
+(이 인플루언서는 섬뜩하다.)
+- This influencer is strange.
+(이 인플루언서는 이상하다.)
+- This influencer is creepy.
+(이 인플루언서는 소름끼친다.)</t>
+        </is>
+      </c>
+      <c r="O913" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="n">
+        <v>913</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>김지희</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>SNS 패션 콘텐츠 이용자의 FoMO 지각이 명품 브랜드 소비에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>서울대학교 대학원 의류학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>자아 개념 이론 (Self-Concept Theory), 사회 비교 이론 (Social Comparison Theory), 자기결정성 이론 (Self-Determination Theory)</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>[IV] SNS 패션 콘텐츠 이용동기 (자아표현 동기, 정보탐색 동기, 대인커뮤니케이션 동기), 보상소비성향 -&gt; [Mediator] FoMO 지각 -&gt; [DV] 명품 브랜드 소비의도 (조절변수: 소비 유형 [경험소비 vs 물질소비])</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>H1-1: 자아표현 동기는 FoMO에 정적인 영향을 미칠 것이다.
+H1-2: 정보탐색 동기는 FoMO에 정적인 영향을 미칠 것이다.
+H1-3: 대인커뮤니케이션 동기는 FoMO에 정적인 영향을 미칠 것이다.
+H1-4: 보상소비성향은 FoMO에 정적인 영향을 미칠 것이다.
+H2: FoMO는 명품 브랜드 소비의도에 정적인 영향을 미칠 것이다.
+H3-1: FoMO 지각은 자아표현 동기와 명품 브랜드 소비의도 간 관계를 매개할 것이다.
+H3-2: FoMO 지각은 정보탐색 동기와 명품 브랜드 소비의도 간 관계를 매개할 것이다.
+H3-3: FoMO 지각은 대인커뮤니케이션 동기와 명품 브랜드 소비의도 간 관계를 매개할 것이다.
+H3-4: FoMO 지각은 보상소비성향과 명품 브랜드 소비의도 간 관계를 매개할 것이다.
+H4-1: 자아표현 동기가 FoMO에 미치는 영향은 소비 유형에 따라 차이가 있을 것이다.
+H4-2: 정보탐색 동기가 FoMO에 미치는 영향은 소비 유형에 따라 차이가 있을 것이다.
+H4-3: 대인커뮤니케이션 동기가 FoMO에 미치는 영향은 소비 유형에 따라 차이가 있을 것이다.
+H4-4: 보상소비성향이 FoMO에 미치는 영향은 소비 유형에 따라 차이가 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>SNS 패션 콘텐츠 이용동기 (자아표현 동기, 정보탐색 동기, 대인커뮤니케이션 동기), 보상소비성향</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>명품 브랜드 소비의도</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>FoMO 지각</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>소비 유형 (경험소비, 물질소비)</t>
+        </is>
+      </c>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>첫째, SNS 패션 콘텐츠 이용동기 중 자아표현 동기, 대인커뮤니케이션 동기 및 보상소비성향은 FoMO 지각에 유의한 정적(+) 영향을 미쳤으나, 정보탐색 동기는 FoMO 지각에 유의한 부적(-) 영향을 미쳤다. 둘째, FoMO 지각은 명품 브랜드 소비의도에 유의한 정적(+) 영향을 미쳤다. 셋째, FoMO 지각은 SNS 패션 콘텐츠 이용동기(자아표현, 정보탐색, 대인커뮤니케이션) 및 보상소비성향과 명품 브랜드 소비의도 간의 관계를 유의하게 매개하였다. 넷째, 소비 유형(경험소비 vs 물질소비)의 조절효과는 유의하지 않은 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>[SNS 패션 콘텐츠 이용동기 - 자아표현 동기]
+- I use SNS fashion content to deliver fashion information or knowledge that I know.
+(나는 SNS 패션 콘텐츠를 내가 알고 있는 패션 정보나 지식을 전달하기 위해 이용한다.)
+- I use SNS fashion content to freely express my daily life or thoughts about fashion.
+(나는 SNS 패션 콘텐츠를 패션에 관한 나의 일상이나 생각을 자유롭게 표현하기 위해 이용한다.)
+- I use SNS fashion content to promote myself and express my image or style.
+(나는 SNS 패션 콘텐츠를 나를 알리고 나의 이미지나 스타일을 표현하기 위해 이용한다.)
+- I use SNS fashion content to get help with my expertise and business.
+(나는 SNS 패션 콘텐츠를 나의 전문성과 비즈니스에 도움을 받기 위해 이용한다.)
+- I use SNS fashion content to express my values regarding fashion.
+(나는 SNS 패션 콘텐츠를 패션에 관한 나의 가치관을 표현하기 위해 이용한다.)
+[SNS 패션 콘텐츠 이용동기 - 정보탐색 동기]
+- I use SNS fashion content to obtain new information about fashion brand products, services, events, etc.
+(나는 SNS 패션 콘텐츠를 패션 브랜드 제품, 서비스, 이벤트 등에 관한 새로운 정보를 얻기 위해 이용한다.)
+- I use SNS fashion content to obtain useful information about fashion brand products, services, events, etc.
+(나는 SNS 패션 콘텐츠를 패션 브랜드 제품, 서비스, 이벤트 등에 관한 유용한 정보를 얻기 위해 이용한다.)
+- I use SNS fashion content to obtain accurate information about fashion brand products, services, events, etc.
+(나는 SNS 패션 콘텐츠를 패션 브랜드 제품, 서비스, 이벤트 등에 관한 정확한 정보를 얻기 위해 이용한다.)
+- I use SNS fashion content to encounter the daily fashion of celebrities, fashion influencers, and other famous people.
+(나는 SNS 패션 콘텐츠를 연예인, 패션 인플루언서 등 유명인들의 일상 패션을 접하기 위해 이용한다.)
+- I use SNS fashion content to observe others' fashion consumption experiences.
+(나는 SNS 패션 콘텐츠를 타인의 패션 소비 경험을 관찰하기 위해 이용한다.)
+[SNS 패션 콘텐츠 이용동기 - 대인커뮤니케이션 동기]
+- I use SNS fashion content to talk with others about fashion.
+(나는 SNS 패션 콘텐츠를 타인과 패션에 대한 이야기를 나누기 위해 이용한다.)
+- I use SNS fashion content to exchange advice or information about fashion with others.
+(나는 SNS 패션 콘텐츠를 타인과 패션에 대한 조언이나 정보를 교류하기 위해 이용한다.)
+- I use SNS fashion content to connect with people who share similar interests in fashion.
+(나는 SNS 패션 콘텐츠를 패션에 있어 비슷한 관심사를 가진 사람들과 접하기 위해 이용한다.)
+- I use SNS fashion content to build and maintain relationships with others.
+(나는 SNS 패션 콘텐츠를 타인과 관계를 맺고 유지하기 위해 이용한다.)
+- I use SNS fashion content to receive attention from others regarding fashion.
+(나는 SNS 패션 콘텐츠를 타인들로부터 패션에 대한 관심을 받기 위해 이용한다.)
+[브랜드-자아 동일시]
+- This brand fits my image well.
+(이 브랜드는 나의 이미지와 잘 맞는다.)
+- This brand fits my lifestyle well.
+(이 브랜드는 나의 라이프스타일과 잘 맞는다.)
+- This brand fits my personality well.
+(이 브랜드는 나의 성격과 잘 맞는다.)
+- This brand fits my values well.
+(이 브랜드는 나의 가치관과 잘 맞는다.)
+- This brand fits the image of me that others perceive.
+(이 브랜드는 타인이 생각하는 나의 이미지와 잘 맞는다.)
+- This brand expresses my social status well.
+(이 브랜드는 나의 사회적 신분을 잘 표현해 준다.)
+- This brand expresses well to others what kind of person I am.
+(이 브랜드는 타인에게 내가 어떤 사람인지를 잘 표현해 준다.)
+- This brand helps me be socially recognized.
+(이 브랜드는 내가 사회적으로 인정받는 데 도움을 준다.)
+[FoMO 지각]
+- I am anxious that if I miss this opportunity, I will not be able to make a personally rewarding purchase.
+(이 기회를 놓치게 되면 개인적으로 보람찬 소비를 하지 못할 것 같아 불안하다.)
+- I am anxious that I might miss this opportunity because it is clear that it will be important or interesting to me.
+(이 기회가 내게 중요하거나 혹은 재미있을 것이 분명해서, 이를 놓치게 될까봐 불안하다.)
+- I am anxious that I might miss this opportunity due to other circumstances.
+(다른 사정으로 인해 이 기회를 놓치게 될까봐 불안하다.)
+- I am anxious that if I miss this opportunity, I will regret it in the future.
+(이 기회를 놓치게 되면 훗날 스스로 후회하게 될 것 같아 불안하다.)
+- I am anxious that if I miss this opportunity, my group will consider me unimportant.
+(이 기회를 놓치게 되면 내가 속한 집단에서 나를 중요하지 않게 여길 것 같아 불안하다.)
+- I am anxious that if I miss this opportunity, I will be ignored or forgotten by my group.
+(이 기회를 놓치게 되면 내가 속한 집단에서 무시당하거나, 잊혀질 것 같아 불안하다.)
+- I am anxious that if I miss this opportunity, I will not meet the standards of my group.
+(이 기회를 놓치게 되면 내가 속한 집단의 기준에 부합하지 않는 것 같아 불안하다.)
+- I am anxious that if I miss this opportunity, I will be excluded from my group.
+(이 기회를 놓치게 되면 내가 속한 집단에서 배제될 것 같아 불안하다.)
+- I am anxious that if I miss this opportunity, others will make more rewarding purchases than me.
+(이 기회를 놓치게 되면 남들이 나보다 더 보람찬 소비를 하게 될 것 같아 불안하다.)
+[보상소비성향]
+- I tend to consume to relieve my feelings when I am upset.
+(나는 속상할 때, 이를 해소하기 위해 소비를 하는 경향이 있다.)
+- I tend to consume to relieve my feelings when I am sad or depressed.
+(나는 슬프거나 우울할 때, 이를 해소하기 위해 소비를 하는 경향이 있다.)
+- I tend to consume to relieve my feelings when I am angry.
+(나는 화가 날 때, 이를 해소하기 위해 소비를 하는 경향이 있다.)
+- I tend to consume to relieve my feelings when I am stressed.
+(나는 스트레스를 받을 때, 이를 해소하기 위해 소비를 하는 경향이 있다.)
+- I tend to consume to relieve my feelings when I am in a bad mood.
+(나는 기분이 좋지 않을 때, 이를 해소하기 위해 소비를 하는 경향이 있다.)
+- I tend to consume to relieve my feelings when I feel helpless.
+(나는 무력감을 느낄 때, 이를 해소하기 위해 소비를 하는 경향이 있다.)
+[명품 브랜드 소비의도]
+- If I have the time and financial resources, I will consume the brand in the near future.
+(나는 시간적·경제적으로 여유가 있다면, 가까운 미래에 해당 브랜드를 소비할 것이다.)
+- I will recommend the brand to my acquaintances.
+(나는 해당 브랜드를 지인들에게 추천할 것이다.)
+- I will encourage my acquaintances to consume the brand when they are trying to choose a brand.
+(나는 지인들이 브랜드를 선택하려고 할 때 해당 브랜드를 소비하도록 권유할 것이다.)
+- If I have the time and financial resources, I am willing to continuously consume the brand.
+(나는 시간적·경제적으로 여유가 있다면, 해당 브랜드를 지속적으로 소비할 의향이 있다.)</t>
+        </is>
+      </c>
+      <c r="O914" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="n">
+        <v>914</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Gwonyoon Lee (이권윤)</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>The Impact of Customer Satisfaction on Usage Behavior (고객만족이 이용행동에 미치는 영향)</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Department of Management of Technology (기술경영학 학위논문)</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>기대불일치이론 (Expectancy-Disconfirmation Theory), 관계몰입-신뢰이론 (Commitment-Trust Theory)</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>[고객만족 (Customer Satisfaction)] -&gt; [고객신뢰 (Customer Trust)] -&gt; [이용행동 (Usage Behavior)] (조절변수: 인지적 특성 [Cognitive Traits])</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>H1: 고객만족은 고객신뢰에 정(+)의 영향을 미칠 것이다.
+H2: 고객신뢰는 이용행동에 정(+)의 영향을 미칠 것이다.
+H3: 고객만족은 이용행동에 정(+)의 영향을 미칠 것이다.
+H4: 고객신뢰는 고객만족과 이용행동 간의 관계를 매개할 것이다.
+H5: 인지적 특성(정보탐색성향, 다양성추구성향, 사전기대수준, 유사소비경험수준)은 고객만족, 신뢰, 이용행동 간의 관계를 조절할 것이다.</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>고객만족 (Customer Satisfaction)</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>이용행동 (Usage Behavior)</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>고객신뢰 (Customer Trust)</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>인지적 특성 (Cognitive Traits: 정보탐색성향, 다양성추구성향, 사전기대수준, 유사소비경험수준)</t>
+        </is>
+      </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>첫째, 고객만족은 이용행동과 신뢰 모두에 유의한 정(+)의 영향을 미쳤으며, 신뢰 역시 이용행동에 정(+)의 영향을 미쳤습니다. 둘째, 신뢰는 만족과 이용행동 간의 관계를 부분 매개하는 것으로 나타났습니다. 셋째, 인지적 특성의 조절효과와 관련하여 정보탐색성향과 사전기대수준이 높을 때 만족이 이용행동으로 전환되는 효과가 약화되었으며, 다양성추구성향이 높을 때 신뢰의 행동 전환력이 감소하는 것으로 확인되었습니다.</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>[Customer Satisfaction (고객만족)]
+I am generally satisfied with the service of this clinic.
+(나는 이 병원의 서비스에 전반적으로 만족한다.)
+My choice to visit this clinic was wise.
+(이 병원을 방문한 나의 선택은 현명했다.)
+The service of this clinic met my expectations.
+(이 병원의 서비스는 나의 기대에 부합했다.)
+I am pleased with the overall experience at this clinic.
+(나는 이 병원에서의 전반적인 경험에 기쁘다.)
+[Customer Trust (고객신뢰)]
+The clinic provides services reliably and accurately.
+(이 병원은 서비스를 신뢰성 있고 정확하게 제공한다.)
+The staff of the clinic are trustworthy.
+(이 병원의 직원들은 신뢰할 수 있다.)
+I feel safe in my transactions with this clinic.
+(나는 이 병원과의 거래에서 안전함을 느낀다.)
+The clinic keeps its promises to customers.
+(이 병원은 고객과의 약속을 잘 지킨다.)
+[Usage Behavior (이용행동)]
+I will continue to use this clinic in the future.
+(나는 향후에도 이 병원을 계속 이용할 것이다.)
+I will recommend this clinic to others.
+(나는 이 병원을 다른 사람들에게 추천할 것이다.)
+I will say positive things about this clinic to other people.
+(나는 다른 사람들에게 이 병원에 대해 긍정적으로 말할 것이다.)
+I will consider this clinic as my first choice for future treatments.
+(나는 향후 치료를 위해 이 병원을 최우선으로 고려할 것이다.)
+I will visit this clinic again even if the price increases.
+(나는 가격이 인상되더라도 이 병원을 다시 방문할 것이다.)
+[Prior Expectation Level (사전기대수준)]
+I had high expectations before visiting this clinic.
+(나는 이 병원을 방문하기 전에 높은 기대를 가지고 있었다.)
+I expected the quality of service at this clinic to be excellent.
+(나는 이 병원의 서비스 품질이 우수할 것이라고 기대했다.)
+My overall expectation for this clinic was very high.
+(이 병원에 대한 나의 전반적인 기대는 매우 높았다.)
+[Information Search Propensity (정보탐색성향)]
+I search for a lot of information before choosing a clinic.
+(나는 병원을 선택하기 전에 많은 정보를 탐색한다.)
+I compare various clinics using different information sources.
+(나는 다양한 정보원을 활용하여 여러 병원을 비교한다.)
+I spend a lot of time and effort searching for clinic information.
+(나는 병원 정보를 탐색하는 데 많은 시간과 노력을 들인다.)
+I actively seek advice from others when choosing a clinic.
+(나는 병원을 선택할 때 타인의 조언을 적극적으로 구한다.)
+[Variety-Seeking Tendency (다양성추구성향)]
+I like to try new and different clinics rather than visiting the same one.
+(나는 동일한 병원을 방문하기보다 새롭고 다른 병원을 시도하는 것을 좋아한다.)
+I easily get bored with visiting the same clinic repeatedly.
+(나는 동일한 병원을 반복해서 방문하는 것에 쉽게 지루함을 느낀다.)
+I prefer to experience various clinics for a change.
+(나는 기분 전환을 위해 다양한 병원을 경험하는 것을 선호한다.)
+I am always looking for better alternative clinics.
+(나는 항상 더 나은 대안 병원을 찾고 있다.)
+[Similar Consumption Experience Level (유사소비경험수준)]
+I have a lot of experience visiting similar clinics.
+(나는 유사한 병원을 방문한 경험이 많다.)
+I am very familiar with the services of similar clinics.
+(나는 유사한 병원의 서비스에 대해 매우 잘 알고 있다.)
+I have frequently used services similar to those of this clinic.
+(나는 이 병원과 유사한 서비스를 자주 이용해 왔다.)
+I consider myself an experienced consumer of these clinic services.
+(나는 이러한 병원 서비스의 경험이 풍부한 소비자라고 생각한다.)</t>
+        </is>
+      </c>
+      <c r="O915" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="n">
+        <v>915</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>함석영</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>2020년대 이후 국내 영화관의 참여형 관람 현상 분석: 체험의 다층성과 문화적 의미</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 영상문화학협동과정 (석사학위논문)</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>현상학적 영화 이론(메를로퐁티, 비비안 섭책), 공동체 존재론(장 뤽 낭시), 유토피아 정동 이론(리처드 다이어), 집합 의례론(에밀 뒤르켐), 팬덤 및 참여문화 이론(헨리 젠킨스, 맷 힐스)</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>[독립변수: 참여형 영화 상영 방식(싱어롱, 응원, 콘서트 실황)] -&gt; [매개변수: 감각적 몰입, 신체적 동원, 집단적 흥분] -&gt; [종속변수: 관객의 다층적 체험 및 공동체적 정서 연대]</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>Q1. 참여적 영화 보기는 무엇이고 기존의 영화 감상 방식과 어떻게 구별되는가?
+Q2. 참여형 상영 방식은 영화 체험의 감각적, 정서적, 공동체적 층위를 어떻게 확장하고 재구성하는가?
+Q3. 관객은 참여적 영화 보기가 이뤄지는 영화관 속에서 어떠한 방식으로 참여하고 실천하는가?</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>참여형 영화 상영 유형 (싱어롱 상영, 응원 상영, 콘서트 실황 상영)</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>관객의 다층적 체험 (감각적 몰입, 공동체적 정서 연대, 팬덤 집단 실천)</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>신체적 동원 및 감각적 상호작용, 집단적 흥분(Collective Effervescence)</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>상영관 분위기, 관객 간의 관계성 및 자발성, 팬덤의 관람 규범</t>
+        </is>
+      </c>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>첫째, 참여형 상영은 관객의 신체적 반응과 수행적 행위를 통해 영화관 공간의 의미를 수동적 감상실에서 능동적 참여와 감각 교류의 장으로 전환시킵니다. 둘째, 관객은 단순한 수용자를 넘어 영화 텍스트에 응답하고 실천하며 의미를 재구성하는 감각적 주체이자 공동 창작자로 작동합니다. 셋째, 이러한 상영 방식은 현대 관객이 요구하는 감각 중심적 경험, 즉각적 반응성, 공동체적 몰입에 부응하는 실천 구조이며, 현대적 집합 의례를 통한 정서적 연대 형성의 구현입니다.</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>I synchronized my bodily movements and reactions with the rhythm and emotional flow of the film.
+(나는 영화의 리듬과 정서적 흐름에 나의 신체적 반응과 움직임을 동기화하였다.)
+I felt a strong sense of emotional solidarity and connection with other audience members in the theater.
+(나는 상영관 내의 다른 관객들과 강한 정서적 연대감과 연결감을 느꼈다.)
+I actively expressed my emotions through cheering, singing along, or using props during the screening.
+(나는 상영 중 응원, 싱어롱, 또는 소품 사용을 통해 나의 감정을 적극적으로 표현하였다.)
+The cinema space felt like a participatory platform for collective ritual rather than just a place for quiet viewing.
+(영화관 공간이 단순히 조용히 관람하는 곳이 아니라 집합적 의례를 위한 참여형 플랫폼처럼 느껴졌다.)
+I engaged in post-screening activities such as sharing reviews or creating memes on social media.
+(나는 상영 후 SNS에 후기를 공유하거나 밈을 제작하는 등의 사후 활동에 참여하였다.)</t>
+        </is>
+      </c>
+      <c r="O916" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="n">
+        <v>916</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>정현정</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>K-콘텐츠노출유형에따른외국인의독립한식당선택속성이만족및재방문의도에미치는영향</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>연세대학교 생활환경대학원 호텔·외식·급식경영전공 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>기대불일치이론 (Expectancy Disconfirmation Theory), 서비스스케이프 이론 (Servicescape/DINESCAPE Theory), 에스닉 진정성 이론 (Ethnic Authenticity Theory)</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>[IV] K-콘텐츠 노출유형 (K-Movie, K-Drama, K-POP) -&gt; [Mediator 1] 독립한식당 선택속성 (음식품질, 직원 및 언어서비스, 부가적 서비스, 물리적 환경) -&gt; [Mediator 2] 만족 -&gt; [DV] 재방문의도</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>H1: K-콘텐츠 노출유형은 외국인의 독립한식당 선택속성에 유의한 정(+)의 영향을 미칠 것이다.
+H1-1: K-Movie 노출은 독립한식당 선택속성에 유의한 정(+)의 영향을 미칠 것이다.
+H1-2: K-Drama 노출은 독립한식당 선택속성에 유의한 정(+)의 영향을 미칠 것이다.
+H1-3: K-POP 노출은 독립한식당 선택속성에 유의한 정(+)의 영향을 미칠 것이다.
+H2: 외국인의 독립한식당 선택속성은 만족에 유의한 정(+)의 영향을 미칠 것이다.
+H2-1: 독립한식당의 음식품질은 만족에 유의한 정(+)의 영향을 미칠 것이다.
+H2-2: 독립한식당의 직원 및 언어서비스는 만족에 유의한 정(+)의 영향을 미칠 것이다.
+H2-3: 독립한식당의 부가적 서비스는 만족에 유의한 정(+)의 영향을 미칠 것이다.
+H2-4: 독립한식당의 물리적 환경은 만족에 유의한 정(+)의 영향을 미칠 것이다.
+H3: 만족은 재방문의도에 유의한 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>K-콘텐츠 노출유형 (K-Movie, K-Drama, K-POP)</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>재방문의도 (Revisit Intention)</t>
+        </is>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>독립한식당 선택속성 (음식품질, 직원 및 언어서비스, 부가적 서비스, 물리적 환경), 만족 (Satisfaction)</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>1. K-콘텐츠 노출유형은 독립한식당 선택속성에 차별적인 영향을 미침: K-Movie 노출은 직원 및 언어서비스와 물리적 환경에 유의한 정(+)의 영향을 미쳤고, K-Drama 노출은 음식품질에 유의한 정(+)의 영향을 미쳤으며, K-POP 노출은 모든 선택속성(음식품질, 직원 및 언어서비스, 부가적 서비스, 물리적 환경)에 유의한 정(+)의 영향을 미침.
+2. 외국인이 지각하는 독립한식당 선택속성 4개 요인(음식품질, 직원 및 언어서비스, 부가적 서비스, 물리적 환경)은 모두 만족에 유의한 정(+)의 영향을 미침.
+3. 만족은 재방문의도에 유의한 정(+)의 영향을 미치며, 만족도가 높을수록 재방문의도도 증가함.
+4. 연령, 최종학력, 월평균가구소득, 국적, 한국방문횟수, 한국체류기간, 한국여행형태 등에 따라 주요 변수 간 유의한 차이가 확인됨.</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>[K-Movies]
+- I like Korean movies.
+(나는 한국영화를 좋아한다.)
+- I enjoy watching Korean movies.
+(나는 한국영화를 보는 것을 즐긴다.)
+- I find Korean movies interesting.
+(나는 한국영화가 흥미롭다고 생각한다.)
+- I intend to continue watching Korean movies in the future.
+(나는 앞으로도 계속 한국영화를 보고 싶다.)
+- Watching Korean movies has increased my interest in Korean food.
+(한국영화를 통해 한국음식에 관심이 많아졌다.)
+[K-Dramas]
+- I like Korean Dramas.
+(나는 한국드라마를 좋아한다.)
+- I enjoy watching Korean Dramas.
+(나는 한국드라마를 보는 것을 즐긴다.)
+- I find Korean Dramas interesting.
+(나는 한국드라마가 흥미롭다고 생각한다.)
+- I intend to continue watching Korean Dramas in the future.
+(나는 앞으로도 계속 한국드라마를 보고 싶다.)
+- Watching Korean Dramas has increased my interest in Korean food.
+(한국드라마를 통해 한국음식에 관심이 많아졌다.)
+[K-Pop]
+- I like K-Pop.
+(나는 케이팝을 좋아한다.)
+- I enjoy listening to K-Pop.
+(나는 케이팝을 듣는 것을 즐긴다.)
+- I find K-Pop interesting.
+(나는 케이팝을 흥미롭다고 생각한다.)
+- I intend to continue listening to K-Pop in the future.
+(나는 앞으로도 계속 케이팝을 듣고 싶다.)
+- Consuming K-Pop has increased my interest in Korean food.
+(케이팝을 통해 한국음식에 관심이 많아졌다.)
+[Food Quality]
+- The food smells appetizing.
+(한식당의 음식은 향이 좋다.)
+- Korean dishes are nutritious and include many healthy options.
+(한식 메뉴는 영양이 풍부하고 건강에 도움이 되는 메뉴가 많다.)
+- The food is hygienically prepared.
+(한식당의 음식은 위생적이다.)
+- The ingredients are fresh and high-quality.
+(한식 재료가 신선하고 품질이 좋다고 생각한다.)
+[Employee &amp; Language Service]
+- Staff can communicate with customers.
+(직원이 고객들과 의사소통이 가능하다.)
+- Staff respond accurately to customer requests.
+(직원이 고객의 요구에 대해 정확하게 응대한다.)
+- Staff know the menu well and explain it clearly.
+(직원이 메뉴에 대해 정확하게 인지하고 설명해준다.)
+[Ancillary Services]
+- Service is prompt.
+(서비스가 신속하다.)
+- Orders are delivered accurately.
+(주문한 식사가 정확하게 나온다.)
+- Side dishes are provided at no additional cost.
+(무료로 반찬을 제공한다.)
+[Physical Environment]
+- The exterior conveys a Korean image.
+(건물 외관을 통해 한국적 이미지를 느낄 수 있다.)
+- The interior environment nicely reflects Korean aesthetics.
+(실내 환경이 한국의 이미지를 잘 나타내고 있다.)
+- The interior design and decor are harmonious and comfortable overall.
+(내부 인테리어와 장식은 전반적으로 조화롭고 쾌적하다.)
+- The indoor ambiance—lighting, music, and smells—makes my dining experience more enjoyable.
+(조명, 음악, 향기 등 실내 분위기가 식사 경험을 더욱 즐겁게 만든다.)
+- The restaurant is overall clean and well organized.
+(전반적으로 청결하고 정돈되어 있다.)
+[Satisfaction]
+- I am satisfied overall with the taste of food at the independent Korean restaurant.
+(독립한식당의 음식 맛에 전반적으로 만족한다.)
+- I am satisfied overall with the service at the independent Korean restaurant.
+(독립한식당의 서비스에 전반적으로 만족한다.)
+- I am satisfied overall with the physical environment at the independent Korean restaurant.
+(독립한식당의 물리적 환경에 전반적으로 만족한다.)
+- I am satisfied overall with the amount I paid at the independent Korean restaurant.
+(독립한식당에 지출한 비용에 전반적으로 만족한다.)
+- My experience at the independent Korean restaurant was more satisfying than expected.
+(독립한식당의 경험은 기대보다 만족스럽다.)
+[Revisit Intention]
+- I intend to revisit independent Korean restaurants on my next trip to Korea.
+(다음 한국 방문 시 독립한식당을 다시 이용할 의향이 있다.)
+- I intend to set aside time to visit independent Korean restaurants on my next trip to Korea.
+(다음 한국 방문 시 독립한식당을 찾아갈 시간을 일부러 배정할 의향이 있다.)
+- I am willing to spend additional money to visit independent Korean restaurants.
+(독립한식당을 이용하기 위해 일정 비용을 더 지불할 의향이 있다.)
+- I intend to recommend independent Korean restaurants to others.
+(독립한식당을 지인에게 추천할 의향이 있다.)
+- I intend to continue dining at Korean restaurants in my home country.
+(귀국 후 자국에서도 한식당을 다시 방문할 의향이 있다.)</t>
+        </is>
+      </c>
+      <c r="O917" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="n">
+        <v>917</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>이예원</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Kano 모델을 활용한 건강기능식품 품질 속성이 고객 만족 및 지속 이용 의도에 미치는 영향 분석</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>연세대학교 생활환경대학원 호텔·외식·급식경영 전공 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Kano 모델 (Kano Model), 고객만족계수 (Customer Satisfaction Coefficient, CSC)</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>[독립변수: 건강기능식품 품질 속성 (영양품질, 정보품질, 가격품질)] -&gt; [매개변수: 고객 만족] -&gt; [종속변수: 지속 이용 의도] (집단비교 변수: 구매방식)</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>H1. 건강기능식품의 품질 속성은 고객 만족에 정(+)의 영향을 미칠 것이다.
+H1-1. 건강기능식품의 영양품질 속성은 고객 만족에 정(+)의 영향을 미칠 것이다.
+H1-2. 건강기능식품의 정보품질 속성은 고객 만족에 정(+)의 영향을 미칠 것이다.
+H1-3. 건강기능식품의 가격품질 속성은 고객 만족에 정(+)의 영향을 미칠 것이다.
+H2. 고객 만족은 지속 이용 의도에 정(+)의 영향을 미칠 것이다.
+H3. 건강기능식품의 품질 속성은 지속 이용 의도에 정(+)의 영향을 미칠 것이다.
+H3-1. 건강기능식품의 영양품질 속성은 지속 이용 의도에 정(+)의 영향을 미칠 것이다.
+H3-2. 건강기능식품의 정보품질 속성은 지속 이용 의도에 정(+)의 영향을 미칠 것이다.
+H3-3. 건강기능식품의 가격품질 속성은 지속 이용 의도에 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>건강기능식품 품질 속성 (영양품질, 정보품질, 가격품질)</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>지속 이용 의도</t>
+        </is>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>고객 만족</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>구매방식 (온라인/오프라인)</t>
+        </is>
+      </c>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>1. 건강기능식품의 품질 속성 중 영양품질과 정보품질은 고객 만족에 유의한 정(+)의 영향을 미쳤으나, 가격품질은 유의한 영향을 미치지 않았다.
+2. 고객 만족은 지속 이용 의도에 유의한 정(+)의 영향을 미쳤다.
+3. 영양품질과 정보품질은 지속 이용 의도에 유의한 정(+)의 영향을 미쳤으나, 가격품질은 유의한 영향을 미치지 않았다.
+4. 구매방식에 따른 집단별 분석 결과, 온라인 구매자 집단에서는 정보품질과 영양품질이 고객 만족 및 지속 이용 의도에 유의한 영향을 미쳤으나, 오프라인 구매자 집단에서는 개별 품질 속성의 유의한 영향이 나타나지 않았다.
+5. Kano 모델 분석 결과, '성분이 안전하게 검증된 원료', '제조사 및 원산지 정보 신뢰성', '정확하고 정직한 효능·기능 설명', '지불한 가격 대비 우수한 효능과 만족도', '적절한 가격으로 좋은 품질 제공' 등 5개 속성은 일원적 품질(O)로 분류되었고, 나머지 10개 속성은 무관심 품질(I)로 분류되었다.</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>[Nutritional Quality]
+- I feel anticipation that my health will improve when taking this health functional food.
+(복용 전 이 건강기능식품을 섭취하면 건강이 좋아질 것이라는 기대감이 든다.)
+- The health functional food contains sufficient scientifically recognized functional ingredients.
+(건강기능식품에 과학적으로 인정된 기능성 성분이 충분히 포함되어 있다.)
+- After taking the health functional food, I feel that my physical condition or health has actually improved.
+(건강기능식품을 복용한 후, 실제로 몸 상태나 컨디션이 좋아졌다.)
+- The ingredients contained in the health functional food consist of safely verified raw materials.
+(건강기능식품에 포함된 성분이 안전하게 검증된 원료로 구성되어 있다.)
+- The health functional food simultaneously provides various functions such as immunity enhancement, fatigue recovery, and gut health.
+(건강기능식품이 면역력 강화, 피로 개선, 장 건강 등 다양한 기능을 동시에 제공한다.)
+[Information Quality]
+- The main ingredients, content, and raw material names of the health functional food are clearly displayed.
+(건강기능식품의 주요 성분, 함량, 원료명 등이 명확하게 표시되어 있다.)
+- The manufacturer and origin information of the health functional food are clearly provided in a reliable manner.
+(건강기능식품의 제조사 및 원산지 정보가 신뢰할 수 있는 방식으로 명확히 제공된다.)
+- The efficacy and function descriptions of the health functional food are not exaggerated and are guided accurately and honestly.
+(건강기능식품의 효능·기능 설명이 과장되지 않고, 정확하고 정직하게 안내되어 있다.)
+- I feel that the health functional food brand is trustworthy.
+(건강기능식품 브랜드를 신뢰할 수 있다고 느낀다.)
+- The health functional food possesses official certification marks such as GMP or Ministry of Food and Drug Safety certification.
+(건강기능식품이 GMP, 식약처 인증 등 공식 인증 마크를 보유하고 있다.)
+[Price Quality]
+- I think the health functional food provides excellent efficacy and satisfaction compared to the price paid.
+(건강기능식품이 지불한 가격에 비해 우수한 효능과 만족도를 제공한다.)
+- I think the health functional food provides good quality at an appropriate price.
+(건강기능식품이 적절한 가격으로 좋은 품질을 제공한다.)
+- I judge that the price of the health functional food is reasonable and acceptable compared to similar products.
+(건강기능식품의 가격이 유사 제품과 비교해 타당하고 납득 가능한 수준이다.)
+- Additional benefits such as discounts, free gifts, and free shipping are provided when purchasing the health functional food.
+(건강기능식품 구매 시 할인, 사은품, 무료배송 등 추가적인 혜택이 제공된다.)
+- The price of the health functional food is reasonable, so I can purchase it without burden.
+(건강기능식품의 가격이 합리적이어서 부담 없이 구매할 수 있다.)
+[Customer Satisfaction]
+- The health functional food I consumed provides the expected effect and quality.
+(귀하가 섭취했던 건강기능식품은 기대했던 만큼의 효과와 품질을 제공한다.)
+- I intend to repurchase or continue using the health functional food I consumed.
+(귀하가 섭취했던 건강기능식품을 다시 구매하거나 계속 사용할 의향이 있다.)
+- I feel favorable and positive emotions toward the brand of the health functional food I consumed.
+(귀하가 섭취했던 건강기능식품의 brand에 호감과 긍정적인 감정을 느낀다.)
+- I am satisfied with the overall service, such as delivery, packaging, and customer response, of the health functional food I consumed.
+(귀하가 섭취했던 건강기능식품의 배송, 포장, 고객 응대 등 서비스 전반에 만족한다.)
+- I am overall satisfied with the health functional food I consumed.
+(귀하가 섭취했던 건강기능식품에 전반적으로 만족한다.)
+[Continuous Use Intention]
+- I plan to continue using this health functional food in the future.
+(앞으로도 이 건강기능식품을 계속 사용할 계획이다.)
+- I can confidently recommend the health functional food I consumed to family or friends.
+(귀하가 섭취했던 건강기능식품을 가족이나 친구에게 자신 있게 추천할 수 있다.)
+- If there are no special problems, I intend to use this health functional food continuously.
+(특별한 문제가 없다면 이 건강기능식품을 지속적으로 사용할 생각이다.)
+- Even if there are other brand products, there is a high possibility that I will continue to choose this health functional food.
+(다른 브랜드 제품이 있어도 이 건강기능식품을 계속 선택할 가능성이 높다.)</t>
+        </is>
+      </c>
+      <c r="O918" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="n">
+        <v>918</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>알 수 없음</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>알 수 없음</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>팝산업의 진화동력은 무엇인가</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>알 수 없음 (학위논문 또는 보고서 추정)</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>진화이론 (Evolutionary Theory), 토픽 모델링 (Topic Modeling)</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>[언론 보도 데이터 (5대 일간지)] -&gt; [토픽 모델링 (LDA)] -&gt; [팝 산업의 진화 동력 도출]</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>본 연구는 가설 검증형 연구가 아닌 토픽 모델링을 통한 탐색적 연구로, 명시적인 가설(H1, H2 등)은 제시되지 않았거나 제공된 텍스트에서 확인할 수 없습니다.</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>언론 보도 데이터 (조선일보, 중앙일보, 동아일보, 경향신문, 한겨레 기사)</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>팝 산업의 진화 동력 (토픽 및 트렌드)</t>
+        </is>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>조선일보, 중앙일보, 동아일보, 경향신문, 한겨레 등 5대 일간지의 기사 데이터(총 9,674건 및 4,615건 등)를 수집하여 토픽 모델링(LDA) 분석을 수행함. 이를 통해 팝 산업의 진화 동력을 시계열적 또는 주제별로 규명하고자 시도함.</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>No survey items are available because this study utilizes topic modeling on newspaper articles.
+(본 연구는 신문 기사를 대상으로 한 토픽 모델링 분석을 사용하였기 때문에 설문 문항이 존재하지 않습니다.)</t>
+        </is>
+      </c>
+      <c r="O919" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="n">
+        <v>919</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>김하나</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>IT스타트업 구성원의 잡 크래프팅이 조직몰입을 통해 고객지향성에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>직무요구-자원모델 (Job Demands-Resources Model), 조절초점이론 (Regulatory Focus Theory)</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>[독립변수: 잡 크래프팅 (과업 크래프팅, 인지 크래프팅, 관계 크래프팅)] -&gt; [매개변수: 조직몰입] -&gt; [종속변수: 고객지향성 (친절의 욕구, 니즈 이해의 욕구, 전달의 욕구)]</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>H1. IT스타트업 구성원의 잡 크래프팅은 고객지향성에 정(+)적 영향을 미칠 것이다.
+H1-1. 과업 크래프팅은 친절의 욕구에 정(+)적인 영향을 미칠 것이다.
+H1-2. 과업 크래프팅은 니즈 이해의 욕구에 정(+)적 영향을 미칠 것이다.
+H1-3. 과업 크래프팅은 전달의 욕구에 정(+)적 영향을 미칠 것이다.
+H1-4. 인지 크래프팅은 친절의 욕구에 정(+)적 영향을 미칠 것이다.
+H1-5. 인지 크래프팅은 니즈 이해의 욕구에 정(+)적 영향을 미칠 것이다.
+H1-6. 인지 크래프팅은 전달의 욕구에 정(+)적 영향을 미칠 것이다.
+H1-7. 관계 크래프팅은 친절의 욕구에 정(+)적 영향을 미칠 것이다.
+H1-8. 관계 크래프팅은 니즈 이해의 욕구에 정(+)적 영향을 미칠 것이다.
+H1-9. 관계 크래프팅은 전달의 욕구에 정(+)적 영향을 미칠 것이다.
+H2. IT스타트업 구성원의 잡 크래프팅은 조직몰입에 정(+)적 영향을 미칠 것이다.
+H2-1. 과업 크래프팅은 조직몰입에 정(+)적 영향을 미칠 것이다.
+H2-2. 인지 크래프팅은 조직몰입에 정(+)적 영향을 미칠 것이다.
+H2-3. 관계 크래프팅은 조직몰입에 정(+)적 영향을 미칠 것이다.
+H3. IT스타트업 구성원의 조직몰입은 고객지향성에 정(+)적 영향을 미칠 것이다.
+H3-1. 조직몰입은 친절의 욕구에 정(+)적 영향을 미칠 것이다.
+H3-2. 조직몰입은 니즈 이해의 욕구에 정(+)적 영향을 미칠 것이다.
+H3-3. 조직몰입은 전달의 욕구에 정(+)적 영향을 미칠 것이다.
+H4. IT스타트업 구성원의 조직몰입은 잡 크래프팅과 고객지향성과의 관계에서 매개역할을 할 것이다.
+H4-1 ~ H4-9. 조직몰입은 각 잡 크래프팅 하위요인과 고객지향성 하위요인 간의 관계를 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>잡 크래프팅 (과업 크래프팅, 인지 크래프팅, 관계 크래프팅)</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>고객지향성 (친절의 욕구, 니즈 이해의 욕구, 전달의 욕구)</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>조직몰입 (정서적 몰입)</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>1. 잡 크래프팅의 세 하위 요인(과업, 인지, 관계) 모두 고객지향성의 세 하위 요인(친절, 니즈 이해, 전달)에 유의미한 정(+)의 영향을 미침. 특히 과업 크래프팅의 영향력이 가장 큼.
+2. 인지 크래프팅과 관계 크래프팅은 조직몰입에 정(+)의 영향을 미쳤으나, 과업 크래프팅은 조직몰입에 유의미한 영향을 미치지 않음.
+3. 조직몰입은 고객지향성의 세 하위 요인 모두에 유의미한 정(+)의 영향을 미침.
+4. 조직몰입은 잡 크래프팅의 모든 하위 요인과 고객지향성의 모든 하위 요인 간의 관계를 유의미하게 매개함.</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>[잡 크래프팅 - 과업 크래프팅]
+1. I try new ways of doing my job to do it better.
+(나는 일을 더 잘하기 위해 새로운 방식을 시도해본다.)
+2. I change the scope or types of my tasks as needed while working.
+(나는 필요에 따라 맡은 업무의 범위나 종류를 변경해가며 일한다.)
+3. I try new tasks to better utilize my abilities or interests.
+(나는 내 능력이나 흥미를 더 잘 활용할 수 있도록 새로운 업무를 시도해본다.)
+4. I willingly take on extra tasks when working.
+(나는 일을 할 때 추가적인 업무를 기꺼이 맡는다.)
+5. I prioritize tasks that well reflect my abilities or interests.
+(나는 내 능력이나 흥미가 잘 반영될 수 있는 업무를 우선시한다.)
+[잡 크래프팅 - 인지 크래프팅]
+6. I think about how my work connects to my personal life purpose.
+(나는 내 일이 개인적인 삶의 목적과 어떻게 연결될 수 있는지 생각한다.)
+7. I remind myself that the tasks I perform are important for the success of the organization.
+(나는 내가 맡은 업무가 조직의 성공을 위해 중요하다는 것을 되새긴다.)
+8. I think about how my work contributes to our society.
+(나는 내 일이 우리 사회에 기여하는 바를 생각한다.)
+9. I think about how my work can have a positive impact on my life.
+(나는 내 일이 내 삶에 어떤 긍정적인 영향을 미칠 수 있는지 생각한다.)
+10. I think about what role my work plays in the happiness of my life.
+(나는 내 일이 내 삶의 행복에 어떤 역할을 하는지 생각한다.)
+[잡 크래프팅 - 관계 크래프팅]
+11. I try to get along well with people at work.
+(나는 직장에서 사람들과 잘 지내려고 노력한다.)
+12. I am willing to lead or actively participate in work-related social activities and gatherings.
+(나는 업무와 관련된 친목활동과 모임 등을 주도하거나 적극적으로 참석할 의향이 있다.)
+13. I organize special events (e.g., colleagues' birthday parties) at work.
+(나는 직장에서 특별한 이벤트(예, 동료의 생일 파티)를 주도한다.)
+14. I am willing to be a mentor to juniors or new employees, either officially or unofficially.
+(나는 공식적으로나 비공식적으로 기꺼이 후배나 신입사원의 멘토가 될 의향이 있다.)
+15. I try to stay close to people at work who have similar skills or interests as me.
+(나는 회사에서 나와 유사한 기술이나 흥미를 가진 사람들과 가깝게 지내려고 노력한다.)
+[조직몰입 - 정서적 몰입]
+1. I would be happy to spend the rest of my career with this company.
+(내가 이 회사에서 끝까지 직장생활을 하면 행복할 것이다.)
+2. I enjoy discussing my company with people outside it.
+(나는 회사 밖의 사람들과 내가 근무하는 회사에 대해 이야기하는 것을 좋아한다.)
+3. I think of this company's problems as my own.
+(나는 회사의 문제를 나의 문제처럼 생각한다.)
+4. If I were to change companies, I would not easily develop the same attachment as I have for this company.
+(내가 만약 다른 회사로 이직한다면, 이 회사만큼의 애착이 쉽게 생기지 않을 것이다.)
+5. I feel like a member of this company.
+(나는 이 회사에서 한 일원이라는 느낌을 받는다.)
+6. I feel emotionally attached to this company.
+(나는 이 회사에 대해 감정적인 애착을 느낀다.)
+7. This company has a great deal of personal meaning for me.
+(이 회사는 나에게 있어 매우 큰 의미가 있다.)
+8. I feel a strong sense of belonging to this company.
+(나는 이 회사에 대해 강한 소속감을 느낀다.)
+[고객지향성 - 친절의 욕구]
+1. I enjoy thinking about customers.
+(나는 고객에 대해 생각하는 것이 즐겁다.)
+2. I want to make every customer feel like they are the only customer.
+(나는 모든 고객에게 ‘당신은 유일한 고객’이라는 생각이 들도록 하고 싶다.)
+3. Customer problems are important to me too.
+(고객의 문제는 나에게도 중요하다.)
+4. I pay attention to each customer in a way that fits them.
+(나는 고객 한사람 한사람에게 그 고객에 맞는 관심을 쏟는다.)
+[고객지향성 - 니즈 이해의 욕구]
+5. I can naturally figure out what customers need.
+(나는 고객이 무엇이 필요한지 고객의 마음을 파악할 수 있다.)
+6. I generally know what customers want before they ask.
+(나는 대체로 고객이 요청하기 전에 그들이 원하는 것을 알고 있다.)
+7. I enjoy anticipating what customers will need.
+(나는 고객이 필요로 하는 것을 예상하는 것을 즐긴다.)
+8. I interact with customers by carefully paying attention to their expressions.
+(나는 고객의 의사표현을 유심히 참고해서 고객과 상호작용한다.)
+[고객지향성 - 전달의 욕구]
+9. I provide services at the promised time.
+(나는 서비스를 약속된 시간에 제공한다.)
+10. I feel great satisfaction in clearly delivering the service that customers want.
+(나는 고객이 원하는 서비스를 확실하게 제공하는 것에 큰 만족을 느낀다.)
+11. I have confidence in providing excellent service to customers.
+(나는 고객에게 훌륭한 서비스를 제공하는 것에 대한 자신감을 갖고 있다.)</t>
+        </is>
+      </c>
+      <c r="O920" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="n">
+        <v>920</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>미상 (제시된 텍스트에 명시되지 않음)</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>2023 (추정)</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>광고요금제 채택과 지속 이용 의도에 영향을 미치는 요인: 요금제의 지각된 특성, 광고 회피 성향, 지각된 광고 침입성, 콘텐츠 이용 동기 및 이용 행태를 중심으로</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>학위논문 또는 학술지 (제시된 텍스트에 명시되지 않음)</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>이용과 충족 이론 (Uses and Gratifications Theory), 혁신확산이론 (Diffusion of Innovations Theory)</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>[요금제의 지각된 특성, 광고 회피 성향, 지각된 광고 침입성, 콘텐츠 이용 동기, 이용 행태] -&gt; [광고요금제 채택 의도] -&gt; [지속 이용 의도]</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>H1: 요금제의 지각된 특성(경제성, 유용성 등)은 광고요금제 채택 의도에 정(+)의 영향을 미칠 것이다.
+H2: 소비자의 광고 회피 성향은 광고요금제 채택 의도에 부(-)의 영향을 미칠 것이다.
+H3: 지각된 광고 침입성은 광고요금제 채택 의도에 부(-)의 영향을 미칠 것이다.
+H4: 콘텐츠 이용 동기는 광고요금제 채택 의도에 정(+)의 영향을 미칠 것이다.
+H5: 광고요금제 채택 의도는 지속 이용 의도에 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>요금제의 지각된 특성 (경제성, 유용성 등), 광고 회피 성향, 지각된 광고 침입성, 콘텐츠 이용 동기, 이용 행태</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>광고요금제 채택 의도, 지속 이용 의도</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>광고요금제 채택 의도</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>1. 요금제의 지각된 경제적 혜택과 유용성은 광고요금제 채택 의도를 유의미하게 증가시키는 핵심 요인임.
+2. 사용자의 광고 회피 성향과 지각된 광고 침입성은 광고요금제 채택 의도에 강력한 부정적 영향을 미침.
+3. 콘텐츠 이용 동기 및 이용 행태에 따라 광고요금제에 대한 수용 태도와 지속 이용 의도에 차이가 존재함.</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>지각된 경제성 (Perceived Economic Benefit)
+- Using the ad-supported subscription plan is economically beneficial to me.
+(광고요금제를 사용하는 것은 나에게 경제적으로 이득이 된다.)
+- The ad-supported plan helps me save subscription costs.
+(광고요금제는 구독 비용을 절약하는 데 도움이 된다.)
+광고 회피 성향 (Ad Avoidance Tendency)
+- I intentionally ignore or avoid advertisements while watching content.
+(나는 콘텐츠를 시청하는 동안 의도적으로 광고를 무시하거나 피한다.)
+- I tend to do other things when advertisements start playing.
+(나는 광고가 시작되면 다른 일을 하는 경향이 있다.)
+지각된 광고 침입성 (Perceived Ad Intrusiveness)
+- I feel that advertisements interrupt my content viewing flow.
+(나는 광고가 나의 콘텐츠 시청 흐름을 방해한다고 느낀다.)
+- The advertisements shown during the service are intrusive.
+(서비스 중 제공되는 광고는 침입적이라고 느껴진다.)
+지속 이용 의도 (Continuous Use Intention)
+- I intend to continue using this ad-supported subscription plan in the future.
+(나는 향후 이 광고요금제를 지속적으로 이용할 의향이 있다.)
+- I will recommend this ad-supported subscription plan to people around me.
+(나는 주변 사람들에게 이 광고요금제를 추천할 것이다.)</t>
+        </is>
+      </c>
+      <c r="O921" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="n">
+        <v>921</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>현주, 윤지환</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>가치기반 수용모델에서의 혁신저항 매개효과와 디지털피로감 조절효과 분석 - 모바일기반 멤버십서비스를 기반으로-</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>고려대학교 기술경영전문대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>가치기반수용모델(Value-Based Adoption Model, VAM), 혁신저항이론(Innovation Resistance Theory), 전망이론(Prospect Theory), 인지-평가이론(Cognitive Evaluation Theory)</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>[지각된 혜택(실용적, 쾌락적, 상징적), 지각된 희생(기술 복잡성, 보안 위험성)] -&gt; [지각된 가치, 혁신저항] -&gt; [사용의도] -&gt; [실제사용] (조절변수: 디지털 피로도)</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>H1-1: 모바일기반 멤버십서비스의 실용적혜택은 지각된 가치에 정(+)의 영향을 미칠 것이다.
+H1-2: 모바일기반 멤버십서비스의 쾌락적혜택은 지각된 가치에 정(+)의 영향을 미칠 것이다.
+H1-3: 모바일기반 멤버십서비스의 상징적혜택은 지각된 가치에 정(+)의 영향을 미칠 것이다.
+H2-1: 모바일 기반의 멤버십의 지각된 희생요소인 기술적 복잡성은 지각된 가치에 부(-)의 영향을 미칠 것이다.
+H2-2: 모바일 기반의 멤버십의 지각된 희생 및 비용요소인 보안위험성은 지각된 가치에 부(-)의 영향을 미칠 것이다
+H3-1: 모바일기반 멤버십서비스의 실용적혜택은 혁신저항에 부(-)의 영향을 미칠 것이다.
+H3-2: 모바일기반 멤버십서비스의 쾌락적혜택은 혁신저항에 부(-)의 영향을 미칠 것이다.
+H3-3: 모바일기반 멤버십서비스의 상징적혜택은 혁신저항에 부(-)의 영향을 미칠 것이다.
+H4-1: 모바일 기반의 멤버십의 지각된 희생요소인 기술적 복잡성은 혁신저항에 정(+)의 영향을 미칠 것이다.
+H4-2: 모바일 기반의 멤버십의 지각된 희생 및 비용요소인 보안위험성은 혁신저항에 정(+)의 영향을 미칠 것이다.
+H5: 모바일 기반의 멤버십서비스의 지각된 가치는 사용의도에 정(+)의 영향을 미칠 것이다.
+H6: 모바일 기반의 멤버십서비스에 대한 혁신저항은 사용의도에 정(+)의 영향을 미칠 것이다. (원문 표기 오기재 수정: 부(-)의 영향)
+H7: 모바일 기반의 멤버십서비스의 지각된 가치와 실 사용에서 사용의도는 매개효과가 있을 것이다.
+H8: 모바일 기반의 멤버십서비스의 혁신저항과 지각된 가치는 사용의도의 매개효과가 있을 것이다.
+H9: 모바일 기반의 멤버십서비스의 혁신저항 및 사용의도 간 디지털 피로감은 조절효과가 있을 것이다.
+H10: 모바일 기반의 멤버십서비스의 사용의도와 실제 사용 간 디지털 피로감은 조절효과가 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>실용적 혜택, 쾌락적 혜택, 상징적 혜택, 기술 복잡성, 보안 위험성</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>실제 사용</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>지각된 가치, 혁신저항, 사용의도</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>디지털 피로도</t>
+        </is>
+      </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>모바일 멤버십 서비스의 혜택(실용적, 상징적)은 지각된 가치에 긍정적 영향을 미치며, 희생 요소(기술 복잡성, 보안 위험성)와 일부 혜택은 혁신저항에 유의한 영향을 미치는 것으로 나타났다. 또한 지각된 가치와 혁신저항은 사용의도에 유의한 영향을 미치며 이는 실제 사용으로 이어진다. 디지털 피로감은 혁신저항과 사용의도 간의 관계 및 사용의도와 실제 사용 간의 관계에서 조절효과를 발휘함을 실증하였다.</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>- Using mobile membership services can reduce the costs paid.
+(모바일 멤버십 서비스를 이용하는 것이 지불하는 비용을 줄일 수 있다.)
+- Using mobile membership services can save money.
+(모바일 멤버십 서비스를 이용하는 것이 돈을 아낄 수 있다.)
+- Using mobile membership services can make purchasing more practical.
+(모바일 멤버십 서비스를 이용하는 것이 구매를 더 실속 있게 할 수 있다.)
+- I can feel pleasure while using mobile membership services.
+(모바일 멤버십서비스를 이용하면서 즐거움을 느낄 수 있다.)
+- I can feel fun while using mobile membership services.
+(모바일 멤버십서비스를 이용하면서 재미를 느낄 수 있다)
+- I can feel a sense of fulfillment while using mobile membership services.
+(모바일 멤버십 서비스를 이용하면서 뿌듯함을 느낄 수 있다.)
+- I can feel like a smart consumer while using mobile membership services.
+(모바일 멤버십 서비스를 이용하면서 현명한 소비자로 느낄 수 있다.)
+- Mobile membership point services seem to respect me more.
+(모바일 멤버십포인트 서비스는 나를 더 존중해주는 것 같다.)
+- Mobile membership point services seem to treat me better.
+(모바일 멤버십포인트 서비스는 나를 더 대우해주는 것 같다.)
+- Mobile membership point services will make me socially recognized.
+(모바일 멤버십포인트 서비스는 사회적으로 인정받게 해 줄 것이다.)
+- I think the usage of mobile membership is difficult.
+(모바일 멤버십포인트 사용법이 어렵다고 생각한다.)
+- I think it is difficult to learn how to use mobile membership.
+(모바일 멤버십 사용 방법을 익히는 것이 어렵다고 생각한다.)
+- I think it will take a lot of effort to use mobile membership.
+(모바일 멤버십 사용하기 위해서는 큰 노력이 필요할 것이라 생각한다.)
+- I think it is difficult to use membership habitually.
+(나는 멤버십을 익숙하게 사용하기 어렵다고 생각한다.)
+- I think there is a possibility that my personal information may be leaked when signing up for and using mobile membership services.
+(나는 모바일 멤버십 서비스 가입과 사용시 나의 개인정보가 유출될 가능성이 있다고 생각한다.)
+- I am worried that my assets will be threatened by attacks such as hacking when signing up for and using mobile membership services.
+(나는 모바일 멤버십 서비스 가입과 사용시 해킹 등의 공격으로부터 자산이 위협을 받을까 걱정된다.)
+- I am concerned that transaction information may be leaked and used for hacking or crime when signing up for and using mobile membership services.
+(나는 모바일 멤버십 서비스 가입과 사용시 거래정보가 유출되고 해킹이나 범죄에 사용될 우려가 있을 것 같다.)
+- I think it will be difficult to control leaked personal information when signing up for and using mobile membership services.
+(나는 모바일 멤버십 서비스 가입과 사용시 유출된 개인정보에 대해 통제가 어려울 것으로 생각한다.)
+- I think the benefits gained compared to the costs incurred to use mobile membership will be higher.
+(나는 모바일 멤버십 사용하기 위해 들이는 비용 대비 얻는 혜택이 더 높을 것으로 생각한다)
+- I think the benefits gained compared to the effort incurred to use mobile membership will be higher.
+(나는 모바일 멤버십 사용하기 위해 들이는 노력 대비 얻는 혜택이 더 높을 것으로 생각한다.)
+- Overall, I think using the mobile membership I currently use provides me with great value.
+(전반적으로 현재 사용하고 있는 모바일 멤버십 이용은 나에게 훌륭한 가치를 제공한다고 생각한다.)
+- I have a sense of resistance to using mobile membership.
+(나는 모바일 멤버십 사용에 대해 거부감을 가지고 있다.)
+- I have anxiety about using mobile membership.
+(나는 모바일 멤버십 사용에 대해 불안감을 가지고 있다)
+- I do not want to use mobile membership.
+(나는 모바일 멤버십을 사용하고 싶지 않다.)
+- I am willing to oppose the use of mobile membership.
+(나는 모바일 멤버십 사용에 반대할 의향이 있다.)
+- I have no interest in using mobile membership.
+(나는 모바일 멤버십 사용에 관해 관심이 없다.)
+- I have the intention to continuously use mobile membership services.
+(나는 모바일 멤버십 서비스를 지속 사용할 의향이 있다)
+- If given the opportunity, I will continue to use mobile membership services.
+(나는 기회가 된다면 모바일 멤버십 서비스를 지속 사용할 것이다.)
+- I plan to continuously use mobile membership services.
+(나는 모바일 멤버십 서비스를 지속적으로 사용할 계획이 있다.)
+- I think mobile membership services are necessary.
+(나는 모바일 멤버십 서비스가 필요하다고 생각한다.)
+- I am willing to recommend mobile membership services to others.
+(나는 모바일 멤버십서비스를 다른 사람에게 추천할 의향이 있다.)
+- I am using mobile membership services.
+(나는 모바일 멤버십 서비스를 이용하고 있다.)
+- I am actually using and continuously using mobile membership services.
+(나는 모바일 멤버십서비스를 실제 이용하고 지속 이용중이다.)
+- I am regularly using mobile membership services.
+(나는 모바일 멤버십서비스를 정기적으로 이용하고 있다.)
+- I am willing to recommend mobile membership services to others.
+(나는 모바일 멤버십서비스를 다른 사람에게 추천할 의향이 있다.)
+- I intend to use mobile membership services whenever needed.
+(나는 모바일 멤버십서비스를 필요할 때마다 사용할 의사가 있다.)
+- There are times when I do not want to search for information anymore if excessive information search causes confusion in service use.
+(과도한 정보탐색으로 서비스이용 혼란을 느끼게 되면 더 이상 정보탐색을 하고 싶지 않을 때가 있다.)
+- There are times when I feel mentally very fatigued if excessive information search causes confusion in service use.
+(과도한 정보탐색으로 서비스이용 혼란을 느끼게 되면 정신적으로 매우 피로함을 느낄 때가 있다.)
+- There are times when I cannot judge what additional information to search for if confusion arises due to too much, similar, or ambiguous acquired information.
+(획득한 정보가 너무 많거나 유사 또는 모호한 정보들로 인해 혼란이 오면 어떤 정보를 추가적으로 탐색해야 하는지 판단이 서지 않을 때가 있다.)
+- There are times when I lose interest in using the service if confusion arises due to too much, similar, or ambiguous acquired information.
+(획득한 정보가 너무 많거나 유사 또는 모호한 정보들로 인해 혼란이 오면 서비스 이용에 흥미를 잃어버릴 때가 있다.)</t>
+        </is>
+      </c>
+      <c r="O922" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O922"/>
+  <dimension ref="A1:O930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73948,6 +73948,839 @@
         </is>
       </c>
     </row>
+    <row r="923">
+      <c r="A923" t="n">
+        <v>922</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>박지선</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>데이터 경제 활성화를 위한 개인정보 처리제도 개선 연구 - EU GDPR 검토를 바탕으로 한 동의제도 개선 및 동의 없는 개인정보 처리를 중심으로 -</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>이익형량론, EU GDPR 비교법적 분석, 브뤼셀 효과, 위험기반 접근법</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>[EU GDPR 검토] -&gt; [현행 한국 개인정보보호법 한계 분석] -&gt; [동의제도 개선 및 동의 없는 개인정보 처리/인공지능 학습 데이터 활용 법제 개선 방안 도출]</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>본 논문은 가설 중심의 실증 연구가 아닌 법학 석사학위 논문으로서, EU GDPR과 한국 개인정보보호법의 비교 분석을 통해 사전 동의제도의 한계를 극복하고 정당한 이익 및 과학적 연구 목적 등의 동의 없는 개인정보 처리 확대를 주장함</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>EU GDPR 법규정, 개인정보 처리 적법요건(정당한 이익, 과학적 연구 목적, 양립 가능한 목적 등), 가명정보 처리제도</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>데이터 경제 활성화, 개인정보 보호와 활용의 균형, 인공지능 학습 데이터 활용 합법화</t>
+        </is>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>현행 한국 개인정보보호법은 지나치게 사전 동의제도에 의존하여 형식적인 동의 피로를 야기하고 데이터 경제 활성화를 저해하므로, EU GDPR을 참고하여 사전 동의제도를 폐기 또는 완화하고 '옵트아웃(opt-out)' 제도 및 '목적 중심 동의제도'를 도입해야 함. 또한 정당한 이익 조항의 실질적 확대, 과학적 연구 및 통계 목적의 상업적 활용 포함, 가명정보 결합 주체 제한 완화, 인공지능 학습을 위한 공개된 개인정보의 합법적 활용 근거 마련이 필요함.</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O923" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="n">
+        <v>923</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>김나연</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>기부 메시지의 감정적 가치가 기부 의도에 미치는 영향 - 예상 감정의 매개 효과와 의사결정 성향의 조절 효과 -</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>서울대학교 대학원 경영학과 경영학석사 학위논문</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>부정적 상태 완화 모델(NSR), 공감-이타주의 가설, 기분 유지 가설, 쾌락적 조건성 가설, 조절초점 이론</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>[기부 메시지의 감정적 가치(IV)] -&gt; [예상 긍정 감정 / 예상 부정 감정(Mediator)] -&gt; [기부 의도(DV)] (의사결정 성향(Moderator))</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>H1: 기부 메시지의 감정적 가치(valence)는 서로 다른 예상 감정 경로를 통해 기부 의도에 영향을 미칠 것이다.
+H1a: 부정적 메시지 조건은 예상 부정(vs.긍정) 감정이 기부 의도에 더 큰 영향을 미칠 것이다.
+H1b: 긍정적 메시지 조건은 예상 긍정(vs.부정) 감정이 기부 의도에 더 큰 영향을 미칠 것이다.
+H2: 의사결정 성향은 예상 감정이 기부 의도에 미치는 영향을 조절할 것이다.
+H2a: 극대화(maximizing) 성향이 높은 경우, 예상 부정(vs.긍정) 감정이 기부 의도에 더 큰 영향을 미칠 것이다.
+H2b: 만족화(satisficing) 성향이 높은 경우, 예상 긍정(vs.부정) 감정이 기부 의도에 더 큰 영향을 미칠 것이다.
+H3: 의사결정 성향에 따라 기부 메시지의 감정적 가치가 기부 의도에 미치는 영향이 달라질 것이다.
+H3a: 극대화 성향이 높은 경우, 부정적 메시지 조건에서 기부 의도가 더 높을 것이다.
+H3b: 만족화 성향이 높은 경우, 긍정적 메시지 조건에서 기부 의도가 더 높을 것이다.</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>기부 메시지의 감정적 가치 (긍정적 메시지 vs. 부정적 메시지)</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>기부 의도</t>
+        </is>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>예상 긍정 감정, 예상 부정 감정</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>의사결정 성향 (극대화 성향 vs. 만족화 성향)</t>
+        </is>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>기부 메시지의 긍정적 가치는 예상 긍정 및 부정 감정을 통해 기부 의도에 완전 매개 효과를 보였으며, 긍정 메시지는 예상 긍정 감정이, 부정 메시지는 예상 부정 감정이 기부 의도에 더 강한 영향을 미쳤다. 또한 의사결정 성향에 따라 민감한 예상 감정의 차이가 나타나, 극대화 성향은 예상 부정 감정에, 만족화 성향은 예상 긍정 감정에 더 민감하게 반응하였다. 전반적으로 긍정적 메시지가 기부 유도에 더 효과적인 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>- If I donate to BonBon Food bank, I will feel… [excited / delighted / happy / glad / satisfied / proud / self-assured]
+(만약 내가 본본 푸드뱅크에 기부한다면, 나는… 느낄 것이다. [신나는 / 즐거운 / 행복한 / 기쁜 / 만족하는 / 자랑스러운 / 자신감 있는])
+- If I do not donate to BonBon Food bank, I will feel… [guilty / sad / depressed / worried / uncomfortable]
+(만약 내가 본본 푸드뱅크에 기부하지 않는다면, 나는… 느낄 것이다. [죄책감이 드는 / 슬픈 / 우울한 / 걱정스러운 / 불편한])
+- I don’t like having to settle for “good enough”.
+(나는 '충분히 좋은' 것에 안주하는 것을 좋아하지 않는다.)
+- I will wait for the best option, no matter how long it takes.
+(나는 아무리 시간이 오래 걸리더라도 최선의 선택지를 기다릴 것이다.)
+- I can’t come to a decision unless I have carefully considered all of my options.
+(나는 모든 선택지를 신중하게 고려하지 않으면 결정을 내릴 수 없다.)
+- I will usually continue shopping for an item until it reaches all of my criteria.
+(나는 보통 어떤 물품이 내 기준을 모두 충족할 때까지 쇼핑을 계속한다.)
+- When shopping, if I can’t find exactly what I’m looking for, I will continue to search for it.
+(쇼핑할 때 내가 찾던 것을 정확히 찾지 못하면, 계속해서 그것을 찾아 헤맬 것이다.)
+- If a store doesn’t have exactly what I’m shopping for, then I will go somewhere else.
+(만약 상점에 내가 찾던 물건이 정확히 없다면, 나는 다른 곳으로 갈 것이다.)
+- How interested are you in giving a donation to the charity?
+(당신은 이 자선단체에 기부하는 것에 얼마나 관심이 있습니까?)
+- To what extent would you consider giving a donation to the charity?
+(당신은 이 자선단체에 기부하는 것을 어느 정도 고려하고 있습니까?)
+- How likely would you be to give a donation to the charity?
+(당신이 이 자선단체에 기부할 가능성은 얼마나 됩니까?)</t>
+        </is>
+      </c>
+      <c r="O924" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="n">
+        <v>924</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>정희도</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>구매패턴기반 고객군집화를 통한 업종별 매출 예측 고도화</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>연세대학교 정보대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>고객 행동 분석 및 세분화 이론, 시계열 예측 이론</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>[인구통계학적 특성 및 구매패턴 시계열 데이터] -&gt; [DTW 기반 K-means 클러스터링 / K-modes 클러스터링] -&gt; [시계열 예측 모델 (SARIMA, LSTM, GRU)] -&gt; [업종별 매출 건수 예측 성능 비교]</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>H1: DTW기반 K-means클러스터링은 음식업 구매패턴 데이터를 기반으로 고객의 소비행동을 효과적으로 군집화하며, 이를 통해 매출건수 예측 모델의 성능을 높일 수 있다.
+H2: 음식업종에서 구매패턴기반 군집화와 인구통계학적 특성 기반 군집화의 예측 성능은 데이터 특성 및 군집화 방법론의 차이에 따라 상이한 결과를 나타낸다.</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>고객 군집화 기법 (DTW 기반 K-means 클러스터링, K-modes 클러스터링, 전체 데이터 비교군)</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>매출 건수 예측 정확도 (RMSE, MAE, DTW Distance)</t>
+        </is>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>본 연구는 DTW 기반 K-means 클러스터링을 활용하여 소비자의 인구통계학적 특성과 구매패턴 시계열 데이터를 통합 군집화한 결과, 단순 전체 데이터나 K-modes 클러스터링을 적용한 경우보다 매출 예측 정확도가 크게 향상됨을 입증하였다. 특히 일식회집, 주점, 중국음식 업종의 특정 군집에서 높은 예측 성능을 확인하였으며, 이를 바탕으로 소상공인이 실무에 활용할 수 있는 맞춤형 타겟 마케팅 전략과 시기별 대응 방안을 도출하였다.</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O925" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="n">
+        <v>925</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>李 浩 京 (이호경)</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>라이브 커머스 ‘사람-상품-장면’ 마케팅 특성이 구매의도에 미치는 영향 - 지각 신뢰 관점 -</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>성균관대학교 일반대학원 경영학과 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>S-O-R 모델(Stimulus-Organism-Response Model), 일치성 이론(Consistency Theory)</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>[라이브 커머스 마케팅 특성: 전문성, 상호작용성, 자기일치성, 진실성, 혜택성, 시각적 매력, 가시성] -&gt; [지각 신뢰: 스트리머 신뢰, 제품 신뢰] -&gt; [소비자 구매의도]</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>H1a: 라이브 커머스에서 스트리머의 전문성은 스트리머 신뢰에 긍정적인 영향을 줄 것이다.
+H1b: 라이브 커머스에서 스트리머의 전문성은 제품 신뢰에 긍정적인 영향을 줄 것이다.
+H2a: 라이브 커머스에서 스트리머의 상호작용성은 스트리머 신뢰에 긍정적인 영향을 미친다.
+H2b: 라이브 커머스에서 스트리머의 상호작용성은 제품 신뢰에 긍정적인 영향을 미친다.
+H3a: 라이브 커머스에서 소비자의 자기일치성은 스트리머 신뢰에 긍정적인 영향을 미친다.
+H3b: 라이브 커머스에서 소비자의 자기일치성은 제품 신뢰에 긍정적인 영향을 미친다.
+H4a: 라이브 커머스에서 제품의 진실성은 스트리머 신뢰에 긍정적인 영향을 미친다.
+H4b: 라이브 커머스에서 제품의 진실성은 제품 신뢰에 긍정적인 영향을 미친다.
+H5a: 라이브 커머스에서 제품의 혜택성은 스트리머 신뢰에 긍정적인 영향을 미친다.
+H5b: 라이브 커머스에서 제품의 혜택성은 제품 신뢰에 긍정적인 영향을 미친다.
+H6a: 라이브 커머스의 시각적 매력은 스트리머 신뢰에 긍정적인 영향을 미친다.
+H6b: 라이브 커머스의 시각적 매력은 제품 신뢰에 긍정적인 영향을 미친다.
+H7a: 라이브 커머스의 장면 가시성은 스트리머 신뢰에 긍정적인 영향을 미친다.
+H7b: 라이브 커머스의 장면 가시성은 제품 신뢰에 긍정적인 영향을 미친다.
+H8: 라이브 커머스에서 스트리머 신뢰는 제품 신뢰에 긍정적인 영향을 미친다.
+H9a: 라이브 커머스에서 스트리머 신뢰는 소비자의 구매의도에 긍정적인 영향을 미친다.
+H9b: 라이브 커머스에서 제품 신뢰는 소비자의 구매의도에 긍정적인 영향을 미친다.
+H10a~H15b: 스트리머 신뢰 및 제품 신뢰의 매개효과 가설들</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>라이브 커머스 마케팅 특성 (전문성, 상호작용성, 자기일치성, 진실성, 혜택성, 시각적 매력, 가시성)</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>소비자 구매의도</t>
+        </is>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>소비자 지각 신뢰 (스트리머 신뢰, 제품 신뢰)</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>실증분석 결과, 스트리머의 전문성, 상호작용성, 진실성, 시각적 매력은 스트리머 신뢰에 유의한 정(+)의 영향을 미쳤으며, 자기일치성, 진실성, 혜택성, 시각적 매력은 제품 신뢰에 유의한 정(+)의 영향을 미치는 것으로 나타났다. 또한 스트리머 신뢰와 제품 신뢰는 모두 소비자의 구매의도에 유의한 긍정적 영향을 미쳤으며, 지각 신뢰의 매개효과가 통계적으로 검증되었다.</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>- The streamer I watched has professional live-selling skills.
+(내가 시청한 스트리머는 전문적인 라이브 판매 기술을 가지고 있다.)
+- The streamer I watched has rich usage experience regarding the recommended products.
+(내가 시청한 스트리머는 추천 제품에 대한 풍부한 사용 경험을 가지고 있다.)
+- The streamer I watched possesses professional knowledge.
+(내가 시청한 스트리머는 전문적인 지식을 보유하고 있다.)
+- The streamer I watched maintains a good interactive relationship with viewers.
+(내가 시청한 스트리머는 시청자와 좋은 상호작용 관계를 유지한다.)
+- The broadcasting content of the streamer I watched enables me to actively participate.
+(내가 시청한 스트리머의 방송 내용은 내가 적극적으로 참여할 수 있게 한다.)
+- The broadcasting content of the streamer I watched arouses my interest.
+(내가 시청한 스트리머의 방송 내용은 내 흥미를 유발한다.)
+- The product types in the live broadcast fit me well.
+(라이브 방송의 제품 유형은 나에게 잘 맞는다.)
+- I like the personal style of the streamer in the live broadcast.
+(라이브 방송의 스트리머 개인 스타일이 마음에 든다.)
+- The personality of the streamer or brand covered in the live broadcast is similar to mine.
+(라이브 방송에서 다루는 스트리머 또는 브랜드의 성격은 나의 성격과 유사하다.)
+- I believe the quality and efficacy of the products introduced by the streamer are authentic.
+(나는 스트리머가 소개하는 상품의 품질과 효능이 진실하다고 믿는다.)
+- The streamer visually presents the product from various angles.
+(스트리머는 다양한 각도에서 제품을 시각적으로 보여준다.)
+- The streamer helps me understand the product more deeply during the product introduction process.
+(스트리머는 상품 소개 과정에서 내가 그 상품을 더 깊이 이해하도록 돕는다.)
+- I think the products in this live broadcast have high cost-performance.
+(나는 이 라이브 방송의 제품이 가성비가 높다고 생각한다.)
+- I think the discount margin in this live broadcast is large.
+(나는 이 라이브 방송에서의 할인 폭이 크다고 생각한다.)
+- I think I can buy products more cheaply through this live broadcast.
+(나는 이 라이브 방송을 통해 제품을 더 저렴하게 구매할 수 있다고 생각한다.)
+- The scene of the live broadcast is visually very attractive.
+(라이브 방송의 장면이 시각적으로 매우 매력적이다.)
+- The visual design of the live broadcast feels professional and high-end.
+(라이브 방송의 시각적 디자인은 전문적이고 고급스럽게 느껴진다.)
+- The overall screen composition of the live broadcast feels comfortable and pleasant.
+(라이브 방송의 전반적인 화면 구성은 편안하고 쾌적하게 느껴진다.)
+- The live broadcast intuitively shows the appearance and details of the products.
+(라이브 방송은 제품의 외관과 세부 사항을 직관적으로 보여준다.)
+- The product demonstration angle of the live broadcast facilitates the understanding of product functions.
+(라이브 방송의 제품 시연 각도는 제품 기능 이해를 용이하게 한다.)
+- I can clearly know the usage effect of the product through the live broadcast.
+(라이브 방송을 통해 제품의 사용 효과를 명확히 알 수 있다.)
+- I trust the information provided by the streamer in the broadcast.
+(나는 스트리머가 방송에서 제공하는 정보를 신뢰한다.)
+- I believe that the streamer considers the basic interests of buyers.
+(나는 스트리머가 구매자의 기본 이익을 고려한다고 믿는다.)
+- The streamer helps me understand the product more deeply during the process of introducing goods.
+(스트리머는 상품을 소개하는 과정에서 내가 제품을 더 깊이 이해하도록 돕는다.)
+- I believe the streamer has the ability to handle online transactions smoothly.
+(나는 스트리머가 온라인 거래를 원활히 처리할 능력이 있다고 믿는다.)
+- I believe the products and services recommended by the streamer are useful.
+(나는 스트리머가 추천하는 제품과 서비스가 유용하다고 믿는다.)
+- I believe the products sold in the live broadcast are genuine.
+(나는 라이브 방송에서 판매되는 제품이 정품이라고 믿는다.)
+- I think the quality of the products sold in the live broadcast is reliable.
+(나는 라이브 방송에서 판매되는 제품의 품질이 신뢰할 만하다고 생각한다.)
+- I believe the received product is the same as the one demonstrated in the broadcast.
+(나는 수령한 제품이 방송에서 시연된 제품과 동일하다고 믿는다.)
+- I believe I will be satisfied with the received product.
+(나는 수령한 제품에 만족할 것이라고 믿는다.)
+- I believe the product provides a complete after-sales guarantee service.
+(나는 제품이 완전한 사후보장 서비스를 제공한다고 믿는다.)
+- After watching the live broadcast, I consider purchasing the relevant product.
+(라이브 방송을 본 후, 나는 해당 제품을 구매할 것을 고려한다.)
+- After watching the live broadcast, I will recommend this product to others.
+(라이브 방송을 본 후, 나는 이 제품을 다른 사람에게 추천할 것이다.)
+- When needed, I have the intention to purchase directly through the live broadcast.
+(필요할 때, 나는 라이브 방송을 통해 직접 구매할 의향이 있다.)
+- If it is the same product, I prefer to purchase it in the live broadcast.
+(동일한 상품이라면, 나는 라이브 방송에서 구매하는 것을 선호한다.)
+- In the future, I will purchase goods more frequently through e-commerce live broadcasts.
+(앞으로 나는 전자상거래 라이브 방송을 통해 더 자주 상품을 구매할 것이다.)</t>
+        </is>
+      </c>
+      <c r="O926" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="n">
+        <v>926</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>최정윤</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>디지털 컨버전스 제품 외관의 심미성이 소비자 구매 관심에 미치는 영향에 관한 실증연구: 소비자 미적 반응과 기대 기능성의 매개 효과와 심미적 성향(CVPA)의 조절 효과를 중심으로</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 박사학위 논문</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>예술 실험 미학(New Experimental Aesthetics), 기술수용모델(Technology Acceptance Model), 감정 전이 이론(Affect transfer theory), 이중 처리 과정 이론(Dual process theory)</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>[제품 외관의 심미성(참신성, 균형성, 조화성)] -&gt; [소비자 미적 반응 / 제품의 기대 기능성(유용성, 혁신성, 용이성)] -&gt; [소비자 구매 관심] (조절변수: 소비자의 심미적 성향)</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>H1-1: 디지털 컨버전스 제품 외관의 참신성이 높을수록 소비자 구매 관심이 더욱 클 것이다.
+H1-2: 디지털 컨버전스 제품 외관의 균형성이 높을수록 소비자 구매 관심이 더욱 클 것이다.
+H1-3: 디지털 컨버전스 제품 외관의 조화성이 높을수록 소비자 구매 관심이 더욱 클 것이다.
+H2-1: 디지털 컨버전스 제품 외관의 참신성이 높을수록 소비자 미적 반응이 높을 것이다.
+H2-2: 디지털 컨버전스 제품 외관의 균형성이 높을수록 소비자 미적 반응이 높을 것이다.
+H2-3: 디지털 컨버전스 제품 외관의 조화성이 높을수록 소비자 미적 반응이 높을 것이다.
+H3-1: 소비자의 미적 반응이 높을수록 소비자 구매 관심이 더욱 클 것이다.
+H4-1: 소비자의 심미적 성향은 디지털 컨버전스 제품 외관의 참신성과 소비자 미적 반응을 조절할 것이다.
+H4-2: 소비자의 심미적 성향은 디지털 컨버전스 제품 외관의 균형성과 소비자 미적 반응을 조절할 것이다.
+H4-3: 소비자의 심미적 성향은 디지털 컨버전스 제품 외관의 조화성과 소비자 미적 반응을 조절할 것이다.
+H5-1: 디지털 컨버전스 제품 외관의 참신성과 소비자 구매 관심을 소비자 미적 반응이 매개할 것이다.
+H5-2: 디지털 컨버전스 제품 외관의 균형성과 소비자 구매 관심을 소비자 미적 반응이 매개할 것이다.
+H5-3: 디지털 컨버전스 제품 외관의 조화성과 소비자 구매 관심을 소비자 미적 반응이 매개할 것이다.
+H6-1: 디지털 컨버전스 제품 외관의 참신성과 소비자 구매 관심 간의 관계에서 소비자의 심미적 성향과 소비자 미적 반응은 조절된 매개를 할 것이다.
+H6-2: 디지털 컨버전스 제품 외관의 균형성과 소비자 구매 관심 간의 관계에서 소비자의 심미적 성향과 소비자 미적 반응은 조절된 매개를 할 것이다.
+H6-3: 디지털 컨버전스 제품 외관의 조화성과 소비자 구매 관심 간의 관계에서 소비자의 심미적 성향과 소비자 미적 반응은 조절된 매개를 할 것이다.
+H7-1: 디지털 컨버전스 제품 외관의 참신성이 높을수록 기대 유용성이 높을 것이다.
+H7-2: 디지털 컨버전스 제품 외관의 균형성이 높을수록 기대 유용성이 높을 것이다.
+H7-3: 디지털 컨버전스 제품 외관의 조화성이 높을수록 기대 유용성이 높을 것이다.
+H7-4: 디지털 컨버전스 제품 외관의 참신성이 높을수록 기대 혁신성이 높을 것이다.
+H7-5: 디지털 컨버전스 제품 외관의 균형성이 높을수록 기대 혁신성이 높을 것이다.
+H7-6: 디지털 컨버전스 제품 외관의 조화성이 높을수록 기대 혁신성이 높을 것이다.
+H7-7: 디지털 컨버전스 제품 외관의 참신성이 높을수록 기대 용이성이 높을 것이다.
+H7-8: 디지털 컨버전스 제품 외관의 균형성이 높을수록 기대 용이성이 높을 것이다.
+H7-9: 디지털 컨버전스 제품 외관의 조화성이 높을수록 기대 용이성이 높을 것이다.
+H8-1: 기대 유용성이 높을수록 소비자 구매 관심이 높을 것이다.
+H8-2: 기대 혁신성이 높을수록 소비자 구매 관심이 높을 것이다.
+H8-3: 기대 용이성이 높을수록 소비자 구매 관심이 높을 것이다.
+H9-1: 디지털 제품 외관의 참신성과 소비자 구매 관심을 기대 유용성이 매개할 것이다.
+H9-2: 디지털 제품 외관의 균형성과 소비자 구매 관심을 기대 유용성이 매개할 것이다.
+H9-3: 디지털 제품 외관의 조화성과 소비자 구매 관심을 기대 유용성이 매개할 것이다.
+H9-4: 디지털 제품 외관의 참신성과 소비자 구매 관심을 기대 혁신성이 매개할 것이다.
+H9-5: 디지털 제품 외관의 균형성과 소비자 구매 관심을 기대 혁신성이 매개할 것이다.
+H9-6: 디지털 제품 외관의 조화성과 소비자 구매 관심을 기대 혁신성이 매개할 것이다.
+H9-7: 디지털 제품 외관의 참신성과 소비자 구매 관심을 기대 용이성이 매개할 것이다.
+H9-8: 디지털 제품 외관의 균형성과 소비자 구매 관심을 기대 용이성이 매개할 것이다.
+H9-9: 디지털 제품 외관의 조화성과 소비자 구매 관심을 기대 용이성이 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>제품 외관의 심미성 (참신성, 균형성, 조화성)</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>소비자 구매 관심</t>
+        </is>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>소비자 미적 반응, 제품의 기대 기능성 (기대 유용성, 기대 혁신성, 기대 용이성)</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>소비자의 심미적 성향 (CVPA)</t>
+        </is>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>디지털 컨버전스 제품 외관의 심미성 요소 중 조화성과 참신성은 소비자 구매 관심에 유의한 정적(+) 영향을 미치는 반면 균형성은 유의미한 영향을 미치지 않는 것으로 나타났다. 또한 참신성, 균형성, 조화성 모두 소비자 미적 반응에 정적(+) 영향을 미쳤으며, 소비자 미적 반응은 구매 관심에 강력한 매개 역할을 수행함을 확인하였다. 소비자의 심미적 성향은 참신성과 조화성이 미적 반응에 미치는 영향을 조절하는 것으로 나타났으나 균형성과의 관계에서는 조절효과가 유의하지 않았다. 아울러 제품 외관의 심미성은 기대 유용성, 기대 혁신성, 기대 용이성과 같은 기대 기능성을 매개하여 소비자 구매 관심에 긍정적인 영향을 미치는 것으로 검증되었다.</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>- The appearance of this digital convergence product looks completely new compared to existing products.
+(이 디지털 컨버전스 제품의 외관은 기존 제품과 비교하여 완전히 새롭게 보인다.)
+- The design elements of this product are original and unique.
+(이 제품의 디자인 요소는 독창적이고 독특하다.)
+- The overall exterior of this product provides a fresh visual feeling.
+(이 제품의 전체적인 외관은 신선한 시각적 느낌을 제공한다.)
+- The visual elements of this product are well-balanced without leaning to one side.
+(이 제품의 시각적 요소들은 어느 한쪽으로 치우치지 않고 잘 균형 잡혀 있다.)
+- The symmetry and structure of the product exterior appear stable and steady.
+(제품 외관의 대칭성과 구조는 안정적이고 견고해 보인다.)
+- The visual weight of this product exterior feels evenly distributed.
+(이 제품 외관의 시각적 무게감은 고르게 분산되어 느껴진다.)
+- The shape, color, and texture of this product exterior harmonize very well together.
+(이 제품 외관의 형태, 색상, 질감이 서로 매우 조화롭게 어우러져 있다.)
+- The design elements of this product fit together without any awkwardness.
+(이 제품의 디자인 요소들은 어색함 없이 서로 잘 어울린다.)
+- The overall visual composition of this product exterior gives a unified and smooth impression.
+(이 제품 외관의 전반적인 시각적 구성은 통일감 있고 매끄러운 인상을 준다.)
+- Looking at the exterior of this product makes me feel visually pleased.
+(이 제품의 외관을 바라보는 것만으로도 시각적인 즐거움을 느낀다.)
+- The exterior of this product is attractive and beautiful.
+(이 제품의 외관은 매력적이고 아름답다.)
+- I feel a positive emotional response when viewing the design of this product.
+(이 제품의 디자인을 볼 때 긍정적인 감정적 반응이 느껴진다.)
+- The visual appearance of this product gives me a sense of aesthetic satisfaction.
+(이 제품의 시각적 외관은 내게 미적 만족감을 준다.)
+- I am happy and satisfied to see such a well-designed product exterior.
+(이처럼 잘 디자인된 제품 외관을 보게 되어 기쁘고 만족스럽다.)
+- The aesthetic impression of this product creates a wonderful sensory experience for me.
+(이 제품의 미적 인상은 나에게 훌륭한 감각적 경험을 창조한다.)
+- Owning a product with a visually attractive design is important to me.
+(시각적으로 매력적인 디자인을 가진 제품을 소유하는 것은 내게 중요하다.)
+- I like to buy products that have superior visual aesthetics.
+(나는 뛰어난 시각적 심미성을 가진 제품을 구매하는 것을 좋아한다.)
+- A product's aesthetic design plays a major role in my life quality.
+(제품의 미적 디자인은 내 삶의 질에 중요한 역할을 한다.)
+- I have a strong appreciation for fine product aesthetics compared to others.
+(나는 다른 사람들보다 뛰어난 제품 미적 감식을 가지고 있다.)
+- I can easily distinguish between products with good aesthetics and bad aesthetics.
+(나는 심미성이 좋은 제품과 나쁜 제품을 쉽게 구별할 수 있다.)
+- I pay close attention to the visual details and style of products.
+(나는 제품의 시각적 세부 사항과 스타일에 깊은 주의를 기울인다.)
+- I strongly react to beautiful product designs when I first encounter them.
+(나는 아름다운 제품 디자인을 처음 접할 때 강하게 반응한다.)
+- Beautiful product exteriors evoke strong feelings and excitement in me.
+(아름다운 제품 외관은 나에게 강한 감정과 설렘을 불러일으킨다.)
+- I am easily moved by the aesthetic appeal of a well-designed product.
+(나는 잘 디자인된 제품의 미적 호소력에 쉽게 감동한다.)
+- Using this product is expected to be very useful for my daily life.
+(이 제품을 사용하는 것은 나의 일상생활에 매우 유용할 것으로 기대된다.)
+- This product is anticipated to enhance my task performance and efficiency.
+(이 제품은 나의 과제 수행 능력과 효율성을 향상시킬 것으로 예상된다.)
+- I expect this product to provide practical benefits when I use it.
+(나는 이 제품을 사용할 때 실질적인 혜택을 제공할 것으로 기대한다.)
+- This product looks much more innovative compared to traditional products.
+(이 제품은 전통적인 제품과 비교하여 훨씬 더 혁신적으로 보인다.)
+- I expect this product to incorporate advanced and novel technological concepts.
+(나는 이 제품이 진보하고 참신한 기술적 개념을 통합할 것으로 기대한다.)
+- The design of this product implies a high level of technological advancement.
+(이 제품의 디자인은 높은 수준의 기술적 진보를 암시한다.)
+- Using this product is expected to be easy and effortless.
+(이 제품을 사용하는 것은 쉽고 힘들이지 않을 것으로 기대된다.)
+- I anticipate that learning to operate this product will be simple and straightforward.
+(나는 이 제품의 조작법을 배우는 것이 단순하고 직관적일 것이라고 예상한다.)
+- The exterior design suggests that the product will be user-friendly and convenient.
+(외관 디자인은 이 제품이 사용자 친화적이고 편리할 것임을 시사한다.)
+- I am very interested in purchasing this product.
+(나는 이 제품을 구매하는 데 매우 관심이 많다.)
+- I would actively consider buying this product in the near future.
+(나는 가까운 미래에 이 제품을 구매하는 것을 적극적으로 고려할 것이다.)
+- My intention to purchase this product is high based on its appearance.
+(그 외관을 바탕으로 이 제품을 구매하고자 하는 나의 의도는 높다.)</t>
+        </is>
+      </c>
+      <c r="O927" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="n">
+        <v>927</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>유지아</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>디지털 창작환경 변화에 따른 공정이용 제도의 재설계</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 법학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>공정이용 이론, 3단계 테스트 이론, 변형적 이용 이론</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>[디지털 창작환경의 변화(밈, 숏폼, 리액션 비디오)] -&gt; [공정이용 4요소(변형성, 필요 최소 사용, 시장 대체성, 절차적 공정성)의 재구성 및 유형별 적용] -&gt; [플랫폼 집행 구조 개선 및 공정이용 자율평가 가이드라인 제정]</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>H1: 디지털 창작물의 특성에 맞추어 재구성된 공정이용 4요소(변형성, 필요 최소 사용, 시장 대체성, 절차적 공정성)는 기존의 법적 불확실성을 해소하고 예측 가능성을 높인다.
+H2: 밈, 숏폼, 리액션 비디오 등 신유형 디지털 창작물은 각 유형의 기능과 특성에 따라 차별화된 공정이용 판단 기준이 적용되어야 한다.
+H3: 플랫폼의 자동 탐지, 필터링, 그리고 이의제기 절차의 개선은 사후적 법원 판단에 의존하는 한계를 보완하고 공정이용의 실효성을 확보한다.</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>디지털 창작환경의 변화 (밈, 숏폼, 리액션 비디오의 확산)</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>공정이용 제도의 재설계 및 실효성 확보 (판단 기준 정립, 플랫폼 절차 공정성 제고)</t>
+        </is>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>1. 밈, 숏폼, 리액션 비디오와 같은 디지털 창작물은 전통적인 인용 규범으로는 포섭하기 어려운 특성을 가지므로, 일반조항인 공정이용 제도를 통해 규율할 필요가 있다.
+2. 미국의 4요소와 국제조약상 3단계 테스트를 결합한 국내 저작권법 제35조의5는 디지털 환경에 맞추어 ‘변형성, 필요 최소 사용, 시장 대체성, 절차적 공정성’의 4대 축으로 재구성되어야 한다.
+3. 법원의 사후적 판단뿐만 아니라 플랫폼의 자동 탐지, 필터링, 이의제기 절차 등 기술적 집행 구조의 공정성을 확보하는 것이 공정이용의 실효성을 높이는 핵심 요건이다.
+4. 밈(추가형·합성형·변형형·반응형·복합형), 숏폼(재편집형·상황 설명형·댓글 모음형·사진 나열형), 리액션 비디오(단순 시청 반응형·비평 해설 중심형·변형 가공형) 등 세부 유형별로 가중치와 판단 기준을 달리 적용해야 한다.</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O928" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="n">
+        <v>928</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>한영아</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>기업지배구조 개선 및 금융시장 발전에 대한 연구: 인적분할을 통한 지주회사 전환의 이론적 고찰, 사례, 실증 연구 및 한국 펀드시장 발전사</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 박사학위 논문</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>조절초점이론, 피라미드식 소유구조 이론, 지배주주와 소수주주의 이해상충 이론</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>[인적분할 및 지주회사 전환 발표 및 이벤트] -&gt; [지배주주와 소수주주의 이질적 공개매수 응답 (이해상충)] -&gt; [지배주주의 지주회사 지분율 상승 및 의결권 지배력 강화 / 소수주주의 수익률 차이 (CAR)]</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>H1: 지주회사 전환을 위한 공개매수 시, 같은 조건하에서도 지배주주와 소수주주는 상이한 응답률을 보일 것이다.
+H2: 지주회사 전환 과정에서, 공개매수 종료 후 지주회사에 대한 지배주주(최대주주)의 지분율은 전환 이전에 비해 유의하게 증가할 것이다.
+H3: 공개매수 이후 사업자회사에 대한 지배주주의 직접적 지분율은 감소하나, 실질적 의결권 지배력을 나타내는 지주회사와 지배주주 합산 지분율은 확대되거나 적어도 유지될 것이다.
+H4: 공개매수 시 매수에 응하는 경우와 응하지 않는 경우 수익률에는 차이가 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>지주회사 전환을 위한 인적분할 및 공개매수 참여 여부 (지배주주 vs 소수주주)</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>공개매수 응답률, 지배주주 지분율 변화, 의결권 영향력, 누적초과수익률(CAR)</t>
+        </is>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>인적분할 후 공개매수를 통한 지주회사 전환 과정에서 지배주주의 평균 응답률은 65.7%인 반면 소수주주의 응답률은 5.7%에 그쳐 양 집단 간 심각한 이해상충이 실증적으로 확인되었다. 공개매수 결과 지배주주의 지주회사 지분율은 33.4%에서 53.9%로 크게 상승하여 지배력이 강화되었고, 사업회사에 대한 직접 지분율은 하락했으나 합산 의결권 지배력은 오히려 증가하여 소유-지배 괴리가 확대되었다. 또한 공개매수에 응하여 지주회사 신주를 수령한 그룹은 응하지 않은 그룹에 비해 30영업일 동안 유의하게 낮은 누적초과수익률(CAR)을 기록하였다.</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O929" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="n">
+        <v>929</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O930" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O930"/>
+  <dimension ref="A1:O931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74781,6 +74781,81 @@
         </is>
       </c>
     </row>
+    <row r="931">
+      <c r="A931" t="n">
+        <v>930</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O931" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O931"/>
+  <dimension ref="A1:O947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74856,6 +74856,1665 @@
         </is>
       </c>
     </row>
+    <row r="932">
+      <c r="A932" t="n">
+        <v>931</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>김세훈</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>보험회사의 고객을 위한 부가가치서비스(Value-Added Service) 제공에 관한 연구</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>연세대학교 경제대학원 금융보험전공 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>거래비용이론(Transaction Cost Theory), 유인구조이론(Incentive Structure Theory), 정보경제학이론(Information Economics Theory), 고객생애가치이론(Customer Lifetime Value Theory), 네트워크 외부성이론(Network Externality Theory), 플랫폼이론(Platform Theory)</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>[독립변수: 부가가치서비스(VAS) 제공 및 안내] -&gt; [매개변수: 고객 인식 및 선호도] -&gt; [종속변수: 보험 가입 의사결정, 계약 유지율, 추천 의향]</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>H1: 보험회사가 제공하는 부가가치서비스에 대해 많은 고객이 인식하고 있으며 이용자가 많을 것이다.
+H2: 보험회사가 제공하는 부가가치서비스에 대해 많은 고객이 인식하지 못하고 있으며, 이용률도 낮을 것이다.</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>부가가치서비스(VAS) 제공 및 안내 현황 (건강관리서비스, 생활서비스 등)</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>고객의 서비스 인지도, 이용 경험, 서비스 선호도, 보험 가입 의사결정 영향, 보험 계약 유지 영향, 추천 의향</t>
+        </is>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>1. 보험회사의 적극적인 서비스 제공에도 불구하고, 고객의 부가가치서비스 인지도(77.6%가 모르고 있음)와 이용률(89.3%가 이용 경험 없음)은 매우 저조한 것으로 나타남.
+2. 이는 보험회사 및 보험판매인의 안내 및 홍보 부족(57.3%가 가입 후 안내 못 받음, 70.3%가 판매인에게 설명 못 들음)에 기인함.
+3. 그럼에도 불구하고 고객의 74%는 부가가치서비스가 실질적으로 도움이 될 것이라고 긍정적으로 평가함.
+4. 가장 선호하는 서비스는 건강관리 정보 및 서비스(53.7%)이며, 세부 건강관리 항목 중에서는 건강검진 우대서비스(67%)와 주요 병원 예약서비스(42%)를 선호함.
+5. 부가가치서비스는 향후 보험 가입(43.3%), 계약 유지(51%), 주변 추천(52%)에 긍정적인 영향을 미치는 것으로 분석되어, 인지도 제고를 위한 체계적인 홍보 및 판매인 교육이 시급함.</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>1. What is your gender?
+(고객님의 성별은 어떻게 되시나요?)
+2. What is your age group?
+(고객님의 연령대는 어떻게 되시나요?)
+3. What is your current occupation?
+(현재 고객님의 직업은 무엇인가요?)
+4. What is your current residential area?
+(현재 고객님의 거주지역은 어디인가요?)
+5. Have you ever purchased an insurance product as a policyholder, or are you currently enrolled in one?
+(고객님은 본인이 계약자로 보험상품을 가입했거나, 현재 보험상품에 가입하고 있으신 가요?)
+6. Through which channel do you obtain information about insurance products?
+(보험상품에 관한 정보는 어떤 채널을 통해 얻고 계신가요?)
+7. Have you ever directly visited an insurance company's website?
+(보험회사의 홈페이지를 직접 방문해 보신 경험이 있으신 가요?)
+8. Are you aware of the value-added services provided by insurance companies to policyholders?
+(보험회사에서 보험 가입자에게 제공하는 부가서비스에 대해 알고 계시나요?)
+9. Have you ever used a value-added service provided by an insurance company?
+(보험회사에서 제공하는 부가서비스를 이용해 보신 경험이 있으신 가요?)
+10. What kind of value-added services do you think would be helpful if provided by an insurance company?
+(보험회사에서 부가서비스를 제공할 경우 어떠한 서비스가 도움이 된다고 생각하시나요?)
+11. Insurance companies provide various health management services to customers for free. Which of the following health management services do you think is most necessary?
+(보험회사들은 고객에게 무료로 다양한 건강관리 서비스를 제공하고 있습니다. 다음 중 건강관리서비스에 가장 필요하다고 생각하는 서비스는 무엇인가요?)
+12. Regarding the service items in Question 11, do you think the value-added services provided by insurance companies will be of practical help to your health management or daily life?
+((11 번) 질문의 서비스 항목과 관련하여 보험회사에서 제공하는 부가서비스가 고객님에게 실질적인 건강관리나 일상생활에 도움이 될 것이라고 생각하시나요?)
+13. What is your opinion on services that provide health management by accessing your smartphone based on the latest IT technology?
+(최신 IT 기술을 기반으로 고객님의 스마트폰에 접속하여 건강관리를 제공하는 서비스에 대한 고객님의 의견은 어떠신 가요?)
+14. Do you intend to use the value-added services provided by insurance companies?
+(보험회사에서 제공하는 부가서비스를 이용할 의사가 있으신 가요?)
+15. When purchasing an insurance product, do you think the availability or content of value-added services affects your decision to sign up?
+(보험상품을 가입할 때 부가서비스 제공 여부나 부가서비스 내용이 보험 가입 결정에 영향이 있다고 생각하시나요?)
+16. After purchasing insurance, do you think the availability or content of value-added services affects your decision to maintain the insurance contract?
+(보험을 가입한 후에 부가서비스 제공 여부나 부가서비스 내용에 따라 보험 계약을 유지하는데 미치는 영향이 있다고 생각하시나요?)
+17. After purchasing an insurance product, have you ever received information about value-added services from the insurance company through verbal explanations by an insurance planner, guides, emails, or text messages?
+(보험상품을 가입한 후에 보험회사로부터 부가서비스에 대한 안내를 보험설계사를 통한 구두설명, 안내장, 이메일, 문자 등의 방법을 통해 안내를 받으신 적이 있으신 가요?)
+18. When purchasing an insurance product or receiving consultation, have you ever received information about the value-added services provided by the insurance company from an insurance sales consultant?
+(보험상품을 가입할 때 또는 보험상품 상담을 받을 때 보험 판매 상담자로부터 보험회사에서 제공하는 부가서비스에 대한 안내를 받으신 적이 있으신 가요?)
+19. If you are satisfied with the value-added services provided by the insurance company, would you be willing to recommend the company's value-added services to others around you?
+(고객님이 보험회사가 제공하는 부가서비스에 대해 만족하신다면 다른 주변 사람에게 해당 보험회사의 부가서비스를 소개 추천하실 의사가 있으신 가요?)</t>
+        </is>
+      </c>
+      <c r="O932" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="n">
+        <v>932</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>이서주</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>밈 마케팅의 역설 - 밈 마케팅의 기대 불일치가 소비자 태도에 미치는 영향 -</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>서울대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>기대 불일치 이론(Expectancy Disconfirmation Theory), 브랜드 관계 규범 이론(Brand Relationship Norms Theory), 스키마 이론(Schema Theory)</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>[IV: 밈 사용] -&gt; [Mediator 1: 기대 불일치] -&gt; [Mediator 2: 광고 태도] -&gt; [DV: 브랜드 태도] (조절변수: 브랜드 친숙도)</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>H1: 광고에서 밈 사용은 브랜드 태도에 부정적 영향을 미친다.
+H2: 밈 사용이 브랜드에 대한 호감도에 미치는 영향은 기대 불일치(expectancy violations)와 광고 태도를 통해 단계적으로 매개된다.
+H3: 밈 사용이 기대 불일치에 미치는 효과는 브랜드 친숙도가 높을수록 강화된다.</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>밈 사용 여부 (사용 vs. 비사용)</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>브랜드 태도</t>
+        </is>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>기대 불일치, 광고 태도</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>브랜드 친숙도</t>
+        </is>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>1. 밈이 사용된 광고는 밈이 사용되지 않은 광고에 비해 브랜드 태도를 유의하게 저하시켰다.
+2. 밈 사용은 기대 불일치를 증가시키고, 높아진 기대 불일치는 광고 태도를 악화시키며, 부정적으로 형성된 광고 태도가 다시 브랜드 태도를 저하시키는 순차적 매개 경로가 확인되었다.
+3. 브랜드 친숙도는 밈 사용이 기대 불일치와 광고 태도를 거쳐 브랜드 태도에 미치는 부정적 영향을 강화하는 조절효과를 보였다.</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>- The advertising copy used by the brand in this advertisement feels like a meme.
+(이 광고에서 브랜드가 사용하는 광고 문구가 밈처럼 느껴진다.)
+- The wording of this advertisement felt informal and meme-like.
+(이 광고의 문구는 비격식적이고 밈처럼 느껴졌다.)
+- The advertising copy used by the brand looked like slang of the younger generation.
+(브랜드가 사용하는 광고 문구는 젊은 층의 유행어처럼 보였다.)
+- I have heard of this brand before.
+(이 브랜드 이름을 들어본 적이 있다.)
+- When I see this brand's logo or visual elements, I immediately know what brand it is.
+(이 브랜드의 로고나 시각 요소를 보면 어떤 브랜드인지 바로 알겠다.)
+- I feel that I know a lot about this brand.
+(나는 이 브랜드에 대해 잘 안다고 느낀다.)
+- Overall, this brand is familiar to me.
+(전반적으로, 이 브랜드는 나에게 익숙하다(친숙하다).)
+- This is the kind of post this brand would normally put up.
+(이 브랜드가 평소에 올릴 것 같은 게시물이다.)
+- It is appropriate for this brand to talk in this way.
+(이 브랜드가 이런 식으로 말하는 것은 적절하다.)
+- This post fits well with this brand image.
+(이 게시물은 이 브랜드 이미지랑 잘 어울린다.)
+- The tone of this post/advertisement was different from what I normally expect from this brand.
+(이번 게시물/광고의 말투는 내가 이 브랜드에게서 보통 기대하는 말투와는 달랐다.)
+- Overall, I like the corresponding advertisement.
+(전반적으로 해당 광고에 호감이 간다.)
+- I am satisfied with this advertisement.
+(본 광고에 마음에 든다.)
+- I like the corresponding advertisement.
+(나는 해당 광고가 좋다.)
+- Overall, I am positive about the brand featured in the advertisement.
+(나는 전반적으로 광고에 나오는 브랜드에 긍정적이다.)
+- I like the brand in this advertisement.
+(나는 본 광고의 브랜드가 좋다.)
+- I am favorable toward the brand featured in this advertisement.
+(나는 본 광고에 나오는 브랜드에 호의적이다.)
+- People expect me to say funny things.
+(사람들은 내가 웃긴 말을 하기를 기대합니다.)
+- I can make people laugh with what I say.
+(나는 내가 하는 말로 사람들을 웃게 만들 수 있습니다.)
+- I often come up with witty remarks.
+(나는 종종 재치 있는 말을 떠올립니다.)
+- I am good at telling jokes or funny stories.
+(나는 농담이나 재미있는 이야기를 잘합니다.)
+- People say I am witty.
+(사람들은 나를 재치 있다고 말합니다.)
+- I often feel the urge to make other people laugh.
+(나는 종종 다른 사람들을 웃게 만들고 싶은 욕구를 느낍니다.)
+- I am a person who likes humor.
+(나는 유머를 좋아하는 사람입니다.)</t>
+        </is>
+      </c>
+      <c r="O933" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="n">
+        <v>933</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>김유진</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>리타게팅 광고에서 해석수준과 인지된 개인화가 광고효과에 미치는 영향 : 인지된 유용성과 인지된 침입성의 매개효과 중심으로</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>해석수준이론, 기술수용모델(TAM)</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>[독립변수: 해석수준, 조절변수: 인지된 개인화] -&gt; [매개변수: 인지된 유용성 / 인지된 침입성] -&gt; [종속변수: 광고효과(클릭의도, 구매의도)]</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>H1. 리타게팅 광고 메시지에 대한 해석수준(구체적/추상적)에 따라 광고효과가 다르게 나타날 것이다.
+H2. 리타게팅광고의 해석수준에 따라 매개된 인지된 유용성이 광고 효과에 어떻게 나타나는가?
+H3. 리타게팅광고에서 느끼는 해석수준에 따라서 매개된 침입성이 광고 효과에 어떻게 나타나는가?
+H4. 리타게팅 광고에 대한 해석수준이 매개된 인지된 유용성과 인지된 침입성과 광고효과에 미치는 영향을 인지된 개인화가 조절하는가?</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>해석수준(구체적/추상적)</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>광고효과(클릭의도, 구매의도)</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>인지된 유용성, 인지된 침입성</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>인지된 개인화</t>
+        </is>
+      </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>구체적 해석수준과 인지된 개인화가 높을수록 인지된 유용성을 매개로 하여 광고효과가 유의하게 증가하였으나, 인지된 침입성의 경우 해석수준에 의해 유의한 영향을 받지 않는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>- 빨간 글씨를 봤을 때 리타게팅 광고가 구체적인 정보를 제공한다.
+(When looking at the red text, the retargeting advertisement provides concrete information.)
+- 빨간 글씨를 봤을 때 리타게팅 광고가 나한테 필요한 정보를 준다.
+(When looking at the red text, the retargeting advertisement gives me the necessary information.)
+- 빨간 글씨를 봤을 때 리타게팅 광고의 정보가 나한테 실용적이다.
+(When looking at the red text, the information in the retargeting advertisement is practical to me.)
+- 빨간 글씨를 봤을 때, 리타게팅 광고의 정보가 나하고 관련이 깊다고 느낀다.
+(When looking at the red text, I feel that the information in the retargeting advertisement is closely related to me.)
+- 파란글씨를 볼 때 리타게팅 광고는 내가 필요로 하는 정보를 제공한다.
+(When looking at the blue text, the retargeting advertisement provides the information I need.)
+- 파란글씨를 볼 때 리타게팅 광고가 내 필요에 맞는 추천을 해준 것으로 보여진다.
+(When looking at the blue text, it appears that the retargeting advertisement provides recommendations tailored to my needs.)
+- 파란글씨를 볼 때 리타게팅 광고는 내가 궁금한 정보에 맞게 개인화 되어 있다고 보여진다.
+(When looking at the blue text, the retargeting advertisement appears to be personalized according to the information I am curious about.)
+- 파란글씨를 볼 때 나의 상황에 맞춰서 리타게팅 광고가 제시된 거 같다.
+(When looking at the blue text, it seems that the retargeting advertisement was presented in line with my situation.)
+- 내가 본 리타게팅 광고의 정보는 전반적으로 나에게 유용한 정보를 제공한다.
+(Overall, the information in the retargeting advertisement I saw provides useful information to me.)
+- 내가 본 리타게팅 광고의 정보는 나의 상황에 맞춰서 제공한다.
+(The information in the retargeting advertisement I saw is provided tailored to my situation.)
+- 내가 본 리타게팅 광고의 정보는 필요했던 정보를 얻기까지 들이는 수고와 시간을 덜어준다.
+(The information in the retargeting advertisement I saw reduces the effort and time taken to obtain the necessary information.)
+- 내가 본 리타게팅 광고의 정보는 나에게 효율적으로 보여 진다.
+(The information in the retargeting advertisement I saw appears efficient to me.)
+- 내가 본 리타게팅 광고의 정보는 나한테 불필요한 정보로 보여져서 SNS 사용에 방해가 된다.
+(The information in the retargeting advertisement I saw appears unnecessary to me, which interferes with my SNS usage.)
+- 내가 본 리타게팅 광고의 정보는 나의 관심사와 관련이 없는 내용이여서 눈에 거슬린다.
+(The information in the retargeting advertisement I saw is bothersome because it is irrelevant to my interests.)
+- 내가 본 리타게팅 광고의 정보는 나에게 유용하지 않아서 나의 활동을 방해한다.
+(The information in the retargeting advertisement I saw is not useful to me, thus hindering my activities.)
+- 내가 경험한 리타게팅광고의 정보는 나의 상황에 맞게 유익하다.
+(The information in the retargeting advertisement I experienced is beneficial according to my situation.)
+- 내가 경험한 리타게팅광고의 정보는 나에게 적합하여 긍정적인 태도를 가지고 있다.
+(The information in the retargeting advertisement I experienced is appropriate for me, so I have a positive attitude toward it.)
+- 내가 경험한 리타게팅광고의 정보가 적절하여 신뢰도가 높다.
+(The information in the retargeting advertisement I experienced is appropriate, resulting in high reliability.)
+- 내가 경험한 리타게팅광고의 정보가 유익하여 클릭하고 싶다.
+(The information in the retargeting advertisement I experienced is beneficial, making me want to click it.)
+- 내가 경험한 리타게팅광고를 클릭할 예정이다.
+(I plan to click on the retargeting advertisement I experienced.)</t>
+        </is>
+      </c>
+      <c r="O934" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="n">
+        <v>934</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>윤지형</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>순차적 추천 모델의 성능 향상 연구: 클릭률(Click Through Rate)예측을 중심으로</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>연세대학교 정보대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>사용자 행동 모델링(User Behavior Modeling), 어텐션 메커니즘(Self-Attention), 딥러닝 기반 추천 시스템 이론</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>[사용자 과거 행동 시퀀스 &amp; 컨텍스트 피처] -&gt; [BERT4Rec / SASRec / DIN (하이브리드 및 앙상블)] -&gt; [클릭률(CTR) 예측 (AUC-ROC, Log Loss)]</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>H1: 양방향 셀프 어텐션을 사용하는 BERT4Rec과 단방향 셀프 어텐션을 사용하는 SASRec은 클릭률 예측에서 정확도와 효율성 측면에서 상충관계(Trade-off)를 보일 것이다.
+H2: 데이터 불균형 처리(리샘플링), 하이퍼파라미터 최적화(Optuna) 및 앙상블 기법(스태킹 등)을 적용하면 순차적 추천 모델의 클릭률 예측 성능이 유의미하게 향상될 것이다.</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>사용자 과거 행동 시퀀스, 컨텍스트 피처(시간, 디바이스 정보, 배너 위치 등), 추천 모델 아키텍처(BERT4Rec, SASRec, DIN)</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>클릭률(CTR) 예측 성능 (AUC-ROC, Log Loss)</t>
+        </is>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>데이터 불균형 처리 기법(SMOTE, 언더샘플링), 하이퍼파라미터 최적화(Learning Rate, Batch Size, Hidden Layer), 앙상블 기법(스태킹, 블렌딩 등)</t>
+        </is>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>1. 초기 실험에서 BERT4Rec과 SASRec은 데이터 불균형 및 최적화 부재로 인해 무작위 추측 수준의 성능(AUC-ROC 0.5, Log Loss 8.18)을 기록함.
+2. SMOTE 오버샘플링 및 다수 클래스 언더샘플링을 통한 데이터 불균형 해결, Optuna를 통한 하이퍼파라미터 최적화(Hidden Layer: 93, Learning Rate: 0.0041, Batch Size: 32), 그리고 앙상블 기법을 적용한 결과 예측 성능이 대폭 향상됨.
+3. 단순 평균, 가중 평균, 블렌딩, 배깅, 스태킹 등 5가지 앙상블 기법 중 DIN(Deep Interest Network)을 메타러너로 활용한 스태킹(Stacking) 기법이 가장 우수한 성능을 나타냄.</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O935" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="n">
+        <v>935</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>백승권</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>소비가치가 녹색기술제품의 구매의도에 미치는 영향 - 녹색기술제품 제도인식의 매개효과 분석 -</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>연세대학교 행정대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>소비가치이론 (Consumer Value Theory)</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>[소비가치(기능적, 감성적, 사회적, 진귀적, 이타적)] -&gt; [녹색기술제품 제도인식] -&gt; [녹색기술제품 구매의도]</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>H1: 소비가치는 녹색기술제품 구매의도에 정(+)의 영향을 미친다.
+H2: 소비가치는 녹색기술제품 제도인식에 정(+)의 영향을 미친다.
+H3: 녹색기술제품 제도인식은 녹색기술제품 구매의도에 정(+)의 영향을 미친다.
+H4: 녹색기술제품 제도인식은 소비가치와 구매의도간의 관계를 매개한다.</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>소비가치 (기능적 가치, 감성적 가치, 사회적 가치, 진귀적 가치, 이타적 가치)</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>녹색기술제품 구매의도</t>
+        </is>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>녹색기술제품 제도인식</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>감성적 가치와 이타적 가치는 녹색기술제품 구매의도에 유의한 정(+)의 영향을 미쳤으며, 녹색기술제품 제도인식은 이들 관계에서 부분매개효과를 나타내었다. 반면 연령, 성별, 소득 수준 등의 인구통계학적 통제변수는 구매의도에 유의한 영향을 미치지 않았다.</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>- Functional Value (Practicality, Rationality, Value for money)
+(기능적 가치: 실용성, 합리성, 값어치를 고려하는가?)
+- Emotional Value (Joy, Happiness, Sensory pleasure)
+(감성적 가치: 기대 이상으로 즐거움, 행복감, 감각적인 요소를 고려하는가?)
+- Social Value (Social class, Social recognition, Status/prestige)
+(사회적 가치: 사회적 계층, 사회적인식, 지위 및 품위 부합을 고려하는가?)
+- Epistemic Value (Trends, Differentiation/Uniqueness, Scarcity/Limited edition)
+(진귀적 가치: 유행 및 트렌드, 차별화 및 독특함, 희소성 및 한정판매를 고려하는가?)
+- Altruistic Value (Trust/Responsiveness, Conviction/Safety, Empathy/Tangibility)
+(이타적 가치: 신뢰 및 대응성, 확신 및 안정성, 공감 및 유형성을 고려하는가?)
+- Awareness of Green Technology Product Certification System (Renewable energy, Carbon reduction, Advanced water resources, Green IT, Green vehicles/vessels, Advanced green housing/cities, New materials, Clean production, Eco-friendly agri-food, Environmental protection and conservation)
+(녹색기술제품 제도인식: 신재생에너지, 탄소저감, 첨단수자원, 그린IT, 그린차량/선박, 첨단그린주택도시, 신소재, 청정생산, 친환경농식품, 환경보호 및 보전 인식 및 이해도)
+- Purchase Intention (Positive review of purchase, Recommendation to others, Favorable word-of-mouth, Priority selection over general products, Consideration of regular purchase)
+(구매의도: 녹색기술제품 구매를 긍정적으로 검토하고, 다른 사람에게 추천하며, 긍정적으로 말하고, 일반제품보다 우선적으로 구매 선택하며, 정기적으로 구매할 생각을 하는가?)</t>
+        </is>
+      </c>
+      <c r="O936" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="n">
+        <v>936</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>장윤주</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>비영리조직 최고관리자 특성과 재무성과 : 경력과 책무성의 역할</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 박사학위 논문</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>최고관리자이론(Upper Echelons Theory), 인적자본이론(Human Capital Theory), 자원의존이론(Resource Dependence Theory), 사회자본이론(Social Capital Theory)</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>[최고관리자 특성(임원경력, 외부영입, 근무개월수, 주요섹터경력, 섹터수, 외부지향성)] -&gt; [재무성과(수입다양성, 기부금)], [책무성(조절변수)]의 조절효과</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>H1: 비영리조직 최고관리자의 임원경력은 조직성과와 정(+)의 관계를 가질 것이다.
+H2: 비영리조직 최고관리자의 현재 조직의 근속년수는 조직성과와 정(+)의 관계를 가질 것이다.
+H3: 내부승진 최고관리자는 외부영입 최고관리자보다 조직성과가 높을 것이다.
+H4: 최고관리자의 섹터 경력은 재무성과에 차별적 영향을 미칠 것이다.
+H4a: 비영리경력이 많은 최고관리자가 영리나 공공의 경력이 많은 최고관리자에 비해 재무성과가 높을 것이다.
+H4b: 비영리조직 최고관리자의 다양한 섹터 경험은 재무성과와 정(+)의 관계를 가질 것이다.
+H5: 비영리조직 최고관리자의 외부지향성은 성과와 정(+)의 관계를 가질 것이다.
+H6: 책무성은 비영리 이외 섹터 경력 최고관리자의 재무성과를 향상시킬 것이다.</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>최고관리자의 인적자본 및 사회자본 특성 (임원경력, 외부영입, 근무개월수, 주요섹터경력, 섹터수, 외부지향성)</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>비영리조직 재무성과 (수입다양성, 기부금수익)</t>
+        </is>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>책무성 (거버넌스, 반응성, 성과, 준수성, 투명성)</t>
+        </is>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>최고관리자의 임원경력과 근속년수는 수입다양성과 기부금에 유의한 부(-)의 영향을 미치는 것으로 나타나 장기근속과 임원경력이 오히려 조직 관성을 강화할 수 있음을 확인하였다. 내부승진자는 수입다양성에서 더 높은 성과를 보였으며, 비영리 경력보다 공공섹터 경력이 수입다양성에 유의한 정(+)의 영향을 미쳤다. 최고관리자의 외부지향성은 수입다양성과 기부금 모두에 유의한 정(+)의 영향을 미쳐 이해관계자 네트워킹과 외부 자원 개발 능력의 중요성을 입증하였다. 또한 책무성은 최고관리자의 특성과 재무성과 간의 관계를 유의미하게 조절하는 것으로 확인되었다.</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>- Board Diversity: Donor/Member representative, Beneficiary representative, Volunteer representative, Expert (lawyer, doctor, professor, accountant, etc.), Related party, Business person, Founder.
+(이사회 다양성: 기부자/회원 대표, 수혜자 대표, 자원봉사자 대표, 전문가(변호사, 의사, 교수, 회계사 등), 특수관계인, 기업인, 기관 설립자)
+- Board Activity: Strategy establishment (direction), Mission and vision setting, Executive performance evaluation and new recruitment, Budget and settlement establishment and execution, Resource mobilization (fundraising) activities, Direct donation, Stakeholder representation, PR and marketing activities, Community network activities.
+(이사회 적극성: 전략수립(방향), 미션과 비전 설정, 최고관리자 성과평가 및 신규채용, 예결산 수립 및 집행, 자원동원(모금)활동, 직접 기부, 이해관계자 대변, 홍보 및 마케팅 활동, 지역사회네트워크 활동)
+- Responsiveness: Stakeholder opinion presentation channels, Response procedures for opinion presentation, Accurate answers to questions, Reflection of stakeholder opinions.
+(반응성: 이해관계자 의견 제시 수단, 의견제시 대응 절차, 질문에 대한 정확한 답변, 이해관계자 의견 반영)
+- Performance: Public interest orientation, Contribution to social development.
+(성과: 공익성 지향, 사회발전 기여)
+- Compliance: Financial/business audit, Compliance with laws.
+(준수성: 재정/사업 감사, 법률 준수)
+- Transparency: Transparent procedures and communication, Information disclosure, Utilization of information disclosure means.
+(투명성: 투명한 절차와 의사소통, 정보 공개, 정보 공개 수단 활용)
+- External Orientation: Resource mobilization (fundraising) activities, Stakeholder representation, PR and marketing activities, Community networking (participating in other organizations' boards of directors, committees, and community gatherings).
+(외부지향: 자원동원(모금)활동, 이해관계자 대변, 홍보 마케팅 활동, 지역사회네트워크)</t>
+        </is>
+      </c>
+      <c r="O937" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="n">
+        <v>937</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>손영혜</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>메가 인플루언서 보다 큰 마이크로 인플루언서: 틈새 시장에서 지위에 따른 사회적 전염</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>연세대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>최적차별화이론 (Optimal Distinctiveness Theory), 사회적 전염 이론 (Social Contagion Theory)</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>[동료의 지위(Status) 및 제품 독특성(Nicheness)] -&gt; [사회적 전염 효과] -&gt; [신곡 채택 가능성(Adoption Trial)]</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>H1: 동료의 지위는 사회적 전염이 미치는 효과를 증가시킬 것이다.
+H2: 제품의 독특성은 동료의 지위가 사회적 전염에 미치는 효과를 감소시키는 방향으로 조절할 것이다.</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>동료의 지위 (Status), 제품의 독특성 (Nicheness)</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>신곡 채택 여부 (Adoption Trial)</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>제품의 독특성 (Nicheness)</t>
+        </is>
+      </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>신곡을 청취한 동료의 수가 늘어날수록 소비자가 해당 곡을 청취할 가능성(사회적 전염 효과)이 유의미하게 증가하며, 동료의 지위가 높을수록 이 전염 효과는 더 커진다. 그러나 제품의 독특성이 높을수록(틈새 시장 제품일수록) 동료의 지위가 사회적 전염에 미치는 정(+)의 효과는 유의미하게 감소하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O938" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="n">
+        <v>938</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>김태현</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>로컬푸드를 활용한 미식관광기념품의 글로벌 시장진출 가능성 연구 - 외국인 관광객의 여행 성향에 따른 제품 속성 중요도를 중심으로 -</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>서울대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>관광활동 기반 시장세분화 이론, 미식관광 및 관광기념품 속성 이론</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>[Travel Types (Cultural Heritage, Shopping, Wellness, Gastronomy, Experiential)] -&gt; [Product Attribute Importance (Locality, Tradition, Food Tech, Design and Packaging)] (Covariates: Age, Frequency of Overseas Travel)</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>Q1. 외국인 관광객의 여행 성향에 따라 미식관광 기념품의 각 제품 속성에 대한 중요도는 어떻게 나타나는가?
+Q2. 어떤 여행 성향의 관광객이 특정 제품 속성(예: 디자인, 푸드테크 등)을 상대적으로 더 중요하게 평가하는가?</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>외국인 관광객의 여행 성향 (문화유산관광, 쇼핑관광, 웰니스관광, 미식관광, 체험관광)</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>미식관광기념품 제품 속성 중요도 (지역성, 전통성, 푸드테크, 디자인과 패키지)</t>
+        </is>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>1. ANCOVA 주효과 검정 결과, 여행 성향에 따라 각 제품 속성에 대한 중요도 인식 차이는 통계적으로 유의하지 않았다(p&gt;.05). 그러나 조정평균값 비교 시 여행 성향에 따라 상대적으로 중요하게 평가된 제품 속성 순위에 차이가 있었다.
+2. 모든 여행 성향 유형에서 '디자인과 패키지' 속성이가장 높게 평가되었다.
+3. 공변량 분석 결과, 해외여행 경험이 많은 응답자일수록 푸드테크에 대한 수용성이 높았고, 연령대가 높을수록 전통성에 대한 중요도 인식이 높은 경향이 나타났다.</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>- Food souvenirs should show the special features of the area visited.
+(식품 기념품은 방문한 지역의 특별한 특색을 보여주어야 한다.)
+- Food souvenirs should be created using symbols or local food from the area.
+(식품 기념품은 해당 지역의 상징이나 로컬푸드를 사용하여 제작되어야 한다.)
+- Food souvenirs should incorporate cultural stories or historical significance.
+(식품 기념품은 문화적 이야기나 역사적 중요성을 포함해야 한다.)
+- My purchasing decisions are influenced by how closely foodsouvenirs are connected to the region I visited.
+(나의 구매 결정은 식품 기념품이 내가 방문한 지역과 얼마나 긴밀하게 연결되어 있는지에 영향을 받는다.)
+- Food souvenirs should be made with traditional cooking methods.
+(식품 기념품은 전통적인 조리 방식으로 만들어져야 한다.)
+- Food souvenirs should include traditional patterns or colors of the area.
+(식품 기념품은 해당 지역의 전통적인 문양이나 색상을 포함해야 한다.)
+- Food souvenirs should contain a story about traditional culture.
+(식품 기념품은 전통문화에 대한 이야기를 담고 있어야 한다.)
+- I think that tradition is a key factor in enhancing the credibility of foodsouvenirs.
+(나는 전통이 식품 기념품의 신뢰성을 높이는 핵심 요인이라고 생각한다.)
+- I consider sustainability when buying food souvenirs.
+(나는 식품 기념품을 살 때 지속 가능성을 고려한다.)
+- Food souvenirs using food tech (like low sugar, high protein) should also be developed (created).
+(저당, 고단백 등 푸드테크를 활용한 식품 기념품도 개발되어야 한다.)
+- Food souvenirs should be packed in eco-friendly packaging.
+(식품 기념품은 친환경 포장재로 포장되어야 한다.)
+- Food souvenirs using food tech will give me a new experience.
+(푸드테크를 활용한 식품 기념품은 나에게 새로운 경험을 선사할 것이다.)
+- The packaging and design of food souvenirs should be easy to carry and store.
+(식품 기념품의 포장과 디자인은 휴대와 보관이 쉬워야 한다.)
+- The packaging and design of food souvenirs should be good for giving as a gift.
+(식품 기념품의 포장과 디자인은 선물하기에 좋아야 한다.)
+- The packaging and design of food souvenirs should show the culture of the area well.
+(식품 기념품의 포장과 디자인은 해당 지역의 문화를 잘 보여주어야 한다.)
+- I think the design and packaging of food souvenirs are key factors that I consider when making a purchase decision.
+(나는 식품 기념품의 디자인과 패키지가 구매 결정을 내릴 때 고려하는 핵심 요인이라고 생각한다.)</t>
+        </is>
+      </c>
+      <c r="O939" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="n">
+        <v>939</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>박재현</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>스마트폰 온디바이스 생성형 AI 기능 이용자의 사용 의도에 영향을 미치는 요인에 관한 연구</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>고려대학교 기술경영전문대학원 박사학위 논문</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>통합기술수용모형 (UTAUT2), 정보시스템성공모형 (ISSM)</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>[UTAUT2 요인 및 PNSI, PSEC, PBCR] -&gt; [성능 기대 / 노력 기대 / 정보 품질] -&gt; [사용 만족도 및 사용 의도] (조절변수: 성별, AI 사전 지식, 사용 빈도)</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>H1: 성능 기대는 온디바이스 생성형 AI 사용 의도에 정(+)의 영향을 미칠 것이다.
+H2: 노력 기대는 온디바이스 생성형 AI 사용 의도에 정(+)의 영향을 미칠 것이다.
+H3: 사회적 영향은 온디바이스 생성형 AI 사용 의도에 정(+)의 영향을 미칠 것이다.
+H4: 인지된 네트워크 서버 독립성은 성능 기대에 정(+)의 영향을 미칠 것이다.
+H5: 인지된 보안 성능은 노력 기대에 정(+)의 영향을 미칠 것이다.
+H6: 인지된 배터리 소모 위험은 온디바이스 생성형 AI 사용 의도에 부(-)의 영향을 미칠 것이다.
+H7: 정보 품질은 사용자 만족도에 정(+)의 영향을 미칠 것이다.
+H8: 사용자 만족도는 온디바이스 생성형 AI 사용 의도에 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>성능 기대, 노력 기대, 사회적 영향, 인지된 네트워크 서버 독립성, 인지된 보안 성능, 인지된 배터리 소모 위험, 정보 품질</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>사용 의도</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>성능 기대, 노력 기대, 사용자 만족도</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>성별, AI에 대한 사전 지식, 해당 기능의 사용 빈도</t>
+        </is>
+      </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>UTAUT2 분석 결과 성능 기대와 사회적 영향은 사용 의도에 긍정적 영향을 미쳤으나 노력 기대와 인지된 배터리 소모 위험은 유의미한 영향을 미치지 않았다. 인지된 네트워크 서버 독립성은 성능 기대에, 인지된 보안 성능은 노력 기대에 각각 정(+)의 영향을 주었다. ISSM 분석에서는 정보 품질이 사용자 만족도에 강한 영향을 미치는 것으로 확인되었다.</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>- Performance Expectancy (PE)
+- Using the on-device generative AI features improves my productivity.
+(온디바이스 생성형 AI 기능을 사용하면 내 생산성이 향상된다.)
+- Using the on-device generative AI features helps me complete tasks more quickly.
+(온디바이스 생성형 AI 기능을 사용하면 작업을 더 빠르게 완료할 수 있다.)
+- Using the on-device generative AI features increases my work efficiency.
+(온디바이스 생성형 AI 기능을 사용하면 업무 효율성이 높아진다.)
+- Effort Expectancy (EE)
+- Learning to use the on-device generative AI features is easy for me.
+(온디바이스 생성형 AI 기능의 사용법을 배우는 것은 나에게 쉽다.)
+- My interaction with the on-device generative AI features is clear and understandable.
+(온디바이스 생성형 AI 기능과의 상호작용은 명확하고 이해하기 쉽다.)
+- It is easy for me to become skillful at using the on-device generative AI features.
+(온디바이스 생성형 AI 기능 사용에 능숙해지는 것은 쉽다.)
+- Social Influence (SI)
+- People who are important to me think that I should use the on-device generative AI features.
+(나에게 중요한 사람들은 내가 온디바이스 생성형 AI 기능을 사용해야 한다고 생각한다.)
+- People who influence my behavior think that I should use the on-device generative AI features.
+(내 행동에 영향을 미치는 사람들은 내가 온디바이스 생성형 AI 기능을 사용해야 한다고 생각한다.)
+- People whose opinions I value prefer me to use the on-device generative AI features.
+(내가 가치를 두는 의견을 가진 사람들은 내가 온디바이스 생성형 AI 기능을 사용하는 것을 선호한다.)
+- Perceived Network and Server Independence (PNSI)
+- The on-device generative AI features can operate stably without an internet connection.
+(온디바이스 생성형 AI 기능은 인터넷 연결 없이도 안정적으로 작동할 수 있다.)
+- I can use the generative AI features independently of external cloud servers.
+(외부 클라우드 서버와 무관하게 독자적으로 생성형 AI 기능을 사용할 수 있다.)
+- The on-device AI processing reduces my dependence on network availability.
+(온디바이스 AI 처리는 네트워크 가용성에 대한 의존도를 줄여준다.)
+- Perceived Security (PSEC)
+- Using on-device generative AI features makes me feel secure about my personal data.
+(온디바이스 생성형 AI 기능을 사용하면 내 개인 데이터에 대해 안전하다고 느낀다.)
+- My data processed by on-device AI is well protected from external leakage.
+(온디바이스 AI에 의해 처리된 내 데이터는 외부 유출로부터 잘 보호된다.)
+- On-device generative AI features provide a high level of privacy compared to cloud AI.
+(온디바이스 생성형 AI 기능은 클라우드 AI에 비해 높은 수준의 프라이버시를 제공한다.)
+- Perceived Battery Consumption Risks (PBCR)
+- Using on-device generative AI features is likely to drain my smartphone battery quickly.
+(온디바이스 생성형 AI 기능을 사용하면 스마트폰 배터리가 빨리 닳을 가능성이 높다.)
+- I am concerned that executing generative AI on the device will increase power consumption.
+(기기에서 생성형 AI를 실행하면 전력 소비가 증가할까 걱정된다.)
+- The heavy computation of on-device AI causes excessive battery depletion.
+(온디바이스 AI의 무거운 연산은 과도한 배터리 소모를 유발한다.)
+- Information Quality (IQ)
+- The information provided by the on-device generative AI features is accurate.
+(온디바이스 생성형 AI 기능이 제공하는 정보는 정확하다.)
+- The output generated by the on-device AI is relevant to my requests.
+(온디바이스 AI가 생성한 결과물은 나의 요청과 관련성이 높다.)
+- The on-device generative AI provides up-to-date and useful information.
+(온디바이스 생성형 AI는 최신이며 유용한 정보를 제공한다.)
+- User Satisfaction (US)
+- I am satisfied with my overall experience using the on-device generative AI features.
+(나는 온디바이스 생성형 AI 기능의 전반적인 사용 경험에 만족한다.)
+- Using the on-device generative AI features is a pleasant experience.
+(온디바이스 생성형 AI 기능을 사용하는 것은 즐거운 경험이다.)
+- The on-device generative AI features meet my expectations.
+(온디바이스 생성형 AI 기능은 나의 기대를 충족시킨다.)
+- Use Intention (UI)
+- I intend to continue using the on-device generative AI features in the future.
+(나는 앞으로도 온디바이스 생성형 AI 기능을 계속 사용할 의향이 있다.)
+- I will frequently use the on-device generative AI features on my smartphone.
+(나는 스마트폰에서 온디바이스 생성형 AI 기능을 자주 사용할 것이다.)
+- I plan to recommend the on-device generative AI features to others.
+(나는 다른 사람들에게 온디바이스 생성형 AI 기능을 추천할 계획이다.)</t>
+        </is>
+      </c>
+      <c r="O940" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="n">
+        <v>940</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>김나연</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>시각-청각 간 정합성이 구매의도에 미치는 영향 : 시각적 제시와 배경음악의 템포를 중심으로</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>연세대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>공감각적 관점, 시각-청각 간 정합성(Cross-modal Congruency), 인지-용량 가설(Cognitive-capacity Hypothesis), 인지 부하(Cognitive Load)</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>[시각적 제시 방식(평면적 vs. 입체적) × 배경음악 템포(빠른 vs. 느린)] -&gt; [인지 자원(매개/경계조건)] -&gt; [구매의도]</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>H1: 소비자들은 평면적 제시가 빠른 템포의 배경음악과 함께 제시될 때, 더 높은 구매의도를 보일 것이다.
+H2: 소비자들은 입체적 제시가 느린 템포의 배경음악과 함께 제시될 때, 더 높은 구매의도를 보일 것이다.</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>시각적 제시 방식(평면적 제시 vs. 입체적 제시), 배경음악의 템포(빠른 템포 vs. 느린 템포)</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>구매의도</t>
+        </is>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>인지 자원 수준</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>빠른 템포의 배경음악은 평면적 제시와 결합되었을 때 구매의도를 높이고, 느린 템포의 배경음악은 입체적 제시와 결합되었을 때 구매의도를 향상시킴(Study 1). 그러나 인지 자원이 고갈된 상태에서는 배경음악의 템포와 무관하게 평면적 제시에 대한 구매의도가 더 높은 것으로 나타나 인지 자원이 핵심 메커니즘이자 경계 조건임을 입증함(Study 2).</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>- I plan to buy this brand’s product.
+(나는 이 브랜드의 제품을 구매할 계획이다.)
+- I would consider purchasing this brand’s product.
+(나는 이 브랜드의 제품 구매를 고려할 것이다.)
+- It is likely that I will try this brand’s product.
+(나는 이 브랜드의 제품을 이용해 볼 가능성이 높다.)
+- I am interested in buying this brand’s product.
+(나는 이 브랜드의 제품을 구매하는 것에 관심이 있다.)
+- My mental energy is running low.
+(나의 정신적 에너지가 부족해지고 있다.)
+- I feel like my willpower is gone.
+(나의 의지력이 소진된 것 같다.)
+- It would take a lot of effort for me to concentrate on this task.
+(이 과제에 집중하는 데 많은 노력이 필요할 것이다.)</t>
+        </is>
+      </c>
+      <c r="O941" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="n">
+        <v>941</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>김지원</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>숏폼 쇼핑 큐레이션 콘텐츠 성과에 영향을 미치는 요인</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>고려대학교 창업경영대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>인지적 구두쇠 이론 (Cognitive Miser Theory)</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>[콘텐츠 특성(점포유형, 품목, 정보유형, 콘텐츠내용, 플랫폼)] -&gt; [소비자 반응(조회수, 추천수, 공유수, 댓글수, 부정댓글수)]</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>연구문제1: 점포 유형(순수 온라인 vs 오프라인 병행)에 따라 숏폼 큐레이션 콘텐츠의 조회수, 추천수에는 차이가 있는가?
+연구문제2: 제품 품목별(생활잡화, 식품, 뷰티, 전자, 패션)로 숏폼 큐레이션 콘텐츠의 조회수, 댓글수, 콘텐츠 정보성격에는 차이가 있는가?
+연구문제3: 제품의 정보 유형(이성적 정보 vs 감성적 정보)에 따라 숏폼 큐레이션 콘텐츠의 조회수, 공유수에는 차이가 있는가?
+연구문제4: 제품의 콘텐츠 내용(필템·꿀템 추천, 솔직 경험 후기, 개인 베스트)에 따라 부정댓글의 반응의 차이가 있는가?
+연구문제5: 플랫폼(YouTube Shorts, Instagram Reels, TikTok Lite)에 따라 숏폼 큐레이션 콘텐츠의 댓글 및 정보성격에는 차이가 있는가?</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>점포 유형, 판매 품목, 정보 유형, 콘텐츠 내용, 플랫폼</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>소비자 반응 (조회수, 추천수, 공유수, 댓글 수, 부정 댓글 수, 정보의 성격)</t>
+        </is>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>오프라인 병행 점포와 제품 추천 콘텐츠가 높은 조회수와 추천·공유 반응을 유도하였으며, 식품 및 생활잡화 품목이 높은 조회수와 댓글 수를 기록했다. 또한, 개인 베스트 콘텐츠는 가장 높은 부정 댓글 수를 기록한 반면 솔직 경험 후기는 가장 낮았고, 유튜브 쇼츠는 타 플랫폼 대비 압도적으로 높은 댓글 수를 보여주었다.</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O942" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="n">
+        <v>942</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Jang Gyeongmin</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Factors Influencing Sales Performance of Small Businesses: Through an Analysis of Data by Districts in Seoul</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Yonsei University Graduate School of Economics</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>Commercial area economics, Fixed effects model, Lagged effects analysis</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>[Independent Variables: Business opening rate, pedestrian traffic, adjusted rental prices, total stores, franchise store ratio, 3-year survival rate, net population inflow] -&gt; [Dependent Variable: Log growth rate of annual average sales]</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>Business opening rate, pedestrian traffic at street level, adjusted rental prices, total number of stores, franchise store ratio, 3-year survival rate of new businesses, and net population inflow</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>Log growth rate of annual average sales for small businesses in Seoul</t>
+        </is>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>Pedestrian traffic and adjusted rental prices had significant positive impacts on small business sales growth, whereas the growth rate of total stores had a negative impact due to intensified competition.</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O943" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="n">
+        <v>943</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>서수정</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>소비절제행동이 환경에 대한 지각된 소비자 효능감과 환경을 위한 불매행동의도에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>반소비(Anti-consumption) 이론, 지각된 소비자 효능감(PCE) 이론, 불매운동(Boycott) 이론</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>[개인적 목적의 소비절제행동, 이타적 목적의 소비절제행동] -&gt; [환경에 대한 지각된 소비자 효능감] -&gt; [환경을 위한 불매행동의도]</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>H1: 소비 절제 행동은 환경에 대한 지각된 소비자 효능감에 영향을 미칠 것이다.
+H1-1: 개인적 목적의 소비 절제 행동은 환경에 대한 지각된 소비자 효능감에 정(+)의 영향을 미칠 것이다.
+H1-2: 이타적 목적의 소비 절제 행동은 환경에 대한 지각된 소비자 효능감에 정(+)의 영향을 미칠 것이다.
+H2: 환경에 대한 지각된 소비자 효능감은 환경을 위한 불매 행동 의도에 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>소비절제행동 (개인적 목적, 이타적 목적)</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>환경을 위한 불매행동의도</t>
+        </is>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>환경에 대한 지각된 소비자 효능감</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>본 연구 결과, 개인적 목적과 이타적 목적의 소비절제행동 모두 환경에 대한 지각된 소비자 효능감에 정(+)의 영향을 미치는 것으로 나타났으며, 특히 개인적 목적보다 이타적 목적의 소비절제행동이 환경에 대한 지각된 소비자 효능감에 더 큰 영향을 미치는 것으로 확인되었다. 또한 환경에 대한 지각된 소비자 효능감이 높을수록 환경을 위한 불매행동의도가 높아지는 것으로 검증되었다.</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>- 나는 물건의 가격과 상관없이 잘 관리하여 오래 사용하려고 노력한다
+(I try to use things for a long time by taking good care of them regardless of the price.)
+- 나는 낭비하지 않기 위해 실제로 소비할 수 있는 양만 구매하는 편이다
+(I tend to purchase only the amount I can actually consume to avoid waste.)
+- 나는 비용 절감을 위해 고장난 물건을 수리해 다시 사용하는 편이다
+(I tend to repair and reuse broken items to reduce costs.)
+- 나는 새제품을 살 수 있는 돈이 있어도 중고 제품을 구매하려는 편이다
+(Even if I have the money to buy a new product, I tend to buy second-hand products.)
+- 나는 옷과 신발을 신중하게 구매하는 편이다
+(I tend to purchase clothes and shoes carefully.)
+- 나는 환경 보호를 위해 일회용 플라스틱 컵 사용을 줄이고 다회용 컵(텀블러)을 사용하려 한다
+(I try to reduce the use of disposable plastic cups and use reusable cups/tumblers for environmental protection.)
+- 나는 환경 보호를 위해 일회용 봉투 사용을 줄이고 개인 장바구니를 사용하려 한다
+(I try to reduce the use of disposable bags and use personal shopping bags for environmental protection.)
+- 나는 노동 착취 논란이 있는 기업의 제품 구매를 자제하는 편이다
+(I tend to refrain from purchasing products from companies involved in labor exploitation controversies.)
+- 나는 불공정한 임금 지급으로 윤리적 문제가 있는 기업의 제품 소비를 줄이는 편이다
+(I tend to reduce the consumption of products from companies with ethical issues regarding unfair wage payments.)
+- 나는 동물 실험을 하는 기업의 제품 소비를 줄이려 한다
+(I try to reduce the consumption of products from companies that conduct animal testing.)
+- 나는 동물 복지를 고려하여 육류 소비를 줄이려고 한다
+(I try to reduce meat consumption considering animal welfare.)
+- 나는 동물 복지를 고려하여 공장식 사육방식으로 생산된 제품 구매를 자제하는 편이다
+(I try to refrain from purchasing products produced through factory farming methods considering animal welfare.)
+- 내가 소비자로서 환경 파괴를 줄이기 위해 할 수 있는 일은 거의 없다
+(There is very little I can do as a consumer to reduce environmental degradation.)
+- 내가 불필요한 소비를 줄이는 것은 환경 보호에 실질적으로 도움이 될 것이다
+(My reducing unnecessary consumption will practically help protect the environment.)
+- 내가 전반적인 소비를 줄이면 탄소 발자국을 줄이는데 유의미한 차이를 만들 수 있을 것이다
+(My reducing overall consumption will make a meaningful difference in reducing my carbon footprint.)
+- 나의 물건을 오래 쓰는 습관은 자원의 낭비를 줄이는데 실질적으로 도움이 될 것이다
+(My habit of using things for a long time will practically help reduce resource waste.)
+- 위에서 제시된 상황은 현실적이다
+(The situation presented above is realistic.)
+- 위에서 제시된 상황을 상상하는데 어려움이 없었다
+(I had no difficulty imagining the situation presented above.)
+- 위에서 제시된 상황은 신뢰할 수 있다고 느껴진다
+(The situation presented above feels trustworthy.)
+- 나는 A기업의 제품 구매를 보류할 것이다
+(I will postpone purchasing Company A's products.)
+- 나는 다른 경쟁사 제품이나 대체품을 찾아보고 구매할 것이다
+(I will look for and purchase other competitor products or substitutes.)
+- 나는 A 기업에 대한 불만을 가족들이나 주변 친구들에게 말할 것이다
+(I will express my dissatisfaction with Company A to my family or friends around me.)
+- 나는 A 기업에 대한 불만을 SNS에 게시할 것이다
+(I will post my dissatisfaction with Company A on social media.)
+- 나는 주변 사람들에게 기업 A의 제품을 불매하도록 권할 것이다
+(I will encourage people around me to boycott Company A's products.)</t>
+        </is>
+      </c>
+      <c r="O944" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="n">
+        <v>944</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>金 민 솔 (김민솔)</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>블로그 리뷰의 구조적 특성과 인센티브 여부가 마케팅 성과에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>성균관대학교 일반대학원 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>전자적 구전(eWOM) 이론, 신호이론, 규범충돌이론</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>[인센티브 리뷰 수, 비인센티브 리뷰 수, 이미지 수, 동영상 수] -&gt; [마케팅 성과: 전화하기, 저장하기, 길찾기, 공유하기 클릭 수] (조절변수: 상권 유형, 프랜차이즈 여부)</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>연구질문 1: 리뷰 내 시각적 요소(Image &amp; Video)는 마케팅 성과에 긍정적인 영향을 미치는가?
+연구질문 2: 경제적 대가의 제공 여부에 따라 구분되는 리뷰 유형(Incentive vs. Non-incentive)은 마케팅 성과에 각각 어떤 영향을 미치는가?
+연구질문 3: 리뷰 유형 및 멀티미디어 요소의 효과는 상권 유형과 프랜차이즈 매장 여부에 따라 어떻게 달라지는가?</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>인센티브 블로그 리뷰 수, 비인센티브 블로그 리뷰 수, 블로그 리뷰 당 이미지 수, 블로그 리뷰 당 비디오 수</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>주별 전화하기 클릭 수, 주별 저장하기 클릭 수, 주별 길 찾기 클릭 수, 주별 공유하기 클릭 수</t>
+        </is>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>상권 유형 (상권 vs. 비 상권), 프랜차이즈 매장 여부</t>
+        </is>
+      </c>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>인센티브 및 비인센티브 리뷰 모두 마케팅 성과(클릭 수)에 전반적으로 긍정적인 영향을 미쳤으나, 그 효과는 외부 환경 요인(상권 유형, 프랜차이즈 여부)에 따라 이질적으로 나타났다. 인센티브 리뷰는 비 상권 지역에서 더 효과적인 반면, 비인센티브 리뷰는 상권 지역에서 더 강한 영향을 보였다. 또한 블로그 리뷰는 프랜차이즈 여부와 관계없이 비 프랜차이즈 매장에서 일관되게 더 긍정적인 효과를 보였으며, 멀티미디어 요소는 단독으로보다는 리뷰 수와의 상호작용 속에서 소비자 행동을 보완적으로 촉진하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>- Call_Clicks (주별 전화하기 클릭 수)
+(주별 전화하기 클릭 수)
+- Save_Clicks (주별 저장하기 클릭 수)
+(주별 저장하기 클릭 수)
+- Routesearch_Clicks (주별 길 찾기 클릭 수)
+(주별 길 찾기 클릭 수)
+- Share_Clicks (주별 공유하기 클릭 수)
+(주별 공유하기 클릭 수)
+- Incentive_Blog_Review_cnt (주별 인센티브 블로그 리뷰 수)
+(주별 인센티브 블로그 리뷰 수)
+- Non_Incentive_Blog_Review_cnt (주별 비인센티브 블로그 리뷰 수)
+(주별 비인센티브 블로그 리뷰 수)
+- Image_cnt (주별 블로그 리뷰 당 이미지 수 평균)
+(주별 블로그 리뷰 당 이미지 수 평균)
+- Video_cnt (주별 블로그 리뷰 당 비디오 수 평균)
+(주별 블로그 리뷰 당 비디오 수 평균)
+- Franchise (프랜차이즈 매장 여부)
+(프랜차이즈 매장 여부)
+- Commercial (상권 유형)
+(상권 유형)
+- Total_Visitor_Review_cnt (주별 소비자 리뷰 수)
+(주별 소비자 리뷰 수)</t>
+        </is>
+      </c>
+      <c r="O945" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="n">
+        <v>945</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>김민지</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>세대간 디지털 콘텐츠 소비 패턴 비교와 디지털 기술의 역할: 알파세대를 중심으로</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 광고PR학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>기술수용모델(Technology Acceptance Model, TAM), 사회인지학습이론(Social Cognitive Learning Theory)</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>[독립변수(디지털기기 사용 수준, 관찰학습, 자기효능감, AI 제품 및 서비스 반응 등)] -&gt; [매개변수/TAM 요인(인지된 유용성, 인지된 사용 용이성)] -&gt; [종속변수(AI 기반 맞춤형 마케팅 반응 및 디지털 콘텐츠 소비 패턴)]</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>H1: 알파세대는 다른 세대에 비해 스마트 기기의 사용 수준에서 차이가 있는가?
+H2: 알파세대는 다른 세대에 비해 기술수용모델에서 차이가 있는가?
+H2-1: 알파세대는 다른 세대에 비해 인지된 유용성에서 차이가 있는가?
+H2-2: 알파세대는 다른 세대에 비해 인지된 사용 용이성에서 차이가 있는가?
+H3: 기술수용모델에 영향을 미치는 요인은 무엇인가?
+H3-1: 인지된 유용성에 영향을 미치는 요인은 무엇인가?
+H3-2: 인지된 사용 용이성에 영향을 미치는 요인은 무엇인가?</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>디지털기기 사용 수준, 관찰학습, 자기효능감, AI 기반 제품 및 서비스 반응</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>기술수용모델(TAM) 요인(인지된 유용성, 인지된 사용 용이성) 및 AI 맞춤형 마케팅 반응</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>인지된 유용성, 인지된 사용 용이성</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>알파세대는 학습과 놀이를 융합한 독특한 디지털 콘텐츠 소비 패턴을 보이며, 개인화된 추천 시스템을 통한 자기 주도적 학습에서 차별적인 특성을 나타냈다. 기술수용모델 분석 결과, Z세대와 밀레니얼 세대는 기술의 유용성과 사용 용이성을 보다 긍정적으로 평가한 반면, X세대와 베이비부머 세대는 디지털 기술 적응도가 상대적으로 낮았다. 다중회귀분석을 통해 자기효능감과 관찰학습, AI 활용 마케팅 등이 인지된 유용성과 사용 용이성에 유의미한 영향을 미치는 주요 요인임을 실증하였다.</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>- I think that using artificial intelligence (AI) helps me in my daily life.
+(나는 인공지능(AI)을 사용하는 것이 나의 일상생활에 도움이 된다고 생각한다.)
+- I feel that I can handle tasks more efficiently through artificial intelligence (AI).
+(인공지능(AI)을 통해 더 효율적으로 일을 처리할 수 있다고 느낀다.)
+- I feel that artificial intelligence (AI) is useful in helping or improving my decisions.
+(인공지능(AI)은 나의 결정을 도와주거나 개선하는 데 유용하다고 느낀다.)
+- I feel that using artificial intelligence (AI) is easy.
+(인공지능(AI)을 사용하는 것이 쉽다고 느낀다.)
+- Even if I use artificial intelligence (AI)-related technology or apps for the first time, I can quickly learn them.
+(인공지능(AI) 관련 기술이나 앱을 처음 사용해도 금방 익힐 수 있다.)
+- I do not feel any difficulty when using artificial intelligence (AI).
+(나는 인공지능(AI)을 사용할 때 어려움을 느끼지 않는다.)
+- Seeing people around me using artificial intelligence (AI) led me to use it as well.
+(주변 사람들이 인공지능(AI)을 사용하는 것을 보고 나도 따라 사용하게 되었다.)
+- I have used artificial intelligence (AI) services or apps recommended by friends or family.
+(친구나 가족이 추천한 인공지능(AI) 서비스나 앱을 사용한 적이 있다.)
+- I observed and learned from the artificial intelligence (AI) technology used by my parents, and I am using the same technology.
+(부모님이 사용하는 인공지능(AI) 기술을 보고 배우고, 나도 같은 기술을 사용하고 있다.)
+- I am confident that I can use artificial intelligence (AI) technology well enough.
+(나는 인공지능(AI) 기술을 충분히 잘 사용할 수 있다고 자신한다.)
+- I can effectively perform desired tasks using artificial intelligence (AI).
+(나는 인공지능(AI)을 이용해 원하는 작업을 효과적으로 수행할 수 있다.)
+- When a new artificial intelligence (AI) technology comes out, I think I can learn it quickly.
+(새로운 인공지능(AI) 기술이 나왔을 때, 나는 그것을 빠르게 익힐 수 있을 것이라고 생각한다.)
+- I have a positive perception of products or services utilizing artificial intelligence (AI).
+(나는 인공지능(AI)을 활용한 제품이나 서비스에 대해 긍정적인 인식을 가지고 있다.)
+- I am more interested in advertising or marketing messages based on artificial intelligence (AI) technology.
+(인공지능(AI) 기술을 기반으로 한 광고나 마케팅 메시지에 더 관심이 간다.)
+- I feel that services or products containing artificial intelligence (AI) are more attractive than other products.
+(인공지능(AI)이 포함된 서비스나 제품은 다른 제품보다 더 매력적이라고 느낀다.)
+- I have experience purchasing services or products containing artificial intelligence (AI).
+(나는 인공지능(AI)을 포함한 서비스나 제품을 구매한 경험이 있다.)
+- When artificial intelligence (AI) provides customized recommendations tailored to my tastes, I show greater interest in that service.
+(인공지능(AI)이 나의 취향에 맞게 맞춤형 추천을 제공할 때, 그 서비스에 더 큰 관심을 보인다.)
+- Customized advertising utilizing artificial intelligence (AI) feels more persuasive to me.
+(인공지능(AI)을 활용한 맞춤형 광고가 나에게 더 설득력 있게 느껴진다.)
+- When the service I use analyzes my behavior through artificial intelligence (AI) and makes customized suggestions, I use that service more frequently.
+(내가 사용하는 서비스가 인공지능(AI)을 통해 나의 행동을 분석하고 맞춤형 제안을 할 때, 더 자주 그 서비스를 사용하게 된다.)</t>
+        </is>
+      </c>
+      <c r="O946" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>946</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>전다현</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>소비자 구매의사결정과정에서의 인플루언서 이용에 관한 연구</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>서울대학교 대학원 소비자학과 박사학위 논문</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>이용과 충족 이론, 제한된 합리성 이론, 행동론적 구매의사결정 이론, 사회인지이론, 기대-불일치 이론</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>[인플루언서 이용 동기 요인] (정보탐색, 정서적 충족, 경제적 혜택, 소비안내, 대리경험) -&gt; [결과기대] (선택 정당화, 선택 자신감, 선택 후회, 선택 비용) -&gt; [만족도] (과정 만족도, 결과 만족도)</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>H1: 구매의사결정과정에서 소비자의 인플루언서 이용 동기는 다차원적 요인으로 구성될 것이다.
+H2: 인플루언서 이용 동기 요인은 결과기대에 유의한 영향을 미칠 것이다.
+H3: 결과기대는 만족도에 유의한 영향을 미칠 것이다.
+H4: 인플루언서 이용 동기 요인은 만족도에 유의한 영향을 미칠 것이다.
+H5: 결과기대는 인플루언서 이용 동기 요인과 만족도 간의 관계를 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>인플루언서 이용 동기 요인 (정보탐색, 정서적 충족, 경제적 혜택, 소비안내, 대리경험)</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>만족도 (과정 만족도, 결과 만족도)</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>결과기대 (선택 정당화, 선택 자신감, 선택 후회, 선택 비용)</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>첫째, 소비자의 인플루언서 이용 동기는 정보탐색, 정서적 충족, 경제적 혜택, 소비안내, 대리경험의 5가지 요인으로 구성되며 대리경험과 정보탐색의 이용 수준이 가장 높았다. 둘째, 이용 동기 요인은 만족도에 차별적인 영향을 미쳐 과정 만족도는 실용적 동기에 의해, 결과 만족도는 정서적 충족 및 실질적 가치에 의해 주로 향상되었다. 셋째, 결과기대는 동기를 만족으로 전환하는 핵심 매개변수이며 선택 비용 감소 기대가 모든 만족 경로의 기저에서 근본적 매개 변수로 작용했다.</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>- Consumers perceived high utility when using the AI service.
+(인플루언서 콘텐츠를 이용하면, 내 선택을 다른 사람들이 쉽게 설명하고 정당화할 수 있다.)
+- When using influencer content, I can immediately know which product is better.
+(인플루언서 콘텐츠를 이용하면, 어떤 제품이 더 좋은지 단번에 알 수 있다.)
+- When using influencer content, I can easily make decisions without worrying about multiple alternatives.
+(인플루언서 콘텐츠를 이용하면, 여러 대안을 고민하지 않고 쉽게 결정을 내릴 수 있다.)
+- I gain confidence when I find the product that best matches my preferences using influencer content.
+(인플루언서 콘텐츠를 이용해, 내 선호와 가장 잘 맞는 제품을 찾으면 자신감이 생긴다.)
+- I am confident that I can find the product that best satisfies my needs using influencer content.
+(인플루언서 콘텐츠를 이용해, 내 필요를 가장 잘 충족하는 제품을 찾을 수 있다고 확신한다.)
+- It is impossible to be sure which product best fits my preferences through influencer content. (R)
+(인플루언서 콘텐츠를 통해 내 선호에 가장 잘 맞는 제품이 무엇인지 확신하는 건 불가능하다.)
+- When purchasing products following influencer content, I worry whether there might be a better competing product after purchase.
+(인플루언서 콘텐츠를 따라 제품을 구매하면, 구매 후에 더 좋은 경쟁 제품이 있을까 걱정된다.)
+- When purchasing products following influencer content, I wonder what it would have been like if I had made a different choice.
+(인플루언서 콘텐츠를 따라 제품을 구매했을 때, 다른 선택을 했더라면 어땠을지 궁금하다.)
+- Even after finding a good product through influencer content, I am afraid of missing out on a better product.
+(인플루언서 콘텐츠를 통해 좋은 제품을 찾은 후에도, 더 나은 제품을 놓쳤을까 봐 두렵다.)
+- When purchasing products following influencer content, I wonder if it would have been better if I had purchased another competing product.
+(인플루언서 콘텐츠를 따라 제품을 구매했을 때, 다른 경쟁 제품을 구매했다면 더 좋았을지 궁금하다.)
+- Using influencer content reduces the time and effort spent comparing and evaluating other products.
+(인플루언서 콘텐츠를 이용하면, 다른 제품과 비교하고 평가하는 데 시간과 노력을 덜 들일 수 있다.)
+- Using influencer content ensures sufficient time to evaluate other available products.
+(인플루언서 콘텐츠를 이용하면, 구매 가능한 다른 제품들을 충분히 평가할 시간이 확보된다.)
+- Using influencer content makes it easy to compare various products.
+(인플루언서 콘텐츠를 이용하면, 다양한 제품을 쉽게 비교할 수 있다.)
+- Using influencer content makes it easy to make purchasing decisions.
+(인플루언서 콘텐츠를 이용하면, 쉽게 구매결정을 쉽게 내릴 수 있다.)
+- The process of making purchase decisions using influencer content feels frustrating. (R)
+(인플루언서 콘텐츠를 이용해 구매 결정을 하는 과정이 답답하게 느껴진다.)
+- The process of deciding which product to buy using influencer content is interesting.
+(인플루언서 콘텐츠를 이용해 어떤 제품을 살지 결정을 하는 과정이 흥미롭다.)
+- The experience of deciding which product to choose using influencer content is satisfactory.
+(인플루언서 콘텐츠를 이용해 어떤 제품을 선택할지 결정하는 경험이 만족스럽다.)
+- Products purchased using influencer content are often the exact products I need.
+(인플루언서 콘텐츠를 이용해 구매한 제품은 내가 정확히 필요로 하는 제품인 경우가 많다.)
+- I am often satisfied with products purchased using influencer content.
+(인플루언서 콘텐츠를 이용해 구매한 제품에 만족하는 경우가 많다.)
+- I think purchasing products using influencer content is generally a wise decision.
+(인플루언서 콘텐츠를 이용해 제품을 구매한 것이 대체로 현명한 결정이라고 생각한다.)
+- I generally like products purchased using influencer content very much.
+(나는 인플루언서 콘텐츠를 이용해 구매한 제품을 대체로 매우 좋아한다.)
+- I think using products purchased through influencer content was generally a good experience.
+(나는 인플루언서 콘텐츠를 이용해 제품을 사용하는 것이 대체로 좋은 경험이었다고 생각한다.)</t>
+        </is>
+      </c>
+      <c r="O947" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O947"/>
+  <dimension ref="A1:O964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76515,6 +76515,1982 @@
         </is>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>947</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>양수영</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>클릭을 이끄는 썸네일 속 사람 행동은 무엇일까?: 비디오 커머스에서 언어적·비언어적 요소의 영향</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>연세대학교 정보대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Mehrabian's Communication Theory (7-38-55 Rule)</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>[IV (Nonverbal Cues: Body Language, Facial Expression, Physical Distance 등)] -&gt; [DV (Clicks)]</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>H1: 동적 썸네일 내 인물의 비언어적 행동 단서(바디랭기지, 표정, 물리적 거리 등)는 소비자 클릭 행동에 유의미한 정(+)의 영향을 미칠 것이다.
+H2: 썸네일 내 언어적 정보(정보성 메시지)는 비언어적 요소에 비해 상대적으로 클릭 유도에 미치는 영향력이 낮거나 부(-)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>비언어적 요소 (Body Language, Facial Expression, Physical Distance, Facial Attractiveness, Eye Gaze Direction), 언어적 요소 (Information Message, Information Message Length, Information Message Category)</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>클릭 수 (Clicks, t ~ t+7)</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>제품 주문 수 (Product Sales Count), 매출 (Product Sales Revenue)</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>상품 속성 (검색재 vs. 경험재), 업로드 시간대, 브랜드 인기도, 방송 인기도, 인물 수, 쇼호스트 성별 및 연령대, 상품 가격대</t>
+        </is>
+      </c>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>동적 썸네일 내 인물의 역동적인 바디랭기지, 밝은 표정, 가까운 물리적 거리(줌 인) 등 비언어적 단서는 사용자 클릭 수와 조회수를 뚜렷하게 증가시키는 반면, 과도한 텍스트 정보는 오히려 클릭을 저해하는 경향이 있음을 확인하였다. 이러한 비언어적 요소의 효과는 제품 속성 및 방송 맥락에 따라 이질적으로 나타나며, 본 연구의 변수를 예측 모델에 적용할 경우 기존 정적 이미지 모델 대비 클릭 예측 정확도가 크게 향상되었다.</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O948" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>948</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>김진용</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>채무조정 프로그램의 프레이밍 효과 - 접근 기반 소비 방식이 참여에 미치는 영향 -</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>프레이밍 이론(Framing Theory), 전망이론(Prospect Theory), 접근 기반 소비(Access-Based Consumption), 목표-경사 가설(Goal-Gradient Hypothesis), 재결합 효과(Re-coupling Effect)</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>[IV (계약방식, 상환방식)] x [Moderator (표기방식)] -&gt; [Mediator (기대효용, 기대비용)] -&gt; [DV (참여 의사)]</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>H1: 채무조정 프로그램의 계약방식을 갱신 가능한 형태로 제시하면, 채무자들의 프로그램 참여 의사가 증가할 것이다.
+H2: 채무조정 프로그램의 상환방식을 계좌별 순서를 지정할 수 있는 방식으로 제시하면, 채무자들의 프로그램 참여 의사가 증가할 것이다.
+H3: '채무상환' 표현을 '신용 회복 서비스'로 표기방식을 전환하면, 가설 1과 가설 2의 긍정적 효과가 강화될 것이다.</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>계약방식 (갱신형 vs. 고정형), 상환방식 (순서 지정형 vs. 일괄 통합형)</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>프로그램 참여 의사</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>기대효용, 기대비용</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>표기방식 (신용회복지원 서비스 이용 vs. 채무 상환)</t>
+        </is>
+      </c>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>갱신형 계약 및 상환 순서 지정 옵션 그 자체는 채무조정 참여 의사에 유의미한 긍정적 영향을 미치지 않거나 일부 부정적 영향을 주었으나, '신용회복지원 서비스'라는 표기방식과 결합(상호작용)할 경우 프로그램 참여 의사를 유의미하게 증가시키는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>- I expect high utility when participating in the debt adjustment program.
+(채무조정 프로그램에 참여할 때 높은 효용을 기대한다.)
+- I perceive high costs when participating in the debt adjustment program.
+(채무조정 프로그램에 참여할 때 높은 비용을 지각한다.)
+- I have a strong intention to participate in the debt adjustment program.
+(채무조정 프로그램에 참여할 의사가 매우 높다.)</t>
+        </is>
+      </c>
+      <c r="O949" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>949</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>김선희</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>지역특산 디저트의 선택속성이 구매의도에 미치는 영향에 관한 연구 –소비자의 건강지향성, 친환경의식을 조절변수로–</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>연세대학교 정경대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>조절효과 모형, 선택속성 이론</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>[지역특산 디저트 선택속성 (맛/품질, 가격적정성, 건강성, 다양성, 독창성)] -&gt; [구매의도] (조절변수: 건강지향성, 친환경의식)</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>H1: 지역특산 디저트의 선택속성은 구매의도에 유의한 정(+)의 영향을 미친다.
+H2: 지역특산 디저트의 선택속성은 소비자의 건강지향성과 작용하여 구매의도에 더 큰 유의한 정(+)의 영향을 미친다.
+H3: 지역특산 디저트의 선택속성은 소비자의 친환경의식과 작용하여 구매의도에 더 큰 유의한 정(+)의 영향을 미친다.</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>지역특산 디저트의 선택속성 (맛/품질, 가격적정성, 건강성, 다양성, 독창성)</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>구매의도</t>
+        </is>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>소비자의 건강지향성, 친환경의식</t>
+        </is>
+      </c>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>지역특산 디저트의 선택속성 중 가격적정성과 건강성은 구매의도에 유의미한 긍정적 영향을 미쳤으나, 맛/품질, 다양성, 독창성은 유의한 영향을 미치지 않았다. 건강지향성은 조절효과를 보이지 않은 반면, 친환경의식은 건강성과 구매의도 간의 관계를 강화하는 조절효과를 나타냈다.</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>- The taste of local specialty desserts is excellent.
+(지역특산 디저트의 맛은 훌륭하다.)
+- The taste of local specialty desserts is consistent.
+(지역특산 디저트의 맛은 일정하다.)
+- The taste of local specialty desserts is harmonious.
+(지역특산 디저트의 맛은 조화롭다.)
+- The taste of local specialty dessert menu is diverse.
+(지역특산 디저트 메뉴의 맛은 다양하다.)
+- Local specialty desserts have a distinctive taste.
+(지역특산 디저트는 차별적인 맛이 있다.)
+- Local specialty desserts visually stimulate taste.
+(지역특산 디저트는 시각적으로 맛을 자극한다.)
+- The taste of local specialty desserts is worth the price.
+(지역특산 디저트의 맛은 가격에 비해 가치가 있다.)
+- The color of local specialty desserts looks appetizing.
+(지역특산 디저트의 색감은 먹음직스럽다.)
+- The quality of ingredients for local specialty desserts is good.
+(지역특산 디저트 재료의 질은 양질이다.)
+- The price of local specialty desserts is reasonable.
+(지역특산 디저트 가격이 적당하다.)
+- Local specialty desserts are worth the price.
+(지역특산 디저트는 가격만큼 가치가 있다.)
+- Local specialty desserts have good quality for the price.
+(지역특산 디저트는 가격 대비 품질이 좋다.)
+- Additional benefits (discounts, affiliate cards) are provided when purchasing local specialty desserts.
+(지역특산 디저트 구매시 부가적인 혜택(할인, 제휴카드)등이 제공된다.)
+- There are dessert menus considering health such as low-salt, low-sugar, low-fat, and low-calorie.
+(저염, 저당, 저지방, 저칼로리 등 건강을 고려한 디저트 메뉴가 있다.)
+- Local specialty dessert menu is a health food menu.
+(지역특산 디저트 메뉴는 건강식 메뉴이다.)
+- Local specialty dessert menu considered nutritional aspects.
+(지역특산 디저트 메뉴는 영양적인 면을 고려했다.)
+- Local specialty desserts have products for diet.
+(지역특산 디저트는 다이어트를 위한 제품이 있다.)
+- Local specialty desserts use eco-friendly and organic ingredients.
+(지역특산 디저트는 친환경, 유기농 식재료를 사용한다.)
+- Local specialty desserts use ingredients considering health.
+(지역특산 디저트는 건강을 고려한 식재료를 사용한다.)
+- Local specialty desserts use various ingredients.
+(지역특산 디저트는 다양한 식재료를 사용한다.)
+- Local specialty desserts use fresh ingredients.
+(지역특산 디저트는 신선한 재료를 사용한다.)
+- Local specialty dessert menu is fresh.
+(지역특산 디저트 메뉴는 신선하다.)
+- Local specialty dessert menu is eco-friendly.
+(지역특산 디저트 메뉴는 친환경적이다.)
+- Local specialty dessert menu is a healing menu.
+(지역특산 디저트 메뉴는 힐링메뉴이다.)
+- Local specialty desserts specify origin and nutritional information.
+(지역특산 디저트는 원산지 및 영양성분 정보가 명시되어 있다.)
+- Local specialty dessert menu is provided according to the season.
+(지역특산 디저트 메뉴는 계절에 맞게 제공된다.)
+- Local specialty dessert shapes are prepared in various ways.
+(지역특산 디저트 모양은 다양하게 준비되어 있다.)
+- Various types of local specialty desserts are prepared.
+(지역특산 디저트 종류가 다양하게 준비되어 있다.)
+- Local specialty desserts have many menus that fit tastes.
+(지역특산 디저트는 기호에 맞는 메뉴가 많다.)
+- Local specialty desserts vary by ingredient.
+(지역특산 디저트는 재료별로 다양하다.)
+- Local specialty desserts allow frequent contact with new products.
+(지역특산 디저트는 신제품을 자주 접할 수 있다.)
+- Local specialty dessert menu is original.
+(지역특산 디저트 메뉴는 독창적이다.)
+- Local specialty desserts have menu differentiation.
+(지역특산 디저트는 메뉴의 차별성이 있다.)
+- Local specialty dessert shapes are differentiated.
+(지역특산 디저트 모양은 차별화 되어 있다.)
+- Local specialty desserts have ingredient characteristics.
+(지역특산 디저트는 재료의 특성이 있다.)
+- The menu composition of local specialty dessert products is trendier than other desserts.
+(지역특산 디저트 제품의 메뉴 구성은 다른 디저트에 비해 트렌디하다.)
+- I choose foods that fit the season.
+(나는 계절에 맞는 음식을 선택한다.)
+- I consider health and nutrition when eating food.
+(나는 음식을 먹을 때 건강과 영양을 고려한다.)
+- I purchase nutritious food even if it is expensive.
+(가격이 비싸더라도 영양가 있는 식품을 구입한다.)
+- I check nutritional information displays such as calories and nutritional components when buying food.
+(식품을 살 때 칼로리, 영양성분 등 영양정보 표시를 확인한다.)
+- When choosing food, I check whether the nutritional components are good rather than whether the quantity is large.
+(식품을 고를 때는 양이 많은가 보다는 영양성분이 좋은가를 따져본다.)
+- When choosing food, I check whether the nutritional components are good rather than whether it tastes good.
+(식품을 고를 때는 맛이 있는가 보다는 영양성분이 좋은가를 따져본다.)
+- When buying food, I check the expiration date, food additives, and component analysis.
+(식품을 살 때 유통기간과 식품첨가물 및 성분분석을 확인한다.)
+- I tend to purchase organic or eco-friendly products considering health even if food is expensive.
+(식품은 가격이 비싸더라도 건강을 생각하여 유기농이나, 친환경 제품을 구입하는 편이다.)
+- I carefully select food for my health.
+(나는 건강을 위해 음식을 신중하게 고른다.)
+- I consider my health a lot.
+(나는 내 건강에 대해 많이 고려한다.)
+- I choose foods that use natural seasonings.
+(나는 자연조미료를 사용하는 음식을 선택한다.)
+- I consider calories when choosing food.
+(나는 음식을 선택할 때 칼로리를 고려한다.)
+- I choose foods using health functional food ingredients.
+(나는 건강 기능식 재료를 사용한 음식을 선택한다.)
+- I have knowledge about eco-friendly products.
+(나는 친환경 제품에 관한 지식을 알고 있다.)
+- I have knowledge about eco-friendly labels.
+(나는 친환경 관련 표시(라벨)에 관한 지식을 알고 있다.)
+- I am very interested in eco-friendly products and information.
+(친환경 상품과 정보에 관심이 많다.)
+- I think purchasing eco-friendly products contributes to environmental preservation.
+(나는 친환경상품 구입이 환경보존에 기여한다고 생각한다.)
+- I try to use eco-friendly products as daily necessities.
+(일상용품으로 친환경제품을 사용하려고 노력한다.)
+- I intend to purchase eco-friendly products.
+(나는 친환경 제품을 구매할 의사가 있다.)
+- I think the development of eco-friendly products by companies should be revitalized.
+(기업의 친환경 상품개발이 활성화 되어야 한다고 생각한다.)
+- I intend to purchase local specialty desserts.
+(나는 지역특산 디저트를 구매할 의향이 있다.)
+- I will recommend purchasing local specialty desserts to people around me.
+(나는 주변사람들에게 지역특산 디저트 구매를 권유할 것이다.)
+- I will consider local specialty dessert products as a priority.
+(나는 지역특산 디저트 상품을 우선적으로 고려할 것이다.)
+- I am willing to pay money to buy local specialty desserts.
+(나는 지역특산 디저트를 구매하기 위해 돈을 지불할 의향이 있다.)
+- I have a thought to purchase local specialty dessert products even if they are expensive.
+(지역특산 디저트 제품이 비싸더라도 구매할 생각이 있다.)
+- I am positive about purchasing local specialty dessert products.
+(나는 지역특산 디저트 제품을 구매하는 것에 긍정적이다.)
+- I have the intention to purchase local specialty desserts in the future.
+(나는 앞으로도 지역특산 디저트를 구매할 용의가 있다.)
+- I will continuously purchase local specialty desserts.
+(나는 지속적으로 지역특산 디저트를 구매할 것이다.)</t>
+        </is>
+      </c>
+      <c r="O950" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>950</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>정현우</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>지배적 소매상이 주변 소매상에 미치는 영향 분석: 도매가격 할인을 중심으로</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>연세대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>시공간 자료분석, 도구변수를 활용한 통제함수 접근법, 유통채널 권력 이론</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>[Dominant Retailer Discount (IV)] -&gt; [General Pharmacy Wholesale Price Discount (DV)], 이 관계는 영업사원과의 거래기간(Moderator)에 의해 역 U자 형태로 조절됨</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>H1: 지배적 소매상의 도매가격 할인은 주변 일반 소매상의 도매가격 할인금액을 증가시킬 것이다.
+H2: 지배적 소매상의 할인이 주변 소매상에 미치는 영향은 영업사원과의 거래기간에 따라 역 U자(inverted U-shape) 형태로 조절될 것이다.</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>약국 i의 k번째 주문 이전 3개월 동안 주변 난매약국들이 받은 도매가격 할인금액 (DR_discountik)</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>약국 i의 k 번째 주문 시 받은 도매가격의 할인금액 (discountik)</t>
+        </is>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>약국 i의 k번째 주문을 담당했던 영업사원과의 누적 거래기간 (rapportik)</t>
+        </is>
+      </c>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>난매약국이 1000 원의 할인을 받으면 일반약국들의 도매가격 할인금액도 16.64% 증가하여 제조사의 이익을 감소시키는 것으로 나타났다. 한편, 이러한 난매약국의 영향은 영업사원과의 거래기간에 따라 역 U자 형태로 조절되어, 거래기간이 약 27.5개월(약 2년)까지는 영향이 커지다가 그 이후에는 감소하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O951" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>951</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>최한솔</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>제조업의 D2C 비즈니스에서 개인정보보호 활용 전략에 관한 연구</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>고려대학교 기술경영전문대학원 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>프라이버시 계산 이론(Privacy Calculus Theory)</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>[개인정보보호 역량(투명성, 통제권 보장, 정보 최소 수집, 보안성)] -&gt; [브랜드 신뢰] -&gt; [마케팅 성과(데이터 공유 의사, 구매 의도, 지속이용의도)]</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>H1: 제조업 D2C 비즈니스의 개인정보보호 역량에 대한 소비자의 인식은 브랜드 신뢰에 정(+)의 영향을 미칠 것이다.
+H2: 브랜드 신뢰는 마케팅 성과(데이터 공유 의사, 구매 의도, 지속이용의도)에 정(+)의 영향을 미칠 것이다.
+H3: 브랜드 신뢰는 개인정보보호 역량과 마케팅 성과 사이의 관계를 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>개인정보보호 역량 (투명성, 통제권 보장, 정보 최소 수집, 보안성)</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>마케팅 성과 (데이터 공유 의사, 구매 의도, 지속이용의도)</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>브랜드 신뢰</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>소비자는 기업의 개인정보보호 역량을 세부 요인보다 브랜드가 제공하는 '통합된 안전감'으로 인식하며, 이는 브랜드 신뢰에 정(+)의 영향을 미치고 나아가 마케팅 성과를 강화함. 브랜드 신뢰의 부분 매개 효과가 확인됨.</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>- 자사몰은 개인정보 수집 및 이용 목적을 명확하고 이해하기 쉽게 안내합니다.
+(The official online store clearly and easily guides the purpose of collecting and using personal information.)
+- 나는 해당 자사몰이 나의 개인정보를 어떻게 활용하는지에 대해 쉽게 인지할 수 있습니다.
+(I can easily perceive how the online store utilizes my personal information.)
+- 자사몰의 개인정보 처리방침은 투명하게 공개되어 있습니다.
+(The personal information processing policy of the online store is transparently disclosed.)
+- 나는 해당 자사몰에서 나의 개인정보 수집/활용 동의 여부를 스스로 선택하고 변경할 수 있다고 생각합니다.
+(I believe that I can independently choose and change my consent to the collection and use of my personal information in the online store.)
+- 자사몰은 마케팅 정보 수신 동의 여부를 내가 원할 때 쉽게 철회(변경)할 수 있도록 보장합니다.
+(The online store ensures that I can easily withdraw or change my consent to receive marketing information whenever I want.)
+- 나는 해당 자사몰에 제공한 내 개인정보에 대해 충분한 통제권을 가지고 있다고 생각합니다.
+(I believe I have sufficient control over the personal information I provided to the online store.)
+- 자사몰은 서비스 제공에 꼭 필요한 최소한의 개인정보만을 수집한다고 생각합니다.
+(I believe the online store collects only the minimum personal information strictly necessary for service provision.)
+- 자사몰이 요구하는 개인정보는 서비스 이용과 관련성이 높다고(밀접하다고) 생각합니다.
+(I think the personal information requested by the online store is highly relevant to using the service.)
+- 나는 이 자사몰이 수집하는 개인정보의 양이 제공되는 혜택에 비해 적절하다고 생각한다.
+(I think the amount of personal information collected by this online store is appropriate compared to the benefits provided.)
+- 나는 해당 자사몰이 나의 개인정보(결제정보 포함)를 안전하게 보호할 것이라고 믿습니다.
+(I believe that the online store will securely protect my personal information, including payment information.)
+- 나는 해당 자사몰의 온라인 구매 시스템(결제 포함)이 안전하다고 생각합니다.
+(I think that the online store's online purchasing system, including payment, is secure.)
+- 나는 해당 자사몰의 개인정보 기술적·관리적 보안 조치를 신뢰할 수 있습니다.
+(I trust the technical and administrative security measures for personal information of the online store.)
+- 나는 해당 자사몰과 그 브랜드를 전반적으로 신뢰합니다.
+(I generally trust the online store and its brand.)
+- 자사몰의 브랜드는 고객과의 약속을 잘 지킨다고 생각합니다.
+(I believe that the online store's brand keeps its promises to customers.)
+- 자사몰의 브랜드는 고객의 이익을 고려하고 정직하게 운영된다고 믿습니다.
+(I believe that the online store's brand considers customer interests and operates honestly.)
+- 나는 해당 자사몰의 브랜드가 나의 개인정보를 안전하게 다룰 것이라고 믿습니다.
+(I believe that the online store's brand will handle my personal information securely.)
+- 나는 맞춤형 서비스나 혜택을 제공받기 위해 해당 자사몰에 나의 개인정보(관심사, 취향 등)를 기꺼이 제공할 의향이 있습니다.
+(I am willing to willingly provide my personal information, such as interests and tastes, to the online store to receive customized services or benefits.)
+- 나는 해당 자사몰이 나의 행동 데이터(예: 방문 기록, 검색 기록)를 수집 및 활용하는 것에 동의할 의향이 있습니다.
+(I am willing to agree to the online store collecting and utilizing my behavioral data, such as visit and search history.)
+- 나는 앞으로도 해당 자사몰에 나의 개인정보를 계속 제공할 것 같습니다.
+(I am likely to continue providing my personal information to the online store in the future.)
+- 나는 앞으로 해당 자사몰에서 제품을 구매할 의향이 있습니다.
+(I am willing to purchase products from the online store in the future.)
+- 나는 제품 구매 시, 다른 쇼핑몰보다 해당 자사몰을 우선적으로 고려할 것입니다.
+(When purchasing products, I will consider the online store preferentially over other shopping malls.)
+- 나는 해당 자사몰의 제품을 다른 사람에게 추천할 의향이 있습니다.
+(I am willing to recommend the online store's products to others.)
+- 나는 앞으로도 해당 자사몰을 지속적으로 이용할 것입니다.
+(I will continue to use the online store in the future.)
+- 나는 다른 쇼핑 플랫폼보다 해당 자사몰을 우선적으로 이용할 것입니다.
+(I will use the online store preferentially over other shopping platforms.)
+- 나는 해당 자사몰의 이용 빈도를 늘릴 의향이 있습니다.
+(I am willing to increase the frequency of using the online store.)</t>
+        </is>
+      </c>
+      <c r="O952" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>952</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>김나연</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>제로슈가 음료의 소비 동기 요인 탐구: 개인차 특성과 소비 행동을 중심으로</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>이용과 충족 이론, 조절초점이론</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>[개인차 특성 및 동기 요인] -&gt; [태도, 구매의도, 입소문]</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>H1: 제로슈가 음료 소비에 영향을 미치는 주요 동기 요인은 무엇인가?
+H2: 제로슈가 음료 소비 동기는 소비 행동과 어떤 관계가 있는가?
+H3: 제로슈가 음료 소비에 영향을 미치는 개인차 특성은 무엇인가?
+H4: 제로슈가 음료 소비 행동은 소비자의 개인차 특성에 따라 다르게 나타나는가?</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>제로슈가 음료 소비 동기 요인 (사회적 승인, 건강 및 체중 관리, 제품 효용성, 인상 관리, 죄책감 회피, 보상적 건강 신념, 주관적 규범), 개인차 특성 (소비자 지식, 제품 관여도, 건강 의식, 이상화된 신체 이미지, 조절초점)</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>제로슈가 음료 소비 행동 (태도, 구매의도, 입소문)</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>탐색적 요인분석을 통해 제로슈가 음료 소비 동기로 사회적 승인, 건강 및 체중 관리, 제품 효용성, 인상 관리, 죄책감 회피, 보상적 건강 신념, 주관적 규범의 7가지 요인이 도출됨. 관여도는 소비 행동 전반에서 가장 중요한 역할을 하였으며, 건강 및 체중 관리와 제품 효용성 동기는 태도, 구매의도, 입소문에 전반적으로 유의한 긍정적 영향을 미치는 것으로 나타남.</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>- I drink zero-sugar beverages because the calorie content is low.
+(나는 칼로리가 낮기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because it helps with weight loss.
+(나는 체중 감량에 도움이 되기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I can control and reduce calories in my diet.
+(나는 식단의 칼로리를 조절하고 줄일 수 있기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages as a realistic choice for weight loss or sugar intake control.
+(나는 체중 감량이나 당분 섭취 조절을 위한 현실적인 선택지로서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I believe it can improve my health.
+(나는 건강을 향상시킬 수 있다고 믿기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I expect to live longer.
+(나는 더 오래 살 수 있다고 기대하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I believe it helps prevent health problems like diabetes.
+(나는 당뇨병 같은 건강 문제 예방에 도움이 될 수 있다고 믿기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I think it helps prevent diseases.
+(나는 질병 예방에 도움이 된다고 생각하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I think it can contribute to solving obesity problems.
+(나는 비만 문제 해결에 기여할 수 있다고 생각하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I am a person who consumes healthy food.
+(나는 건강한 음식을 소비하는 사람이기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because consuming healthy food is an important part of who I am.
+(나는 건강한 음식 섭취가 나를 나타내는 중요한 부분이기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because of my lifestyle of reducing sugar.
+(나는 설탕을 줄이려는 생활방식 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages as a person who values self-management.
+(나는 자기관리를 중시하는 사람으로서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I value other people's attention and praise for my body shape.
+(나는 몸매에 대한 타인의 관심과 칭찬을 중요하게 여기기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I enjoy other people's recognition.
+(나는 타인의 인정을 즐기기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I want to look good and healthy in terms of body shape.
+(나는 몸매가 좋고 건강해 보이고 싶기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I want to be recognized as a self-managing person.
+(나는 자기관리하는 사람으로 인정받고 싶어서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I want to look like a self-managing person.
+(나는 자기관리하는 사람으로 보이고 싶어서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I think I can offset the effects even if I eat high-calorie food.
+(나는 칼로리가 높은 음식을 먹더라도 그 영향을 상쇄할 수 있다고 생각하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I think it is okay to eat a lot of high-calorie food if I drink them.
+(나는 제로슈가 음료를 마시면 칼로리가 높은 음식을 많이 먹어도 괜찮다고 생각하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I think it is okay to occasionally eat high-calorie food if I usually drink them.
+(나는 가끔 고칼로리 음식을 먹어도 평소에 제로슈가 음료를 마시면 괜찮다고 생각하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I think zero-sugar beverages can compensate for the negative effects of regular beverages.
+(나는 제로슈가 음료가 일반 음료의 부정적 영향을 보상해 줄 수 있다고 생각하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I feel guilty when drinking regular beverages that are not healthy.
+(나는 건강에 좋지 않은 일반 음료를 마실 때 죄책감을 느끼기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I feel guilty when drinking regular beverages.
+(나는 일반 음료를 마실 때 죄책감을 느끼기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages in order not to feel guilty from regular beverage consumption.
+(나는 일반 음료 소비로부터 오는 죄책감을 느끼지 않기 위해 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages in order not to feel guilty when eating food.
+(나는 음식을 먹을 때 죄책감을 느끼기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I feel trendy.
+(나는 트렌디하다고 느끼기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I think it is hip.
+(나는 힙하다고 생각해서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I feel they are attractive.
+(나는 제로슈가 음료가 매력적이라고 느끼기 때문에 이 음료를 마신다.)
+- I drink zero-sugar beverages because I think zero-sugar beverages are a major trend.
+(나는 제로슈가 음료가 대세라고 생각하기 때문에 이 음료를 마신다.)
+- I drink zero-sugar beverages because I think zero-sugar is very popular.
+(나는 제로슈가 인기가 많다고 생각하기 때문에 이 음료를 마신다.)
+- I drink zero-sugar beverages because my friends drink them.
+(나는 친구들이 제로슈가 음료를 마시기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because my family drinks them.
+(나는 가족들이 제로슈가 음료를 마시기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because close people expect me to buy them.
+(나는 가까운 사람들이 내가 제로슈가 음료를 살 거라고 기대하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because the atmosphere around me chooses them.
+(나는 주변에서 제로슈가 음료를 선택하는 분위기여서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I feel accepted by other people.
+(나는 다른 사람들에게 받아들여진다고 느끼기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I want to make my perception to others better.
+(나는 나에 대한 인식을 더 좋게 만들고 싶기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I can give a good impression to others.
+(나는 다른 사람들에게 좋은 인상을 줄 수 있기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I want to be socially recognized.
+(나는 사회적으로 인정받고 싶기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because it is important that other people like the drink I am drinking.
+(나는 다른 사람들이 내가 마시는 음료를 좋아해 주는 것이 중요해서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I tend to choose brands that other people will view favorably.
+(나는 다른 사람들이 좋게 볼 것 같은 브랜드를 고르는 편이라서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I feel a sense of belonging when following brands that people around me drink.
+(나는 주변 사람들이 마시는 브랜드를 따라 마시면 소속감을 느껴서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I want to choose brands that people I look up to drink.
+(나는 닮고 싶은 사람이 마시는 브랜드를 선택하고 싶어서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because most family members usually drink them.
+(나는 가족 구성원 대부분이 평소 제로슈가 음료를 마시기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because most family members purchase them.
+(나는 가족 구성원 대부분이 제로슈가 음료를 구매하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because most friends I consider important purchase them.
+(나는 내가 중요하게 생각하는 친구들 대부분이 제로슈가 음료를 구매하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because people in the area where I live purchase them.
+(나는 내가 사는 지역의 사람들이 제로슈가 음료를 구매하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I think the general public purchases them.
+(나는 일반 대중이 제로슈가 음료를 구매한다고 생각하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I can easily obtain them in the market.
+(나는 시중에서 쉽게 구할 수 있기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because there are diverse choices of brands and tastes.
+(나는 브랜드와 맛의 선택지가 다양하기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I can easily purchase them in places I frequently visit (convenience stores, vending machines, cafes, etc.).
+(내가 자주 가는 곳(편의점·자판기·카페 등)에서 쉽게 구입할 수 있기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I feel the utility compared to price is decent.
+(나는 가격 대비 효용이 괜찮다고 느끼기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because the price is reasonable compared to quality.
+(나는 품질 대비 가격이 합리적이기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I feel the price is affordable compared to other beverages.
+(나는 다른 음료와 비교해도 부담되지 않는 가격이라고 느끼기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because I feel the taste is better than regular products.
+(나는 제로슈가 음료가 일반 제품보다 맛이 더 낫다고 느껴서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because the taste is not significantly different from regular products.
+(나는 제로슈가 음료가 일반 제품과 맛이 크게 다르지 않아서 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because it does not ruin the taste of food.
+(나는 음식 맛을 해치지 않기 때문에 제로슈가 음료를 마신다.)
+- I drink zero-sugar beverages because the taste feels less sweet and light.
+(나는 맛이 덜 달고 가볍게 느껴지기 때문에 제로슈가 음료를 마신다.)
+- I think I know zero-sugar beverages very well.
+(나는 제로슈가 음료를 잘 알고 있다고 생각한다.)
+- I feel that I do not know much about zero-sugar beverages.
+(나는 제로슈가 음료에 대해 잘 모른다고 느껴진다.)
+- Among my friends, I belong to the relatively knowledgeable 'expert' regarding zero-sugar beverages.
+(내 친구들 사이에서 나는 제로슈가 음료를 비교적 잘 아는 “전문가”에 속한다.)
+- Honestly, I am not very knowledgeable about zero-sugar beverages.
+(제로슈가 음료에 대해서는 솔직히 잘 아는 편이 아니다.)
+- Zero-sugar beverages are important to me.
+(제로슈가 음료는 나에게 중요하다.)
+- Zero-sugar beverages are highly relevant to me.
+(제로슈가 음료는 나와 관련성이 크다.)
+- Zero-sugar beverages have great meaning to me.
+(제로슈가 음료는 나에게 의미가 크다.)
+- I am very interested in zero-sugar beverages.
+(나는 제로슈가 음료에 관심이 많다.)
+- Zero-sugar beverages are useful to me.
+(제로슈가 음료는 나에게 유용하다.)
+- I think a lot about my health.
+(나는 내 건강에 대해 깊은 생각을 많이 한다.)
+- I pay attention to my health status in daily life.
+(나는 일상생활 중 내 건강 상태에 주의를 기울인다.)
+- I am sensitive to changes in my health status.
+(나는 내 건강 상태의 변화를 민감하게 알아차린다.)
+- I am well aware of how my body feels in daily life.
+(나는 일상생활 중 내 몸 상태가 어떤지 잘 알아차린다.)
+- I actively engage in health management.
+(나는 건강 관리에 적극적으로 관여한다.)
+- I would like my body to look very slim.
+(나는 내 몸이 매우 날씬해 보이면 좋겠다.)
+- I want my body to look almost free of fat.
+(나는 내 몸이 지방이 거의 없어 보이길 원한다.)
+- I frequently think about having a slim appearance.
+(나는 날씬해 보이는 외모에 대해 자주 생각한다.)
+- I feel pressure from the media to be slim.
+(나는 미디어로부터 날씬해져야 한다는 압박을 느낀다.)
+- I feel pressure from the media to reduce body fat.
+(나는 미디어로부터 체지방을 줄여야 한다는 압박을 느낀다.)
+- I like zero-sugar beverages.
+(나는 제로슈가 음료가 좋다.)
+- I have a favorable feeling toward zero-sugar beverages.
+(나는 제로슈가 음료에 호감이 간다.)
+- I am satisfied with zero-sugar beverages.
+(나는 제로슈가 음료가 마음에 든다.)
+- The likelihood of purchasing zero-sugar beverages is high.
+(제로슈가 음료를 구매할 가능성이 높다.)
+- If I need something to drink, the likelihood of choosing zero-sugar beverages is high.
+(마실 것이 필요할 경우, 제로슈가 음료를 선택할 가능성이 높다.)
+- I will actively use zero-sugar beverages.
+(나는 적극적으로 제로슈가 음료를 이용해 볼 것이다.)
+- If a friend asks me to recommend something to drink, I will recommend zero-sugar beverages.
+(친구가 나에게 마실 것을 추천해달라고 할 경우, 제로슈가 음료를 추천하겠다.)
+- I will speak positively to other people about my experience of drinking zero-sugar beverages.
+(나는 제로슈가 음료를 마신 경험을 다른 사람들에게 긍정적으로 말할 것이다.)
+- I will talk positively about zero-sugar beverages to other people.
+(나는 제로슈가 음료에 대해 다른 사람들에게 긍정적으로 이야기할 것이다.)
+- I will recommend zero-sugar beverages to other people.
+(나는 제로슈가 음료를 다른 사람들에게 추천할 것이다.)</t>
+        </is>
+      </c>
+      <c r="O953" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>953</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>유鑫 (지도교수: 이해완)</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>저작권법상 캐릭터의 보호에 관한 연구</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>성균관대학교 일반대학원 법학과 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>분리관찰설, 본질설, 아이디어와 표현의 이분법, 개발정도 테스트(Specificity test), 이야기 구성 테스트(Story being told test)</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>[캐릭터의 창작적 표현(IV)] -&gt; [실질적 유사성 판단(Mediator)] -&gt; [저작권 침해 여부(DV)]</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>본 논문은 실증 연구 논문이 아니며, 가설 검증 형태가 아닌 문헌 연구, 판례 분석, 비교 법적 분석을 통해 캐릭터의 독자적 저작물성 인정 여부와 보호 범위를 검토함</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>캐릭터의 창작적 표현 (시각적 캐릭터 및 어문적 캐릭터의 형상, 묘사, 비문언적 표현)</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>저작권 침해 여부 및 독자적 저작물성 인정 여부</t>
+        </is>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>실질적 유사성 (Substantial Similarity)</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>캐릭터는 구체적 표현에 창작성이 있는 경우 원저작물과 별개로 저작권법상 독자적 저작물로 보호될 수 있으며, 시각적 캐릭터는 창작적 시각 형상을 통해, 어문적 캐릭터는 개별 캐릭터보다 집합적 캐릭터의 비문언적 표현(사건 전개 및 인물 상호작용)을 통해 보호받을 가능성이 높음. 다만 아이디어, 캐릭터 명칭, 공공 영역의 요소는 보호 범위에서 제외됨.</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O954" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>954</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>이지윤</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>인플루언서 마케팅의 광고 고지 유형과 정보원 속성이 소비자 태도와 행동 의도에 미치는 영향: 건강기능식품을 중심으로</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 박사학위 논문</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>설득지식모델(Persuasion Knowledge Model), 귀인 이론(Attribution Theory), 컴퓨터 매개 커뮤니케이션 진정성 모델(Authenticity model of computer-mediated communication), 설득에 대한 저항을 극복하는 즐거움 모델(The entertainment overcoming resistance model)</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>[독립변수: 광고 고지 유형, 정보원 속성] -&gt; [매개변수: 진정성 -&gt; 반박주장] -&gt; [종속변수: 제품에 대한 태도, 구매 의도, 공유 의도]</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>연구 가설은 연구 2와 연구 3에 걸쳐 검증됨. 연구 2는 정보원 유형과 광고 고지 유형(경험 강조 여부)에 따른 진정성, 반박주장, 제품 태도, 구매 의도, 공유 의도의 차이 및 순차적 매개효과를 검증하며, 연구 3은 보상 고지 유형(금전적 vs 물질적)에 따른 효과와 진정성의 조절효과를 검증함.</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>광고 고지 유형(경험 강조 고지, 보상 고지 유형 등), 정보원 속성(전문가, 일반인)</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>제품에 대한 태도, 구매 의도, 공유 의도</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>진정성, 반박주장</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>진정성 (연구 3의 조절변수)</t>
+        </is>
+      </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>경험을 강조하는 광고 고지 유형은 일반인 콘텐츠에서 가장 긍정적인 효과를 나타냈으며, 전문가 콘텐츠에서도 긍정적 효과가 확인됨. 진정성 증가에 따른 반박주장 감소의 순차적 매개효과는 실제 팔로우하는 일반인에 대해서만 유의미하게 나타남. 보상 고지 유형에서는 금전적 보상 고지와 일반인 콘텐츠일 때 태도와 행동 의도가 더 높게 나타났으며, 진정성의 조절효과는 소비자가 전문가의 진정성을 평균보다 낮게 평가했을 때만 유의미하게 작용함.</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O955" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>955</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>백지현</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>유튜브의 지속이용의도에 영향을 미치는 요인에 관한 연구: 확장된 후기수용모델을 중심으로</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>고려대학교 기술경영전문대학원 박사학위논문</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>이용과 충족이론(UGT), 확장된 통합기술수용이론(UTAUT2), 후기수용모델(PAM), 혁신확산 이론(IDT)</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>[이용동기(정보추구, 재미추구, 관계추구), 가격가치, 기대일치, 인지된 유용성] -&gt; [만족도, 인지된 유용성] -&gt; [지속이용의도] (조절변수: 연령, 성별, 개인혁신성)</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>H1: 정보추구 동기가 만족도에 정(+)의 영향을 미칠 것이다.
+H2: 재미추구 동기가 만족도에 정(+)의 영향을 미칠 것이다.
+H3: 관계추구 동기가 만족도에 정(+)의 영향을 미칠 것이다.
+H4: 가격가치가 만족도에 정(+)의 영향을 미칠 것이다.
+H5: 기대일치가 만족도에 정(+)의 영향을 미칠 것이다.
+H6: 기대일치가 인지된 유용성에 정(+)의 영향을 미칠 것이다.
+H7: 인지된 유용성이 만족도에 정(+)의 영향을 미칠 것이다.
+H8: 인지된 유용성이 지속이용의도에 정(+)의 영향을 미칠 것이다.
+H9: 만족도가 지속이용의도에 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>정보추구 동기, 재미추구 동기, 관계추구 동기, 가격가치, 기대일치</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>지속이용의도</t>
+        </is>
+      </c>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>만족도, 인지된 유용성</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>연령, 성별, 개인혁신성</t>
+        </is>
+      </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>정보추구 동기, 재미추구 동기, 가격가치, 기대일치는 만족도에 긍정적인 영향을 미치며, 특히 재미추구 동기가 만족도에 가장 큰 영향을 미치는 것으로 나타났다. 유튜브의 지속이용의도에는 만족도와 인지된 유용성이 긍정적인 영향을 미치며, 인지된 유용성이 지속이용의도를 결정하는 핵심 요인으로 확인되었다. 또한 연령, 성별, 개인혁신성의 조절효과가 유의하게 검증되었다.</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O956" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>956</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>감경일</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>정책자금 목적별 지원이 기업 생애주기 단계별 성과에 미치는 효과: 중소벤처기업진흥공단 정책자금을 중심으로</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>서울대학교 행정대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>기업 생애주기 이론, 시장실패 이론, 정책자금 추가성 이론</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>[정책자금 지원(목적별/생애주기별)] -&gt; [경영 의사결정 및 자금용처 변화] -&gt; [중간성과(투자, 조직, 사업구조 변화)] -&gt; [최종성과(초과성과: 성장성, 수익성, 고용, 재무안정성)]</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>H1: 정책자금 수혜는 수혜기업의 성과를 동종 집단 평균 대비 유의하게 향상시킬 것이다. (H1-1: 성장성, H1-2: 수익성, H1-3: 고용, H1-4: 재무안정성)
+H2: 정책자금의 선행 개선 지표는 기업의 생애주기에 따라 차별적으로 나타날 것이다. (H2-1: 창업기는 성장·고용 선행 및 수익성 지연, H2-2: 재도약기는 재무안정성 선행 및 성장·수익성 후행)</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>정책자금 지원 (창업기/재도약기 목적별 트랙)</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>기업 생애주기 단계별 초과성과 (Abnormal Performance: 성장성, 수익성, 고용, 재무안정성)</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>기업 생애주기 (창업기, 재도약기)</t>
+        </is>
+      </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>창업기 기업(링크플로우)의 경우 정책자금이 정보 비대칭과 무담보·무실적에 기인한 초기 자금제약을 완화하는 '존속 보장(lifeline)' 역할을 수행하여 성장률과 고용 증가율에서 동종 집단 대비 초과성과를 보였으나 단기 수익성은 지연 개선됨. 재도약기 기업(지성중공업)의 경우 정책자금이 유동성 완충 및 채무 재조정의 촉매로 작용하여 재무안정성 지표(부채비율, 이자보상배율)에서 동종 집단 대비 유의미한 초과성과가 확인되었으나 단기 수익성 효과는 제한적이었음. 즉, 정책자금의 한계효과는 기업의 생애주기에 따라 상이하게 나타나며 창업기에는 자본의 첫 단추, 재도약기에는 연착륙 장치로 작동함.</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O957" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>957</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>최창환</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>인공지능 신뢰 정도가 공익목적 개인정보 제공의도에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>서울대학교 대학원 정책학석사 학위논문</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>프라이버시 계산이론, 보호동기이론</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>[인공지능 신뢰 정도] -&gt; [개인정보자기결정권 효능감] -&gt; [공익목적 개인정보 제공의도]</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>H1: 인공지능 신뢰 정도가 높을수록 공익목적 개인정보 제공의도는 높아질 것이다.
+H2: 인공지능 신뢰 정도는 개인정보자기결정권 효능감에 의해 매개되어 공익목적 개인정보 제공의도에 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>인공지능 신뢰 정도</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>공익목적 개인정보 제공의도</t>
+        </is>
+      </c>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>개인정보자기결정권 효능감</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>첫째, 인공지능 신뢰 정도가 공익목적 개인정보 제공의도에 정(+)의 유의한 영향을 미치는 것으로 확인되었다. 둘째, 개인정보자기결정권 효능감은 인공지능 신뢰 정도와 공익목적 개인정보 제공의도 간의 관계를 부분 매개하는 것으로 확인되었다. 셋째, 통제변수 중 디지털 역량이 공익목적 개인정보 제공의도에 가장 강한 정(+)의 영향을 미치는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>- 인공지능과 로봇이 작업을 수행할 때, 그 결과는 사람이 같은 일을 할 때보다 더 객관적인 경향이 있다.
+(When artificial intelligence and robots perform tasks, the results tend to be more objective than when humans do the same work.)
+- 인공지능과 로봇의 작업 과정은 투명하게 공개될 수 있어, 그들의 의사결정 과정은 쉽게 훼손되지 않을 것이다.
+(The working process of artificial intelligence and robots can be disclosed transparently, so their decision-making process will not be easily compromised.)
+- 인공지능과 로봇은 높은 정확도를 가지고 있어, 기계가 제공하는 정보는 사람보다 오류가 적은 경향이 있다.
+(Artificial intelligence and robots have high accuracy, so the information provided by machines tends to have fewer errors than that of humans.)
+- 인공지능과 로봇은 개인적 이해관계가 없으므로, 그들의 의사결정은 상대적으로 편향되지 않을 가능성이 높다.
+(Since artificial intelligence and robots have no personal interests, their decisions are likely to be relatively unbiased.)
+- 인공지능은 인간이 더 나은 판단을 내리는 데 도움을 줄 수 있는 유용한 도구다.
+(Artificial intelligence is a useful tool that can help humans make better judgments.)
+- 인공지능은 정보의 사실 여부를 검증하는 데 효과적으로 활용될 수 있다.
+(Artificial intelligence can be effectively utilized to verify the truth of information.)
+- 개인은 지능정보활용 능력을 이용하여 자신의 개인정보 노출 정도를 선택하고 능동적으로 결정할 수 있을 것이다.
+(Individuals will be able to select and actively determine the degree of exposure of their personal information by using intelligent information utilization capabilities.)
+- 귀하는 서비스나 앱을 이용하면서 공익을 위해 대학 및 연구기관이 개인정보를 사용하도록 허용하는 것을 어느 정도 받아들일 수 있습니까?
+(To what extent can you accept allowing universities and research institutes to use personal information for the public interest while using services or apps?)
+- 온라인 간편결제(네이버페이, 카카오페이 등)를 이용해 물건을 살 수 있다.
+(I can buy things using online easy payment methods such as Naver Pay and Kakao Pay.)
+- 당근마켓과 같은 중고 거래 앱을 통해 새 상품보다 저렴한 가격에 물건을 구매할 수 있다.
+(I can purchase items at a lower price than new products through secondhand trading apps like Danggeun Market.)
+- 행정업무처리(민원서류 열람 및 발급, 공과금 조회 및 납부 등)를 위한 전자민원서비스를 이용할 수 있다.
+(I can use electronic civil petition services for administrative tasks such as viewing and issuing civil petition documents, and checking and paying utility bills.)
+- 인터넷이나 앱을 이용해 교통수단(기차, 버스, 택시 등)을 예약/호출할 수 있다.
+(I can reserve or call transportation means such as trains, buses, and taxis using the internet or apps.)
+- 스마트폰 앱을 통해 언제 어디서나 보험 상품 등에 가입할 수 있다.
+(I can subscribe to insurance products anytime and anywhere through smartphone apps.)
+- 키오스크로 음식 주문, 영화티켓 및 교통수단 승차권 구매, 병원 수납 등을 할 수 있다.
+(I can order food, purchase movie tickets and transportation tickets, and pay hospital bills using kiosks.)
+- 방송통신심의위원회가 무슨 일을 하는지 알고 있다.
+(I know what the Korea Communications Standards Commission does.)
+- 피싱을 당했을 때, 신고하는 방법과 피해 구제방법을 알고 있다.
+(When scammed by phishing, I know how to report it and seek remedies for damages.)
+- 저작권(동영상, 글 등)이 침해됐을 때, 신고하고 피해를 구제 받는 방법을 알고 있다.
+(When copyright such as videos and writings is infringed, I know how to report it and receive remedies for damages.)
+- 포털이나 소셜미디어에서 누군가 내 권리(명예훼손, 저작권침해 등)를 침해했을 때 신고하는 방법을 안다.
+(I know how to report when someone infringes on my rights such as defamation or copyright infringement on portals or social media.)
+- 스마트폰 앱을 통해 불법 사이트나 사이버범죄를 즉시 신고하고 실시간으로 처리 상황을 확인할 수 있다.
+(Through smartphone apps, I can immediately report illegal sites or cybercrimes and check the processing status in real time.)
+- 팩트체크 툴을 사용하여 온라인 정보의 신뢰성을 실시간으로 검증하고 원본 출처를 추적할 수 있다.
+(I can use fact-checking tools to verify the reliability of online information in real time and trace the original source.)
+- 다른 자료들과 비교해 검색 결과에서 믿을만한 정보를 구별할 수 있다.
+(I can distinguish reliable information from search results compared to other materials.)
+- 광고성 정보를 구별해 낼 수 있다.
+(I can distinguish promotional information.)
+- 방문한 사이트의 신뢰도를 실시간으로 확인하고 피싱 및 사기 사이트를 자동으로 차단할 수 있다.
+(I can check the reliability of visited sites in real-time and automatically block phishing and scam sites.)
+- 모바일 앱을 사용하여 스마트폰으로 촬영한 영상을 편집할 수 있다.
+(I can edit videos filmed with a smartphone using mobile apps.)
+- 모바일 앱으로 사진을 보정하고, 원하는 스타일로 변환하거나 없는 요소를 추가할 수 있다.
+(I can retouch photos with mobile apps, convert them to desired styles, or add missing elements.)
+- 드라마, 애니메이션, 뮤직비디오, 영화 등의 영상을 숏폼 콘텐츠로 변환할 수 있다.
+(I can convert videos such as dramas, animations, music videos, and movies into short-form contents.)
+- 시민 참여 플랫폼을 통해 국회의원 및 지방의원 선거의 온라인 투표에 참여하고, 크라우드펀딩으로 정당이나 후보자를 실시간 후원할 수 있다.
+(Through civic participation platforms, I can participate in online voting for national assembly member and local council member elections, and sponsor political parties or candidates in real-time through crowdfunding.)
+- 정치/사회 문제에 대해 토론하거나 서명/청원 등을 할 수 있다.
+(I can debate political and social issues or participate in signatures and petitions.)
+- 기부 플랫폼을 통해 실시간으로 전 세계 다양한 프로젝트에 암호화폐 등으로 기부할 수 있다.
+(Through donation platforms, I can donate in real-time to various projects around the world using cryptocurrency and others.)
+- 소셜미디어 앱의 개인정보 설정을 사용하여 게시물을 볼 수 있는 사람을 선택할 수 있다.
+(I can select who can view my posts by using the privacy settings of social media apps.)
+- AI 기반 통합 보안 앱을 설치하여 실시간으로 악성코드를 탐지하고 치료할 수 있다.
+(I can install AI-based integrated security apps to detect and cure malware in real-time.)
+- PC, 스마트폰, 태블릿PC에서 쿠키와 방문 기록을 삭제할 수 있다.
+(I can delete cookies and browsing history on PCs, smartphones, and tablet PCs.)
+- 서버에 귀하의 이용 정보 기록이 아래와 남을 수 있습니다. 이러한 이유로 해당 시스템 또는 서비스 이용을 주저한 적이 있습니까? - 맞춤형 마케팅 정보 제공에 동의하기
+(Your usage information records may remain on the server as below. Have you ever hesitated to use the system or service for this reason? - Agreeing to provide customized marketing information)</t>
+        </is>
+      </c>
+      <c r="O958" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="n">
+        <v>958</v>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>이지민</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>이중제형 건강기능식품 속성이 소비자 선호와 구매 의도에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>서울대학교 대학원 농학석사 학위논문</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>계획된행동이론, 속성기반선택이론, 가격민감도이론, 생애주기가설</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>[제품속성(제형, 가격, 기능성)] -&gt; [소비자선호(부분효용값, 상대적중요도)] (조절변수: 연령대, 소득수준)</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>H1: 제형은 가격 및 기능성보다 소비자 선호에 더 큰 영향을 미칠 것이다.
+H2: 20·30대 소비자는 고연령층보다 체지방 감소 기능성 속성에 더 높은 선호도를 보일 것이다.
+H3: 40대 소비자는 다른 연령대보다 가격 민감도가 높을 것이다.
+H4: 소득수준이 높을수록 가격 민감도는 낮을 것이다.
+H5: 60대 이상 소비자는 저연령층보다 제형 속성의 중요도를 더 높게 평가할 것이다.</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>제형, 가격, 기능성</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>소비자 선호도 (부분효용값, 상대적중요도)</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>연령대, 소득수준</t>
+        </is>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>이중제형 건강기능식품의 소비자 선호에 가장 큰 영향을 미치는 속성은 제형(65.40%)으로 나타났으며, 가격(24.79%)과 기능성(9.81%)이 그 뒤를 이었다. 제형 중에서는 정제와 액상의 조합이 가장 선호되었고, 분말과 액상의 조합은 상대적으로 낮은 선호도를 보였다. 연령대별로는 고령층일수록 제형의 중요도가 증가하였고, 40대는 가격에 대한 민감도가 다른 연령대보다 높았다. 소득수준별 분석에서는 저소득층이가격을 더 중시하는 반면, 고소득층은 제형을 더 중요하게 평가하는 경향이 확인되었다.</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>- The ranking of product profiles based on formulation, price, and functionality.
+(제형, 가격, 기능성을 바탕으로 한 제품 프로파일 순위 평가)
+- Demographic characteristics including age, monthly household income, and gender.
+(연령, 월 가구 소득, 성별을 포함한 인구통계학적 특성)</t>
+        </is>
+      </c>
+      <c r="O959" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="n">
+        <v>959</v>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>윤소영</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>유튜브 주류 협찬 광고의 법적 권고사항 분석: 인플루언서 유형별 차이를 중심으로</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>이화여자대학교 대학원 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>메시지해석과정 모델 (Message Interpretation Process Model)</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>[인플루언서 유형 및 콘텐츠 특성] -&gt; [주류 협찬 광고 내용 표현 (긍정적 묘사, 잘못된 음주 문화, 미성년자 보호 조치, 경고문구)]</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>연구문제 1: 주류 제품의 유튜브 협찬 광고에서 음주와 관련된 긍정적 내용 묘사는 인플루언서 유형별로 차이를 보이는가?
+연구문제 2: 주류 제품의 유튜브 협찬 광고에서 잘못된 음주 문화의 묘사는 인플루언서 유형별로 차이를 보이는가?
+연구문제 3: 주류 제품의 유튜브 협찬 광고에서 음주 후 문제 행동 묘사는 인플루언서 유형별로 차이를 보이는가?
+연구문제 4: 주류 제품의 유튜브 협찬 광고에서 미성년자의 보호를 위한 조치는 인플루언서 유형별로 차이를 보이는가?
+연구문제 5: 주류 제품의 유튜브 협찬 광고에서 경고문구 기입은 인플루언서 유형별로 차이를 보이는가?</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>인플루언서 유형 (연예인, 메가 인플루언서, 매크로 인플루언서, 마이크로 인플루언서)</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>주류 협찬 광고의 법적 권고사항 반영 여부 및 내용 표현 양상 (긍정적 묘사, 잘못된 음주 문화 묘사, 미성년자 보호 조치, 경고문구 기입)</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>유튜브 주류 협찬 광고에서 음주에 대한 긍정적 묘사(사회적 관계 도움, 분위기 개선, 긴장 완화 등)와 잘못된 음주 문화 묘사(과도한 음주, 과음 희화화, 폭탄주 제조, 음주 도전 등)는 주로 연예인 및 메가 인플루언서 콘텐츠에서 빈번하게 나타나 인플루언서 유형별 유의미한 차이를 보였다. 반면, 모든 콘텐츠에서 연령 제한 기능을 사용하지 않았으며, 실제 모델의 만 25세 미만 노출 등은 연예인 콘텐츠(아이돌 중심)에서만 확인되었다. 경고문구 기입률은 마이크로 인플루언서가 가장 높았으나, 전반적으로 국내외 규정의 사각지대와 미비점이 확인되었다.</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>- The video content depicts drinking as helpful for social relationships.
+(영상 콘텐츠는 음주가 사회적 관계에 도움이 되는 것으로 묘사하였다.)
+- The consumption or presence of alcohol implies improving mood or atmosphere.
+(주류의 소비나 존재가 기분이나 분위기를 개선시킨다는 암시를 포함하였다.)
+- The content includes expressions that drinking helps relieve tension.
+(콘텐츠는 긴장을 푸는 데 도움이 된다는 표현을 포함하였다.)
+- The content directly mentions the alcohol by volume (ABV).
+(콘텐츠는 알코올 도수를 직접적으로 언급하였다.)
+- The scene depicts drinking quickly and excessively.
+(장면은 빠르게 과도하게 마시는 음주 장면을 묘사하였다.)
+- Heavy drinking or loss of control is portrayed as fun or amusing.
+(과음이나 제어력 상실이 재미있거나 웃음거리로 적절하다는 암시를 포함하였다.)
+- The content depicts making bomb shots (such as somaek).
+(콘텐츠는 폭탄주 제조 장면을 묘사하였다.)
+- The content depicts challenging others to drink.
+(콘텐츠는 타인에게 음주를 도전하게 하는 묘사를 포함하였다.)
+- The actual model featured appears to be under 25 years of age.
+(실제 모델의 나이가 만 25세 미만이다.)
+- Warning messages regarding excessive drinking are included in the post or video.
+(게시글이나 영상에 과음 관련 경고문구가 기입되어 있다.)</t>
+        </is>
+      </c>
+      <c r="O960" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="n">
+        <v>960</v>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>김남수</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>온라인유통채널 서비스품질이가정간편식 구매자의 만족과 재이용의도에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>연세대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>기대일치-불일치 모델, E-SERVQUAL 모형</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>[온라인유통채널 서비스품질 하위요인(배송품질 및 시간, 포장·위생 및 신선도, 상품다양성, 고객맞춤형 정보제공, 상품차별성, 정보 및 리뷰 신뢰성, 거래편의성, 프로모션 혜택, 친환경활동)] -&gt; [고객만족] -&gt; [재이용의도]</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>H1. 온라인 유통채널의 서비스품질은 간편식 구매자의 만족에 유의한 정(+)의 영향을 미칠 것이다.
+H2. 온라인 유통채널의 서비스품질은 간편식 구매자의 재이용의도에 유의한 정(+)의 영향을 미칠 것이다.
+H3. 고객만족은 재이용의도에 유의한 정(+)의 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>온라인유통채널 서비스품질 (배송품질 및 시간, 포장·위생 및 신선도, 상품다양성, 고객맞춤형 정보제공, 상품차별성, 정보 및 리뷰 신뢰성, 거래편의성, 프로모션 혜택, 친환경활동)</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>재이용의도</t>
+        </is>
+      </c>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>고객만족</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>온라인 유통채널의 서비스품질 하위요인 중 배송품질 및 시간, 포장·위생 및 신선도, 상품다양성, 정보 및 리뷰 신뢰성, 거래편의성, 프로모션 혜택은 고객만족에 유의한 정(+)의 영향을 미쳤으며, 배송품질 및 시간, 포장·위생 및 신선도, 상품다양성, 거래편의성, 프로모션 혜택은 재이용의도에도 유의한 정(+)의 영향을 미치는 것으로 나타났다. 또한 고객만족은 재이용의도에 유의한 정(+)의 영향을 미치는 핵심 변수임이 입증되었다.</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>- 주문한 상품이 정확하게 (누락/오배송 없이) 도착한다.
+(The ordered products arrive accurately without omission or misdelivery.)
+- 배송 과정에서 상품이 파손되거나 손상 없이 잘 보존된다.
+(Products are well preserved without breakage or damage during the delivery process.)
+- 상품이 약속된 배송 시간에 맞춰 도착한다.
+(Products arrive on time according to the promised delivery schedule.)
+- 포장이 위생적이고 청결하다.
+(The packaging is hygienic and clean.)
+- 제품이 변질 없이 안전하게 전달된다.
+(Products are delivered safely without deterioration.)
+- 소비기한이 충분히 남아 있다.
+(There is plenty of shelf life remaining.)
+- 다양한 종의 간편식 상품을 제공한다.
+(It provides a variety of home meal replacement products.)
+- 여러 브랜드/메뉴 선택이 가능하다.
+(Various brand and menu selections are available.)
+- 신제품이 빠르게 업데이트된다.
+(New products are updated quickly.)
+- 내 취향에 맞는 제품을 추천해준다.
+(It recommends products that suit my taste.)
+- 나에게 맞는 혜택을 미리 알려준다.
+(It informs me of benefits tailored to me in advance.)
+- 부가 혜택을 받을 수 있는 방법을 알려준다.
+(It guides me on how to receive additional benefits.)
+- 이 채널에서만 구매할 수 있는 전용 상품이 있다.
+(There are exclusive products that can only be purchased on this channel.)
+- 전용상품의 종류가 다양하다.
+(The types of exclusive products are diverse.)
+- 전용상품의 품질이 타 채널보다 우수하다.
+(The quality of exclusive products is superior to other channels.)
+- 제품 정보(성분·조리법·보관법 등)가 충분하다.
+(Product information such as ingredients, recipes, and storage methods is sufficient.)
+- 제품 설명과 실제품질이 일치한다.
+(Product descriptions match the actual product quality.)
+- 리뷰·평점이 신뢰할 만하다.
+(Reviews and ratings are reliable.)
+- 상품 검색과 비교가 쉽다.
+(Product search and comparison are easy.)
+- 주문·결제 과정이 간편하다.
+(The ordering and payment processes are simple.)
+- 취소·환불 등 사후처리 절차가 신속하고 원활하다.
+(After-sales procedures such as cancellation and refund are prompt and smooth.)
+- 쿠폰·적립금·할인 등 혜택이 다양하다.
+(Benefits such as coupons, reward points, and discounts are diverse.)
+- 이벤트·프로모션이 정기적으로 제공된다.
+(Events and promotions are provided regularly.)
+- 혜택 정보가 명확하고 적용이 편리하다.
+(Benefit information is clear and application is convenient.)
+- 과대포장을 지양하고 친환경 포장재를 사용한다.
+(It avoids excessive packaging and uses eco-friendly packaging materials.)
+- 재활용 안내 및 분리배출 정보가 명확하다.
+(Recycling guides and separation disposal information are clear.)
+- 친환경·지속가능성 관련 활동을 수행한다.
+(It performs eco-friendly and sustainability-related activities.)
+- 이 온라인 유통채널을 통한 간편식 구매 경험에 전반적으로 만족한다.
+(I am generally satisfied with the experience of purchasing home meal replacement through this online distribution channel.)
+- 이 채널의 간편식 품질과 서비스는 나의 기대를 충족시켰다.
+(The quality and service of home meal replacement on this channel met my expectations.)
+- 이 채널을 이용한 간편식 구매 경험은 전반적으로 긍정적이다.
+(The experience of purchasing home meal replacement using this channel is generally positive.)
+- 이 채널은 다른 채널보다 간편식 구매 만족도가 높다.
+(This channel has higher satisfaction with home meal replacement purchases than other channels.)
+- 앞으로도 이 온라인 유통채널을 통해 간편식을 다시 구매할 의향이 있다.
+(I intend to purchase home meal replacement again through this online distribution channel in the future.)
+- 앞으로도 해당 채널을 계속 이용할 것이다.
+(I will continue to use this channel in the future.)
+- 주변 사람들에게 이 채널을 추천하고 싶다.
+(I want to recommend this channel to people around me.)
+- 이 채널에서 새로운 간편식이나 관련 상품이 출시될 경우 구매할 가능성이 높다.
+(There is a high possibility of purchasing if new home meal replacement or related products are launched on this channel.)</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="n">
+        <v>961</v>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>임승표</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>온라인 맞춤형 광고와 개인정보 보호에 관한 연구</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>연세대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>개인정보보호이론, 정보자기결정권이론, 프라이버시 경제학</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>[온라인 행태정보 수집 및 처리] -&gt; [개인정보 침해 및 정보 비대칭 발생] -&gt; [개인정보 보호법 및 글로벌 규제(GDPR, CCPA) 적용 / 동의의 한계] -&gt; [정책적 개선방안 및 자율규제(TCF, Privacy Manifest) 도입]</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>본 연구는 가설 검정을 목적으로 하는 실증 연구가 아닌 문헌 연구, 비교법적 분석 및 사례 분석 중심의 법적·정책적 연구이므로 별도의 가설이 존재하지 않음.</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>온라인 맞춤형 광고 생태계 내 행태정보 수집 및 처리 방식 (쿠키, 픽셀, SDK 등)</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>이용자의 개인정보 자기결정권 및 프라이버시 보호 수준</t>
+        </is>
+      </c>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>온라인 맞춤형 광고는 쿠키, 픽셀, SDK 등 다양한 추적 기술을 통해 광범위한 행태정보를 수집·프로파일링하므로 정보 비대칭과 사생활 침해 위험을 초래한다. 2022년 구글·메타 과징금 부과 사례에서 확인되듯, 행태정보는 다른 정보와 결합 시 개인정보에 해당하며 플랫폼 사업자가 실질적 처리 주체로서 명확한 사전 동의를 받을 의무가 있다. 그러나 현행 '동의' 제도는 복잡한 광고 생태계 속에서 정보주체가 내용을 충분히 인지하지 못한 채 형식적으로 이루어지며, 동의 철회 시 이미 유통된 데이터의 회수가 불가능하다는 구조적 한계를 지닌다. 따라서 법적 규제 외에도 IAB Europe의 TCF나 애플의 Privacy Manifest와 같은 기술 표준 및 자율규제 프레임워크를 연계하여 투명성을 높이고 실질적인 동의·철회 권한을 보장해야 한다.</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O962" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="n">
+        <v>962</v>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>박지연</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>알고리즘 추천 서비스에 대한 소비자 저항 요인 탐색 : 혁신 저항 이론을 중심으로</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>혁신 저항 이론 (Innovation Resistance Theory)</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>[소비자 특성, 알고리즘 특성] -&gt; [기능적 장벽, 심리적 장벽] -&gt; [소비자 저항]</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>본 연구는 가설을 명시적으로 번호(H1, H2 등) 매겨 검정하기보다, 탐색적 요인 분석을 통해 요인을 추출하고 상관관계 및 위계적 회귀분석을 수행하는 연구 문제(Research Questions) 중심의 탐색적 연구 모형으로 구성됨.</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>소비자 특성(알고리즘 리터러시, 인지 욕구, 알고리즘 불안, 신기성 추구, 알고리즘 기술 통제감, 알고리즘 효능감), 알고리즘 특성(투명성, 설명 가능성, 공정성)</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>소비자 저항</t>
+        </is>
+      </c>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>소비자 특성 6가지 요인(알고리즘 리터러시, 인지 욕구, 알고리즘 불안, 신기성 추구, 알고리즘 기술 통제감, 알고리즘 효능감)과 알고리즘 특성 3가지 요인(투명성, 설명 가능성, 공정성)을 도출하였으며, 위계적 회귀분석 결과 알고리즘 불안, 기술 통제감, 투명성 등이 소비자 저항에 유의미한 영향을 미치는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>- I always look for new ideas and experiences.
+(나는 항상 새로운 아이디어와 경험을 찾는다)
+- When things get boring, I like to find new and familiar things.
+(지루해질 때 새롭고 친숙한 것들에 대해 발견하는 것을 좋아한다)
+- I like my life to change constantly.
+(나는 내 삶이 끊임없이 변화하는 것이 좋다)
+- I enjoy experiencing novelty and change in my daily life.
+(나는 일상 속에서 새로움과 변화를 경험하는 것을 즐긴다)
+- I prefer complex problems to simple problems.
+(나는 단순한 문제보다도 복잡한 문제를 더 좋아한다)
+- I find it fun to think about new solutions to problems.
+(나는 어떤 문제에 대한 새로운 해결방법을 고민하는게 재미있다)
+- I try to solve difficult and time-consuming problems to the end if possible.
+(나는 어렵고 시간이 많이 드는 문제도 가능한 끝까지 풀기 위해 노력한다)
+- I am more active in tasks that require a lot of thought than tasks that are low in importance and do not require much thought.
+(나는 중요도가 낮고 많은 생각할 필요가 없는 일보다 많은 생각을 필요로 하는 일에 더욱 적극적이다)
+- I don't feel that thinking activities are fun.
+(나는 생각하는 활동을 재미있다고 느끼지 않는다)
+- I prefer things that do not require much thought rather than things that challenge my thinking ability.
+(나는 내 사고 능력에 도전하는 일보다는 생각을 많이 하지 않아도 되는 일이 좋다)
+- I feel helpless when dealing with electronic devices and try not to touch them if possible.
+(나는 전자기기를 다룰 때 무력함을 느껴 가능한 손대지 않으려고 한다)
+- My solving technical problems is mostly due to good luck.
+(내가 기술적인 문제를 해결하는 것은 주로 운이 좋아서 해결되는 것이다)
+- Most technical problems feel too complex to make sense to deal with.
+(대부분의 기술 문제는 너무 복잡해서 다루는 것이 의미 없다고 느껴진다)
+- Since I have solved technical problems well before, I am optimistic that I can solve future problems as well.
+(이전에 기술 문제를 잘 해결해왔기 때문에, 앞으로의 문제도 잘 해결할 수 있을 것이라고 낙관한다)
+- Electronic devices are often too complex and difficult to control.
+(전자 기기는 종종 너무 복잡하고 제어하기 어려움)
+- Even if I encounter technical problems, I try to solve them.
+(나는 기술적인 문제에 부딪히더라도, 문제를 해결하기 위해 노력한다)
+- I enjoy solving technical problems.
+(나는 기술적인 문제를 해결하는 것을 즐긴다)
+- I can solve many technical problems I face on my own.
+(나는 직면한 많은 기술적인 문제를 혼자서 해결할 수 있다)
+- Algorithms are not scary at all to me.
+(알고리즘은 나에게 전혀 무섭지 않다)
+- Working with algorithms makes me anxious.
+(알고리즘으로 작업하는 것은 나를 불안하게 만든다)
+- Algorithm recommendation services make me uncomfortable.
+(알고리즘 추천 서비스는 나를 불편하게 만든다)
+- Algorithm recommendation services make me anxious.
+(알고리즘 추천 서비스는 나를 불안하게 만든다)
+- Algorithms are used to present recommendation services to me on the platform.
+(알고리즘은 플랫폼 상에서 나에게 추천서비스를 제시하는 데 사용된다)
+- Algorithms operate to prioritize certain recommended items over others.
+(알고리즘은 특정 추천 항목을 다른 것보다 우선시하도록 작동한다)
+- Algorithms are used to provide me with personalized recommendation services.
+(알고리즘은 나에게 맞춤형 추천 서비스를 제공하는데 사용된다)
+- Algorithms show me different recommendation services on the platform than others see.
+(알고리즘은 플랫폼에서 다른 사람에게 내가 보는 것과 다른 추천 서비스를 보여준다)
+- Algorithms are used to show me recommendation services based on automated decisions.
+(알고리즘은 자동회된 결정에 따라 나에게 추천 서비스를 보여주는데 사용된다)
+- Algorithms do not require human judgment when deciding which recommendation services to show.
+(알고리즘이 어떤 추천 서비스를 보여줄 지 결정할 때 사람의 판단을 필요로 하지 않는다)
+- Algorithms automatically decide which recommendation services I will see.
+(알고리즘은 어떤 추천 서비스를 보게 될 지 자동으로 결정한다)
+- The recommendation services algorithms suggest to me depend on my online behavior and activities using the platform.
+(알고리즘이 나에게 추천하는 서비스는 해당 플랫폼을 사용하는 나의 온라인 행동 및 활동에 따라 달라진다)
+- The recommendation services algorithms suggest to me are determined by my online behavior data.
+(알고리즘이 나에게 추천하는 서비스는 나의 온라인 행동 데이터에 따라 결정된다)
+- The recommendation services algorithms suggest to me depend on the data I provide online.
+(알고리즘이 나에게 추천하는 서비스는 내가 온라인 상에서 제공한 데이터에 따라 달라진다)
+- The reason algorithms show me certain content is not always clear.
+(알고리즘이 나에게 특정 콘텐츠를 보여주는 이유는 항상 명확하지 않다)
+- The recommendation services algorithms suggest to me can be influenced by human biases such as prejudice or stereotypes.
+(알고리즘이 나에게 추천하는 서비스는 편견이나 고정관념과 같은 인간의 편향에 영향을 받을 수 있다)
+- Algorithms use my personal information to present recommendation services, which can affect my online privacy.
+(알고리즘은 나의 개인정보를 이용해 추천 서비스를 제시하며 이는 나의 온라인 프라이버시에 영향을 미칠 수 있다)
+- Algorithms do not show favoritism and do not discriminate against people.
+(알고리즘은 편애하지 않으며, 사람들을 차별하지 않는다)
+- Data sources across algorithms are identified, recorded, and evaluated according to standards.
+(알고리즘 전반에 걸친 데이터 출처는 식별되고 기록되고 기준에 따라 평가된다)
+- I think algorithm recommendation services follow fair procedures without bias.
+(나는 알고리즘 추천 서비스가 편견 없이 공정한 절차를 따른다고 생각한다)
+- Algorithm recommendation systems need a responsible person in charge when they have negative impacts on individuals or society.
+(알고리즘 추천 시스템은 개인이나 사회에 부정적인 영향을 미쳤을 때, 책임질 수 있는 담당자가 필요하다고 생각한다)
+- Algorithms should be designed so that third parties can inspect and review how they work.
+(알고리즘은 제 3자가 작동 방식을 검사하고 검토할 수 있도록 설계되어야 한다)
+- Algorithms should have the ability to modify the entire system with only specific manipulations.
+(알고리즘은 특정한 조작만으로 시스템 전체를 수정할 수 있는 기능을 가져야 한다)
+- I think the evaluation methods and criteria of algorithms should be made public so that people can understand them.
+(알고리즘의 평가 방식과 기준은 공개되어 사람들이 이해할 수 있어야 한다고 생각한다)
+- The results produced by algorithmic systems should be understandable to those affected by them.
+(알고리즘 시스템이 만든 결과는 그 영향을 받는 사람들이 이해할 수 있어야 한다)
+- Algorithms should be able to show how understandable the internal state is to the user by looking at the results generated by the system.
+(알고리즘은 시스템이 생성하는 결과를 보고 내부 상태가 사용자에게 어느 정도로 이해 가능한지를 보여줄 수 있어야 한다)
+- I found algorithms easy to understand.
+(나는 알고리즘이 이해하기 쉽다고 느꼈다)
+- I think algorithmic services are easily interpretable.
+(나는 알고리즘 서비스가 쉽게 해석 가능하다고 생각한다)
+- I think I can grasp the internal structure of machine learning, and algorithms can be clearly explained.
+(나는 머신러닝의 내부 구조를 파악할 수 있다고 생각하며, 알고리즘이 명확하게 설명될 수 있다고 생각한다)
+- Algorithm recommendation services are difficult to use.
+(알고리즘 추천 서비스는 사용하기 어렵다)
+- Algorithm recommendation services are inconvenient to use.
+(알고리즘 추천 서비스는 사용하기 불편하다)
+- Using algorithm recommendation services will slow down decision making.
+(알고리즘 추천 서비스를 사용하면 의사결정이 느려질 것이다)
+- The procedures of algorithm recommendation services are unclear.
+(알고리즘 추천 서비스의 절차는 불분명하다)
+- Using algorithm recommendation services is not economical.
+(알고리즘 추천 서비스를 사용하는 것은 경제적이지 않다)
+- Algorithm recommendation services offer no advantages over current decision-making methods.
+(알고리즘 추천 서비스는 현재의 의사결정 방식에 비해 아무런 이점을 주지 못한다)
+- Using algorithm recommendation services will not increase control over decision making.
+(알고리즘 추천 서비스를 사용하는 것은 의사결정에 대한 통제력을 높여주지는 않을 것이다)
+- Algorithm recommendation services are not a good way to replace current decision-making methods.
+(알고리즘 추천 서비스는 현재 의사결정 방식을 대체할 수 있는 좋은 방법이 아니다)
+- Algorithm recommendation services fail to solve problems that occur in current decision-making methods.
+(알고리즘 추천 서비스는 현재 의사결정 방식에서 발생하는 문제를 해결하지 못한다)
+- Algorithm recommendation services frustrate me due to poor performance.
+(알고리즘 추천 서비스는 성과가 좋지 않아 나를 답답하게 만든다)
+- Compared to current methods, algorithm recommendation services have more uncertainty.
+(현재 방식에 비해 알고리즘 추천 서비스는 더 많은 불확실성을 가지고 있다)
+- It is uncertain whether algorithm recommendation services will be as effective as I expect.
+(알고리즘 추천 서비스가 내가 기대하는 만큼 효과적일지는 확실하지 않다)
+- Algorithm recommendation services do not work properly.
+(알고리즘 추천 서비스는 제대로 작동하지 않는다)
+- Overall, using algorithm recommendation services is risky.
+(전반적으로 알고리즘 추천 서비스를 사용하는 것은 위험하다)
+- I am satisfied with the existing recommendation methods by humans.
+(나는 기존의 인간에 의한 추천 방식에 따른 추천 서비스에 만족한다)
+- I am used to evaluating myself when making decisions, making it difficult to switch to algorithms.
+(나는 의사결정을 할 때 스스로 평가하는 데 익숙해서 알고리즘으로 전환하는 것이 어렵다)
+- I prefer making decisions myself rather than following recommendation decisions provided by algorithms.
+(나는 알고리즘이 제공한 추천 결정을 따르기보다 내가 직접 의사결정을 내리는 것이 더 좋다)
+- I have a very negative image of algorithm recommendation services.
+(나는 알고리즘 추천 서비스에 대해 매우 부정적인 이미지를 가지고 있다)
+- I think new technologies are often too complex to be useful.
+(새로운 기술이 종종 너무 복잡해서 유용하지 않다고 생각한다)
+- I have an image that algorithm recommendation services are difficult to use.
+(나는 알고리즘 추천 서비스가 사용하기 어렵다는 이미지를 가지고 있다)
+- I feel resistant to using platforms where algorithms are applied.
+(나는 알고리즘이 적용된 플랫폼 사용에 대한 거부감이 있다)
+- I feel no need to use platforms where algorithms are applied.
+(나는 알고리즘이 적용된 플랫폼 사용에 대한 필요성을 느끼지 못한다)
+- I am using algorithmic platforms, but I do not want to adapt to the new ways required accordingly.
+(나는 알고리즘 플랫폼을 사용하고 있지만, 그에 따라 요구되는 새로운 방식에 적응하고 싶지 않다)</t>
+        </is>
+      </c>
+      <c r="O963" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="n">
+        <v>963</v>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>孫東旭 (손동욱)</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>지역축제 성공 요인에 관한 실증 연구 - 수요자와 공급자의 인식 차이 분석: 평균 지표를 중심으로 -</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>성균관대학교 미디어문화융합대학원 문화융합학과 문화예술경영전공 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>체험경제 이론, 자원 기반 이론, 기대 불일치 이론</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>[상위 계층(축제기반, 환경적, 프로그램 요인) 및 하위 계층(9개 세부 요인)] -&gt; [수요자 vs 공급자 인식 차이 비교(AHP 및 T-검정)] -&gt; [지속 가능한 지역축제 운영 전략 도출]</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>H1: 수요자 집단은 체험경제 이론에 기반한 요소(오락성, 심미성, 일탈성)가 축제 성공 요인으로 크게 인식할 것이다.
+H2: 공급자 집단은 자원 기반 이론에 기반하여 축제 성공에 필요한 핵심 자원의 우선순위를 설정할 것이다.
+H3: 기대 불일치 이론에 기반하여 수요자와 공급자가 인식하는 지역축제 성공 요인 간에는 차이가 존재할 것이다.</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>축제 성공 요인 (축제기반 요인, 환경적 요인, 프로그램 요인 및 9개 하위 요인)</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>지역축제 성공 및 지속 가능성, 수요자·공급자 간 인식 차이</t>
+        </is>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>수요자 집단 vs 공급자 집단</t>
+        </is>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>두 집단 모두 프로그램 요인을 가장 중요한 성공 요인으로 평가했으나, 세부적으로 수요자는 독창성과 차별성(체험경제 이론)을 중시한 반면, 공급자는 실행 가능성과 자원 효율성(자원 기반 이론)을 중시하였다. 기대 불일치 이론을 통해 수요자의 기대와 공급자의 실행 기준 사이에 통계적으로 유의한 인식 차이가 있음을 확인하였으며, 양측의 관점을 조율하는 협력적 전략의 필요성을 도출하였다.</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>- Consumers perceived high utility when using the AI service.
+(소비자는 AI 서비스를 사용할 때 높은 유효성을 지각하였다.)
+- The festival reflects unique regional characteristics, history, and culture.
+(축제는 지역 고유의 특성과 역사·문화적 정체성을 반영하고 있다.)
+- The festival provides convenient transportation and accessibility for visitors.
+(축제장은 방문객을 위한 편리한 교통과 접근성을 제공한다.)
+- The festival effectively utilizes local resources and infrastructure.
+(축제는 지역의 물적 자원과 인프라를 효과적으로 활용하고 있다.)
+- The local government provides stable and sufficient financial support for the festival.
+(지방정부는 축제 운영을 위한 안정적이고 충분한 재정적 지원을 제공한다.)
+- The festival is supported by appropriate institutional policies and regulations.
+(축제는 적절한 제도적 정책과 규정의 지원을 받고 있다.)
+- The local government provides active administrative support for festival operations.
+(지방정부는 축제 운영과 관련하여 적극적인 행정적 지원을 제공한다.)
+- The festival programs offer valuable and meaningful experiences aligned with its purpose.
+(축제 프로그램은 목적에 부합하는 가치 있고 의미 있는 경험을 제공한다.)
+- The festival utilizes effective promotional strategies to reach the public.
+(축제는 대중에게 도달하기 위해 효과적인 홍보 전략을 활용한다.)
+- The festival features unique and differentiated contents compared to others.
+(축제는 다른 축제와 비교하여 독특하고 차별화된 콘텐츠를 갖추고 있다.)</t>
+        </is>
+      </c>
+      <c r="O964" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O964"/>
+  <dimension ref="A1:O979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78491,6 +78491,1719 @@
         </is>
       </c>
     </row>
+    <row r="965">
+      <c r="A965" t="n">
+        <v>964</v>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Chenyan Gu, Shuyue Jia, Jiaying Lai, Ruli Chen, Xinsiyu Chang</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Exploring Consumer Acceptance of AI-Generated Advertisements: From the Perspectives of Perceived Eeriness and Perceived Intelligence</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Journal of Theoretical and Applied Electronic Commerce Research</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>SOR Theory (Stimulus-Organism-Response Theory)</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>[Verisimilitude, Vitality, Imagination, Synthesis] -&gt; [Perceived Eeriness, Perceived Intelligence] -&gt; [Willingness to Accept]</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>H1a: Verisimilitude has a negative influence on the perceived eeriness of AI-generated advertisements.
+H1b: Verisimilitude has a positive influence on the perceived intelligence of AI-generated advertisements.
+H2a: Vitality has a negative influence on the perceived eeriness of AI-generated advertisements.
+H2b: Vitality has a positive influence on the perceived intelligence of AI-generated advertisements.
+H3a: Imagination has a negative influence on the perceived eeriness of AI-generated advertisements.
+H3b: Imagination has a positive influence on the perceived intelligence of AI-generated advertisements.
+H4a: Synthesis has a positive influence on the perceived eeriness of AI-generated advertisements.
+H4b: Synthesis has a negative influence on the perceived intelligence of AI-generated advertisements.
+H5a: Perceived eeriness has a negative influence on the consumers' willingness to accept AI-generated advertisements.
+H5b: Perceived intelligence has a positive influence on the willingness to accept AI-generated advertisements.
+H6: Perceived eeriness mediates the path from verisimilitude (H6a), vitality (H6b), imagination (H6c), and synthesis (H6d) to willingness to accept the AI-generated advertisements.
+H7: Perceived intelligence mediates the path from verisimilitude (H7a), vitality (H7b), imagination (H7c), and synthesis (H7d) to willingness to accept the AI-generated advertisements.</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>Verisimilitude, Vitality, Imagination, Synthesis</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>Willingness to Accept</t>
+        </is>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>Perceived Eeriness, Perceived Intelligence</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>Verisimilitude and imagination negatively affect perceived eeriness while synthesis positively affects it. Verisimilitude, vitality, and imagination positively affect perceived intelligence while synthesis negatively affects it. Perceived eeriness negatively affects acceptance willingness, whereas perceived intelligence positively affects it. Furthermore, perceived eeriness and perceived intelligence mediate these relationships significantly (except for vitality through eeriness).</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>- AI-generated advertisements present a realistic scenario.
+(AI 생성 광고는 현실적인 시나리오를 제시한다.)
+- The details in AI-generated advertisements look realistic yet natural.
+(AI 생성 광고의 세부 사항은 사실적이면서도 자연스러워 보인다.)
+- The details in AI-generated advertisements are similar to scenes we see in real life.
+(AI 생성 광고의 세부 사항은 우리가 실생활에서 보는 장면과 유사하다.)
+- The AI-generated advertisements show the spirit of life and personality.
+(AI 생성 광고는 생명의 정신과 개성을 보여준다.)
+- The AI-generated advertisements show raw vitality.
+(AI 생성 광고는 원초적인 활력을 보여준다.)
+- The AI-generated advertisements can be inherited and innovated.
+(AI 생성 광고는 계승되고 혁신될 수 있다.)
+- The AI-generated advertisements have creative ideas.
+(AI 생성 광고는 창의적인 아이디어를 가지고 있다.)
+- The AI-generated advertisements are innovative.
+(AI 생성 광고는 혁신적이다.)
+- The AI-generated advertisements show originality.
+(AI 생성 광고는 독창성을 보여준다.)
+- The AI-generated advertisements are imaginative.
+(AI 생성 광고는 상상력이 풍부하다.)
+- There are obvious signs of synthesis between different elements in AI-generated advertisements.
+(AI 생성 광고의 서로 다른 요소들 사이에는 명백한 합성의 흔적이 있다.)
+- AI-generated advertisements as a whole give me the impression that they are cobbled together from different materials.
+(AI 생성 광고는 전체적으로 서로 다른 소재들이 엉성하게 짜깁기되었다는 인상을 준다.)
+- Some of the detail articulation in the AI advertisements is unnatural.
+(AI 광고의 일부 세부 표현은 부자연스럽다.)
+- AI-generated advertisements as a whole give me a sense of disjointed combinations.
+(AI 생성 광고는 전체적으로 부조화스러운 조합의 느낌을 준다.)
+- I think the advertisements created by AI are creepy.
+(나는 AI가 만든 광고가 소름 끼친다고 생각한다.)
+- I think AI-generated advertisements are weird.
+(나는 AI 생성 광고가 기괴하다고 생각한다.)
+- I think AI-generated advertisements are unnatural.
+(나는 AI 생성 광고가 부자연스럽다고 생각한다.)
+- I think AI-generated advertisements are bizarre.
+(나는 AI 생성 광고가 별나다고 생각한다.)
+- AI-generated advertisements are of great quality.
+(AI 생성 광고는 품질이 뛰어나다.)
+- I believe the products in AI-generated advertisements are functionally excellent.
+(나는 AI 생성 광고에 등장하는 제품이 기능적으로 우수하다고 믿는다.)
+- I think AI-generated advertisements demonstrate a high level of technology.
+(나는 AI 생성 광고가 높은 수준의 기술을 보여준다고 생각한다.)
+- I am willing (or will be willing) to accept AI-generated advertisements.
+(나는 AI 생성 광고를 수용할 의향이 있다(또는 앞으로 있을 것이다).)
+- I am willing to actively browse or watch incoming AI-generated advertisements messages.
+(나는 수신되는 AI 생성 광고 메시지를 적극적으로 탐색하거나 시청할 의향이 있다.)
+- I am willing (or will be willing in the future) to purchase the product or service featured in the AI-generated advertisements.
+(나는 AI 생성 광고에 등장하는 제품이나 서비스를 구매할 의향이 있다(또는 미래에 그럴 의향이 있다).)</t>
+        </is>
+      </c>
+      <c r="O965" t="inlineStr">
+        <is>
+          <t>10.3390/jtaer19030108</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="n">
+        <v>965</v>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>김유정</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>AI로 제작한 광고에서 AI의 사회적 역할에 대한 인식이 광고 신뢰도와 브랜드 태도에 미치는 영향: AI 제작 표기 여부와 메시지 소구 유형의 조절효과를 중심으로</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>홍익대학교 일반대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>미디어 등가성(Media Equation), 의인화 이론(Anthropomorphism)</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>[AI의 사회적 역할 인식 (파트너/하인)] -&gt; [광고 신뢰도 (진실성, 호감, 선의, 의존의향) 및 브랜드 태d도] (조절변수: AI 제작 표기 유무, 메시지 소구 유형)</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>H1: AI 제작 표기 유무에 따라 AI의 사회적 역할 인식, 광고 신뢰도, 브랜드 태도 등에 차이가 있을 것이다.
+H2: 메시지 소구 유형에 따라 AI의 사회적 역할 인식, 광고 신뢰도, 브랜드 태도 등에 차이가 있을 것이다.
+H3: 소비자가 AI를 파트너(협력자)로 인식할수록 광고 신뢰도 및 브랜드 태도는 높아질 것이며, 하인/도구로 인식할수록 낮아질 것이다.
+H4: AI의 사회적 역할 인식이 광고 신뢰도 및 브랜드 태도에 미치는 영향은 AI 제작 표기 유무에 따라 달라질 것이다.
+H5: AI의 사회적 역할 인식이 광고 신뢰도 및 브랜드 태도에 미치는 영향은 메시지 소구 유형에 따라 달라질 것이다.</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>AI의 사회적 역할에 대한 소비자의 인식 (파트너 인식, 하인 인식)</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>광고 신뢰도 (진실성, 호감, 선의, 의존의향), 브랜드 태도</t>
+        </is>
+      </c>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>AI 제작 표기 유무, 메시지 소구 유형</t>
+        </is>
+      </c>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>소비자가 AI를 파트너로 인식할수록 광고 신뢰도와 브랜드 태도가 유의미하게 높게 나타났으며, AI 제작 표기가 없는 경우와 정보적 메시지 소구 조건에서 의존 의향과 브랜드 태도가 더 높게 나타났다. 또한, AI 제작 표기 유무와 메시지 소구 유형은 AI 사회적 역할 인식이 의존 의향 및 브랜드 태도에 미치는 영향을 일부 조절하는 것으로 확인되었다.</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>- The creator is a partner to me.
+(AI는 나에게 파트너와 같다.)
+- The creator cocreates value with me.
+(AI는 나와 함께 가치를 공동 창출한다.)
+- The creator is a servant to me.
+(AI는 나에게 하인과 같다.)
+- The creator obeys me.
+(AI는 나의 지시에 따른다.)
+- 이 광고가 전달하는 제품 관련 정보는 진실하다.
+(The product-related information conveyed by this ad is truthful.)
+- 이 광고가 전달하는 제품 관련 정보는 솔직하다.
+(The product-related information conveyed by this ad is honest.)
+- 이 광고는 객관적인 정보를 제공한다.
+(This ad provides objective information.)
+- 이 광고에 나오는 제품 관련 정보는 믿을 만하다.
+(The product-related information presented in this ad is reliable.)
+- 이 광고는 제품의 성능 및 효능에 관해 책임감 있는 주장을 한다.
+(This ad makes responsible claims regarding product performance and efficacy.)
+- 이 광고가 전달하는 정보는 재미있다.
+(The information conveyed by this ad is entertaining.)
+- 이 광고가 전달하는 정보는 유쾌하다.
+(The information conveyed by this ad is pleasant.)
+- 이 광고를 보거나 읽는 것은 대체로 즐겁다.
+(Watching or reading this ad is generally enjoyable.)
+- 광고가 전달하는 정보는 흥미롭다.
+(The information conveyed by the ad is interesting.)
+- 광고는 소비자의 이익을 고려한다.
+(The ad considers consumers' interests.)
+- 광고는 소비자의 혜택을 중요하게 생각한다.
+(The ad places importance on consumers' benefits.)
+- 나는 최근 제품 동향을 알아보고자 할 때 관련 제품의 광고를 살펴볼 생각이 있다.
+(I intend to look at related product ads when I want to find out about recent product trends.)
+- 나는 나의 개성과 취향에 어울리는 제품을 찾기 위하여 관련 광고를 살펴볼 의향이 있다.
+(I intend to look at related ads to find products that match my personality and taste.)
+- 나는 나의 목적에 맞는 제품을 찾기 위하여 관련 광고를 살펴볼 의향이 있다.
+(I intend to look at related ads to find products that suit my purpose.)
+- Bad – Good
+(나쁘다 - 좋다)
+- Unfavorable – Favorable
+(비호의적이다 — 호의적이다)
+- Unpleasant – Pleasant
+(불쾌하다 — 즐겁다)
+- Unlikable – Likable
+(호감이 가지 않는다 — 호감이 간다)
+- Unappealing – Appealing
+(매력적이지 않다 — 매력적이다)</t>
+        </is>
+      </c>
+      <c r="O966" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="n">
+        <v>966</v>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>오만비</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>AI 맞춤형 광고의 지각된 개인화, 지각된 유용성 및 프라이버시 우려의 광고 효과에 관한 연구: 공정한 정보 활용(Fair Information Practices, FIPs) 원칙에 대한 이용자의 인식을 중심으로</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>한양대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>기술수용모델(Technology Acceptance Model, TAM), 프라이버시 계산 이론(Privacy Calculus Theory), 절차적 정의 이론(Procedural Justice Theory)</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>[지각된 개인화 (IV)] -&gt; [지각된 유용성 / 프라이버시 우려 (Mediators)] -&gt; [광고 클릭의도 (DV)] (조절변수: FIPs 원칙에 대한 인식)</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>H1: 소셜미디어 AI 맞춤형 광고에 대해 이용자가 지각하는 개인화는 이용자의 유용성 인식을 높일 것이다.
+H2: 소셜미디어 AI 맞춤형 광고에 대해 이용자가 지각하는 개인화는 해당 광고에 대한 이용자의 클릭의도를 높일 것이다.
+H3: 소셜미디어 AI 맞춤형 광고에 대한 이용자의 유용성 인식은 지각된 개인화와 광고 클릭 의도 간의 관계를 매개할 것이다.
+H4: 소셜미디어 AI 맞춤형 광고에 대해 이용자가 지각하는 개인화는 이용자의 프라이버시 우려를 높일 것이다.
+H5: 소셜미디어 AI 맞춤형 광고에 대한 이용자의 프라이버시 우려는 지각된 개인화와 광고 클릭 의도 간의 관계를 매개할 것이다.</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>지각된 개인화 (Perceived Personalization)</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>광고 클릭의도 (Click Intention)</t>
+        </is>
+      </c>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>지각된 유용성 (Perceived Usefulness), 프라이버시 우려 (Privacy Concern)</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>공정한 정보 활용(Fair Information Practices, FIPs) 원칙에 대한 인식</t>
+        </is>
+      </c>
+      <c r="M967" t="inlineStr">
+        <is>
+          <t>지각된 개인화는 광고의 유용성과 프라이버시 우려 모두를 유의미하게 증가시켰으며, 지각된 유용성은 개인화와 클릭 의도 간의 관계를 매개하였다. 반면 프라이버시 우려는 긍정적 효과를 약화시키는 경향을 보였다. 또한 FIPs 준수에 대한 소비자의 긍정적 인식은 지각된 개인화와 프라이버시 우려 사이의 관계를 조절하여 프라이버시 우려를 완화하는 역할을 하는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>- AI 맞춤형 광고는 나를 위해 특별히 설계된 것이다.
+(AI-based customized advertising is designed specifically for me.)
+- AI 맞춤형 광고는 나의 개인적인 요구를 충분히 반영한다.
+(AI-based customized advertising fully reflects my personal needs.)
+- AI 맞춤형 광고는 나의 개인적인 요구를 충족시키기 위해 설계되었다.
+(AI-based customized advertising is designed to meet my personal needs.)
+- AI 맞춤형 광고는 나의 온라인 행동을 기반으로 설계되었다.
+(AI-based customized advertising is designed based on my online behavior.)
+- AI 맞춤형 광고는 내 개인 정보를 사용하고 있다.
+(AI-based customized advertising uses my personal information.)
+- AI 맞춤형 광고는 나에게 특정된 광고이다.
+(AI-based customized advertising is targeted specifically to me.)
+- AI 맞춤형 광고는 내 개인 정보와 관련되어 있다.
+(AI-based customized advertising is related to my personal information.)
+- AI 맞춤형 광고는 경제적인 혜택을 제공한다.
+(AI-based customized advertising provides economic benefits.)
+- AI 맞춤형 광고는 유용한 정보를 제공한다.
+(AI-based customized advertising provides useful information.)
+- AI 맞춤형 광고는 적절한 시기에 필요한 정보를 제공한다.
+(AI-based customized advertising provides necessary information at the right time.)
+- AI 맞춤형 광고는 전반적으로 유용하다.
+(AI-based customized advertising is generally useful.)
+- 소셜미디어가 AI 맞춤형 광고를 제공하기 위해 나의 개인정보를 수집할까 봐 걱정된다.
+(I am worried that social media will collect my personal information to provide AI-based customized advertising.)
+- 소셜미디어에서 나의 개인정보가 안전하게 보호되지 않을 것 같아 걱정된다.
+(I am worried that my personal information may not be safely protected on social media.)
+- 소셜미디어의 AI 맞춤형 광고가 나의 사생활을 침해할까봐 걱정된다.
+(I am worried that AI-based customized advertising on social media will invade my privacy.)
+- AI 맞춤형 광고는 나에 대한 정보를 너무 많이 가지고 있는 것 같다.
+(AI-based customized advertising seems to have too much information about me.)
+- AI 맞춤형 광고는 나의 사적인 정보에 접근하는 것 같다.
+(AI-based customized advertising seems to access my private information.)
+- AI 맞춤형 광고에 쓰인 내 정보가 내가 예상하지 못하는 방법으로 사용될까 염려된다.
+(I am concerned that my information used in AI-based customized advertising will be used in ways I did not expect.)
+- AI 맞춤형 광고가 제품을 추천할 때 내 개인정보가 악용될까봐 걱정된다.
+(I am worried that my personal information will be misused when AI-based customized advertising recommends products.)
+- AI 맞춤형 광고가 내 개인 정보를 사용해 제품을 추천할 때 프라이버시 문제가 걱정된다.
+(I am concerned about privacy issues when AI-based customized advertising recommends products using my personal information.)
+- AI 맞춤형 광고가 내 개인 정보를 악용할 가능성이 있다고 생각한다.
+(I think there is a possibility that AI-based customized advertising will misuse my personal information.)
+- 소셜미디어의 AI 맞춤형 광고에서 추천하는 제품의 링크를 클릭할 의향이 있다.
+(I am willing to click on the link of the product recommended in the AI-based customized advertising of social media.)
+- 소셜미디어의 AI 맞춤형 광고에서 추천하는 제품의 추가 정보를 확인할 의향이 있다.
+(I am willing to check additional information on the product recommended in the AI-based customized advertising of social media.)
+- 소셜미디어의 AI 맞춤형 광고에서 추천하는 제품의 상세 정보 페이지를 방문할 의향이 있다.
+(I am willing to visit the detailed information page of the product recommended in the AI-based customized advertising of social media.)</t>
+        </is>
+      </c>
+      <c r="O967" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="n">
+        <v>967</v>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>강희원</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>AI 라벨 표기 광고에 대한 인지적 반응이 광고 효과에 미치는 영향: 인스타그램 광고를 중심으로</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>설득지식모델(Persuasion Knowledge Model), CARE 모델, 역전 이론</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>[AI 라벨 표기 광고에 대한 인지적 반응(지각된 신뢰성, 지각된 상업성, 조작적 의도에 대한 추론, 호기심)] -&gt; [광고 태도] -&gt; [브랜드 태도, 구매 의도] (조절변인: AI 친숙도, 인스타그램 쇼핑 태도)</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>H1: AI 라벨 표기 광고에 대한 인지적 반응은 (a) 광고 태도, (b) 브랜드 태도, (c) 구매 의도에 영향을 미칠 것이다.
+H2: AI 라벨 표기 광고에 대한 인지적 반응이 (a) 브랜드 태도와 (b) 구매 의도에 미치는 영향은 광고 태도에 의해 매개될 것이다.
+H3: AI 라벨 표기 광고에 대한 인지적 반응이 광고 태도를 통해 (a) 브랜드 태도와 (b) 구매 의도에 미치는 영향은 AI 친숙도에 의해 조절될 것이다.
+H4: AI 라벨 표기 광고에 대한 인지적 반응이 광고 태도를 통해 (a) 브랜드 태도와 (b) 구매 의도에 미치는 영향은 인스타그램 쇼핑 태도에 의해 조절될 것이다.</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>AI 라벨 표기 광고에 대한 인지적 반응 (지각된 신뢰성, 지각된 상업성, 조작적 의도에 대한 추론, 호기심)</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>광고 효과 (광고 태도, 브랜드 태도, 구매 의도)</t>
+        </is>
+      </c>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>광고 태도</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>AI 친숙도, 인스타그램 쇼핑 태도</t>
+        </is>
+      </c>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>지각된 신뢰성과 호기심은 광고 태도, 브랜드 태도, 구매 의도 전반에 긍정적인 영향을 미쳤으며, 지각된 상업성은 광고 태도와 구매 의도를 강화하였으나 브랜드 태도에는 유의한 영향을 주지 않았다. 조작적 의도에 대한 추론은 광고 태도를 약화시키는 방향에서만 유의하게 나타났다. 또한 네 가지 인지적 반응 모두 광고 태도를 매개할 때 브랜드 태도와 구매 의도에 유의한 간접효과를 보였다. 아울러 AI 친숙도와 인스타그램 쇼핑 태도는 지각된 신뢰성, 지각된 상업성, 호기심이 광고 태도를 경유하여 후속 광고 효과로 이어지는 간접 경로의 강도를 증폭하는 조절된 매개효과를 나타냈다.</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>지각된 신뢰성:
+- This advertisement is reliable.
+(이 광고는 신뢰할 수 있다.)
+- This advertisement is trustworthy.
+(이 광고는 믿을 만하다.)
+- This advertisement is not deceptive.
+(이 광고는 허위적이지 않다.)
+- I have no doubts about this advertisement.
+(이 광고에 대해서는 의구심이 들지 않는다.)
+- The product advertised through this advertisement is reliable.
+(이 광고를 통해 광고되는 제품은 믿을 만하다.)
+지각된 상업성:
+- This advertisement tries to make me find out more about the product.
+(이 광고는 내가 제품을 더 알아보게 만들려고 한다.)
+- This advertisement strives to make me want the product.
+(이 광고는 내가 제품을 원하게 만들려고 애쓴다.)
+- This advertisement has the intention of persuading me to buy this product.
+(이 광고는 내가 이 제품을 구매하도록 설득하려는 의도가 있다.)
+- This advertisement tries to make me think positively about this product.
+(이 광고는 내가 이 제품에 대해 긍정적으로 생각하게 만들려고 한다.)
+- This advertisement tries to make me purchase this product.
+(이 광고는 내가 이 제품을 구매하게 만들려고 한다.)
+조작적 의도에 대한 추론:
+- I think this advertisement was produced in a subtle or artificial way.
+(이 광고는 교묘하거나 인위적인 방식으로 제작되었다고 생각한다.)
+- I think this advertisement uses inappropriate methods to persuade consumers.
+(이 광고는 소비자를 설득하기 위해 부적절한 방식을 사용한다고 생각한다.)
+- I think this advertisement uses somewhat excessive or unnatural persuasion methods.
+(이 광고는 다소 과도하거나 부자연스러운 설득 방식을 사용한다고 생각한다.)
+- The expression of this advertisement feels artificial.
+(이 광고의 표현은 인위적으로 느껴진다.)
+- The way this advertisement tries to persuade people is hard to accept.
+(이 광고가 사람들을 설득하려는 방식은 수용하기 어렵다.)
+호기심:
+- This advertisement is new and arouses my curiosity.
+(이 광고는 새롭고 나의 호기심을 끈다.)
+- I want to know more about this advertisement.
+(이 광고에 대해 더욱 알고 싶다.)
+- I am interested in this advertisement.
+(이 광고에 관심이 간다.)
+- I am curious about the product featured in this advertisement.
+(이 광고에 등장한 제품에 대해 호기심이 생긴다.)
+광고 태도:
+- I like this advertisement.
+(나는 이 광고가 마음에 든다.)
+- I am satisfied with this advertisement.
+(나는 이 광고에 대해 만족한다.)
+- I have a favorable feeling toward this advertisement.
+(나는 이 광고에 대해 호감이 간다.)
+- I am positive about this advertisement.
+(나는 이 광고에 대해 긍정적이다.)
+- This advertisement is good.
+(나는 이 광고가 좋다.)
+브랜드 태도:
+- I like the brand.
+(마음에 든다.)
+- I have a favorable feeling toward the brand.
+(호감이 간다.)
+- The brand is attractive.
+(매력적이다.)
+- I think I will remember the brand well.
+(기억이 잘 날 것 같다.)
+구매 의도:
+- I want to buy the product featured in this advertisement.
+(나는 이 광고에 나온 제품을 구매하고 싶다.)
+- I will buy the product featured in this advertisement if I need it.
+(나는 이 광고에 나온 제품이 필요하면 살 것이다.)
+- There is a possibility that I will buy the product featured in this advertisement.
+(나는 이 광고에 나온 제품을 구매할 가능성이 있다.)
+- I will purchase the product featured in this advertisement if I have the opportunity.
+(나는 기회가 있으면 이 광고에 나온 제품을 구매하겠다.)
+AI 친숙도:
+- I am familiar with AI application technologies.
+(나는 AI 응용 기술에 익숙한 편이다.)
+- I use AI frequently.
+(나는 AI를 자주 사용하는 편이다.)
+인스타그램 쇼핑 태도:
+- I am satisfied with shopping on Instagram.
+(나는 인스타그램에서 쇼핑하는 것에 대해 만족한다.)
+- I am positive about shopping on Instagram.
+(나는 인스타그램에서 쇼핑하는 것에 대해 긍정적이다.)
+- I like shopping on Instagram.
+(나는 인스타그램에서 쇼핑하는 것이 좋다.)</t>
+        </is>
+      </c>
+      <c r="O968" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="n">
+        <v>968</v>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>LIU YUE</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>AI 동영상 광고가 유발하는 불쾌함 -원인, 결과, 수용자 특성의 영향력 탐색을 중심으로-</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>경희대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>불쾌한 골짜기 가설 (Uncanny Valley Hypothesis), 계획된 행동이론 (Theory of Planned Behavior)</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>[AI 인식 / 수용자 특성] -&gt; [불쾌함 (영상/음성)] -&gt; [광고태도] -&gt; [행동의도]</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>H1: AI 인식 여부는 불쾌감에 영향을 미칠 것이다.
+H2: 수용자 특성은 불쾌감 인식에 영향을 미칠 것이다.
+H3: 시청각 요소는 불쾌감을 증가시킨다.
+H4: 수용자 특성은 AI 인식 확률에 영향을 미칠 것이다.
+H5: AI 인식 여부는 광고태도에 부정적 영향을 줄 것이다.
+H6: 불쾌감은 광고태도에 부정적 영향을 줄 것이다.
+H7: 수용자 특성은 광고태도에 영향을 미칠 것이다.
+H8: 광고태도는 행동의도에 정(+)적 영향을 미칠 것이다.
+H9: 수용자 특성은 행동의도에 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>AI 인식 여부, 수용자 특성 (성격 요인, 이슈관여도 등)</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>광고태도, 행동의도</t>
+        </is>
+      </c>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>불쾌함 (영상 및 음성)</t>
+        </is>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M969" t="inlineStr">
+        <is>
+          <t>AI 생성 여부에 대한 인식은 불쾌감 형성에 유의한 영향을 미치며, 특히 음성의 인공성과 부자연스러움이 강력한 불쾌 유발 요인으로 작용함. 또한 불쾌감은 광고태도를 악화시키는 매개적 역할을 하며, 광고태도는 다시 행동의도를 유의하게 예측함.</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>- I like this advertisement.
+(나는 이 광고가 마음에 든다.)
+- This advertisement is good.
+(나는 이 광고가 좋다.)
+- I feel favorable toward this advertisement.
+(나는 이 광고에 호감이 간다.)
+- I think positively about this advertisement.
+(이 광고에 대해 긍정적으로 생각한다.)
+- The video of this advertisement felt eerie.
+(이 광고의 영상은 섬뜩하게 느껴졌다.)
+- The video of this advertisement felt creepy.
+(이 광고의 영상은 오싹하게 느껴졌다.)
+- The video of this advertisement felt weird.
+(이 광고의 영상은 기괴하게 느껴졌다.)
+- The video of this advertisement felt unpleasant.
+(이 광고의 영상은 불쾌하게 느껴졌다.)
+- The voice of this advertisement felt eerie.
+(이 광고의 음성은 섬뜩하게 느껴졌다.)
+- The voice of this advertisement felt creepy.
+(이 광고의 음성은 오싹하게 느껴졌다.)
+- The voice of this advertisement felt weird.
+(이 광고의 음성은 기괴하게 느껴졌다.)
+- The voice of this advertisement felt unpleasant.
+(이 광고의 음성은 불쾌하게 느껴졌다.)
+- The issue covered in this advertisement (environmental problem) is highly relevant to me.
+(이 광고에서 다룬 이슈(=환경문제)는 나와 관련성이 높다.)
+- The issue covered in this advertisement is socially valuable.
+(이 광고에서 다룬 이슈(=환경문제)는 사회적으로 가치가 있다고 생각한다.)
+- The issue covered in this advertisement is an important problem.
+(이 광고에서 다룬 이슈(=환경문제)는 중요한 문제라고 생각한다.)
+- The issue covered in this advertisement is a meaningful topic.
+(이 광고에서 다룬 이슈(=환경문제)는 의미 있는 주제라고 생각한다.)
+- I intend to participate in activities related to environmental protection covered in this advertisement in the future.
+(앞으로 이 광고의 주제인 ‘환경보호’와 관련된 활동에 참여할 생각이 있다.)
+- I have the intention to personally practice the message conveyed by this advertisement in my daily life.
+(일상에서 이 광고가 전하는 메시지를 몸소 실천할 의향이 있다.)
+- I want to pass on the message of this advertisement to people around me.
+(이 광고의 메시지를 주변 사람들에게 전달해주고 싶다.)
+- If circumstances permit, I will prioritize consumption or choices that consider the environment.
+(상황이 허락된다면, 나는 환경을 고려한 소비나 선택을 우선시할 것이다.)</t>
+        </is>
+      </c>
+      <c r="O969" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="n">
+        <v>969</v>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>김인혜</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>AI 광고의 개인화 수준이 광고 효과에 미치는 영향: 주어의 조절효과</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>동국대학교 대학원 박사학위논문</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>자기결정이론(Self-determination theory), 심리적 저항 이론(Psychological reactance theory), 역할 이론(Role theory), 행위 주체감(Sense of agency)</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>[개인화 수준 × 주어] -&gt; [프라이버시 우려 / 사회적 현존감 / 인지된 자율성] -&gt; [챗봇 및 광고에 대한 반응]</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>H1: 개인화 수준과 주어 간 상호작용에 의하여 프라이버시 우려가 달라질 것이다.
+H2: 개인화 수준과 주어 간 상호작용에 의하여 사회적 현존감이 달라질 것이다.
+H3: 개인화 수준과 주어 간 상호작용에 의하여 인지된 자율성이 달라질 것이다.
+H4: 개인화 수준과 주어 간 상호작용에 의하여 챗봇에 대한 반응이 달라질 것이다.
+H5: 개인화 수준과 주어 간 상호작용에 의하여 광고에 대한 반응이 달라질 것이다.
+H6: 개인화 수준이 프라이버시 우려를 매개로 챗봇에 대한 반응에 미치는 효과는 주어에 의해 조절될 것이다.
+H7: 개인화 수준이 프라이버시 우려를 매개로 광고에 대한 반응에 미치는 효과는 주어에 의해 조절될 것이다.
+H8: 개인화 수준이 사회적 현존감을 매개로 챗봇에 대한 반응에 미치는 효과는 주어에 의해 조절될 것이다.
+H9: 개인화 수준이 사회적 현존감을 매개로 광고에 대한 반응에 미치는 효과는 주어에 의해 조절될 것이다.
+H10: 개인화 수준이 인지된 자율성을 매개로 챗봇에 대한 반응에 미치는 효과는 주어에 의해 조절될 것이다.
+H11: 개인화 수준이 인지된 자율성을 매개로 광고에 대한 반응에 미치는 효과는 주어에 의해 조절될 것이다.</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>AI 개인화 광고의 개인화 수준 (높음 vs. 낮음)</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>챗봇에 대한 반응(챗봇 태도, 챗봇 사용 의도), 광고에 대한 반응(브랜드 태도, 구매의도)</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>프라이버시 우려, 사회적 현존감, 인지된 자율성</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>주어 (소비자 주어 'You' vs. AI 주어 'I')</t>
+        </is>
+      </c>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>개인화 수준이 높을 때, 소비자 주어가 정보 탐색의 주체로 설정되면 프라이버시는 낮아지고 사회적 현존감과 인지된 자율성은 높아져 챗봇과 광고에 대한 반응이 호의적으로 나타났다. 반면 AI 주어가 설정되면 프라이버시 우려가 높아지고 반응이 저하되는 조절된 매개효과가 확인되었다.</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>- I am worried about the misuse of personal information used when the chatbot recommends products.
+(나는 챗봇이 제품을 추천할 때 사용된 개인정보의 오용이 걱정된다.)
+- I am worried about the privacy issues of personal information used when the chatbot recommends products.
+(나는 챗봇이 제품을 추천할 때 사용된 개인정보의 프라이버시 문제가 걱정된다.)
+- I am worried that my personal information might be misused by this chatbot.
+(나는 이 챗봇에 의해 나의 개인정보가 잘못 사용될까 걱정된다.)
+- I am worried that the chatbot might use my information when recommending products to other consumers.
+(나는 챗봇이 다른 소비자들에게 제품을 추천할 때 내 정보를 사용할 것 같아 걱정된다.)
+- I think the chatbot shares personal information without permission.
+(내 생각에 챗봇은 개인정보를 허가 없이 공유하는 것 같다.)
+- I believe that I can make purchase decisions freely without being manipulated by the chatbot.
+(나는 내가 챗봇에 의해 조종되지 않고 자유롭게 구매 결정을 내릴 수 있다고 믿는다.)
+- I believe that whether I make a purchase is up to me, and the chatbot does not want to influence my purchase decision.
+(나는 내가 구매를 할지 말지는 나에게 달렸고, 챗봇은 내 구매 결정에 영향을 미치고 싶지 않아 한다고 믿는다.)
+- Human contact
+(인간 접촉)
+- Personal
+(개인적임)
+- Social
+(사회적임)
+- Human sensitivity
+(인간의 감성)</t>
+        </is>
+      </c>
+      <c r="O970" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="n">
+        <v>970</v>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>채혜진</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>광고의 AI 활용 공개 수준이 광고 경험에 미치는 영향 -AI 혁신 태도를 중심으로-</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>홍익대학교 영상·커뮤니케이션대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>인지부하 이론(Cognitive Load Theory), 플로우 이론(Flow Theory)</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>[AI 활용 공개 수준] -&gt; [광고 경험 (인지된 진정성, 투명성, 인지부하, 몰입도, 구매의도)] (조절변수: AI 혁신 태도)</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>H1-1. AI 활용 공개 수준에 따라 인지된 진정성에 차이가 있을 것이다.
+H1-2. AI 활용 공개 수준에 따라 투명성에 차이가 있을 것이다.
+H1-3. AI 활용 공개 수준에 따라 인지부하에 차이가 있을 것이다.
+H1-4. AI 활용 공개 수준에 따라 몰입도에 차이가 있을 것이다.
+H1-5. AI 활용 공개 수준에 따라 구매의도에 차이가 있을 것이다.
+H2-1. AI 활용 공개 수준은 AI 혁신 태도에 따라 인지된 진정성에 상호작용 효과가 있을 것이다.
+H2-2. AI 활용 공개 수준은 AI 혁신 태도에 따라 투명성에 상호작용 효과가 있을 것이다.
+H2-3. AI 활용 공개 수준은 AI 혁신 태도에 따라 인지부하에 상호작용 효과가 있을 것이다.
+H2-4. AI 활용 공개 수준은 AI 혁신 태도에 따라 몰입도에 상호작용 효과가 있을 것이다.
+H2-5. AI 활용 공개 수준은 AI 혁신 태도에 따라 구매의도에 상호작용 효과가 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>AI 활용 공개 수준 (AI 활용 미공개, AI 활용 여부 공개, AI 활용 도구 공개, AI 활용 방법 공개)</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>광고 경험 (인지된 진정성, 투명성, 인지부하, 몰입도, 구매의도)</t>
+        </is>
+      </c>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>AI 혁신 태도 (기대, 불안)</t>
+        </is>
+      </c>
+      <c r="M971" t="inlineStr">
+        <is>
+          <t>광고 내 AI 활용 공개 수준에 따라 인지된 진정성, 투명성, 인지부하, 몰입도에서 통계적으로 유의한 차이가 나타났다. 방법 공개 조건에서 인지된 진정성과 투명성이 가장 높았으나, 도구 공개 조건에서는 낯선 용어로 인해 인지부하가 높고 몰입도가 낮았다. 또한 AI 혁신 태도에 따라 인지부하와 몰입도에서 유의한 상호작용 효과가 확인되었다. 반면 구매의도는 유의한 차이가 없었다.</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>- AI를 활용하면 인간이 수행했던 작업보다 월등한 결과를 만들어 낼 것이다.
+(AI를 활용하면 인간이 수행했던 작업보다 월등한 결과를 만들어 낼 것이다.)
+- AI은 사람이 수행하기 어려운 일을 대신 해줌으로써, 인류의 삶의 질은 개선될 것이다.
+(AI는 사람이 수행하기 어려운 일을 대신 해줌으로써, 인류의 삶의 질은 개선될 것이다.)
+- AI로 인해 사람들은 각자에게 맞춤화된 지식 또는 능력을 향상시킬 수 있을 것이다.
+(AI로 인해 사람들은 각자에게 맞춤화된 지식 또는 능력을 향상시킬 수 있을 것이다.)
+- AI로 인해 그동안 일부 전문가 집단에 한정되었던 능력이나 지식들을 빠르게 활용할 수 있을 것이다.
+(AI로 인해 그동안 일부 전문가 집단에 한정되었던 능력이나 지식들을 빠르게 활용할 수 있을 것이다.)
+- 원하는 작업 수행의 결과를 위해 AI를 활용하는 것은 가치 있다고 생각한다.
+(원하는 작업 수행의 결과를 위해 AI를 활용하는 것은 가치 있다고 생각한다.)
+- AI를 활용해 환경문제, 사회갈등과 같은 복잡한 문제에 대한 해결이 가능해질 것이다.
+(AI를 활용해 환경문제, 사회갈등과 같은 복잡한 문제에 대한 해결이 가능해질 것이다.)
+- AI는 뛰어난 업무적 능력을 발휘하여, 인간을 의존적으로 만들 것이다.
+(AI는 뛰어난 업무적 능력을 발휘하여, 인간을 의존적으로 만들 것이다.)
+- AI로 인해 프라이버시는 위협받을 수 있을 것이다.
+(AI로 인해 프라이버시는 위협받을 수 있을 것이다.)
+- AI는 업무수행에 대한 인간의 책임감을 무력화 할 것이다.
+(AI는 업무수행에 대한 인간의 책임감을 무력화 할 것이다.)
+- AI는 인간을 심리적, 감정적으로 AI에 의존하게 만들 것이다.
+(AI는 인간을 심리적, 감정적으로 AI에 의존하게 만들 것이다.)
+- 인간의 복잡한 생각 프로세스는 AI의 몫이 될 것이다.
+(인간의 복잡한 생각 프로세스는 AI의 몫이 될 것이다.)
+- AI로 인해 사람들은 상업적 또는 정치적으로 조종당할 수 있을 것이다.
+(AI로 인해 사람들은 상업적 또는 정치적으로 조종당할 수 있을 것이다.)
+- 이 광고는 제작 방식을 솔직하게 공개했다고 느껴진다.
+(이 광고는 제작 방식을 솔직하게 공개했다고 느껴진다.)
+- 이 광고의 제작 방식은 정직하게 느껴진다.
+(이 광고의 제작 방식은 정직하게 느껴진다.)
+- 이 광고는 제작 방식에 대해 충분한 정보를 제공한다.
+(이 광고는 제작 방식에 대해 충분한 정보를 제공한다.)
+- 이 광고는 이해하기 쉽게 제작 방식에 대한 정보를 제공한다.
+(이 광고는 이해하기 쉽게 제작 방식에 대한 정보를 제공한다.)
+- 이 광고의 제작 방식에 대해 이해하기 쉽다.
+(이 광고의 제작 방식에 대해 이해하기 쉽다.)
+- 이 광고의 제작 방식을 이해하는 데에 노력이 필요했다.
+(이 광고의 제작 방식을 이해하는 데에 노력이 필요했다.)
+- 이 광고의 제작 방식이 복잡하다고 생각한다.
+(이 광고의 제작 방식이 복잡하다고 생각한다.)
+- 이 광고의 제작 정보보다 광고의 내용에 몰두했다.
+(이 광고의 제작 정보보다 광고의 내용에 몰두했다.)
+- 이 광고의 제작 방식으로 인해 광고를 보는데 방해가 되었다.
+(이 광고의 제작 방식으로 인해 광고를 보는데 방해가 되었다.)
+- 이 광고의 제작 방식이 광고의 내용 보다 눈길이 간다.
+(이 광고의 제작 방식이 광고의 내용 보다 눈길이 간다.)
+- 이 광고의 제작 방식은 내가 이 제품을 구매하는 데 긍정적 영향을 준다.
+(이 광고의 제작 방식은 내가 이 제품을 구매하는 데 긍정적 영향을 준다.)
+- 이 광고의 제품을 사용해 볼 의향이 있다.
+(이 광고의 제품을 사용해 볼 의향이 있다.)</t>
+        </is>
+      </c>
+      <c r="O971" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="n">
+        <v>971</v>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>양흔예</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>인스타그램 인피드 광고의 개인화 수준에 따른 광고 인게이지먼트 효과에 관한 연구-광고 불쾌감의 매개효과 및 프라이버시 계산 이론을 중심으로-</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>동국대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>프라이버시 계산 이론 (Privacy Calculus Theory)</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>[독립변수: 개인화 수준] -&gt; [매개변수: 광고 불쾌감] -&gt; [종속변수: 광고 인게이지먼트] / [조절변수: 프라이버시 침해 우려, 인지된 혜택]</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>H1: 인스타그램 인피드 광고의 개인화 수준은 광고 인게이지먼트에 긍정적 영향을 미치며, 그 과정에서 광고 불쾌감이 매개할 것이다.
+H1-1: 인스타그램 인피드 광고 중, 개인화 수준이 낮은 광고에 비하여 개인화 수준이 높은 광고는 광고 수용자의 광고 인게이지먼트가 높게 나타날 것이다.
+H1-2: 인스타그램 인피드 광고 중, 개인화 수준이 낮은 광고에 비하여 개인화 수준이 높은 광고는 광고 수용자의 광고 불쾌감이 낮게 나타날 것이다.
+H1-3: 인스타그램 인피드 광고 불쾌감이 낮을수록 광고 인게이지먼트가 높아질 것이다.
+H2-1: 인스타그램 인피드 광고에서 개인화 수준에 따른 광고 불쾌감은 프라이버시 침해 우려에 따라 조절될 것이다.
+H2-2: 인스타그램 인피드 광고에서 개인화 수준에 따른 광고 인게이지먼트는 프라이버시 침해 우려에 따라 조절될 것이다.
+H3-1: 인스타그램 인피드 광고에서 개인화 수준에 따른 광고 불쾌감은 인지된 혜택에 따라 조절될 것이다.
+H3-2: 인스타그램 인피드 광고에서 개인화 수준에 따른 광고 인게이지먼트는 인지된 혜택에 따라 조절될 것이다.</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>인스타그램 인피드 광고의 개인화 수준</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>광고 인게이지먼트</t>
+        </is>
+      </c>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>광고 불쾌감</t>
+        </is>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>프라이버시 침해 우려, 인지된 혜택</t>
+        </is>
+      </c>
+      <c r="M972" t="inlineStr">
+        <is>
+          <t>개인화 수준이 높은 광고가 노출되었을 때 더 높은 수준의 광고 인게이지먼트를 얻었으나, 이 과정은 프라이버시 침해 우려와 인지된 혜택에 따라 조절되는 것으로 나타났다. 구체적으로 프라이버시 침해 우려가 높을 때 개인화 수준이 높으면 광고 인게이지먼트가 낮아지는 반면, 프라이버시 침해 우려가 낮을 때 개인화 수준이 높으면 광고 인게이지먼트가 높아졌다. 또한 인지된 혜택이 높을수록 개인화 수준에 따른 광고 불쾌감이 낮아지는 조절효과가 확인되었다.</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>- This ad is tailored to me in the situation I just imagined.
+(이 광고는 방금 상상한 상황 속의 내게 맞춰진 광고이다.)
+- This ad provides customized information to me in the situation I just imagined.
+(이 광고는 방금 상상한 상황 속의 내게 맞춤화된 정보를 제공한다.)
+- I felt displeased while watching this in-feed ad.
+(이 인피드 광고를 보면서 불쾌하였다.)
+- I felt annoyed while watching this in-feed ad.
+(이 인피드 광고를 보면서 짜증이 났다.)
+- I felt bad while watching this in-feed ad.
+(이 인피드 광고를 보면서 기분이 나빴다.)
+- I am interested in the information presented in this ad.
+(나는 이 광고에서 제시하는 정보에 관심이 있다.)
+- Watching this ad is valuable to me.
+(이 광고를 보는 것은 나에게 가치가 있다.)
+- I was immersed in watching this ad.
+(나는 이 광고를 몰입하여 보았다.)
+- This ad will remain vividly in my memory.
+(이 광고는 나의 기억에 뚜렷하게 남을 것 같다.)
+- I want to press the 'Like' button on this ad.
+(나는 이 광고의 ‘좋아요’ 버튼을 누르고 싶다.)
+- I want to press the 'Share' button on this ad.
+(나는 이 광고의 ‘공유’ 버튼을 누르고 싶다.)
+- I want to watch this ad and press the 'Learn More' button to explore additional relevant information.
+(이 광고를 보고 ‘더 알아보기’ 버튼을 누르고 관련 정보를 추가로 탐색하고 싶다.)
+- I wanted to buy the product in the ad after watching this ad.
+(나는 이 광고를 보고 광고 속 제품을 구매하고 싶어졌다.)
+- It seems like this ad has a lot of information about me.
+(이 광고를 보면 나에 대한 정보를 많이 가지고 있는 것 같다.)
+- It seems like this ad is monitoring my behavior.
+(이 광고는 나의 행동을 감시하는 것 같다.)
+- I am concerned that my information used in this ad will be used in ways I did not expect.
+(이 광고에 사용된 내 정보가 예상치 못한 방법으로 사용될까 염려된다.)
+- This ad provided the information I need.
+(이 광고는 내게 필요한 정보를 제공했다.)
+- This ad provided useful information to me.
+(이 광고는 나에게 유용한 정보를 제공했다.)
+- This ad provided benefits to me.
+(이 광고는 나에게 편익을 제공해 주었다.)
+- This ad provided timely information relevant to me.
+(이 광고는 내게 시의성 있는 정보를 제공했다)</t>
+        </is>
+      </c>
+      <c r="O972" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="n">
+        <v>972</v>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Richard E. Petty, John T. Cacioppo</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Communication and Persuasion: Central and Peripheral Routes to Attitude Change</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>Springer Series in Social Psychology</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Elaboration Likelihood Model (ELM), Cognitive Response Theory, Social Comparison Theory, Heuristic Model of Persuasion</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>[Persuasive Communication] -&gt; [Motivation &amp; Ability to Process] -&gt; [Central Route (Argument Scrutiny) vs. Peripheral Route (Peripheral Cues)] -&gt; [Attitude Change (Enduring vs. Temporary)]</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>H1: People are motivated to hold correct attitudes.
+H2: The amount and nature of issue-relevant elaboration vary with individual and situational factors.
+H3: Variables affect attitude and persuasion by serving as arguments, peripheral cues, or affecting elaboration.
+H4: Variables affecting objective processing enhance or reduce argument scrutiny.
+H5: Variables affecting biased processing produce positive or negative biases to thoughts.
+H6: As processing motivation/ability decreases, peripheral cues become more important; as scrutiny increases, they become less important.
+H7: Attitude changes via the central route show greater temporal persistence, behavioral prediction, and resistance than those via the peripheral route.</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>Source, Message, Recipient, Channel, and Context Variables (e.g., Argument Quality, Personal Relevance, Distraction, Repetition, Need for Cognition)</t>
+        </is>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>Attitude Change, Persistence, Resistance to Counterpersuasion, Attitude-Behavior Consistency</t>
+        </is>
+      </c>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>Cognitive Responses / Issue-Relevant Elaboration (Thoughts generated)</t>
+        </is>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>Motivation and Ability to Process (e.g., Personal Relevance, Need for Cognition, Distraction)</t>
+        </is>
+      </c>
+      <c r="M973" t="inlineStr">
+        <is>
+          <t>Persuasion occurs via two distinct routes: the central route (based on thoughtful consideration of argument merits, yielding enduring attitude changes) and the peripheral route (based on simple cues or heuristics, yielding temporary attitude changes). The ELM successfully integrates seemingly conflicting research findings under a unified framework.</t>
+        </is>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>- Rate how you feel about requiring college seniors to take a comprehensive exam in their major as a requirement for graduation on the scales below. COMPREHENSIVE EXAMS ARE:
+(졸업 요건으로 대학 4학년생들에게 전공 종합시험을 치르게 하는 것에 대해 아래 척도를 바탕으로 어떻게 느끼는지 평가하시오. 종합시험은 다음과 같다:)
+- To what extent do you agree with the proposal requiring college seniors to take a comprehensive exam in their major before graduating?
+(졸업하기 전에 대학 4학년생들에게 전공 종합시험을 치르게 하자는 제안에 어느 정도 동의하십니까?)</t>
+        </is>
+      </c>
+      <c r="O973" t="inlineStr">
+        <is>
+          <t>10.1007/978-1-4612-4964-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="n">
+        <v>973</v>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Tony Berber Sardinha</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>AI-generated vs human-authored texts: A multidimensional comparison</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>Applied Corpus Linguistics</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Biber's (1988) Multidimensional Analysis of Register Variation</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>[Authorship (AI vs Human) &amp; Register] -&gt; [Multidimensional Linguistic Profiles (Dimension Scores)] -&gt; [Authorship Classification / Differentiation]</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>H1: AI-generated texts will exhibit significant disparities from human-authored texts across the main dimensions of register variation when register is accounted for.
+H2: Linear discriminant analysis using dimension scores can effectively predict and classify text authorship (AI vs human) across different registers.</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>Authorship condition (AI-generated vs Human-authored) and Register (Academic, Conversation, L2 Essay, News)</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>Dimension scores across the five main dimensions of register variation (and authorship classification accuracy)</t>
+        </is>
+      </c>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M974" t="inlineStr">
+        <is>
+          <t>When register is factored in, AI-generated texts show significant disparities from human-authored texts across all five linguistic dimensions, particularly in involvement (Dim. 1), persuasion (Dim. 4), and abstraction (Dim. 5). AI models struggle to accurately capture register-specific linguistic features (e.g., failing to emulate natural conversation or appropriate academic referencing), leading to high classification accuracy (79% for AI texts) via discriminant analysis.</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O974" t="inlineStr">
+        <is>
+          <t>10.1016/j.acorp.2023.100083</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="n">
+        <v>974</v>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>박동현</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>ESG Publicity의 협력사 프레이밍(패킹 vs. 언패킹)이 기업이미지에 미치는 영향: 처리유창성과 진정성의 매개효과를 중심으로</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>국립금오공과대학교 대학원</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>기대이론(Prospect Theory), 지지이론(Support Theory)</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>[협력사 프레이밍] -&gt; [처리유창성 / 진정성] -&gt; [기업태도] -&gt; [기업이미지]</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>H1: 협력사 프레이밍이 패킹일 때보다 언패킹일 때 처리유창성이 높을 것이다.
+H2: 협력사 프레이밍은 패킹일 때보다 언패킹일 때 진정성이 높을 것이다.
+H3: 처리유창성이 높을수록 기업태도는 호의적일 것이다.
+H4: 진정성이 높을수록 기업태도는 호의적일 것이다.
+H5: 기업에 대한 태도가 호의적일 때 기업이미지는 좋아질 것이다.
+H6: 처리유창성과 기업태도는 협력사 프레이밍과 기업이미지의 관계를 매개할 것이다.
+H7: 진정성과 기업태도는 협력사 프레이밍과 기업이미지의 관계를 매개할 것이다.
+H8: E, S, G 활동은 협력사 프레이밍과 처리유창성, 진정성의 관계를 조절할 것이다.</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>협력사 프레이밍 (패킹 vs. 언패킹)</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>기업이미지</t>
+        </is>
+      </c>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>처리유창성, 진정성, 기업태도</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>E, S, G 활동</t>
+        </is>
+      </c>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>협력사 정보를 구체적으로 나열하는 언패킹 프레이밍이 포괄적인 패킹 프레이밍보다 처리유창성과 진정성을 높이는 데 더 효과적이며, 이는 호의적인 기업태도를 거쳐 기업이미지 제고에 긍정적인 영향을 미친다. E, S, G 활동의 조절효과는 통계적으로 기각되었으나, 친환경(E) 활동이 처리유창성과 진정성에 가장 큰 영향을 미치는 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>- The information about the partners stands out well.
+(협력사의 정보는 눈에 잘 들어온다.)
+- The information about the partners can be easily perceived.
+(협력사의 정보는 쉽게 인지할 수 있다.)
+- All information about the partners can be distinguished without any restrictions.
+(협력사의 정보는 아무런 제약없이 모두 구별할 수 있다.)
+- The information about the partners can be easily known.
+(협력사의 정보는 쉽게 알 수 있다.)
+- The information about the partners can be understood without difficulty.
+(협력사의 정보는 어려움없이 이해 할 수 있다.)
+- The ESG activities with partners are considered to be from the heart.
+(협력사와 함께하는 ESG활동은 진심에서 우러난 활동이라고 생각된다.)
+- The ESG activities with partners are felt to genuinely care for members of society.
+(협력사와 함께하는 ESG활동은 사회구성원을 진정으로 배려해주는 것으로 느껴진다.)
+- The belief is created that the ESG activities with partners are for the public interest of our society.
+(협력사와 함께하는 ESG활동은 우리사회의 공익을 위한다는 믿음이 생긴다.)
+- Unfavorable / Favorable
+(비호의적인 / 호의적인)
+- Bad / Good
+(나쁜 / 좋은)
+- Uninteresting / Interesting
+(흥미롭지 않은 / 흥미로운)
+- Gana Group doing ESG activities with partners will receive a good reputation in the local community.
+(협력사와 함께 ESG활동을 하는 가나그룹은 지역 사회에서 좋은 평판을 받을 것이다.)
+- Gana Group doing ESG activities with partners will receive a good reputation in the industry.
+(협력사와 함께 ESG활동을 하는 가나그룹은 업계에서 좋은 평판을 받을 것이다.)
+- Gana Group doing ESG activities with partners will receive a good reputation among customers.
+(협력사와 함께 ESG활동을 하는 가나그룹은 고객 사이에서 좋은 평판을 받을 것이다.)
+- Gana Group doing ESG activities with partners will actively participate in the local community.
+(협력사와 함께 ESG활동을 하는 가나그룹은 지역 사회에 적극적으로 참여하고 있을 것이다.)
+- The overall image of Gana Group doing ESG activities with partners will be good.
+(협력사와 함께 ESG활동을 하는 가나그룹의 전반적인 이미지는 좋을 것이다.)</t>
+        </is>
+      </c>
+      <c r="O975" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="n">
+        <v>975</v>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Paul W. Miniard, Joel B. Cohen</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Modeling Personal and Normative Influences on Behavior</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Journal of Consumer Research</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Fishbein behavioral intention model, Informational and Normative Social Influence Theory</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>[Personal Evaluation (PE), Normative Evaluation (NE)] -&gt; [Behavioral Intention (BI)] -&gt; [Behavior (B)]</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>H1: The proposed model separating personal and normative motivations will successfully distinguish between personal and normative influences underlying behavioral intentions and choices.
+H2: Personal considerations will dominate behavioral intentions in personal consumption situations, whereas normative considerations will dominate in social consumption situations.</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>Attitude manipulation (Att), Normative manipulation (Norm)</t>
+        </is>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>Behavioral intention, Brand choice</t>
+        </is>
+      </c>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M976" t="inlineStr">
+        <is>
+          <t>The proposed model effectively distinguishes between personal and normative motivations, overcoming the confounding issues present in the traditional Fishbein model. Both personal and normative components significantly predicted intentions and choices across different contexts.</t>
+        </is>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>- Suppose that you were to recommend Brand A on the sole basis of your own personal considerations. Given this, how favorable or unfavorable would you then feel toward recommending Brand A?
+(만약 당신이 오직 개인적 고려 사항만을 바탕으로 브랜드 A를 추천한다고 가정해보라. 이를 고려할 때, 브랜드 A를 추천하는 것에 대해 얼마나 호의적이거나 비호의적으로 느끼겠는가?)
+- Suppose that you bought beer for serving to your friends at a party on the sole basis of interpersonal considerations (e.g., what important others might think about you and/or how they might act toward you). Given this (considering only important others' reactions), how favorable or unfavorable would you feel toward buying each of the following brands of beer for serving to your friends at a party?
+(만약 당신이 오직 대인관계적 고려 사항(예: 중요한 타인들이 당신에 대해 어떻게 생각할지 그리고/또는 그들이 당신에게 어떻게 행동할지)만을 바탕으로 파티에서 친구들에게 제공할 맥주를 샀다고 가정해보라. 이를 고려할 때(중요한 타인들의 반응만을 고려할 때), 파티에서 친구들에게 제공하기 위해 다음 각 브랜드의 맥주를 구매하는 것에 대해 얼마나 호의적이거나 비호의적으로 느끼겠는가?)
+- The individual feels that the purchase or use of a particular brand will enhance the image which others have of him/her.
+(개인은 특정 브랜드의 구매나 사용이 다른 사람들이 자신에 대해 가지고 있는 이미지를 향상시킬 것이라고 느낀다.)
+- The individual's decision to purchase a particular brand is influenced by the preferences of people with whom s/he has social interaction.
+(개인의 특정 브랜드 구매 결정은 그가 사회적 상호작용을 하는 사람들의 선호에 의해 영향을 받는다.)
+- The desire to satisfy the expectations which others have of him/her has an impact on the individual's brand choice.
+(다른 사람들이 자신에게 갖고 있는 기대를 충족시키고자 하는 욕구는 개인이 브랜드 선택을 하는 데 영향을 미친다.)</t>
+        </is>
+      </c>
+      <c r="O976" t="inlineStr">
+        <is>
+          <t>10.1086/209353</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="n">
+        <v>976</v>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>정한솔</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>AI 도입이 광고 산업에 미치는 영향과 전망</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>기술결정주의, 이용과 충족 이론</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>[AI 기술 도입] -&gt; [광고 효율성 및 직무 환경 변화] -&gt; [소비자 인식/브랜드 충성도 및 광고 운영 효율성]</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>H1-1: AI 기반 개인화 광고는 비개인화 광고보다 더 높은 클릭률(CTR)을 기록할 것이다.
+H1-2: AI 도입 후 광고의 전환율(CVR)이 유의미하게 상승할 것이다.
+H2-1: AI 기반 개인화 광고는 소비자의 광고 신뢰도를 높일 것이다.
+H2-2: 개인화된 광고 경험은 소비자의 브랜드 충성도를 강화할 것이다.
+H3-1: AI 도입은 광고 산업 내 특정 직무에서 인원 감축을 유발할 것이다.
+H3-2: AI 도입 후 광고업계 종사자들은 새로운 기술적 역량을 요구받으며, 이에 따라 직무 재배치 또는 새로운 직무가 창출될 것이다.
+H4-1: AI 도입으로 광고 운영의 실시간 최적화가 가능해져 광고 성과가 향상될 것이다.
+H4-2: AI 기반 시스템은 광고 예산 관리의 효율성을 높여 비용 대비 성과를 증대시킬 것이다.</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>AI 기술 도입</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>광고 효율성, 소비자 행동 및 인식, 광고 산업 직무 환경, 광고 운영 및 예산 관리 효율성</t>
+        </is>
+      </c>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M977" t="inlineStr">
+        <is>
+          <t>AI 기술 도입은 광고의 전환율(CVR), 소비자 신뢰, 브랜드 충성도 향상에 긍정적인 영향을 미쳤으나, 클릭률(CTR) 측면에서는 두 광고 간 유의미한 차이가 나타나지 않았다. 종사자 측면에서는 반복 업무의 자동화와 새로운 기술 습득 요구가 확인되었으며, 실시간 최적화를 통한 광고 운영 및 예산 관리의 효율성이 증대된 것으로 나타났다.</t>
+        </is>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>- A 광고가 귀하의 관심을 더 잘 반영한다고 생각하십니까?
+(Does A advertisement reflect your interest better?)
+- A 광고가 신뢰할 수 있는 광고라고 느끼십니까?
+(Do you feel that A advertisement is trustworthy?)
+- AI를 통해 맞춤형으로 제공된 광고가 브랜드에 대한 충성도에 긍정적 영향을 미쳤다고 생각하십니까?
+(Do you think that personalized advertisements provided through AI have had a positive impact on brand loyalty?)
+- 온라인 광고로 제공된 맞춤형 정보가 귀하의 구매 결정에 긍정적인 영향을 미쳤습니까?
+(Did the personalized information provided through online advertising positively influence your purchase decision?)
+- AI 도입 전후 광고 성과(CTR, CVR, ROAS 등)를 비교했을 때, 성과가 향상되었습니까?
+(When comparing advertising performance before and after AI adoption, has performance improved?)
+- AI 도입 후 귀하의 직무에서 반복적 작업 또는 업무량이 줄어들었습니까?
+(Has the repetitive work or workload in your job decreased after AI adoption?)
+- AI 활용 및 데이터 분석이 업무에 필요하다고 생각하십니까?
+(Do you think that AI utilization and data analysis are necessary for your work?)
+- AI 도입이 광고업계의 인력 변화에 영향을 미쳤다고 생각하십니까?
+(Do you think that AI adoption has influenced workforce changes in the advertising industry?)
+- AI가 광고 캠페인을 실시간 최적화하는 데 도움이 되었습니까?
+(Has AI been helpful in real-time optimization of advertising campaigns?)
+- AI가 예산 관리 효율성을 높여 비용 대비 성과를 증가시키는 데 기여하였습니까?
+(Has AI contributed to increasing cost-effectiveness by enhancing budget management efficiency?)</t>
+        </is>
+      </c>
+      <c r="O977" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="n">
+        <v>977</v>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Tamara Dinev, Paul Hart</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>An Extended Privacy Calculus Model for E-Commerce Transactions</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>Information Systems Research</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>프라이버시 계산 모델 (Privacy Calculus Model), 기대 이론 (Expectancy Theory)</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>[Perceived Internet Privacy Risk, Internet Trust, Personal Internet Interest, Internet Privacy Concerns] -&gt; [Willingness to Provide Personal Information to Transact on the Internet]</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>H1: 지각된 인터넷 프라이버시 위험이 높을수록 인터넷 거래 시 개인정보 제공 의도가 낮아진다.
+H2: 지각된 인터넷 프라이버시 위험이 높을수록 인터넷 프라이버시 우려가 높아진다.
+H3: 인터넷 프라이버시 우려가 높을수록 인터넷 거래 시 개인정보 제공 의도가 낮아진다.
+H4: 인터넷 신뢰가 높을수록 인터넷 거래 시 개인정보 제공 의도가 높아진다.
+H5: 지각된 인터넷 프라이버시 위험이 낮을수록 인터넷 신뢰가 높아진다.
+H6: 개인의 인터넷 관심도가 높을수록 인터넷 거래 시 개인정보 제공 의도가 높아진다.</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>지각된 인터넷 프라이버시 위험(Perceived Internet Privacy Risk), 인터넷 신뢰(Internet Trust), 개인의 인터넷 관심도(Personal Internet Interest)</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>인터넷 거래를 위한 개인정보 제공 의도(Willingness to Provide Personal Information to Transact on the Internet)</t>
+        </is>
+      </c>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>인터넷 프라이버시 우려(Internet Privacy Concerns)</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M978" t="inlineStr">
+        <is>
+          <t>인터넷 프라이버시 우려는 전자상거래 거래를 저해하는 요인이지만, 인터넷 신뢰와 개인적 인터넷 관심도의 누적된 영향은 개인정보 공개 결정에서 프라이버시 위험 지각을 압도할 수 있는 중요한 요소로 작용함이 확인되었다. 구조방정식 모형 분석 결과, 제안된 확장된 프라이버시 계산 모형의 타당성이 실증적으로 검증되었다.</t>
+        </is>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>- PPIT 1: Purchase goods (e.g., books or CDs) or services (e.g., airline tickets or hotel reservations) from websites that require me to submit accurate and identifiable information (i.e., credit card information)
+(정확하고 식별 가능한 정보(즉, 신용카드 정보)를 제출해야 하는 웹사이트에서 상품(예: 책 또는 CD) 또는 서비스(예: 항공권 또는 호텔 예약)를 구매한다.)
+- PPIT 2: Retrieve information from websites that require me to submit accurate and identifiable registration information, possibly including credit card information (e.g., using sites that provide personalized stock quotes, insurance rates, or loan rates; or using sexual or gambling websites)
+(신용카드 정보를 포함할 수 있는 정확하고 식별 가능한 등록 정보를 제출해야 하는 웹사이트에서 정보를 검색한다(예: 개인화된 주가 정보, 보험료 또는 대출 금리를 제공하는 사이트 이용, 성인용 또는 도박 웹사이트 이용))
+- PPIT 3: Conduct sales transactions at e-commerce sites that require me to provide credit card information (e.g., using sites for purchasing goods or software)
+(신용카드 정보 제공을 요구하는 전자상거래 사이트에서 판매 거래를 수행한다(예: 상품이나 소프트웨어 구매를 위한 사이트 이용))
+- PPIT 4: Retrieve highly personal and password-protected financial information (e.g., using websites that allow me to access my bank account or my credit card account)
+(매우 개인적이고 비밀번호로 보호되는 금융 정보를 검색한다(예: 은행 계좌나 신용카드 계좌에 접속할 수 있는 웹사이트 이용))
+- PR1: Records of transactions could be sold to third parties?
+(거래 기록이 제3자에게 판매될 수 있는가?)
+- PR2: Personal information submitted could be misused?
+(제출된 개인정보가 오용될 수 있는가?)
+- PR3: Personal information could be made available to unknown individuals or companies without your knowledge?
+(귀하가 모르는 사이에 개인정보가 알 수 없는 개인이나 회사에 제공될 수 있는가?)
+- PR4: Personal information could be made available to government agencies?
+(개인정보가 정부 기관에 제공될 수 있는가?)
+- PC1: I am concerned that the information I submit on the Internet could be misused.
+(나는 인터넷에 제출하는 정보가 오용될까 우려된다.)
+- PC2: I am concerned that a person can find private information about me on the Internet.
+(나는 누군가가 인터넷에서 나의 사생활에 관한 정보를 찾아낼 수 있을까 우려된다.)
+- PC3: I am concerned about submitting information on the Internet, because of what others might do with it.
+(다른 사람들이 그것을 가지고 무엇을 할지 모르기 때문에, 나는 인터넷에 정보를 제출하는 것이 우려된다.)
+- PC4: I am concerned about submitting information on the Internet, because it could be used in a way I did not foresee.
+(내가 예상하지 못한 방식으로 사용될 수 있기 때문에, 나는 인터넷에 정보를 제출하는 것이 우려된다.)
+- T1: Internet websites are safe environments in which to exchange information with others.
+(인터넷 웹사이트는 다른 사람들과 정보를 교환하기에 안전한 환경이다.)
+- T2: Internet websites are reliable environments in which to conduct business transactions.
+(인터넷 웹사이트는 비즈니스 거래를 수행하기에 신뢰할 수 있는 환경이다.)
+- T3: Internet websites handle personal information submitted by users in a competent fashion.
+(인터넷 웹사이트는 사용자가 제출한 개인정보를 유능한 방식으로 처리한다.)
+- PI1: I find that personal interest in the information that I want to obtain from the Internet overrides my concerns of possible risk or vulnerability that I may have regarding my privacy.
+(나는 인터넷으로부터 얻고자 하는 정보에 대한 개인적 관심이 나의 프라이버시와 관련하여 내가 가질 수 있는 잠재적 위험이나 취약성에 대한 우려보다 우선한다고 생각한다.)
+- PI2: The greater my interest to obtain a certain information or service from the Internet, the more I tend to suppress my privacy concerns.
+(인터넷으로부터 특정 정보나 서비스를 얻고자 하는 관심이 클수록, 나는 프라이버시 우려를 억제하는 경향이 있다.)
+- PI3: In general, my need to obtain certain information or services from the Internet is greater than my concern about privacy.
+(일반적으로, 인터넷으로부터 특정 정보나 서비스를 얻고자 하는 나의 필요성은 프라이버시에 대한 우려보다 크다.)</t>
+        </is>
+      </c>
+      <c r="O978" t="inlineStr">
+        <is>
+          <t>10.1287/isre.1060.0080</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="n">
+        <v>978</v>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Oscar Chrismadian Noventa, Maria Rosa Ratna Sri Anggraeni Widjojo, Martius Parnawa Putranta</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Exploration of Factors Affecting Consumer Perceptions of Advertisements Generated by Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Research Horizon</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Stimulus-Organism-Response (SOR) framework</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>[Perceived Realism, Vitality, Imagination, Synthesis] -&gt; [Perceived Intelligence] -&gt; [Willingness to Accept]</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>H1: Perceived realism has a positive effect on perceived intelligence.
+H2: Vitality has a positive effect on perceived intelligence.
+H3: Imagination has a positive effect on perceived intelligence.
+H4: Synthesis has a negative effect on perceived intelligence.
+H5: Perceived intelligence has a positive effect on willingness to accept.</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>Perceived realism, Vitality, Imagination, Synthesis</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>Willingness to accept AI-generated advertising</t>
+        </is>
+      </c>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>Perceived intelligence</t>
+        </is>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M979" t="inlineStr">
+        <is>
+          <t>Perceived realism, vitality, imagination, and synthesis all positively influence perceived intelligence, with imagination being the strongest predictor. Perceived intelligence significantly enhances consumers' willingness to accept AI-generated advertising.</t>
+        </is>
+      </c>
+      <c r="N979" t="inlineStr">
+        <is>
+          <t>- The AI-generated advertisement looks realistic and resembles real-world conditions.
+(AI로 생성된 광고는 현실감 있고 실제 조건과 유사해 보인다.)
+- The visuals in the AI-generated ad appear authentic and lifelike.
+(AI로 생성된 광고의 시각적 요소는 진정성 있고 생생해 보인다.)
+- The details presented in the advertisement reflect real-life situations accurately.
+(광고에 제시된 세부 사항들은 실제 상황을 정확하게 반영한다.)
+- The AI-generated advertisement exhibits high vitality and expressive energy.
+(AI로 생성된 광고는 높은 활력과 표현 에너지를 보여준다.)
+- The visuals in the ad are lively and dynamic.
+(광고의 시각적 요소들은 생동감 있고 역동적이다.)
+- The advertisement displays a strong sense of aliveness and movement.
+(광고는 강한 생명력과 움직임의 느낌을 보여준다.)
+- The AI-generated advertisement shows a high level of imagination.
+(AI로 생성된 광고는 높은 수준의 상상력을 보여준다.)
+- The ad presents novel and creative visual concepts.
+(광고는 참신하고 창의적인 시각적 개념들을 제시한다.)
+- The ideas generated in the advertisement are original and unique.
+(광고에서 생성된 아이디어들은 독창적이고 독특하다.)
+- The advertisement demonstrates inventive thinking in its design.
+(광고는 디자인에서 독창적인 사고를 보여준다.)
+- The AI-generated advertisement appears artificially assembled or disjointed in its visual elements.
+(AI로 생성된 광고는 시각적 요소들에서 인위적으로 조립되었거나 단절되어 보인다.)
+- The visual components in the ad display awkward positioning or unnatural proportions.
+(광고의 시각적 구성 요소들은 어색한 배치나 부자연스러운 비율을 보여준다.)
+- There is a noticeable lack of seamless integration among objects within the advertisement composition.
+(광고 구성 내 객체들 간에 매끄러운 통합이 눈에 띄게 부족하다.)
+- The advertisement displays structural irregularities or disharmonious elements.
+(광고는 구조적 불규칙성이나 부조화스러운 요소들을 보여준다.)
+- The AI system behind the advertisement demonstrates high intelligence and competence.
+(광고 이면의 AI 시스템은 높은 지능과 유능함을 보여준다.)
+- The AI-generated output reflects accurate and smart processing capabilities.
+(AI로 생성된 결과물은 정확하고 영리한 처리 능력을 반영한다.)
+- The advertisement shows that the technology is capable of generating sophisticated solutions.
+(광고는 해당 기술이 정교한 해결책을 생성할 수 능력이 있음을 보여준다.)
+- I am willing to accept and engage with AI-generated advertisements.
+(나는 AI로 생성된 광고를 수용하고 관여할 의향이 있다.)
+- I would consider purchasing products promoted through AI-generated advertisements.
+(나는 AI로 생성된 광고를 통해 홍보되는 제품을 구매하는 것을 고려할 것이다.)
+- I have a positive intention to view and respond to AI-generated advertising content.
+(나는 AI로 생성된 광고 콘텐츠를 보고 반응할 긍정적인 의도를 가지고 있다.)</t>
+        </is>
+      </c>
+      <c r="O979" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/GBC_연구논문_DB.xlsx
+++ b/database/GBC_연구논문_DB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O979"/>
+  <dimension ref="A1:O988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80204,6 +80204,1467 @@
         </is>
       </c>
     </row>
+    <row r="980">
+      <c r="A980" t="n">
+        <v>979</v>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>이주희</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>맞춤형 광고에 대한 소비자 반응 연구: 소비자 구매 여정과 프라이버시 계산 모델을 중심으로</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>숙명여자대학교 대학원 박사학위논문</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>소비자 구매 여정 모델(Consumer Decision Journey Model), 프라이버시 계산 모델(Privacy Calculus Model), 기술수용모델(Technology Acceptance Model)</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>[독립변수: 소비자 구매 여정 단계] -&gt; [매개변수: 인지된 유용성, 프라이버시 염려] (조절변수: 광고의 적시성) -&gt; [종속변수: 광고 태도, 반응의도, 광고 수용의도]</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>H1: 소비자 구매 여정에 따라 소비자가 인지하는 맞춤형 광고의 반응인 (a) 광고 태도, (b) 반응의도, (c) 광고 수용의도가 다르게 나타날 것이다.
+H2: 소비자가 인지하는 맞춤형 광고의 인지된 유용성이 높아질수록 맞춤형 광고에 대한 반응인 (a) 광고 태도, (b) 반응의도, (c) 광고 수용의도가 높아질 것이다.
+H3: 소비자가 인지하는 맞춤형 광고의 프라이버시 염려가 높아질수록 맞춤형 광고에 대한 반응인 (a) 광고 태도, (b) 반응의도, (c) 광고 수용의도가 낮아질 것이다.</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>소비자 구매 여정 단계 (초기 고려 단계, 적극적 평가 단계, 구매 결정 단계, 구매 후 단계)</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>맞춤형 광고에 대한 반응 (광고 태도, 반응의도, 광고 수용의도)</t>
+        </is>
+      </c>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>인지된 유용성, 프라이버시 염려</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>광고의 적시성</t>
+        </is>
+      </c>
+      <c r="M980" t="inlineStr">
+        <is>
+          <t>1. 소비자 구매 여정에 따라 맞춤형 광고에 대한 태도, 반응의도, 광고 수용의도에 유의미한 차이가 존재하였으며, 구매 후 단계에서 소비자의 광고 반응이 공통적으로 가장 낮게 나타남.
+2. 맞춤형 광고에 대한 인지된 유용성이 높을수록 광고 반응(태도, 반응의도, 수용의도)이 긍정적이었고, 프라이버시 염려가 높을수록 광고 반응이 부정적이었음.
+3. 소비자 구매 여정에 따라 프라이버시 계산 모델의 영향력이 상이하게 나타남. 인지된 유용성의 정적 영향력은 구매 결정 단계까지 점차 커지다가 구매 후 단계에서 감소하는 반면, 프라이버시 염려의 부적 영향력은 구매 후 단계에서 다시 커지는 경향을 보임.
+4. 소비자 구매 여정과 맞춤형 광고 반응 간의 관계에서 인지된 유용성의 매개효과에 대한 광고 적시성의 조절된 매개효과가 검증됨 (프라이버시 염려의 조절된 매개효과는 유의하지 않음).</t>
+        </is>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>[인지된 유용성]
+I can get the information I want through this ad.
+(나는 이 광고를 통해 내가 원하는 정보를 얻을 수 있다.)
+This ad provides useful information to me.
+(이 광고는 나에게 유용한 정보를 제공한다.)
+I can easily find the information I want through this ad.
+(이 광고를 통해 원하는 정보를 쉽게 찾을 수 있다.)
+I think this ad is generally useful to me.
+(이 광고는 전반적으로 나에게 유용하다고 생각한다.)
+[프라이버시 염려]
+Seeing this ad makes me feel like the site is tracking information about me.
+(이 광고를 보면 해당 사이트가 나에 대한 정보를 추적하는 것 같다.)
+Seeing this ad makes me feel like the site has too much information about me.
+(이 광고를 보면 해당 사이트가 나에 대한 정보를 너무 많이 가지고 있는 것 같다.)
+Seeing this ad makes me feel like the site is accessing information about me.
+(이 광고를 보면 해당 사이트가 나에 대한 정보에 접근하는 것 같다.)
+I am concerned that my information used in this ad will be used in ways I did not expect.
+(이 광고에 쓰인 내 정보가 내가 예상하지 못하는 방법으로 사용될까 염려된다.)
+[광고 태도]
+I am satisfied with personalized ads.
+(나는 맞춤형 광고에 만족한다.)
+For me, personalized ads are a pleasant experience.
+(나에게 맞춤형 광고는 즐거운 경험이다.)
+I feel favorable toward personalized ads.
+(나는 맞춤형 광고에 호감이 간다.)
+[반응의도]
+I want to click 'Like' on this ad.
+(이 광고에 '좋아요'를 누르고 싶다.)
+I want to click and check this ad.
+(이 광고를 클릭해서 확인하고 싶다.)
+I want to recommend this ad to others.
+(이 광고를 다른 사람에게 추천하고 싶다.)
+I will talk about this ad with people around me.
+(이 광고를 보고 주변 사람들과 이야기할 것이다.)
+[광고 수용의도]
+I intend to continue using personalized ads.
+(나는 맞춤형 광고를 계속 사용할 의향이 있다.)
+I will continue to use personalized ads at the current level.
+(나는 현재와 같은 수준으로 맞춤형 광고의 이용을 지속할 것이다.)
+I intend to increase my use of personalized ads in the future.
+(나는 앞으로 맞춤형 광고의 사용을 늘릴 의향이 있다.)
+[광고의 적시성]
+This ad provides information about the product in a timely manner.
+(이 광고는 제품에 대한 정보를 적시에 제공한다.)
+This ad is provided by reflecting my recent online behavior information.
+(이 광고는 나의 최근 온라인 행태 정보를 반영하여 제공된다.)
+This ad reflects my current situation.
+(이 광고는 현재 나의 상황을 반영한다.)
+I consider interaction with real-time information provided by this ad to be important.
+(나는 이 광고가 주는 실시간 정보와의 상호작용을 중요하게 생각한다.)</t>
+        </is>
+      </c>
+      <c r="O980" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="n">
+        <v>980</v>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>김도형</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>OBA의 정보가치가 인지부하 및 광고태도에 미치는 영향: CLT의 조절효과를 중심으로</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>국립금오공과대학교 컨설팅대학원 컨설팅학과 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>인지부하이론 (Cognitive Load Theory), 해석수준이론 (Construal Level Theory), 광고가치모형 (Ducoffe's Advertising Value Model)</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>[독립변수: 광고 유형 (맞춤형 OBA vs. 비맞춤형)] -&gt; [매개변수 1: 지각된 정보가치 (정보성, 유용성, 신뢰성)] -&gt; [매개변수 2: 인지부하] -&gt; [종속변수: 광고태도] (조절변수: 해석수준이 지각된 정보가치와 인지부하 간의 관계를 조절)</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>H1: 온라인 맞춤형 광고는 비맞춤형 광고보다 지각된 정보성이 더 높을 것이다.
+H2: 온라인 맞춤형 광고는 비맞춤형 광고보다 지각된 유용성이 더 높을 것이다.
+H3: 온라인 맞춤형 광고는 비맞춤형 광고보다 지각된 신뢰성이 더 높을 것이다.
+H4: 지각된 정보성이 높을수록 인지부하는 감소할 것이다.
+H5: 지각된 유용성이 높을수록 인지부하는 감소할 것이다.
+H6: 지각된 신뢰성이 높을수록 인지부하는 감소할 것이다.
+H7: 인지부하가 높을수록 광고태도는 부정적일 것이다.
+H8: 해석수준은 지각된 정보성과 인지부하의 관계를 조절할 것이다.
+H9: 해석수준은 지각된 유용성과 인지부하의 관계를 조절할 것이다.
+H10: 해석수준은 지각된 신뢰성과 인지부하의 관계를 조절할 것이다.</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>광고 유형 (온라인 맞춤형 광고 vs. 비맞춤형 광고)</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>광고태도</t>
+        </is>
+      </c>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>지각된 정보가치 (정보성, 유용성, 신뢰성), 인지부하</t>
+        </is>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>해석수준 (Construal Level)</t>
+        </is>
+      </c>
+      <c r="M981" t="inlineStr">
+        <is>
+          <t>1. 온라인 맞춤형 광고(OBA)는 비맞춤형 광고에 비해 소비자의 지각된 정보성, 유용성, 신뢰성을 유의하게 향상시킴.
+2. 정보가치의 하위 요인 중 지각된 유용성만이 인지부하를 유의하게 감소시키는 직접적인 예측 요인으로 작용함.
+3. 인지부하는 광고태도에 유의한 부정적(-) 영향을 미침.
+4. '광고유형 -&gt; 지각된 정보가치 -&gt; 인지부하 -&gt; 광고태도'로 이어지는 순차적 간접효과가 유의하게 나타남.
+5. 해석수준은 정보가치(정보성, 유용성, 신뢰성)와 인지부하 간의 관계를 유의하게 조절함. 특히 높은 해석수준(추상적 사고) 집단에서 정보가치가 인지부하를 감소시키는 효과가 낮은 해석수준 집단에 비해 2배 이상 강력하게 나타남.</t>
+        </is>
+      </c>
+      <c r="N981" t="inlineStr">
+        <is>
+          <t>[지각된 정보성 (Perceived Informativeness)]
+- The ad provided the information I needed.
+(필요한 정보를 제공했다.)
+- The ad provided an appropriate level of information.
+(적절한 수준의 정보를 제공했다.)
+- The ad provided timely information.
+(시의적절한 정보를 제공했다.)
+[지각된 유용성 (Perceived Usefulness)]
+- The ad is helpful for my decision-making.
+(나의 의사결정에 도움이 된다.)
+- The ad helps save time and effort.
+(시간/노력 절감에 도움이 된다.)
+- Overall, the ad is useful.
+(전반적으로 유용하다.)
+[지각된 신뢰성 (Perceived Credibility)]
+- The content of the ad/recommendation is truthful.
+(광고/추천 내용은 진실성이 있다.)
+- The source (platform/brand) is trustworthy.
+(출처(플랫폼/브랜드)를 믿을 만하다.)
+- Overall, the ad is credible.
+(전반적으로 신뢰할 수 있다.)
+[인지부하 (Cognitive Load)]
+- The presentation/layout of the ad was confusing.
+(표현/배치가 혼란스러웠다.)
+- There was too much unnecessary information, which interfered with my understanding.
+(불필요한 정보가 많아 이해가 방해됐다.)
+- The content of the ad itself was difficult.
+(내용 자체가 어렵다.)
+- Understanding the ad required significant mental effort.
+(이해에 상당한 정신적 노력이 필요했다.)
+- This ad/recommendation was helpful in summarizing the core points.
+(이 광고/추천은 핵심을 정리하는 데 도움이 됐다.)
+- This ad/recommendation was helpful in clarifying the decision criteria.
+(결정 기준을 명확히 하는 데 도움이 됐다.)
+[광고태도 (Advertising Attitude)]
+- Overall, the ad is good.
+(전반적으로 좋다.)
+- The ad is appealing.
+(호감이 간다.)
+- The ad gives a positive feeling.
+(긍정적 느낌이 든다.)
+[해석수준 (Construal Level - BIF)]
+- Making a list: (a) Getting organized vs. (b) Writing things down
+(목록 만들기: (a) 정리 정돈하기 vs. (b) 할 일/항목을 적어 두기)
+- Reading a book: (a) Following lines of print vs. (b) Gaining knowledge
+(책 읽기: (a) 글줄을 따라가기 vs. (b) 지식을 얻기)
+- Washing clothes: (a) Removing odors from clothes vs. (b) Putting clothes into the washing machine
+(옷 세탁하기: (a) 옷에서 불쾌한 냄새 없애기 vs. (b) 옷을 세탁기에 넣기)
+- Picking apples: (a) Getting something to eat vs. (b) Pulling an apple from a branch
+(사과 따기: (a) 먹을 것을 얻기 vs. (b) 가지에서 사과를 따기)
+- Locking a door: (a) Putting a key in the lock vs. (b) Securing the house
+(문 잠그기/닫기: (a) 열쇠를 자물쇠에 꽂기 vs. (b) 집을 안전하게 지키기)
+- Voting: (a) Influencing an election outcome vs. (b) Marking a ballot
+(투표하기: (a) 선거 결과에 영향을 미치기 vs. (b) 투표용지에 선택을 표시하기)
+- Brushing teeth: (a) Preventing tooth decay vs. (b) Moving a brush in one's mouth
+(양치질하기: (a) 충치를 예방하기 vs. (b) 입 안에서 칫솔을 움직이기)</t>
+        </is>
+      </c>
+      <c r="O981" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>981</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>전현수</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>OTT 라이브 스포츠 중계 컨텐츠에서 스포츠 경기상황과 맥락 일치성에 따른 시청자의 광고 태도와 지각된 침입성</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>서울대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>제한된 인지자원이론(LC4MP), 매체 스포츠 이론(핫/쿨 스포츠), 일관성 이론, 촉발 효과</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>[스포츠 경기상황(핫/쿨), 맥락 일치성(일치/불일치)] -&gt; [광고 태도, 지각된 침입성]</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>H1: 핫 맥락의 스포츠 경기상황은 쿨 맥락보다 광고 태도가 더 높을 것이다.
+H2: 핫 맥락의 스포츠 경기상황은 쿨 맥락보다 지각된 침입성이 더 낮을 것이다.
+H3: 컨텐츠와 맥락이 일치하는 광고는 불일치하는 광고보다 광고 태도가 더 높을 것이다.
+H4: 컨텐츠와 맥락이 일치하는 광고는 불일치하는 광고보다 지각된 침입성이 더 낮을 것이다.
+H5: 스포츠 경기상황과 광고의 맥락 일치성은 광고 태도에 유의한 상호작용 효과를 보일 것이다.
+H6: 스포츠 경기상황과 광고의 맥락 일치성은 지각된 침입성에 유의한 상호작용 효과를 보일 것이다.</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>스포츠 경기상황(핫 맥락 vs. 쿨 맥락), 광고의 맥락 일치성(일치 vs. 불일치)</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>광고 태도, 지각된 침입성</t>
+        </is>
+      </c>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M982" t="inlineStr">
+        <is>
+          <t>첫째, 핫 맥락의 스포츠 경기상황은 쿨 맥락보다 광고 태도가 더 높고 지각된 침입성이 더 낮게 나타났다. 둘째, 컨텐츠와 맥락이 일치하는 광고는 불일치하는 광고보다 광고 태도가 더 높았으나, 지각된 침입성에서는 유의한 차이가 없었다. 셋째, 광고 태도에서는 상호작용이 없었으나, 지각된 침입성에서는 경기상황과 맥락 일치성의 유의한 상호작용이 확인되어 쿨 맥락에서는 불일치 광고의 침입성이 가장 높게 나타났다.</t>
+        </is>
+      </c>
+      <c r="N982" t="inlineStr">
+        <is>
+          <t>- 나는 경기 중에 나타난 광고가 좋다.
+(I like the advertisement shown during the game.)
+- 나는 경기 중에 나타난 광고를 긍정적으로 생각한다.
+(I think positively of the advertisement shown during the game.)
+- 나는 경기 중에 나타난 광고가 흥미롭다.
+(I find the advertisement shown during the game interesting.)
+- 나는 경기 중에 나타난 광고가 불쾌하다.
+(I find the advertisement shown during the game unpleasant.)
+- 나는 경기 중에 나타난 광고가 짜증난다.
+(I find the advertisement shown during the game annoying.)
+- 경기 중 광고가 나왔을 때 집중이 흐트러졌다.
+(My concentration was disturbed when the advertisement appeared during the game.)
+- 경기 중 광고가 나왔을 때 불쾌감을 느꼈다.
+(I felt a sense of displeasure when the advertisement appeared during the game.)
+- 경기 중 광고가 자연스럽지 않고 억지로 삽입된 것처럼 느껴졌다.
+(The advertisement during the game felt unnatural and forcibly inserted.)
+- 광고가 경기 시청을 방해하는 것처럼 느껴졌다.
+(The advertisement felt like it was disrupting my game viewing.)
+- 광고가 내 경기 시청 경험에 침입(개입)하는 것처럼 느껴졌다.
+(The advertisement felt like an intrusion into my game viewing experience.)
+- 경기 중에 나온 광고가 너무 눈에 띄어 거슬렸다.
+(The advertisement shown during the game was too prominent and bothersome.)
+- 이 광고는 스포츠중계방송과 잘 어울린다.
+(This advertisement goes well with the sports broadcasting.)
+- 이 광고는 스포츠중계방송과 일관성이 있다.
+(This advertisement is consistent with the sports broadcasting.)
+- 이 광고는 스포츠중계방송과 공통점이 많다.
+(This advertisement has a lot in common with the sports broadcasting.)
+- 이 광고가 스포츠중계방송 중간에 나올 때 중계방송의 신뢰도를 낮춘다.
+(When this advertisement appears in the middle of sports broadcasting, it lowers the credibility of the broadcast.)
+- 이 광고가 스포츠중계방송 중간에 나오는 것은 광고와 중계방송 모두에게 긍정적인 효과를 준다.
+(The appearance of this advertisement in the middle of sports broadcasting has a positive effect on both the advertisement and the broadcast.)
+- 이 경기의 진행속도는 빠르다.
+(The pacing of this game is fast.)
+- 이 경기의 진행형태는 복잡하다.
+(The progression format of this game is complex.)
+- 이 경기에서 예상치 못한 동작(흐름)의 발생 확률은 높은 편이다.
+(The probability of unexpected actions or flows occurring in this game is high.)
+- 이 경기에 등장하는 선수들의 움직임은 활발하고 다양하게 전개된다.
+(The movements of the players in this game are active and diverse.)
+- 이 경기를 시청하는 데 있어서 주의를 끌어당기는 요인들이 많다.
+(There are many factors that attract attention when watching this game.)
+- 나는 경기를 시청할 때 경기에 깊이 몰두해 있었다.
+(I was deeply immersed in the game when watching it.)
+- 나는 경기를 시청할 때 경기에 빠져들었다.
+(I was absorbed in the game when watching it.)
+- 나는 경기를 시청할 때 경기에서 눈을 뗄 수 없었다.
+(I could not take my eyes off the game when watching it.)
+- 나는 경기를 시청할 때 다른 일들은 생각나지 않았다.
+(I could not think of anything else when watching the game.)
+- 나는 경기를 시청할 때 시간이 생각보다 빨리 지나갔다.
+(Time passed faster than expected when watching the game.)</t>
+        </is>
+      </c>
+      <c r="O982" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>982</v>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>고현우</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>광고홍보학교육분야에서 생성형 AI를 활용한 광고 사용 의도: 혁신저항의 조절 효과를 중심으로</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>한양대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>확장된 통합기술수용이론 (UTAUT2), 혁신저항이론</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>[성과기대, 노력기대, 사회적영향, 쾌락적동기] -&gt; [사용의도] (혁신저항의 조절효과)</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>H1: UTAUT2를 바탕으로한 기술수용 요인은 대학생들의 생성형 AI 사용 의도에 정(+)적 영향을 미칠 것이다.
+H1-1: 성과기대는 생성형 AI 광고제작 사용 의도에 정(+)적 영향을 미칠 것이다.
+H1-2: 노력기대는 생성형 AI 광고제작 사용 의도에 정(+)적 영향을 미칠 것이다.
+H1-3: 사회적영향은 생성형 AI 광고제작 사용 의도에 정(+)적 영향을 미칠 것이다.
+H1-4: 촉진조건은 생성형 AI 광고제작 사용 의도에 정(+)적 영향을 미칠 것이다.
+H1-5: 쾌락적동기는 생성형 AI 광고제작 사용 의도에 정(+)적 영향을 미칠 것이다.
+연구문제 1: 혁신저항은 UTAUT2 변인과 생성형 AI 광고제작 사용 의도간의 관계를 조절하는 역할을 수행할 것인가?</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>성과기대, 노력기대, 사회적영향, 촉진조건, 쾌락적동기</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>생성형 AI 광고제작 사용의도</t>
+        </is>
+      </c>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>혁신저항</t>
+        </is>
+      </c>
+      <c r="M983" t="inlineStr">
+        <is>
+          <t>성과기대, 사회적영향, 쾌락적동기는 사용의도에 정(+)적 영향을 미쳤으나, 노력기대는 유의한 영향을 미치지 않았다. 또한 혁신저항의 조절효과는 통계적으로 유의하지 않았다.</t>
+        </is>
+      </c>
+      <c r="N983" t="inlineStr">
+        <is>
+          <t>- Performance Expectancy
+- Generative AI is useful in daily life.
+(생성형 AI는 일상생활에 유용하다고 생각한다.)
+- Using generative AI would help me save time.
+(생성형 AI를 사용하면 시간을 절약하게 해 줄 것이라고 생각한다.)
+- Using generative AI helps me perform tasks faster.
+(생성형 AI를 사용하면 업무를 더 빠르게 수행하는 데 도움이 된다.)
+- Using generative AI increases the likelihood of achieving important goals.
+(생성형 AI를 사용하면 중요한 목표를 달성할 가능성이 높아진다고 생각한다.)
+- Effort Expectancy
+- Learning how to use generative AI is not difficult.
+(생성형 AI의 이용방법을 배우고 익히는 것은 어렵지 않다.)
+- Becoming fluent in using generative AI is easy.
+(생성형 AI 사용에 익숙해지는 것은 쉽다.)
+- The instructions for using generative AI are easy.
+(생성형 AI 사용법은 쉽다고 생각한다.)
+- Interacting with generative AI is easy.
+(생성형 AI와 상호작용하는 것은 쉽다.)
+- Social Influence
+- My friends think I should use generative AI.
+(나의 친구들은 내가 생성형 AI를 사용해야 한다고 생각한다.)
+- Not using generative AI makes me feel alienated from people around me.
+(생성형 AI를 사용하지 않으면 주변 사람들과 소외된 느낌을 받는다.)
+- People who are important to me recommend that I use generative AI.
+(내가 중요하게 생각하는 사람들은 내가 생성형 AI를 이용하는 것을 추천한다.)
+- Hedonic Motivation
+- Using generative AI is interesting.
+(생성형 AI를 사용하는 것은 흥미롭다고 생각한다.)
+- Using generative AI provides a unique experience.
+(생성형 AI를 사용하는 것은 독특한 경험을 제공한다고 생각한다.)
+- Using generative AI stimulates my curiosity.
+(생성형 AI를 사용하는 것은 나의 호기심을 자극한다.)
+- Using generative AI is enjoyable.
+(생성형 AI를 사용하는 것은 즐겁다.)
+- Innovative Resistance
+- Viewers may react negatively to advertisements using generative AI.
+(생성형 AI를 이용한 광고에 대해 시청자들은 부정적인 반응을 보일 수 있다고 생각한다.)
+- Using generative AI poses legal risks such as copyright or personal information.
+(생성형 AI를 사용하는 경우 저작권이나 개인정보와 같은 법적 위험이 있다고 생각한다.)
+- Planning advertisements using generative AI could damage the planner's reputation.
+(생성형 AI를 사용해서 광고를 기획한다면 기획자의 평판이 손상될 수 있다고 생각한다.)
+- Using generative AI is dangerous due to false information such as deepfakes or fake news.
+(생성형 AI는 딥페이크나 가짜 뉴스 등의 허위 정보로 인해 사용하는 것은 위험하다.)
+- Intention to Use
+- I intend to plan advertising marketing using generative AI.
+(나는 생성형 AI를 활용하여 광고 마케팅을 기획할 의향이 있다.)
+- Generative AI is a necessary service for me.
+(생성형 AI는 나에게 필요한 서비스이다.)
+- I will actively use generative AI.
+(나는 생성형 AI를 적극적으로 사용할 것이다.)</t>
+        </is>
+      </c>
+      <c r="O983" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>983</v>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>백충현</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>생성형 AI 활용 영상 광고에서 AI 활용 표기 여부가 소비자 광고 태도에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>고려대학교 대학원 미디어학과 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>정보원 공신력 이론, 설득지식모델(PKM), 효과의 위계 모델</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>[생성형 AI 활용 표기 조건 / 정서적 반응] -&gt; [정보원 공신력 및 메시지 공신력(매개/조절)] -&gt; [광고 태도 -&gt; 브랜드 태도 -&gt; 구매 의도]</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>H1: 생성형 AI에 대해 긍정적 혹은 부정적 정서는 광고 태도에 영향을 미칠 것이다.
+H1-1: 생성형 AI에 대해 긍정적 정서는 광고 태도에 긍정적 영향을 미칠 것이다.
+H1-2: 생성형 AI에 대해 부정적 정서는 광고 태도에 부정적 영향을 미칠 것이다.
+H2: 생성형 AI 활용 광고 영상에 AI 활용 표기가 있는 경우, 없는 경우에 비해 소비자의 광고 태도가 더 부정적일 것이다.
+H3: 생성형 AI 활용 광고 영상에서 AI 활용 표기의 위치(전반 vs. 후반)는 전반에 위치할 경우 소비자의 광고 태도 평가에 더 긍정적인 영향을 미칠 것이다.
+H4: 정보원 공신력은 생성형 AI 활용 광고 영상의 생성형 AI 활용 표기 조건과 광고 태도에 미치는 영향을 조절할 것이다.
+H5: 정보원 공신력은 생성형 AI에 대한 긍정적 혹은 부정적 정서가 광고 태도에 미치는 영향을 조절할 것이다.</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>생성형 AI 활용 표기 조건 (없음, 전반, 후반), 생성형 AI에 대한 정서적 반응</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>광고 태도 (전반적 광고 태도, 광고 인지, 감성적 반응)</t>
+        </is>
+      </c>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>메시지 공신력</t>
+        </is>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>정보원 공신력 (전문성, 신뢰성)</t>
+        </is>
+      </c>
+      <c r="M984" t="inlineStr">
+        <is>
+          <t>생성형 AI 활용 표기 위치의 직접적 효과는 유의하지 않았으나, 정보원 공신력의 조절효과를 통해 표기 위치와 광고 태도의 상호작용이 확인됨. 정보원 공신력의 신뢰성과 전문성이 긍정적 정서와 결합될 때 광고 태도가 유의미하게 개선되었으며, 부정적 정서와 결합된 경우에도 부정적 영향을 완화하는 경향을 보임.</t>
+        </is>
+      </c>
+      <c r="N984" t="inlineStr">
+        <is>
+          <t>- Generative AI will make the world a better place.
+(생성형 AI는 세상을 더 나은 곳으로 만들 것이다.)
+- I want to use technology based on generative AI.
+(나는 생성형 AI에 기반으로 하는 기술을 사용하고 싶다.)
+- I look forward to the future development of generative AI.
+(향후 생성형 AI의 발전을 기대한다.)
+- Generative AI provides solutions to many world problems.
+(생성형 AI는 많은 세계 문제에 대한 해결책을 제공한다.)
+- I would choose technology with generative AI over technology without generative AI.
+(나는 생성형 AI가 없는 기술보다 생성형 AI가 있는 기술을 선택하겠다.)
+- I generally feel positive emotions when thinking about generative AI.
+(생성형 AI에 대해 생각할 때 대체적으로 긍정적인 감정을 느낀다.)
+- I have strong negative emotions about generative AI.
+(나는 생성형 AI에 대해 강한 부정적 감정을 가지고 있다.)
+- Generative AI has more disadvantages than advantages.
+(생성형 AI는 장점보다 단점이 더 많다.)
+- I prefer technology without generative AI features.
+(나는 생성형 AI 기능이 없는 기술을 선호한다.)
+- I am afraid of generative AI.
+(나는 생성형 AI가 두렵다.)
+- Generative AI creates problems rather than solves them.
+(생성형 AI는 문제를 해결하기보다는 문제를 만든다.)
+- I want to avoid technology based on generative AI.
+(나는 생성형 AI를 기반으로 하는 기술을 피하고 싶다.)
+- I have a favorable attitude toward this advertisement.
+(나는 이 광고에 대해 호의적인 태도를 가지고 있다.)
+- I like this advertisement.
+(나는 이 광고가 마음에 든다.)
+- I think positively of this advertisement.
+(나는 이 광고를 긍정적으로 생각한다.)
+- This advertisement provides useful information.
+(이 광고는 유용한 정보를 제공한다.)
+- This advertisement is entertaining.
+(이 광고는 재미있다.)
+- This advertisement is original.
+(이 광고는 독창적이다.)
+- The production quality of this advertisement is excellent.
+(이 광고의 제작 품질은 우수하다.)
+- I felt joyful emotions while watching this advertisement.
+(이 광고를 보고 즐거운 감정을 느꼈다.)
+- I felt warm emotions while watching this advertisement.
+(이 광고를 보고 따뜻한 감정을 느꼈다.)
+- I felt excited emotions while watching this advertisement.
+(이 광고를 보고 흥분되는 감정을 느꼈다.)
+- I felt relaxed emotions while watching this advertisement.
+(이 광고를 보고 편안한 감정을 느꼈다.)
+- The brand appearing in this advertisement is great.
+(이 광고에서 등장하는 브랜드는 훌륭하다)
+- The brand appearing in this advertisement is attractive.
+(이 광고에서 등장하는 브랜드는 매력적이다.)
+- I want to try the products of the brand appearing in this advertisement.
+(이 광고에서 등장하는 브랜드의 제품을 이용해보고 싶다.)
+- I like the brand appearing in this advertisement.
+(이 광고에서 등장하는 브랜드가 좋다.)
+- I intend to buy the car appearing in this advertisement.
+(나는 이 광고에서 등장하는 자동차를 구매할 의향이 있다)
+- I have purchase interest in the car appearing in this advertisement.
+(나는 이 광고에서 등장하는 자동차에 대해 구매 관심이 있다.)
+- I will definitely buy the car appearing in this advertisement.
+(나는 이 광고에서 등장하는 자동차가 반드시 구매할 것이다.)
+- I will buy the car appearing in this advertisement if I need it.
+(나는 이 광고에서 등장하는 자동차가 필요해질 경우 구매할 것이다.)
+- This advertisement looks accurate.
+(이 광고는 정확해 보인다.)
+- This advertisement looks complete.
+(이 광고는 완전해 보인다.)
+- This advertisement looks intellectual.
+(이 광고는 지성적으로 보인다.)
+- This advertisement feels honest.
+(이 광고는 정직하게 느껴진다.)
+- This advertisement feels reliable.
+(이 광고는 믿을 만하게 느껴진다.)
+- This advertisement is trustworthy.
+(이 광고는 신뢰할 수 있다.)
+- This advertisement is clear.
+(이 광고는 명확하다.)
+- This advertisement is confusing.
+(이 광고는 혼란스럽다.)
+- This advertisement is easy to understand.
+(이 광고는 이해하기 쉽다.)
+- This advertisement is interesting.
+(이 광고는 흥미롭다.)
+- This advertisement draws attention.
+(이 광고는 주의를 집중시킨다.)</t>
+        </is>
+      </c>
+      <c r="O984" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>984</v>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>전세진</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>생성형 챗봇 내 광고 디자인에 대한 사용자 경험 연구</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>홍익대학교 대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>사용자 경험(UX) 이론, 다크패턴(Dark Patterns) 이론, 광고 태도 및 수용도 이론</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>[독립변수: 생성형 챗봇 내 광고 유형 (하단검색형, 태그형, 후속질문형, 배너형)] -&gt; [종속변수: 광고 인지, 지각된 침입성, 불쾌감, 광고 수용도]</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>H1: 생성형 챗봇 내 광고 유형은 광고 인지에 차이를 보일 것이다.
+H2: 생성형 챗봇 내 광고 유형은 지각된 침입성에 차이를 보일 것이다.
+H3: 생성형 챗봇 내 광고 유형은 불쾌감에 차이를 보일 것이다.
+H4: 생성형 챗봇 내 광고 유형은 광고 수용도에 차이를 보일 것이다.</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>생성형 챗봇 내 광고 유형 (하단검색형, 태그형, 후속질문형, 배너형)</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>광고 인지, 지각된 침입성, 불쾌감, 광고 수용도</t>
+        </is>
+      </c>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M985" t="inlineStr">
+        <is>
+          <t>생성형 챗봇 내 광고 유형에 따라 사용자 경험(광고 인지, 지각된 침입성, 불쾌감, 광고 수용도)에서 유의한 차이가 나타났다. 태그형과 후속질문형은 광고 인지가 낮고 불쾌감이 높아 다크패턴의 위험성을 내포하고 있음을 확인하였고, 배너형은 지각된 침입성이 가장 높았다. 반면 하단검색형은 광고와 정보의 비교가 용이하여 가장 높은 광고 수용도를 보였다.</t>
+        </is>
+      </c>
+      <c r="N985" t="inlineStr">
+        <is>
+          <t>- 해당 챗봇이 생성한 응답은 광고가 포함되어 있다.
+(The response generated by the chatbot contains advertising.)
+- 해당 챗봇이 생성한 응답은 광고를 포함해 제공되었다.
+(The response generated by the chatbot was provided including advertising.)
+- 해당 광고는 내가 원하는 정보 탐색에 방해된다.
+(The advertisement interferes with my desired information search.)
+- 해당 광고는 정보를 확인하는데 주의를 분산시킨다.
+(The advertisement distracts my attention when checking information.)
+- 해당 광고는 숨겨져 있다는 느낌이 든다.
+(The advertisement gives a feeling of being hidden.)
+- 해당 광고는 사용자에게 광고를 구분함에 있어 혼동을 준다.
+(The advertisement confuses users in distinguishing advertisements.)
+- 해당 광고를 보면 내용을 확인할 의향이 있다.
+(I have the intention to check the content when seeing the advertisement.)
+- 해당 광고를 본 후 구매 또는 이용할 의향이 있다.
+(I have the intention to purchase or use after seeing the advertisement.)</t>
+        </is>
+      </c>
+      <c r="O985" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>985</v>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>박서연</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>광고디자인을 위한 생성형 기반 프레임워크: AI 광고 영상 제작을 중심으로</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>건국대학교 예술디자인대학원 석사학위 논문</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>디자인씽킹(Design Thinking), 더블 다이아몬드 모델(Double Diamond Model), 멀티모달 생성 모델(Multimodal Generative Models)</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>[기획(Planning)] -&gt; [생성(Generation)] -&gt; [편집(Editing)] 의 3단계 프레임워크 기반 AI 광고 영상 제작 프로세스</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>본 연구는 가설 검정 중심의 실증 논문이 아닌, 생성형 AI 도구를 활용한 광고 영상 제작 프레임워크의 실무적 적용 가능성과 단계별 효과를 탐색적으로 고찰함.</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>생성형 AI 도구 활용 (ChatGPT, Midjourney, SORA, Veo2·3, Suno 등)</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>광고 디자인 제작 효율성, 시각적 일관성, 콘텐츠 완성도 및 플랫폼 맞춤 최적화</t>
+        </is>
+      </c>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M986" t="inlineStr">
+        <is>
+          <t>기획-생성-편집의 3단계 프레임워크를 통해 텍스트, 이미지, 영상, 사운드를 유기적으로 연계함으로써 수작업 대비 제작 시간 단축, 브랜드 일관성 유지, 그리고 멀티모달 자동화의 실무적 강점을 확인하였음. 다만 프롬프트 해석 오류나 환각 현상 등은 전문가의 검수와 후반 조정을 통해 보완되어야 함을 제시함.</t>
+        </is>
+      </c>
+      <c r="N986" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O986" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>986</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>김태형</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>생성형 AI 활용이 광고 평가에 미치는 영향 - 메시지 유형의 조절 효과를 중심으로 -</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>고려대학교 미디어대학원 석사학위논문</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>계산 창의성 이론(Computational Creativity), 광고 소구 이론(이성적 소구 및 감성적 소구)</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>[독립변수: 생성형 AI 활용 여부] x [조절변수: 메시지 소구 유형] -&gt; [종속변수: 광고 평가(광고 태도, 광고 창의성, 광고 신뢰도, 브랜드 태도, 구매 의도)]</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>H1: 생성형 AI의 활용은 광고 평가에 긍정적인 영향을 미칠 것이다.
+H1-1: 생성형 AI가 제작한 광고물은 광고 전문가가 제작한 광고물보다 더 긍정적인 광고 태도를 가질 것이다.
+H1-2: 생성형 AI가 제작한 광고물은 광고 전문가가 제작한 광고물보다 더 긍정적인 광고 창의성을 가질 것이다.
+H1-3: 생성형 AI가 제작한 광고물은 광고 전문가가 제작한 광고물보다 더 긍정적인 광고 신뢰도를 가질 것이다.
+H1-4: 생성형 AI가 제작한 광고물은 광고 전문가가 제작한 광고물보다 더 긍정적인 브랜드 태도를 가질 것이다.
+H1-5: 생성형 AI가 제작한 광고물은 광고 전문가가 제작한 광고물보다 더 긍정적인 구매 의도를 가질 것이다.
+H2: 생성형 AI의 활용과 메시지 소구 유형의 상호작용 효과는 광고 평가에 영향을 미칠 것이다.
+H2-1: 생성형 AI가 제작한 광고와 광고 전문가가 제작한 광고에 따른 광고 태도는 메시지 소구 유형에 따라 다를 것이다.
+H2-2: 생성형 AI가 제작한 광고와 광고 전문가가 제작한 광고에 따른 광고 창의성은 메시지 소구 유형에 따라 다를 것이다.
+H2-3: 생성형 AI가 제작한 광고와 광고 전문가가 제작한 광고에 따른 광고 신뢰도는 메시지 소구 유형에 따라 다를 것이다.
+H2-4: 생성형 AI가 제작한 광고와 광고 전문가가 제작한 광고에 따른 브랜드 태도는 메시지 소구 유형에 따라 다를 것이다.
+H2-5: 생성형 AI가 제작한 광고와 광고 전문가가 제작한 광고에 따른 구매 의도는 메시지 소구 유형에 따라 다를 것이다.</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>생성형 AI 활용 여부 (생성형 AI 제작 vs 광고 전문가 제작)</t>
+        </is>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>광고 평가 (광고 태도, 광고 창의성, 광고 신뢰도, 브랜드 태도, 구매 의도)</t>
+        </is>
+      </c>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>메시지 소구 유형 (이성적 소구 vs 감성적 소구)</t>
+        </is>
+      </c>
+      <c r="M987" t="inlineStr">
+        <is>
+          <t>1. 생성형 AI를 활용한 광고는 광고 전문가가 제작한 광고에 비해 소비자로부터 통계적으로 유의미하게 더 높은 '광고 창의성' 평가와 '구매 의도'를 끌어내는 것으로 나타났다.
+2. 생성형 AI 활용 여부는 '광고 태도', '광고 신뢰도', '브랜드 태도'에는 유의미한 주효과를 미치지 않았다.
+3. 생성형 AI 활용 여부와 메시지 소구 유형(이성적/감성적 소구) 간의 상호작용 효과는 모든 종속변인(광고 태도, 광고 창의성, 광고 신뢰도, 브랜드 태도, 구매 의도)에서 통계적으로 유의미하지 않게 나타났다.</t>
+        </is>
+      </c>
+      <c r="N987" t="inlineStr">
+        <is>
+          <t>[광고 태도 / Attitude toward the Ad]
+- I like this advertisement.
+(나는 이 광고에 호감이 간다)
+- I find this advertisement impressive.
+(나는 이 광고가 인상적이다)
+- I find this advertisement persuasive.
+(나는 이 광고가 설득력이 있다)
+- I can trust this advertisement.
+(나는 이 광고를 신뢰할 수 있다)
+- I think this advertisement is more impressive than advertisements for other products.
+(나는 이 광고가 타제품 광고보다 인상적이라고 생각한다)
+- After viewing this advertisement, I developed a good feeling about the product.
+(나는 이 광고를 보고 제품에 대해 좋은 느낌을 가지게 되었다)
+[광고 창의성 / Advertising Creativity]
+- This advertisement is novel.
+(이 광고는 새롭다)
+- This advertisement is fresh.
+(이 광고는 신선하다)
+- This advertisement is original.
+(이 광고는 독창적이다)
+- I think this advertisement breaks away from the existing framework.
+(이 광고는 기존의 틀에서 벗어난다고 생각한다)
+[광고 신뢰도 / Advertising Credibility]
+- I trust this advertisement.
+(나는 이 광고에 신뢰가 간다)
+- I have belief in this advertisement.
+(나는 이 광고에 믿음이 간다)
+- This advertisement is unbiased.
+(이 광고는 편파적이지 않다)
+- This advertisement is professional.
+(이 광고는 전문적이다)
+[브랜드 태도 / Brand Attitude]
+- This brand is wonderful.
+(이 브랜드는 훌륭하다)
+- I find this brand interesting.
+(나는 이 브랜드가 흥미롭다)
+- To me, this brand is appealing.
+(나에게 이 브랜드는 매력적이다)
+- I would like to try using products from this brand.
+(나는 이 브랜드의 제품을 사용해보고 싶다)
+- I like this brand.
+(나는 이 브랜드가 좋다)
+[구매 의도 / Purchase Intention]
+- I will purchase these running shoes.
+(나는 이 런닝화를 구매할 것이다)
+- I intend to purchase these running shoes.
+(나는 이 런닝화를 구매할 의향이 있다)
+- I intend to search for information about these running shoes.
+(나는 이 런닝화에 대한 정보를 검색할 의향이 있다)
+- I want to use these running shoes.
+(나는 이 런닝화를 이용하고 싶다)
+- I will recommend the product shown in this advertisement to others.
+(나는 이 광고에 나온 제품을 다른 사람들에게 추천할 것이다)</t>
+        </is>
+      </c>
+      <c r="O987" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>987</v>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>김나경 (지도교수: 고한준)</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>맞춤형 OOH 광고 효과에 영향을 미치는 요인에 관한 연구 - 유형별 측정척도개발을 중심으로 -</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>국민대학교 일반대학원 언론정보학과 광고홍보학전공 박사학위논문</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>기술수용모델(TAM), 웹광고태도모델, 프라이버시계산모델, 인게이지먼트 이론</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>[개인인식형/사물인식형/상황인식형 구성요인] -&gt; [광고태도, 구매의도, 수용의도]</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>H1: 개인인식형 맞춤형 OOH 광고의 주요 구성요인은 광고효과(광고태도, 구매의도, 수용의도)에 유의한 영향을 미칠 것이다.
+H2: 사물인식형 맞춤형 OOH 광고의 주요 구성요인은 광고효과(광고태도, 구매의도, 수용의도)에 유의한 영향을 미칠 것이다.
+H3: 상황인식형 맞춤형 OOH 광고의 주요 구성요인은 광고효과(광고태도, 구매의도, 수용의도)에 유의한 영향을 미칠 것이다.</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>맞춤형 OOH 광고 유형별 구성요인 (인게이지먼트, 개인맞춤화, 프라이버시 염려, 정확신뢰, 맥락적시, 편익혜택, 가치유용, 이용편의, 정보유용 등)</t>
+        </is>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>광고효과 (광고태도, 구매의도, 수용의도)</t>
+        </is>
+      </c>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M988" t="inlineStr">
+        <is>
+          <t>맞춤형 OOH 광고를 개인인식형, 사물인식형, 상황인식형으로 구분하여 측정한 결과, 세 유형의 공통적 구성요인으로 인게이지먼트, 개인맞춤화, 프라이버시 염려가 도출되었다. 광고태도에는 세 유형 모두 인게이지먼트가 긍정적 영향을, 프라이버시가 부정적 영향을 미치는 것으로 나타났다. 구매의도 및 수용의도에서는 프라이버시 염려가 유의한 영향을 미치지 않는 것으로 나타났으며, 개인맞춤화 수준이 일정 수준보다 높아지면 역U자형의 효과가 나타남을 확인하였다.</t>
+        </is>
+      </c>
+      <c r="N988" t="inlineStr">
+        <is>
+          <t>- Personalized OOH advertising provides the information I need.
+(맞춤형 OOH 광고는 내가 필요로 하는 정보를 제공한다)
+- Personalized OOH advertising provides recommendations tailored to my needs.
+(맞춤형 OOH 광고는 나의 필요에 맞는 추천을 해준다)
+- Personalized OOH advertising provides customized advertisements for me.
+(맞춤형 OOH 광고는 내게 맞춤화된 광고를 제공한다)
+- Personalized OOH advertising provides advertisements tailored to my situation.
+(맞춤형 OOH 광고는 나의 상황에 맞춰진 광고를 제공한다)
+- Personalized OOH advertising provides advertisements tailored to my requests.
+(맞춤형 OOH 광고는 내 요구에 맞는 광고를 제공한다)
+- Personalized OOH advertising content is provided immediately.
+(맞춤형 OOH 광고는 내용이 즉각적으로 제공된다)
+- Content or information is reflected promptly in personalized OOH advertising.
+(맞춤형 OOH 광고는 콘텐츠나 정보가 신속하게 반영된다)
+- Content is continuously reflected in personalized OOH advertising.
+(맞춤형 OOH 광고는 콘텐츠가 지속적으로 반영된다)
+- Personalized OOH advertising allows receiving information through the latest technology.
+(맞춤형 OOH 광고를 통해 최신기술 정보를 제공 받을 수 있다)
+- I sympathize with the content of personalized OOH advertising.
+(맞춤형 OOH 광고의 내용에 공감한다)
+- I sympathize with the experience of the model shown in personalized OOH advertising.
+(맞춤형 OOH 광고에 나온 모델의 경험에 공감한다)
+- I can feel an indirect experience through personalized OOH advertising.
+(맞춤형 OOH 광고를 통해 간접적인 경험을 느낀다)
+- I feel interaction in personalized OOH advertising.
+(맞춤형 OOH 광고에서 상호작용을 느낀다)
+- I get a feeling of communicating with personalized OOH advertising.
+(맞춤형 OOH 광고와 소통하는 느낌을 받는다)
+- The content of personalized OOH advertising is trustworthy.
+(맞춤형 OOH 광고의 콘텐츠가 믿을만하다)
+- Personalized OOH advertising allows getting non-calculative information.
+(맞춤형 OOH 광고는 이해타산적이지 않은 정보를 얻을 수 있다)
+- Personalized OOH advertising is reliable.
+(맞춤형 OOH 광고는 신뢰할 수 있다)
+- Personalized OOH advertising is honest.
+(맞춤형 OOH 광고는 정직하다)
+- Personalized OOH advertising is bothersome.
+(맞춤형 OOH 광고는 불편하다)
+- Personalized OOH advertising is intrusive.
+(맞춤형 OOH 광고는 거슬린다)
+- Personalized OOH advertising is confusing.
+(맞춤형 OOH 광고는 혼란스럽다)
+- Personalized OOH advertising has too much content.
+(맞춤형 OOH 광고는 내용가 너무 많다)
+- Personalized OOH advertising is complex.
+(맞춤형 OOH 광고는 복잡하다)
+- Personalized OOH advertising annoys me.
+(맞춤형 OOH 광고는 나를 귀찮게 한다)
+- Personalized OOH advertising is enjoyable.
+(맞춤형 OOH 광고는 즐겁다)
+- Personalized OOH advertising is interesting.
+(맞춤형 OOH 광고는 흥미롭다)
+- Personalized OOH advertising is fun.
+(맞춤형 OOH 광고는 재미있다)
+- Personalized OOH advertising is entertaining.
+(맞춤형 OOH 광고는 오락적이다)
+- Personalized OOH advertising is pleasant.
+(맞춤형 OOH 광고는 유쾌하다)
+- Personalized OOH advertising includes important product contents.
+(맞춤형 OOH 광고는 제품의 중요내용을 포함한다)
+- Personalized OOH advertising provides recent information.
+(맞춤형 OOH 광고는 최근정보를 제공해 준다)
+- Personalized OOH advertising provides relevant product information.
+(맞춤형 OOH 광고는 제품의 관련 정보를 제공해 준다)
+- Personalized OOH advertising delivers sources of product information.
+(맞춤형 OOH 광고는 제품정보의 원천을 전달한다)
+- Personalized OOH advertising provides information when consumers want it.
+(맞춤형 OOH 광고는 소비자가 원할 때 정보 제공한다)
+- Personalized OOH advertising is a good information source.
+(맞춤형 OOH 광고는 좋은 정보원이다)
+- Personalized OOH advertising provides complete product information.
+(맞춤형 OOH 광고는 완벽한 제품정보를 제공한다)
+- The content of personalized OOH advertising is important.
+(맞춤형 OOH 광고는 내용이 중요하다)
+- Personalized OOH advertising is useful to me.
+(맞춤형 OOH 광고는 내게 유용하다)
+- Personalized OOH advertising has value to me.
+(맞춤형 OOH 광고는 내게 가치가 있다)
+- I like personalized OOH advertising.
+(맞춤형 OOH 광고를 좋아한다)
+- I feel like I am participating in personalized OOH advertising.
+(맞춤형 OOH 광고는 참여하고 있다는 느낌이 든다)
+- Personalized OOH advertising increases concentration.
+(맞춤형 OOH 광고는 집중도를 높여준다)
+- Personalized OOH advertising is attractive and induces participation.
+(맞춤형 OOH 광고는 매력적이라 참여를 유발한다)
+- Personalized OOH advertising is available anytime.
+(맞춤형 OOH 광고는 언제나 이용이 가능하다)
+- Personalized OOH advertising is available regardless of location.
+(맞춤형 OOH 광고는 장소에 상관없이 이용이 가능하다)
+- Personalized OOH advertising is easy to access.
+(맞춤형 OOH 광고는 접근이 용이하다)
+- Personalized OOH advertising gives various information.
+(맞춤형 OOH 광고는 다양한 정보를 준다)
+- Personalized OOH advertising gives appropriate information.
+(맞춤형 OOH 광고는 적합한 정보를 준다)
+- Personalized OOH advertising is very useful.
+(맞춤형 OOH 광고는 매우 유용하다)
+- The advertisement of personalized OOH advertising helps me get the information I want.
+(맞춤형 OOH 광고의 광고는 내가 얻고자 하는 정보를 얻는데 도움이 된다)
+- Anyone can easily use personalized OOH advertising.
+(맞춤형 OOH 광고는 누구나 쉽게 이용 할 수있다)
+- Personalized OOH advertising is convenient to use.
+(맞춤형 OOH 광고는 이용이 편리하다)
+- Personalized OOH advertising is trustworthy.
+(맞춤형 OOH 광고는 신뢰할만하다)
+- Personalized OOH advertising is certain.
+(맞춤형 OOH 광고는 확실하다)
+- Personalized OOH advertising is reliable.
+(맞춤형 OOH 광고는 믿을만하다)
+- Personalized OOH advertising is truthful.
+(맞춤형 OOH 광고는 진실되다)
+- Personalized OOH advertising is not fraudulent.
+(맞춤형 OOH 광고는 사기성이 없다)
+- I tend to believe personalized OOH advertising.
+(맞춤형 OOH 광고를 믿는 편이다)
+- Personalized OOH advertising safely protects personal information.
+(맞춤형 OOH 광고는 개인정보를 안전하게 보호한다)
+- Providing personal information to personalized OOH advertising is reassuring.
+(맞춤형 OOH 광고에 개인정보 제공은 안심된다)
+- There is no risk of personal information leakage in personalized OOH advertising.
+(맞춤형 OOH 광고는 개인정보 유출 위험이 없다)
+- Personalized OOH advertising is reassuring.
+(맞춤형 OOH 광고는 안심된다)
+- Personalized OOH advertising provides compensation.
+(맞춤형 OOH 광고는 보상을 제공한다)
+- Personalized OOH advertising provides tangible benefits.
+(맞춤형 OOH 광고는 유형적 혜택을 제공한다)
+- Personalized OOH advertising provides incentives.
+(맞춤형 OOH 광고는 인센티브를 제공한다)
+- Personalized OOH advertising is satisfying.
+(맞춤형 OOH 광고는 만족스럽다)
+- I am overall satisfied with personalized OOH advertising services.
+(맞춤형 OOH 광고 서비스에 대해 전반적으로 만족한다)
+- I evaluate personalized OOH advertising positively.
+(맞춤형 OOH 광고에 대해 긍정적으로 평가한다)
+- Personalized OOH advertising has few information errors.
+(맞춤형 OOH 광고는 정보의 오류가 적다)
+- The content of information in personalized OOH advertising is very accurate.
+(맞춤형 OOH 광고는 정보의 내용이 매우 정확하다)
+- I can know the information of personalized OOH advertising very accurately.
+(맞춤형 OOH 광고는 정보를 매우 정확하게 알수있다)
+- Personalized OOH advertising seems to track information about me.
+(맞춤형 OOH 광고는 나에 대한 정보를 추적하는 것 같다)
+- Personalized OOH advertising has too much information about me.
+(맞춤형 OOH 광고는 나에 대한 정보를 너무 많이 가지고 있다)
+- Personalized OOH advertising seems to access information about me.
+(맞춤형 OOH 광고는 나에 대한 정보에 접근하는 것 같다)
+- I am worried that my information might be used unexpectedly in personalized OOH advertising.
+(맞춤형 OOH 광고에 내 정보가 예상치 못하게 사용될까 걱정된다)
+- Personalized OOH advertising entails risks to personal information.
+(맞춤형 OOH 광고는 개인정보에 위험이 수반된다)
+- Personalized OOH advertising can cause personal information-related problems.
+(맞춤형 OOH 광고는 개인정보 관련 문제를 발생시킬 수 있다)
+- Personalized OOH advertising has a lot of uncertainties.
+(맞춤형 OOH 광고는 불확실성이 많다)
+- Personalized OOH advertising will cause a loss to my privacy.
+(맞춤형 OOH 광고는 나의 사생활에 손실을 입힐것이다)
+- Personalized OOH advertising is not safe for privacy.
+(맞춤형 OOH 광고는 프라이버시에 안전하지 못하다)
+- Personalized OOH advertising protects personal information.
+(맞춤형 OOH 광고는 개인정보를 보호한다고 생각한다)
+- Personalized OOH advertising safely manages my personal information.
+(맞춤형 OOH 광고는 내 개인정보를 안전하게 관리한다)
+- The privacy protection policy of personalized OOH advertising protects privacy.
+(맞춤형 OOH 광고의 개인보호정책은 프라이버시를 보호한다)
+- Personalized OOH advertising is reliable in terms of personal information protection.
+(맞춤형 OOH 광고는 개인정보보호 측면에서 믿을 수 있다)
+- Personalized OOH advertising is convenient to announce what I am working on.
+(맞춤형 OOH 광고는 내가 진행중인 일을 알리기에 편리하다)
+- Personalized OOH advertising can save time when I want to share.
+(맞춤형 OOH 광고는 공유하고싶을때 시간을 절약할 수있다)
+- Personalized OOH advertising is efficient for sharing information with friends.
+(맞춤형 OOH 광고는 친구들과 정보 공유에 효율적이다)
+- Personalized OOH advertising is helpful.
+(맞춤형 OOH 광고는 도움이된다)
+- The benefit of personalized OOH advertising is large compared to effort.
+(맞춤형 OOH 광고는 노력대비 이익이 크다)
+- The benefit of personalized OOH advertising is large compared to time.
+(맞춤형 OOH 광고는 시간대비 이익이크다)
+- Personalized OOH advertising will bring many benefits.
+(맞춤형 OOH 광고는 많은이익을 가져다줄것이다)
+- Personalized OOH advertising becomes an object of enjoyment.
+(맞춤형 OOH 광고는 즐거움의 대상이 된다)
+- Personalized OOH advertising makes me want to use it.
+(맞춤형 OOH 광고는 이용하고 싶은 욕구를 갖게 한다)
+- Personalized OOH advertising gives a sense of security.
+(맞춤형 OOH 광고는 안정감을 준다)
+- Personalized OOH advertising gives enjoyment.
+(맞춤형 OOH 광고는 즐거움을 준다)
+- Personalized OOH advertising can enhance my fame (recognition).
+(맞춤형 OOH 광고로 나의 명성(인정)을 높일 수 있다)
+- I can show off myself through personalized OOH advertising.
+(맞춤형 OOH 광고로 나를 과시할 수 있다)
+- My image can be positively reinforced through personalized OOH advertising.
+(맞춤형 OOH 광고로 나의 이미지를 긍정적으로 강화할 수 있다)
+- Personalized OOH advertising can give a good impression.
+(맞춤형 OOH 광고로 좋은 인상을 줄수있다)
+- Personalized OOH advertising provides appropriate information according to the situation.
+(맞춤형 OOH 광고는 상황에 맞는 적절한 정보를 한다)
+- Personalized OOH advertising provides information matching interests or preferences.
+(맞춤형 OOH 광고는 관심이나 선호도에 맞는 정보를 제공한다)
+- Personalized OOH advertising provides convenience in accessing desired information.
+(맞춤형 OOH 광고는 원하는 정보 접근에 편리함을 제공한다)
+- Personalized OOH advertising provides information on products in a timely manner.
+(맞춤형 OOH 광고는 제품에 대한 정보를 적시에 제공한다)
+- Personalized OOH advertising reflects recent online behavioral information.
+(맞춤형 OOH 광고는 최근 온라인 행태 정보를 반영하여 제공된다)
+- Personalized OOH advertising reflects my current situation.
+(맞춤형 OOH 광고는 현재 나의 상황을 반영한다)
+- Personalized OOH advertising considers interaction with real-time information important.
+(맞춤형 OOH 광고는 실시간 정보와의 상호작용을 중요시한다)
+- Personalized OOH advertising stands out well.
+(맞춤형 OOH 광고는 눈에 잘 띄었다)
+- The advertisement of personalized OOH advertising caught my eye.
+(맞춤형 OOH 광고의 광고는 나의 눈길을 잡아끌었다)
+- The advertisement of personalized OOH advertising is easy to find.
+(맞춤형 OOH 광고의 광고는 쉽게 찾을 수 있다)
+- The advertisement of personalized OOH advertising is visible from a distance.
+(맞춤형 OOH 광고의 광고는 멀리서도 잘 보였다)
+- Advertising through personalized OOH advertising is special.
+(맞춤형 OOH 광고를 통한 광고는 특별하다)
+- The time using personalized OOH advertising is enjoyable.
+(맞춤형 OOH 광고를 이용하는 시간은 즐겁다)
+- I have an emotional connection with personalized OOH advertising.
+(맞춤형 OOH 광고와 감정적인 연결감을 갖고 있다)
+- Personalized OOH advertising provides me with some motivation or stimulation.
+(맞춤형 OOH 광고는 내게 어떤 계기나 자극을 제공한다)
+- The time doing personalized OOH advertising is considered 'time for me'.
+(맞춤형 OOH 광고를 하는 시간은 ‘나를 위한 시간’으로 생각된다)
+- Personalized OOH advertising provides things that help my decision-making.
+(맞춤형 OOH 광고는 나의 의사결정에 도움이 되는 것들을 제공한다)
+- I think sincere communication takes place in personalized OOH advertising.
+(맞춤형 OOH 광고에서 진실한 커뮤니케이션이 이루어진다고 생각한다)
+- I cannot do other things while doing personalized OOH advertising.
+(맞춤형 OOH 광고를 하는 동안 다른 일을 할 수 없다)
+- I cannot do other behaviors while using personalized OOH advertising.
+(맞춤형 OOH 광고를 사용하는 동안은 다른 행동을 하지 않는다)
+- I cannot leave my seat while using personalized OOH advertising.
+(맞춤형 OOH 광고를 사용하는 중에는 자리를 비울 수 없다)
+- I can share information with people through personalized OOH advertising.
+(맞춤형 OOH 광고를 통해 사람들과 정보를 공유할 수 있다)
+- Personalized OOH advertising tells me how to communicate with people.
+(맞춤형 OOH 광고는 사람들과 소통방법을 알려준다)
+- Personalized OOH advertising tells me how to solve problems.
+(맞춤형 OOH 광고는 문제 해결 방법을 알려준다)
+- Personalized OOH advertising allows me to relate to other people.
+(맞춤형 OOH 광고는 다른 사람들과 관계를 맺게 해준다)
+- Personalized OOH advertising provides conversation topics.
+(맞춤형 OOH 광고는 대화의 주제를 제공한다)
+- Personalized OOH advertising allows me to understand other people's opinions.
+(맞춤형 OOH 광고는 사람들의 의견을 이해할 수 있게 해준다)
+- Personalized OOH advertising is relevant to me.
+(맞춤형 OOH 광고는 나와 관련이 있다)
+- Personalized OOH advertising is indispensable to me.
+(맞춤형 OOH 광고는 내게 없어서는 안된다)
+- Personalized OOH advertising is definitely needed for me now.
+(맞춤형 OOH 광고는 내게 지금 꼭 필요하다)
+- Personalized OOH advertising arouses my passion.
+(맞춤형 OOH 광고는 나의 열정을 불러일으킨다)
+- I feel vigorous when looking at personalized OOH advertising.
+(맞춤형 OOH 광고를 볼 때, 원기 왕성함을 느낀다)
+- Personalized OOH advertising is passionate.
+(맞춤형 OOH 광고는 열정적이다)
+- I feel overflowing energy from personalized OOH advertising.
+(맞춤형 OOH 광고는 힘이 넘침을 느낀다)
+- I feel happiness when concentrating on personalized OOH advertising.
+(맞춤형 OOH 광고에 집중할 때, 행복감을 느낀다)
+- I use personalized OOH advertising for a long time.
+(맞춤형 OOH 광고를 장시간 이용한다)
+- I want to check personalized OOH advertising when I wake up in the morning.
+(맞춤형 OOH 광고를 아침에 일어났을 때 확인하고 싶다)
+- I am deeply immersed in personalized OOH advertising.
+(맞춤형 OOH 광고에 푹 빠져있다)
+- I often lose track of time while watching personalized OOH advertising.
+(맞춤형 OOH 광고를 보면서 시간 가는 줄 모르는 때가 자주 있다)
+- I do not do other behaviors while using personalized OOH advertising.
+(맞춤형 OOH 광고를 사용하는 동안 다른 행동을 하지 않는다)
+- I feel proud/confident in using personalized OOH advertising.
+(맞춤형 OOH 광고 이용에 뿌듯한/자부심을 느낀다)
+- Personalized OOH advertising is very fun.
+(맞춤형 OOH 광고가 매우 재미있다)
+- Personalized OOH advertising provides things to talk about with friends and family.
+(맞춤형 OOH 광고는 대화 주제를 제공해준다)
+- The time using personalized OOH advertising is enjoyable.
+(맞춤형 OOH 광고를 이용하는 시간이 즐겁다)
+- Personalized OOH advertising helps my decision-making.
+(맞춤형 OOH 광고는 나의 의사결정에 도움이된다)
+- Personalized OOH advertising is a message containing a specific ideological phenomenon.
+(맞춤형 OOH 광고는 특정 이데올로기적 현상을 담은 메시지이다)
+- The content of personalized OOH advertising creates meaning in a narrative structure.
+(맞춤형 OOH 광고의 내용이 이야기 구조에 라 의미를 생성한다)
+- Personalized OOH advertising gives an experience created by psychological cognitive processes.
+(맞춤형 OOH 광고를 통해 심리적 인식과정에 의해 창조되는 경험을 준다)
+- Personalized OOH advertising made me enthusiastic.
+(맞춤형 OOH 광고는 나를 열광적으로 만들었다)
+- Personalized OOH advertising discovered me.
+(맞춤형 OOH 광고는 나를 발견했다)
+- Personalized OOH advertising is original and unique.
+(맞춤형 OOH 광고는 독창적이고 독특하다)
+- Personalized OOH advertising kept telling me new trends.
+(맞춤형 OOH 광고는 새로운 동향을 계속 알려 주었다)
+- Personalized OOH advertising suggested something new to me.
+(맞춤형 OOH 광고는 내게 새로운 것을 제안했다)
+- I got to know myself through personalized OOH advertising.
+(맞춤형 OOH 광고를 통해 나 자신을 알게 되었다)
+- I sympathize with the content through personalized OOH advertising.
+(맞춤형 OOH 광고를 통해 내용을 공감한다)
+- I can clearly express my own views through personalized OOH advertising.
+(맞춤형 OOH 광고를 통해 나 자신의 견해를 확실히 표현할 수 있다)
+- Personalized OOH advertising provided useful ideas.
+(맞춤형 OOH 광고는 유용한 아이디어를 제공했다)
+- Personalized OOH advertising induced me to find more information.
+(맞춤형 OOH 광고는 더 많은 정보를 찾도록 유도했다)
+- Personalized OOH advertising taught me how to solve problems.
+(맞춤형 OOH 광고는 어떻게 문제를 해결할 것인지를 알려 주었다)
+- Personalized OOH advertising gave reliable information.
+(맞춤형 OOH 광고는 믿을 만한 정보를 주었다)
+- Personalized OOH advertising gave me an opportunity to encounter fresh objects.
+(맞춤형 OOH 광고는 신선한 사물을 접할 수 있는 기회를 주었다)
+- I lead other people through personalized OOH advertising.
+(맞춤형 OOH 광고를 통해 다른 사람을 리드한다)
+- Personalized OOH advertising makes other people like and respect me.
+(맞춤형 OOH 광고는 다른 사람들이 나를 좋아하고 존경하게한다)
+- Personalized OOH advertising informs information promptly.
+(맞춤형 OOH 광고는 정보를 신속하게 알려준다)
+- Personalized OOH advertising gives the latest information.
+(맞춤형 OOH 광고는 최신의 정보를 준다)
+- Personalized OOH advertising gives me useful information.
+(맞춤형 OOH 광고는내게 유용한 정보를 준다)
+- I can help other people through personalized OOH advertising.
+(맞춤형 OOH 광고를 통해 다른 사람들을 도울 수 있다)
+- Personalized OOH advertising makes me influential to others.
+(맞춤형 OOH 광고는 나를 다른 사람들에게 영향력이 있게 한다)
+- Personalized OOH advertising interrupted me.
+(맞춤형 OOH 광고는 나를 방해했다)
+- Personalized OOH advertising bothered me.
+(맞춤형 OOH 광고는 나를 귀찮게 했다)
+- Personalized OOH advertising is somewhat unclear.
+(맞춤형 OOH 광고는 다소 불분명하다)
+- I will inform other people of personalized OOH advertising.
+(맞춤형 OOH 광고를 다른사람에게 알릴 것이다)
+- I will post on SNS about personalized OOH advertising.
+(맞춤형 OOH 광고에 대해 SNS에 글을 올릴 것이다)
+- I will talk via SNS about personalized OOH advertising.
+(맞춤형 OOH 광고에 대해 SNS로 대화할것이다)
+- I will let other people know about personalized OOH advertising.
+(맞춤형 OOH 광고를 다른 사람에게 알려줄 것이다)
+- I want to recommend personalized OOH advertising to others.
+(맞춤형 OOH 광고를 다른 사람에게 추천하고 싶다)
+- I want to recommend the content seen in personalized OOH advertising to others.
+(맞춤형 OOH 광고에서 본 내용에 대해 추천하고 싶다)
+- I want to talk to acquaintances about the content seen in personalized OOH advertising.
+(맞춤형 OOH 광고에서 본 내용에 대해 지인에게 이야기 하고 싶다)
+- Personalized OOH advertising is not important to me.
+(맞춤형 OOH 광고는 내게 중요하지 않다)
+- Personalized OOH advertising is important to me.
+(맞춤형 OOH 광고는 내게 중요하다)
+- Personalized OOH advertising is meaningless to me.
+(맞춤형 OOH 광고는 내게 무의미하다)
+- Personalized OOH advertising is meaningful to me.
+(맞춤형 OOH 광고는 내게 의미 있다)
+- Personalized OOH advertising has nothing to do with me.
+(맞춤형 OOH 광고는 나와 관련 없다)
+- Personalized OOH advertising has to do with me.
+(맞춤형 OOH 광고는 나와 관련 있다)
+- Personalized OOH advertising provides appropriate information according to my location situation.
+(맞춤형 OOH 광고는 위치 상황에 맞게 적절한 정보를 제공한다)
+- Personalized OOH advertising provides information at an appropriate time to use.
+(맞춤형 OOH 광고는 이용하기 적절한 시간에 정보를 제공한다)
+- Personalized OOH advertising provides necessary information according to the optimal situation.
+(맞춤형 OOH 광고는 필요한 정보를 최적의 상황에 맞게 제공한다)
+- The message presented in personalized OOH advertising touches me.
+(맞춤형 OOH 광고에서 제시된 메시지는 내게 감동을 준다)
+- The message presented in personalized OOH advertising makes me feel good.
+(맞춤형 OOH 광고에서 제시된 메시지는 나를 기분 좋게한다)
+- The message presented in personalized OOH advertising comes to me impressively.
+(맞춤형 OOH 광고에서 제시된 메시지는 내게 인상적으로 다가온다)
+- It is easy to understand the product features of this advertisement.
+(맞춤형 OOH 광고의 제품 특징을 이해하기 쉽다)</t>
+        </is>
+      </c>
+      <c r="O988" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
